--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A1_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A1_session_analysis.xlsx
@@ -589,45 +589,45 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>A1-A1</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>17/05/2026</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr"/>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>0/34</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>0/34</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
       <c r="K3" s="1" t="inlineStr">
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="L7" s="5" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8">
@@ -893,7 +893,7 @@
         </is>
       </c>
       <c r="L8" s="5" t="n">
-        <v>318</v>
+        <v>312</v>
       </c>
     </row>
     <row r="9">
@@ -1286,10 +1286,10 @@
         <v>0</v>
       </c>
       <c r="P15" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q15" s="5" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="R15" s="5" t="inlineStr">
         <is>
@@ -1364,10 +1364,10 @@
         <v>0</v>
       </c>
       <c r="P16" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q16" s="5" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="R16" s="5" t="inlineStr">
         <is>
@@ -1442,10 +1442,10 @@
         <v>0</v>
       </c>
       <c r="P17" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q17" s="5" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="R17" s="5" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         <v>0</v>
       </c>
       <c r="P18" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q18" s="5" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="R18" s="5" t="inlineStr">
         <is>
@@ -1598,10 +1598,10 @@
         <v>0</v>
       </c>
       <c r="P19" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q19" s="5" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="R19" s="5" t="inlineStr">
         <is>
@@ -1676,10 +1676,10 @@
         <v>0</v>
       </c>
       <c r="P20" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q20" s="5" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="R20" s="5" t="inlineStr">
         <is>
@@ -2295,45 +2295,45 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="4" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B30" s="4" t="inlineStr">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>A1-A2</t>
         </is>
       </c>
-      <c r="C30" s="4" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D30" s="4" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E30" s="4" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>17/05/2026</t>
         </is>
       </c>
-      <c r="F30" s="4" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G30" s="4" t="inlineStr"/>
-      <c r="H30" s="4" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>0/33</t>
         </is>
       </c>
-      <c r="I30" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
       <c r="K30" s="1" t="inlineStr">
@@ -3516,45 +3516,45 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="4" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B57" s="4" t="inlineStr">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
         <is>
           <t>A1-B1</t>
         </is>
       </c>
-      <c r="C57" s="4" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D57" s="4" t="inlineStr">
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E57" s="4" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>17/05/2026</t>
         </is>
       </c>
-      <c r="F57" s="4" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G57" s="4" t="inlineStr"/>
-      <c r="H57" s="4" t="inlineStr">
-        <is>
-          <t>0/34</t>
-        </is>
-      </c>
-      <c r="I57" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr"/>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>0/34</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -4677,45 +4677,45 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="4" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B84" s="4" t="inlineStr">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
         <is>
           <t>A1-B2</t>
         </is>
       </c>
-      <c r="C84" s="4" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D84" s="4" t="inlineStr">
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E84" s="4" t="inlineStr">
+      <c r="E84" s="2" t="inlineStr">
         <is>
           <t>17/05/2026</t>
         </is>
       </c>
-      <c r="F84" s="4" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G84" s="4" t="inlineStr"/>
-      <c r="H84" s="4" t="inlineStr">
-        <is>
-          <t>0/34</t>
-        </is>
-      </c>
-      <c r="I84" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr"/>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>0/34</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -5838,45 +5838,45 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="4" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B111" s="4" t="inlineStr">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
         <is>
           <t>A1-C1</t>
         </is>
       </c>
-      <c r="C111" s="4" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D111" s="4" t="inlineStr">
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E111" s="4" t="inlineStr">
+      <c r="E111" s="2" t="inlineStr">
         <is>
           <t>17/05/2026</t>
         </is>
       </c>
-      <c r="F111" s="4" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G111" s="4" t="inlineStr"/>
-      <c r="H111" s="4" t="inlineStr">
-        <is>
-          <t>0/34</t>
-        </is>
-      </c>
-      <c r="I111" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G111" s="2" t="inlineStr"/>
+      <c r="H111" s="2" t="inlineStr">
+        <is>
+          <t>0/34</t>
+        </is>
+      </c>
+      <c r="I111" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -6999,45 +6999,45 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="4" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B138" s="4" t="inlineStr">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
         <is>
           <t>A1-C2</t>
         </is>
       </c>
-      <c r="C138" s="4" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D138" s="4" t="inlineStr">
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E138" s="4" t="inlineStr">
+      <c r="E138" s="2" t="inlineStr">
         <is>
           <t>17/05/2026</t>
         </is>
       </c>
-      <c r="F138" s="4" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G138" s="4" t="inlineStr"/>
-      <c r="H138" s="4" t="inlineStr">
+      <c r="F138" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G138" s="2" t="inlineStr"/>
+      <c r="H138" s="2" t="inlineStr">
         <is>
           <t>0/33</t>
         </is>
       </c>
-      <c r="I138" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I138" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A1_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A1_session_analysis.xlsx
@@ -853,7 +853,7 @@
         </is>
       </c>
       <c r="L7" s="5" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8">
@@ -904,7 +904,7 @@
         </is>
       </c>
       <c r="L8" s="5" t="n">
-        <v>306</v>
+        <v>300</v>
       </c>
     </row>
     <row r="9">
@@ -1765,10 +1765,10 @@
         <v>0</v>
       </c>
       <c r="P21" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q21" s="5" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="R21" s="5" t="inlineStr">
         <is>
@@ -1843,10 +1843,10 @@
         <v>0</v>
       </c>
       <c r="P22" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q22" s="5" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="R22" s="5" t="inlineStr">
         <is>
@@ -1921,10 +1921,10 @@
         <v>0</v>
       </c>
       <c r="P23" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q23" s="5" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="R23" s="5" t="inlineStr">
         <is>
@@ -1999,10 +1999,10 @@
         <v>0</v>
       </c>
       <c r="P24" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q24" s="5" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="R24" s="5" t="inlineStr">
         <is>
@@ -2077,10 +2077,10 @@
         <v>0</v>
       </c>
       <c r="P25" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q25" s="5" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="R25" s="5" t="inlineStr">
         <is>
@@ -2155,10 +2155,10 @@
         <v>0</v>
       </c>
       <c r="P26" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q26" s="5" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="R26" s="5" t="inlineStr">
         <is>
@@ -8168,45 +8168,45 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B164" s="6" t="inlineStr">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
         <is>
           <t>A1-D1</t>
         </is>
       </c>
-      <c r="C164" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D164" s="6" t="inlineStr">
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E164" s="6" t="inlineStr">
+      <c r="E164" s="2" t="inlineStr">
         <is>
           <t>19/05/2026</t>
         </is>
       </c>
-      <c r="F164" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G164" s="6" t="inlineStr"/>
-      <c r="H164" s="6" t="inlineStr">
-        <is>
-          <t>0/34</t>
-        </is>
-      </c>
-      <c r="I164" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F164" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G164" s="2" t="inlineStr"/>
+      <c r="H164" s="2" t="inlineStr">
+        <is>
+          <t>0/34</t>
+        </is>
+      </c>
+      <c r="I164" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -9329,45 +9329,45 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B191" s="6" t="inlineStr">
+      <c r="A191" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B191" s="2" t="inlineStr">
         <is>
           <t>A1-D2</t>
         </is>
       </c>
-      <c r="C191" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D191" s="6" t="inlineStr">
+      <c r="C191" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D191" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E191" s="6" t="inlineStr">
+      <c r="E191" s="2" t="inlineStr">
         <is>
           <t>19/05/2026</t>
         </is>
       </c>
-      <c r="F191" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G191" s="6" t="inlineStr"/>
-      <c r="H191" s="6" t="inlineStr">
-        <is>
-          <t>0/34</t>
-        </is>
-      </c>
-      <c r="I191" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F191" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G191" s="2" t="inlineStr"/>
+      <c r="H191" s="2" t="inlineStr">
+        <is>
+          <t>0/34</t>
+        </is>
+      </c>
+      <c r="I191" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -10490,45 +10490,45 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B218" s="6" t="inlineStr">
+      <c r="A218" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B218" s="2" t="inlineStr">
         <is>
           <t>A1-E1</t>
         </is>
       </c>
-      <c r="C218" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D218" s="6" t="inlineStr">
+      <c r="C218" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D218" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E218" s="6" t="inlineStr">
+      <c r="E218" s="2" t="inlineStr">
         <is>
           <t>19/05/2026</t>
         </is>
       </c>
-      <c r="F218" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G218" s="6" t="inlineStr"/>
-      <c r="H218" s="6" t="inlineStr">
+      <c r="F218" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G218" s="2" t="inlineStr"/>
+      <c r="H218" s="2" t="inlineStr">
         <is>
           <t>0/38</t>
         </is>
       </c>
-      <c r="I218" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I218" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -11651,45 +11651,45 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B245" s="6" t="inlineStr">
+      <c r="A245" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B245" s="2" t="inlineStr">
         <is>
           <t>A1-E2</t>
         </is>
       </c>
-      <c r="C245" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D245" s="6" t="inlineStr">
+      <c r="C245" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D245" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E245" s="6" t="inlineStr">
+      <c r="E245" s="2" t="inlineStr">
         <is>
           <t>19/05/2026</t>
         </is>
       </c>
-      <c r="F245" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G245" s="6" t="inlineStr"/>
-      <c r="H245" s="6" t="inlineStr">
+      <c r="F245" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G245" s="2" t="inlineStr"/>
+      <c r="H245" s="2" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I245" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I245" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -12812,45 +12812,45 @@
       </c>
     </row>
     <row r="272">
-      <c r="A272" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B272" s="6" t="inlineStr">
+      <c r="A272" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B272" s="2" t="inlineStr">
         <is>
           <t>A1-F1</t>
         </is>
       </c>
-      <c r="C272" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D272" s="6" t="inlineStr">
+      <c r="C272" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D272" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E272" s="6" t="inlineStr">
+      <c r="E272" s="2" t="inlineStr">
         <is>
           <t>19/05/2026</t>
         </is>
       </c>
-      <c r="F272" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G272" s="6" t="inlineStr"/>
-      <c r="H272" s="6" t="inlineStr">
+      <c r="F272" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G272" s="2" t="inlineStr"/>
+      <c r="H272" s="2" t="inlineStr">
         <is>
           <t>0/38</t>
         </is>
       </c>
-      <c r="I272" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I272" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -13973,45 +13973,45 @@
       </c>
     </row>
     <row r="299">
-      <c r="A299" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B299" s="6" t="inlineStr">
+      <c r="A299" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B299" s="2" t="inlineStr">
         <is>
           <t>A1-F2</t>
         </is>
       </c>
-      <c r="C299" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D299" s="6" t="inlineStr">
+      <c r="C299" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D299" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E299" s="6" t="inlineStr">
+      <c r="E299" s="2" t="inlineStr">
         <is>
           <t>19/05/2026</t>
         </is>
       </c>
-      <c r="F299" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G299" s="6" t="inlineStr"/>
-      <c r="H299" s="6" t="inlineStr">
+      <c r="F299" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G299" s="2" t="inlineStr"/>
+      <c r="H299" s="2" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I299" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I299" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A1_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A1_session_analysis.xlsx
@@ -853,7 +853,7 @@
         </is>
       </c>
       <c r="L7" s="5" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8">
@@ -904,7 +904,7 @@
         </is>
       </c>
       <c r="L8" s="5" t="n">
-        <v>300</v>
+        <v>294</v>
       </c>
     </row>
     <row r="9">
@@ -1765,10 +1765,10 @@
         <v>0</v>
       </c>
       <c r="P21" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q21" s="5" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="R21" s="5" t="inlineStr">
         <is>
@@ -1843,10 +1843,10 @@
         <v>0</v>
       </c>
       <c r="P22" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q22" s="5" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="R22" s="5" t="inlineStr">
         <is>
@@ -1921,10 +1921,10 @@
         <v>0</v>
       </c>
       <c r="P23" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q23" s="5" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="R23" s="5" t="inlineStr">
         <is>
@@ -1999,10 +1999,10 @@
         <v>0</v>
       </c>
       <c r="P24" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q24" s="5" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="R24" s="5" t="inlineStr">
         <is>
@@ -2077,10 +2077,10 @@
         <v>0</v>
       </c>
       <c r="P25" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q25" s="5" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="R25" s="5" t="inlineStr">
         <is>
@@ -2155,10 +2155,10 @@
         <v>0</v>
       </c>
       <c r="P26" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q26" s="5" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="R26" s="5" t="inlineStr">
         <is>
@@ -8211,45 +8211,45 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B165" s="6" t="inlineStr">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
         <is>
           <t>A1-D1</t>
         </is>
       </c>
-      <c r="C165" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D165" s="6" t="inlineStr">
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E165" s="6" t="inlineStr">
+      <c r="E165" s="2" t="inlineStr">
         <is>
           <t>20/05/2026</t>
         </is>
       </c>
-      <c r="F165" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G165" s="6" t="inlineStr"/>
-      <c r="H165" s="6" t="inlineStr">
-        <is>
-          <t>0/34</t>
-        </is>
-      </c>
-      <c r="I165" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F165" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G165" s="2" t="inlineStr"/>
+      <c r="H165" s="2" t="inlineStr">
+        <is>
+          <t>0/34</t>
+        </is>
+      </c>
+      <c r="I165" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -9372,45 +9372,45 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B192" s="6" t="inlineStr">
+      <c r="A192" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B192" s="2" t="inlineStr">
         <is>
           <t>A1-D2</t>
         </is>
       </c>
-      <c r="C192" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D192" s="6" t="inlineStr">
+      <c r="C192" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D192" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E192" s="6" t="inlineStr">
+      <c r="E192" s="2" t="inlineStr">
         <is>
           <t>20/05/2026</t>
         </is>
       </c>
-      <c r="F192" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G192" s="6" t="inlineStr"/>
-      <c r="H192" s="6" t="inlineStr">
-        <is>
-          <t>0/34</t>
-        </is>
-      </c>
-      <c r="I192" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F192" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G192" s="2" t="inlineStr"/>
+      <c r="H192" s="2" t="inlineStr">
+        <is>
+          <t>0/34</t>
+        </is>
+      </c>
+      <c r="I192" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -10533,45 +10533,45 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B219" s="6" t="inlineStr">
+      <c r="A219" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B219" s="2" t="inlineStr">
         <is>
           <t>A1-E1</t>
         </is>
       </c>
-      <c r="C219" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D219" s="6" t="inlineStr">
+      <c r="C219" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D219" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E219" s="6" t="inlineStr">
+      <c r="E219" s="2" t="inlineStr">
         <is>
           <t>20/05/2026</t>
         </is>
       </c>
-      <c r="F219" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G219" s="6" t="inlineStr"/>
-      <c r="H219" s="6" t="inlineStr">
+      <c r="F219" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G219" s="2" t="inlineStr"/>
+      <c r="H219" s="2" t="inlineStr">
         <is>
           <t>0/38</t>
         </is>
       </c>
-      <c r="I219" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I219" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -11694,45 +11694,45 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B246" s="6" t="inlineStr">
+      <c r="A246" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B246" s="2" t="inlineStr">
         <is>
           <t>A1-E2</t>
         </is>
       </c>
-      <c r="C246" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D246" s="6" t="inlineStr">
+      <c r="C246" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D246" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E246" s="6" t="inlineStr">
+      <c r="E246" s="2" t="inlineStr">
         <is>
           <t>20/05/2026</t>
         </is>
       </c>
-      <c r="F246" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G246" s="6" t="inlineStr"/>
-      <c r="H246" s="6" t="inlineStr">
+      <c r="F246" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G246" s="2" t="inlineStr"/>
+      <c r="H246" s="2" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I246" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I246" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -12855,45 +12855,45 @@
       </c>
     </row>
     <row r="273">
-      <c r="A273" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B273" s="6" t="inlineStr">
+      <c r="A273" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B273" s="2" t="inlineStr">
         <is>
           <t>A1-F1</t>
         </is>
       </c>
-      <c r="C273" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D273" s="6" t="inlineStr">
+      <c r="C273" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D273" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E273" s="6" t="inlineStr">
+      <c r="E273" s="2" t="inlineStr">
         <is>
           <t>20/05/2026</t>
         </is>
       </c>
-      <c r="F273" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G273" s="6" t="inlineStr"/>
-      <c r="H273" s="6" t="inlineStr">
+      <c r="F273" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G273" s="2" t="inlineStr"/>
+      <c r="H273" s="2" t="inlineStr">
         <is>
           <t>0/38</t>
         </is>
       </c>
-      <c r="I273" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I273" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -14016,45 +14016,45 @@
       </c>
     </row>
     <row r="300">
-      <c r="A300" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B300" s="6" t="inlineStr">
+      <c r="A300" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B300" s="2" t="inlineStr">
         <is>
           <t>A1-F2</t>
         </is>
       </c>
-      <c r="C300" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D300" s="6" t="inlineStr">
+      <c r="C300" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D300" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E300" s="6" t="inlineStr">
+      <c r="E300" s="2" t="inlineStr">
         <is>
           <t>20/05/2026</t>
         </is>
       </c>
-      <c r="F300" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G300" s="6" t="inlineStr"/>
-      <c r="H300" s="6" t="inlineStr">
+      <c r="F300" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G300" s="2" t="inlineStr"/>
+      <c r="H300" s="2" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I300" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I300" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A1_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A1_session_analysis.xlsx
@@ -802,7 +802,7 @@
         </is>
       </c>
       <c r="L6" s="5" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7">
@@ -853,7 +853,7 @@
         </is>
       </c>
       <c r="L7" s="5" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8">
@@ -956,7 +956,7 @@
       </c>
       <c r="L9" s="5" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>5.6%</t>
         </is>
       </c>
     </row>
@@ -1009,7 +1009,7 @@
       </c>
       <c r="L10" s="5" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>65.5%</t>
         </is>
       </c>
     </row>
@@ -1762,22 +1762,22 @@
         <v>27</v>
       </c>
       <c r="O21" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P21" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q21" s="5" t="n">
         <v>25</v>
       </c>
       <c r="R21" s="5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="S21" s="5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>52.9%</t>
         </is>
       </c>
     </row>
@@ -1840,22 +1840,22 @@
         <v>27</v>
       </c>
       <c r="O22" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P22" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q22" s="5" t="n">
         <v>25</v>
       </c>
       <c r="R22" s="5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="S22" s="5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -1918,22 +1918,22 @@
         <v>27</v>
       </c>
       <c r="O23" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P23" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q23" s="5" t="n">
         <v>25</v>
       </c>
       <c r="R23" s="5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="S23" s="5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>89.5%</t>
         </is>
       </c>
     </row>
@@ -1996,22 +1996,22 @@
         <v>27</v>
       </c>
       <c r="O24" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P24" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q24" s="5" t="n">
         <v>25</v>
       </c>
       <c r="R24" s="5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="S24" s="5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>76.9%</t>
         </is>
       </c>
     </row>
@@ -2074,22 +2074,22 @@
         <v>27</v>
       </c>
       <c r="O25" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P25" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q25" s="5" t="n">
         <v>25</v>
       </c>
       <c r="R25" s="5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="S25" s="5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>86.8%</t>
         </is>
       </c>
     </row>
@@ -2152,22 +2152,22 @@
         <v>27</v>
       </c>
       <c r="O26" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P26" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q26" s="5" t="n">
         <v>25</v>
       </c>
       <c r="R26" s="5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="S26" s="5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>69.2%</t>
         </is>
       </c>
     </row>
@@ -8211,45 +8211,49 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B165" s="2" t="inlineStr">
+      <c r="A165" s="4" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B165" s="4" t="inlineStr">
         <is>
           <t>A1-D1</t>
         </is>
       </c>
-      <c r="C165" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D165" s="2" t="inlineStr">
+      <c r="C165" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D165" s="4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E165" s="2" t="inlineStr">
+      <c r="E165" s="4" t="inlineStr">
         <is>
           <t>20/05/2026</t>
         </is>
       </c>
-      <c r="F165" s="2" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G165" s="2" t="inlineStr"/>
-      <c r="H165" s="2" t="inlineStr">
-        <is>
-          <t>0/34</t>
-        </is>
-      </c>
-      <c r="I165" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F165" s="4" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G165" s="4" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H165" s="4" t="inlineStr">
+        <is>
+          <t>18/34</t>
+        </is>
+      </c>
+      <c r="I165" s="4" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -9372,45 +9376,49 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B192" s="2" t="inlineStr">
+      <c r="A192" s="4" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B192" s="4" t="inlineStr">
         <is>
           <t>A1-D2</t>
         </is>
       </c>
-      <c r="C192" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D192" s="2" t="inlineStr">
+      <c r="C192" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D192" s="4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E192" s="2" t="inlineStr">
+      <c r="E192" s="4" t="inlineStr">
         <is>
           <t>20/05/2026</t>
         </is>
       </c>
-      <c r="F192" s="2" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G192" s="2" t="inlineStr"/>
-      <c r="H192" s="2" t="inlineStr">
-        <is>
-          <t>0/34</t>
-        </is>
-      </c>
-      <c r="I192" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F192" s="4" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G192" s="4" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H192" s="4" t="inlineStr">
+        <is>
+          <t>17/34</t>
+        </is>
+      </c>
+      <c r="I192" s="4" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -10533,45 +10541,49 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B219" s="2" t="inlineStr">
+      <c r="A219" s="4" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B219" s="4" t="inlineStr">
         <is>
           <t>A1-E1</t>
         </is>
       </c>
-      <c r="C219" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D219" s="2" t="inlineStr">
+      <c r="C219" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D219" s="4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E219" s="2" t="inlineStr">
+      <c r="E219" s="4" t="inlineStr">
         <is>
           <t>20/05/2026</t>
         </is>
       </c>
-      <c r="F219" s="2" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G219" s="2" t="inlineStr"/>
-      <c r="H219" s="2" t="inlineStr">
-        <is>
-          <t>0/38</t>
-        </is>
-      </c>
-      <c r="I219" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F219" s="4" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G219" s="4" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H219" s="4" t="inlineStr">
+        <is>
+          <t>34/38</t>
+        </is>
+      </c>
+      <c r="I219" s="4" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -11694,45 +11706,49 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B246" s="2" t="inlineStr">
+      <c r="A246" s="4" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B246" s="4" t="inlineStr">
         <is>
           <t>A1-E2</t>
         </is>
       </c>
-      <c r="C246" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D246" s="2" t="inlineStr">
+      <c r="C246" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D246" s="4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E246" s="2" t="inlineStr">
+      <c r="E246" s="4" t="inlineStr">
         <is>
           <t>20/05/2026</t>
         </is>
       </c>
-      <c r="F246" s="2" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G246" s="2" t="inlineStr"/>
-      <c r="H246" s="2" t="inlineStr">
-        <is>
-          <t>0/39</t>
-        </is>
-      </c>
-      <c r="I246" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F246" s="4" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G246" s="4" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H246" s="4" t="inlineStr">
+        <is>
+          <t>30/39</t>
+        </is>
+      </c>
+      <c r="I246" s="4" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -12855,45 +12871,49 @@
       </c>
     </row>
     <row r="273">
-      <c r="A273" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B273" s="2" t="inlineStr">
+      <c r="A273" s="4" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B273" s="4" t="inlineStr">
         <is>
           <t>A1-F1</t>
         </is>
       </c>
-      <c r="C273" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D273" s="2" t="inlineStr">
+      <c r="C273" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D273" s="4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E273" s="2" t="inlineStr">
+      <c r="E273" s="4" t="inlineStr">
         <is>
           <t>20/05/2026</t>
         </is>
       </c>
-      <c r="F273" s="2" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G273" s="2" t="inlineStr"/>
-      <c r="H273" s="2" t="inlineStr">
-        <is>
-          <t>0/38</t>
-        </is>
-      </c>
-      <c r="I273" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F273" s="4" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G273" s="4" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H273" s="4" t="inlineStr">
+        <is>
+          <t>33/38</t>
+        </is>
+      </c>
+      <c r="I273" s="4" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -14016,45 +14036,49 @@
       </c>
     </row>
     <row r="300">
-      <c r="A300" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B300" s="2" t="inlineStr">
+      <c r="A300" s="4" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B300" s="4" t="inlineStr">
         <is>
           <t>A1-F2</t>
         </is>
       </c>
-      <c r="C300" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D300" s="2" t="inlineStr">
+      <c r="C300" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D300" s="4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E300" s="2" t="inlineStr">
+      <c r="E300" s="4" t="inlineStr">
         <is>
           <t>20/05/2026</t>
         </is>
       </c>
-      <c r="F300" s="2" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G300" s="2" t="inlineStr"/>
-      <c r="H300" s="2" t="inlineStr">
-        <is>
-          <t>0/39</t>
-        </is>
-      </c>
-      <c r="I300" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F300" s="4" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G300" s="4" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H300" s="4" t="inlineStr">
+        <is>
+          <t>27/39</t>
+        </is>
+      </c>
+      <c r="I300" s="4" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A1_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A1_session_analysis.xlsx
@@ -802,7 +802,7 @@
         </is>
       </c>
       <c r="L6" s="5" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7">
@@ -904,7 +904,7 @@
         </is>
       </c>
       <c r="L8" s="5" t="n">
-        <v>294</v>
+        <v>288</v>
       </c>
     </row>
     <row r="9">
@@ -956,7 +956,7 @@
       </c>
       <c r="L9" s="5" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>7.4%</t>
         </is>
       </c>
     </row>
@@ -1009,7 +1009,7 @@
       </c>
       <c r="L10" s="5" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>65.1%</t>
         </is>
       </c>
     </row>
@@ -1762,22 +1762,22 @@
         <v>27</v>
       </c>
       <c r="O21" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P21" s="5" t="n">
         <v>1</v>
       </c>
       <c r="Q21" s="5" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="R21" s="5" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="S21" s="5" t="inlineStr">
         <is>
-          <t>52.9%</t>
+          <t>39.7%</t>
         </is>
       </c>
     </row>
@@ -1840,22 +1840,22 @@
         <v>27</v>
       </c>
       <c r="O22" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P22" s="5" t="n">
         <v>1</v>
       </c>
       <c r="Q22" s="5" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="R22" s="5" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="S22" s="5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>41.2%</t>
         </is>
       </c>
     </row>
@@ -1918,22 +1918,22 @@
         <v>27</v>
       </c>
       <c r="O23" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P23" s="5" t="n">
         <v>1</v>
       </c>
       <c r="Q23" s="5" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="R23" s="5" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="S23" s="5" t="inlineStr">
         <is>
-          <t>89.5%</t>
+          <t>86.8%</t>
         </is>
       </c>
     </row>
@@ -1996,17 +1996,17 @@
         <v>27</v>
       </c>
       <c r="O24" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P24" s="5" t="n">
         <v>1</v>
       </c>
       <c r="Q24" s="5" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="R24" s="5" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="S24" s="5" t="inlineStr">
@@ -2074,22 +2074,22 @@
         <v>27</v>
       </c>
       <c r="O25" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P25" s="5" t="n">
         <v>1</v>
       </c>
       <c r="Q25" s="5" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="R25" s="5" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="S25" s="5" t="inlineStr">
         <is>
-          <t>86.8%</t>
+          <t>82.9%</t>
         </is>
       </c>
     </row>
@@ -2152,22 +2152,22 @@
         <v>27</v>
       </c>
       <c r="O26" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P26" s="5" t="n">
         <v>1</v>
       </c>
       <c r="Q26" s="5" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="R26" s="5" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="S26" s="5" t="inlineStr">
         <is>
-          <t>69.2%</t>
+          <t>76.9%</t>
         </is>
       </c>
     </row>
@@ -8258,45 +8258,49 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B166" s="6" t="inlineStr">
+      <c r="A166" s="4" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B166" s="4" t="inlineStr">
         <is>
           <t>A1-D1</t>
         </is>
       </c>
-      <c r="C166" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D166" s="6" t="inlineStr">
+      <c r="C166" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D166" s="4" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E166" s="6" t="inlineStr">
+      <c r="E166" s="4" t="inlineStr">
         <is>
           <t>21/05/2026</t>
         </is>
       </c>
-      <c r="F166" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G166" s="6" t="inlineStr"/>
-      <c r="H166" s="6" t="inlineStr">
-        <is>
-          <t>0/34</t>
-        </is>
-      </c>
-      <c r="I166" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F166" s="4" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G166" s="4" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H166" s="4" t="inlineStr">
+        <is>
+          <t>9/34</t>
+        </is>
+      </c>
+      <c r="I166" s="4" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -9423,45 +9427,49 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B193" s="6" t="inlineStr">
+      <c r="A193" s="4" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B193" s="4" t="inlineStr">
         <is>
           <t>A1-D2</t>
         </is>
       </c>
-      <c r="C193" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D193" s="6" t="inlineStr">
+      <c r="C193" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D193" s="4" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E193" s="6" t="inlineStr">
+      <c r="E193" s="4" t="inlineStr">
         <is>
           <t>21/05/2026</t>
         </is>
       </c>
-      <c r="F193" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G193" s="6" t="inlineStr"/>
-      <c r="H193" s="6" t="inlineStr">
-        <is>
-          <t>0/34</t>
-        </is>
-      </c>
-      <c r="I193" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F193" s="4" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G193" s="4" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H193" s="4" t="inlineStr">
+        <is>
+          <t>11/34</t>
+        </is>
+      </c>
+      <c r="I193" s="4" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -10588,45 +10596,49 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B220" s="6" t="inlineStr">
+      <c r="A220" s="4" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B220" s="4" t="inlineStr">
         <is>
           <t>A1-E1</t>
         </is>
       </c>
-      <c r="C220" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D220" s="6" t="inlineStr">
+      <c r="C220" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D220" s="4" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E220" s="6" t="inlineStr">
+      <c r="E220" s="4" t="inlineStr">
         <is>
           <t>21/05/2026</t>
         </is>
       </c>
-      <c r="F220" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G220" s="6" t="inlineStr"/>
-      <c r="H220" s="6" t="inlineStr">
-        <is>
-          <t>0/38</t>
-        </is>
-      </c>
-      <c r="I220" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F220" s="4" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G220" s="4" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H220" s="4" t="inlineStr">
+        <is>
+          <t>32/38</t>
+        </is>
+      </c>
+      <c r="I220" s="4" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -11753,45 +11765,49 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B247" s="6" t="inlineStr">
+      <c r="A247" s="4" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B247" s="4" t="inlineStr">
         <is>
           <t>A1-E2</t>
         </is>
       </c>
-      <c r="C247" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D247" s="6" t="inlineStr">
+      <c r="C247" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D247" s="4" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E247" s="6" t="inlineStr">
+      <c r="E247" s="4" t="inlineStr">
         <is>
           <t>21/05/2026</t>
         </is>
       </c>
-      <c r="F247" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G247" s="6" t="inlineStr"/>
-      <c r="H247" s="6" t="inlineStr">
-        <is>
-          <t>0/39</t>
-        </is>
-      </c>
-      <c r="I247" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F247" s="4" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G247" s="4" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H247" s="4" t="inlineStr">
+        <is>
+          <t>30/39</t>
+        </is>
+      </c>
+      <c r="I247" s="4" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -12918,45 +12934,49 @@
       </c>
     </row>
     <row r="274">
-      <c r="A274" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B274" s="6" t="inlineStr">
+      <c r="A274" s="4" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B274" s="4" t="inlineStr">
         <is>
           <t>A1-F1</t>
         </is>
       </c>
-      <c r="C274" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D274" s="6" t="inlineStr">
+      <c r="C274" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D274" s="4" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E274" s="6" t="inlineStr">
+      <c r="E274" s="4" t="inlineStr">
         <is>
           <t>21/05/2026</t>
         </is>
       </c>
-      <c r="F274" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G274" s="6" t="inlineStr"/>
-      <c r="H274" s="6" t="inlineStr">
-        <is>
-          <t>0/38</t>
-        </is>
-      </c>
-      <c r="I274" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F274" s="4" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G274" s="4" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H274" s="4" t="inlineStr">
+        <is>
+          <t>30/38</t>
+        </is>
+      </c>
+      <c r="I274" s="4" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -14083,45 +14103,49 @@
       </c>
     </row>
     <row r="301">
-      <c r="A301" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B301" s="6" t="inlineStr">
+      <c r="A301" s="4" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B301" s="4" t="inlineStr">
         <is>
           <t>A1-F2</t>
         </is>
       </c>
-      <c r="C301" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D301" s="6" t="inlineStr">
+      <c r="C301" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D301" s="4" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E301" s="6" t="inlineStr">
+      <c r="E301" s="4" t="inlineStr">
         <is>
           <t>21/05/2026</t>
         </is>
       </c>
-      <c r="F301" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G301" s="6" t="inlineStr"/>
-      <c r="H301" s="6" t="inlineStr">
-        <is>
-          <t>0/39</t>
-        </is>
-      </c>
-      <c r="I301" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F301" s="4" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G301" s="4" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H301" s="4" t="inlineStr">
+        <is>
+          <t>33/39</t>
+        </is>
+      </c>
+      <c r="I301" s="4" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A1_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A1_session_analysis.xlsx
@@ -81,7 +81,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -103,9 +103,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -484,7 +481,7 @@
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
     <col width="22" customWidth="1" min="11" max="11"/>
     <col width="8" customWidth="1" min="12" max="12"/>
     <col width="18" customWidth="1" min="13" max="13"/>
@@ -581,7 +578,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>13/34</t>
+          <t>15/34</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -806,7 +803,7 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7">
@@ -857,7 +854,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -960,7 +957,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>9.0%</t>
+          <t>11.1%</t>
         </is>
       </c>
     </row>
@@ -1013,7 +1010,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>56.7%</t>
+          <t>54.7%</t>
         </is>
       </c>
     </row>
@@ -1313,7 +1310,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>49.0%</t>
+          <t>51.0%</t>
         </is>
       </c>
     </row>
@@ -1391,7 +1388,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>46.5%</t>
         </is>
       </c>
     </row>
@@ -1469,7 +1466,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>55.9%</t>
+          <t>67.6%</t>
         </is>
       </c>
     </row>
@@ -1547,7 +1544,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>43.1%</t>
+          <t>54.9%</t>
         </is>
       </c>
     </row>
@@ -1625,7 +1622,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>52.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -1688,22 +1685,22 @@
         <v>27</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q20" s="4" t="n">
         <v>24</v>
       </c>
       <c r="R20" s="4" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>44.4%</t>
         </is>
       </c>
     </row>
@@ -1766,22 +1763,22 @@
         <v>27</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q21" s="4" t="n">
         <v>24</v>
       </c>
       <c r="R21" s="4" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>39.7%</t>
+          <t>41.2%</t>
         </is>
       </c>
     </row>
@@ -1844,17 +1841,17 @@
         <v>27</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q22" s="4" t="n">
         <v>24</v>
       </c>
       <c r="R22" s="4" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="S22" s="4" t="inlineStr">
@@ -1922,22 +1919,22 @@
         <v>27</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q23" s="4" t="n">
         <v>24</v>
       </c>
       <c r="R23" s="4" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>86.8%</t>
+          <t>65.8%</t>
         </is>
       </c>
     </row>
@@ -2000,22 +1997,22 @@
         <v>27</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q24" s="4" t="n">
         <v>24</v>
       </c>
       <c r="R24" s="4" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>76.9%</t>
+          <t>54.7%</t>
         </is>
       </c>
     </row>
@@ -2078,22 +2075,22 @@
         <v>27</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q25" s="4" t="n">
         <v>24</v>
       </c>
       <c r="R25" s="4" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>82.9%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -2156,22 +2153,22 @@
         <v>27</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q26" s="4" t="n">
         <v>24</v>
       </c>
       <c r="R26" s="4" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>76.9%</t>
+          <t>55.6%</t>
         </is>
       </c>
     </row>
@@ -2299,7 +2296,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>8/33</t>
+          <t>9/33</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -3537,7 +3534,7 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>4/34</t>
+          <t>16/34</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
@@ -4710,7 +4707,7 @@
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>1/34</t>
+          <t>13/34</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
@@ -5883,7 +5880,7 @@
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>2/34</t>
+          <t>17/34</t>
         </is>
       </c>
       <c r="I110" s="2" t="inlineStr">
@@ -7019,45 +7016,49 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B137" s="9" t="inlineStr">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
         <is>
           <t>A1-C2</t>
         </is>
       </c>
-      <c r="C137" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D137" s="9" t="inlineStr">
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E137" s="9" t="inlineStr">
+      <c r="E137" s="2" t="inlineStr">
         <is>
           <t>16/05/2026</t>
         </is>
       </c>
-      <c r="F137" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G137" s="9" t="inlineStr"/>
-      <c r="H137" s="9" t="inlineStr">
-        <is>
-          <t>0/33</t>
-        </is>
-      </c>
-      <c r="I137" s="9" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F137" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G137" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H137" s="2" t="inlineStr">
+        <is>
+          <t>11/33</t>
+        </is>
+      </c>
+      <c r="I137" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -8188,45 +8189,49 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B164" s="9" t="inlineStr">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
         <is>
           <t>A1-D1</t>
         </is>
       </c>
-      <c r="C164" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D164" s="9" t="inlineStr">
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E164" s="9" t="inlineStr">
+      <c r="E164" s="2" t="inlineStr">
         <is>
           <t>19/05/2026</t>
         </is>
       </c>
-      <c r="F164" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G164" s="9" t="inlineStr"/>
-      <c r="H164" s="9" t="inlineStr">
-        <is>
-          <t>0/34</t>
-        </is>
-      </c>
-      <c r="I164" s="9" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F164" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G164" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H164" s="2" t="inlineStr">
+        <is>
+          <t>15/34</t>
+        </is>
+      </c>
+      <c r="I164" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -9357,45 +9362,49 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B191" s="9" t="inlineStr">
+      <c r="A191" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B191" s="2" t="inlineStr">
         <is>
           <t>A1-D2</t>
         </is>
       </c>
-      <c r="C191" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D191" s="9" t="inlineStr">
+      <c r="C191" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D191" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E191" s="9" t="inlineStr">
+      <c r="E191" s="2" t="inlineStr">
         <is>
           <t>19/05/2026</t>
         </is>
       </c>
-      <c r="F191" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G191" s="9" t="inlineStr"/>
-      <c r="H191" s="9" t="inlineStr">
-        <is>
-          <t>0/34</t>
-        </is>
-      </c>
-      <c r="I191" s="9" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F191" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G191" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H191" s="2" t="inlineStr">
+        <is>
+          <t>14/34</t>
+        </is>
+      </c>
+      <c r="I191" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -10526,45 +10535,49 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B218" s="9" t="inlineStr">
+      <c r="A218" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B218" s="2" t="inlineStr">
         <is>
           <t>A1-E1</t>
         </is>
       </c>
-      <c r="C218" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D218" s="9" t="inlineStr">
+      <c r="C218" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D218" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E218" s="9" t="inlineStr">
+      <c r="E218" s="2" t="inlineStr">
         <is>
           <t>19/05/2026</t>
         </is>
       </c>
-      <c r="F218" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G218" s="9" t="inlineStr"/>
-      <c r="H218" s="9" t="inlineStr">
-        <is>
-          <t>0/38</t>
-        </is>
-      </c>
-      <c r="I218" s="9" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F218" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G218" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H218" s="2" t="inlineStr">
+        <is>
+          <t>9/38</t>
+        </is>
+      </c>
+      <c r="I218" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -11695,45 +11708,49 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B245" s="9" t="inlineStr">
+      <c r="A245" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B245" s="2" t="inlineStr">
         <is>
           <t>A1-E2</t>
         </is>
       </c>
-      <c r="C245" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D245" s="9" t="inlineStr">
+      <c r="C245" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D245" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E245" s="9" t="inlineStr">
+      <c r="E245" s="2" t="inlineStr">
         <is>
           <t>19/05/2026</t>
         </is>
       </c>
-      <c r="F245" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G245" s="9" t="inlineStr"/>
-      <c r="H245" s="9" t="inlineStr">
-        <is>
-          <t>0/39</t>
-        </is>
-      </c>
-      <c r="I245" s="9" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F245" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G245" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H245" s="2" t="inlineStr">
+        <is>
+          <t>4/39</t>
+        </is>
+      </c>
+      <c r="I245" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -12864,45 +12881,49 @@
       </c>
     </row>
     <row r="272">
-      <c r="A272" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B272" s="9" t="inlineStr">
+      <c r="A272" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B272" s="2" t="inlineStr">
         <is>
           <t>A1-F1</t>
         </is>
       </c>
-      <c r="C272" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D272" s="9" t="inlineStr">
+      <c r="C272" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D272" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E272" s="9" t="inlineStr">
+      <c r="E272" s="2" t="inlineStr">
         <is>
           <t>19/05/2026</t>
         </is>
       </c>
-      <c r="F272" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G272" s="9" t="inlineStr"/>
-      <c r="H272" s="9" t="inlineStr">
-        <is>
-          <t>0/38</t>
-        </is>
-      </c>
-      <c r="I272" s="9" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F272" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G272" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H272" s="2" t="inlineStr">
+        <is>
+          <t>13/38</t>
+        </is>
+      </c>
+      <c r="I272" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -14033,45 +14054,49 @@
       </c>
     </row>
     <row r="299">
-      <c r="A299" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B299" s="9" t="inlineStr">
+      <c r="A299" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B299" s="2" t="inlineStr">
         <is>
           <t>A1-F2</t>
         </is>
       </c>
-      <c r="C299" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D299" s="9" t="inlineStr">
+      <c r="C299" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D299" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E299" s="9" t="inlineStr">
+      <c r="E299" s="2" t="inlineStr">
         <is>
           <t>19/05/2026</t>
         </is>
       </c>
-      <c r="F299" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G299" s="9" t="inlineStr"/>
-      <c r="H299" s="9" t="inlineStr">
-        <is>
-          <t>0/39</t>
-        </is>
-      </c>
-      <c r="I299" s="9" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F299" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G299" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H299" s="2" t="inlineStr">
+        <is>
+          <t>5/39</t>
+        </is>
+      </c>
+      <c r="I299" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A1_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A1_session_analysis.xlsx
@@ -759,45 +759,45 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>A1-A1</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E6" s="6" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>31/05/2026</t>
         </is>
       </c>
-      <c r="F6" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G6" s="6" t="inlineStr"/>
-      <c r="H6" s="6" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr"/>
+      <c r="H6" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I6" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
       <c r="K6" s="4" t="inlineStr">
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8">
@@ -908,7 +908,7 @@
         </is>
       </c>
       <c r="L8" s="4" t="n">
-        <v>282</v>
+        <v>276</v>
       </c>
     </row>
     <row r="9">
@@ -1301,10 +1301,10 @@
         <v>3</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R15" s="4" t="inlineStr">
         <is>
@@ -1379,10 +1379,10 @@
         <v>3</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R16" s="4" t="inlineStr">
         <is>
@@ -1457,10 +1457,10 @@
         <v>3</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R17" s="4" t="inlineStr">
         <is>
@@ -1535,10 +1535,10 @@
         <v>3</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R18" s="4" t="inlineStr">
         <is>
@@ -1613,10 +1613,10 @@
         <v>3</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R19" s="4" t="inlineStr">
         <is>
@@ -1691,10 +1691,10 @@
         <v>3</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R20" s="4" t="inlineStr">
         <is>
@@ -2496,45 +2496,45 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B33" s="6" t="inlineStr">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
         <is>
           <t>A1-A2</t>
         </is>
       </c>
-      <c r="C33" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D33" s="6" t="inlineStr">
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E33" s="6" t="inlineStr">
+      <c r="E33" s="5" t="inlineStr">
         <is>
           <t>31/05/2026</t>
         </is>
       </c>
-      <c r="F33" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G33" s="6" t="inlineStr"/>
-      <c r="H33" s="6" t="inlineStr">
+      <c r="F33" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G33" s="5" t="inlineStr"/>
+      <c r="H33" s="5" t="inlineStr">
         <is>
           <t>0/33</t>
         </is>
       </c>
-      <c r="I33" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I33" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
       <c r="K33" s="4" t="inlineStr">
@@ -3684,45 +3684,45 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B60" s="6" t="inlineStr">
+      <c r="A60" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B60" s="5" t="inlineStr">
         <is>
           <t>A1-B1</t>
         </is>
       </c>
-      <c r="C60" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D60" s="6" t="inlineStr">
+      <c r="C60" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D60" s="5" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E60" s="6" t="inlineStr">
+      <c r="E60" s="5" t="inlineStr">
         <is>
           <t>31/05/2026</t>
         </is>
       </c>
-      <c r="F60" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G60" s="6" t="inlineStr"/>
-      <c r="H60" s="6" t="inlineStr">
+      <c r="F60" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G60" s="5" t="inlineStr"/>
+      <c r="H60" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I60" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I60" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -4857,45 +4857,45 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B87" s="6" t="inlineStr">
+      <c r="A87" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B87" s="5" t="inlineStr">
         <is>
           <t>A1-B2</t>
         </is>
       </c>
-      <c r="C87" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D87" s="6" t="inlineStr">
+      <c r="C87" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D87" s="5" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E87" s="6" t="inlineStr">
+      <c r="E87" s="5" t="inlineStr">
         <is>
           <t>31/05/2026</t>
         </is>
       </c>
-      <c r="F87" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G87" s="6" t="inlineStr"/>
-      <c r="H87" s="6" t="inlineStr">
+      <c r="F87" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G87" s="5" t="inlineStr"/>
+      <c r="H87" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I87" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I87" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -6030,45 +6030,45 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B114" s="6" t="inlineStr">
+      <c r="A114" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B114" s="5" t="inlineStr">
         <is>
           <t>A1-C1</t>
         </is>
       </c>
-      <c r="C114" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D114" s="6" t="inlineStr">
+      <c r="C114" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D114" s="5" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E114" s="6" t="inlineStr">
+      <c r="E114" s="5" t="inlineStr">
         <is>
           <t>31/05/2026</t>
         </is>
       </c>
-      <c r="F114" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G114" s="6" t="inlineStr"/>
-      <c r="H114" s="6" t="inlineStr">
+      <c r="F114" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G114" s="5" t="inlineStr"/>
+      <c r="H114" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I114" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I114" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -7203,45 +7203,45 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B141" s="6" t="inlineStr">
+      <c r="A141" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B141" s="5" t="inlineStr">
         <is>
           <t>A1-C2</t>
         </is>
       </c>
-      <c r="C141" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D141" s="6" t="inlineStr">
+      <c r="C141" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D141" s="5" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E141" s="6" t="inlineStr">
+      <c r="E141" s="5" t="inlineStr">
         <is>
           <t>31/05/2026</t>
         </is>
       </c>
-      <c r="F141" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G141" s="6" t="inlineStr"/>
-      <c r="H141" s="6" t="inlineStr">
+      <c r="F141" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G141" s="5" t="inlineStr"/>
+      <c r="H141" s="5" t="inlineStr">
         <is>
           <t>0/33</t>
         </is>
       </c>
-      <c r="I141" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I141" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A1_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A1_session_analysis.xlsx
@@ -704,7 +704,7 @@
         </is>
       </c>
       <c r="L4" s="4" t="n">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="5">
@@ -806,49 +806,53 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>A1-A1</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E7" s="6" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>01/06/2026</t>
         </is>
       </c>
-      <c r="F7" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G7" s="6" t="inlineStr"/>
-      <c r="H7" s="6" t="inlineStr">
-        <is>
-          <t>0/34</t>
-        </is>
-      </c>
-      <c r="I7" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>14/34</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
       <c r="K7" s="4" t="inlineStr">
@@ -908,7 +912,7 @@
         </is>
       </c>
       <c r="L8" s="4" t="n">
-        <v>276</v>
+        <v>270</v>
       </c>
     </row>
     <row r="9">
@@ -960,7 +964,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>13.0%</t>
         </is>
       </c>
     </row>
@@ -1013,7 +1017,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>58.5%</t>
         </is>
       </c>
     </row>
@@ -1298,22 +1302,22 @@
         <v>27</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P15" s="4" t="n">
         <v>2</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R15" s="4" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>51.0%</t>
+          <t>48.5%</t>
         </is>
       </c>
     </row>
@@ -1376,22 +1380,22 @@
         <v>27</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P16" s="4" t="n">
         <v>2</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R16" s="4" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>46.5%</t>
+          <t>44.7%</t>
         </is>
       </c>
     </row>
@@ -1454,22 +1458,22 @@
         <v>27</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P17" s="4" t="n">
         <v>2</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R17" s="4" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>67.6%</t>
+          <t>65.4%</t>
         </is>
       </c>
     </row>
@@ -1532,22 +1536,22 @@
         <v>27</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P18" s="4" t="n">
         <v>2</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R18" s="4" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>54.4%</t>
         </is>
       </c>
     </row>
@@ -1610,22 +1614,22 @@
         <v>27</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P19" s="4" t="n">
         <v>2</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R19" s="4" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>63.2%</t>
         </is>
       </c>
     </row>
@@ -1688,22 +1692,22 @@
         <v>27</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P20" s="4" t="n">
         <v>2</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R20" s="4" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>44.7%</t>
         </is>
       </c>
     </row>
@@ -1760,7 +1764,7 @@
         </is>
       </c>
       <c r="M21" s="4" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="N21" s="4" t="n">
         <v>27</v>
@@ -1781,7 +1785,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>44.8%</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1863,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>47.1%</t>
         </is>
       </c>
     </row>
@@ -1937,7 +1941,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>65.8%</t>
+          <t>76.3%</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2019,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>70.1%</t>
         </is>
       </c>
     </row>
@@ -2093,7 +2097,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>78.9%</t>
         </is>
       </c>
     </row>
@@ -2171,7 +2175,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>74.4%</t>
         </is>
       </c>
     </row>
@@ -2554,45 +2558,49 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B34" s="6" t="inlineStr">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>A1-A2</t>
         </is>
       </c>
-      <c r="C34" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D34" s="6" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E34" s="6" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>01/06/2026</t>
         </is>
       </c>
-      <c r="F34" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G34" s="6" t="inlineStr"/>
-      <c r="H34" s="6" t="inlineStr">
-        <is>
-          <t>0/33</t>
-        </is>
-      </c>
-      <c r="I34" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>13/33</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -3727,45 +3735,49 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B61" s="6" t="inlineStr">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
         <is>
           <t>A1-B1</t>
         </is>
       </c>
-      <c r="C61" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D61" s="6" t="inlineStr">
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E61" s="6" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>01/06/2026</t>
         </is>
       </c>
-      <c r="F61" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G61" s="6" t="inlineStr"/>
-      <c r="H61" s="6" t="inlineStr">
-        <is>
-          <t>0/34</t>
-        </is>
-      </c>
-      <c r="I61" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>20/34</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -4804,7 +4816,7 @@
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>23/34</t>
+          <t>21/34</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
@@ -4900,45 +4912,49 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B88" s="6" t="inlineStr">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
         <is>
           <t>A1-B2</t>
         </is>
       </c>
-      <c r="C88" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D88" s="6" t="inlineStr">
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E88" s="6" t="inlineStr">
+      <c r="E88" s="2" t="inlineStr">
         <is>
           <t>01/06/2026</t>
         </is>
       </c>
-      <c r="F88" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G88" s="6" t="inlineStr"/>
-      <c r="H88" s="6" t="inlineStr">
-        <is>
-          <t>0/34</t>
-        </is>
-      </c>
-      <c r="I88" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>20/34</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -6073,45 +6089,49 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B115" s="6" t="inlineStr">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
         <is>
           <t>A1-C1</t>
         </is>
       </c>
-      <c r="C115" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D115" s="6" t="inlineStr">
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E115" s="6" t="inlineStr">
+      <c r="E115" s="2" t="inlineStr">
         <is>
           <t>01/06/2026</t>
         </is>
       </c>
-      <c r="F115" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G115" s="6" t="inlineStr"/>
-      <c r="H115" s="6" t="inlineStr">
-        <is>
-          <t>0/34</t>
-        </is>
-      </c>
-      <c r="I115" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H115" s="2" t="inlineStr">
+        <is>
+          <t>18/34</t>
+        </is>
+      </c>
+      <c r="I115" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -7246,45 +7266,49 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B142" s="6" t="inlineStr">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
         <is>
           <t>A1-C2</t>
         </is>
       </c>
-      <c r="C142" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D142" s="6" t="inlineStr">
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E142" s="6" t="inlineStr">
+      <c r="E142" s="2" t="inlineStr">
         <is>
           <t>01/06/2026</t>
         </is>
       </c>
-      <c r="F142" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G142" s="6" t="inlineStr"/>
-      <c r="H142" s="6" t="inlineStr">
-        <is>
-          <t>0/33</t>
-        </is>
-      </c>
-      <c r="I142" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F142" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G142" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H142" s="2" t="inlineStr">
+        <is>
+          <t>15/33</t>
+        </is>
+      </c>
+      <c r="I142" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -8229,7 +8253,7 @@
       </c>
       <c r="H164" s="2" t="inlineStr">
         <is>
-          <t>15/34</t>
+          <t>19/35</t>
         </is>
       </c>
       <c r="I164" s="2" t="inlineStr">
@@ -8276,7 +8300,7 @@
       </c>
       <c r="H165" s="2" t="inlineStr">
         <is>
-          <t>18/34</t>
+          <t>19/35</t>
         </is>
       </c>
       <c r="I165" s="2" t="inlineStr">
@@ -8323,7 +8347,7 @@
       </c>
       <c r="H166" s="2" t="inlineStr">
         <is>
-          <t>9/34</t>
+          <t>9/35</t>
         </is>
       </c>
       <c r="I166" s="2" t="inlineStr">
@@ -8366,7 +8390,7 @@
       <c r="G167" s="6" t="inlineStr"/>
       <c r="H167" s="6" t="inlineStr">
         <is>
-          <t>0/34</t>
+          <t>0/35</t>
         </is>
       </c>
       <c r="I167" s="6" t="inlineStr">
@@ -8409,7 +8433,7 @@
       <c r="G168" s="6" t="inlineStr"/>
       <c r="H168" s="6" t="inlineStr">
         <is>
-          <t>0/34</t>
+          <t>0/35</t>
         </is>
       </c>
       <c r="I168" s="6" t="inlineStr">
@@ -8452,7 +8476,7 @@
       <c r="G169" s="6" t="inlineStr"/>
       <c r="H169" s="6" t="inlineStr">
         <is>
-          <t>0/34</t>
+          <t>0/35</t>
         </is>
       </c>
       <c r="I169" s="6" t="inlineStr">
@@ -8495,7 +8519,7 @@
       <c r="G170" s="6" t="inlineStr"/>
       <c r="H170" s="6" t="inlineStr">
         <is>
-          <t>0/34</t>
+          <t>0/35</t>
         </is>
       </c>
       <c r="I170" s="6" t="inlineStr">
@@ -8538,7 +8562,7 @@
       <c r="G171" s="6" t="inlineStr"/>
       <c r="H171" s="6" t="inlineStr">
         <is>
-          <t>0/34</t>
+          <t>0/35</t>
         </is>
       </c>
       <c r="I171" s="6" t="inlineStr">
@@ -8581,7 +8605,7 @@
       <c r="G172" s="6" t="inlineStr"/>
       <c r="H172" s="6" t="inlineStr">
         <is>
-          <t>0/34</t>
+          <t>0/35</t>
         </is>
       </c>
       <c r="I172" s="6" t="inlineStr">
@@ -8624,7 +8648,7 @@
       <c r="G173" s="6" t="inlineStr"/>
       <c r="H173" s="6" t="inlineStr">
         <is>
-          <t>0/34</t>
+          <t>0/35</t>
         </is>
       </c>
       <c r="I173" s="6" t="inlineStr">
@@ -8667,7 +8691,7 @@
       <c r="G174" s="6" t="inlineStr"/>
       <c r="H174" s="6" t="inlineStr">
         <is>
-          <t>0/34</t>
+          <t>0/35</t>
         </is>
       </c>
       <c r="I174" s="6" t="inlineStr">
@@ -8710,7 +8734,7 @@
       <c r="G175" s="6" t="inlineStr"/>
       <c r="H175" s="6" t="inlineStr">
         <is>
-          <t>0/34</t>
+          <t>0/35</t>
         </is>
       </c>
       <c r="I175" s="6" t="inlineStr">
@@ -8753,7 +8777,7 @@
       <c r="G176" s="6" t="inlineStr"/>
       <c r="H176" s="6" t="inlineStr">
         <is>
-          <t>0/34</t>
+          <t>0/35</t>
         </is>
       </c>
       <c r="I176" s="6" t="inlineStr">
@@ -8796,7 +8820,7 @@
       <c r="G177" s="6" t="inlineStr"/>
       <c r="H177" s="6" t="inlineStr">
         <is>
-          <t>0/34</t>
+          <t>0/35</t>
         </is>
       </c>
       <c r="I177" s="6" t="inlineStr">
@@ -8839,7 +8863,7 @@
       <c r="G178" s="6" t="inlineStr"/>
       <c r="H178" s="6" t="inlineStr">
         <is>
-          <t>0/34</t>
+          <t>0/35</t>
         </is>
       </c>
       <c r="I178" s="6" t="inlineStr">
@@ -8882,7 +8906,7 @@
       <c r="G179" s="6" t="inlineStr"/>
       <c r="H179" s="6" t="inlineStr">
         <is>
-          <t>0/34</t>
+          <t>0/35</t>
         </is>
       </c>
       <c r="I179" s="6" t="inlineStr">
@@ -8925,7 +8949,7 @@
       <c r="G180" s="6" t="inlineStr"/>
       <c r="H180" s="6" t="inlineStr">
         <is>
-          <t>0/34</t>
+          <t>0/35</t>
         </is>
       </c>
       <c r="I180" s="6" t="inlineStr">
@@ -8968,7 +8992,7 @@
       <c r="G181" s="6" t="inlineStr"/>
       <c r="H181" s="6" t="inlineStr">
         <is>
-          <t>0/34</t>
+          <t>0/35</t>
         </is>
       </c>
       <c r="I181" s="6" t="inlineStr">
@@ -9011,7 +9035,7 @@
       <c r="G182" s="6" t="inlineStr"/>
       <c r="H182" s="6" t="inlineStr">
         <is>
-          <t>0/34</t>
+          <t>0/35</t>
         </is>
       </c>
       <c r="I182" s="6" t="inlineStr">
@@ -9054,7 +9078,7 @@
       <c r="G183" s="6" t="inlineStr"/>
       <c r="H183" s="6" t="inlineStr">
         <is>
-          <t>0/34</t>
+          <t>0/35</t>
         </is>
       </c>
       <c r="I183" s="6" t="inlineStr">
@@ -9097,7 +9121,7 @@
       <c r="G184" s="6" t="inlineStr"/>
       <c r="H184" s="6" t="inlineStr">
         <is>
-          <t>0/34</t>
+          <t>0/35</t>
         </is>
       </c>
       <c r="I184" s="6" t="inlineStr">
@@ -9140,7 +9164,7 @@
       <c r="G185" s="6" t="inlineStr"/>
       <c r="H185" s="6" t="inlineStr">
         <is>
-          <t>0/34</t>
+          <t>0/35</t>
         </is>
       </c>
       <c r="I185" s="6" t="inlineStr">
@@ -9183,7 +9207,7 @@
       <c r="G186" s="6" t="inlineStr"/>
       <c r="H186" s="6" t="inlineStr">
         <is>
-          <t>0/34</t>
+          <t>0/35</t>
         </is>
       </c>
       <c r="I186" s="6" t="inlineStr">
@@ -9226,7 +9250,7 @@
       <c r="G187" s="6" t="inlineStr"/>
       <c r="H187" s="6" t="inlineStr">
         <is>
-          <t>0/34</t>
+          <t>0/35</t>
         </is>
       </c>
       <c r="I187" s="6" t="inlineStr">
@@ -9269,7 +9293,7 @@
       <c r="G188" s="6" t="inlineStr"/>
       <c r="H188" s="6" t="inlineStr">
         <is>
-          <t>0/34</t>
+          <t>0/35</t>
         </is>
       </c>
       <c r="I188" s="6" t="inlineStr">
@@ -9312,7 +9336,7 @@
       <c r="G189" s="6" t="inlineStr"/>
       <c r="H189" s="6" t="inlineStr">
         <is>
-          <t>0/34</t>
+          <t>0/35</t>
         </is>
       </c>
       <c r="I189" s="6" t="inlineStr">
@@ -9355,7 +9379,7 @@
       <c r="G190" s="6" t="inlineStr"/>
       <c r="H190" s="6" t="inlineStr">
         <is>
-          <t>0/34</t>
+          <t>0/35</t>
         </is>
       </c>
       <c r="I190" s="6" t="inlineStr">
@@ -9402,7 +9426,7 @@
       </c>
       <c r="H191" s="2" t="inlineStr">
         <is>
-          <t>14/34</t>
+          <t>20/34</t>
         </is>
       </c>
       <c r="I191" s="2" t="inlineStr">
@@ -10575,7 +10599,7 @@
       </c>
       <c r="H218" s="2" t="inlineStr">
         <is>
-          <t>9/38</t>
+          <t>21/38</t>
         </is>
       </c>
       <c r="I218" s="2" t="inlineStr">
@@ -11748,7 +11772,7 @@
       </c>
       <c r="H245" s="2" t="inlineStr">
         <is>
-          <t>4/39</t>
+          <t>22/39</t>
         </is>
       </c>
       <c r="I245" s="2" t="inlineStr">
@@ -12921,7 +12945,7 @@
       </c>
       <c r="H272" s="2" t="inlineStr">
         <is>
-          <t>13/38</t>
+          <t>27/38</t>
         </is>
       </c>
       <c r="I272" s="2" t="inlineStr">
@@ -14094,7 +14118,7 @@
       </c>
       <c r="H299" s="2" t="inlineStr">
         <is>
-          <t>5/39</t>
+          <t>27/39</t>
         </is>
       </c>
       <c r="I299" s="2" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A1_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A1_session_analysis.xlsx
@@ -806,7 +806,7 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7">
@@ -912,7 +912,7 @@
         </is>
       </c>
       <c r="L8" s="4" t="n">
-        <v>270</v>
+        <v>264</v>
       </c>
     </row>
     <row r="9">
@@ -964,7 +964,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>14.8%</t>
         </is>
       </c>
     </row>
@@ -1017,7 +1017,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>58.5%</t>
+          <t>59.8%</t>
         </is>
       </c>
     </row>
@@ -1770,22 +1770,22 @@
         <v>27</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P21" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="R21" s="4" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>44.8%</t>
+          <t>53.6%</t>
         </is>
       </c>
     </row>
@@ -1848,22 +1848,22 @@
         <v>27</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P22" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="R22" s="4" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>57.4%</t>
         </is>
       </c>
     </row>
@@ -1926,22 +1926,22 @@
         <v>27</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P23" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="R23" s="4" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>76.3%</t>
+          <t>77.0%</t>
         </is>
       </c>
     </row>
@@ -2004,22 +2004,22 @@
         <v>27</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P24" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="R24" s="4" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>70.1%</t>
+          <t>65.4%</t>
         </is>
       </c>
     </row>
@@ -2082,22 +2082,22 @@
         <v>27</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P25" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="R25" s="4" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>78.9%</t>
+          <t>77.0%</t>
         </is>
       </c>
     </row>
@@ -2160,22 +2160,22 @@
         <v>27</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P26" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="R26" s="4" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>74.4%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -8357,45 +8357,49 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B167" s="6" t="inlineStr">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
         <is>
           <t>A1-D1</t>
         </is>
       </c>
-      <c r="C167" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D167" s="6" t="inlineStr">
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E167" s="6" t="inlineStr">
+      <c r="E167" s="2" t="inlineStr">
         <is>
           <t>02/06/2026</t>
         </is>
       </c>
-      <c r="F167" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G167" s="6" t="inlineStr"/>
-      <c r="H167" s="6" t="inlineStr">
-        <is>
-          <t>0/35</t>
-        </is>
-      </c>
-      <c r="I167" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F167" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G167" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H167" s="2" t="inlineStr">
+        <is>
+          <t>28/35</t>
+        </is>
+      </c>
+      <c r="I167" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -9530,45 +9534,49 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B194" s="6" t="inlineStr">
+      <c r="A194" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B194" s="2" t="inlineStr">
         <is>
           <t>A1-D2</t>
         </is>
       </c>
-      <c r="C194" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D194" s="6" t="inlineStr">
+      <c r="C194" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D194" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E194" s="6" t="inlineStr">
+      <c r="E194" s="2" t="inlineStr">
         <is>
           <t>02/06/2026</t>
         </is>
       </c>
-      <c r="F194" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G194" s="6" t="inlineStr"/>
-      <c r="H194" s="6" t="inlineStr">
-        <is>
-          <t>0/34</t>
-        </is>
-      </c>
-      <c r="I194" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F194" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G194" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H194" s="2" t="inlineStr">
+        <is>
+          <t>30/34</t>
+        </is>
+      </c>
+      <c r="I194" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -10703,45 +10711,49 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B221" s="6" t="inlineStr">
+      <c r="A221" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B221" s="2" t="inlineStr">
         <is>
           <t>A1-E1</t>
         </is>
       </c>
-      <c r="C221" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D221" s="6" t="inlineStr">
+      <c r="C221" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D221" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E221" s="6" t="inlineStr">
+      <c r="E221" s="2" t="inlineStr">
         <is>
           <t>02/06/2026</t>
         </is>
       </c>
-      <c r="F221" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G221" s="6" t="inlineStr"/>
-      <c r="H221" s="6" t="inlineStr">
-        <is>
-          <t>0/38</t>
-        </is>
-      </c>
-      <c r="I221" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F221" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G221" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H221" s="2" t="inlineStr">
+        <is>
+          <t>30/38</t>
+        </is>
+      </c>
+      <c r="I221" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -11876,45 +11888,49 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B248" s="6" t="inlineStr">
+      <c r="A248" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B248" s="2" t="inlineStr">
         <is>
           <t>A1-E2</t>
         </is>
       </c>
-      <c r="C248" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D248" s="6" t="inlineStr">
+      <c r="C248" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D248" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E248" s="6" t="inlineStr">
+      <c r="E248" s="2" t="inlineStr">
         <is>
           <t>02/06/2026</t>
         </is>
       </c>
-      <c r="F248" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G248" s="6" t="inlineStr"/>
-      <c r="H248" s="6" t="inlineStr">
-        <is>
-          <t>0/39</t>
-        </is>
-      </c>
-      <c r="I248" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F248" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G248" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H248" s="2" t="inlineStr">
+        <is>
+          <t>20/39</t>
+        </is>
+      </c>
+      <c r="I248" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -13049,45 +13065,49 @@
       </c>
     </row>
     <row r="275">
-      <c r="A275" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B275" s="6" t="inlineStr">
+      <c r="A275" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B275" s="2" t="inlineStr">
         <is>
           <t>A1-F1</t>
         </is>
       </c>
-      <c r="C275" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D275" s="6" t="inlineStr">
+      <c r="C275" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D275" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E275" s="6" t="inlineStr">
+      <c r="E275" s="2" t="inlineStr">
         <is>
           <t>02/06/2026</t>
         </is>
       </c>
-      <c r="F275" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G275" s="6" t="inlineStr"/>
-      <c r="H275" s="6" t="inlineStr">
-        <is>
-          <t>0/38</t>
-        </is>
-      </c>
-      <c r="I275" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F275" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G275" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H275" s="2" t="inlineStr">
+        <is>
+          <t>27/38</t>
+        </is>
+      </c>
+      <c r="I275" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -14222,45 +14242,49 @@
       </c>
     </row>
     <row r="302">
-      <c r="A302" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B302" s="6" t="inlineStr">
+      <c r="A302" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B302" s="2" t="inlineStr">
         <is>
           <t>A1-F2</t>
         </is>
       </c>
-      <c r="C302" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D302" s="6" t="inlineStr">
+      <c r="C302" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D302" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E302" s="6" t="inlineStr">
+      <c r="E302" s="2" t="inlineStr">
         <is>
           <t>02/06/2026</t>
         </is>
       </c>
-      <c r="F302" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G302" s="6" t="inlineStr"/>
-      <c r="H302" s="6" t="inlineStr">
-        <is>
-          <t>0/39</t>
-        </is>
-      </c>
-      <c r="I302" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F302" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G302" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H302" s="2" t="inlineStr">
+        <is>
+          <t>17/39</t>
+        </is>
+      </c>
+      <c r="I302" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A1_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A1_session_analysis.xlsx
@@ -861,7 +861,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8">
@@ -912,7 +912,7 @@
         </is>
       </c>
       <c r="L8" s="4" t="n">
-        <v>264</v>
+        <v>258</v>
       </c>
     </row>
     <row r="9">
@@ -1773,10 +1773,10 @@
         <v>4</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R21" s="4" t="inlineStr">
         <is>
@@ -1851,10 +1851,10 @@
         <v>4</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R22" s="4" t="inlineStr">
         <is>
@@ -1929,10 +1929,10 @@
         <v>4</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R23" s="4" t="inlineStr">
         <is>
@@ -2007,10 +2007,10 @@
         <v>4</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R24" s="4" t="inlineStr">
         <is>
@@ -2085,10 +2085,10 @@
         <v>4</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R25" s="4" t="inlineStr">
         <is>
@@ -2163,10 +2163,10 @@
         <v>4</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R26" s="4" t="inlineStr">
         <is>
@@ -8404,45 +8404,45 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B168" s="6" t="inlineStr">
+      <c r="A168" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B168" s="5" t="inlineStr">
         <is>
           <t>A1-D1</t>
         </is>
       </c>
-      <c r="C168" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D168" s="6" t="inlineStr">
+      <c r="C168" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D168" s="5" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E168" s="6" t="inlineStr">
+      <c r="E168" s="5" t="inlineStr">
         <is>
           <t>03/06/2026</t>
         </is>
       </c>
-      <c r="F168" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G168" s="6" t="inlineStr"/>
-      <c r="H168" s="6" t="inlineStr">
+      <c r="F168" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G168" s="5" t="inlineStr"/>
+      <c r="H168" s="5" t="inlineStr">
         <is>
           <t>0/35</t>
         </is>
       </c>
-      <c r="I168" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I168" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -9581,45 +9581,45 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B195" s="6" t="inlineStr">
+      <c r="A195" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B195" s="5" t="inlineStr">
         <is>
           <t>A1-D2</t>
         </is>
       </c>
-      <c r="C195" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D195" s="6" t="inlineStr">
+      <c r="C195" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D195" s="5" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E195" s="6" t="inlineStr">
+      <c r="E195" s="5" t="inlineStr">
         <is>
           <t>03/06/2026</t>
         </is>
       </c>
-      <c r="F195" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G195" s="6" t="inlineStr"/>
-      <c r="H195" s="6" t="inlineStr">
+      <c r="F195" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G195" s="5" t="inlineStr"/>
+      <c r="H195" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I195" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I195" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -10758,45 +10758,45 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B222" s="6" t="inlineStr">
+      <c r="A222" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B222" s="5" t="inlineStr">
         <is>
           <t>A1-E1</t>
         </is>
       </c>
-      <c r="C222" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D222" s="6" t="inlineStr">
+      <c r="C222" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D222" s="5" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E222" s="6" t="inlineStr">
+      <c r="E222" s="5" t="inlineStr">
         <is>
           <t>03/06/2026</t>
         </is>
       </c>
-      <c r="F222" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G222" s="6" t="inlineStr"/>
-      <c r="H222" s="6" t="inlineStr">
+      <c r="F222" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G222" s="5" t="inlineStr"/>
+      <c r="H222" s="5" t="inlineStr">
         <is>
           <t>0/38</t>
         </is>
       </c>
-      <c r="I222" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I222" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -11935,45 +11935,45 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B249" s="6" t="inlineStr">
+      <c r="A249" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B249" s="5" t="inlineStr">
         <is>
           <t>A1-E2</t>
         </is>
       </c>
-      <c r="C249" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D249" s="6" t="inlineStr">
+      <c r="C249" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D249" s="5" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E249" s="6" t="inlineStr">
+      <c r="E249" s="5" t="inlineStr">
         <is>
           <t>03/06/2026</t>
         </is>
       </c>
-      <c r="F249" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G249" s="6" t="inlineStr"/>
-      <c r="H249" s="6" t="inlineStr">
+      <c r="F249" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G249" s="5" t="inlineStr"/>
+      <c r="H249" s="5" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I249" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I249" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -13112,45 +13112,45 @@
       </c>
     </row>
     <row r="276">
-      <c r="A276" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B276" s="6" t="inlineStr">
+      <c r="A276" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B276" s="5" t="inlineStr">
         <is>
           <t>A1-F1</t>
         </is>
       </c>
-      <c r="C276" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D276" s="6" t="inlineStr">
+      <c r="C276" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D276" s="5" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E276" s="6" t="inlineStr">
+      <c r="E276" s="5" t="inlineStr">
         <is>
           <t>03/06/2026</t>
         </is>
       </c>
-      <c r="F276" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G276" s="6" t="inlineStr"/>
-      <c r="H276" s="6" t="inlineStr">
+      <c r="F276" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G276" s="5" t="inlineStr"/>
+      <c r="H276" s="5" t="inlineStr">
         <is>
           <t>0/38</t>
         </is>
       </c>
-      <c r="I276" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I276" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -14289,45 +14289,45 @@
       </c>
     </row>
     <row r="303">
-      <c r="A303" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B303" s="6" t="inlineStr">
+      <c r="A303" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B303" s="5" t="inlineStr">
         <is>
           <t>A1-F2</t>
         </is>
       </c>
-      <c r="C303" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D303" s="6" t="inlineStr">
+      <c r="C303" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D303" s="5" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E303" s="6" t="inlineStr">
+      <c r="E303" s="5" t="inlineStr">
         <is>
           <t>03/06/2026</t>
         </is>
       </c>
-      <c r="F303" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G303" s="6" t="inlineStr"/>
-      <c r="H303" s="6" t="inlineStr">
+      <c r="F303" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G303" s="5" t="inlineStr"/>
+      <c r="H303" s="5" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I303" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I303" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A1_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A1_session_analysis.xlsx
@@ -806,7 +806,7 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
     </row>
     <row r="7">
@@ -861,7 +861,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8">
@@ -964,7 +964,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>16.7%</t>
         </is>
       </c>
     </row>
@@ -1017,7 +1017,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>59.8%</t>
+          <t>60.9%</t>
         </is>
       </c>
     </row>
@@ -1770,22 +1770,22 @@
         <v>27</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q21" s="4" t="n">
         <v>22</v>
       </c>
       <c r="R21" s="4" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>53.6%</t>
+          <t>56.0%</t>
         </is>
       </c>
     </row>
@@ -1848,22 +1848,22 @@
         <v>27</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q22" s="4" t="n">
         <v>22</v>
       </c>
       <c r="R22" s="4" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>62.9%</t>
         </is>
       </c>
     </row>
@@ -1926,22 +1926,22 @@
         <v>27</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q23" s="4" t="n">
         <v>22</v>
       </c>
       <c r="R23" s="4" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>77.0%</t>
+          <t>73.7%</t>
         </is>
       </c>
     </row>
@@ -2004,22 +2004,22 @@
         <v>27</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q24" s="4" t="n">
         <v>22</v>
       </c>
       <c r="R24" s="4" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>65.4%</t>
+          <t>63.6%</t>
         </is>
       </c>
     </row>
@@ -2082,22 +2082,22 @@
         <v>27</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q25" s="4" t="n">
         <v>22</v>
       </c>
       <c r="R25" s="4" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>77.0%</t>
+          <t>76.3%</t>
         </is>
       </c>
     </row>
@@ -2160,22 +2160,22 @@
         <v>27</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q26" s="4" t="n">
         <v>22</v>
       </c>
       <c r="R26" s="4" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>68.7%</t>
         </is>
       </c>
     </row>
@@ -8404,45 +8404,49 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B168" s="5" t="inlineStr">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
         <is>
           <t>A1-D1</t>
         </is>
       </c>
-      <c r="C168" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D168" s="5" t="inlineStr">
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E168" s="5" t="inlineStr">
+      <c r="E168" s="2" t="inlineStr">
         <is>
           <t>03/06/2026</t>
         </is>
       </c>
-      <c r="F168" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G168" s="5" t="inlineStr"/>
-      <c r="H168" s="5" t="inlineStr">
-        <is>
-          <t>0/35</t>
-        </is>
-      </c>
-      <c r="I168" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F168" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G168" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H168" s="2" t="inlineStr">
+        <is>
+          <t>23/35</t>
+        </is>
+      </c>
+      <c r="I168" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -9581,45 +9585,49 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B195" s="5" t="inlineStr">
+      <c r="A195" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B195" s="2" t="inlineStr">
         <is>
           <t>A1-D2</t>
         </is>
       </c>
-      <c r="C195" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D195" s="5" t="inlineStr">
+      <c r="C195" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D195" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E195" s="5" t="inlineStr">
+      <c r="E195" s="2" t="inlineStr">
         <is>
           <t>03/06/2026</t>
         </is>
       </c>
-      <c r="F195" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G195" s="5" t="inlineStr"/>
-      <c r="H195" s="5" t="inlineStr">
-        <is>
-          <t>0/34</t>
-        </is>
-      </c>
-      <c r="I195" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F195" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G195" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H195" s="2" t="inlineStr">
+        <is>
+          <t>29/34</t>
+        </is>
+      </c>
+      <c r="I195" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -10758,45 +10766,49 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B222" s="5" t="inlineStr">
+      <c r="A222" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B222" s="2" t="inlineStr">
         <is>
           <t>A1-E1</t>
         </is>
       </c>
-      <c r="C222" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D222" s="5" t="inlineStr">
+      <c r="C222" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D222" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E222" s="5" t="inlineStr">
+      <c r="E222" s="2" t="inlineStr">
         <is>
           <t>03/06/2026</t>
         </is>
       </c>
-      <c r="F222" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G222" s="5" t="inlineStr"/>
-      <c r="H222" s="5" t="inlineStr">
-        <is>
-          <t>0/38</t>
-        </is>
-      </c>
-      <c r="I222" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F222" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G222" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H222" s="2" t="inlineStr">
+        <is>
+          <t>23/38</t>
+        </is>
+      </c>
+      <c r="I222" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -11935,45 +11947,49 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B249" s="5" t="inlineStr">
+      <c r="A249" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B249" s="2" t="inlineStr">
         <is>
           <t>A1-E2</t>
         </is>
       </c>
-      <c r="C249" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D249" s="5" t="inlineStr">
+      <c r="C249" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D249" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E249" s="5" t="inlineStr">
+      <c r="E249" s="2" t="inlineStr">
         <is>
           <t>03/06/2026</t>
         </is>
       </c>
-      <c r="F249" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G249" s="5" t="inlineStr"/>
-      <c r="H249" s="5" t="inlineStr">
-        <is>
-          <t>0/39</t>
-        </is>
-      </c>
-      <c r="I249" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F249" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G249" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H249" s="2" t="inlineStr">
+        <is>
+          <t>22/39</t>
+        </is>
+      </c>
+      <c r="I249" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -13112,45 +13128,49 @@
       </c>
     </row>
     <row r="276">
-      <c r="A276" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B276" s="5" t="inlineStr">
+      <c r="A276" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B276" s="2" t="inlineStr">
         <is>
           <t>A1-F1</t>
         </is>
       </c>
-      <c r="C276" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D276" s="5" t="inlineStr">
+      <c r="C276" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D276" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E276" s="5" t="inlineStr">
+      <c r="E276" s="2" t="inlineStr">
         <is>
           <t>03/06/2026</t>
         </is>
       </c>
-      <c r="F276" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G276" s="5" t="inlineStr"/>
-      <c r="H276" s="5" t="inlineStr">
-        <is>
-          <t>0/38</t>
-        </is>
-      </c>
-      <c r="I276" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F276" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G276" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H276" s="2" t="inlineStr">
+        <is>
+          <t>28/38</t>
+        </is>
+      </c>
+      <c r="I276" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -14289,45 +14309,49 @@
       </c>
     </row>
     <row r="303">
-      <c r="A303" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B303" s="5" t="inlineStr">
+      <c r="A303" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B303" s="2" t="inlineStr">
         <is>
           <t>A1-F2</t>
         </is>
       </c>
-      <c r="C303" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D303" s="5" t="inlineStr">
+      <c r="C303" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D303" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E303" s="5" t="inlineStr">
+      <c r="E303" s="2" t="inlineStr">
         <is>
           <t>03/06/2026</t>
         </is>
       </c>
-      <c r="F303" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G303" s="5" t="inlineStr"/>
-      <c r="H303" s="5" t="inlineStr">
-        <is>
-          <t>0/39</t>
-        </is>
-      </c>
-      <c r="I303" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F303" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G303" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H303" s="2" t="inlineStr">
+        <is>
+          <t>30/39</t>
+        </is>
+      </c>
+      <c r="I303" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A1_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A1_session_analysis.xlsx
@@ -861,7 +861,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8">
@@ -912,7 +912,7 @@
         </is>
       </c>
       <c r="L8" s="4" t="n">
-        <v>258</v>
+        <v>252</v>
       </c>
     </row>
     <row r="9">
@@ -1773,10 +1773,10 @@
         <v>5</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R21" s="4" t="inlineStr">
         <is>
@@ -1851,10 +1851,10 @@
         <v>5</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R22" s="4" t="inlineStr">
         <is>
@@ -1929,10 +1929,10 @@
         <v>5</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R23" s="4" t="inlineStr">
         <is>
@@ -2007,10 +2007,10 @@
         <v>5</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R24" s="4" t="inlineStr">
         <is>
@@ -2085,10 +2085,10 @@
         <v>5</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R25" s="4" t="inlineStr">
         <is>
@@ -2163,10 +2163,10 @@
         <v>5</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R26" s="4" t="inlineStr">
         <is>
@@ -8451,45 +8451,45 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B169" s="6" t="inlineStr">
+      <c r="A169" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B169" s="5" t="inlineStr">
         <is>
           <t>A1-D1</t>
         </is>
       </c>
-      <c r="C169" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D169" s="6" t="inlineStr">
+      <c r="C169" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D169" s="5" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E169" s="6" t="inlineStr">
+      <c r="E169" s="5" t="inlineStr">
         <is>
           <t>04/06/2026</t>
         </is>
       </c>
-      <c r="F169" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G169" s="6" t="inlineStr"/>
-      <c r="H169" s="6" t="inlineStr">
+      <c r="F169" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G169" s="5" t="inlineStr"/>
+      <c r="H169" s="5" t="inlineStr">
         <is>
           <t>0/35</t>
         </is>
       </c>
-      <c r="I169" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I169" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -9632,45 +9632,45 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B196" s="6" t="inlineStr">
+      <c r="A196" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B196" s="5" t="inlineStr">
         <is>
           <t>A1-D2</t>
         </is>
       </c>
-      <c r="C196" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D196" s="6" t="inlineStr">
+      <c r="C196" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D196" s="5" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E196" s="6" t="inlineStr">
+      <c r="E196" s="5" t="inlineStr">
         <is>
           <t>04/06/2026</t>
         </is>
       </c>
-      <c r="F196" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G196" s="6" t="inlineStr"/>
-      <c r="H196" s="6" t="inlineStr">
+      <c r="F196" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G196" s="5" t="inlineStr"/>
+      <c r="H196" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I196" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I196" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -10813,45 +10813,45 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B223" s="6" t="inlineStr">
+      <c r="A223" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B223" s="5" t="inlineStr">
         <is>
           <t>A1-E1</t>
         </is>
       </c>
-      <c r="C223" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D223" s="6" t="inlineStr">
+      <c r="C223" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D223" s="5" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E223" s="6" t="inlineStr">
+      <c r="E223" s="5" t="inlineStr">
         <is>
           <t>04/06/2026</t>
         </is>
       </c>
-      <c r="F223" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G223" s="6" t="inlineStr"/>
-      <c r="H223" s="6" t="inlineStr">
+      <c r="F223" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G223" s="5" t="inlineStr"/>
+      <c r="H223" s="5" t="inlineStr">
         <is>
           <t>0/38</t>
         </is>
       </c>
-      <c r="I223" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I223" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -11994,45 +11994,45 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B250" s="6" t="inlineStr">
+      <c r="A250" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B250" s="5" t="inlineStr">
         <is>
           <t>A1-E2</t>
         </is>
       </c>
-      <c r="C250" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D250" s="6" t="inlineStr">
+      <c r="C250" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D250" s="5" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E250" s="6" t="inlineStr">
+      <c r="E250" s="5" t="inlineStr">
         <is>
           <t>04/06/2026</t>
         </is>
       </c>
-      <c r="F250" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G250" s="6" t="inlineStr"/>
-      <c r="H250" s="6" t="inlineStr">
+      <c r="F250" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G250" s="5" t="inlineStr"/>
+      <c r="H250" s="5" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I250" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I250" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -13175,45 +13175,45 @@
       </c>
     </row>
     <row r="277">
-      <c r="A277" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B277" s="6" t="inlineStr">
+      <c r="A277" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B277" s="5" t="inlineStr">
         <is>
           <t>A1-F1</t>
         </is>
       </c>
-      <c r="C277" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D277" s="6" t="inlineStr">
+      <c r="C277" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D277" s="5" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E277" s="6" t="inlineStr">
+      <c r="E277" s="5" t="inlineStr">
         <is>
           <t>04/06/2026</t>
         </is>
       </c>
-      <c r="F277" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G277" s="6" t="inlineStr"/>
-      <c r="H277" s="6" t="inlineStr">
+      <c r="F277" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G277" s="5" t="inlineStr"/>
+      <c r="H277" s="5" t="inlineStr">
         <is>
           <t>0/38</t>
         </is>
       </c>
-      <c r="I277" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I277" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -14356,45 +14356,45 @@
       </c>
     </row>
     <row r="304">
-      <c r="A304" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B304" s="6" t="inlineStr">
+      <c r="A304" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B304" s="5" t="inlineStr">
         <is>
           <t>A1-F2</t>
         </is>
       </c>
-      <c r="C304" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D304" s="6" t="inlineStr">
+      <c r="C304" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D304" s="5" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E304" s="6" t="inlineStr">
+      <c r="E304" s="5" t="inlineStr">
         <is>
           <t>04/06/2026</t>
         </is>
       </c>
-      <c r="F304" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G304" s="6" t="inlineStr"/>
-      <c r="H304" s="6" t="inlineStr">
+      <c r="F304" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G304" s="5" t="inlineStr"/>
+      <c r="H304" s="5" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I304" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I304" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A1_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A1_session_analysis.xlsx
@@ -861,49 +861,49 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>A1-A1</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E8" s="6" t="inlineStr">
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>06/06/2026</t>
         </is>
       </c>
-      <c r="F8" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G8" s="6" t="inlineStr"/>
-      <c r="H8" s="6" t="inlineStr">
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr"/>
+      <c r="H8" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I8" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
       <c r="K8" s="4" t="inlineStr">
@@ -912,7 +912,7 @@
         </is>
       </c>
       <c r="L8" s="4" t="n">
-        <v>252</v>
+        <v>246</v>
       </c>
     </row>
     <row r="9">
@@ -1305,10 +1305,10 @@
         <v>4</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="R15" s="4" t="inlineStr">
         <is>
@@ -1383,10 +1383,10 @@
         <v>4</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="R16" s="4" t="inlineStr">
         <is>
@@ -1461,10 +1461,10 @@
         <v>4</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="R17" s="4" t="inlineStr">
         <is>
@@ -1539,10 +1539,10 @@
         <v>4</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="R18" s="4" t="inlineStr">
         <is>
@@ -1617,10 +1617,10 @@
         <v>4</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="R19" s="4" t="inlineStr">
         <is>
@@ -1695,10 +1695,10 @@
         <v>4</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="R20" s="4" t="inlineStr">
         <is>
@@ -2605,45 +2605,45 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B35" s="6" t="inlineStr">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
         <is>
           <t>A1-A2</t>
         </is>
       </c>
-      <c r="C35" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D35" s="6" t="inlineStr">
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E35" s="6" t="inlineStr">
+      <c r="E35" s="5" t="inlineStr">
         <is>
           <t>06/06/2026</t>
         </is>
       </c>
-      <c r="F35" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G35" s="6" t="inlineStr"/>
-      <c r="H35" s="6" t="inlineStr">
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G35" s="5" t="inlineStr"/>
+      <c r="H35" s="5" t="inlineStr">
         <is>
           <t>0/33</t>
         </is>
       </c>
-      <c r="I35" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I35" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -3782,45 +3782,45 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B62" s="6" t="inlineStr">
+      <c r="A62" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B62" s="5" t="inlineStr">
         <is>
           <t>A1-B1</t>
         </is>
       </c>
-      <c r="C62" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D62" s="6" t="inlineStr">
+      <c r="C62" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D62" s="5" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E62" s="6" t="inlineStr">
+      <c r="E62" s="5" t="inlineStr">
         <is>
           <t>06/06/2026</t>
         </is>
       </c>
-      <c r="F62" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G62" s="6" t="inlineStr"/>
-      <c r="H62" s="6" t="inlineStr">
+      <c r="F62" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G62" s="5" t="inlineStr"/>
+      <c r="H62" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I62" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I62" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -4959,45 +4959,45 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B89" s="6" t="inlineStr">
+      <c r="A89" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B89" s="5" t="inlineStr">
         <is>
           <t>A1-B2</t>
         </is>
       </c>
-      <c r="C89" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D89" s="6" t="inlineStr">
+      <c r="C89" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D89" s="5" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E89" s="6" t="inlineStr">
+      <c r="E89" s="5" t="inlineStr">
         <is>
           <t>06/06/2026</t>
         </is>
       </c>
-      <c r="F89" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G89" s="6" t="inlineStr"/>
-      <c r="H89" s="6" t="inlineStr">
+      <c r="F89" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G89" s="5" t="inlineStr"/>
+      <c r="H89" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I89" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I89" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -6136,45 +6136,45 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B116" s="6" t="inlineStr">
+      <c r="A116" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B116" s="5" t="inlineStr">
         <is>
           <t>A1-C1</t>
         </is>
       </c>
-      <c r="C116" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D116" s="6" t="inlineStr">
+      <c r="C116" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D116" s="5" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E116" s="6" t="inlineStr">
+      <c r="E116" s="5" t="inlineStr">
         <is>
           <t>06/06/2026</t>
         </is>
       </c>
-      <c r="F116" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G116" s="6" t="inlineStr"/>
-      <c r="H116" s="6" t="inlineStr">
+      <c r="F116" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G116" s="5" t="inlineStr"/>
+      <c r="H116" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I116" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I116" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -7313,45 +7313,45 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B143" s="6" t="inlineStr">
+      <c r="A143" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B143" s="5" t="inlineStr">
         <is>
           <t>A1-C2</t>
         </is>
       </c>
-      <c r="C143" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D143" s="6" t="inlineStr">
+      <c r="C143" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D143" s="5" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E143" s="6" t="inlineStr">
+      <c r="E143" s="5" t="inlineStr">
         <is>
           <t>06/06/2026</t>
         </is>
       </c>
-      <c r="F143" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G143" s="6" t="inlineStr"/>
-      <c r="H143" s="6" t="inlineStr">
+      <c r="F143" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G143" s="5" t="inlineStr"/>
+      <c r="H143" s="5" t="inlineStr">
         <is>
           <t>0/33</t>
         </is>
       </c>
-      <c r="I143" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I143" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A1_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A1_session_analysis.xlsx
@@ -806,7 +806,7 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7">
@@ -861,49 +861,53 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>A1-A1</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>06/06/2026</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G8" s="5" t="inlineStr"/>
-      <c r="H8" s="5" t="inlineStr">
-        <is>
-          <t>0/34</t>
-        </is>
-      </c>
-      <c r="I8" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>27/34</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
       <c r="K8" s="4" t="inlineStr">
@@ -964,7 +968,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>18.5%</t>
         </is>
       </c>
     </row>
@@ -1017,7 +1021,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>60.9%</t>
+          <t>62.9%</t>
         </is>
       </c>
     </row>
@@ -1302,22 +1306,22 @@
         <v>27</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q15" s="4" t="n">
         <v>20</v>
       </c>
       <c r="R15" s="4" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>48.5%</t>
+          <t>54.7%</t>
         </is>
       </c>
     </row>
@@ -1380,22 +1384,22 @@
         <v>27</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q16" s="4" t="n">
         <v>20</v>
       </c>
       <c r="R16" s="4" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>44.7%</t>
+          <t>52.7%</t>
         </is>
       </c>
     </row>
@@ -1458,22 +1462,22 @@
         <v>27</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q17" s="4" t="n">
         <v>20</v>
       </c>
       <c r="R17" s="4" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>65.4%</t>
+          <t>68.8%</t>
         </is>
       </c>
     </row>
@@ -1536,22 +1540,22 @@
         <v>27</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q18" s="4" t="n">
         <v>20</v>
       </c>
       <c r="R18" s="4" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>54.4%</t>
+          <t>60.0%</t>
         </is>
       </c>
     </row>
@@ -1614,22 +1618,22 @@
         <v>27</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q19" s="4" t="n">
         <v>20</v>
       </c>
       <c r="R19" s="4" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>63.2%</t>
+          <t>66.5%</t>
         </is>
       </c>
     </row>
@@ -1692,22 +1696,22 @@
         <v>27</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q20" s="4" t="n">
         <v>20</v>
       </c>
       <c r="R20" s="4" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>44.7%</t>
+          <t>50.9%</t>
         </is>
       </c>
     </row>
@@ -2605,45 +2609,49 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B35" s="5" t="inlineStr">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>A1-A2</t>
         </is>
       </c>
-      <c r="C35" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D35" s="5" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E35" s="5" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>06/06/2026</t>
         </is>
       </c>
-      <c r="F35" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G35" s="5" t="inlineStr"/>
-      <c r="H35" s="5" t="inlineStr">
-        <is>
-          <t>0/33</t>
-        </is>
-      </c>
-      <c r="I35" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>28/33</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -3782,45 +3790,49 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B62" s="5" t="inlineStr">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
         <is>
           <t>A1-B1</t>
         </is>
       </c>
-      <c r="C62" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D62" s="5" t="inlineStr">
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E62" s="5" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>06/06/2026</t>
         </is>
       </c>
-      <c r="F62" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G62" s="5" t="inlineStr"/>
-      <c r="H62" s="5" t="inlineStr">
-        <is>
-          <t>0/34</t>
-        </is>
-      </c>
-      <c r="I62" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>28/34</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -4959,45 +4971,49 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B89" s="5" t="inlineStr">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
         <is>
           <t>A1-B2</t>
         </is>
       </c>
-      <c r="C89" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D89" s="5" t="inlineStr">
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E89" s="5" t="inlineStr">
+      <c r="E89" s="2" t="inlineStr">
         <is>
           <t>06/06/2026</t>
         </is>
       </c>
-      <c r="F89" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G89" s="5" t="inlineStr"/>
-      <c r="H89" s="5" t="inlineStr">
-        <is>
-          <t>0/34</t>
-        </is>
-      </c>
-      <c r="I89" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>28/34</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -6136,45 +6152,49 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B116" s="5" t="inlineStr">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
         <is>
           <t>A1-C1</t>
         </is>
       </c>
-      <c r="C116" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D116" s="5" t="inlineStr">
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E116" s="5" t="inlineStr">
+      <c r="E116" s="2" t="inlineStr">
         <is>
           <t>06/06/2026</t>
         </is>
       </c>
-      <c r="F116" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G116" s="5" t="inlineStr"/>
-      <c r="H116" s="5" t="inlineStr">
-        <is>
-          <t>0/34</t>
-        </is>
-      </c>
-      <c r="I116" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H116" s="2" t="inlineStr">
+        <is>
+          <t>27/34</t>
+        </is>
+      </c>
+      <c r="I116" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -7313,45 +7333,49 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B143" s="5" t="inlineStr">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
         <is>
           <t>A1-C2</t>
         </is>
       </c>
-      <c r="C143" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D143" s="5" t="inlineStr">
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E143" s="5" t="inlineStr">
+      <c r="E143" s="2" t="inlineStr">
         <is>
           <t>06/06/2026</t>
         </is>
       </c>
-      <c r="F143" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G143" s="5" t="inlineStr"/>
-      <c r="H143" s="5" t="inlineStr">
-        <is>
-          <t>0/33</t>
-        </is>
-      </c>
-      <c r="I143" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F143" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G143" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H143" s="2" t="inlineStr">
+        <is>
+          <t>25/33</t>
+        </is>
+      </c>
+      <c r="I143" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A1_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A1_session_analysis.xlsx
@@ -806,7 +806,7 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
     </row>
     <row r="7">
@@ -916,49 +916,53 @@
         </is>
       </c>
       <c r="L8" s="4" t="n">
-        <v>246</v>
+        <v>240</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>A1-A1</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E9" s="6" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>07/06/2026</t>
         </is>
       </c>
-      <c r="F9" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G9" s="6" t="inlineStr"/>
-      <c r="H9" s="6" t="inlineStr">
-        <is>
-          <t>0/34</t>
-        </is>
-      </c>
-      <c r="I9" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>24/34</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
       <c r="K9" s="4" t="inlineStr">
@@ -968,7 +972,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>20.4%</t>
         </is>
       </c>
     </row>
@@ -1021,7 +1025,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>62.9%</t>
+          <t>64.7%</t>
         </is>
       </c>
     </row>
@@ -1306,22 +1310,22 @@
         <v>27</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P15" s="4" t="n">
         <v>2</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="R15" s="4" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>57.4%</t>
         </is>
       </c>
     </row>
@@ -1384,22 +1388,22 @@
         <v>27</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P16" s="4" t="n">
         <v>2</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="R16" s="4" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>52.7%</t>
+          <t>59.6%</t>
         </is>
       </c>
     </row>
@@ -1462,22 +1466,22 @@
         <v>27</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P17" s="4" t="n">
         <v>2</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="R17" s="4" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>68.8%</t>
+          <t>72.5%</t>
         </is>
       </c>
     </row>
@@ -1540,22 +1544,22 @@
         <v>27</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P18" s="4" t="n">
         <v>2</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="R18" s="4" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>64.2%</t>
         </is>
       </c>
     </row>
@@ -1618,22 +1622,22 @@
         <v>27</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P19" s="4" t="n">
         <v>2</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="R19" s="4" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>70.1%</t>
         </is>
       </c>
     </row>
@@ -1696,22 +1700,22 @@
         <v>27</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P20" s="4" t="n">
         <v>2</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="R20" s="4" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>50.9%</t>
+          <t>53.5%</t>
         </is>
       </c>
     </row>
@@ -2656,45 +2660,49 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B36" s="6" t="inlineStr">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>A1-A2</t>
         </is>
       </c>
-      <c r="C36" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D36" s="6" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E36" s="6" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>07/06/2026</t>
         </is>
       </c>
-      <c r="F36" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G36" s="6" t="inlineStr"/>
-      <c r="H36" s="6" t="inlineStr">
-        <is>
-          <t>0/33</t>
-        </is>
-      </c>
-      <c r="I36" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>31/33</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -3837,45 +3845,49 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B63" s="6" t="inlineStr">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
         <is>
           <t>A1-B1</t>
         </is>
       </c>
-      <c r="C63" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D63" s="6" t="inlineStr">
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E63" s="6" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>07/06/2026</t>
         </is>
       </c>
-      <c r="F63" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G63" s="6" t="inlineStr"/>
-      <c r="H63" s="6" t="inlineStr">
-        <is>
-          <t>0/34</t>
-        </is>
-      </c>
-      <c r="I63" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>31/34</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -5018,45 +5030,49 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B90" s="6" t="inlineStr">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
         <is>
           <t>A1-B2</t>
         </is>
       </c>
-      <c r="C90" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D90" s="6" t="inlineStr">
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E90" s="6" t="inlineStr">
+      <c r="E90" s="2" t="inlineStr">
         <is>
           <t>07/06/2026</t>
         </is>
       </c>
-      <c r="F90" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G90" s="6" t="inlineStr"/>
-      <c r="H90" s="6" t="inlineStr">
-        <is>
-          <t>0/34</t>
-        </is>
-      </c>
-      <c r="I90" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>29/34</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -6199,45 +6215,49 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B117" s="6" t="inlineStr">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
         <is>
           <t>A1-C1</t>
         </is>
       </c>
-      <c r="C117" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D117" s="6" t="inlineStr">
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E117" s="6" t="inlineStr">
+      <c r="E117" s="2" t="inlineStr">
         <is>
           <t>07/06/2026</t>
         </is>
       </c>
-      <c r="F117" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G117" s="6" t="inlineStr"/>
-      <c r="H117" s="6" t="inlineStr">
-        <is>
-          <t>0/34</t>
-        </is>
-      </c>
-      <c r="I117" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H117" s="2" t="inlineStr">
+        <is>
+          <t>30/34</t>
+        </is>
+      </c>
+      <c r="I117" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -7380,45 +7400,49 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B144" s="6" t="inlineStr">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
         <is>
           <t>A1-C2</t>
         </is>
       </c>
-      <c r="C144" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D144" s="6" t="inlineStr">
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E144" s="6" t="inlineStr">
+      <c r="E144" s="2" t="inlineStr">
         <is>
           <t>07/06/2026</t>
         </is>
       </c>
-      <c r="F144" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G144" s="6" t="inlineStr"/>
-      <c r="H144" s="6" t="inlineStr">
-        <is>
-          <t>0/33</t>
-        </is>
-      </c>
-      <c r="I144" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F144" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G144" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H144" s="2" t="inlineStr">
+        <is>
+          <t>22/33</t>
+        </is>
+      </c>
+      <c r="I144" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A1_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A1_session_analysis.xlsx
@@ -806,7 +806,7 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
     </row>
     <row r="7">
@@ -916,7 +916,7 @@
         </is>
       </c>
       <c r="L8" s="4" t="n">
-        <v>240</v>
+        <v>234</v>
       </c>
     </row>
     <row r="9">
@@ -972,50 +972,54 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>20.4%</t>
+          <t>22.2%</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>A1-A1</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="E10" s="6" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>08/06/2026</t>
         </is>
       </c>
-      <c r="F10" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G10" s="6" t="inlineStr"/>
-      <c r="H10" s="6" t="inlineStr">
-        <is>
-          <t>0/34</t>
-        </is>
-      </c>
-      <c r="I10" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>7/34</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
       <c r="K10" s="4" t="inlineStr">
@@ -1025,7 +1029,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>64.7%</t>
+          <t>64.3%</t>
         </is>
       </c>
     </row>
@@ -1310,22 +1314,22 @@
         <v>27</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P15" s="4" t="n">
         <v>2</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="R15" s="4" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>52.1%</t>
         </is>
       </c>
     </row>
@@ -1388,22 +1392,22 @@
         <v>27</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P16" s="4" t="n">
         <v>2</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="R16" s="4" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>59.6%</t>
+          <t>56.7%</t>
         </is>
       </c>
     </row>
@@ -1466,22 +1470,22 @@
         <v>27</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P17" s="4" t="n">
         <v>2</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="R17" s="4" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>72.5%</t>
+          <t>71.4%</t>
         </is>
       </c>
     </row>
@@ -1544,22 +1548,22 @@
         <v>27</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P18" s="4" t="n">
         <v>2</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="R18" s="4" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>64.2%</t>
+          <t>66.8%</t>
         </is>
       </c>
     </row>
@@ -1622,22 +1626,22 @@
         <v>27</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P19" s="4" t="n">
         <v>2</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="R19" s="4" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>70.1%</t>
+          <t>71.4%</t>
         </is>
       </c>
     </row>
@@ -1700,22 +1704,22 @@
         <v>27</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P20" s="4" t="n">
         <v>2</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="R20" s="4" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>53.5%</t>
+          <t>56.3%</t>
         </is>
       </c>
     </row>
@@ -2707,45 +2711,49 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B37" s="6" t="inlineStr">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>A1-A2</t>
         </is>
       </c>
-      <c r="C37" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D37" s="6" t="inlineStr">
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="E37" s="6" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>08/06/2026</t>
         </is>
       </c>
-      <c r="F37" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G37" s="6" t="inlineStr"/>
-      <c r="H37" s="6" t="inlineStr">
-        <is>
-          <t>0/33</t>
-        </is>
-      </c>
-      <c r="I37" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>13/33</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -3892,45 +3900,49 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B64" s="6" t="inlineStr">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
         <is>
           <t>A1-B1</t>
         </is>
       </c>
-      <c r="C64" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D64" s="6" t="inlineStr">
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="E64" s="6" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>08/06/2026</t>
         </is>
       </c>
-      <c r="F64" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G64" s="6" t="inlineStr"/>
-      <c r="H64" s="6" t="inlineStr">
-        <is>
-          <t>0/34</t>
-        </is>
-      </c>
-      <c r="I64" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>22/34</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -5077,45 +5089,49 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B91" s="6" t="inlineStr">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
         <is>
           <t>A1-B2</t>
         </is>
       </c>
-      <c r="C91" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D91" s="6" t="inlineStr">
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="E91" s="6" t="inlineStr">
+      <c r="E91" s="2" t="inlineStr">
         <is>
           <t>08/06/2026</t>
         </is>
       </c>
-      <c r="F91" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G91" s="6" t="inlineStr"/>
-      <c r="H91" s="6" t="inlineStr">
-        <is>
-          <t>0/34</t>
-        </is>
-      </c>
-      <c r="I91" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>28/34</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -6262,45 +6278,49 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B118" s="6" t="inlineStr">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
         <is>
           <t>A1-C1</t>
         </is>
       </c>
-      <c r="C118" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D118" s="6" t="inlineStr">
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="E118" s="6" t="inlineStr">
+      <c r="E118" s="2" t="inlineStr">
         <is>
           <t>08/06/2026</t>
         </is>
       </c>
-      <c r="F118" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G118" s="6" t="inlineStr"/>
-      <c r="H118" s="6" t="inlineStr">
-        <is>
-          <t>0/34</t>
-        </is>
-      </c>
-      <c r="I118" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G118" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H118" s="2" t="inlineStr">
+        <is>
+          <t>27/34</t>
+        </is>
+      </c>
+      <c r="I118" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -7447,45 +7467,49 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B145" s="6" t="inlineStr">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
         <is>
           <t>A1-C2</t>
         </is>
       </c>
-      <c r="C145" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D145" s="6" t="inlineStr">
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="E145" s="6" t="inlineStr">
+      <c r="E145" s="2" t="inlineStr">
         <is>
           <t>08/06/2026</t>
         </is>
       </c>
-      <c r="F145" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G145" s="6" t="inlineStr"/>
-      <c r="H145" s="6" t="inlineStr">
-        <is>
-          <t>0/33</t>
-        </is>
-      </c>
-      <c r="I145" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F145" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G145" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H145" s="2" t="inlineStr">
+        <is>
+          <t>24/33</t>
+        </is>
+      </c>
+      <c r="I145" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A1_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A1_session_analysis.xlsx
@@ -806,7 +806,7 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>72</v>
+        <v>78</v>
       </c>
     </row>
     <row r="7">
@@ -916,7 +916,7 @@
         </is>
       </c>
       <c r="L8" s="4" t="n">
-        <v>234</v>
+        <v>228</v>
       </c>
     </row>
     <row r="9">
@@ -972,7 +972,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>24.1%</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1029,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>64.3%</t>
+          <t>65.1%</t>
         </is>
       </c>
     </row>
@@ -1782,22 +1782,22 @@
         <v>27</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P21" s="4" t="n">
         <v>1</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="R21" s="4" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>59.5%</t>
         </is>
       </c>
     </row>
@@ -1860,22 +1860,22 @@
         <v>27</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P22" s="4" t="n">
         <v>1</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="R22" s="4" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>62.9%</t>
+          <t>65.2%</t>
         </is>
       </c>
     </row>
@@ -1938,17 +1938,17 @@
         <v>27</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P23" s="4" t="n">
         <v>1</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="R23" s="4" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="S23" s="4" t="inlineStr">
@@ -2016,22 +2016,22 @@
         <v>27</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P24" s="4" t="n">
         <v>1</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="R24" s="4" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>65.4%</t>
         </is>
       </c>
     </row>
@@ -2094,22 +2094,22 @@
         <v>27</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P25" s="4" t="n">
         <v>1</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="R25" s="4" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>76.3%</t>
+          <t>75.9%</t>
         </is>
       </c>
     </row>
@@ -2172,22 +2172,22 @@
         <v>27</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P26" s="4" t="n">
         <v>1</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="R26" s="4" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>68.7%</t>
+          <t>69.2%</t>
         </is>
       </c>
     </row>
@@ -8566,45 +8566,49 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B170" s="6" t="inlineStr">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
         <is>
           <t>A1-D1</t>
         </is>
       </c>
-      <c r="C170" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D170" s="6" t="inlineStr">
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E170" s="6" t="inlineStr">
+      <c r="E170" s="2" t="inlineStr">
         <is>
           <t>09/06/2026</t>
         </is>
       </c>
-      <c r="F170" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G170" s="6" t="inlineStr"/>
-      <c r="H170" s="6" t="inlineStr">
-        <is>
-          <t>0/35</t>
-        </is>
-      </c>
-      <c r="I170" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F170" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G170" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H170" s="2" t="inlineStr">
+        <is>
+          <t>27/35</t>
+        </is>
+      </c>
+      <c r="I170" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -9747,45 +9751,49 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B197" s="6" t="inlineStr">
+      <c r="A197" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B197" s="2" t="inlineStr">
         <is>
           <t>A1-D2</t>
         </is>
       </c>
-      <c r="C197" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D197" s="6" t="inlineStr">
+      <c r="C197" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D197" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E197" s="6" t="inlineStr">
+      <c r="E197" s="2" t="inlineStr">
         <is>
           <t>09/06/2026</t>
         </is>
       </c>
-      <c r="F197" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G197" s="6" t="inlineStr"/>
-      <c r="H197" s="6" t="inlineStr">
-        <is>
-          <t>0/34</t>
-        </is>
-      </c>
-      <c r="I197" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F197" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G197" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H197" s="2" t="inlineStr">
+        <is>
+          <t>26/34</t>
+        </is>
+      </c>
+      <c r="I197" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -10928,45 +10936,49 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B224" s="6" t="inlineStr">
+      <c r="A224" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B224" s="2" t="inlineStr">
         <is>
           <t>A1-E1</t>
         </is>
       </c>
-      <c r="C224" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D224" s="6" t="inlineStr">
+      <c r="C224" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D224" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E224" s="6" t="inlineStr">
+      <c r="E224" s="2" t="inlineStr">
         <is>
           <t>09/06/2026</t>
         </is>
       </c>
-      <c r="F224" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G224" s="6" t="inlineStr"/>
-      <c r="H224" s="6" t="inlineStr">
-        <is>
-          <t>0/38</t>
-        </is>
-      </c>
-      <c r="I224" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F224" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G224" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H224" s="2" t="inlineStr">
+        <is>
+          <t>28/38</t>
+        </is>
+      </c>
+      <c r="I224" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -12109,45 +12121,49 @@
       </c>
     </row>
     <row r="251">
-      <c r="A251" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B251" s="6" t="inlineStr">
+      <c r="A251" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B251" s="2" t="inlineStr">
         <is>
           <t>A1-E2</t>
         </is>
       </c>
-      <c r="C251" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D251" s="6" t="inlineStr">
+      <c r="C251" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D251" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E251" s="6" t="inlineStr">
+      <c r="E251" s="2" t="inlineStr">
         <is>
           <t>09/06/2026</t>
         </is>
       </c>
-      <c r="F251" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G251" s="6" t="inlineStr"/>
-      <c r="H251" s="6" t="inlineStr">
-        <is>
-          <t>0/39</t>
-        </is>
-      </c>
-      <c r="I251" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F251" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G251" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H251" s="2" t="inlineStr">
+        <is>
+          <t>29/39</t>
+        </is>
+      </c>
+      <c r="I251" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -13290,45 +13306,49 @@
       </c>
     </row>
     <row r="278">
-      <c r="A278" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B278" s="6" t="inlineStr">
+      <c r="A278" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B278" s="2" t="inlineStr">
         <is>
           <t>A1-F1</t>
         </is>
       </c>
-      <c r="C278" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D278" s="6" t="inlineStr">
+      <c r="C278" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D278" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E278" s="6" t="inlineStr">
+      <c r="E278" s="2" t="inlineStr">
         <is>
           <t>09/06/2026</t>
         </is>
       </c>
-      <c r="F278" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G278" s="6" t="inlineStr"/>
-      <c r="H278" s="6" t="inlineStr">
-        <is>
-          <t>0/38</t>
-        </is>
-      </c>
-      <c r="I278" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F278" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G278" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H278" s="2" t="inlineStr">
+        <is>
+          <t>28/38</t>
+        </is>
+      </c>
+      <c r="I278" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -14471,45 +14491,49 @@
       </c>
     </row>
     <row r="305">
-      <c r="A305" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B305" s="6" t="inlineStr">
+      <c r="A305" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B305" s="2" t="inlineStr">
         <is>
           <t>A1-F2</t>
         </is>
       </c>
-      <c r="C305" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D305" s="6" t="inlineStr">
+      <c r="C305" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D305" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E305" s="6" t="inlineStr">
+      <c r="E305" s="2" t="inlineStr">
         <is>
           <t>09/06/2026</t>
         </is>
       </c>
-      <c r="F305" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G305" s="6" t="inlineStr"/>
-      <c r="H305" s="6" t="inlineStr">
-        <is>
-          <t>0/39</t>
-        </is>
-      </c>
-      <c r="I305" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F305" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G305" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H305" s="2" t="inlineStr">
+        <is>
+          <t>28/39</t>
+        </is>
+      </c>
+      <c r="I305" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A1_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A1_session_analysis.xlsx
@@ -806,7 +806,7 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>78</v>
+        <v>84</v>
       </c>
     </row>
     <row r="7">
@@ -916,7 +916,7 @@
         </is>
       </c>
       <c r="L8" s="4" t="n">
-        <v>228</v>
+        <v>222</v>
       </c>
     </row>
     <row r="9">
@@ -972,7 +972,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>24.1%</t>
+          <t>25.9%</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1029,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>65.1%</t>
+          <t>65.7%</t>
         </is>
       </c>
     </row>
@@ -1782,22 +1782,22 @@
         <v>27</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P21" s="4" t="n">
         <v>1</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="R21" s="4" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>59.5%</t>
+          <t>62.0%</t>
         </is>
       </c>
     </row>
@@ -1860,22 +1860,22 @@
         <v>27</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P22" s="4" t="n">
         <v>1</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="R22" s="4" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>65.2%</t>
+          <t>68.5%</t>
         </is>
       </c>
     </row>
@@ -1938,22 +1938,22 @@
         <v>27</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P23" s="4" t="n">
         <v>1</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="R23" s="4" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>73.7%</t>
+          <t>74.1%</t>
         </is>
       </c>
     </row>
@@ -2016,22 +2016,22 @@
         <v>27</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P24" s="4" t="n">
         <v>1</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="R24" s="4" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>65.4%</t>
+          <t>64.5%</t>
         </is>
       </c>
     </row>
@@ -2094,17 +2094,17 @@
         <v>27</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P25" s="4" t="n">
         <v>1</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="R25" s="4" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="S25" s="4" t="inlineStr">
@@ -2172,22 +2172,22 @@
         <v>27</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P26" s="4" t="n">
         <v>1</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="R26" s="4" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>69.2%</t>
+          <t>68.5%</t>
         </is>
       </c>
     </row>
@@ -8613,45 +8613,49 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B171" s="6" t="inlineStr">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
         <is>
           <t>A1-D1</t>
         </is>
       </c>
-      <c r="C171" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D171" s="6" t="inlineStr">
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E171" s="6" t="inlineStr">
+      <c r="E171" s="2" t="inlineStr">
         <is>
           <t>10/06/2026</t>
         </is>
       </c>
-      <c r="F171" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G171" s="6" t="inlineStr"/>
-      <c r="H171" s="6" t="inlineStr">
-        <is>
-          <t>0/35</t>
-        </is>
-      </c>
-      <c r="I171" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F171" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G171" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H171" s="2" t="inlineStr">
+        <is>
+          <t>27/35</t>
+        </is>
+      </c>
+      <c r="I171" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -9798,45 +9802,49 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B198" s="6" t="inlineStr">
+      <c r="A198" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B198" s="2" t="inlineStr">
         <is>
           <t>A1-D2</t>
         </is>
       </c>
-      <c r="C198" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D198" s="6" t="inlineStr">
+      <c r="C198" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D198" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E198" s="6" t="inlineStr">
+      <c r="E198" s="2" t="inlineStr">
         <is>
           <t>10/06/2026</t>
         </is>
       </c>
-      <c r="F198" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G198" s="6" t="inlineStr"/>
-      <c r="H198" s="6" t="inlineStr">
-        <is>
-          <t>0/34</t>
-        </is>
-      </c>
-      <c r="I198" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F198" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G198" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H198" s="2" t="inlineStr">
+        <is>
+          <t>30/34</t>
+        </is>
+      </c>
+      <c r="I198" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -10983,45 +10991,49 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B225" s="6" t="inlineStr">
+      <c r="A225" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B225" s="2" t="inlineStr">
         <is>
           <t>A1-E1</t>
         </is>
       </c>
-      <c r="C225" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D225" s="6" t="inlineStr">
+      <c r="C225" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D225" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E225" s="6" t="inlineStr">
+      <c r="E225" s="2" t="inlineStr">
         <is>
           <t>10/06/2026</t>
         </is>
       </c>
-      <c r="F225" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G225" s="6" t="inlineStr"/>
-      <c r="H225" s="6" t="inlineStr">
-        <is>
-          <t>0/38</t>
-        </is>
-      </c>
-      <c r="I225" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F225" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G225" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H225" s="2" t="inlineStr">
+        <is>
+          <t>29/38</t>
+        </is>
+      </c>
+      <c r="I225" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -12168,45 +12180,49 @@
       </c>
     </row>
     <row r="252">
-      <c r="A252" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B252" s="6" t="inlineStr">
+      <c r="A252" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B252" s="2" t="inlineStr">
         <is>
           <t>A1-E2</t>
         </is>
       </c>
-      <c r="C252" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D252" s="6" t="inlineStr">
+      <c r="C252" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D252" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E252" s="6" t="inlineStr">
+      <c r="E252" s="2" t="inlineStr">
         <is>
           <t>10/06/2026</t>
         </is>
       </c>
-      <c r="F252" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G252" s="6" t="inlineStr"/>
-      <c r="H252" s="6" t="inlineStr">
-        <is>
-          <t>0/39</t>
-        </is>
-      </c>
-      <c r="I252" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F252" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G252" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H252" s="2" t="inlineStr">
+        <is>
+          <t>23/39</t>
+        </is>
+      </c>
+      <c r="I252" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -13353,45 +13369,49 @@
       </c>
     </row>
     <row r="279">
-      <c r="A279" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B279" s="6" t="inlineStr">
+      <c r="A279" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B279" s="2" t="inlineStr">
         <is>
           <t>A1-F1</t>
         </is>
       </c>
-      <c r="C279" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D279" s="6" t="inlineStr">
+      <c r="C279" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D279" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E279" s="6" t="inlineStr">
+      <c r="E279" s="2" t="inlineStr">
         <is>
           <t>10/06/2026</t>
         </is>
       </c>
-      <c r="F279" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G279" s="6" t="inlineStr"/>
-      <c r="H279" s="6" t="inlineStr">
-        <is>
-          <t>0/38</t>
-        </is>
-      </c>
-      <c r="I279" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F279" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G279" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H279" s="2" t="inlineStr">
+        <is>
+          <t>29/38</t>
+        </is>
+      </c>
+      <c r="I279" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -14538,45 +14558,49 @@
       </c>
     </row>
     <row r="306">
-      <c r="A306" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B306" s="6" t="inlineStr">
+      <c r="A306" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B306" s="2" t="inlineStr">
         <is>
           <t>A1-F2</t>
         </is>
       </c>
-      <c r="C306" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D306" s="6" t="inlineStr">
+      <c r="C306" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D306" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E306" s="6" t="inlineStr">
+      <c r="E306" s="2" t="inlineStr">
         <is>
           <t>10/06/2026</t>
         </is>
       </c>
-      <c r="F306" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G306" s="6" t="inlineStr"/>
-      <c r="H306" s="6" t="inlineStr">
-        <is>
-          <t>0/39</t>
-        </is>
-      </c>
-      <c r="I306" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F306" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G306" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H306" s="2" t="inlineStr">
+        <is>
+          <t>25/39</t>
+        </is>
+      </c>
+      <c r="I306" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A1_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A1_session_analysis.xlsx
@@ -861,7 +861,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8">
@@ -916,7 +916,7 @@
         </is>
       </c>
       <c r="L8" s="4" t="n">
-        <v>222</v>
+        <v>216</v>
       </c>
     </row>
     <row r="9">
@@ -1785,10 +1785,10 @@
         <v>7</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="R21" s="4" t="inlineStr">
         <is>
@@ -1863,10 +1863,10 @@
         <v>7</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="R22" s="4" t="inlineStr">
         <is>
@@ -1941,10 +1941,10 @@
         <v>7</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="R23" s="4" t="inlineStr">
         <is>
@@ -2019,10 +2019,10 @@
         <v>7</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="R24" s="4" t="inlineStr">
         <is>
@@ -2097,10 +2097,10 @@
         <v>7</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="R25" s="4" t="inlineStr">
         <is>
@@ -2175,10 +2175,10 @@
         <v>7</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="R26" s="4" t="inlineStr">
         <is>
@@ -8660,45 +8660,45 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B172" s="6" t="inlineStr">
+      <c r="A172" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B172" s="5" t="inlineStr">
         <is>
           <t>A1-D1</t>
         </is>
       </c>
-      <c r="C172" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D172" s="6" t="inlineStr">
+      <c r="C172" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D172" s="5" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="E172" s="6" t="inlineStr">
+      <c r="E172" s="5" t="inlineStr">
         <is>
           <t>11/06/2026</t>
         </is>
       </c>
-      <c r="F172" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G172" s="6" t="inlineStr"/>
-      <c r="H172" s="6" t="inlineStr">
+      <c r="F172" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G172" s="5" t="inlineStr"/>
+      <c r="H172" s="5" t="inlineStr">
         <is>
           <t>0/35</t>
         </is>
       </c>
-      <c r="I172" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I172" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -9849,45 +9849,45 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B199" s="6" t="inlineStr">
+      <c r="A199" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B199" s="5" t="inlineStr">
         <is>
           <t>A1-D2</t>
         </is>
       </c>
-      <c r="C199" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D199" s="6" t="inlineStr">
+      <c r="C199" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D199" s="5" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="E199" s="6" t="inlineStr">
+      <c r="E199" s="5" t="inlineStr">
         <is>
           <t>11/06/2026</t>
         </is>
       </c>
-      <c r="F199" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G199" s="6" t="inlineStr"/>
-      <c r="H199" s="6" t="inlineStr">
+      <c r="F199" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G199" s="5" t="inlineStr"/>
+      <c r="H199" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I199" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I199" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -11038,45 +11038,45 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B226" s="6" t="inlineStr">
+      <c r="A226" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B226" s="5" t="inlineStr">
         <is>
           <t>A1-E1</t>
         </is>
       </c>
-      <c r="C226" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D226" s="6" t="inlineStr">
+      <c r="C226" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D226" s="5" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="E226" s="6" t="inlineStr">
+      <c r="E226" s="5" t="inlineStr">
         <is>
           <t>11/06/2026</t>
         </is>
       </c>
-      <c r="F226" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G226" s="6" t="inlineStr"/>
-      <c r="H226" s="6" t="inlineStr">
+      <c r="F226" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G226" s="5" t="inlineStr"/>
+      <c r="H226" s="5" t="inlineStr">
         <is>
           <t>0/38</t>
         </is>
       </c>
-      <c r="I226" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I226" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -12227,45 +12227,45 @@
       </c>
     </row>
     <row r="253">
-      <c r="A253" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B253" s="6" t="inlineStr">
+      <c r="A253" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B253" s="5" t="inlineStr">
         <is>
           <t>A1-E2</t>
         </is>
       </c>
-      <c r="C253" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D253" s="6" t="inlineStr">
+      <c r="C253" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D253" s="5" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="E253" s="6" t="inlineStr">
+      <c r="E253" s="5" t="inlineStr">
         <is>
           <t>11/06/2026</t>
         </is>
       </c>
-      <c r="F253" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G253" s="6" t="inlineStr"/>
-      <c r="H253" s="6" t="inlineStr">
+      <c r="F253" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G253" s="5" t="inlineStr"/>
+      <c r="H253" s="5" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I253" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I253" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -13416,45 +13416,45 @@
       </c>
     </row>
     <row r="280">
-      <c r="A280" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B280" s="6" t="inlineStr">
+      <c r="A280" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B280" s="5" t="inlineStr">
         <is>
           <t>A1-F1</t>
         </is>
       </c>
-      <c r="C280" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D280" s="6" t="inlineStr">
+      <c r="C280" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D280" s="5" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="E280" s="6" t="inlineStr">
+      <c r="E280" s="5" t="inlineStr">
         <is>
           <t>11/06/2026</t>
         </is>
       </c>
-      <c r="F280" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G280" s="6" t="inlineStr"/>
-      <c r="H280" s="6" t="inlineStr">
+      <c r="F280" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G280" s="5" t="inlineStr"/>
+      <c r="H280" s="5" t="inlineStr">
         <is>
           <t>0/38</t>
         </is>
       </c>
-      <c r="I280" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I280" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -14605,45 +14605,45 @@
       </c>
     </row>
     <row r="307">
-      <c r="A307" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B307" s="6" t="inlineStr">
+      <c r="A307" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B307" s="5" t="inlineStr">
         <is>
           <t>A1-F2</t>
         </is>
       </c>
-      <c r="C307" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D307" s="6" t="inlineStr">
+      <c r="C307" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D307" s="5" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="E307" s="6" t="inlineStr">
+      <c r="E307" s="5" t="inlineStr">
         <is>
           <t>11/06/2026</t>
         </is>
       </c>
-      <c r="F307" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G307" s="6" t="inlineStr"/>
-      <c r="H307" s="6" t="inlineStr">
+      <c r="F307" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G307" s="5" t="inlineStr"/>
+      <c r="H307" s="5" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I307" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I307" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A1_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A1_session_analysis.xlsx
@@ -806,7 +806,7 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>84</v>
+        <v>90</v>
       </c>
     </row>
     <row r="7">
@@ -861,7 +861,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8">
@@ -972,7 +972,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>27.8%</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1029,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>65.7%</t>
+          <t>66.1%</t>
         </is>
       </c>
     </row>
@@ -1782,22 +1782,22 @@
         <v>27</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q21" s="4" t="n">
         <v>18</v>
       </c>
       <c r="R21" s="4" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>62.0%</t>
+          <t>63.2%</t>
         </is>
       </c>
     </row>
@@ -1860,22 +1860,22 @@
         <v>27</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q22" s="4" t="n">
         <v>18</v>
       </c>
       <c r="R22" s="4" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>68.5%</t>
+          <t>70.2%</t>
         </is>
       </c>
     </row>
@@ -1938,22 +1938,22 @@
         <v>27</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q23" s="4" t="n">
         <v>18</v>
       </c>
       <c r="R23" s="4" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>74.1%</t>
+          <t>72.4%</t>
         </is>
       </c>
     </row>
@@ -2016,22 +2016,22 @@
         <v>27</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q24" s="4" t="n">
         <v>18</v>
       </c>
       <c r="R24" s="4" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>64.5%</t>
+          <t>66.0%</t>
         </is>
       </c>
     </row>
@@ -2094,22 +2094,22 @@
         <v>27</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q25" s="4" t="n">
         <v>18</v>
       </c>
       <c r="R25" s="4" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>75.9%</t>
+          <t>75.7%</t>
         </is>
       </c>
     </row>
@@ -2172,22 +2172,22 @@
         <v>27</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q26" s="4" t="n">
         <v>18</v>
       </c>
       <c r="R26" s="4" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>68.5%</t>
+          <t>68.3%</t>
         </is>
       </c>
     </row>
@@ -8660,45 +8660,49 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B172" s="5" t="inlineStr">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
         <is>
           <t>A1-D1</t>
         </is>
       </c>
-      <c r="C172" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D172" s="5" t="inlineStr">
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="E172" s="5" t="inlineStr">
+      <c r="E172" s="2" t="inlineStr">
         <is>
           <t>11/06/2026</t>
         </is>
       </c>
-      <c r="F172" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G172" s="5" t="inlineStr"/>
-      <c r="H172" s="5" t="inlineStr">
-        <is>
-          <t>0/35</t>
-        </is>
-      </c>
-      <c r="I172" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F172" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G172" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H172" s="2" t="inlineStr">
+        <is>
+          <t>25/35</t>
+        </is>
+      </c>
+      <c r="I172" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -9849,45 +9853,49 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B199" s="5" t="inlineStr">
+      <c r="A199" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B199" s="2" t="inlineStr">
         <is>
           <t>A1-D2</t>
         </is>
       </c>
-      <c r="C199" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D199" s="5" t="inlineStr">
+      <c r="C199" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D199" s="2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="E199" s="5" t="inlineStr">
+      <c r="E199" s="2" t="inlineStr">
         <is>
           <t>11/06/2026</t>
         </is>
       </c>
-      <c r="F199" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G199" s="5" t="inlineStr"/>
-      <c r="H199" s="5" t="inlineStr">
-        <is>
-          <t>0/34</t>
-        </is>
-      </c>
-      <c r="I199" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F199" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G199" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H199" s="2" t="inlineStr">
+        <is>
+          <t>28/34</t>
+        </is>
+      </c>
+      <c r="I199" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -11038,45 +11046,49 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B226" s="5" t="inlineStr">
+      <c r="A226" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B226" s="2" t="inlineStr">
         <is>
           <t>A1-E1</t>
         </is>
       </c>
-      <c r="C226" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D226" s="5" t="inlineStr">
+      <c r="C226" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D226" s="2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="E226" s="5" t="inlineStr">
+      <c r="E226" s="2" t="inlineStr">
         <is>
           <t>11/06/2026</t>
         </is>
       </c>
-      <c r="F226" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G226" s="5" t="inlineStr"/>
-      <c r="H226" s="5" t="inlineStr">
-        <is>
-          <t>0/38</t>
-        </is>
-      </c>
-      <c r="I226" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F226" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G226" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H226" s="2" t="inlineStr">
+        <is>
+          <t>23/38</t>
+        </is>
+      </c>
+      <c r="I226" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -12227,45 +12239,49 @@
       </c>
     </row>
     <row r="253">
-      <c r="A253" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B253" s="5" t="inlineStr">
+      <c r="A253" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B253" s="2" t="inlineStr">
         <is>
           <t>A1-E2</t>
         </is>
       </c>
-      <c r="C253" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D253" s="5" t="inlineStr">
+      <c r="C253" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D253" s="2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="E253" s="5" t="inlineStr">
+      <c r="E253" s="2" t="inlineStr">
         <is>
           <t>11/06/2026</t>
         </is>
       </c>
-      <c r="F253" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G253" s="5" t="inlineStr"/>
-      <c r="H253" s="5" t="inlineStr">
-        <is>
-          <t>0/39</t>
-        </is>
-      </c>
-      <c r="I253" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F253" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G253" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H253" s="2" t="inlineStr">
+        <is>
+          <t>30/39</t>
+        </is>
+      </c>
+      <c r="I253" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -13416,45 +13432,49 @@
       </c>
     </row>
     <row r="280">
-      <c r="A280" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B280" s="5" t="inlineStr">
+      <c r="A280" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B280" s="2" t="inlineStr">
         <is>
           <t>A1-F1</t>
         </is>
       </c>
-      <c r="C280" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D280" s="5" t="inlineStr">
+      <c r="C280" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D280" s="2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="E280" s="5" t="inlineStr">
+      <c r="E280" s="2" t="inlineStr">
         <is>
           <t>11/06/2026</t>
         </is>
       </c>
-      <c r="F280" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G280" s="5" t="inlineStr"/>
-      <c r="H280" s="5" t="inlineStr">
-        <is>
-          <t>0/38</t>
-        </is>
-      </c>
-      <c r="I280" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F280" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G280" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H280" s="2" t="inlineStr">
+        <is>
+          <t>28/38</t>
+        </is>
+      </c>
+      <c r="I280" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -14605,45 +14625,49 @@
       </c>
     </row>
     <row r="307">
-      <c r="A307" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B307" s="5" t="inlineStr">
+      <c r="A307" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B307" s="2" t="inlineStr">
         <is>
           <t>A1-F2</t>
         </is>
       </c>
-      <c r="C307" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D307" s="5" t="inlineStr">
+      <c r="C307" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D307" s="2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="E307" s="5" t="inlineStr">
+      <c r="E307" s="2" t="inlineStr">
         <is>
           <t>11/06/2026</t>
         </is>
       </c>
-      <c r="F307" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G307" s="5" t="inlineStr"/>
-      <c r="H307" s="5" t="inlineStr">
-        <is>
-          <t>0/39</t>
-        </is>
-      </c>
-      <c r="I307" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F307" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G307" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H307" s="2" t="inlineStr">
+        <is>
+          <t>26/39</t>
+        </is>
+      </c>
+      <c r="I307" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A1_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A1_session_analysis.xlsx
@@ -861,7 +861,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8">
@@ -916,7 +916,7 @@
         </is>
       </c>
       <c r="L8" s="4" t="n">
-        <v>216</v>
+        <v>210</v>
       </c>
     </row>
     <row r="9">
@@ -1034,45 +1034,45 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>A1-A1</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E11" s="6" t="inlineStr">
+      <c r="E11" s="5" t="inlineStr">
         <is>
           <t>13/06/2026</t>
         </is>
       </c>
-      <c r="F11" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G11" s="6" t="inlineStr"/>
-      <c r="H11" s="6" t="inlineStr">
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr"/>
+      <c r="H11" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I11" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -1317,10 +1317,10 @@
         <v>7</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="R15" s="4" t="inlineStr">
         <is>
@@ -1395,10 +1395,10 @@
         <v>7</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="R16" s="4" t="inlineStr">
         <is>
@@ -1473,10 +1473,10 @@
         <v>7</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="R17" s="4" t="inlineStr">
         <is>
@@ -1551,10 +1551,10 @@
         <v>7</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="R18" s="4" t="inlineStr">
         <is>
@@ -1629,10 +1629,10 @@
         <v>7</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="R19" s="4" t="inlineStr">
         <is>
@@ -1707,10 +1707,10 @@
         <v>7</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="R20" s="4" t="inlineStr">
         <is>
@@ -2758,45 +2758,45 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B38" s="6" t="inlineStr">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
         <is>
           <t>A1-A2</t>
         </is>
       </c>
-      <c r="C38" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D38" s="6" t="inlineStr">
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E38" s="6" t="inlineStr">
+      <c r="E38" s="5" t="inlineStr">
         <is>
           <t>13/06/2026</t>
         </is>
       </c>
-      <c r="F38" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G38" s="6" t="inlineStr"/>
-      <c r="H38" s="6" t="inlineStr">
+      <c r="F38" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G38" s="5" t="inlineStr"/>
+      <c r="H38" s="5" t="inlineStr">
         <is>
           <t>0/33</t>
         </is>
       </c>
-      <c r="I38" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I38" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -3947,45 +3947,45 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B65" s="6" t="inlineStr">
+      <c r="A65" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B65" s="5" t="inlineStr">
         <is>
           <t>A1-B1</t>
         </is>
       </c>
-      <c r="C65" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D65" s="6" t="inlineStr">
+      <c r="C65" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D65" s="5" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E65" s="6" t="inlineStr">
+      <c r="E65" s="5" t="inlineStr">
         <is>
           <t>13/06/2026</t>
         </is>
       </c>
-      <c r="F65" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G65" s="6" t="inlineStr"/>
-      <c r="H65" s="6" t="inlineStr">
+      <c r="F65" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G65" s="5" t="inlineStr"/>
+      <c r="H65" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I65" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I65" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -5136,45 +5136,45 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B92" s="6" t="inlineStr">
+      <c r="A92" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B92" s="5" t="inlineStr">
         <is>
           <t>A1-B2</t>
         </is>
       </c>
-      <c r="C92" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D92" s="6" t="inlineStr">
+      <c r="C92" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D92" s="5" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E92" s="6" t="inlineStr">
+      <c r="E92" s="5" t="inlineStr">
         <is>
           <t>13/06/2026</t>
         </is>
       </c>
-      <c r="F92" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G92" s="6" t="inlineStr"/>
-      <c r="H92" s="6" t="inlineStr">
+      <c r="F92" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G92" s="5" t="inlineStr"/>
+      <c r="H92" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I92" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I92" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -6325,45 +6325,45 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B119" s="6" t="inlineStr">
+      <c r="A119" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B119" s="5" t="inlineStr">
         <is>
           <t>A1-C1</t>
         </is>
       </c>
-      <c r="C119" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D119" s="6" t="inlineStr">
+      <c r="C119" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D119" s="5" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E119" s="6" t="inlineStr">
+      <c r="E119" s="5" t="inlineStr">
         <is>
           <t>13/06/2026</t>
         </is>
       </c>
-      <c r="F119" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G119" s="6" t="inlineStr"/>
-      <c r="H119" s="6" t="inlineStr">
+      <c r="F119" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G119" s="5" t="inlineStr"/>
+      <c r="H119" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I119" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I119" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -7514,45 +7514,45 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B146" s="6" t="inlineStr">
+      <c r="A146" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B146" s="5" t="inlineStr">
         <is>
           <t>A1-C2</t>
         </is>
       </c>
-      <c r="C146" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D146" s="6" t="inlineStr">
+      <c r="C146" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D146" s="5" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E146" s="6" t="inlineStr">
+      <c r="E146" s="5" t="inlineStr">
         <is>
           <t>13/06/2026</t>
         </is>
       </c>
-      <c r="F146" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G146" s="6" t="inlineStr"/>
-      <c r="H146" s="6" t="inlineStr">
+      <c r="F146" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G146" s="5" t="inlineStr"/>
+      <c r="H146" s="5" t="inlineStr">
         <is>
           <t>0/33</t>
         </is>
       </c>
-      <c r="I146" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I146" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A1_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A1_session_analysis.xlsx
@@ -806,7 +806,7 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>90</v>
+        <v>96</v>
       </c>
     </row>
     <row r="7">
@@ -861,7 +861,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8">
@@ -972,7 +972,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>29.6%</t>
         </is>
       </c>
     </row>
@@ -1029,50 +1029,54 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>66.6%</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>A1-A1</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>13/06/2026</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G11" s="5" t="inlineStr"/>
-      <c r="H11" s="5" t="inlineStr">
-        <is>
-          <t>0/34</t>
-        </is>
-      </c>
-      <c r="I11" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>25/34</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -1314,22 +1318,22 @@
         <v>27</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q15" s="4" t="n">
         <v>17</v>
       </c>
       <c r="R15" s="4" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>52.1%</t>
+          <t>54.8%</t>
         </is>
       </c>
     </row>
@@ -1392,22 +1396,22 @@
         <v>27</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q16" s="4" t="n">
         <v>17</v>
       </c>
       <c r="R16" s="4" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>56.7%</t>
+          <t>58.0%</t>
         </is>
       </c>
     </row>
@@ -1470,22 +1474,22 @@
         <v>27</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q17" s="4" t="n">
         <v>17</v>
       </c>
       <c r="R17" s="4" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>72.4%</t>
         </is>
       </c>
     </row>
@@ -1548,22 +1552,22 @@
         <v>27</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q18" s="4" t="n">
         <v>17</v>
       </c>
       <c r="R18" s="4" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>66.8%</t>
+          <t>68.4%</t>
         </is>
       </c>
     </row>
@@ -1626,22 +1630,22 @@
         <v>27</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q19" s="4" t="n">
         <v>17</v>
       </c>
       <c r="R19" s="4" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>70.2%</t>
         </is>
       </c>
     </row>
@@ -1704,22 +1708,22 @@
         <v>27</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q20" s="4" t="n">
         <v>17</v>
       </c>
       <c r="R20" s="4" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>56.3%</t>
+          <t>59.5%</t>
         </is>
       </c>
     </row>
@@ -2758,45 +2762,49 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B38" s="5" t="inlineStr">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>A1-A2</t>
         </is>
       </c>
-      <c r="C38" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D38" s="5" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E38" s="5" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>13/06/2026</t>
         </is>
       </c>
-      <c r="F38" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G38" s="5" t="inlineStr"/>
-      <c r="H38" s="5" t="inlineStr">
-        <is>
-          <t>0/33</t>
-        </is>
-      </c>
-      <c r="I38" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>22/33</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -3947,45 +3955,49 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B65" s="5" t="inlineStr">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
         <is>
           <t>A1-B1</t>
         </is>
       </c>
-      <c r="C65" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D65" s="5" t="inlineStr">
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E65" s="5" t="inlineStr">
+      <c r="E65" s="2" t="inlineStr">
         <is>
           <t>13/06/2026</t>
         </is>
       </c>
-      <c r="F65" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G65" s="5" t="inlineStr"/>
-      <c r="H65" s="5" t="inlineStr">
-        <is>
-          <t>0/34</t>
-        </is>
-      </c>
-      <c r="I65" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>27/34</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -5136,45 +5148,49 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B92" s="5" t="inlineStr">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
         <is>
           <t>A1-B2</t>
         </is>
       </c>
-      <c r="C92" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D92" s="5" t="inlineStr">
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E92" s="5" t="inlineStr">
+      <c r="E92" s="2" t="inlineStr">
         <is>
           <t>13/06/2026</t>
         </is>
       </c>
-      <c r="F92" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G92" s="5" t="inlineStr"/>
-      <c r="H92" s="5" t="inlineStr">
-        <is>
-          <t>0/34</t>
-        </is>
-      </c>
-      <c r="I92" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>27/34</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -6325,45 +6341,49 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B119" s="5" t="inlineStr">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
         <is>
           <t>A1-C1</t>
         </is>
       </c>
-      <c r="C119" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D119" s="5" t="inlineStr">
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E119" s="5" t="inlineStr">
+      <c r="E119" s="2" t="inlineStr">
         <is>
           <t>13/06/2026</t>
         </is>
       </c>
-      <c r="F119" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G119" s="5" t="inlineStr"/>
-      <c r="H119" s="5" t="inlineStr">
-        <is>
-          <t>0/34</t>
-        </is>
-      </c>
-      <c r="I119" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F119" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G119" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H119" s="2" t="inlineStr">
+        <is>
+          <t>21/34</t>
+        </is>
+      </c>
+      <c r="I119" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -7514,45 +7534,49 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B146" s="5" t="inlineStr">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
         <is>
           <t>A1-C2</t>
         </is>
       </c>
-      <c r="C146" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D146" s="5" t="inlineStr">
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E146" s="5" t="inlineStr">
+      <c r="E146" s="2" t="inlineStr">
         <is>
           <t>13/06/2026</t>
         </is>
       </c>
-      <c r="F146" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G146" s="5" t="inlineStr"/>
-      <c r="H146" s="5" t="inlineStr">
-        <is>
-          <t>0/33</t>
-        </is>
-      </c>
-      <c r="I146" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F146" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G146" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H146" s="2" t="inlineStr">
+        <is>
+          <t>27/33</t>
+        </is>
+      </c>
+      <c r="I146" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A1_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A1_session_analysis.xlsx
@@ -708,45 +708,49 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>A1-A1</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>30/05/2026</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G5" s="5" t="inlineStr"/>
-      <c r="H5" s="5" t="inlineStr">
-        <is>
-          <t>0/34</t>
-        </is>
-      </c>
-      <c r="I5" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>32/34</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
       <c r="K5" s="4" t="inlineStr">
@@ -806,7 +810,7 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>96</v>
+        <v>101</v>
       </c>
     </row>
     <row r="7">
@@ -861,7 +865,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8">
@@ -916,7 +920,7 @@
         </is>
       </c>
       <c r="L8" s="4" t="n">
-        <v>210</v>
+        <v>204</v>
       </c>
     </row>
     <row r="9">
@@ -972,7 +976,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>31.2%</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1033,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>66.0%</t>
         </is>
       </c>
     </row>
@@ -1081,45 +1085,45 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>A1-A1</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E12" s="6" t="inlineStr">
+      <c r="E12" s="5" t="inlineStr">
         <is>
           <t>14/06/2026</t>
         </is>
       </c>
-      <c r="F12" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G12" s="6" t="inlineStr"/>
-      <c r="H12" s="6" t="inlineStr">
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr"/>
+      <c r="H12" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I12" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -1318,22 +1322,22 @@
         <v>27</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P15" s="4" t="n">
         <v>2</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="R15" s="4" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>59.2%</t>
         </is>
       </c>
     </row>
@@ -1396,22 +1400,22 @@
         <v>27</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P16" s="4" t="n">
         <v>2</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="R16" s="4" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>58.0%</t>
+          <t>61.3%</t>
         </is>
       </c>
     </row>
@@ -1474,22 +1478,22 @@
         <v>27</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P17" s="4" t="n">
         <v>2</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="R17" s="4" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>72.4%</t>
+          <t>71.2%</t>
         </is>
       </c>
     </row>
@@ -1552,22 +1556,22 @@
         <v>27</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P18" s="4" t="n">
         <v>2</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="R18" s="4" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>68.4%</t>
+          <t>63.4%</t>
         </is>
       </c>
     </row>
@@ -1630,22 +1634,22 @@
         <v>27</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P19" s="4" t="n">
         <v>2</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="R19" s="4" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>70.2%</t>
+          <t>62.7%</t>
         </is>
       </c>
     </row>
@@ -1711,10 +1715,10 @@
         <v>8</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="R20" s="4" t="inlineStr">
         <is>
@@ -2458,45 +2462,49 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B32" s="5" t="inlineStr">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>A1-A2</t>
         </is>
       </c>
-      <c r="C32" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D32" s="5" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E32" s="5" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>30/05/2026</t>
         </is>
       </c>
-      <c r="F32" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G32" s="5" t="inlineStr"/>
-      <c r="H32" s="5" t="inlineStr">
-        <is>
-          <t>0/33</t>
-        </is>
-      </c>
-      <c r="I32" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>29/33</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
       <c r="K32" s="4" t="inlineStr">
@@ -2809,45 +2817,45 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B39" s="6" t="inlineStr">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
         <is>
           <t>A1-A2</t>
         </is>
       </c>
-      <c r="C39" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D39" s="6" t="inlineStr">
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E39" s="6" t="inlineStr">
+      <c r="E39" s="5" t="inlineStr">
         <is>
           <t>14/06/2026</t>
         </is>
       </c>
-      <c r="F39" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G39" s="6" t="inlineStr"/>
-      <c r="H39" s="6" t="inlineStr">
+      <c r="F39" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G39" s="5" t="inlineStr"/>
+      <c r="H39" s="5" t="inlineStr">
         <is>
           <t>0/33</t>
         </is>
       </c>
-      <c r="I39" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I39" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -3681,45 +3689,49 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B59" s="5" t="inlineStr">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
         <is>
           <t>A1-B1</t>
         </is>
       </c>
-      <c r="C59" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D59" s="5" t="inlineStr">
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E59" s="5" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>30/05/2026</t>
         </is>
       </c>
-      <c r="F59" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G59" s="5" t="inlineStr"/>
-      <c r="H59" s="5" t="inlineStr">
-        <is>
-          <t>0/34</t>
-        </is>
-      </c>
-      <c r="I59" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>21/34</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -4002,45 +4014,45 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B66" s="6" t="inlineStr">
+      <c r="A66" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B66" s="5" t="inlineStr">
         <is>
           <t>A1-B1</t>
         </is>
       </c>
-      <c r="C66" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D66" s="6" t="inlineStr">
+      <c r="C66" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D66" s="5" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E66" s="6" t="inlineStr">
+      <c r="E66" s="5" t="inlineStr">
         <is>
           <t>14/06/2026</t>
         </is>
       </c>
-      <c r="F66" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G66" s="6" t="inlineStr"/>
-      <c r="H66" s="6" t="inlineStr">
+      <c r="F66" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G66" s="5" t="inlineStr"/>
+      <c r="H66" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I66" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I66" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -4874,45 +4886,49 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B86" s="5" t="inlineStr">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
         <is>
           <t>A1-B2</t>
         </is>
       </c>
-      <c r="C86" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D86" s="5" t="inlineStr">
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E86" s="5" t="inlineStr">
+      <c r="E86" s="2" t="inlineStr">
         <is>
           <t>30/05/2026</t>
         </is>
       </c>
-      <c r="F86" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G86" s="5" t="inlineStr"/>
-      <c r="H86" s="5" t="inlineStr">
-        <is>
-          <t>0/34</t>
-        </is>
-      </c>
-      <c r="I86" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>8/34</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -5195,45 +5211,45 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B93" s="6" t="inlineStr">
+      <c r="A93" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B93" s="5" t="inlineStr">
         <is>
           <t>A1-B2</t>
         </is>
       </c>
-      <c r="C93" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D93" s="6" t="inlineStr">
+      <c r="C93" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D93" s="5" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E93" s="6" t="inlineStr">
+      <c r="E93" s="5" t="inlineStr">
         <is>
           <t>14/06/2026</t>
         </is>
       </c>
-      <c r="F93" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G93" s="6" t="inlineStr"/>
-      <c r="H93" s="6" t="inlineStr">
+      <c r="F93" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G93" s="5" t="inlineStr"/>
+      <c r="H93" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I93" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I93" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -6067,45 +6083,49 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B113" s="5" t="inlineStr">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
         <is>
           <t>A1-C1</t>
         </is>
       </c>
-      <c r="C113" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D113" s="5" t="inlineStr">
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E113" s="5" t="inlineStr">
+      <c r="E113" s="2" t="inlineStr">
         <is>
           <t>30/05/2026</t>
         </is>
       </c>
-      <c r="F113" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G113" s="5" t="inlineStr"/>
-      <c r="H113" s="5" t="inlineStr">
-        <is>
-          <t>0/34</t>
-        </is>
-      </c>
-      <c r="I113" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G113" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H113" s="2" t="inlineStr">
+        <is>
+          <t>1/34</t>
+        </is>
+      </c>
+      <c r="I113" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -6388,45 +6408,45 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B120" s="6" t="inlineStr">
+      <c r="A120" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B120" s="5" t="inlineStr">
         <is>
           <t>A1-C1</t>
         </is>
       </c>
-      <c r="C120" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D120" s="6" t="inlineStr">
+      <c r="C120" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D120" s="5" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E120" s="6" t="inlineStr">
+      <c r="E120" s="5" t="inlineStr">
         <is>
           <t>14/06/2026</t>
         </is>
       </c>
-      <c r="F120" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G120" s="6" t="inlineStr"/>
-      <c r="H120" s="6" t="inlineStr">
+      <c r="F120" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G120" s="5" t="inlineStr"/>
+      <c r="H120" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I120" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I120" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -7581,45 +7601,45 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B147" s="6" t="inlineStr">
+      <c r="A147" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B147" s="5" t="inlineStr">
         <is>
           <t>A1-C2</t>
         </is>
       </c>
-      <c r="C147" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D147" s="6" t="inlineStr">
+      <c r="C147" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D147" s="5" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E147" s="6" t="inlineStr">
+      <c r="E147" s="5" t="inlineStr">
         <is>
           <t>14/06/2026</t>
         </is>
       </c>
-      <c r="F147" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G147" s="6" t="inlineStr"/>
-      <c r="H147" s="6" t="inlineStr">
+      <c r="F147" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G147" s="5" t="inlineStr"/>
+      <c r="H147" s="5" t="inlineStr">
         <is>
           <t>0/33</t>
         </is>
       </c>
-      <c r="I147" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I147" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A1_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A1_session_analysis.xlsx
@@ -810,7 +810,7 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>101</v>
+        <v>114</v>
       </c>
     </row>
     <row r="7">
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8">
@@ -920,7 +920,7 @@
         </is>
       </c>
       <c r="L8" s="4" t="n">
-        <v>204</v>
+        <v>198</v>
       </c>
     </row>
     <row r="9">
@@ -976,7 +976,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>35.2%</t>
         </is>
       </c>
     </row>
@@ -1033,7 +1033,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>66.0%</t>
+          <t>70.0%</t>
         </is>
       </c>
     </row>
@@ -1085,88 +1085,96 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>A1-A1</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>14/06/2026</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G12" s="5" t="inlineStr"/>
-      <c r="H12" s="5" t="inlineStr">
-        <is>
-          <t>0/34</t>
-        </is>
-      </c>
-      <c r="I12" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>31/34</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>A1-A1</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="E13" s="6" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>15/06/2026</t>
         </is>
       </c>
-      <c r="F13" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G13" s="6" t="inlineStr"/>
-      <c r="H13" s="6" t="inlineStr">
-        <is>
-          <t>0/34</t>
-        </is>
-      </c>
-      <c r="I13" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>29/34</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
@@ -1322,22 +1330,22 @@
         <v>27</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R15" s="4" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>40.7%</t>
         </is>
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>59.2%</t>
+          <t>64.4%</t>
         </is>
       </c>
     </row>
@@ -1400,22 +1408,22 @@
         <v>27</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R16" s="4" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>40.7%</t>
         </is>
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>61.3%</t>
+          <t>64.2%</t>
         </is>
       </c>
     </row>
@@ -1478,22 +1486,22 @@
         <v>27</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R17" s="4" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>40.7%</t>
         </is>
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>71.2%</t>
+          <t>77.3%</t>
         </is>
       </c>
     </row>
@@ -1556,22 +1564,22 @@
         <v>27</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R18" s="4" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>40.7%</t>
         </is>
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>63.4%</t>
+          <t>74.1%</t>
         </is>
       </c>
     </row>
@@ -1634,22 +1642,22 @@
         <v>27</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R19" s="4" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>40.7%</t>
         </is>
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>62.7%</t>
+          <t>77.0%</t>
         </is>
       </c>
     </row>
@@ -1712,22 +1720,22 @@
         <v>27</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R20" s="4" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>40.7%</t>
         </is>
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>59.5%</t>
+          <t>66.1%</t>
         </is>
       </c>
     </row>
@@ -2817,88 +2825,96 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B39" s="5" t="inlineStr">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>A1-A2</t>
         </is>
       </c>
-      <c r="C39" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D39" s="5" t="inlineStr">
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E39" s="5" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>14/06/2026</t>
         </is>
       </c>
-      <c r="F39" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G39" s="5" t="inlineStr"/>
-      <c r="H39" s="5" t="inlineStr">
-        <is>
-          <t>0/33</t>
-        </is>
-      </c>
-      <c r="I39" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>25/33</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B40" s="6" t="inlineStr">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>A1-A2</t>
         </is>
       </c>
-      <c r="C40" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D40" s="6" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="E40" s="6" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>15/06/2026</t>
         </is>
       </c>
-      <c r="F40" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G40" s="6" t="inlineStr"/>
-      <c r="H40" s="6" t="inlineStr">
-        <is>
-          <t>0/33</t>
-        </is>
-      </c>
-      <c r="I40" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>26/33</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3742,7 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>21/34</t>
+          <t>34/34</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
@@ -4014,88 +4030,96 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B66" s="5" t="inlineStr">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
         <is>
           <t>A1-B1</t>
         </is>
       </c>
-      <c r="C66" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D66" s="5" t="inlineStr">
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E66" s="5" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>14/06/2026</t>
         </is>
       </c>
-      <c r="F66" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G66" s="5" t="inlineStr"/>
-      <c r="H66" s="5" t="inlineStr">
-        <is>
-          <t>0/34</t>
-        </is>
-      </c>
-      <c r="I66" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>29/34</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B67" s="6" t="inlineStr">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
         <is>
           <t>A1-B1</t>
         </is>
       </c>
-      <c r="C67" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D67" s="6" t="inlineStr">
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="E67" s="6" t="inlineStr">
+      <c r="E67" s="2" t="inlineStr">
         <is>
           <t>15/06/2026</t>
         </is>
       </c>
-      <c r="F67" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G67" s="6" t="inlineStr"/>
-      <c r="H67" s="6" t="inlineStr">
-        <is>
-          <t>0/34</t>
-        </is>
-      </c>
-      <c r="I67" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>29/34</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -4923,7 +4947,7 @@
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>8/34</t>
+          <t>33/34</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
@@ -5211,88 +5235,96 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B93" s="5" t="inlineStr">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
         <is>
           <t>A1-B2</t>
         </is>
       </c>
-      <c r="C93" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D93" s="5" t="inlineStr">
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E93" s="5" t="inlineStr">
+      <c r="E93" s="2" t="inlineStr">
         <is>
           <t>14/06/2026</t>
         </is>
       </c>
-      <c r="F93" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G93" s="5" t="inlineStr"/>
-      <c r="H93" s="5" t="inlineStr">
-        <is>
-          <t>0/34</t>
-        </is>
-      </c>
-      <c r="I93" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>30/34</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B94" s="6" t="inlineStr">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
         <is>
           <t>A1-B2</t>
         </is>
       </c>
-      <c r="C94" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D94" s="6" t="inlineStr">
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="E94" s="6" t="inlineStr">
+      <c r="E94" s="2" t="inlineStr">
         <is>
           <t>15/06/2026</t>
         </is>
       </c>
-      <c r="F94" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G94" s="6" t="inlineStr"/>
-      <c r="H94" s="6" t="inlineStr">
-        <is>
-          <t>0/34</t>
-        </is>
-      </c>
-      <c r="I94" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>28/34</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -6120,7 +6152,7 @@
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t>1/34</t>
+          <t>34/34</t>
         </is>
       </c>
       <c r="I113" s="2" t="inlineStr">
@@ -6408,88 +6440,96 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B120" s="5" t="inlineStr">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
         <is>
           <t>A1-C1</t>
         </is>
       </c>
-      <c r="C120" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D120" s="5" t="inlineStr">
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E120" s="5" t="inlineStr">
+      <c r="E120" s="2" t="inlineStr">
         <is>
           <t>14/06/2026</t>
         </is>
       </c>
-      <c r="F120" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G120" s="5" t="inlineStr"/>
-      <c r="H120" s="5" t="inlineStr">
-        <is>
-          <t>0/34</t>
-        </is>
-      </c>
-      <c r="I120" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G120" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H120" s="2" t="inlineStr">
+        <is>
+          <t>31/34</t>
+        </is>
+      </c>
+      <c r="I120" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B121" s="6" t="inlineStr">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
         <is>
           <t>A1-C1</t>
         </is>
       </c>
-      <c r="C121" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D121" s="6" t="inlineStr">
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="E121" s="6" t="inlineStr">
+      <c r="E121" s="2" t="inlineStr">
         <is>
           <t>15/06/2026</t>
         </is>
       </c>
-      <c r="F121" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G121" s="6" t="inlineStr"/>
-      <c r="H121" s="6" t="inlineStr">
-        <is>
-          <t>0/34</t>
-        </is>
-      </c>
-      <c r="I121" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G121" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H121" s="2" t="inlineStr">
+        <is>
+          <t>32/34</t>
+        </is>
+      </c>
+      <c r="I121" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -7280,45 +7320,49 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B140" s="5" t="inlineStr">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
         <is>
           <t>A1-C2</t>
         </is>
       </c>
-      <c r="C140" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D140" s="5" t="inlineStr">
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E140" s="5" t="inlineStr">
+      <c r="E140" s="2" t="inlineStr">
         <is>
           <t>30/05/2026</t>
         </is>
       </c>
-      <c r="F140" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G140" s="5" t="inlineStr"/>
-      <c r="H140" s="5" t="inlineStr">
-        <is>
-          <t>0/33</t>
-        </is>
-      </c>
-      <c r="I140" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G140" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H140" s="2" t="inlineStr">
+        <is>
+          <t>30/33</t>
+        </is>
+      </c>
+      <c r="I140" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -7601,88 +7645,96 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B147" s="5" t="inlineStr">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
         <is>
           <t>A1-C2</t>
         </is>
       </c>
-      <c r="C147" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D147" s="5" t="inlineStr">
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E147" s="5" t="inlineStr">
+      <c r="E147" s="2" t="inlineStr">
         <is>
           <t>14/06/2026</t>
         </is>
       </c>
-      <c r="F147" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G147" s="5" t="inlineStr"/>
-      <c r="H147" s="5" t="inlineStr">
-        <is>
-          <t>0/33</t>
-        </is>
-      </c>
-      <c r="I147" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F147" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G147" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H147" s="2" t="inlineStr">
+        <is>
+          <t>28/33</t>
+        </is>
+      </c>
+      <c r="I147" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B148" s="6" t="inlineStr">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
         <is>
           <t>A1-C2</t>
         </is>
       </c>
-      <c r="C148" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D148" s="6" t="inlineStr">
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="E148" s="6" t="inlineStr">
+      <c r="E148" s="2" t="inlineStr">
         <is>
           <t>15/06/2026</t>
         </is>
       </c>
-      <c r="F148" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G148" s="6" t="inlineStr"/>
-      <c r="H148" s="6" t="inlineStr">
-        <is>
-          <t>0/33</t>
-        </is>
-      </c>
-      <c r="I148" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F148" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G148" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H148" s="2" t="inlineStr">
+        <is>
+          <t>25/33</t>
+        </is>
+      </c>
+      <c r="I148" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A1_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A1_session_analysis.xlsx
@@ -814,7 +814,7 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>126</v>
+        <v>132</v>
       </c>
     </row>
     <row r="7">
@@ -924,7 +924,7 @@
         </is>
       </c>
       <c r="L8" s="4" t="n">
-        <v>192</v>
+        <v>186</v>
       </c>
     </row>
     <row r="9">
@@ -980,7 +980,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>40.7%</t>
         </is>
       </c>
     </row>
@@ -1802,22 +1802,22 @@
         <v>27</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P21" s="4" t="n">
         <v>1</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="R21" s="4" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>37.0%</t>
         </is>
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>66.9%</t>
         </is>
       </c>
     </row>
@@ -1880,22 +1880,22 @@
         <v>27</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P22" s="4" t="n">
         <v>1</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="R22" s="4" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>37.0%</t>
         </is>
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>71.9%</t>
+          <t>71.5%</t>
         </is>
       </c>
     </row>
@@ -1958,22 +1958,22 @@
         <v>27</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P23" s="4" t="n">
         <v>1</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="R23" s="4" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>37.0%</t>
         </is>
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>71.1%</t>
+          <t>70.3%</t>
         </is>
       </c>
     </row>
@@ -2036,22 +2036,22 @@
         <v>27</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P24" s="4" t="n">
         <v>1</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="R24" s="4" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>37.0%</t>
         </is>
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>67.5%</t>
+          <t>67.4%</t>
         </is>
       </c>
     </row>
@@ -2114,22 +2114,22 @@
         <v>27</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P25" s="4" t="n">
         <v>1</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="R25" s="4" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>37.0%</t>
         </is>
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>74.6%</t>
+          <t>74.5%</t>
         </is>
       </c>
     </row>
@@ -2192,22 +2192,22 @@
         <v>27</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P26" s="4" t="n">
         <v>1</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="R26" s="4" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>37.0%</t>
         </is>
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>68.1%</t>
+          <t>68.5%</t>
         </is>
       </c>
     </row>
@@ -8874,45 +8874,49 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B174" s="5" t="inlineStr">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
         <is>
           <t>A1-D1</t>
         </is>
       </c>
-      <c r="C174" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D174" s="5" t="inlineStr">
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E174" s="5" t="inlineStr">
+      <c r="E174" s="2" t="inlineStr">
         <is>
           <t>17/06/2026</t>
         </is>
       </c>
-      <c r="F174" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G174" s="5" t="inlineStr"/>
-      <c r="H174" s="5" t="inlineStr">
-        <is>
-          <t>0/35</t>
-        </is>
-      </c>
-      <c r="I174" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F174" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G174" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H174" s="2" t="inlineStr">
+        <is>
+          <t>25/35</t>
+        </is>
+      </c>
+      <c r="I174" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -10071,45 +10075,49 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B201" s="5" t="inlineStr">
+      <c r="A201" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B201" s="2" t="inlineStr">
         <is>
           <t>A1-D2</t>
         </is>
       </c>
-      <c r="C201" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D201" s="5" t="inlineStr">
+      <c r="C201" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D201" s="2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E201" s="5" t="inlineStr">
+      <c r="E201" s="2" t="inlineStr">
         <is>
           <t>17/06/2026</t>
         </is>
       </c>
-      <c r="F201" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G201" s="5" t="inlineStr"/>
-      <c r="H201" s="5" t="inlineStr">
-        <is>
-          <t>0/34</t>
-        </is>
-      </c>
-      <c r="I201" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F201" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G201" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H201" s="2" t="inlineStr">
+        <is>
+          <t>23/34</t>
+        </is>
+      </c>
+      <c r="I201" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -11268,45 +11276,49 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B228" s="5" t="inlineStr">
+      <c r="A228" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B228" s="2" t="inlineStr">
         <is>
           <t>A1-E1</t>
         </is>
       </c>
-      <c r="C228" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D228" s="5" t="inlineStr">
+      <c r="C228" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D228" s="2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E228" s="5" t="inlineStr">
+      <c r="E228" s="2" t="inlineStr">
         <is>
           <t>17/06/2026</t>
         </is>
       </c>
-      <c r="F228" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G228" s="5" t="inlineStr"/>
-      <c r="H228" s="5" t="inlineStr">
-        <is>
-          <t>0/38</t>
-        </is>
-      </c>
-      <c r="I228" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F228" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G228" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H228" s="2" t="inlineStr">
+        <is>
+          <t>24/38</t>
+        </is>
+      </c>
+      <c r="I228" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -12465,45 +12477,49 @@
       </c>
     </row>
     <row r="255">
-      <c r="A255" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B255" s="5" t="inlineStr">
+      <c r="A255" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B255" s="2" t="inlineStr">
         <is>
           <t>A1-E2</t>
         </is>
       </c>
-      <c r="C255" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D255" s="5" t="inlineStr">
+      <c r="C255" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D255" s="2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E255" s="5" t="inlineStr">
+      <c r="E255" s="2" t="inlineStr">
         <is>
           <t>17/06/2026</t>
         </is>
       </c>
-      <c r="F255" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G255" s="5" t="inlineStr"/>
-      <c r="H255" s="5" t="inlineStr">
-        <is>
-          <t>0/39</t>
-        </is>
-      </c>
-      <c r="I255" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F255" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G255" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H255" s="2" t="inlineStr">
+        <is>
+          <t>26/39</t>
+        </is>
+      </c>
+      <c r="I255" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -13662,45 +13678,49 @@
       </c>
     </row>
     <row r="282">
-      <c r="A282" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B282" s="5" t="inlineStr">
+      <c r="A282" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B282" s="2" t="inlineStr">
         <is>
           <t>A1-F1</t>
         </is>
       </c>
-      <c r="C282" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D282" s="5" t="inlineStr">
+      <c r="C282" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D282" s="2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E282" s="5" t="inlineStr">
+      <c r="E282" s="2" t="inlineStr">
         <is>
           <t>17/06/2026</t>
         </is>
       </c>
-      <c r="F282" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G282" s="5" t="inlineStr"/>
-      <c r="H282" s="5" t="inlineStr">
-        <is>
-          <t>0/38</t>
-        </is>
-      </c>
-      <c r="I282" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F282" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G282" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H282" s="2" t="inlineStr">
+        <is>
+          <t>28/38</t>
+        </is>
+      </c>
+      <c r="I282" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -14859,45 +14879,49 @@
       </c>
     </row>
     <row r="309">
-      <c r="A309" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B309" s="5" t="inlineStr">
+      <c r="A309" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B309" s="2" t="inlineStr">
         <is>
           <t>A1-F2</t>
         </is>
       </c>
-      <c r="C309" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D309" s="5" t="inlineStr">
+      <c r="C309" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D309" s="2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E309" s="5" t="inlineStr">
+      <c r="E309" s="2" t="inlineStr">
         <is>
           <t>17/06/2026</t>
         </is>
       </c>
-      <c r="F309" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G309" s="5" t="inlineStr"/>
-      <c r="H309" s="5" t="inlineStr">
-        <is>
-          <t>0/39</t>
-        </is>
-      </c>
-      <c r="I309" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F309" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G309" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H309" s="2" t="inlineStr">
+        <is>
+          <t>28/39</t>
+        </is>
+      </c>
+      <c r="I309" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A1_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A1_session_analysis.xlsx
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8">
@@ -924,7 +924,7 @@
         </is>
       </c>
       <c r="L8" s="4" t="n">
-        <v>186</v>
+        <v>180</v>
       </c>
     </row>
     <row r="9">
@@ -1805,10 +1805,10 @@
         <v>10</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R21" s="4" t="inlineStr">
         <is>
@@ -1883,10 +1883,10 @@
         <v>10</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R22" s="4" t="inlineStr">
         <is>
@@ -1961,10 +1961,10 @@
         <v>10</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R23" s="4" t="inlineStr">
         <is>
@@ -2039,10 +2039,10 @@
         <v>10</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R24" s="4" t="inlineStr">
         <is>
@@ -2117,10 +2117,10 @@
         <v>10</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R25" s="4" t="inlineStr">
         <is>
@@ -2195,10 +2195,10 @@
         <v>10</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R26" s="4" t="inlineStr">
         <is>
@@ -8921,45 +8921,45 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B175" s="5" t="inlineStr">
+      <c r="A175" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B175" s="9" t="inlineStr">
         <is>
           <t>A1-D1</t>
         </is>
       </c>
-      <c r="C175" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D175" s="5" t="inlineStr">
+      <c r="C175" s="9" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D175" s="9" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="E175" s="5" t="inlineStr">
+      <c r="E175" s="9" t="inlineStr">
         <is>
           <t>18/06/2026</t>
         </is>
       </c>
-      <c r="F175" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G175" s="5" t="inlineStr"/>
-      <c r="H175" s="5" t="inlineStr">
+      <c r="F175" s="9" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G175" s="9" t="inlineStr"/>
+      <c r="H175" s="9" t="inlineStr">
         <is>
           <t>0/35</t>
         </is>
       </c>
-      <c r="I175" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I175" s="9" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -10122,45 +10122,45 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B202" s="5" t="inlineStr">
+      <c r="A202" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B202" s="9" t="inlineStr">
         <is>
           <t>A1-D2</t>
         </is>
       </c>
-      <c r="C202" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D202" s="5" t="inlineStr">
+      <c r="C202" s="9" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D202" s="9" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="E202" s="5" t="inlineStr">
+      <c r="E202" s="9" t="inlineStr">
         <is>
           <t>18/06/2026</t>
         </is>
       </c>
-      <c r="F202" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G202" s="5" t="inlineStr"/>
-      <c r="H202" s="5" t="inlineStr">
+      <c r="F202" s="9" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G202" s="9" t="inlineStr"/>
+      <c r="H202" s="9" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I202" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I202" s="9" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -11323,45 +11323,45 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B229" s="5" t="inlineStr">
+      <c r="A229" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B229" s="9" t="inlineStr">
         <is>
           <t>A1-E1</t>
         </is>
       </c>
-      <c r="C229" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D229" s="5" t="inlineStr">
+      <c r="C229" s="9" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D229" s="9" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="E229" s="5" t="inlineStr">
+      <c r="E229" s="9" t="inlineStr">
         <is>
           <t>18/06/2026</t>
         </is>
       </c>
-      <c r="F229" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G229" s="5" t="inlineStr"/>
-      <c r="H229" s="5" t="inlineStr">
+      <c r="F229" s="9" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G229" s="9" t="inlineStr"/>
+      <c r="H229" s="9" t="inlineStr">
         <is>
           <t>0/38</t>
         </is>
       </c>
-      <c r="I229" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I229" s="9" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -12524,45 +12524,45 @@
       </c>
     </row>
     <row r="256">
-      <c r="A256" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B256" s="5" t="inlineStr">
+      <c r="A256" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B256" s="9" t="inlineStr">
         <is>
           <t>A1-E2</t>
         </is>
       </c>
-      <c r="C256" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D256" s="5" t="inlineStr">
+      <c r="C256" s="9" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D256" s="9" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="E256" s="5" t="inlineStr">
+      <c r="E256" s="9" t="inlineStr">
         <is>
           <t>18/06/2026</t>
         </is>
       </c>
-      <c r="F256" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G256" s="5" t="inlineStr"/>
-      <c r="H256" s="5" t="inlineStr">
+      <c r="F256" s="9" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G256" s="9" t="inlineStr"/>
+      <c r="H256" s="9" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I256" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I256" s="9" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -13725,45 +13725,45 @@
       </c>
     </row>
     <row r="283">
-      <c r="A283" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B283" s="5" t="inlineStr">
+      <c r="A283" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B283" s="9" t="inlineStr">
         <is>
           <t>A1-F1</t>
         </is>
       </c>
-      <c r="C283" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D283" s="5" t="inlineStr">
+      <c r="C283" s="9" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D283" s="9" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="E283" s="5" t="inlineStr">
+      <c r="E283" s="9" t="inlineStr">
         <is>
           <t>18/06/2026</t>
         </is>
       </c>
-      <c r="F283" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G283" s="5" t="inlineStr"/>
-      <c r="H283" s="5" t="inlineStr">
+      <c r="F283" s="9" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G283" s="9" t="inlineStr"/>
+      <c r="H283" s="9" t="inlineStr">
         <is>
           <t>0/38</t>
         </is>
       </c>
-      <c r="I283" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I283" s="9" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -14926,45 +14926,45 @@
       </c>
     </row>
     <row r="310">
-      <c r="A310" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B310" s="5" t="inlineStr">
+      <c r="A310" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B310" s="9" t="inlineStr">
         <is>
           <t>A1-F2</t>
         </is>
       </c>
-      <c r="C310" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D310" s="5" t="inlineStr">
+      <c r="C310" s="9" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D310" s="9" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="E310" s="5" t="inlineStr">
+      <c r="E310" s="9" t="inlineStr">
         <is>
           <t>18/06/2026</t>
         </is>
       </c>
-      <c r="F310" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G310" s="5" t="inlineStr"/>
-      <c r="H310" s="5" t="inlineStr">
+      <c r="F310" s="9" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G310" s="9" t="inlineStr"/>
+      <c r="H310" s="9" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I310" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I310" s="9" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A1_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A1_session_analysis.xlsx
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8">
@@ -924,7 +924,7 @@
         </is>
       </c>
       <c r="L8" s="4" t="n">
-        <v>174</v>
+        <v>168</v>
       </c>
     </row>
     <row r="9">
@@ -1276,45 +1276,45 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="inlineStr">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>A1-A1</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D15" s="6" t="inlineStr">
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="E15" s="6" t="inlineStr">
+      <c r="E15" s="5" t="inlineStr">
         <is>
           <t>21/06/2026</t>
         </is>
       </c>
-      <c r="F15" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G15" s="6" t="inlineStr"/>
-      <c r="H15" s="6" t="inlineStr">
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr"/>
+      <c r="H15" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I15" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
       <c r="K15" s="4" t="inlineStr">
@@ -1337,10 +1337,10 @@
         <v>12</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="R15" s="4" t="inlineStr">
         <is>
@@ -1415,10 +1415,10 @@
         <v>12</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="R16" s="4" t="inlineStr">
         <is>
@@ -1493,10 +1493,10 @@
         <v>12</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="R17" s="4" t="inlineStr">
         <is>
@@ -1571,10 +1571,10 @@
         <v>12</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="R18" s="4" t="inlineStr">
         <is>
@@ -1649,10 +1649,10 @@
         <v>12</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="R19" s="4" t="inlineStr">
         <is>
@@ -1727,10 +1727,10 @@
         <v>12</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="R20" s="4" t="inlineStr">
         <is>
@@ -2970,45 +2970,45 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B42" s="6" t="inlineStr">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
         <is>
           <t>A1-A2</t>
         </is>
       </c>
-      <c r="C42" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D42" s="6" t="inlineStr">
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="E42" s="6" t="inlineStr">
+      <c r="E42" s="5" t="inlineStr">
         <is>
           <t>21/06/2026</t>
         </is>
       </c>
-      <c r="F42" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G42" s="6" t="inlineStr"/>
-      <c r="H42" s="6" t="inlineStr">
+      <c r="F42" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G42" s="5" t="inlineStr"/>
+      <c r="H42" s="5" t="inlineStr">
         <is>
           <t>0/33</t>
         </is>
       </c>
-      <c r="I42" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I42" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -4179,45 +4179,45 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B69" s="6" t="inlineStr">
+      <c r="A69" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B69" s="5" t="inlineStr">
         <is>
           <t>A1-B1</t>
         </is>
       </c>
-      <c r="C69" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D69" s="6" t="inlineStr">
+      <c r="C69" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D69" s="5" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="E69" s="6" t="inlineStr">
+      <c r="E69" s="5" t="inlineStr">
         <is>
           <t>21/06/2026</t>
         </is>
       </c>
-      <c r="F69" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G69" s="6" t="inlineStr"/>
-      <c r="H69" s="6" t="inlineStr">
+      <c r="F69" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G69" s="5" t="inlineStr"/>
+      <c r="H69" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I69" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I69" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -5388,45 +5388,45 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B96" s="6" t="inlineStr">
+      <c r="A96" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B96" s="5" t="inlineStr">
         <is>
           <t>A1-B2</t>
         </is>
       </c>
-      <c r="C96" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D96" s="6" t="inlineStr">
+      <c r="C96" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D96" s="5" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="E96" s="6" t="inlineStr">
+      <c r="E96" s="5" t="inlineStr">
         <is>
           <t>21/06/2026</t>
         </is>
       </c>
-      <c r="F96" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G96" s="6" t="inlineStr"/>
-      <c r="H96" s="6" t="inlineStr">
+      <c r="F96" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G96" s="5" t="inlineStr"/>
+      <c r="H96" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I96" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I96" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -6597,45 +6597,45 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B123" s="6" t="inlineStr">
+      <c r="A123" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B123" s="5" t="inlineStr">
         <is>
           <t>A1-C1</t>
         </is>
       </c>
-      <c r="C123" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D123" s="6" t="inlineStr">
+      <c r="C123" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D123" s="5" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="E123" s="6" t="inlineStr">
+      <c r="E123" s="5" t="inlineStr">
         <is>
           <t>21/06/2026</t>
         </is>
       </c>
-      <c r="F123" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G123" s="6" t="inlineStr"/>
-      <c r="H123" s="6" t="inlineStr">
+      <c r="F123" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G123" s="5" t="inlineStr"/>
+      <c r="H123" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I123" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I123" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -7806,45 +7806,45 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B150" s="6" t="inlineStr">
+      <c r="A150" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B150" s="5" t="inlineStr">
         <is>
           <t>A1-C2</t>
         </is>
       </c>
-      <c r="C150" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D150" s="6" t="inlineStr">
+      <c r="C150" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D150" s="5" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="E150" s="6" t="inlineStr">
+      <c r="E150" s="5" t="inlineStr">
         <is>
           <t>21/06/2026</t>
         </is>
       </c>
-      <c r="F150" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G150" s="6" t="inlineStr"/>
-      <c r="H150" s="6" t="inlineStr">
+      <c r="F150" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G150" s="5" t="inlineStr"/>
+      <c r="H150" s="5" t="inlineStr">
         <is>
           <t>0/33</t>
         </is>
       </c>
-      <c r="I150" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I150" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A1_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A1_session_analysis.xlsx
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8">
@@ -924,7 +924,7 @@
         </is>
       </c>
       <c r="L8" s="4" t="n">
-        <v>168</v>
+        <v>162</v>
       </c>
     </row>
     <row r="9">
@@ -1337,10 +1337,10 @@
         <v>12</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="R15" s="4" t="inlineStr">
         <is>
@@ -1354,45 +1354,45 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="inlineStr">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>A1-A1</t>
         </is>
       </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D16" s="6" t="inlineStr">
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="E16" s="6" t="inlineStr">
+      <c r="E16" s="5" t="inlineStr">
         <is>
           <t>22/06/2026</t>
         </is>
       </c>
-      <c r="F16" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G16" s="6" t="inlineStr"/>
-      <c r="H16" s="6" t="inlineStr">
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr"/>
+      <c r="H16" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I16" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
       <c r="K16" s="4" t="inlineStr">
@@ -1415,10 +1415,10 @@
         <v>12</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="R16" s="4" t="inlineStr">
         <is>
@@ -1493,10 +1493,10 @@
         <v>12</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="R17" s="4" t="inlineStr">
         <is>
@@ -1571,10 +1571,10 @@
         <v>12</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="R18" s="4" t="inlineStr">
         <is>
@@ -1649,10 +1649,10 @@
         <v>12</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="R19" s="4" t="inlineStr">
         <is>
@@ -1727,10 +1727,10 @@
         <v>12</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="R20" s="4" t="inlineStr">
         <is>
@@ -3013,45 +3013,45 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B43" s="6" t="inlineStr">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
         <is>
           <t>A1-A2</t>
         </is>
       </c>
-      <c r="C43" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D43" s="6" t="inlineStr">
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="E43" s="6" t="inlineStr">
+      <c r="E43" s="5" t="inlineStr">
         <is>
           <t>22/06/2026</t>
         </is>
       </c>
-      <c r="F43" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G43" s="6" t="inlineStr"/>
-      <c r="H43" s="6" t="inlineStr">
+      <c r="F43" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G43" s="5" t="inlineStr"/>
+      <c r="H43" s="5" t="inlineStr">
         <is>
           <t>0/33</t>
         </is>
       </c>
-      <c r="I43" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I43" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -4222,45 +4222,45 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B70" s="6" t="inlineStr">
+      <c r="A70" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B70" s="5" t="inlineStr">
         <is>
           <t>A1-B1</t>
         </is>
       </c>
-      <c r="C70" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D70" s="6" t="inlineStr">
+      <c r="C70" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D70" s="5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="E70" s="6" t="inlineStr">
+      <c r="E70" s="5" t="inlineStr">
         <is>
           <t>22/06/2026</t>
         </is>
       </c>
-      <c r="F70" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G70" s="6" t="inlineStr"/>
-      <c r="H70" s="6" t="inlineStr">
+      <c r="F70" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G70" s="5" t="inlineStr"/>
+      <c r="H70" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I70" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I70" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -5431,45 +5431,45 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B97" s="6" t="inlineStr">
+      <c r="A97" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B97" s="5" t="inlineStr">
         <is>
           <t>A1-B2</t>
         </is>
       </c>
-      <c r="C97" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D97" s="6" t="inlineStr">
+      <c r="C97" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D97" s="5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="E97" s="6" t="inlineStr">
+      <c r="E97" s="5" t="inlineStr">
         <is>
           <t>22/06/2026</t>
         </is>
       </c>
-      <c r="F97" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G97" s="6" t="inlineStr"/>
-      <c r="H97" s="6" t="inlineStr">
+      <c r="F97" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G97" s="5" t="inlineStr"/>
+      <c r="H97" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I97" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I97" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -6640,45 +6640,45 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B124" s="6" t="inlineStr">
+      <c r="A124" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B124" s="5" t="inlineStr">
         <is>
           <t>A1-C1</t>
         </is>
       </c>
-      <c r="C124" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D124" s="6" t="inlineStr">
+      <c r="C124" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D124" s="5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="E124" s="6" t="inlineStr">
+      <c r="E124" s="5" t="inlineStr">
         <is>
           <t>22/06/2026</t>
         </is>
       </c>
-      <c r="F124" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G124" s="6" t="inlineStr"/>
-      <c r="H124" s="6" t="inlineStr">
+      <c r="F124" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G124" s="5" t="inlineStr"/>
+      <c r="H124" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I124" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I124" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -7849,45 +7849,45 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B151" s="6" t="inlineStr">
+      <c r="A151" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B151" s="5" t="inlineStr">
         <is>
           <t>A1-C2</t>
         </is>
       </c>
-      <c r="C151" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D151" s="6" t="inlineStr">
+      <c r="C151" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D151" s="5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="E151" s="6" t="inlineStr">
+      <c r="E151" s="5" t="inlineStr">
         <is>
           <t>22/06/2026</t>
         </is>
       </c>
-      <c r="F151" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G151" s="6" t="inlineStr"/>
-      <c r="H151" s="6" t="inlineStr">
+      <c r="F151" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G151" s="5" t="inlineStr"/>
+      <c r="H151" s="5" t="inlineStr">
         <is>
           <t>0/33</t>
         </is>
       </c>
-      <c r="I151" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I151" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A1_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A1_session_analysis.xlsx
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8">
@@ -924,7 +924,7 @@
         </is>
       </c>
       <c r="L8" s="4" t="n">
-        <v>162</v>
+        <v>156</v>
       </c>
     </row>
     <row r="9">
@@ -1805,10 +1805,10 @@
         <v>10</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="R21" s="4" t="inlineStr">
         <is>
@@ -1883,10 +1883,10 @@
         <v>10</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="R22" s="4" t="inlineStr">
         <is>
@@ -1961,10 +1961,10 @@
         <v>10</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="R23" s="4" t="inlineStr">
         <is>
@@ -2039,10 +2039,10 @@
         <v>10</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="R24" s="4" t="inlineStr">
         <is>
@@ -2117,10 +2117,10 @@
         <v>10</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="R25" s="4" t="inlineStr">
         <is>
@@ -2195,10 +2195,10 @@
         <v>10</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="R26" s="4" t="inlineStr">
         <is>
@@ -8964,45 +8964,45 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B176" s="6" t="inlineStr">
+      <c r="A176" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B176" s="5" t="inlineStr">
         <is>
           <t>A1-D1</t>
         </is>
       </c>
-      <c r="C176" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D176" s="6" t="inlineStr">
+      <c r="C176" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D176" s="5" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="E176" s="6" t="inlineStr">
+      <c r="E176" s="5" t="inlineStr">
         <is>
           <t>23/06/2026</t>
         </is>
       </c>
-      <c r="F176" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G176" s="6" t="inlineStr"/>
-      <c r="H176" s="6" t="inlineStr">
+      <c r="F176" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G176" s="5" t="inlineStr"/>
+      <c r="H176" s="5" t="inlineStr">
         <is>
           <t>0/35</t>
         </is>
       </c>
-      <c r="I176" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I176" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -10165,45 +10165,45 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B203" s="6" t="inlineStr">
+      <c r="A203" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B203" s="5" t="inlineStr">
         <is>
           <t>A1-D2</t>
         </is>
       </c>
-      <c r="C203" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D203" s="6" t="inlineStr">
+      <c r="C203" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D203" s="5" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="E203" s="6" t="inlineStr">
+      <c r="E203" s="5" t="inlineStr">
         <is>
           <t>23/06/2026</t>
         </is>
       </c>
-      <c r="F203" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G203" s="6" t="inlineStr"/>
-      <c r="H203" s="6" t="inlineStr">
+      <c r="F203" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G203" s="5" t="inlineStr"/>
+      <c r="H203" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I203" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I203" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -11366,45 +11366,45 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B230" s="6" t="inlineStr">
+      <c r="A230" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B230" s="5" t="inlineStr">
         <is>
           <t>A1-E1</t>
         </is>
       </c>
-      <c r="C230" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D230" s="6" t="inlineStr">
+      <c r="C230" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D230" s="5" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="E230" s="6" t="inlineStr">
+      <c r="E230" s="5" t="inlineStr">
         <is>
           <t>23/06/2026</t>
         </is>
       </c>
-      <c r="F230" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G230" s="6" t="inlineStr"/>
-      <c r="H230" s="6" t="inlineStr">
+      <c r="F230" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G230" s="5" t="inlineStr"/>
+      <c r="H230" s="5" t="inlineStr">
         <is>
           <t>0/38</t>
         </is>
       </c>
-      <c r="I230" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I230" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -12567,45 +12567,45 @@
       </c>
     </row>
     <row r="257">
-      <c r="A257" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B257" s="6" t="inlineStr">
+      <c r="A257" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B257" s="5" t="inlineStr">
         <is>
           <t>A1-E2</t>
         </is>
       </c>
-      <c r="C257" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D257" s="6" t="inlineStr">
+      <c r="C257" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D257" s="5" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="E257" s="6" t="inlineStr">
+      <c r="E257" s="5" t="inlineStr">
         <is>
           <t>23/06/2026</t>
         </is>
       </c>
-      <c r="F257" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G257" s="6" t="inlineStr"/>
-      <c r="H257" s="6" t="inlineStr">
+      <c r="F257" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G257" s="5" t="inlineStr"/>
+      <c r="H257" s="5" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I257" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I257" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -13768,45 +13768,45 @@
       </c>
     </row>
     <row r="284">
-      <c r="A284" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B284" s="6" t="inlineStr">
+      <c r="A284" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B284" s="5" t="inlineStr">
         <is>
           <t>A1-F1</t>
         </is>
       </c>
-      <c r="C284" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D284" s="6" t="inlineStr">
+      <c r="C284" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D284" s="5" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="E284" s="6" t="inlineStr">
+      <c r="E284" s="5" t="inlineStr">
         <is>
           <t>23/06/2026</t>
         </is>
       </c>
-      <c r="F284" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G284" s="6" t="inlineStr"/>
-      <c r="H284" s="6" t="inlineStr">
+      <c r="F284" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G284" s="5" t="inlineStr"/>
+      <c r="H284" s="5" t="inlineStr">
         <is>
           <t>0/38</t>
         </is>
       </c>
-      <c r="I284" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I284" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -14969,45 +14969,45 @@
       </c>
     </row>
     <row r="311">
-      <c r="A311" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B311" s="6" t="inlineStr">
+      <c r="A311" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B311" s="5" t="inlineStr">
         <is>
           <t>A1-F2</t>
         </is>
       </c>
-      <c r="C311" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D311" s="6" t="inlineStr">
+      <c r="C311" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D311" s="5" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="E311" s="6" t="inlineStr">
+      <c r="E311" s="5" t="inlineStr">
         <is>
           <t>23/06/2026</t>
         </is>
       </c>
-      <c r="F311" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G311" s="6" t="inlineStr"/>
-      <c r="H311" s="6" t="inlineStr">
+      <c r="F311" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G311" s="5" t="inlineStr"/>
+      <c r="H311" s="5" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I311" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I311" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A1_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A1_session_analysis.xlsx
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
     </row>
     <row r="8">
@@ -924,7 +924,7 @@
         </is>
       </c>
       <c r="L8" s="4" t="n">
-        <v>156</v>
+        <v>150</v>
       </c>
     </row>
     <row r="9">
@@ -1805,10 +1805,10 @@
         <v>10</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="R21" s="4" t="inlineStr">
         <is>
@@ -1883,10 +1883,10 @@
         <v>10</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="R22" s="4" t="inlineStr">
         <is>
@@ -1961,10 +1961,10 @@
         <v>10</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="R23" s="4" t="inlineStr">
         <is>
@@ -2039,10 +2039,10 @@
         <v>10</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="R24" s="4" t="inlineStr">
         <is>
@@ -2117,10 +2117,10 @@
         <v>10</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="R25" s="4" t="inlineStr">
         <is>
@@ -2195,10 +2195,10 @@
         <v>10</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="R26" s="4" t="inlineStr">
         <is>
@@ -9007,45 +9007,45 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B177" s="6" t="inlineStr">
+      <c r="A177" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B177" s="5" t="inlineStr">
         <is>
           <t>A1-D1</t>
         </is>
       </c>
-      <c r="C177" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D177" s="6" t="inlineStr">
+      <c r="C177" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D177" s="5" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="E177" s="6" t="inlineStr">
+      <c r="E177" s="5" t="inlineStr">
         <is>
           <t>24/06/2026</t>
         </is>
       </c>
-      <c r="F177" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G177" s="6" t="inlineStr"/>
-      <c r="H177" s="6" t="inlineStr">
+      <c r="F177" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G177" s="5" t="inlineStr"/>
+      <c r="H177" s="5" t="inlineStr">
         <is>
           <t>0/35</t>
         </is>
       </c>
-      <c r="I177" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I177" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -10208,45 +10208,45 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B204" s="6" t="inlineStr">
+      <c r="A204" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B204" s="5" t="inlineStr">
         <is>
           <t>A1-D2</t>
         </is>
       </c>
-      <c r="C204" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D204" s="6" t="inlineStr">
+      <c r="C204" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D204" s="5" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="E204" s="6" t="inlineStr">
+      <c r="E204" s="5" t="inlineStr">
         <is>
           <t>24/06/2026</t>
         </is>
       </c>
-      <c r="F204" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G204" s="6" t="inlineStr"/>
-      <c r="H204" s="6" t="inlineStr">
+      <c r="F204" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G204" s="5" t="inlineStr"/>
+      <c r="H204" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I204" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I204" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -11409,45 +11409,45 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B231" s="6" t="inlineStr">
+      <c r="A231" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B231" s="5" t="inlineStr">
         <is>
           <t>A1-E1</t>
         </is>
       </c>
-      <c r="C231" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D231" s="6" t="inlineStr">
+      <c r="C231" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D231" s="5" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="E231" s="6" t="inlineStr">
+      <c r="E231" s="5" t="inlineStr">
         <is>
           <t>24/06/2026</t>
         </is>
       </c>
-      <c r="F231" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G231" s="6" t="inlineStr"/>
-      <c r="H231" s="6" t="inlineStr">
+      <c r="F231" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G231" s="5" t="inlineStr"/>
+      <c r="H231" s="5" t="inlineStr">
         <is>
           <t>0/38</t>
         </is>
       </c>
-      <c r="I231" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I231" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -12610,45 +12610,45 @@
       </c>
     </row>
     <row r="258">
-      <c r="A258" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B258" s="6" t="inlineStr">
+      <c r="A258" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B258" s="5" t="inlineStr">
         <is>
           <t>A1-E2</t>
         </is>
       </c>
-      <c r="C258" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D258" s="6" t="inlineStr">
+      <c r="C258" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D258" s="5" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="E258" s="6" t="inlineStr">
+      <c r="E258" s="5" t="inlineStr">
         <is>
           <t>24/06/2026</t>
         </is>
       </c>
-      <c r="F258" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G258" s="6" t="inlineStr"/>
-      <c r="H258" s="6" t="inlineStr">
+      <c r="F258" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G258" s="5" t="inlineStr"/>
+      <c r="H258" s="5" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I258" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I258" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -13811,45 +13811,45 @@
       </c>
     </row>
     <row r="285">
-      <c r="A285" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B285" s="6" t="inlineStr">
+      <c r="A285" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B285" s="5" t="inlineStr">
         <is>
           <t>A1-F1</t>
         </is>
       </c>
-      <c r="C285" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D285" s="6" t="inlineStr">
+      <c r="C285" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D285" s="5" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="E285" s="6" t="inlineStr">
+      <c r="E285" s="5" t="inlineStr">
         <is>
           <t>24/06/2026</t>
         </is>
       </c>
-      <c r="F285" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G285" s="6" t="inlineStr"/>
-      <c r="H285" s="6" t="inlineStr">
+      <c r="F285" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G285" s="5" t="inlineStr"/>
+      <c r="H285" s="5" t="inlineStr">
         <is>
           <t>0/38</t>
         </is>
       </c>
-      <c r="I285" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I285" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -15012,45 +15012,45 @@
       </c>
     </row>
     <row r="312">
-      <c r="A312" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B312" s="6" t="inlineStr">
+      <c r="A312" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B312" s="5" t="inlineStr">
         <is>
           <t>A1-F2</t>
         </is>
       </c>
-      <c r="C312" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D312" s="6" t="inlineStr">
+      <c r="C312" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D312" s="5" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="E312" s="6" t="inlineStr">
+      <c r="E312" s="5" t="inlineStr">
         <is>
           <t>24/06/2026</t>
         </is>
       </c>
-      <c r="F312" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G312" s="6" t="inlineStr"/>
-      <c r="H312" s="6" t="inlineStr">
+      <c r="F312" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G312" s="5" t="inlineStr"/>
+      <c r="H312" s="5" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I312" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I312" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A1_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A1_session_analysis.xlsx
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8">
@@ -924,7 +924,7 @@
         </is>
       </c>
       <c r="L8" s="4" t="n">
-        <v>150</v>
+        <v>144</v>
       </c>
     </row>
     <row r="9">
@@ -1805,10 +1805,10 @@
         <v>10</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="R21" s="4" t="inlineStr">
         <is>
@@ -1883,10 +1883,10 @@
         <v>10</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="R22" s="4" t="inlineStr">
         <is>
@@ -1961,10 +1961,10 @@
         <v>10</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="R23" s="4" t="inlineStr">
         <is>
@@ -2039,10 +2039,10 @@
         <v>10</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="R24" s="4" t="inlineStr">
         <is>
@@ -2117,10 +2117,10 @@
         <v>10</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="R25" s="4" t="inlineStr">
         <is>
@@ -2195,10 +2195,10 @@
         <v>10</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="R26" s="4" t="inlineStr">
         <is>
@@ -9050,45 +9050,45 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B178" s="6" t="inlineStr">
+      <c r="A178" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B178" s="5" t="inlineStr">
         <is>
           <t>A1-D1</t>
         </is>
       </c>
-      <c r="C178" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D178" s="6" t="inlineStr">
+      <c r="C178" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D178" s="5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="E178" s="6" t="inlineStr">
+      <c r="E178" s="5" t="inlineStr">
         <is>
           <t>25/06/2026</t>
         </is>
       </c>
-      <c r="F178" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G178" s="6" t="inlineStr"/>
-      <c r="H178" s="6" t="inlineStr">
+      <c r="F178" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G178" s="5" t="inlineStr"/>
+      <c r="H178" s="5" t="inlineStr">
         <is>
           <t>0/35</t>
         </is>
       </c>
-      <c r="I178" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I178" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -10251,45 +10251,45 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B205" s="6" t="inlineStr">
+      <c r="A205" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B205" s="5" t="inlineStr">
         <is>
           <t>A1-D2</t>
         </is>
       </c>
-      <c r="C205" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D205" s="6" t="inlineStr">
+      <c r="C205" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D205" s="5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="E205" s="6" t="inlineStr">
+      <c r="E205" s="5" t="inlineStr">
         <is>
           <t>25/06/2026</t>
         </is>
       </c>
-      <c r="F205" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G205" s="6" t="inlineStr"/>
-      <c r="H205" s="6" t="inlineStr">
+      <c r="F205" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G205" s="5" t="inlineStr"/>
+      <c r="H205" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I205" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I205" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -11452,45 +11452,45 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B232" s="6" t="inlineStr">
+      <c r="A232" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B232" s="5" t="inlineStr">
         <is>
           <t>A1-E1</t>
         </is>
       </c>
-      <c r="C232" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D232" s="6" t="inlineStr">
+      <c r="C232" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D232" s="5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="E232" s="6" t="inlineStr">
+      <c r="E232" s="5" t="inlineStr">
         <is>
           <t>25/06/2026</t>
         </is>
       </c>
-      <c r="F232" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G232" s="6" t="inlineStr"/>
-      <c r="H232" s="6" t="inlineStr">
+      <c r="F232" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G232" s="5" t="inlineStr"/>
+      <c r="H232" s="5" t="inlineStr">
         <is>
           <t>0/38</t>
         </is>
       </c>
-      <c r="I232" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I232" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -12653,45 +12653,45 @@
       </c>
     </row>
     <row r="259">
-      <c r="A259" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B259" s="6" t="inlineStr">
+      <c r="A259" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B259" s="5" t="inlineStr">
         <is>
           <t>A1-E2</t>
         </is>
       </c>
-      <c r="C259" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D259" s="6" t="inlineStr">
+      <c r="C259" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D259" s="5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="E259" s="6" t="inlineStr">
+      <c r="E259" s="5" t="inlineStr">
         <is>
           <t>25/06/2026</t>
         </is>
       </c>
-      <c r="F259" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G259" s="6" t="inlineStr"/>
-      <c r="H259" s="6" t="inlineStr">
+      <c r="F259" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G259" s="5" t="inlineStr"/>
+      <c r="H259" s="5" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I259" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I259" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -13854,45 +13854,45 @@
       </c>
     </row>
     <row r="286">
-      <c r="A286" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B286" s="6" t="inlineStr">
+      <c r="A286" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B286" s="5" t="inlineStr">
         <is>
           <t>A1-F1</t>
         </is>
       </c>
-      <c r="C286" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D286" s="6" t="inlineStr">
+      <c r="C286" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D286" s="5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="E286" s="6" t="inlineStr">
+      <c r="E286" s="5" t="inlineStr">
         <is>
           <t>25/06/2026</t>
         </is>
       </c>
-      <c r="F286" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G286" s="6" t="inlineStr"/>
-      <c r="H286" s="6" t="inlineStr">
+      <c r="F286" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G286" s="5" t="inlineStr"/>
+      <c r="H286" s="5" t="inlineStr">
         <is>
           <t>0/38</t>
         </is>
       </c>
-      <c r="I286" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I286" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -15055,45 +15055,45 @@
       </c>
     </row>
     <row r="313">
-      <c r="A313" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B313" s="6" t="inlineStr">
+      <c r="A313" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B313" s="5" t="inlineStr">
         <is>
           <t>A1-F2</t>
         </is>
       </c>
-      <c r="C313" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D313" s="6" t="inlineStr">
+      <c r="C313" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D313" s="5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="E313" s="6" t="inlineStr">
+      <c r="E313" s="5" t="inlineStr">
         <is>
           <t>25/06/2026</t>
         </is>
       </c>
-      <c r="F313" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G313" s="6" t="inlineStr"/>
-      <c r="H313" s="6" t="inlineStr">
+      <c r="F313" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G313" s="5" t="inlineStr"/>
+      <c r="H313" s="5" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I313" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I313" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A1_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A1_session_analysis.xlsx
@@ -704,7 +704,7 @@
         </is>
       </c>
       <c r="L4" s="4" t="n">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="5">
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
     </row>
     <row r="8">
@@ -924,7 +924,7 @@
         </is>
       </c>
       <c r="L8" s="4" t="n">
-        <v>144</v>
+        <v>138</v>
       </c>
     </row>
     <row r="9">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>68.8%</t>
+          <t>69.9%</t>
         </is>
       </c>
     </row>
@@ -1337,10 +1337,10 @@
         <v>12</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="R15" s="4" t="inlineStr">
         <is>
@@ -1415,10 +1415,10 @@
         <v>12</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="R16" s="4" t="inlineStr">
         <is>
@@ -1432,45 +1432,45 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="inlineStr">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>A1-A1</t>
         </is>
       </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D17" s="6" t="inlineStr">
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="E17" s="6" t="inlineStr">
+      <c r="E17" s="5" t="inlineStr">
         <is>
           <t>27/06/2026</t>
         </is>
       </c>
-      <c r="F17" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G17" s="6" t="inlineStr"/>
-      <c r="H17" s="6" t="inlineStr">
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr"/>
+      <c r="H17" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I17" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
       <c r="K17" s="4" t="inlineStr">
@@ -1493,10 +1493,10 @@
         <v>12</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="R17" s="4" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>72.3%</t>
+          <t>75.7%</t>
         </is>
       </c>
     </row>
@@ -1571,10 +1571,10 @@
         <v>12</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="R18" s="4" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>68.1%</t>
+          <t>73.5%</t>
         </is>
       </c>
     </row>
@@ -1649,10 +1649,10 @@
         <v>12</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="R19" s="4" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>72.8%</t>
+          <t>76.5%</t>
         </is>
       </c>
     </row>
@@ -1727,10 +1727,10 @@
         <v>12</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="R20" s="4" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
         </is>
       </c>
       <c r="M25" s="4" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="N25" s="4" t="n">
         <v>27</v>
@@ -2129,7 +2129,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>74.5%</t>
+          <t>73.8%</t>
         </is>
       </c>
     </row>
@@ -3056,45 +3056,45 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B44" s="6" t="inlineStr">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
         <is>
           <t>A1-A2</t>
         </is>
       </c>
-      <c r="C44" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D44" s="6" t="inlineStr">
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="E44" s="6" t="inlineStr">
+      <c r="E44" s="5" t="inlineStr">
         <is>
           <t>27/06/2026</t>
         </is>
       </c>
-      <c r="F44" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G44" s="6" t="inlineStr"/>
-      <c r="H44" s="6" t="inlineStr">
+      <c r="F44" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G44" s="5" t="inlineStr"/>
+      <c r="H44" s="5" t="inlineStr">
         <is>
           <t>0/33</t>
         </is>
       </c>
-      <c r="I44" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I44" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -3797,7 +3797,7 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>6/34</t>
+          <t>20/34</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
@@ -4265,45 +4265,45 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B71" s="6" t="inlineStr">
+      <c r="A71" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B71" s="5" t="inlineStr">
         <is>
           <t>A1-B1</t>
         </is>
       </c>
-      <c r="C71" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D71" s="6" t="inlineStr">
+      <c r="C71" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D71" s="5" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="E71" s="6" t="inlineStr">
+      <c r="E71" s="5" t="inlineStr">
         <is>
           <t>27/06/2026</t>
         </is>
       </c>
-      <c r="F71" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G71" s="6" t="inlineStr"/>
-      <c r="H71" s="6" t="inlineStr">
+      <c r="F71" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G71" s="5" t="inlineStr"/>
+      <c r="H71" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I71" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I71" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -5006,7 +5006,7 @@
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>1/34</t>
+          <t>23/34</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
@@ -5474,45 +5474,45 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B98" s="6" t="inlineStr">
+      <c r="A98" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B98" s="5" t="inlineStr">
         <is>
           <t>A1-B2</t>
         </is>
       </c>
-      <c r="C98" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D98" s="6" t="inlineStr">
+      <c r="C98" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D98" s="5" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="E98" s="6" t="inlineStr">
+      <c r="E98" s="5" t="inlineStr">
         <is>
           <t>27/06/2026</t>
         </is>
       </c>
-      <c r="F98" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G98" s="6" t="inlineStr"/>
-      <c r="H98" s="6" t="inlineStr">
+      <c r="F98" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G98" s="5" t="inlineStr"/>
+      <c r="H98" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I98" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I98" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -6215,7 +6215,7 @@
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t>9/34</t>
+          <t>24/34</t>
         </is>
       </c>
       <c r="I114" s="2" t="inlineStr">
@@ -6683,45 +6683,45 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B125" s="6" t="inlineStr">
+      <c r="A125" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B125" s="5" t="inlineStr">
         <is>
           <t>A1-C1</t>
         </is>
       </c>
-      <c r="C125" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D125" s="6" t="inlineStr">
+      <c r="C125" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D125" s="5" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="E125" s="6" t="inlineStr">
+      <c r="E125" s="5" t="inlineStr">
         <is>
           <t>27/06/2026</t>
         </is>
       </c>
-      <c r="F125" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G125" s="6" t="inlineStr"/>
-      <c r="H125" s="6" t="inlineStr">
+      <c r="F125" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G125" s="5" t="inlineStr"/>
+      <c r="H125" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I125" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I125" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -7892,45 +7892,45 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B152" s="6" t="inlineStr">
+      <c r="A152" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B152" s="5" t="inlineStr">
         <is>
           <t>A1-C2</t>
         </is>
       </c>
-      <c r="C152" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D152" s="6" t="inlineStr">
+      <c r="C152" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D152" s="5" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="E152" s="6" t="inlineStr">
+      <c r="E152" s="5" t="inlineStr">
         <is>
           <t>27/06/2026</t>
         </is>
       </c>
-      <c r="F152" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G152" s="6" t="inlineStr"/>
-      <c r="H152" s="6" t="inlineStr">
+      <c r="F152" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G152" s="5" t="inlineStr"/>
+      <c r="H152" s="5" t="inlineStr">
         <is>
           <t>0/33</t>
         </is>
       </c>
-      <c r="I152" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I152" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -13249,7 +13249,7 @@
       </c>
       <c r="H272" s="2" t="inlineStr">
         <is>
-          <t>27/38</t>
+          <t>27/39</t>
         </is>
       </c>
       <c r="I272" s="2" t="inlineStr">
@@ -13296,7 +13296,7 @@
       </c>
       <c r="H273" s="2" t="inlineStr">
         <is>
-          <t>33/38</t>
+          <t>34/39</t>
         </is>
       </c>
       <c r="I273" s="2" t="inlineStr">
@@ -13343,7 +13343,7 @@
       </c>
       <c r="H274" s="2" t="inlineStr">
         <is>
-          <t>30/38</t>
+          <t>31/39</t>
         </is>
       </c>
       <c r="I274" s="2" t="inlineStr">
@@ -13390,7 +13390,7 @@
       </c>
       <c r="H275" s="2" t="inlineStr">
         <is>
-          <t>27/38</t>
+          <t>27/39</t>
         </is>
       </c>
       <c r="I275" s="2" t="inlineStr">
@@ -13437,7 +13437,7 @@
       </c>
       <c r="H276" s="2" t="inlineStr">
         <is>
-          <t>28/38</t>
+          <t>29/39</t>
         </is>
       </c>
       <c r="I276" s="2" t="inlineStr">
@@ -13480,7 +13480,7 @@
       <c r="G277" s="5" t="inlineStr"/>
       <c r="H277" s="5" t="inlineStr">
         <is>
-          <t>0/38</t>
+          <t>0/39</t>
         </is>
       </c>
       <c r="I277" s="5" t="inlineStr">
@@ -13527,7 +13527,7 @@
       </c>
       <c r="H278" s="2" t="inlineStr">
         <is>
-          <t>28/38</t>
+          <t>29/39</t>
         </is>
       </c>
       <c r="I278" s="2" t="inlineStr">
@@ -13574,7 +13574,7 @@
       </c>
       <c r="H279" s="2" t="inlineStr">
         <is>
-          <t>29/38</t>
+          <t>29/39</t>
         </is>
       </c>
       <c r="I279" s="2" t="inlineStr">
@@ -13621,7 +13621,7 @@
       </c>
       <c r="H280" s="2" t="inlineStr">
         <is>
-          <t>28/38</t>
+          <t>28/39</t>
         </is>
       </c>
       <c r="I280" s="2" t="inlineStr">
@@ -13668,7 +13668,7 @@
       </c>
       <c r="H281" s="2" t="inlineStr">
         <is>
-          <t>25/38</t>
+          <t>26/39</t>
         </is>
       </c>
       <c r="I281" s="2" t="inlineStr">
@@ -13715,7 +13715,7 @@
       </c>
       <c r="H282" s="2" t="inlineStr">
         <is>
-          <t>28/38</t>
+          <t>28/39</t>
         </is>
       </c>
       <c r="I282" s="2" t="inlineStr">
@@ -13758,7 +13758,7 @@
       <c r="G283" s="5" t="inlineStr"/>
       <c r="H283" s="5" t="inlineStr">
         <is>
-          <t>0/38</t>
+          <t>0/39</t>
         </is>
       </c>
       <c r="I283" s="5" t="inlineStr">
@@ -13801,7 +13801,7 @@
       <c r="G284" s="5" t="inlineStr"/>
       <c r="H284" s="5" t="inlineStr">
         <is>
-          <t>0/38</t>
+          <t>0/39</t>
         </is>
       </c>
       <c r="I284" s="5" t="inlineStr">
@@ -13844,7 +13844,7 @@
       <c r="G285" s="5" t="inlineStr"/>
       <c r="H285" s="5" t="inlineStr">
         <is>
-          <t>0/38</t>
+          <t>0/39</t>
         </is>
       </c>
       <c r="I285" s="5" t="inlineStr">
@@ -13887,7 +13887,7 @@
       <c r="G286" s="5" t="inlineStr"/>
       <c r="H286" s="5" t="inlineStr">
         <is>
-          <t>0/38</t>
+          <t>0/39</t>
         </is>
       </c>
       <c r="I286" s="5" t="inlineStr">
@@ -13930,7 +13930,7 @@
       <c r="G287" s="6" t="inlineStr"/>
       <c r="H287" s="6" t="inlineStr">
         <is>
-          <t>0/38</t>
+          <t>0/39</t>
         </is>
       </c>
       <c r="I287" s="6" t="inlineStr">
@@ -13973,7 +13973,7 @@
       <c r="G288" s="6" t="inlineStr"/>
       <c r="H288" s="6" t="inlineStr">
         <is>
-          <t>0/38</t>
+          <t>0/39</t>
         </is>
       </c>
       <c r="I288" s="6" t="inlineStr">
@@ -14016,7 +14016,7 @@
       <c r="G289" s="6" t="inlineStr"/>
       <c r="H289" s="6" t="inlineStr">
         <is>
-          <t>0/38</t>
+          <t>0/39</t>
         </is>
       </c>
       <c r="I289" s="6" t="inlineStr">
@@ -14059,7 +14059,7 @@
       <c r="G290" s="6" t="inlineStr"/>
       <c r="H290" s="6" t="inlineStr">
         <is>
-          <t>0/38</t>
+          <t>0/39</t>
         </is>
       </c>
       <c r="I290" s="6" t="inlineStr">
@@ -14102,7 +14102,7 @@
       <c r="G291" s="6" t="inlineStr"/>
       <c r="H291" s="6" t="inlineStr">
         <is>
-          <t>0/38</t>
+          <t>0/39</t>
         </is>
       </c>
       <c r="I291" s="6" t="inlineStr">
@@ -14145,7 +14145,7 @@
       <c r="G292" s="6" t="inlineStr"/>
       <c r="H292" s="6" t="inlineStr">
         <is>
-          <t>0/38</t>
+          <t>0/39</t>
         </is>
       </c>
       <c r="I292" s="6" t="inlineStr">
@@ -14188,7 +14188,7 @@
       <c r="G293" s="6" t="inlineStr"/>
       <c r="H293" s="6" t="inlineStr">
         <is>
-          <t>0/38</t>
+          <t>0/39</t>
         </is>
       </c>
       <c r="I293" s="6" t="inlineStr">
@@ -14231,7 +14231,7 @@
       <c r="G294" s="6" t="inlineStr"/>
       <c r="H294" s="6" t="inlineStr">
         <is>
-          <t>0/38</t>
+          <t>0/39</t>
         </is>
       </c>
       <c r="I294" s="6" t="inlineStr">
@@ -14274,7 +14274,7 @@
       <c r="G295" s="6" t="inlineStr"/>
       <c r="H295" s="6" t="inlineStr">
         <is>
-          <t>0/38</t>
+          <t>0/39</t>
         </is>
       </c>
       <c r="I295" s="6" t="inlineStr">
@@ -14317,7 +14317,7 @@
       <c r="G296" s="6" t="inlineStr"/>
       <c r="H296" s="6" t="inlineStr">
         <is>
-          <t>0/38</t>
+          <t>0/39</t>
         </is>
       </c>
       <c r="I296" s="6" t="inlineStr">
@@ -14360,7 +14360,7 @@
       <c r="G297" s="6" t="inlineStr"/>
       <c r="H297" s="6" t="inlineStr">
         <is>
-          <t>0/38</t>
+          <t>0/39</t>
         </is>
       </c>
       <c r="I297" s="6" t="inlineStr">
@@ -14403,7 +14403,7 @@
       <c r="G298" s="6" t="inlineStr"/>
       <c r="H298" s="6" t="inlineStr">
         <is>
-          <t>0/38</t>
+          <t>0/39</t>
         </is>
       </c>
       <c r="I298" s="6" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A1_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A1_session_analysis.xlsx
@@ -814,7 +814,7 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>132</v>
+        <v>144</v>
       </c>
     </row>
     <row r="7">
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>54</v>
+        <v>42</v>
       </c>
     </row>
     <row r="8">
@@ -980,7 +980,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>40.7%</t>
+          <t>44.4%</t>
         </is>
       </c>
     </row>
@@ -1037,7 +1037,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>69.9%</t>
+          <t>70.7%</t>
         </is>
       </c>
     </row>
@@ -1188,45 +1188,49 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>A1-A1</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>20/06/2026</t>
         </is>
       </c>
-      <c r="F14" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G14" s="5" t="inlineStr"/>
-      <c r="H14" s="5" t="inlineStr">
-        <is>
-          <t>0/34</t>
-        </is>
-      </c>
-      <c r="I14" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>28/34</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
       <c r="K14" s="1" t="inlineStr">
@@ -1334,22 +1338,22 @@
         <v>27</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q15" s="4" t="n">
         <v>11</v>
       </c>
       <c r="R15" s="4" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>51.9%</t>
         </is>
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>64.2%</t>
+          <t>66.2%</t>
         </is>
       </c>
     </row>
@@ -1412,65 +1416,69 @@
         <v>27</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q16" s="4" t="n">
         <v>11</v>
       </c>
       <c r="R16" s="4" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>51.9%</t>
         </is>
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>64.4%</t>
+          <t>67.3%</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>A1-A1</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="E17" s="5" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>27/06/2026</t>
         </is>
       </c>
-      <c r="F17" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G17" s="5" t="inlineStr"/>
-      <c r="H17" s="5" t="inlineStr">
-        <is>
-          <t>0/34</t>
-        </is>
-      </c>
-      <c r="I17" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>25/34</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
       <c r="K17" s="4" t="inlineStr">
@@ -1490,22 +1498,22 @@
         <v>27</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q17" s="4" t="n">
         <v>11</v>
       </c>
       <c r="R17" s="4" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>51.9%</t>
         </is>
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>75.7%</t>
+          <t>76.7%</t>
         </is>
       </c>
     </row>
@@ -1568,22 +1576,22 @@
         <v>27</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q18" s="4" t="n">
         <v>11</v>
       </c>
       <c r="R18" s="4" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>51.9%</t>
         </is>
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>73.5%</t>
+          <t>74.6%</t>
         </is>
       </c>
     </row>
@@ -1646,22 +1654,22 @@
         <v>27</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q19" s="4" t="n">
         <v>11</v>
       </c>
       <c r="R19" s="4" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>51.9%</t>
         </is>
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>76.5%</t>
+          <t>76.9%</t>
         </is>
       </c>
     </row>
@@ -1724,22 +1732,22 @@
         <v>27</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q20" s="4" t="n">
         <v>11</v>
       </c>
       <c r="R20" s="4" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>51.9%</t>
         </is>
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>65.7%</t>
+          <t>66.5%</t>
         </is>
       </c>
     </row>
@@ -2927,45 +2935,49 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B41" s="5" t="inlineStr">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>A1-A2</t>
         </is>
       </c>
-      <c r="C41" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D41" s="5" t="inlineStr">
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="E41" s="5" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>20/06/2026</t>
         </is>
       </c>
-      <c r="F41" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G41" s="5" t="inlineStr"/>
-      <c r="H41" s="5" t="inlineStr">
-        <is>
-          <t>0/33</t>
-        </is>
-      </c>
-      <c r="I41" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>30/33</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -3056,45 +3068,49 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B44" s="5" t="inlineStr">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>A1-A2</t>
         </is>
       </c>
-      <c r="C44" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D44" s="5" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="E44" s="5" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>27/06/2026</t>
         </is>
       </c>
-      <c r="F44" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G44" s="5" t="inlineStr"/>
-      <c r="H44" s="5" t="inlineStr">
-        <is>
-          <t>0/33</t>
-        </is>
-      </c>
-      <c r="I44" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>26/33</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -4136,45 +4152,49 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B68" s="5" t="inlineStr">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
         <is>
           <t>A1-B1</t>
         </is>
       </c>
-      <c r="C68" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D68" s="5" t="inlineStr">
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="E68" s="5" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t>20/06/2026</t>
         </is>
       </c>
-      <c r="F68" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G68" s="5" t="inlineStr"/>
-      <c r="H68" s="5" t="inlineStr">
-        <is>
-          <t>0/34</t>
-        </is>
-      </c>
-      <c r="I68" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>26/34</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -4265,45 +4285,49 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B71" s="5" t="inlineStr">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
         <is>
           <t>A1-B1</t>
         </is>
       </c>
-      <c r="C71" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D71" s="5" t="inlineStr">
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="E71" s="5" t="inlineStr">
+      <c r="E71" s="2" t="inlineStr">
         <is>
           <t>27/06/2026</t>
         </is>
       </c>
-      <c r="F71" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G71" s="5" t="inlineStr"/>
-      <c r="H71" s="5" t="inlineStr">
-        <is>
-          <t>0/34</t>
-        </is>
-      </c>
-      <c r="I71" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>30/34</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -5345,45 +5369,49 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B95" s="5" t="inlineStr">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
         <is>
           <t>A1-B2</t>
         </is>
       </c>
-      <c r="C95" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D95" s="5" t="inlineStr">
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="E95" s="5" t="inlineStr">
+      <c r="E95" s="2" t="inlineStr">
         <is>
           <t>20/06/2026</t>
         </is>
       </c>
-      <c r="F95" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G95" s="5" t="inlineStr"/>
-      <c r="H95" s="5" t="inlineStr">
-        <is>
-          <t>0/34</t>
-        </is>
-      </c>
-      <c r="I95" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>27/34</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -5474,45 +5502,49 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B98" s="5" t="inlineStr">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
         <is>
           <t>A1-B2</t>
         </is>
       </c>
-      <c r="C98" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D98" s="5" t="inlineStr">
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="E98" s="5" t="inlineStr">
+      <c r="E98" s="2" t="inlineStr">
         <is>
           <t>27/06/2026</t>
         </is>
       </c>
-      <c r="F98" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G98" s="5" t="inlineStr"/>
-      <c r="H98" s="5" t="inlineStr">
-        <is>
-          <t>0/34</t>
-        </is>
-      </c>
-      <c r="I98" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>28/34</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -6554,45 +6586,49 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B122" s="5" t="inlineStr">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
         <is>
           <t>A1-C1</t>
         </is>
       </c>
-      <c r="C122" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D122" s="5" t="inlineStr">
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="E122" s="5" t="inlineStr">
+      <c r="E122" s="2" t="inlineStr">
         <is>
           <t>20/06/2026</t>
         </is>
       </c>
-      <c r="F122" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G122" s="5" t="inlineStr"/>
-      <c r="H122" s="5" t="inlineStr">
-        <is>
-          <t>0/34</t>
-        </is>
-      </c>
-      <c r="I122" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G122" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H122" s="2" t="inlineStr">
+        <is>
+          <t>25/34</t>
+        </is>
+      </c>
+      <c r="I122" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -6683,45 +6719,49 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B125" s="5" t="inlineStr">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
         <is>
           <t>A1-C1</t>
         </is>
       </c>
-      <c r="C125" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D125" s="5" t="inlineStr">
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="E125" s="5" t="inlineStr">
+      <c r="E125" s="2" t="inlineStr">
         <is>
           <t>27/06/2026</t>
         </is>
       </c>
-      <c r="F125" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G125" s="5" t="inlineStr"/>
-      <c r="H125" s="5" t="inlineStr">
-        <is>
-          <t>0/34</t>
-        </is>
-      </c>
-      <c r="I125" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G125" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H125" s="2" t="inlineStr">
+        <is>
+          <t>29/34</t>
+        </is>
+      </c>
+      <c r="I125" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -7763,45 +7803,49 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B149" s="5" t="inlineStr">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
         <is>
           <t>A1-C2</t>
         </is>
       </c>
-      <c r="C149" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D149" s="5" t="inlineStr">
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="E149" s="5" t="inlineStr">
+      <c r="E149" s="2" t="inlineStr">
         <is>
           <t>20/06/2026</t>
         </is>
       </c>
-      <c r="F149" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G149" s="5" t="inlineStr"/>
-      <c r="H149" s="5" t="inlineStr">
-        <is>
-          <t>0/33</t>
-        </is>
-      </c>
-      <c r="I149" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F149" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G149" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H149" s="2" t="inlineStr">
+        <is>
+          <t>22/33</t>
+        </is>
+      </c>
+      <c r="I149" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -7892,45 +7936,49 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B152" s="5" t="inlineStr">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
         <is>
           <t>A1-C2</t>
         </is>
       </c>
-      <c r="C152" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D152" s="5" t="inlineStr">
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="E152" s="5" t="inlineStr">
+      <c r="E152" s="2" t="inlineStr">
         <is>
           <t>27/06/2026</t>
         </is>
       </c>
-      <c r="F152" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G152" s="5" t="inlineStr"/>
-      <c r="H152" s="5" t="inlineStr">
-        <is>
-          <t>0/33</t>
-        </is>
-      </c>
-      <c r="I152" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F152" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G152" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H152" s="2" t="inlineStr">
+        <is>
+          <t>25/33</t>
+        </is>
+      </c>
+      <c r="I152" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A1_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A1_session_analysis.xlsx
@@ -814,7 +814,7 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>144</v>
+        <v>150</v>
       </c>
     </row>
     <row r="7">
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8">
@@ -980,7 +980,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>46.3%</t>
         </is>
       </c>
     </row>
@@ -1037,7 +1037,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>70.7%</t>
+          <t>71.8%</t>
         </is>
       </c>
     </row>
@@ -1280,45 +1280,49 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>A1-A1</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="E15" s="5" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>21/06/2026</t>
         </is>
       </c>
-      <c r="F15" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G15" s="5" t="inlineStr"/>
-      <c r="H15" s="5" t="inlineStr">
-        <is>
-          <t>0/34</t>
-        </is>
-      </c>
-      <c r="I15" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>34/34</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
       <c r="K15" s="4" t="inlineStr">
@@ -1338,22 +1342,22 @@
         <v>27</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q15" s="4" t="n">
         <v>11</v>
       </c>
       <c r="R15" s="4" t="inlineStr">
         <is>
-          <t>51.9%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>68.4%</t>
         </is>
       </c>
     </row>
@@ -1416,22 +1420,22 @@
         <v>27</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q16" s="4" t="n">
         <v>11</v>
       </c>
       <c r="R16" s="4" t="inlineStr">
         <is>
-          <t>51.9%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>69.5%</t>
         </is>
       </c>
     </row>
@@ -1498,22 +1502,22 @@
         <v>27</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q17" s="4" t="n">
         <v>11</v>
       </c>
       <c r="R17" s="4" t="inlineStr">
         <is>
-          <t>51.9%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>76.7%</t>
+          <t>78.2%</t>
         </is>
       </c>
     </row>
@@ -1576,22 +1580,22 @@
         <v>27</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q18" s="4" t="n">
         <v>11</v>
       </c>
       <c r="R18" s="4" t="inlineStr">
         <is>
-          <t>51.9%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>74.6%</t>
+          <t>76.3%</t>
         </is>
       </c>
     </row>
@@ -1654,22 +1658,22 @@
         <v>27</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q19" s="4" t="n">
         <v>11</v>
       </c>
       <c r="R19" s="4" t="inlineStr">
         <is>
-          <t>51.9%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>76.9%</t>
+          <t>78.4%</t>
         </is>
       </c>
     </row>
@@ -1732,22 +1736,22 @@
         <v>27</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q20" s="4" t="n">
         <v>11</v>
       </c>
       <c r="R20" s="4" t="inlineStr">
         <is>
-          <t>51.9%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>68.7%</t>
         </is>
       </c>
     </row>
@@ -2982,45 +2986,49 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B42" s="5" t="inlineStr">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>A1-A2</t>
         </is>
       </c>
-      <c r="C42" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D42" s="5" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="E42" s="5" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>21/06/2026</t>
         </is>
       </c>
-      <c r="F42" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G42" s="5" t="inlineStr"/>
-      <c r="H42" s="5" t="inlineStr">
-        <is>
-          <t>0/33</t>
-        </is>
-      </c>
-      <c r="I42" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>33/33</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -4199,45 +4207,49 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B69" s="5" t="inlineStr">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
         <is>
           <t>A1-B1</t>
         </is>
       </c>
-      <c r="C69" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D69" s="5" t="inlineStr">
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="E69" s="5" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr">
         <is>
           <t>21/06/2026</t>
         </is>
       </c>
-      <c r="F69" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G69" s="5" t="inlineStr"/>
-      <c r="H69" s="5" t="inlineStr">
-        <is>
-          <t>0/34</t>
-        </is>
-      </c>
-      <c r="I69" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>34/34</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -5416,45 +5428,49 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B96" s="5" t="inlineStr">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
         <is>
           <t>A1-B2</t>
         </is>
       </c>
-      <c r="C96" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D96" s="5" t="inlineStr">
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="E96" s="5" t="inlineStr">
+      <c r="E96" s="2" t="inlineStr">
         <is>
           <t>21/06/2026</t>
         </is>
       </c>
-      <c r="F96" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G96" s="5" t="inlineStr"/>
-      <c r="H96" s="5" t="inlineStr">
-        <is>
-          <t>0/34</t>
-        </is>
-      </c>
-      <c r="I96" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>34/34</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -6633,45 +6649,49 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B123" s="5" t="inlineStr">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
         <is>
           <t>A1-C1</t>
         </is>
       </c>
-      <c r="C123" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D123" s="5" t="inlineStr">
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="E123" s="5" t="inlineStr">
+      <c r="E123" s="2" t="inlineStr">
         <is>
           <t>21/06/2026</t>
         </is>
       </c>
-      <c r="F123" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G123" s="5" t="inlineStr"/>
-      <c r="H123" s="5" t="inlineStr">
-        <is>
-          <t>0/34</t>
-        </is>
-      </c>
-      <c r="I123" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G123" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H123" s="2" t="inlineStr">
+        <is>
+          <t>34/34</t>
+        </is>
+      </c>
+      <c r="I123" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -7850,45 +7870,49 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B150" s="5" t="inlineStr">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
         <is>
           <t>A1-C2</t>
         </is>
       </c>
-      <c r="C150" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D150" s="5" t="inlineStr">
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="E150" s="5" t="inlineStr">
+      <c r="E150" s="2" t="inlineStr">
         <is>
           <t>21/06/2026</t>
         </is>
       </c>
-      <c r="F150" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G150" s="5" t="inlineStr"/>
-      <c r="H150" s="5" t="inlineStr">
-        <is>
-          <t>0/33</t>
-        </is>
-      </c>
-      <c r="I150" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F150" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G150" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H150" s="2" t="inlineStr">
+        <is>
+          <t>33/33</t>
+        </is>
+      </c>
+      <c r="I150" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A1_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A1_session_analysis.xlsx
@@ -814,7 +814,7 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>150</v>
+        <v>156</v>
       </c>
     </row>
     <row r="7">
@@ -924,7 +924,7 @@
         </is>
       </c>
       <c r="L8" s="4" t="n">
-        <v>138</v>
+        <v>132</v>
       </c>
     </row>
     <row r="9">
@@ -980,7 +980,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>48.1%</t>
         </is>
       </c>
     </row>
@@ -1037,7 +1037,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>71.8%</t>
+          <t>72.5%</t>
         </is>
       </c>
     </row>
@@ -1342,22 +1342,22 @@
         <v>27</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="P15" s="4" t="n">
         <v>1</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R15" s="4" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>59.3%</t>
         </is>
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>68.4%</t>
+          <t>69.9%</t>
         </is>
       </c>
     </row>
@@ -1420,22 +1420,22 @@
         <v>27</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="P16" s="4" t="n">
         <v>1</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R16" s="4" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>59.3%</t>
         </is>
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>69.5%</t>
+          <t>71.0%</t>
         </is>
       </c>
     </row>
@@ -1502,65 +1502,69 @@
         <v>27</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="P17" s="4" t="n">
         <v>1</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R17" s="4" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>59.3%</t>
         </is>
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>78.2%</t>
+          <t>78.5%</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B18" s="6" t="inlineStr">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>A1-A1</t>
         </is>
       </c>
-      <c r="C18" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D18" s="6" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="E18" s="6" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>28/06/2026</t>
         </is>
       </c>
-      <c r="F18" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G18" s="6" t="inlineStr"/>
-      <c r="H18" s="6" t="inlineStr">
-        <is>
-          <t>0/34</t>
-        </is>
-      </c>
-      <c r="I18" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>31/34</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
       <c r="K18" s="4" t="inlineStr">
@@ -1580,22 +1584,22 @@
         <v>27</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="P18" s="4" t="n">
         <v>1</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R18" s="4" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>59.3%</t>
         </is>
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>76.3%</t>
+          <t>76.7%</t>
         </is>
       </c>
     </row>
@@ -1658,22 +1662,22 @@
         <v>27</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="P19" s="4" t="n">
         <v>1</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R19" s="4" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>59.3%</t>
         </is>
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>78.4%</t>
+          <t>79.0%</t>
         </is>
       </c>
     </row>
@@ -1736,22 +1740,22 @@
         <v>27</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="P20" s="4" t="n">
         <v>1</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R20" s="4" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>59.3%</t>
         </is>
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>68.7%</t>
+          <t>69.9%</t>
         </is>
       </c>
     </row>
@@ -3123,45 +3127,49 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B45" s="6" t="inlineStr">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>A1-A2</t>
         </is>
       </c>
-      <c r="C45" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D45" s="6" t="inlineStr">
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="E45" s="6" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>28/06/2026</t>
         </is>
       </c>
-      <c r="F45" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G45" s="6" t="inlineStr"/>
-      <c r="H45" s="6" t="inlineStr">
-        <is>
-          <t>0/33</t>
-        </is>
-      </c>
-      <c r="I45" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>31/33</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -4344,45 +4352,49 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B72" s="6" t="inlineStr">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
         <is>
           <t>A1-B1</t>
         </is>
       </c>
-      <c r="C72" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D72" s="6" t="inlineStr">
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="E72" s="6" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>28/06/2026</t>
         </is>
       </c>
-      <c r="F72" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G72" s="6" t="inlineStr"/>
-      <c r="H72" s="6" t="inlineStr">
-        <is>
-          <t>0/34</t>
-        </is>
-      </c>
-      <c r="I72" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>28/34</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -5565,45 +5577,49 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B99" s="6" t="inlineStr">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
         <is>
           <t>A1-B2</t>
         </is>
       </c>
-      <c r="C99" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D99" s="6" t="inlineStr">
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="E99" s="6" t="inlineStr">
+      <c r="E99" s="2" t="inlineStr">
         <is>
           <t>28/06/2026</t>
         </is>
       </c>
-      <c r="F99" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G99" s="6" t="inlineStr"/>
-      <c r="H99" s="6" t="inlineStr">
-        <is>
-          <t>0/34</t>
-        </is>
-      </c>
-      <c r="I99" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>28/34</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -6786,45 +6802,49 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B126" s="6" t="inlineStr">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
         <is>
           <t>A1-C1</t>
         </is>
       </c>
-      <c r="C126" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D126" s="6" t="inlineStr">
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="E126" s="6" t="inlineStr">
+      <c r="E126" s="2" t="inlineStr">
         <is>
           <t>28/06/2026</t>
         </is>
       </c>
-      <c r="F126" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G126" s="6" t="inlineStr"/>
-      <c r="H126" s="6" t="inlineStr">
-        <is>
-          <t>0/34</t>
-        </is>
-      </c>
-      <c r="I126" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H126" s="2" t="inlineStr">
+        <is>
+          <t>30/34</t>
+        </is>
+      </c>
+      <c r="I126" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -8007,45 +8027,49 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B153" s="6" t="inlineStr">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
         <is>
           <t>A1-C2</t>
         </is>
       </c>
-      <c r="C153" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D153" s="6" t="inlineStr">
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="E153" s="6" t="inlineStr">
+      <c r="E153" s="2" t="inlineStr">
         <is>
           <t>28/06/2026</t>
         </is>
       </c>
-      <c r="F153" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G153" s="6" t="inlineStr"/>
-      <c r="H153" s="6" t="inlineStr">
-        <is>
-          <t>0/33</t>
-        </is>
-      </c>
-      <c r="I153" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F153" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G153" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H153" s="2" t="inlineStr">
+        <is>
+          <t>29/33</t>
+        </is>
+      </c>
+      <c r="I153" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A1_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A1_session_analysis.xlsx
@@ -814,7 +814,7 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="7">
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="8">
@@ -924,7 +924,7 @@
         </is>
       </c>
       <c r="L8" s="4" t="n">
-        <v>132</v>
+        <v>126</v>
       </c>
     </row>
     <row r="9">
@@ -980,7 +980,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>48.8%</t>
         </is>
       </c>
     </row>
@@ -1037,7 +1037,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>72.5%</t>
+          <t>72.7%</t>
         </is>
       </c>
     </row>
@@ -1345,10 +1345,10 @@
         <v>16</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R15" s="4" t="inlineStr">
         <is>
@@ -1423,10 +1423,10 @@
         <v>16</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R16" s="4" t="inlineStr">
         <is>
@@ -1505,10 +1505,10 @@
         <v>16</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R17" s="4" t="inlineStr">
         <is>
@@ -1587,10 +1587,10 @@
         <v>16</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R18" s="4" t="inlineStr">
         <is>
@@ -1604,45 +1604,45 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="inlineStr">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>A1-A1</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D19" s="6" t="inlineStr">
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="E19" s="6" t="inlineStr">
+      <c r="E19" s="5" t="inlineStr">
         <is>
           <t>29/06/2026</t>
         </is>
       </c>
-      <c r="F19" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G19" s="6" t="inlineStr"/>
-      <c r="H19" s="6" t="inlineStr">
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="inlineStr"/>
+      <c r="H19" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I19" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I19" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
       <c r="K19" s="4" t="inlineStr">
@@ -1665,10 +1665,10 @@
         <v>16</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R19" s="4" t="inlineStr">
         <is>
@@ -1743,10 +1743,10 @@
         <v>16</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R20" s="4" t="inlineStr">
         <is>
@@ -1818,22 +1818,22 @@
         <v>27</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Q21" s="4" t="n">
         <v>12</v>
       </c>
       <c r="R21" s="4" t="inlineStr">
         <is>
-          <t>37.0%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>66.9%</t>
+          <t>71.0%</t>
         </is>
       </c>
     </row>
@@ -3174,45 +3174,45 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B46" s="6" t="inlineStr">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
         <is>
           <t>A1-A2</t>
         </is>
       </c>
-      <c r="C46" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D46" s="6" t="inlineStr">
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="E46" s="6" t="inlineStr">
+      <c r="E46" s="5" t="inlineStr">
         <is>
           <t>29/06/2026</t>
         </is>
       </c>
-      <c r="F46" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G46" s="6" t="inlineStr"/>
-      <c r="H46" s="6" t="inlineStr">
+      <c r="F46" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G46" s="5" t="inlineStr"/>
+      <c r="H46" s="5" t="inlineStr">
         <is>
           <t>0/33</t>
         </is>
       </c>
-      <c r="I46" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I46" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -4399,45 +4399,45 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B73" s="6" t="inlineStr">
+      <c r="A73" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B73" s="5" t="inlineStr">
         <is>
           <t>A1-B1</t>
         </is>
       </c>
-      <c r="C73" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D73" s="6" t="inlineStr">
+      <c r="C73" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D73" s="5" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="E73" s="6" t="inlineStr">
+      <c r="E73" s="5" t="inlineStr">
         <is>
           <t>29/06/2026</t>
         </is>
       </c>
-      <c r="F73" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G73" s="6" t="inlineStr"/>
-      <c r="H73" s="6" t="inlineStr">
+      <c r="F73" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G73" s="5" t="inlineStr"/>
+      <c r="H73" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I73" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I73" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -5624,45 +5624,45 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B100" s="6" t="inlineStr">
+      <c r="A100" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B100" s="5" t="inlineStr">
         <is>
           <t>A1-B2</t>
         </is>
       </c>
-      <c r="C100" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D100" s="6" t="inlineStr">
+      <c r="C100" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D100" s="5" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="E100" s="6" t="inlineStr">
+      <c r="E100" s="5" t="inlineStr">
         <is>
           <t>29/06/2026</t>
         </is>
       </c>
-      <c r="F100" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G100" s="6" t="inlineStr"/>
-      <c r="H100" s="6" t="inlineStr">
+      <c r="F100" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G100" s="5" t="inlineStr"/>
+      <c r="H100" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I100" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I100" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -6849,45 +6849,45 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B127" s="6" t="inlineStr">
+      <c r="A127" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B127" s="5" t="inlineStr">
         <is>
           <t>A1-C1</t>
         </is>
       </c>
-      <c r="C127" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D127" s="6" t="inlineStr">
+      <c r="C127" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D127" s="5" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="E127" s="6" t="inlineStr">
+      <c r="E127" s="5" t="inlineStr">
         <is>
           <t>29/06/2026</t>
         </is>
       </c>
-      <c r="F127" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G127" s="6" t="inlineStr"/>
-      <c r="H127" s="6" t="inlineStr">
+      <c r="F127" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G127" s="5" t="inlineStr"/>
+      <c r="H127" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I127" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I127" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -8074,45 +8074,45 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B154" s="6" t="inlineStr">
+      <c r="A154" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B154" s="5" t="inlineStr">
         <is>
           <t>A1-C2</t>
         </is>
       </c>
-      <c r="C154" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D154" s="6" t="inlineStr">
+      <c r="C154" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D154" s="5" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="E154" s="6" t="inlineStr">
+      <c r="E154" s="5" t="inlineStr">
         <is>
           <t>29/06/2026</t>
         </is>
       </c>
-      <c r="F154" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G154" s="6" t="inlineStr"/>
-      <c r="H154" s="6" t="inlineStr">
+      <c r="F154" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G154" s="5" t="inlineStr"/>
+      <c r="H154" s="5" t="inlineStr">
         <is>
           <t>0/33</t>
         </is>
       </c>
-      <c r="I154" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I154" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -9017,88 +9017,96 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B175" s="5" t="inlineStr">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
         <is>
           <t>A1-D1</t>
         </is>
       </c>
-      <c r="C175" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D175" s="5" t="inlineStr">
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="E175" s="5" t="inlineStr">
+      <c r="E175" s="2" t="inlineStr">
         <is>
           <t>18/06/2026</t>
         </is>
       </c>
-      <c r="F175" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G175" s="5" t="inlineStr"/>
-      <c r="H175" s="5" t="inlineStr">
-        <is>
-          <t>0/35</t>
-        </is>
-      </c>
-      <c r="I175" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F175" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G175" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H175" s="2" t="inlineStr">
+        <is>
+          <t>32/35</t>
+        </is>
+      </c>
+      <c r="I175" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B176" s="5" t="inlineStr">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B176" s="2" t="inlineStr">
         <is>
           <t>A1-D1</t>
         </is>
       </c>
-      <c r="C176" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D176" s="5" t="inlineStr">
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="E176" s="5" t="inlineStr">
+      <c r="E176" s="2" t="inlineStr">
         <is>
           <t>23/06/2026</t>
         </is>
       </c>
-      <c r="F176" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G176" s="5" t="inlineStr"/>
-      <c r="H176" s="5" t="inlineStr">
-        <is>
-          <t>0/35</t>
-        </is>
-      </c>
-      <c r="I176" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F176" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G176" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H176" s="2" t="inlineStr">
+        <is>
+          <t>32/35</t>
+        </is>
+      </c>
+      <c r="I176" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A1_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A1_session_analysis.xlsx
@@ -814,7 +814,7 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>158</v>
+        <v>164</v>
       </c>
     </row>
     <row r="7">
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8">
@@ -980,7 +980,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>48.8%</t>
+          <t>50.6%</t>
         </is>
       </c>
     </row>
@@ -1037,7 +1037,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>72.7%</t>
+          <t>73.2%</t>
         </is>
       </c>
     </row>
@@ -1342,22 +1342,22 @@
         <v>27</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q15" s="4" t="n">
         <v>9</v>
       </c>
       <c r="R15" s="4" t="inlineStr">
         <is>
-          <t>59.3%</t>
+          <t>63.0%</t>
         </is>
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>69.9%</t>
+          <t>71.3%</t>
         </is>
       </c>
     </row>
@@ -1420,22 +1420,22 @@
         <v>27</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q16" s="4" t="n">
         <v>9</v>
       </c>
       <c r="R16" s="4" t="inlineStr">
         <is>
-          <t>59.3%</t>
+          <t>63.0%</t>
         </is>
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>71.0%</t>
+          <t>72.0%</t>
         </is>
       </c>
     </row>
@@ -1502,22 +1502,22 @@
         <v>27</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q17" s="4" t="n">
         <v>9</v>
       </c>
       <c r="R17" s="4" t="inlineStr">
         <is>
-          <t>59.3%</t>
+          <t>63.0%</t>
         </is>
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>78.5%</t>
+          <t>79.2%</t>
         </is>
       </c>
     </row>
@@ -1584,65 +1584,69 @@
         <v>27</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q18" s="4" t="n">
         <v>9</v>
       </c>
       <c r="R18" s="4" t="inlineStr">
         <is>
-          <t>59.3%</t>
+          <t>63.0%</t>
         </is>
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>76.7%</t>
+          <t>77.0%</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>A1-A1</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="E19" s="5" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>29/06/2026</t>
         </is>
       </c>
-      <c r="F19" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G19" s="5" t="inlineStr"/>
-      <c r="H19" s="5" t="inlineStr">
-        <is>
-          <t>0/34</t>
-        </is>
-      </c>
-      <c r="I19" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>32/34</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
       <c r="K19" s="4" t="inlineStr">
@@ -1662,22 +1666,22 @@
         <v>27</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q19" s="4" t="n">
         <v>9</v>
       </c>
       <c r="R19" s="4" t="inlineStr">
         <is>
-          <t>59.3%</t>
+          <t>63.0%</t>
         </is>
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>79.0%</t>
+          <t>79.2%</t>
         </is>
       </c>
     </row>
@@ -1740,22 +1744,22 @@
         <v>27</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q20" s="4" t="n">
         <v>9</v>
       </c>
       <c r="R20" s="4" t="inlineStr">
         <is>
-          <t>59.3%</t>
+          <t>63.0%</t>
         </is>
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>69.9%</t>
+          <t>70.8%</t>
         </is>
       </c>
     </row>
@@ -3174,45 +3178,49 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B46" s="5" t="inlineStr">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>A1-A2</t>
         </is>
       </c>
-      <c r="C46" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D46" s="5" t="inlineStr">
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="E46" s="5" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>29/06/2026</t>
         </is>
       </c>
-      <c r="F46" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G46" s="5" t="inlineStr"/>
-      <c r="H46" s="5" t="inlineStr">
-        <is>
-          <t>0/33</t>
-        </is>
-      </c>
-      <c r="I46" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>29/33</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -4399,45 +4407,49 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B73" s="5" t="inlineStr">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
         <is>
           <t>A1-B1</t>
         </is>
       </c>
-      <c r="C73" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D73" s="5" t="inlineStr">
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="E73" s="5" t="inlineStr">
+      <c r="E73" s="2" t="inlineStr">
         <is>
           <t>29/06/2026</t>
         </is>
       </c>
-      <c r="F73" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G73" s="5" t="inlineStr"/>
-      <c r="H73" s="5" t="inlineStr">
-        <is>
-          <t>0/34</t>
-        </is>
-      </c>
-      <c r="I73" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>31/34</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -5624,45 +5636,49 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B100" s="5" t="inlineStr">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
         <is>
           <t>A1-B2</t>
         </is>
       </c>
-      <c r="C100" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D100" s="5" t="inlineStr">
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="E100" s="5" t="inlineStr">
+      <c r="E100" s="2" t="inlineStr">
         <is>
           <t>29/06/2026</t>
         </is>
       </c>
-      <c r="F100" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G100" s="5" t="inlineStr"/>
-      <c r="H100" s="5" t="inlineStr">
-        <is>
-          <t>0/34</t>
-        </is>
-      </c>
-      <c r="I100" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>28/34</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -6849,45 +6865,49 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B127" s="5" t="inlineStr">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
         <is>
           <t>A1-C1</t>
         </is>
       </c>
-      <c r="C127" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D127" s="5" t="inlineStr">
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="E127" s="5" t="inlineStr">
+      <c r="E127" s="2" t="inlineStr">
         <is>
           <t>29/06/2026</t>
         </is>
       </c>
-      <c r="F127" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G127" s="5" t="inlineStr"/>
-      <c r="H127" s="5" t="inlineStr">
-        <is>
-          <t>0/34</t>
-        </is>
-      </c>
-      <c r="I127" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H127" s="2" t="inlineStr">
+        <is>
+          <t>28/34</t>
+        </is>
+      </c>
+      <c r="I127" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -8074,45 +8094,49 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B154" s="5" t="inlineStr">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
         <is>
           <t>A1-C2</t>
         </is>
       </c>
-      <c r="C154" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D154" s="5" t="inlineStr">
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="E154" s="5" t="inlineStr">
+      <c r="E154" s="2" t="inlineStr">
         <is>
           <t>29/06/2026</t>
         </is>
       </c>
-      <c r="F154" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G154" s="5" t="inlineStr"/>
-      <c r="H154" s="5" t="inlineStr">
-        <is>
-          <t>0/33</t>
-        </is>
-      </c>
-      <c r="I154" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F154" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G154" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H154" s="2" t="inlineStr">
+        <is>
+          <t>28/33</t>
+        </is>
+      </c>
+      <c r="I154" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A1_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A1_session_analysis.xlsx
@@ -814,7 +814,7 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>180</v>
+        <v>190</v>
       </c>
     </row>
     <row r="7">
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8">
@@ -980,7 +980,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>58.6%</t>
         </is>
       </c>
     </row>
@@ -1037,7 +1037,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>75.6%</t>
+          <t>75.1%</t>
         </is>
       </c>
     </row>
@@ -1826,22 +1826,22 @@
         <v>27</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q21" s="4" t="n">
         <v>11</v>
       </c>
       <c r="R21" s="4" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>71.0%</t>
+          <t>71.6%</t>
         </is>
       </c>
     </row>
@@ -1904,22 +1904,22 @@
         <v>27</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q22" s="4" t="n">
         <v>11</v>
       </c>
       <c r="R22" s="4" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>76.2%</t>
+          <t>77.1%</t>
         </is>
       </c>
     </row>
@@ -1982,22 +1982,22 @@
         <v>27</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q23" s="4" t="n">
         <v>11</v>
       </c>
       <c r="R23" s="4" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>51.9%</t>
         </is>
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>75.2%</t>
+          <t>74.6%</t>
         </is>
       </c>
     </row>
@@ -2060,22 +2060,22 @@
         <v>27</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q24" s="4" t="n">
         <v>11</v>
       </c>
       <c r="R24" s="4" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>51.9%</t>
         </is>
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>72.9%</t>
+          <t>71.1%</t>
         </is>
       </c>
     </row>
@@ -2138,22 +2138,22 @@
         <v>27</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q25" s="4" t="n">
         <v>11</v>
       </c>
       <c r="R25" s="4" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>51.9%</t>
         </is>
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>78.2%</t>
+          <t>74.7%</t>
         </is>
       </c>
     </row>
@@ -2216,22 +2216,22 @@
         <v>27</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q26" s="4" t="n">
         <v>11</v>
       </c>
       <c r="R26" s="4" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>51.9%</t>
         </is>
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>73.7%</t>
+          <t>71.8%</t>
         </is>
       </c>
     </row>
@@ -9245,45 +9245,49 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B179" s="9" t="inlineStr">
+      <c r="A179" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B179" s="2" t="inlineStr">
         <is>
           <t>A1-D1</t>
         </is>
       </c>
-      <c r="C179" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D179" s="9" t="inlineStr">
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="E179" s="9" t="inlineStr">
+      <c r="E179" s="2" t="inlineStr">
         <is>
           <t>30/06/2026</t>
         </is>
       </c>
-      <c r="F179" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G179" s="9" t="inlineStr"/>
-      <c r="H179" s="9" t="inlineStr">
-        <is>
-          <t>0/35</t>
-        </is>
-      </c>
-      <c r="I179" s="9" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F179" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G179" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H179" s="2" t="inlineStr">
+        <is>
+          <t>28/35</t>
+        </is>
+      </c>
+      <c r="I179" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -10454,45 +10458,49 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B206" s="9" t="inlineStr">
+      <c r="A206" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B206" s="2" t="inlineStr">
         <is>
           <t>A1-D2</t>
         </is>
       </c>
-      <c r="C206" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D206" s="9" t="inlineStr">
+      <c r="C206" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D206" s="2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="E206" s="9" t="inlineStr">
+      <c r="E206" s="2" t="inlineStr">
         <is>
           <t>30/06/2026</t>
         </is>
       </c>
-      <c r="F206" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G206" s="9" t="inlineStr"/>
-      <c r="H206" s="9" t="inlineStr">
-        <is>
-          <t>0/34</t>
-        </is>
-      </c>
-      <c r="I206" s="9" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F206" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G206" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H206" s="2" t="inlineStr">
+        <is>
+          <t>30/34</t>
+        </is>
+      </c>
+      <c r="I206" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -11577,45 +11585,49 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B231" s="9" t="inlineStr">
+      <c r="A231" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B231" s="2" t="inlineStr">
         <is>
           <t>A1-E1</t>
         </is>
       </c>
-      <c r="C231" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D231" s="9" t="inlineStr">
+      <c r="C231" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D231" s="2" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="E231" s="9" t="inlineStr">
+      <c r="E231" s="2" t="inlineStr">
         <is>
           <t>24/06/2026</t>
         </is>
       </c>
-      <c r="F231" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G231" s="9" t="inlineStr"/>
-      <c r="H231" s="9" t="inlineStr">
-        <is>
-          <t>0/38</t>
-        </is>
-      </c>
-      <c r="I231" s="9" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F231" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G231" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H231" s="2" t="inlineStr">
+        <is>
+          <t>21/38</t>
+        </is>
+      </c>
+      <c r="I231" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -11663,45 +11675,49 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B233" s="9" t="inlineStr">
+      <c r="A233" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B233" s="2" t="inlineStr">
         <is>
           <t>A1-E1</t>
         </is>
       </c>
-      <c r="C233" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D233" s="9" t="inlineStr">
+      <c r="C233" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D233" s="2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="E233" s="9" t="inlineStr">
+      <c r="E233" s="2" t="inlineStr">
         <is>
           <t>30/06/2026</t>
         </is>
       </c>
-      <c r="F233" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G233" s="9" t="inlineStr"/>
-      <c r="H233" s="9" t="inlineStr">
-        <is>
-          <t>0/38</t>
-        </is>
-      </c>
-      <c r="I233" s="9" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F233" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G233" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H233" s="2" t="inlineStr">
+        <is>
+          <t>33/38</t>
+        </is>
+      </c>
+      <c r="I233" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -12786,45 +12802,49 @@
       </c>
     </row>
     <row r="258">
-      <c r="A258" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B258" s="9" t="inlineStr">
+      <c r="A258" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B258" s="2" t="inlineStr">
         <is>
           <t>A1-E2</t>
         </is>
       </c>
-      <c r="C258" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D258" s="9" t="inlineStr">
+      <c r="C258" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D258" s="2" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="E258" s="9" t="inlineStr">
+      <c r="E258" s="2" t="inlineStr">
         <is>
           <t>24/06/2026</t>
         </is>
       </c>
-      <c r="F258" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G258" s="9" t="inlineStr"/>
-      <c r="H258" s="9" t="inlineStr">
-        <is>
-          <t>0/39</t>
-        </is>
-      </c>
-      <c r="I258" s="9" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F258" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G258" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H258" s="2" t="inlineStr">
+        <is>
+          <t>12/39</t>
+        </is>
+      </c>
+      <c r="I258" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -12872,45 +12892,49 @@
       </c>
     </row>
     <row r="260">
-      <c r="A260" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B260" s="9" t="inlineStr">
+      <c r="A260" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B260" s="2" t="inlineStr">
         <is>
           <t>A1-E2</t>
         </is>
       </c>
-      <c r="C260" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D260" s="9" t="inlineStr">
+      <c r="C260" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D260" s="2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="E260" s="9" t="inlineStr">
+      <c r="E260" s="2" t="inlineStr">
         <is>
           <t>30/06/2026</t>
         </is>
       </c>
-      <c r="F260" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G260" s="9" t="inlineStr"/>
-      <c r="H260" s="9" t="inlineStr">
-        <is>
-          <t>0/39</t>
-        </is>
-      </c>
-      <c r="I260" s="9" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F260" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G260" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H260" s="2" t="inlineStr">
+        <is>
+          <t>35/39</t>
+        </is>
+      </c>
+      <c r="I260" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -13995,45 +14019,49 @@
       </c>
     </row>
     <row r="285">
-      <c r="A285" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B285" s="9" t="inlineStr">
+      <c r="A285" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B285" s="2" t="inlineStr">
         <is>
           <t>A1-F1</t>
         </is>
       </c>
-      <c r="C285" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D285" s="9" t="inlineStr">
+      <c r="C285" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D285" s="2" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="E285" s="9" t="inlineStr">
+      <c r="E285" s="2" t="inlineStr">
         <is>
           <t>24/06/2026</t>
         </is>
       </c>
-      <c r="F285" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G285" s="9" t="inlineStr"/>
-      <c r="H285" s="9" t="inlineStr">
-        <is>
-          <t>0/39</t>
-        </is>
-      </c>
-      <c r="I285" s="9" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F285" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G285" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H285" s="2" t="inlineStr">
+        <is>
+          <t>5/39</t>
+        </is>
+      </c>
+      <c r="I285" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -14081,45 +14109,49 @@
       </c>
     </row>
     <row r="287">
-      <c r="A287" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B287" s="9" t="inlineStr">
+      <c r="A287" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B287" s="2" t="inlineStr">
         <is>
           <t>A1-F1</t>
         </is>
       </c>
-      <c r="C287" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D287" s="9" t="inlineStr">
+      <c r="C287" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D287" s="2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="E287" s="9" t="inlineStr">
+      <c r="E287" s="2" t="inlineStr">
         <is>
           <t>30/06/2026</t>
         </is>
       </c>
-      <c r="F287" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G287" s="9" t="inlineStr"/>
-      <c r="H287" s="9" t="inlineStr">
-        <is>
-          <t>0/39</t>
-        </is>
-      </c>
-      <c r="I287" s="9" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F287" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G287" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H287" s="2" t="inlineStr">
+        <is>
+          <t>37/39</t>
+        </is>
+      </c>
+      <c r="I287" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -15204,45 +15236,49 @@
       </c>
     </row>
     <row r="312">
-      <c r="A312" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B312" s="9" t="inlineStr">
+      <c r="A312" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B312" s="2" t="inlineStr">
         <is>
           <t>A1-F2</t>
         </is>
       </c>
-      <c r="C312" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D312" s="9" t="inlineStr">
+      <c r="C312" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D312" s="2" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="E312" s="9" t="inlineStr">
+      <c r="E312" s="2" t="inlineStr">
         <is>
           <t>24/06/2026</t>
         </is>
       </c>
-      <c r="F312" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G312" s="9" t="inlineStr"/>
-      <c r="H312" s="9" t="inlineStr">
-        <is>
-          <t>0/39</t>
-        </is>
-      </c>
-      <c r="I312" s="9" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F312" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G312" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H312" s="2" t="inlineStr">
+        <is>
+          <t>10/39</t>
+        </is>
+      </c>
+      <c r="I312" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -15290,45 +15326,49 @@
       </c>
     </row>
     <row r="314">
-      <c r="A314" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B314" s="9" t="inlineStr">
+      <c r="A314" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B314" s="2" t="inlineStr">
         <is>
           <t>A1-F2</t>
         </is>
       </c>
-      <c r="C314" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D314" s="9" t="inlineStr">
+      <c r="C314" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D314" s="2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="E314" s="9" t="inlineStr">
+      <c r="E314" s="2" t="inlineStr">
         <is>
           <t>30/06/2026</t>
         </is>
       </c>
-      <c r="F314" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G314" s="9" t="inlineStr"/>
-      <c r="H314" s="9" t="inlineStr">
-        <is>
-          <t>0/39</t>
-        </is>
-      </c>
-      <c r="I314" s="9" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F314" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G314" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H314" s="2" t="inlineStr">
+        <is>
+          <t>37/39</t>
+        </is>
+      </c>
+      <c r="I314" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A1_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A1_session_analysis.xlsx
@@ -1037,7 +1037,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>75.1%</t>
+          <t>75.3%</t>
         </is>
       </c>
     </row>
@@ -1997,7 +1997,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>74.6%</t>
+          <t>74.8%</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>71.1%</t>
+          <t>71.4%</t>
         </is>
       </c>
     </row>
@@ -2153,7 +2153,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>74.7%</t>
+          <t>75.5%</t>
         </is>
       </c>
     </row>
@@ -2231,7 +2231,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>71.8%</t>
+          <t>73.1%</t>
         </is>
       </c>
     </row>
@@ -11622,7 +11622,7 @@
       </c>
       <c r="H231" s="2" t="inlineStr">
         <is>
-          <t>21/38</t>
+          <t>22/38</t>
         </is>
       </c>
       <c r="I231" s="2" t="inlineStr">
@@ -12839,7 +12839,7 @@
       </c>
       <c r="H258" s="2" t="inlineStr">
         <is>
-          <t>12/39</t>
+          <t>14/39</t>
         </is>
       </c>
       <c r="I258" s="2" t="inlineStr">
@@ -14056,7 +14056,7 @@
       </c>
       <c r="H285" s="2" t="inlineStr">
         <is>
-          <t>5/39</t>
+          <t>9/39</t>
         </is>
       </c>
       <c r="I285" s="2" t="inlineStr">
@@ -15273,7 +15273,7 @@
       </c>
       <c r="H312" s="2" t="inlineStr">
         <is>
-          <t>10/39</t>
+          <t>17/39</t>
         </is>
       </c>
       <c r="I312" s="2" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A1_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A1_session_analysis.xlsx
@@ -814,7 +814,7 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>190</v>
+        <v>196</v>
       </c>
     </row>
     <row r="7">
@@ -924,7 +924,7 @@
         </is>
       </c>
       <c r="L8" s="4" t="n">
-        <v>120</v>
+        <v>114</v>
       </c>
     </row>
     <row r="9">
@@ -980,7 +980,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>58.6%</t>
+          <t>60.5%</t>
         </is>
       </c>
     </row>
@@ -1037,7 +1037,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>75.3%</t>
+          <t>75.6%</t>
         </is>
       </c>
     </row>
@@ -1826,22 +1826,22 @@
         <v>27</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P21" s="4" t="n">
         <v>3</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R21" s="4" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>51.9%</t>
         </is>
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>71.6%</t>
+          <t>73.1%</t>
         </is>
       </c>
     </row>
@@ -1904,22 +1904,22 @@
         <v>27</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P22" s="4" t="n">
         <v>3</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R22" s="4" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>51.9%</t>
         </is>
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>77.1%</t>
+          <t>77.3%</t>
         </is>
       </c>
     </row>
@@ -1982,22 +1982,22 @@
         <v>27</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="P23" s="4" t="n">
         <v>2</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R23" s="4" t="inlineStr">
         <is>
-          <t>51.9%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>74.8%</t>
+          <t>76.0%</t>
         </is>
       </c>
     </row>
@@ -2060,22 +2060,22 @@
         <v>27</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="P24" s="4" t="n">
         <v>2</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R24" s="4" t="inlineStr">
         <is>
-          <t>51.9%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>72.3%</t>
         </is>
       </c>
     </row>
@@ -2138,22 +2138,22 @@
         <v>27</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="P25" s="4" t="n">
         <v>2</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R25" s="4" t="inlineStr">
         <is>
-          <t>51.9%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>75.5%</t>
+          <t>76.1%</t>
         </is>
       </c>
     </row>
@@ -2216,22 +2216,22 @@
         <v>27</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="P26" s="4" t="n">
         <v>2</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R26" s="4" t="inlineStr">
         <is>
-          <t>51.9%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>73.1%</t>
+          <t>73.2%</t>
         </is>
       </c>
     </row>
@@ -9292,45 +9292,49 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B180" s="5" t="inlineStr">
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B180" s="2" t="inlineStr">
         <is>
           <t>A1-D1</t>
         </is>
       </c>
-      <c r="C180" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D180" s="5" t="inlineStr">
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="E180" s="5" t="inlineStr">
+      <c r="E180" s="2" t="inlineStr">
         <is>
           <t>01/07/2026</t>
         </is>
       </c>
-      <c r="F180" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G180" s="5" t="inlineStr"/>
-      <c r="H180" s="5" t="inlineStr">
-        <is>
-          <t>0/35</t>
-        </is>
-      </c>
-      <c r="I180" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F180" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G180" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H180" s="2" t="inlineStr">
+        <is>
+          <t>32/35</t>
+        </is>
+      </c>
+      <c r="I180" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -10505,45 +10509,49 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B207" s="5" t="inlineStr">
+      <c r="A207" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B207" s="2" t="inlineStr">
         <is>
           <t>A1-D2</t>
         </is>
       </c>
-      <c r="C207" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D207" s="5" t="inlineStr">
+      <c r="C207" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D207" s="2" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="E207" s="5" t="inlineStr">
+      <c r="E207" s="2" t="inlineStr">
         <is>
           <t>01/07/2026</t>
         </is>
       </c>
-      <c r="F207" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G207" s="5" t="inlineStr"/>
-      <c r="H207" s="5" t="inlineStr">
-        <is>
-          <t>0/34</t>
-        </is>
-      </c>
-      <c r="I207" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F207" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G207" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H207" s="2" t="inlineStr">
+        <is>
+          <t>27/34</t>
+        </is>
+      </c>
+      <c r="I207" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -11722,45 +11730,49 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B234" s="5" t="inlineStr">
+      <c r="A234" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B234" s="2" t="inlineStr">
         <is>
           <t>A1-E1</t>
         </is>
       </c>
-      <c r="C234" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D234" s="5" t="inlineStr">
+      <c r="C234" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D234" s="2" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="E234" s="5" t="inlineStr">
+      <c r="E234" s="2" t="inlineStr">
         <is>
           <t>01/07/2026</t>
         </is>
       </c>
-      <c r="F234" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G234" s="5" t="inlineStr"/>
-      <c r="H234" s="5" t="inlineStr">
-        <is>
-          <t>0/38</t>
-        </is>
-      </c>
-      <c r="I234" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F234" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G234" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H234" s="2" t="inlineStr">
+        <is>
+          <t>35/38</t>
+        </is>
+      </c>
+      <c r="I234" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -12939,45 +12951,49 @@
       </c>
     </row>
     <row r="261">
-      <c r="A261" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B261" s="5" t="inlineStr">
+      <c r="A261" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B261" s="2" t="inlineStr">
         <is>
           <t>A1-E2</t>
         </is>
       </c>
-      <c r="C261" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D261" s="5" t="inlineStr">
+      <c r="C261" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D261" s="2" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="E261" s="5" t="inlineStr">
+      <c r="E261" s="2" t="inlineStr">
         <is>
           <t>01/07/2026</t>
         </is>
       </c>
-      <c r="F261" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G261" s="5" t="inlineStr"/>
-      <c r="H261" s="5" t="inlineStr">
-        <is>
-          <t>0/39</t>
-        </is>
-      </c>
-      <c r="I261" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F261" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G261" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H261" s="2" t="inlineStr">
+        <is>
+          <t>33/39</t>
+        </is>
+      </c>
+      <c r="I261" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -14156,45 +14172,49 @@
       </c>
     </row>
     <row r="288">
-      <c r="A288" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B288" s="5" t="inlineStr">
+      <c r="A288" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B288" s="2" t="inlineStr">
         <is>
           <t>A1-F1</t>
         </is>
       </c>
-      <c r="C288" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D288" s="5" t="inlineStr">
+      <c r="C288" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D288" s="2" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="E288" s="5" t="inlineStr">
+      <c r="E288" s="2" t="inlineStr">
         <is>
           <t>01/07/2026</t>
         </is>
       </c>
-      <c r="F288" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G288" s="5" t="inlineStr"/>
-      <c r="H288" s="5" t="inlineStr">
-        <is>
-          <t>0/39</t>
-        </is>
-      </c>
-      <c r="I288" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F288" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G288" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H288" s="2" t="inlineStr">
+        <is>
+          <t>33/39</t>
+        </is>
+      </c>
+      <c r="I288" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -15373,45 +15393,49 @@
       </c>
     </row>
     <row r="315">
-      <c r="A315" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B315" s="5" t="inlineStr">
+      <c r="A315" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B315" s="2" t="inlineStr">
         <is>
           <t>A1-F2</t>
         </is>
       </c>
-      <c r="C315" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D315" s="5" t="inlineStr">
+      <c r="C315" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D315" s="2" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="E315" s="5" t="inlineStr">
+      <c r="E315" s="2" t="inlineStr">
         <is>
           <t>01/07/2026</t>
         </is>
       </c>
-      <c r="F315" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G315" s="5" t="inlineStr"/>
-      <c r="H315" s="5" t="inlineStr">
-        <is>
-          <t>0/39</t>
-        </is>
-      </c>
-      <c r="I315" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F315" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G315" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H315" s="2" t="inlineStr">
+        <is>
+          <t>29/39</t>
+        </is>
+      </c>
+      <c r="I315" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A1_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A1_session_analysis.xlsx
@@ -814,7 +814,7 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>196</v>
+        <v>216</v>
       </c>
     </row>
     <row r="7">
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
@@ -924,7 +924,7 @@
         </is>
       </c>
       <c r="L8" s="4" t="n">
-        <v>114</v>
+        <v>102</v>
       </c>
     </row>
     <row r="9">
@@ -980,7 +980,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>60.5%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -1037,7 +1037,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>75.6%</t>
+          <t>76.6%</t>
         </is>
       </c>
     </row>
@@ -1342,22 +1342,22 @@
         <v>27</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="P15" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R15" s="4" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>70.4%</t>
         </is>
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>72.9%</t>
+          <t>73.7%</t>
         </is>
       </c>
     </row>
@@ -1424,22 +1424,22 @@
         <v>27</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="P16" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R16" s="4" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>70.4%</t>
         </is>
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>73.6%</t>
+          <t>74.6%</t>
         </is>
       </c>
     </row>
@@ -1506,22 +1506,22 @@
         <v>27</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="P17" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R17" s="4" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>70.4%</t>
         </is>
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>80.4%</t>
+          <t>80.5%</t>
         </is>
       </c>
     </row>
@@ -1588,22 +1588,22 @@
         <v>27</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="P18" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R18" s="4" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>70.4%</t>
         </is>
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>78.3%</t>
+          <t>78.0%</t>
         </is>
       </c>
     </row>
@@ -1670,65 +1670,69 @@
         <v>27</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="P19" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R19" s="4" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>70.4%</t>
         </is>
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>80.4%</t>
+          <t>76.5%</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>A1-A1</t>
         </is>
       </c>
-      <c r="C20" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="E20" s="5" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>04/07/2026</t>
         </is>
       </c>
-      <c r="F20" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G20" s="5" t="inlineStr"/>
-      <c r="H20" s="5" t="inlineStr">
-        <is>
-          <t>0/34</t>
-        </is>
-      </c>
-      <c r="I20" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>30/34</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
       <c r="K20" s="4" t="inlineStr">
@@ -1748,22 +1752,22 @@
         <v>27</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="P20" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R20" s="4" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>70.4%</t>
         </is>
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>72.4%</t>
+          <t>68.7%</t>
         </is>
       </c>
     </row>
@@ -1826,22 +1830,22 @@
         <v>27</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R21" s="4" t="inlineStr">
         <is>
-          <t>51.9%</t>
+          <t>63.0%</t>
         </is>
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>73.1%</t>
+          <t>75.6%</t>
         </is>
       </c>
     </row>
@@ -1904,22 +1908,22 @@
         <v>27</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R22" s="4" t="inlineStr">
         <is>
-          <t>51.9%</t>
+          <t>63.0%</t>
         </is>
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>77.3%</t>
+          <t>79.2%</t>
         </is>
       </c>
     </row>
@@ -1982,22 +1986,22 @@
         <v>27</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R23" s="4" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>63.0%</t>
         </is>
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>76.0%</t>
+          <t>78.6%</t>
         </is>
       </c>
     </row>
@@ -2060,22 +2064,22 @@
         <v>27</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R24" s="4" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>63.0%</t>
         </is>
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>72.3%</t>
+          <t>75.9%</t>
         </is>
       </c>
     </row>
@@ -2138,22 +2142,22 @@
         <v>27</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R25" s="4" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>63.0%</t>
         </is>
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>76.1%</t>
+          <t>80.7%</t>
         </is>
       </c>
     </row>
@@ -2216,22 +2220,22 @@
         <v>27</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R26" s="4" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>63.0%</t>
         </is>
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>73.2%</t>
+          <t>77.4%</t>
         </is>
       </c>
     </row>
@@ -3233,45 +3237,49 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B47" s="5" t="inlineStr">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
         <is>
           <t>A1-A2</t>
         </is>
       </c>
-      <c r="C47" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D47" s="5" t="inlineStr">
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="E47" s="5" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>04/07/2026</t>
         </is>
       </c>
-      <c r="F47" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G47" s="5" t="inlineStr"/>
-      <c r="H47" s="5" t="inlineStr">
-        <is>
-          <t>0/33</t>
-        </is>
-      </c>
-      <c r="I47" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>31/33</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -4466,45 +4474,49 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B74" s="5" t="inlineStr">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
         <is>
           <t>A1-B1</t>
         </is>
       </c>
-      <c r="C74" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D74" s="5" t="inlineStr">
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="E74" s="5" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr">
         <is>
           <t>04/07/2026</t>
         </is>
       </c>
-      <c r="F74" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G74" s="5" t="inlineStr"/>
-      <c r="H74" s="5" t="inlineStr">
-        <is>
-          <t>0/34</t>
-        </is>
-      </c>
-      <c r="I74" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>28/34</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -5699,45 +5711,49 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B101" s="5" t="inlineStr">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
         <is>
           <t>A1-B2</t>
         </is>
       </c>
-      <c r="C101" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D101" s="5" t="inlineStr">
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="E101" s="5" t="inlineStr">
+      <c r="E101" s="2" t="inlineStr">
         <is>
           <t>04/07/2026</t>
         </is>
       </c>
-      <c r="F101" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G101" s="5" t="inlineStr"/>
-      <c r="H101" s="5" t="inlineStr">
-        <is>
-          <t>0/34</t>
-        </is>
-      </c>
-      <c r="I101" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>25/34</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -6932,45 +6948,49 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B128" s="5" t="inlineStr">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
         <is>
           <t>A1-C1</t>
         </is>
       </c>
-      <c r="C128" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D128" s="5" t="inlineStr">
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="E128" s="5" t="inlineStr">
+      <c r="E128" s="2" t="inlineStr">
         <is>
           <t>04/07/2026</t>
         </is>
       </c>
-      <c r="F128" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G128" s="5" t="inlineStr"/>
-      <c r="H128" s="5" t="inlineStr">
-        <is>
-          <t>0/34</t>
-        </is>
-      </c>
-      <c r="I128" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H128" s="2" t="inlineStr">
+        <is>
+          <t>2/34</t>
+        </is>
+      </c>
+      <c r="I128" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -8165,45 +8185,49 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B155" s="5" t="inlineStr">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
         <is>
           <t>A1-C2</t>
         </is>
       </c>
-      <c r="C155" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D155" s="5" t="inlineStr">
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="E155" s="5" t="inlineStr">
+      <c r="E155" s="2" t="inlineStr">
         <is>
           <t>04/07/2026</t>
         </is>
       </c>
-      <c r="F155" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G155" s="5" t="inlineStr"/>
-      <c r="H155" s="5" t="inlineStr">
-        <is>
-          <t>0/33</t>
-        </is>
-      </c>
-      <c r="I155" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F155" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G155" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H155" s="2" t="inlineStr">
+        <is>
+          <t>1/33</t>
+        </is>
+      </c>
+      <c r="I155" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -9159,88 +9183,96 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B177" s="9" t="inlineStr">
+      <c r="A177" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B177" s="2" t="inlineStr">
         <is>
           <t>A1-D1</t>
         </is>
       </c>
-      <c r="C177" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D177" s="9" t="inlineStr">
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="E177" s="9" t="inlineStr">
+      <c r="E177" s="2" t="inlineStr">
         <is>
           <t>24/06/2026</t>
         </is>
       </c>
-      <c r="F177" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G177" s="9" t="inlineStr"/>
-      <c r="H177" s="9" t="inlineStr">
-        <is>
-          <t>0/35</t>
-        </is>
-      </c>
-      <c r="I177" s="9" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F177" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G177" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H177" s="2" t="inlineStr">
+        <is>
+          <t>27/35</t>
+        </is>
+      </c>
+      <c r="I177" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B178" s="9" t="inlineStr">
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B178" s="2" t="inlineStr">
         <is>
           <t>A1-D1</t>
         </is>
       </c>
-      <c r="C178" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D178" s="9" t="inlineStr">
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="E178" s="9" t="inlineStr">
+      <c r="E178" s="2" t="inlineStr">
         <is>
           <t>25/06/2026</t>
         </is>
       </c>
-      <c r="F178" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G178" s="9" t="inlineStr"/>
-      <c r="H178" s="9" t="inlineStr">
-        <is>
-          <t>0/35</t>
-        </is>
-      </c>
-      <c r="I178" s="9" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F178" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G178" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H178" s="2" t="inlineStr">
+        <is>
+          <t>30/35</t>
+        </is>
+      </c>
+      <c r="I178" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -9339,45 +9371,49 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B181" s="5" t="inlineStr">
+      <c r="A181" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B181" s="2" t="inlineStr">
         <is>
           <t>A1-D1</t>
         </is>
       </c>
-      <c r="C181" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D181" s="5" t="inlineStr">
+      <c r="C181" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="E181" s="5" t="inlineStr">
+      <c r="E181" s="2" t="inlineStr">
         <is>
           <t>02/07/2026</t>
         </is>
       </c>
-      <c r="F181" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G181" s="5" t="inlineStr"/>
-      <c r="H181" s="5" t="inlineStr">
-        <is>
-          <t>0/35</t>
-        </is>
-      </c>
-      <c r="I181" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F181" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G181" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H181" s="2" t="inlineStr">
+        <is>
+          <t>35/35</t>
+        </is>
+      </c>
+      <c r="I181" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -10376,88 +10412,96 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B204" s="9" t="inlineStr">
+      <c r="A204" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B204" s="2" t="inlineStr">
         <is>
           <t>A1-D2</t>
         </is>
       </c>
-      <c r="C204" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D204" s="9" t="inlineStr">
+      <c r="C204" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D204" s="2" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="E204" s="9" t="inlineStr">
+      <c r="E204" s="2" t="inlineStr">
         <is>
           <t>24/06/2026</t>
         </is>
       </c>
-      <c r="F204" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G204" s="9" t="inlineStr"/>
-      <c r="H204" s="9" t="inlineStr">
-        <is>
-          <t>0/34</t>
-        </is>
-      </c>
-      <c r="I204" s="9" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F204" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G204" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H204" s="2" t="inlineStr">
+        <is>
+          <t>27/34</t>
+        </is>
+      </c>
+      <c r="I204" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B205" s="9" t="inlineStr">
+      <c r="A205" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B205" s="2" t="inlineStr">
         <is>
           <t>A1-D2</t>
         </is>
       </c>
-      <c r="C205" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D205" s="9" t="inlineStr">
+      <c r="C205" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D205" s="2" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="E205" s="9" t="inlineStr">
+      <c r="E205" s="2" t="inlineStr">
         <is>
           <t>25/06/2026</t>
         </is>
       </c>
-      <c r="F205" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G205" s="9" t="inlineStr"/>
-      <c r="H205" s="9" t="inlineStr">
-        <is>
-          <t>0/34</t>
-        </is>
-      </c>
-      <c r="I205" s="9" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F205" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G205" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H205" s="2" t="inlineStr">
+        <is>
+          <t>29/34</t>
+        </is>
+      </c>
+      <c r="I205" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -10556,45 +10600,49 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B208" s="5" t="inlineStr">
+      <c r="A208" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B208" s="2" t="inlineStr">
         <is>
           <t>A1-D2</t>
         </is>
       </c>
-      <c r="C208" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D208" s="5" t="inlineStr">
+      <c r="C208" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D208" s="2" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="E208" s="5" t="inlineStr">
+      <c r="E208" s="2" t="inlineStr">
         <is>
           <t>02/07/2026</t>
         </is>
       </c>
-      <c r="F208" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G208" s="5" t="inlineStr"/>
-      <c r="H208" s="5" t="inlineStr">
-        <is>
-          <t>0/34</t>
-        </is>
-      </c>
-      <c r="I208" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F208" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G208" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H208" s="2" t="inlineStr">
+        <is>
+          <t>34/34</t>
+        </is>
+      </c>
+      <c r="I208" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -11630,7 +11678,7 @@
       </c>
       <c r="H231" s="2" t="inlineStr">
         <is>
-          <t>22/38</t>
+          <t>28/38</t>
         </is>
       </c>
       <c r="I231" s="2" t="inlineStr">
@@ -11640,45 +11688,49 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B232" s="9" t="inlineStr">
+      <c r="A232" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B232" s="2" t="inlineStr">
         <is>
           <t>A1-E1</t>
         </is>
       </c>
-      <c r="C232" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D232" s="9" t="inlineStr">
+      <c r="C232" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D232" s="2" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="E232" s="9" t="inlineStr">
+      <c r="E232" s="2" t="inlineStr">
         <is>
           <t>25/06/2026</t>
         </is>
       </c>
-      <c r="F232" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G232" s="9" t="inlineStr"/>
-      <c r="H232" s="9" t="inlineStr">
-        <is>
-          <t>0/38</t>
-        </is>
-      </c>
-      <c r="I232" s="9" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F232" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G232" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H232" s="2" t="inlineStr">
+        <is>
+          <t>31/38</t>
+        </is>
+      </c>
+      <c r="I232" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -11777,45 +11829,49 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B235" s="5" t="inlineStr">
+      <c r="A235" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B235" s="2" t="inlineStr">
         <is>
           <t>A1-E1</t>
         </is>
       </c>
-      <c r="C235" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D235" s="5" t="inlineStr">
+      <c r="C235" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D235" s="2" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="E235" s="5" t="inlineStr">
+      <c r="E235" s="2" t="inlineStr">
         <is>
           <t>02/07/2026</t>
         </is>
       </c>
-      <c r="F235" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G235" s="5" t="inlineStr"/>
-      <c r="H235" s="5" t="inlineStr">
-        <is>
-          <t>0/38</t>
-        </is>
-      </c>
-      <c r="I235" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F235" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G235" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H235" s="2" t="inlineStr">
+        <is>
+          <t>38/38</t>
+        </is>
+      </c>
+      <c r="I235" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -12851,7 +12907,7 @@
       </c>
       <c r="H258" s="2" t="inlineStr">
         <is>
-          <t>14/39</t>
+          <t>28/39</t>
         </is>
       </c>
       <c r="I258" s="2" t="inlineStr">
@@ -12861,45 +12917,49 @@
       </c>
     </row>
     <row r="259">
-      <c r="A259" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B259" s="9" t="inlineStr">
+      <c r="A259" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B259" s="2" t="inlineStr">
         <is>
           <t>A1-E2</t>
         </is>
       </c>
-      <c r="C259" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D259" s="9" t="inlineStr">
+      <c r="C259" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D259" s="2" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="E259" s="9" t="inlineStr">
+      <c r="E259" s="2" t="inlineStr">
         <is>
           <t>25/06/2026</t>
         </is>
       </c>
-      <c r="F259" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G259" s="9" t="inlineStr"/>
-      <c r="H259" s="9" t="inlineStr">
-        <is>
-          <t>0/39</t>
-        </is>
-      </c>
-      <c r="I259" s="9" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F259" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G259" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H259" s="2" t="inlineStr">
+        <is>
+          <t>27/39</t>
+        </is>
+      </c>
+      <c r="I259" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -12998,45 +13058,49 @@
       </c>
     </row>
     <row r="262">
-      <c r="A262" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B262" s="5" t="inlineStr">
+      <c r="A262" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B262" s="2" t="inlineStr">
         <is>
           <t>A1-E2</t>
         </is>
       </c>
-      <c r="C262" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D262" s="5" t="inlineStr">
+      <c r="C262" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D262" s="2" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="E262" s="5" t="inlineStr">
+      <c r="E262" s="2" t="inlineStr">
         <is>
           <t>02/07/2026</t>
         </is>
       </c>
-      <c r="F262" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G262" s="5" t="inlineStr"/>
-      <c r="H262" s="5" t="inlineStr">
-        <is>
-          <t>0/39</t>
-        </is>
-      </c>
-      <c r="I262" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F262" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G262" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H262" s="2" t="inlineStr">
+        <is>
+          <t>39/39</t>
+        </is>
+      </c>
+      <c r="I262" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -14072,7 +14136,7 @@
       </c>
       <c r="H285" s="2" t="inlineStr">
         <is>
-          <t>9/39</t>
+          <t>31/39</t>
         </is>
       </c>
       <c r="I285" s="2" t="inlineStr">
@@ -14082,45 +14146,49 @@
       </c>
     </row>
     <row r="286">
-      <c r="A286" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B286" s="9" t="inlineStr">
+      <c r="A286" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B286" s="2" t="inlineStr">
         <is>
           <t>A1-F1</t>
         </is>
       </c>
-      <c r="C286" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D286" s="9" t="inlineStr">
+      <c r="C286" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D286" s="2" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="E286" s="9" t="inlineStr">
+      <c r="E286" s="2" t="inlineStr">
         <is>
           <t>25/06/2026</t>
         </is>
       </c>
-      <c r="F286" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G286" s="9" t="inlineStr"/>
-      <c r="H286" s="9" t="inlineStr">
-        <is>
-          <t>0/39</t>
-        </is>
-      </c>
-      <c r="I286" s="9" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F286" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G286" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H286" s="2" t="inlineStr">
+        <is>
+          <t>29/39</t>
+        </is>
+      </c>
+      <c r="I286" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -14219,45 +14287,49 @@
       </c>
     </row>
     <row r="289">
-      <c r="A289" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B289" s="5" t="inlineStr">
+      <c r="A289" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B289" s="2" t="inlineStr">
         <is>
           <t>A1-F1</t>
         </is>
       </c>
-      <c r="C289" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D289" s="5" t="inlineStr">
+      <c r="C289" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D289" s="2" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="E289" s="5" t="inlineStr">
+      <c r="E289" s="2" t="inlineStr">
         <is>
           <t>02/07/2026</t>
         </is>
       </c>
-      <c r="F289" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G289" s="5" t="inlineStr"/>
-      <c r="H289" s="5" t="inlineStr">
-        <is>
-          <t>0/39</t>
-        </is>
-      </c>
-      <c r="I289" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F289" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G289" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H289" s="2" t="inlineStr">
+        <is>
+          <t>39/39</t>
+        </is>
+      </c>
+      <c r="I289" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -15293,7 +15365,7 @@
       </c>
       <c r="H312" s="2" t="inlineStr">
         <is>
-          <t>17/39</t>
+          <t>36/39</t>
         </is>
       </c>
       <c r="I312" s="2" t="inlineStr">
@@ -15303,45 +15375,49 @@
       </c>
     </row>
     <row r="313">
-      <c r="A313" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B313" s="9" t="inlineStr">
+      <c r="A313" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B313" s="2" t="inlineStr">
         <is>
           <t>A1-F2</t>
         </is>
       </c>
-      <c r="C313" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D313" s="9" t="inlineStr">
+      <c r="C313" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D313" s="2" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="E313" s="9" t="inlineStr">
+      <c r="E313" s="2" t="inlineStr">
         <is>
           <t>25/06/2026</t>
         </is>
       </c>
-      <c r="F313" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G313" s="9" t="inlineStr"/>
-      <c r="H313" s="9" t="inlineStr">
-        <is>
-          <t>0/39</t>
-        </is>
-      </c>
-      <c r="I313" s="9" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F313" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G313" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H313" s="2" t="inlineStr">
+        <is>
+          <t>27/39</t>
+        </is>
+      </c>
+      <c r="I313" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -15440,45 +15516,49 @@
       </c>
     </row>
     <row r="316">
-      <c r="A316" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B316" s="5" t="inlineStr">
+      <c r="A316" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B316" s="2" t="inlineStr">
         <is>
           <t>A1-F2</t>
         </is>
       </c>
-      <c r="C316" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D316" s="5" t="inlineStr">
+      <c r="C316" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D316" s="2" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="E316" s="5" t="inlineStr">
+      <c r="E316" s="2" t="inlineStr">
         <is>
           <t>02/07/2026</t>
         </is>
       </c>
-      <c r="F316" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G316" s="5" t="inlineStr"/>
-      <c r="H316" s="5" t="inlineStr">
-        <is>
-          <t>0/39</t>
-        </is>
-      </c>
-      <c r="I316" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F316" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G316" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H316" s="2" t="inlineStr">
+        <is>
+          <t>39/39</t>
+        </is>
+      </c>
+      <c r="I316" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A1_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A1_session_analysis.xlsx
@@ -58,14 +58,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFFE0"/>
-        <bgColor rgb="00FFFFE0"/>
+        <fgColor rgb="00FFB6C1"/>
+        <bgColor rgb="00FFB6C1"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFB6C1"/>
-        <bgColor rgb="00FFB6C1"/>
+        <fgColor rgb="00FFFFE0"/>
+        <bgColor rgb="00FFFFE0"/>
       </patternFill>
     </fill>
   </fills>
@@ -96,16 +96,16 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8">
@@ -924,7 +924,7 @@
         </is>
       </c>
       <c r="L8" s="4" t="n">
-        <v>102</v>
+        <v>96</v>
       </c>
     </row>
     <row r="9">
@@ -1345,10 +1345,10 @@
         <v>19</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R15" s="4" t="inlineStr">
         <is>
@@ -1427,10 +1427,10 @@
         <v>19</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R16" s="4" t="inlineStr">
         <is>
@@ -1509,10 +1509,10 @@
         <v>19</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R17" s="4" t="inlineStr">
         <is>
@@ -1591,10 +1591,10 @@
         <v>19</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R18" s="4" t="inlineStr">
         <is>
@@ -1673,10 +1673,10 @@
         <v>19</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R19" s="4" t="inlineStr">
         <is>
@@ -1755,10 +1755,10 @@
         <v>19</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R20" s="4" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
       </c>
       <c r="I21" s="5" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Not Recorded</t>
         </is>
       </c>
       <c r="K21" s="4" t="inlineStr">
@@ -1850,43 +1850,43 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="inlineStr">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
         <is>
           <t>A1-A1</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="inlineStr">
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="E22" s="5" t="inlineStr">
+      <c r="E22" s="6" t="inlineStr">
         <is>
           <t>06/07/2026</t>
         </is>
       </c>
-      <c r="F22" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G22" s="5" t="inlineStr"/>
-      <c r="H22" s="5" t="inlineStr">
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="inlineStr"/>
+      <c r="H22" s="6" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I22" s="5" t="inlineStr">
+      <c r="I22" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -1928,43 +1928,43 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="inlineStr">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
         <is>
           <t>A1-A1</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="inlineStr">
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="E23" s="5" t="inlineStr">
+      <c r="E23" s="6" t="inlineStr">
         <is>
           <t>11/07/2026</t>
         </is>
       </c>
-      <c r="F23" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G23" s="5" t="inlineStr"/>
-      <c r="H23" s="5" t="inlineStr">
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="inlineStr"/>
+      <c r="H23" s="6" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I23" s="5" t="inlineStr">
+      <c r="I23" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -2006,43 +2006,43 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B24" s="5" t="inlineStr">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
         <is>
           <t>A1-A1</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D24" s="5" t="inlineStr">
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="E24" s="5" t="inlineStr">
+      <c r="E24" s="6" t="inlineStr">
         <is>
           <t>12/07/2026</t>
         </is>
       </c>
-      <c r="F24" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G24" s="5" t="inlineStr"/>
-      <c r="H24" s="5" t="inlineStr">
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G24" s="6" t="inlineStr"/>
+      <c r="H24" s="6" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I24" s="5" t="inlineStr">
+      <c r="I24" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -2084,43 +2084,43 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B25" s="5" t="inlineStr">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
         <is>
           <t>A1-A1</t>
         </is>
       </c>
-      <c r="C25" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="inlineStr">
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="E25" s="5" t="inlineStr">
+      <c r="E25" s="6" t="inlineStr">
         <is>
           <t>13/07/2026</t>
         </is>
       </c>
-      <c r="F25" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G25" s="5" t="inlineStr"/>
-      <c r="H25" s="5" t="inlineStr">
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G25" s="6" t="inlineStr"/>
+      <c r="H25" s="6" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I25" s="5" t="inlineStr">
+      <c r="I25" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -2162,43 +2162,43 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B26" s="5" t="inlineStr">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
         <is>
           <t>A1-A1</t>
         </is>
       </c>
-      <c r="C26" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D26" s="5" t="inlineStr">
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="E26" s="5" t="inlineStr">
+      <c r="E26" s="6" t="inlineStr">
         <is>
           <t>18/07/2026</t>
         </is>
       </c>
-      <c r="F26" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G26" s="5" t="inlineStr"/>
-      <c r="H26" s="5" t="inlineStr">
+      <c r="F26" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G26" s="6" t="inlineStr"/>
+      <c r="H26" s="6" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I26" s="5" t="inlineStr">
+      <c r="I26" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -2240,86 +2240,86 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B27" s="5" t="inlineStr">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
         <is>
           <t>A1-A1</t>
         </is>
       </c>
-      <c r="C27" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="inlineStr">
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="E27" s="5" t="inlineStr">
+      <c r="E27" s="6" t="inlineStr">
         <is>
           <t>19/07/2026</t>
         </is>
       </c>
-      <c r="F27" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G27" s="5" t="inlineStr"/>
-      <c r="H27" s="5" t="inlineStr">
+      <c r="F27" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G27" s="6" t="inlineStr"/>
+      <c r="H27" s="6" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I27" s="5" t="inlineStr">
+      <c r="I27" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B28" s="5" t="inlineStr">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
         <is>
           <t>A1-A1</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D28" s="5" t="inlineStr">
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="E28" s="5" t="inlineStr">
+      <c r="E28" s="6" t="inlineStr">
         <is>
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="F28" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G28" s="5" t="inlineStr"/>
-      <c r="H28" s="5" t="inlineStr">
+      <c r="F28" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G28" s="6" t="inlineStr"/>
+      <c r="H28" s="6" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I28" s="5" t="inlineStr">
+      <c r="I28" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -2490,7 +2490,7 @@
           <t>Recorded</t>
         </is>
       </c>
-      <c r="L31" s="6" t="inlineStr">
+      <c r="L31" s="7" t="inlineStr">
         <is>
           <t>Green</t>
         </is>
@@ -2552,7 +2552,7 @@
           <t>Not Recorded</t>
         </is>
       </c>
-      <c r="L32" s="7" t="inlineStr">
+      <c r="L32" s="8" t="inlineStr">
         <is>
           <t>Red</t>
         </is>
@@ -2614,7 +2614,7 @@
           <t>Pending</t>
         </is>
       </c>
-      <c r="L33" s="8" t="inlineStr">
+      <c r="L33" s="9" t="inlineStr">
         <is>
           <t>Yellow</t>
         </is>
@@ -3322,306 +3322,306 @@
       </c>
       <c r="I48" s="5" t="inlineStr">
         <is>
+          <t>Not Recorded</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B49" s="6" t="inlineStr">
+        <is>
+          <t>A1-A2</t>
+        </is>
+      </c>
+      <c r="C49" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D49" s="6" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="E49" s="6" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
+      <c r="F49" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G49" s="6" t="inlineStr"/>
+      <c r="H49" s="6" t="inlineStr">
+        <is>
+          <t>0/33</t>
+        </is>
+      </c>
+      <c r="I49" s="6" t="inlineStr">
+        <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B49" s="5" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B50" s="6" t="inlineStr">
         <is>
           <t>A1-A2</t>
         </is>
       </c>
-      <c r="C49" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D49" s="5" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="E49" s="5" t="inlineStr">
-        <is>
-          <t>06/07/2026</t>
-        </is>
-      </c>
-      <c r="F49" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G49" s="5" t="inlineStr"/>
-      <c r="H49" s="5" t="inlineStr">
+      <c r="C50" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D50" s="6" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="E50" s="6" t="inlineStr">
+        <is>
+          <t>11/07/2026</t>
+        </is>
+      </c>
+      <c r="F50" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G50" s="6" t="inlineStr"/>
+      <c r="H50" s="6" t="inlineStr">
         <is>
           <t>0/33</t>
         </is>
       </c>
-      <c r="I49" s="5" t="inlineStr">
+      <c r="I50" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B50" s="5" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B51" s="6" t="inlineStr">
         <is>
           <t>A1-A2</t>
         </is>
       </c>
-      <c r="C50" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D50" s="5" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="E50" s="5" t="inlineStr">
-        <is>
-          <t>11/07/2026</t>
-        </is>
-      </c>
-      <c r="F50" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G50" s="5" t="inlineStr"/>
-      <c r="H50" s="5" t="inlineStr">
+      <c r="C51" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D51" s="6" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="E51" s="6" t="inlineStr">
+        <is>
+          <t>12/07/2026</t>
+        </is>
+      </c>
+      <c r="F51" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G51" s="6" t="inlineStr"/>
+      <c r="H51" s="6" t="inlineStr">
         <is>
           <t>0/33</t>
         </is>
       </c>
-      <c r="I50" s="5" t="inlineStr">
+      <c r="I51" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B51" s="5" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B52" s="6" t="inlineStr">
         <is>
           <t>A1-A2</t>
         </is>
       </c>
-      <c r="C51" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D51" s="5" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="E51" s="5" t="inlineStr">
-        <is>
-          <t>12/07/2026</t>
-        </is>
-      </c>
-      <c r="F51" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G51" s="5" t="inlineStr"/>
-      <c r="H51" s="5" t="inlineStr">
+      <c r="C52" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D52" s="6" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="E52" s="6" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="F52" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G52" s="6" t="inlineStr"/>
+      <c r="H52" s="6" t="inlineStr">
         <is>
           <t>0/33</t>
         </is>
       </c>
-      <c r="I51" s="5" t="inlineStr">
+      <c r="I52" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B52" s="5" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B53" s="6" t="inlineStr">
         <is>
           <t>A1-A2</t>
         </is>
       </c>
-      <c r="C52" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D52" s="5" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="E52" s="5" t="inlineStr">
-        <is>
-          <t>13/07/2026</t>
-        </is>
-      </c>
-      <c r="F52" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G52" s="5" t="inlineStr"/>
-      <c r="H52" s="5" t="inlineStr">
+      <c r="C53" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D53" s="6" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E53" s="6" t="inlineStr">
+        <is>
+          <t>18/07/2026</t>
+        </is>
+      </c>
+      <c r="F53" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G53" s="6" t="inlineStr"/>
+      <c r="H53" s="6" t="inlineStr">
         <is>
           <t>0/33</t>
         </is>
       </c>
-      <c r="I52" s="5" t="inlineStr">
+      <c r="I53" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B53" s="5" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B54" s="6" t="inlineStr">
         <is>
           <t>A1-A2</t>
         </is>
       </c>
-      <c r="C53" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D53" s="5" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="E53" s="5" t="inlineStr">
-        <is>
-          <t>18/07/2026</t>
-        </is>
-      </c>
-      <c r="F53" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G53" s="5" t="inlineStr"/>
-      <c r="H53" s="5" t="inlineStr">
+      <c r="C54" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D54" s="6" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="E54" s="6" t="inlineStr">
+        <is>
+          <t>19/07/2026</t>
+        </is>
+      </c>
+      <c r="F54" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G54" s="6" t="inlineStr"/>
+      <c r="H54" s="6" t="inlineStr">
         <is>
           <t>0/33</t>
         </is>
       </c>
-      <c r="I53" s="5" t="inlineStr">
+      <c r="I54" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B54" s="5" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B55" s="6" t="inlineStr">
         <is>
           <t>A1-A2</t>
         </is>
       </c>
-      <c r="C54" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D54" s="5" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="E54" s="5" t="inlineStr">
-        <is>
-          <t>19/07/2026</t>
-        </is>
-      </c>
-      <c r="F54" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G54" s="5" t="inlineStr"/>
-      <c r="H54" s="5" t="inlineStr">
+      <c r="C55" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D55" s="6" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E55" s="6" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="F55" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G55" s="6" t="inlineStr"/>
+      <c r="H55" s="6" t="inlineStr">
         <is>
           <t>0/33</t>
         </is>
       </c>
-      <c r="I54" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B55" s="5" t="inlineStr">
-        <is>
-          <t>A1-A2</t>
-        </is>
-      </c>
-      <c r="C55" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D55" s="5" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="E55" s="5" t="inlineStr">
-        <is>
-          <t>20/07/2026</t>
-        </is>
-      </c>
-      <c r="F55" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G55" s="5" t="inlineStr"/>
-      <c r="H55" s="5" t="inlineStr">
-        <is>
-          <t>0/33</t>
-        </is>
-      </c>
-      <c r="I55" s="5" t="inlineStr">
+      <c r="I55" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -4559,306 +4559,306 @@
       </c>
       <c r="I75" s="5" t="inlineStr">
         <is>
+          <t>Not Recorded</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B76" s="6" t="inlineStr">
+        <is>
+          <t>A1-B1</t>
+        </is>
+      </c>
+      <c r="C76" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D76" s="6" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="E76" s="6" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
+      <c r="F76" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G76" s="6" t="inlineStr"/>
+      <c r="H76" s="6" t="inlineStr">
+        <is>
+          <t>0/34</t>
+        </is>
+      </c>
+      <c r="I76" s="6" t="inlineStr">
+        <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B76" s="5" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B77" s="6" t="inlineStr">
         <is>
           <t>A1-B1</t>
         </is>
       </c>
-      <c r="C76" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D76" s="5" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="E76" s="5" t="inlineStr">
-        <is>
-          <t>06/07/2026</t>
-        </is>
-      </c>
-      <c r="F76" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G76" s="5" t="inlineStr"/>
-      <c r="H76" s="5" t="inlineStr">
+      <c r="C77" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D77" s="6" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="E77" s="6" t="inlineStr">
+        <is>
+          <t>11/07/2026</t>
+        </is>
+      </c>
+      <c r="F77" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G77" s="6" t="inlineStr"/>
+      <c r="H77" s="6" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I76" s="5" t="inlineStr">
+      <c r="I77" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B77" s="5" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B78" s="6" t="inlineStr">
         <is>
           <t>A1-B1</t>
         </is>
       </c>
-      <c r="C77" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D77" s="5" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="E77" s="5" t="inlineStr">
-        <is>
-          <t>11/07/2026</t>
-        </is>
-      </c>
-      <c r="F77" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G77" s="5" t="inlineStr"/>
-      <c r="H77" s="5" t="inlineStr">
+      <c r="C78" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D78" s="6" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="E78" s="6" t="inlineStr">
+        <is>
+          <t>12/07/2026</t>
+        </is>
+      </c>
+      <c r="F78" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G78" s="6" t="inlineStr"/>
+      <c r="H78" s="6" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I77" s="5" t="inlineStr">
+      <c r="I78" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B78" s="5" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B79" s="6" t="inlineStr">
         <is>
           <t>A1-B1</t>
         </is>
       </c>
-      <c r="C78" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D78" s="5" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="E78" s="5" t="inlineStr">
-        <is>
-          <t>12/07/2026</t>
-        </is>
-      </c>
-      <c r="F78" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G78" s="5" t="inlineStr"/>
-      <c r="H78" s="5" t="inlineStr">
+      <c r="C79" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D79" s="6" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="E79" s="6" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="F79" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G79" s="6" t="inlineStr"/>
+      <c r="H79" s="6" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I78" s="5" t="inlineStr">
+      <c r="I79" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B79" s="5" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B80" s="6" t="inlineStr">
         <is>
           <t>A1-B1</t>
         </is>
       </c>
-      <c r="C79" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D79" s="5" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="E79" s="5" t="inlineStr">
-        <is>
-          <t>13/07/2026</t>
-        </is>
-      </c>
-      <c r="F79" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G79" s="5" t="inlineStr"/>
-      <c r="H79" s="5" t="inlineStr">
+      <c r="C80" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D80" s="6" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E80" s="6" t="inlineStr">
+        <is>
+          <t>18/07/2026</t>
+        </is>
+      </c>
+      <c r="F80" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G80" s="6" t="inlineStr"/>
+      <c r="H80" s="6" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I79" s="5" t="inlineStr">
+      <c r="I80" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B80" s="5" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B81" s="6" t="inlineStr">
         <is>
           <t>A1-B1</t>
         </is>
       </c>
-      <c r="C80" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D80" s="5" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="E80" s="5" t="inlineStr">
-        <is>
-          <t>18/07/2026</t>
-        </is>
-      </c>
-      <c r="F80" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G80" s="5" t="inlineStr"/>
-      <c r="H80" s="5" t="inlineStr">
+      <c r="C81" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D81" s="6" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="E81" s="6" t="inlineStr">
+        <is>
+          <t>19/07/2026</t>
+        </is>
+      </c>
+      <c r="F81" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G81" s="6" t="inlineStr"/>
+      <c r="H81" s="6" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I80" s="5" t="inlineStr">
+      <c r="I81" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B81" s="5" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B82" s="6" t="inlineStr">
         <is>
           <t>A1-B1</t>
         </is>
       </c>
-      <c r="C81" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D81" s="5" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="E81" s="5" t="inlineStr">
-        <is>
-          <t>19/07/2026</t>
-        </is>
-      </c>
-      <c r="F81" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G81" s="5" t="inlineStr"/>
-      <c r="H81" s="5" t="inlineStr">
+      <c r="C82" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D82" s="6" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E82" s="6" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="F82" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G82" s="6" t="inlineStr"/>
+      <c r="H82" s="6" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I81" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B82" s="5" t="inlineStr">
-        <is>
-          <t>A1-B1</t>
-        </is>
-      </c>
-      <c r="C82" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D82" s="5" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="E82" s="5" t="inlineStr">
-        <is>
-          <t>20/07/2026</t>
-        </is>
-      </c>
-      <c r="F82" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G82" s="5" t="inlineStr"/>
-      <c r="H82" s="5" t="inlineStr">
-        <is>
-          <t>0/34</t>
-        </is>
-      </c>
-      <c r="I82" s="5" t="inlineStr">
+      <c r="I82" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -5796,306 +5796,306 @@
       </c>
       <c r="I102" s="5" t="inlineStr">
         <is>
+          <t>Not Recorded</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B103" s="6" t="inlineStr">
+        <is>
+          <t>A1-B2</t>
+        </is>
+      </c>
+      <c r="C103" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D103" s="6" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="E103" s="6" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
+      <c r="F103" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G103" s="6" t="inlineStr"/>
+      <c r="H103" s="6" t="inlineStr">
+        <is>
+          <t>0/34</t>
+        </is>
+      </c>
+      <c r="I103" s="6" t="inlineStr">
+        <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B103" s="5" t="inlineStr">
+    <row r="104">
+      <c r="A104" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B104" s="6" t="inlineStr">
         <is>
           <t>A1-B2</t>
         </is>
       </c>
-      <c r="C103" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D103" s="5" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="E103" s="5" t="inlineStr">
-        <is>
-          <t>06/07/2026</t>
-        </is>
-      </c>
-      <c r="F103" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G103" s="5" t="inlineStr"/>
-      <c r="H103" s="5" t="inlineStr">
+      <c r="C104" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D104" s="6" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="E104" s="6" t="inlineStr">
+        <is>
+          <t>11/07/2026</t>
+        </is>
+      </c>
+      <c r="F104" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G104" s="6" t="inlineStr"/>
+      <c r="H104" s="6" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I103" s="5" t="inlineStr">
+      <c r="I104" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B104" s="5" t="inlineStr">
+    <row r="105">
+      <c r="A105" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B105" s="6" t="inlineStr">
         <is>
           <t>A1-B2</t>
         </is>
       </c>
-      <c r="C104" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D104" s="5" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="E104" s="5" t="inlineStr">
-        <is>
-          <t>11/07/2026</t>
-        </is>
-      </c>
-      <c r="F104" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G104" s="5" t="inlineStr"/>
-      <c r="H104" s="5" t="inlineStr">
+      <c r="C105" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D105" s="6" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="E105" s="6" t="inlineStr">
+        <is>
+          <t>12/07/2026</t>
+        </is>
+      </c>
+      <c r="F105" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G105" s="6" t="inlineStr"/>
+      <c r="H105" s="6" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I104" s="5" t="inlineStr">
+      <c r="I105" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B105" s="5" t="inlineStr">
+    <row r="106">
+      <c r="A106" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B106" s="6" t="inlineStr">
         <is>
           <t>A1-B2</t>
         </is>
       </c>
-      <c r="C105" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D105" s="5" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="E105" s="5" t="inlineStr">
-        <is>
-          <t>12/07/2026</t>
-        </is>
-      </c>
-      <c r="F105" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G105" s="5" t="inlineStr"/>
-      <c r="H105" s="5" t="inlineStr">
+      <c r="C106" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D106" s="6" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="E106" s="6" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="F106" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G106" s="6" t="inlineStr"/>
+      <c r="H106" s="6" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I105" s="5" t="inlineStr">
+      <c r="I106" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B106" s="5" t="inlineStr">
+    <row r="107">
+      <c r="A107" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B107" s="6" t="inlineStr">
         <is>
           <t>A1-B2</t>
         </is>
       </c>
-      <c r="C106" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D106" s="5" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="E106" s="5" t="inlineStr">
-        <is>
-          <t>13/07/2026</t>
-        </is>
-      </c>
-      <c r="F106" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G106" s="5" t="inlineStr"/>
-      <c r="H106" s="5" t="inlineStr">
+      <c r="C107" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D107" s="6" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E107" s="6" t="inlineStr">
+        <is>
+          <t>18/07/2026</t>
+        </is>
+      </c>
+      <c r="F107" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G107" s="6" t="inlineStr"/>
+      <c r="H107" s="6" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I106" s="5" t="inlineStr">
+      <c r="I107" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B107" s="5" t="inlineStr">
+    <row r="108">
+      <c r="A108" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B108" s="6" t="inlineStr">
         <is>
           <t>A1-B2</t>
         </is>
       </c>
-      <c r="C107" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D107" s="5" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="E107" s="5" t="inlineStr">
-        <is>
-          <t>18/07/2026</t>
-        </is>
-      </c>
-      <c r="F107" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G107" s="5" t="inlineStr"/>
-      <c r="H107" s="5" t="inlineStr">
+      <c r="C108" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D108" s="6" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="E108" s="6" t="inlineStr">
+        <is>
+          <t>19/07/2026</t>
+        </is>
+      </c>
+      <c r="F108" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G108" s="6" t="inlineStr"/>
+      <c r="H108" s="6" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I107" s="5" t="inlineStr">
+      <c r="I108" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B108" s="5" t="inlineStr">
+    <row r="109">
+      <c r="A109" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B109" s="6" t="inlineStr">
         <is>
           <t>A1-B2</t>
         </is>
       </c>
-      <c r="C108" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D108" s="5" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="E108" s="5" t="inlineStr">
-        <is>
-          <t>19/07/2026</t>
-        </is>
-      </c>
-      <c r="F108" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G108" s="5" t="inlineStr"/>
-      <c r="H108" s="5" t="inlineStr">
+      <c r="C109" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D109" s="6" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E109" s="6" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="F109" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G109" s="6" t="inlineStr"/>
+      <c r="H109" s="6" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I108" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B109" s="5" t="inlineStr">
-        <is>
-          <t>A1-B2</t>
-        </is>
-      </c>
-      <c r="C109" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D109" s="5" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="E109" s="5" t="inlineStr">
-        <is>
-          <t>20/07/2026</t>
-        </is>
-      </c>
-      <c r="F109" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G109" s="5" t="inlineStr"/>
-      <c r="H109" s="5" t="inlineStr">
-        <is>
-          <t>0/34</t>
-        </is>
-      </c>
-      <c r="I109" s="5" t="inlineStr">
+      <c r="I109" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -7033,306 +7033,306 @@
       </c>
       <c r="I129" s="5" t="inlineStr">
         <is>
+          <t>Not Recorded</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B130" s="6" t="inlineStr">
+        <is>
+          <t>A1-C1</t>
+        </is>
+      </c>
+      <c r="C130" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D130" s="6" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="E130" s="6" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
+      <c r="F130" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G130" s="6" t="inlineStr"/>
+      <c r="H130" s="6" t="inlineStr">
+        <is>
+          <t>0/34</t>
+        </is>
+      </c>
+      <c r="I130" s="6" t="inlineStr">
+        <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B130" s="5" t="inlineStr">
+    <row r="131">
+      <c r="A131" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B131" s="6" t="inlineStr">
         <is>
           <t>A1-C1</t>
         </is>
       </c>
-      <c r="C130" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D130" s="5" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="E130" s="5" t="inlineStr">
-        <is>
-          <t>06/07/2026</t>
-        </is>
-      </c>
-      <c r="F130" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G130" s="5" t="inlineStr"/>
-      <c r="H130" s="5" t="inlineStr">
+      <c r="C131" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D131" s="6" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="E131" s="6" t="inlineStr">
+        <is>
+          <t>11/07/2026</t>
+        </is>
+      </c>
+      <c r="F131" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G131" s="6" t="inlineStr"/>
+      <c r="H131" s="6" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I130" s="5" t="inlineStr">
+      <c r="I131" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B131" s="5" t="inlineStr">
+    <row r="132">
+      <c r="A132" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B132" s="6" t="inlineStr">
         <is>
           <t>A1-C1</t>
         </is>
       </c>
-      <c r="C131" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D131" s="5" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="E131" s="5" t="inlineStr">
-        <is>
-          <t>11/07/2026</t>
-        </is>
-      </c>
-      <c r="F131" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G131" s="5" t="inlineStr"/>
-      <c r="H131" s="5" t="inlineStr">
+      <c r="C132" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D132" s="6" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="E132" s="6" t="inlineStr">
+        <is>
+          <t>12/07/2026</t>
+        </is>
+      </c>
+      <c r="F132" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G132" s="6" t="inlineStr"/>
+      <c r="H132" s="6" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I131" s="5" t="inlineStr">
+      <c r="I132" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B132" s="5" t="inlineStr">
+    <row r="133">
+      <c r="A133" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B133" s="6" t="inlineStr">
         <is>
           <t>A1-C1</t>
         </is>
       </c>
-      <c r="C132" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D132" s="5" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="E132" s="5" t="inlineStr">
-        <is>
-          <t>12/07/2026</t>
-        </is>
-      </c>
-      <c r="F132" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G132" s="5" t="inlineStr"/>
-      <c r="H132" s="5" t="inlineStr">
+      <c r="C133" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D133" s="6" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="E133" s="6" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="F133" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G133" s="6" t="inlineStr"/>
+      <c r="H133" s="6" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I132" s="5" t="inlineStr">
+      <c r="I133" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B133" s="5" t="inlineStr">
+    <row r="134">
+      <c r="A134" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B134" s="6" t="inlineStr">
         <is>
           <t>A1-C1</t>
         </is>
       </c>
-      <c r="C133" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D133" s="5" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="E133" s="5" t="inlineStr">
-        <is>
-          <t>13/07/2026</t>
-        </is>
-      </c>
-      <c r="F133" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G133" s="5" t="inlineStr"/>
-      <c r="H133" s="5" t="inlineStr">
+      <c r="C134" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D134" s="6" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E134" s="6" t="inlineStr">
+        <is>
+          <t>18/07/2026</t>
+        </is>
+      </c>
+      <c r="F134" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G134" s="6" t="inlineStr"/>
+      <c r="H134" s="6" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I133" s="5" t="inlineStr">
+      <c r="I134" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="134">
-      <c r="A134" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B134" s="5" t="inlineStr">
+    <row r="135">
+      <c r="A135" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B135" s="6" t="inlineStr">
         <is>
           <t>A1-C1</t>
         </is>
       </c>
-      <c r="C134" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D134" s="5" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="E134" s="5" t="inlineStr">
-        <is>
-          <t>18/07/2026</t>
-        </is>
-      </c>
-      <c r="F134" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G134" s="5" t="inlineStr"/>
-      <c r="H134" s="5" t="inlineStr">
+      <c r="C135" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D135" s="6" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="E135" s="6" t="inlineStr">
+        <is>
+          <t>19/07/2026</t>
+        </is>
+      </c>
+      <c r="F135" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G135" s="6" t="inlineStr"/>
+      <c r="H135" s="6" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I134" s="5" t="inlineStr">
+      <c r="I135" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B135" s="5" t="inlineStr">
+    <row r="136">
+      <c r="A136" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B136" s="6" t="inlineStr">
         <is>
           <t>A1-C1</t>
         </is>
       </c>
-      <c r="C135" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D135" s="5" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="E135" s="5" t="inlineStr">
-        <is>
-          <t>19/07/2026</t>
-        </is>
-      </c>
-      <c r="F135" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G135" s="5" t="inlineStr"/>
-      <c r="H135" s="5" t="inlineStr">
+      <c r="C136" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D136" s="6" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E136" s="6" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="F136" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G136" s="6" t="inlineStr"/>
+      <c r="H136" s="6" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I135" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B136" s="5" t="inlineStr">
-        <is>
-          <t>A1-C1</t>
-        </is>
-      </c>
-      <c r="C136" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D136" s="5" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="E136" s="5" t="inlineStr">
-        <is>
-          <t>20/07/2026</t>
-        </is>
-      </c>
-      <c r="F136" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G136" s="5" t="inlineStr"/>
-      <c r="H136" s="5" t="inlineStr">
-        <is>
-          <t>0/34</t>
-        </is>
-      </c>
-      <c r="I136" s="5" t="inlineStr">
+      <c r="I136" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -8270,306 +8270,306 @@
       </c>
       <c r="I156" s="5" t="inlineStr">
         <is>
+          <t>Not Recorded</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B157" s="6" t="inlineStr">
+        <is>
+          <t>A1-C2</t>
+        </is>
+      </c>
+      <c r="C157" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D157" s="6" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="E157" s="6" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
+      <c r="F157" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G157" s="6" t="inlineStr"/>
+      <c r="H157" s="6" t="inlineStr">
+        <is>
+          <t>0/33</t>
+        </is>
+      </c>
+      <c r="I157" s="6" t="inlineStr">
+        <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="157">
-      <c r="A157" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B157" s="5" t="inlineStr">
+    <row r="158">
+      <c r="A158" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B158" s="6" t="inlineStr">
         <is>
           <t>A1-C2</t>
         </is>
       </c>
-      <c r="C157" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D157" s="5" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="E157" s="5" t="inlineStr">
-        <is>
-          <t>06/07/2026</t>
-        </is>
-      </c>
-      <c r="F157" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G157" s="5" t="inlineStr"/>
-      <c r="H157" s="5" t="inlineStr">
+      <c r="C158" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D158" s="6" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="E158" s="6" t="inlineStr">
+        <is>
+          <t>11/07/2026</t>
+        </is>
+      </c>
+      <c r="F158" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G158" s="6" t="inlineStr"/>
+      <c r="H158" s="6" t="inlineStr">
         <is>
           <t>0/33</t>
         </is>
       </c>
-      <c r="I157" s="5" t="inlineStr">
+      <c r="I158" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="158">
-      <c r="A158" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B158" s="5" t="inlineStr">
+    <row r="159">
+      <c r="A159" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B159" s="6" t="inlineStr">
         <is>
           <t>A1-C2</t>
         </is>
       </c>
-      <c r="C158" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D158" s="5" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="E158" s="5" t="inlineStr">
-        <is>
-          <t>11/07/2026</t>
-        </is>
-      </c>
-      <c r="F158" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G158" s="5" t="inlineStr"/>
-      <c r="H158" s="5" t="inlineStr">
+      <c r="C159" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D159" s="6" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="E159" s="6" t="inlineStr">
+        <is>
+          <t>12/07/2026</t>
+        </is>
+      </c>
+      <c r="F159" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G159" s="6" t="inlineStr"/>
+      <c r="H159" s="6" t="inlineStr">
         <is>
           <t>0/33</t>
         </is>
       </c>
-      <c r="I158" s="5" t="inlineStr">
+      <c r="I159" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="159">
-      <c r="A159" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B159" s="5" t="inlineStr">
+    <row r="160">
+      <c r="A160" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B160" s="6" t="inlineStr">
         <is>
           <t>A1-C2</t>
         </is>
       </c>
-      <c r="C159" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D159" s="5" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="E159" s="5" t="inlineStr">
-        <is>
-          <t>12/07/2026</t>
-        </is>
-      </c>
-      <c r="F159" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G159" s="5" t="inlineStr"/>
-      <c r="H159" s="5" t="inlineStr">
+      <c r="C160" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D160" s="6" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="E160" s="6" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="F160" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G160" s="6" t="inlineStr"/>
+      <c r="H160" s="6" t="inlineStr">
         <is>
           <t>0/33</t>
         </is>
       </c>
-      <c r="I159" s="5" t="inlineStr">
+      <c r="I160" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="160">
-      <c r="A160" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B160" s="5" t="inlineStr">
+    <row r="161">
+      <c r="A161" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B161" s="6" t="inlineStr">
         <is>
           <t>A1-C2</t>
         </is>
       </c>
-      <c r="C160" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D160" s="5" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="E160" s="5" t="inlineStr">
-        <is>
-          <t>13/07/2026</t>
-        </is>
-      </c>
-      <c r="F160" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G160" s="5" t="inlineStr"/>
-      <c r="H160" s="5" t="inlineStr">
+      <c r="C161" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D161" s="6" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E161" s="6" t="inlineStr">
+        <is>
+          <t>18/07/2026</t>
+        </is>
+      </c>
+      <c r="F161" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G161" s="6" t="inlineStr"/>
+      <c r="H161" s="6" t="inlineStr">
         <is>
           <t>0/33</t>
         </is>
       </c>
-      <c r="I160" s="5" t="inlineStr">
+      <c r="I161" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="161">
-      <c r="A161" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B161" s="5" t="inlineStr">
+    <row r="162">
+      <c r="A162" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B162" s="6" t="inlineStr">
         <is>
           <t>A1-C2</t>
         </is>
       </c>
-      <c r="C161" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D161" s="5" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="E161" s="5" t="inlineStr">
-        <is>
-          <t>18/07/2026</t>
-        </is>
-      </c>
-      <c r="F161" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G161" s="5" t="inlineStr"/>
-      <c r="H161" s="5" t="inlineStr">
+      <c r="C162" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D162" s="6" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="E162" s="6" t="inlineStr">
+        <is>
+          <t>19/07/2026</t>
+        </is>
+      </c>
+      <c r="F162" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G162" s="6" t="inlineStr"/>
+      <c r="H162" s="6" t="inlineStr">
         <is>
           <t>0/33</t>
         </is>
       </c>
-      <c r="I161" s="5" t="inlineStr">
+      <c r="I162" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="162">
-      <c r="A162" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B162" s="5" t="inlineStr">
+    <row r="163">
+      <c r="A163" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B163" s="6" t="inlineStr">
         <is>
           <t>A1-C2</t>
         </is>
       </c>
-      <c r="C162" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D162" s="5" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="E162" s="5" t="inlineStr">
-        <is>
-          <t>19/07/2026</t>
-        </is>
-      </c>
-      <c r="F162" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G162" s="5" t="inlineStr"/>
-      <c r="H162" s="5" t="inlineStr">
+      <c r="C163" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D163" s="6" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E163" s="6" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="F163" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G163" s="6" t="inlineStr"/>
+      <c r="H163" s="6" t="inlineStr">
         <is>
           <t>0/33</t>
         </is>
       </c>
-      <c r="I162" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B163" s="5" t="inlineStr">
-        <is>
-          <t>A1-C2</t>
-        </is>
-      </c>
-      <c r="C163" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D163" s="5" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="E163" s="5" t="inlineStr">
-        <is>
-          <t>20/07/2026</t>
-        </is>
-      </c>
-      <c r="F163" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G163" s="5" t="inlineStr"/>
-      <c r="H163" s="5" t="inlineStr">
-        <is>
-          <t>0/33</t>
-        </is>
-      </c>
-      <c r="I163" s="5" t="inlineStr">
+      <c r="I163" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -8811,43 +8811,43 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B169" s="9" t="inlineStr">
+      <c r="A169" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B169" s="5" t="inlineStr">
         <is>
           <t>A1-D1</t>
         </is>
       </c>
-      <c r="C169" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D169" s="9" t="inlineStr">
+      <c r="C169" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D169" s="5" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E169" s="9" t="inlineStr">
+      <c r="E169" s="5" t="inlineStr">
         <is>
           <t>04/06/2026</t>
         </is>
       </c>
-      <c r="F169" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G169" s="9" t="inlineStr"/>
-      <c r="H169" s="9" t="inlineStr">
+      <c r="F169" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G169" s="5" t="inlineStr"/>
+      <c r="H169" s="5" t="inlineStr">
         <is>
           <t>0/35</t>
         </is>
       </c>
-      <c r="I169" s="9" t="inlineStr">
+      <c r="I169" s="5" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
@@ -9418,387 +9418,387 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B182" s="5" t="inlineStr">
+      <c r="A182" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B182" s="6" t="inlineStr">
         <is>
           <t>A1-D1</t>
         </is>
       </c>
-      <c r="C182" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D182" s="5" t="inlineStr">
+      <c r="C182" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D182" s="6" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="E182" s="5" t="inlineStr">
+      <c r="E182" s="6" t="inlineStr">
         <is>
           <t>07/07/2026</t>
         </is>
       </c>
-      <c r="F182" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G182" s="5" t="inlineStr"/>
-      <c r="H182" s="5" t="inlineStr">
+      <c r="F182" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G182" s="6" t="inlineStr"/>
+      <c r="H182" s="6" t="inlineStr">
         <is>
           <t>0/35</t>
         </is>
       </c>
-      <c r="I182" s="5" t="inlineStr">
+      <c r="I182" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B183" s="5" t="inlineStr">
+      <c r="A183" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B183" s="6" t="inlineStr">
         <is>
           <t>A1-D1</t>
         </is>
       </c>
-      <c r="C183" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D183" s="5" t="inlineStr">
+      <c r="C183" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D183" s="6" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="E183" s="5" t="inlineStr">
+      <c r="E183" s="6" t="inlineStr">
         <is>
           <t>08/07/2026</t>
         </is>
       </c>
-      <c r="F183" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G183" s="5" t="inlineStr"/>
-      <c r="H183" s="5" t="inlineStr">
+      <c r="F183" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G183" s="6" t="inlineStr"/>
+      <c r="H183" s="6" t="inlineStr">
         <is>
           <t>0/35</t>
         </is>
       </c>
-      <c r="I183" s="5" t="inlineStr">
+      <c r="I183" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B184" s="5" t="inlineStr">
+      <c r="A184" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B184" s="6" t="inlineStr">
         <is>
           <t>A1-D1</t>
         </is>
       </c>
-      <c r="C184" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D184" s="5" t="inlineStr">
+      <c r="C184" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D184" s="6" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="E184" s="5" t="inlineStr">
+      <c r="E184" s="6" t="inlineStr">
         <is>
           <t>09/07/2026</t>
         </is>
       </c>
-      <c r="F184" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G184" s="5" t="inlineStr"/>
-      <c r="H184" s="5" t="inlineStr">
+      <c r="F184" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G184" s="6" t="inlineStr"/>
+      <c r="H184" s="6" t="inlineStr">
         <is>
           <t>0/35</t>
         </is>
       </c>
-      <c r="I184" s="5" t="inlineStr">
+      <c r="I184" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B185" s="5" t="inlineStr">
+      <c r="A185" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B185" s="6" t="inlineStr">
         <is>
           <t>A1-D1</t>
         </is>
       </c>
-      <c r="C185" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D185" s="5" t="inlineStr">
+      <c r="C185" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D185" s="6" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="E185" s="5" t="inlineStr">
+      <c r="E185" s="6" t="inlineStr">
         <is>
           <t>14/07/2026</t>
         </is>
       </c>
-      <c r="F185" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G185" s="5" t="inlineStr"/>
-      <c r="H185" s="5" t="inlineStr">
+      <c r="F185" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G185" s="6" t="inlineStr"/>
+      <c r="H185" s="6" t="inlineStr">
         <is>
           <t>0/35</t>
         </is>
       </c>
-      <c r="I185" s="5" t="inlineStr">
+      <c r="I185" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B186" s="5" t="inlineStr">
+      <c r="A186" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B186" s="6" t="inlineStr">
         <is>
           <t>A1-D1</t>
         </is>
       </c>
-      <c r="C186" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D186" s="5" t="inlineStr">
+      <c r="C186" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D186" s="6" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="E186" s="5" t="inlineStr">
+      <c r="E186" s="6" t="inlineStr">
         <is>
           <t>15/07/2026</t>
         </is>
       </c>
-      <c r="F186" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G186" s="5" t="inlineStr"/>
-      <c r="H186" s="5" t="inlineStr">
+      <c r="F186" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G186" s="6" t="inlineStr"/>
+      <c r="H186" s="6" t="inlineStr">
         <is>
           <t>0/35</t>
         </is>
       </c>
-      <c r="I186" s="5" t="inlineStr">
+      <c r="I186" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B187" s="5" t="inlineStr">
+      <c r="A187" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B187" s="6" t="inlineStr">
         <is>
           <t>A1-D1</t>
         </is>
       </c>
-      <c r="C187" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D187" s="5" t="inlineStr">
+      <c r="C187" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D187" s="6" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="E187" s="5" t="inlineStr">
+      <c r="E187" s="6" t="inlineStr">
         <is>
           <t>16/07/2026</t>
         </is>
       </c>
-      <c r="F187" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G187" s="5" t="inlineStr"/>
-      <c r="H187" s="5" t="inlineStr">
+      <c r="F187" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G187" s="6" t="inlineStr"/>
+      <c r="H187" s="6" t="inlineStr">
         <is>
           <t>0/35</t>
         </is>
       </c>
-      <c r="I187" s="5" t="inlineStr">
+      <c r="I187" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B188" s="5" t="inlineStr">
+      <c r="A188" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B188" s="6" t="inlineStr">
         <is>
           <t>A1-D1</t>
         </is>
       </c>
-      <c r="C188" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D188" s="5" t="inlineStr">
+      <c r="C188" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D188" s="6" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="E188" s="5" t="inlineStr">
+      <c r="E188" s="6" t="inlineStr">
         <is>
           <t>21/07/2026</t>
         </is>
       </c>
-      <c r="F188" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G188" s="5" t="inlineStr"/>
-      <c r="H188" s="5" t="inlineStr">
+      <c r="F188" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G188" s="6" t="inlineStr"/>
+      <c r="H188" s="6" t="inlineStr">
         <is>
           <t>0/35</t>
         </is>
       </c>
-      <c r="I188" s="5" t="inlineStr">
+      <c r="I188" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B189" s="5" t="inlineStr">
+      <c r="A189" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B189" s="6" t="inlineStr">
         <is>
           <t>A1-D1</t>
         </is>
       </c>
-      <c r="C189" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D189" s="5" t="inlineStr">
+      <c r="C189" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D189" s="6" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="E189" s="5" t="inlineStr">
+      <c r="E189" s="6" t="inlineStr">
         <is>
           <t>22/07/2026</t>
         </is>
       </c>
-      <c r="F189" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G189" s="5" t="inlineStr"/>
-      <c r="H189" s="5" t="inlineStr">
+      <c r="F189" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G189" s="6" t="inlineStr"/>
+      <c r="H189" s="6" t="inlineStr">
         <is>
           <t>0/35</t>
         </is>
       </c>
-      <c r="I189" s="5" t="inlineStr">
+      <c r="I189" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B190" s="5" t="inlineStr">
+      <c r="A190" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B190" s="6" t="inlineStr">
         <is>
           <t>A1-D1</t>
         </is>
       </c>
-      <c r="C190" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D190" s="5" t="inlineStr">
+      <c r="C190" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D190" s="6" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="E190" s="5" t="inlineStr">
+      <c r="E190" s="6" t="inlineStr">
         <is>
           <t>23/07/2026</t>
         </is>
       </c>
-      <c r="F190" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G190" s="5" t="inlineStr"/>
-      <c r="H190" s="5" t="inlineStr">
+      <c r="F190" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G190" s="6" t="inlineStr"/>
+      <c r="H190" s="6" t="inlineStr">
         <is>
           <t>0/35</t>
         </is>
       </c>
-      <c r="I190" s="5" t="inlineStr">
+      <c r="I190" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -10040,43 +10040,43 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B196" s="9" t="inlineStr">
+      <c r="A196" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B196" s="5" t="inlineStr">
         <is>
           <t>A1-D2</t>
         </is>
       </c>
-      <c r="C196" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D196" s="9" t="inlineStr">
+      <c r="C196" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D196" s="5" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E196" s="9" t="inlineStr">
+      <c r="E196" s="5" t="inlineStr">
         <is>
           <t>04/06/2026</t>
         </is>
       </c>
-      <c r="F196" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G196" s="9" t="inlineStr"/>
-      <c r="H196" s="9" t="inlineStr">
+      <c r="F196" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G196" s="5" t="inlineStr"/>
+      <c r="H196" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I196" s="9" t="inlineStr">
+      <c r="I196" s="5" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
@@ -10647,387 +10647,387 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B209" s="5" t="inlineStr">
+      <c r="A209" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B209" s="6" t="inlineStr">
         <is>
           <t>A1-D2</t>
         </is>
       </c>
-      <c r="C209" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D209" s="5" t="inlineStr">
+      <c r="C209" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D209" s="6" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="E209" s="5" t="inlineStr">
+      <c r="E209" s="6" t="inlineStr">
         <is>
           <t>07/07/2026</t>
         </is>
       </c>
-      <c r="F209" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G209" s="5" t="inlineStr"/>
-      <c r="H209" s="5" t="inlineStr">
+      <c r="F209" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G209" s="6" t="inlineStr"/>
+      <c r="H209" s="6" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I209" s="5" t="inlineStr">
+      <c r="I209" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B210" s="5" t="inlineStr">
+      <c r="A210" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B210" s="6" t="inlineStr">
         <is>
           <t>A1-D2</t>
         </is>
       </c>
-      <c r="C210" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D210" s="5" t="inlineStr">
+      <c r="C210" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D210" s="6" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="E210" s="5" t="inlineStr">
+      <c r="E210" s="6" t="inlineStr">
         <is>
           <t>08/07/2026</t>
         </is>
       </c>
-      <c r="F210" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G210" s="5" t="inlineStr"/>
-      <c r="H210" s="5" t="inlineStr">
+      <c r="F210" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G210" s="6" t="inlineStr"/>
+      <c r="H210" s="6" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I210" s="5" t="inlineStr">
+      <c r="I210" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B211" s="5" t="inlineStr">
+      <c r="A211" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B211" s="6" t="inlineStr">
         <is>
           <t>A1-D2</t>
         </is>
       </c>
-      <c r="C211" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D211" s="5" t="inlineStr">
+      <c r="C211" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D211" s="6" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="E211" s="5" t="inlineStr">
+      <c r="E211" s="6" t="inlineStr">
         <is>
           <t>09/07/2026</t>
         </is>
       </c>
-      <c r="F211" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G211" s="5" t="inlineStr"/>
-      <c r="H211" s="5" t="inlineStr">
+      <c r="F211" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G211" s="6" t="inlineStr"/>
+      <c r="H211" s="6" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I211" s="5" t="inlineStr">
+      <c r="I211" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B212" s="5" t="inlineStr">
+      <c r="A212" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B212" s="6" t="inlineStr">
         <is>
           <t>A1-D2</t>
         </is>
       </c>
-      <c r="C212" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D212" s="5" t="inlineStr">
+      <c r="C212" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D212" s="6" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="E212" s="5" t="inlineStr">
+      <c r="E212" s="6" t="inlineStr">
         <is>
           <t>14/07/2026</t>
         </is>
       </c>
-      <c r="F212" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G212" s="5" t="inlineStr"/>
-      <c r="H212" s="5" t="inlineStr">
+      <c r="F212" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G212" s="6" t="inlineStr"/>
+      <c r="H212" s="6" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I212" s="5" t="inlineStr">
+      <c r="I212" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B213" s="5" t="inlineStr">
+      <c r="A213" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B213" s="6" t="inlineStr">
         <is>
           <t>A1-D2</t>
         </is>
       </c>
-      <c r="C213" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D213" s="5" t="inlineStr">
+      <c r="C213" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D213" s="6" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="E213" s="5" t="inlineStr">
+      <c r="E213" s="6" t="inlineStr">
         <is>
           <t>15/07/2026</t>
         </is>
       </c>
-      <c r="F213" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G213" s="5" t="inlineStr"/>
-      <c r="H213" s="5" t="inlineStr">
+      <c r="F213" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G213" s="6" t="inlineStr"/>
+      <c r="H213" s="6" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I213" s="5" t="inlineStr">
+      <c r="I213" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B214" s="5" t="inlineStr">
+      <c r="A214" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B214" s="6" t="inlineStr">
         <is>
           <t>A1-D2</t>
         </is>
       </c>
-      <c r="C214" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D214" s="5" t="inlineStr">
+      <c r="C214" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D214" s="6" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="E214" s="5" t="inlineStr">
+      <c r="E214" s="6" t="inlineStr">
         <is>
           <t>16/07/2026</t>
         </is>
       </c>
-      <c r="F214" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G214" s="5" t="inlineStr"/>
-      <c r="H214" s="5" t="inlineStr">
+      <c r="F214" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G214" s="6" t="inlineStr"/>
+      <c r="H214" s="6" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I214" s="5" t="inlineStr">
+      <c r="I214" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B215" s="5" t="inlineStr">
+      <c r="A215" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B215" s="6" t="inlineStr">
         <is>
           <t>A1-D2</t>
         </is>
       </c>
-      <c r="C215" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D215" s="5" t="inlineStr">
+      <c r="C215" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D215" s="6" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="E215" s="5" t="inlineStr">
+      <c r="E215" s="6" t="inlineStr">
         <is>
           <t>21/07/2026</t>
         </is>
       </c>
-      <c r="F215" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G215" s="5" t="inlineStr"/>
-      <c r="H215" s="5" t="inlineStr">
+      <c r="F215" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G215" s="6" t="inlineStr"/>
+      <c r="H215" s="6" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I215" s="5" t="inlineStr">
+      <c r="I215" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B216" s="5" t="inlineStr">
+      <c r="A216" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B216" s="6" t="inlineStr">
         <is>
           <t>A1-D2</t>
         </is>
       </c>
-      <c r="C216" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D216" s="5" t="inlineStr">
+      <c r="C216" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D216" s="6" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="E216" s="5" t="inlineStr">
+      <c r="E216" s="6" t="inlineStr">
         <is>
           <t>22/07/2026</t>
         </is>
       </c>
-      <c r="F216" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G216" s="5" t="inlineStr"/>
-      <c r="H216" s="5" t="inlineStr">
+      <c r="F216" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G216" s="6" t="inlineStr"/>
+      <c r="H216" s="6" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I216" s="5" t="inlineStr">
+      <c r="I216" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B217" s="5" t="inlineStr">
+      <c r="A217" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B217" s="6" t="inlineStr">
         <is>
           <t>A1-D2</t>
         </is>
       </c>
-      <c r="C217" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D217" s="5" t="inlineStr">
+      <c r="C217" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D217" s="6" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="E217" s="5" t="inlineStr">
+      <c r="E217" s="6" t="inlineStr">
         <is>
           <t>23/07/2026</t>
         </is>
       </c>
-      <c r="F217" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G217" s="5" t="inlineStr"/>
-      <c r="H217" s="5" t="inlineStr">
+      <c r="F217" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G217" s="6" t="inlineStr"/>
+      <c r="H217" s="6" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I217" s="5" t="inlineStr">
+      <c r="I217" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -11269,43 +11269,43 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B223" s="9" t="inlineStr">
+      <c r="A223" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B223" s="5" t="inlineStr">
         <is>
           <t>A1-E1</t>
         </is>
       </c>
-      <c r="C223" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D223" s="9" t="inlineStr">
+      <c r="C223" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D223" s="5" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E223" s="9" t="inlineStr">
+      <c r="E223" s="5" t="inlineStr">
         <is>
           <t>04/06/2026</t>
         </is>
       </c>
-      <c r="F223" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G223" s="9" t="inlineStr"/>
-      <c r="H223" s="9" t="inlineStr">
+      <c r="F223" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G223" s="5" t="inlineStr"/>
+      <c r="H223" s="5" t="inlineStr">
         <is>
           <t>0/38</t>
         </is>
       </c>
-      <c r="I223" s="9" t="inlineStr">
+      <c r="I223" s="5" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
@@ -11876,387 +11876,387 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B236" s="5" t="inlineStr">
+      <c r="A236" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B236" s="6" t="inlineStr">
         <is>
           <t>A1-E1</t>
         </is>
       </c>
-      <c r="C236" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D236" s="5" t="inlineStr">
+      <c r="C236" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D236" s="6" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="E236" s="5" t="inlineStr">
+      <c r="E236" s="6" t="inlineStr">
         <is>
           <t>07/07/2026</t>
         </is>
       </c>
-      <c r="F236" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G236" s="5" t="inlineStr"/>
-      <c r="H236" s="5" t="inlineStr">
+      <c r="F236" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G236" s="6" t="inlineStr"/>
+      <c r="H236" s="6" t="inlineStr">
         <is>
           <t>0/38</t>
         </is>
       </c>
-      <c r="I236" s="5" t="inlineStr">
+      <c r="I236" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B237" s="5" t="inlineStr">
+      <c r="A237" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B237" s="6" t="inlineStr">
         <is>
           <t>A1-E1</t>
         </is>
       </c>
-      <c r="C237" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D237" s="5" t="inlineStr">
+      <c r="C237" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D237" s="6" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="E237" s="5" t="inlineStr">
+      <c r="E237" s="6" t="inlineStr">
         <is>
           <t>08/07/2026</t>
         </is>
       </c>
-      <c r="F237" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G237" s="5" t="inlineStr"/>
-      <c r="H237" s="5" t="inlineStr">
+      <c r="F237" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G237" s="6" t="inlineStr"/>
+      <c r="H237" s="6" t="inlineStr">
         <is>
           <t>0/38</t>
         </is>
       </c>
-      <c r="I237" s="5" t="inlineStr">
+      <c r="I237" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B238" s="5" t="inlineStr">
+      <c r="A238" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B238" s="6" t="inlineStr">
         <is>
           <t>A1-E1</t>
         </is>
       </c>
-      <c r="C238" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D238" s="5" t="inlineStr">
+      <c r="C238" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D238" s="6" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="E238" s="5" t="inlineStr">
+      <c r="E238" s="6" t="inlineStr">
         <is>
           <t>09/07/2026</t>
         </is>
       </c>
-      <c r="F238" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G238" s="5" t="inlineStr"/>
-      <c r="H238" s="5" t="inlineStr">
+      <c r="F238" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G238" s="6" t="inlineStr"/>
+      <c r="H238" s="6" t="inlineStr">
         <is>
           <t>0/38</t>
         </is>
       </c>
-      <c r="I238" s="5" t="inlineStr">
+      <c r="I238" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B239" s="5" t="inlineStr">
+      <c r="A239" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B239" s="6" t="inlineStr">
         <is>
           <t>A1-E1</t>
         </is>
       </c>
-      <c r="C239" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D239" s="5" t="inlineStr">
+      <c r="C239" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D239" s="6" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="E239" s="5" t="inlineStr">
+      <c r="E239" s="6" t="inlineStr">
         <is>
           <t>14/07/2026</t>
         </is>
       </c>
-      <c r="F239" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G239" s="5" t="inlineStr"/>
-      <c r="H239" s="5" t="inlineStr">
+      <c r="F239" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G239" s="6" t="inlineStr"/>
+      <c r="H239" s="6" t="inlineStr">
         <is>
           <t>0/38</t>
         </is>
       </c>
-      <c r="I239" s="5" t="inlineStr">
+      <c r="I239" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B240" s="5" t="inlineStr">
+      <c r="A240" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B240" s="6" t="inlineStr">
         <is>
           <t>A1-E1</t>
         </is>
       </c>
-      <c r="C240" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D240" s="5" t="inlineStr">
+      <c r="C240" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D240" s="6" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="E240" s="5" t="inlineStr">
+      <c r="E240" s="6" t="inlineStr">
         <is>
           <t>15/07/2026</t>
         </is>
       </c>
-      <c r="F240" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G240" s="5" t="inlineStr"/>
-      <c r="H240" s="5" t="inlineStr">
+      <c r="F240" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G240" s="6" t="inlineStr"/>
+      <c r="H240" s="6" t="inlineStr">
         <is>
           <t>0/38</t>
         </is>
       </c>
-      <c r="I240" s="5" t="inlineStr">
+      <c r="I240" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B241" s="5" t="inlineStr">
+      <c r="A241" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B241" s="6" t="inlineStr">
         <is>
           <t>A1-E1</t>
         </is>
       </c>
-      <c r="C241" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D241" s="5" t="inlineStr">
+      <c r="C241" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D241" s="6" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="E241" s="5" t="inlineStr">
+      <c r="E241" s="6" t="inlineStr">
         <is>
           <t>16/07/2026</t>
         </is>
       </c>
-      <c r="F241" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G241" s="5" t="inlineStr"/>
-      <c r="H241" s="5" t="inlineStr">
+      <c r="F241" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G241" s="6" t="inlineStr"/>
+      <c r="H241" s="6" t="inlineStr">
         <is>
           <t>0/38</t>
         </is>
       </c>
-      <c r="I241" s="5" t="inlineStr">
+      <c r="I241" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B242" s="5" t="inlineStr">
+      <c r="A242" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B242" s="6" t="inlineStr">
         <is>
           <t>A1-E1</t>
         </is>
       </c>
-      <c r="C242" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D242" s="5" t="inlineStr">
+      <c r="C242" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D242" s="6" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="E242" s="5" t="inlineStr">
+      <c r="E242" s="6" t="inlineStr">
         <is>
           <t>21/07/2026</t>
         </is>
       </c>
-      <c r="F242" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G242" s="5" t="inlineStr"/>
-      <c r="H242" s="5" t="inlineStr">
+      <c r="F242" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G242" s="6" t="inlineStr"/>
+      <c r="H242" s="6" t="inlineStr">
         <is>
           <t>0/38</t>
         </is>
       </c>
-      <c r="I242" s="5" t="inlineStr">
+      <c r="I242" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B243" s="5" t="inlineStr">
+      <c r="A243" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B243" s="6" t="inlineStr">
         <is>
           <t>A1-E1</t>
         </is>
       </c>
-      <c r="C243" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D243" s="5" t="inlineStr">
+      <c r="C243" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D243" s="6" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="E243" s="5" t="inlineStr">
+      <c r="E243" s="6" t="inlineStr">
         <is>
           <t>22/07/2026</t>
         </is>
       </c>
-      <c r="F243" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G243" s="5" t="inlineStr"/>
-      <c r="H243" s="5" t="inlineStr">
+      <c r="F243" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G243" s="6" t="inlineStr"/>
+      <c r="H243" s="6" t="inlineStr">
         <is>
           <t>0/38</t>
         </is>
       </c>
-      <c r="I243" s="5" t="inlineStr">
+      <c r="I243" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B244" s="5" t="inlineStr">
+      <c r="A244" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B244" s="6" t="inlineStr">
         <is>
           <t>A1-E1</t>
         </is>
       </c>
-      <c r="C244" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D244" s="5" t="inlineStr">
+      <c r="C244" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D244" s="6" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="E244" s="5" t="inlineStr">
+      <c r="E244" s="6" t="inlineStr">
         <is>
           <t>23/07/2026</t>
         </is>
       </c>
-      <c r="F244" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G244" s="5" t="inlineStr"/>
-      <c r="H244" s="5" t="inlineStr">
+      <c r="F244" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G244" s="6" t="inlineStr"/>
+      <c r="H244" s="6" t="inlineStr">
         <is>
           <t>0/38</t>
         </is>
       </c>
-      <c r="I244" s="5" t="inlineStr">
+      <c r="I244" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -12498,43 +12498,43 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B250" s="9" t="inlineStr">
+      <c r="A250" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B250" s="5" t="inlineStr">
         <is>
           <t>A1-E2</t>
         </is>
       </c>
-      <c r="C250" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D250" s="9" t="inlineStr">
+      <c r="C250" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D250" s="5" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E250" s="9" t="inlineStr">
+      <c r="E250" s="5" t="inlineStr">
         <is>
           <t>04/06/2026</t>
         </is>
       </c>
-      <c r="F250" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G250" s="9" t="inlineStr"/>
-      <c r="H250" s="9" t="inlineStr">
+      <c r="F250" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G250" s="5" t="inlineStr"/>
+      <c r="H250" s="5" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I250" s="9" t="inlineStr">
+      <c r="I250" s="5" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
@@ -13105,387 +13105,387 @@
       </c>
     </row>
     <row r="263">
-      <c r="A263" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B263" s="5" t="inlineStr">
+      <c r="A263" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B263" s="6" t="inlineStr">
         <is>
           <t>A1-E2</t>
         </is>
       </c>
-      <c r="C263" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D263" s="5" t="inlineStr">
+      <c r="C263" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D263" s="6" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="E263" s="5" t="inlineStr">
+      <c r="E263" s="6" t="inlineStr">
         <is>
           <t>07/07/2026</t>
         </is>
       </c>
-      <c r="F263" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G263" s="5" t="inlineStr"/>
-      <c r="H263" s="5" t="inlineStr">
+      <c r="F263" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G263" s="6" t="inlineStr"/>
+      <c r="H263" s="6" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I263" s="5" t="inlineStr">
+      <c r="I263" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="264">
-      <c r="A264" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B264" s="5" t="inlineStr">
+      <c r="A264" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B264" s="6" t="inlineStr">
         <is>
           <t>A1-E2</t>
         </is>
       </c>
-      <c r="C264" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D264" s="5" t="inlineStr">
+      <c r="C264" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D264" s="6" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="E264" s="5" t="inlineStr">
+      <c r="E264" s="6" t="inlineStr">
         <is>
           <t>08/07/2026</t>
         </is>
       </c>
-      <c r="F264" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G264" s="5" t="inlineStr"/>
-      <c r="H264" s="5" t="inlineStr">
+      <c r="F264" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G264" s="6" t="inlineStr"/>
+      <c r="H264" s="6" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I264" s="5" t="inlineStr">
+      <c r="I264" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="265">
-      <c r="A265" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B265" s="5" t="inlineStr">
+      <c r="A265" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B265" s="6" t="inlineStr">
         <is>
           <t>A1-E2</t>
         </is>
       </c>
-      <c r="C265" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D265" s="5" t="inlineStr">
+      <c r="C265" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D265" s="6" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="E265" s="5" t="inlineStr">
+      <c r="E265" s="6" t="inlineStr">
         <is>
           <t>09/07/2026</t>
         </is>
       </c>
-      <c r="F265" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G265" s="5" t="inlineStr"/>
-      <c r="H265" s="5" t="inlineStr">
+      <c r="F265" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G265" s="6" t="inlineStr"/>
+      <c r="H265" s="6" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I265" s="5" t="inlineStr">
+      <c r="I265" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="266">
-      <c r="A266" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B266" s="5" t="inlineStr">
+      <c r="A266" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B266" s="6" t="inlineStr">
         <is>
           <t>A1-E2</t>
         </is>
       </c>
-      <c r="C266" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D266" s="5" t="inlineStr">
+      <c r="C266" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D266" s="6" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="E266" s="5" t="inlineStr">
+      <c r="E266" s="6" t="inlineStr">
         <is>
           <t>14/07/2026</t>
         </is>
       </c>
-      <c r="F266" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G266" s="5" t="inlineStr"/>
-      <c r="H266" s="5" t="inlineStr">
+      <c r="F266" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G266" s="6" t="inlineStr"/>
+      <c r="H266" s="6" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I266" s="5" t="inlineStr">
+      <c r="I266" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="267">
-      <c r="A267" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B267" s="5" t="inlineStr">
+      <c r="A267" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B267" s="6" t="inlineStr">
         <is>
           <t>A1-E2</t>
         </is>
       </c>
-      <c r="C267" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D267" s="5" t="inlineStr">
+      <c r="C267" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D267" s="6" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="E267" s="5" t="inlineStr">
+      <c r="E267" s="6" t="inlineStr">
         <is>
           <t>15/07/2026</t>
         </is>
       </c>
-      <c r="F267" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G267" s="5" t="inlineStr"/>
-      <c r="H267" s="5" t="inlineStr">
+      <c r="F267" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G267" s="6" t="inlineStr"/>
+      <c r="H267" s="6" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I267" s="5" t="inlineStr">
+      <c r="I267" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="268">
-      <c r="A268" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B268" s="5" t="inlineStr">
+      <c r="A268" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B268" s="6" t="inlineStr">
         <is>
           <t>A1-E2</t>
         </is>
       </c>
-      <c r="C268" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D268" s="5" t="inlineStr">
+      <c r="C268" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D268" s="6" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="E268" s="5" t="inlineStr">
+      <c r="E268" s="6" t="inlineStr">
         <is>
           <t>16/07/2026</t>
         </is>
       </c>
-      <c r="F268" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G268" s="5" t="inlineStr"/>
-      <c r="H268" s="5" t="inlineStr">
+      <c r="F268" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G268" s="6" t="inlineStr"/>
+      <c r="H268" s="6" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I268" s="5" t="inlineStr">
+      <c r="I268" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="269">
-      <c r="A269" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B269" s="5" t="inlineStr">
+      <c r="A269" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B269" s="6" t="inlineStr">
         <is>
           <t>A1-E2</t>
         </is>
       </c>
-      <c r="C269" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D269" s="5" t="inlineStr">
+      <c r="C269" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D269" s="6" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="E269" s="5" t="inlineStr">
+      <c r="E269" s="6" t="inlineStr">
         <is>
           <t>21/07/2026</t>
         </is>
       </c>
-      <c r="F269" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G269" s="5" t="inlineStr"/>
-      <c r="H269" s="5" t="inlineStr">
+      <c r="F269" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G269" s="6" t="inlineStr"/>
+      <c r="H269" s="6" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I269" s="5" t="inlineStr">
+      <c r="I269" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="270">
-      <c r="A270" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B270" s="5" t="inlineStr">
+      <c r="A270" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B270" s="6" t="inlineStr">
         <is>
           <t>A1-E2</t>
         </is>
       </c>
-      <c r="C270" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D270" s="5" t="inlineStr">
+      <c r="C270" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D270" s="6" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="E270" s="5" t="inlineStr">
+      <c r="E270" s="6" t="inlineStr">
         <is>
           <t>22/07/2026</t>
         </is>
       </c>
-      <c r="F270" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G270" s="5" t="inlineStr"/>
-      <c r="H270" s="5" t="inlineStr">
+      <c r="F270" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G270" s="6" t="inlineStr"/>
+      <c r="H270" s="6" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I270" s="5" t="inlineStr">
+      <c r="I270" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="271">
-      <c r="A271" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B271" s="5" t="inlineStr">
+      <c r="A271" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B271" s="6" t="inlineStr">
         <is>
           <t>A1-E2</t>
         </is>
       </c>
-      <c r="C271" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D271" s="5" t="inlineStr">
+      <c r="C271" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D271" s="6" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="E271" s="5" t="inlineStr">
+      <c r="E271" s="6" t="inlineStr">
         <is>
           <t>23/07/2026</t>
         </is>
       </c>
-      <c r="F271" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G271" s="5" t="inlineStr"/>
-      <c r="H271" s="5" t="inlineStr">
+      <c r="F271" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G271" s="6" t="inlineStr"/>
+      <c r="H271" s="6" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I271" s="5" t="inlineStr">
+      <c r="I271" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -13727,43 +13727,43 @@
       </c>
     </row>
     <row r="277">
-      <c r="A277" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B277" s="9" t="inlineStr">
+      <c r="A277" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B277" s="5" t="inlineStr">
         <is>
           <t>A1-F1</t>
         </is>
       </c>
-      <c r="C277" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D277" s="9" t="inlineStr">
+      <c r="C277" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D277" s="5" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E277" s="9" t="inlineStr">
+      <c r="E277" s="5" t="inlineStr">
         <is>
           <t>04/06/2026</t>
         </is>
       </c>
-      <c r="F277" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G277" s="9" t="inlineStr"/>
-      <c r="H277" s="9" t="inlineStr">
+      <c r="F277" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G277" s="5" t="inlineStr"/>
+      <c r="H277" s="5" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I277" s="9" t="inlineStr">
+      <c r="I277" s="5" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
@@ -14334,387 +14334,387 @@
       </c>
     </row>
     <row r="290">
-      <c r="A290" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B290" s="5" t="inlineStr">
+      <c r="A290" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B290" s="6" t="inlineStr">
         <is>
           <t>A1-F1</t>
         </is>
       </c>
-      <c r="C290" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D290" s="5" t="inlineStr">
+      <c r="C290" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D290" s="6" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="E290" s="5" t="inlineStr">
+      <c r="E290" s="6" t="inlineStr">
         <is>
           <t>07/07/2026</t>
         </is>
       </c>
-      <c r="F290" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G290" s="5" t="inlineStr"/>
-      <c r="H290" s="5" t="inlineStr">
+      <c r="F290" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G290" s="6" t="inlineStr"/>
+      <c r="H290" s="6" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I290" s="5" t="inlineStr">
+      <c r="I290" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="291">
-      <c r="A291" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B291" s="5" t="inlineStr">
+      <c r="A291" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B291" s="6" t="inlineStr">
         <is>
           <t>A1-F1</t>
         </is>
       </c>
-      <c r="C291" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D291" s="5" t="inlineStr">
+      <c r="C291" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D291" s="6" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="E291" s="5" t="inlineStr">
+      <c r="E291" s="6" t="inlineStr">
         <is>
           <t>08/07/2026</t>
         </is>
       </c>
-      <c r="F291" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G291" s="5" t="inlineStr"/>
-      <c r="H291" s="5" t="inlineStr">
+      <c r="F291" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G291" s="6" t="inlineStr"/>
+      <c r="H291" s="6" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I291" s="5" t="inlineStr">
+      <c r="I291" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="292">
-      <c r="A292" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B292" s="5" t="inlineStr">
+      <c r="A292" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B292" s="6" t="inlineStr">
         <is>
           <t>A1-F1</t>
         </is>
       </c>
-      <c r="C292" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D292" s="5" t="inlineStr">
+      <c r="C292" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D292" s="6" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="E292" s="5" t="inlineStr">
+      <c r="E292" s="6" t="inlineStr">
         <is>
           <t>09/07/2026</t>
         </is>
       </c>
-      <c r="F292" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G292" s="5" t="inlineStr"/>
-      <c r="H292" s="5" t="inlineStr">
+      <c r="F292" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G292" s="6" t="inlineStr"/>
+      <c r="H292" s="6" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I292" s="5" t="inlineStr">
+      <c r="I292" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="293">
-      <c r="A293" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B293" s="5" t="inlineStr">
+      <c r="A293" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B293" s="6" t="inlineStr">
         <is>
           <t>A1-F1</t>
         </is>
       </c>
-      <c r="C293" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D293" s="5" t="inlineStr">
+      <c r="C293" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D293" s="6" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="E293" s="5" t="inlineStr">
+      <c r="E293" s="6" t="inlineStr">
         <is>
           <t>14/07/2026</t>
         </is>
       </c>
-      <c r="F293" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G293" s="5" t="inlineStr"/>
-      <c r="H293" s="5" t="inlineStr">
+      <c r="F293" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G293" s="6" t="inlineStr"/>
+      <c r="H293" s="6" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I293" s="5" t="inlineStr">
+      <c r="I293" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="294">
-      <c r="A294" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B294" s="5" t="inlineStr">
+      <c r="A294" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B294" s="6" t="inlineStr">
         <is>
           <t>A1-F1</t>
         </is>
       </c>
-      <c r="C294" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D294" s="5" t="inlineStr">
+      <c r="C294" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D294" s="6" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="E294" s="5" t="inlineStr">
+      <c r="E294" s="6" t="inlineStr">
         <is>
           <t>15/07/2026</t>
         </is>
       </c>
-      <c r="F294" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G294" s="5" t="inlineStr"/>
-      <c r="H294" s="5" t="inlineStr">
+      <c r="F294" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G294" s="6" t="inlineStr"/>
+      <c r="H294" s="6" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I294" s="5" t="inlineStr">
+      <c r="I294" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="295">
-      <c r="A295" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B295" s="5" t="inlineStr">
+      <c r="A295" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B295" s="6" t="inlineStr">
         <is>
           <t>A1-F1</t>
         </is>
       </c>
-      <c r="C295" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D295" s="5" t="inlineStr">
+      <c r="C295" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D295" s="6" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="E295" s="5" t="inlineStr">
+      <c r="E295" s="6" t="inlineStr">
         <is>
           <t>16/07/2026</t>
         </is>
       </c>
-      <c r="F295" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G295" s="5" t="inlineStr"/>
-      <c r="H295" s="5" t="inlineStr">
+      <c r="F295" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G295" s="6" t="inlineStr"/>
+      <c r="H295" s="6" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I295" s="5" t="inlineStr">
+      <c r="I295" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="296">
-      <c r="A296" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B296" s="5" t="inlineStr">
+      <c r="A296" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B296" s="6" t="inlineStr">
         <is>
           <t>A1-F1</t>
         </is>
       </c>
-      <c r="C296" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D296" s="5" t="inlineStr">
+      <c r="C296" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D296" s="6" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="E296" s="5" t="inlineStr">
+      <c r="E296" s="6" t="inlineStr">
         <is>
           <t>21/07/2026</t>
         </is>
       </c>
-      <c r="F296" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G296" s="5" t="inlineStr"/>
-      <c r="H296" s="5" t="inlineStr">
+      <c r="F296" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G296" s="6" t="inlineStr"/>
+      <c r="H296" s="6" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I296" s="5" t="inlineStr">
+      <c r="I296" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="297">
-      <c r="A297" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B297" s="5" t="inlineStr">
+      <c r="A297" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B297" s="6" t="inlineStr">
         <is>
           <t>A1-F1</t>
         </is>
       </c>
-      <c r="C297" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D297" s="5" t="inlineStr">
+      <c r="C297" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D297" s="6" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="E297" s="5" t="inlineStr">
+      <c r="E297" s="6" t="inlineStr">
         <is>
           <t>22/07/2026</t>
         </is>
       </c>
-      <c r="F297" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G297" s="5" t="inlineStr"/>
-      <c r="H297" s="5" t="inlineStr">
+      <c r="F297" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G297" s="6" t="inlineStr"/>
+      <c r="H297" s="6" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I297" s="5" t="inlineStr">
+      <c r="I297" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="298">
-      <c r="A298" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B298" s="5" t="inlineStr">
+      <c r="A298" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B298" s="6" t="inlineStr">
         <is>
           <t>A1-F1</t>
         </is>
       </c>
-      <c r="C298" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D298" s="5" t="inlineStr">
+      <c r="C298" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D298" s="6" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="E298" s="5" t="inlineStr">
+      <c r="E298" s="6" t="inlineStr">
         <is>
           <t>23/07/2026</t>
         </is>
       </c>
-      <c r="F298" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G298" s="5" t="inlineStr"/>
-      <c r="H298" s="5" t="inlineStr">
+      <c r="F298" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G298" s="6" t="inlineStr"/>
+      <c r="H298" s="6" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I298" s="5" t="inlineStr">
+      <c r="I298" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -14956,43 +14956,43 @@
       </c>
     </row>
     <row r="304">
-      <c r="A304" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B304" s="9" t="inlineStr">
+      <c r="A304" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B304" s="5" t="inlineStr">
         <is>
           <t>A1-F2</t>
         </is>
       </c>
-      <c r="C304" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D304" s="9" t="inlineStr">
+      <c r="C304" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D304" s="5" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E304" s="9" t="inlineStr">
+      <c r="E304" s="5" t="inlineStr">
         <is>
           <t>04/06/2026</t>
         </is>
       </c>
-      <c r="F304" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G304" s="9" t="inlineStr"/>
-      <c r="H304" s="9" t="inlineStr">
+      <c r="F304" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G304" s="5" t="inlineStr"/>
+      <c r="H304" s="5" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I304" s="9" t="inlineStr">
+      <c r="I304" s="5" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
@@ -15563,387 +15563,387 @@
       </c>
     </row>
     <row r="317">
-      <c r="A317" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B317" s="5" t="inlineStr">
+      <c r="A317" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B317" s="6" t="inlineStr">
         <is>
           <t>A1-F2</t>
         </is>
       </c>
-      <c r="C317" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D317" s="5" t="inlineStr">
+      <c r="C317" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D317" s="6" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="E317" s="5" t="inlineStr">
+      <c r="E317" s="6" t="inlineStr">
         <is>
           <t>07/07/2026</t>
         </is>
       </c>
-      <c r="F317" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G317" s="5" t="inlineStr"/>
-      <c r="H317" s="5" t="inlineStr">
+      <c r="F317" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G317" s="6" t="inlineStr"/>
+      <c r="H317" s="6" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I317" s="5" t="inlineStr">
+      <c r="I317" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="318">
-      <c r="A318" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B318" s="5" t="inlineStr">
+      <c r="A318" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B318" s="6" t="inlineStr">
         <is>
           <t>A1-F2</t>
         </is>
       </c>
-      <c r="C318" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D318" s="5" t="inlineStr">
+      <c r="C318" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D318" s="6" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="E318" s="5" t="inlineStr">
+      <c r="E318" s="6" t="inlineStr">
         <is>
           <t>08/07/2026</t>
         </is>
       </c>
-      <c r="F318" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G318" s="5" t="inlineStr"/>
-      <c r="H318" s="5" t="inlineStr">
+      <c r="F318" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G318" s="6" t="inlineStr"/>
+      <c r="H318" s="6" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I318" s="5" t="inlineStr">
+      <c r="I318" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="319">
-      <c r="A319" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B319" s="5" t="inlineStr">
+      <c r="A319" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B319" s="6" t="inlineStr">
         <is>
           <t>A1-F2</t>
         </is>
       </c>
-      <c r="C319" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D319" s="5" t="inlineStr">
+      <c r="C319" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D319" s="6" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="E319" s="5" t="inlineStr">
+      <c r="E319" s="6" t="inlineStr">
         <is>
           <t>09/07/2026</t>
         </is>
       </c>
-      <c r="F319" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G319" s="5" t="inlineStr"/>
-      <c r="H319" s="5" t="inlineStr">
+      <c r="F319" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G319" s="6" t="inlineStr"/>
+      <c r="H319" s="6" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I319" s="5" t="inlineStr">
+      <c r="I319" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="320">
-      <c r="A320" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B320" s="5" t="inlineStr">
+      <c r="A320" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B320" s="6" t="inlineStr">
         <is>
           <t>A1-F2</t>
         </is>
       </c>
-      <c r="C320" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D320" s="5" t="inlineStr">
+      <c r="C320" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D320" s="6" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="E320" s="5" t="inlineStr">
+      <c r="E320" s="6" t="inlineStr">
         <is>
           <t>14/07/2026</t>
         </is>
       </c>
-      <c r="F320" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G320" s="5" t="inlineStr"/>
-      <c r="H320" s="5" t="inlineStr">
+      <c r="F320" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G320" s="6" t="inlineStr"/>
+      <c r="H320" s="6" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I320" s="5" t="inlineStr">
+      <c r="I320" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="321">
-      <c r="A321" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B321" s="5" t="inlineStr">
+      <c r="A321" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B321" s="6" t="inlineStr">
         <is>
           <t>A1-F2</t>
         </is>
       </c>
-      <c r="C321" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D321" s="5" t="inlineStr">
+      <c r="C321" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D321" s="6" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="E321" s="5" t="inlineStr">
+      <c r="E321" s="6" t="inlineStr">
         <is>
           <t>15/07/2026</t>
         </is>
       </c>
-      <c r="F321" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G321" s="5" t="inlineStr"/>
-      <c r="H321" s="5" t="inlineStr">
+      <c r="F321" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G321" s="6" t="inlineStr"/>
+      <c r="H321" s="6" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I321" s="5" t="inlineStr">
+      <c r="I321" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="322">
-      <c r="A322" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B322" s="5" t="inlineStr">
+      <c r="A322" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B322" s="6" t="inlineStr">
         <is>
           <t>A1-F2</t>
         </is>
       </c>
-      <c r="C322" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D322" s="5" t="inlineStr">
+      <c r="C322" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D322" s="6" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="E322" s="5" t="inlineStr">
+      <c r="E322" s="6" t="inlineStr">
         <is>
           <t>16/07/2026</t>
         </is>
       </c>
-      <c r="F322" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G322" s="5" t="inlineStr"/>
-      <c r="H322" s="5" t="inlineStr">
+      <c r="F322" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G322" s="6" t="inlineStr"/>
+      <c r="H322" s="6" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I322" s="5" t="inlineStr">
+      <c r="I322" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="323">
-      <c r="A323" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B323" s="5" t="inlineStr">
+      <c r="A323" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B323" s="6" t="inlineStr">
         <is>
           <t>A1-F2</t>
         </is>
       </c>
-      <c r="C323" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D323" s="5" t="inlineStr">
+      <c r="C323" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D323" s="6" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="E323" s="5" t="inlineStr">
+      <c r="E323" s="6" t="inlineStr">
         <is>
           <t>21/07/2026</t>
         </is>
       </c>
-      <c r="F323" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G323" s="5" t="inlineStr"/>
-      <c r="H323" s="5" t="inlineStr">
+      <c r="F323" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G323" s="6" t="inlineStr"/>
+      <c r="H323" s="6" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I323" s="5" t="inlineStr">
+      <c r="I323" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="324">
-      <c r="A324" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B324" s="5" t="inlineStr">
+      <c r="A324" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B324" s="6" t="inlineStr">
         <is>
           <t>A1-F2</t>
         </is>
       </c>
-      <c r="C324" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D324" s="5" t="inlineStr">
+      <c r="C324" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D324" s="6" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="E324" s="5" t="inlineStr">
+      <c r="E324" s="6" t="inlineStr">
         <is>
           <t>22/07/2026</t>
         </is>
       </c>
-      <c r="F324" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G324" s="5" t="inlineStr"/>
-      <c r="H324" s="5" t="inlineStr">
+      <c r="F324" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G324" s="6" t="inlineStr"/>
+      <c r="H324" s="6" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I324" s="5" t="inlineStr">
+      <c r="I324" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="325">
-      <c r="A325" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B325" s="5" t="inlineStr">
+      <c r="A325" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B325" s="6" t="inlineStr">
         <is>
           <t>A1-F2</t>
         </is>
       </c>
-      <c r="C325" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D325" s="5" t="inlineStr">
+      <c r="C325" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D325" s="6" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="E325" s="5" t="inlineStr">
+      <c r="E325" s="6" t="inlineStr">
         <is>
           <t>23/07/2026</t>
         </is>
       </c>
-      <c r="F325" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G325" s="5" t="inlineStr"/>
-      <c r="H325" s="5" t="inlineStr">
+      <c r="F325" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G325" s="6" t="inlineStr"/>
+      <c r="H325" s="6" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I325" s="5" t="inlineStr">
+      <c r="I325" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A1_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A1_session_analysis.xlsx
@@ -58,14 +58,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFB6C1"/>
-        <bgColor rgb="00FFB6C1"/>
+        <fgColor rgb="00FFFFE0"/>
+        <bgColor rgb="00FFFFE0"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFFE0"/>
-        <bgColor rgb="00FFFFE0"/>
+        <fgColor rgb="00FFB6C1"/>
+        <bgColor rgb="00FFB6C1"/>
       </patternFill>
     </fill>
   </fills>
@@ -96,16 +96,16 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -814,7 +814,7 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>216</v>
+        <v>222</v>
       </c>
     </row>
     <row r="7">
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
@@ -980,7 +980,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>68.5%</t>
         </is>
       </c>
     </row>
@@ -1037,7 +1037,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>76.6%</t>
+          <t>76.4%</t>
         </is>
       </c>
     </row>
@@ -1342,22 +1342,22 @@
         <v>27</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q15" s="4" t="n">
         <v>7</v>
       </c>
       <c r="R15" s="4" t="inlineStr">
         <is>
-          <t>70.4%</t>
+          <t>74.1%</t>
         </is>
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>73.7%</t>
+          <t>71.2%</t>
         </is>
       </c>
     </row>
@@ -1424,22 +1424,22 @@
         <v>27</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q16" s="4" t="n">
         <v>7</v>
       </c>
       <c r="R16" s="4" t="inlineStr">
         <is>
-          <t>70.4%</t>
+          <t>74.1%</t>
         </is>
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>74.6%</t>
+          <t>72.4%</t>
         </is>
       </c>
     </row>
@@ -1506,22 +1506,22 @@
         <v>27</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q17" s="4" t="n">
         <v>7</v>
       </c>
       <c r="R17" s="4" t="inlineStr">
         <is>
-          <t>70.4%</t>
+          <t>74.1%</t>
         </is>
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>80.5%</t>
+          <t>81.0%</t>
         </is>
       </c>
     </row>
@@ -1588,22 +1588,22 @@
         <v>27</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q18" s="4" t="n">
         <v>7</v>
       </c>
       <c r="R18" s="4" t="inlineStr">
         <is>
-          <t>70.4%</t>
+          <t>74.1%</t>
         </is>
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>78.0%</t>
+          <t>78.7%</t>
         </is>
       </c>
     </row>
@@ -1670,22 +1670,22 @@
         <v>27</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q19" s="4" t="n">
         <v>7</v>
       </c>
       <c r="R19" s="4" t="inlineStr">
         <is>
-          <t>70.4%</t>
+          <t>74.1%</t>
         </is>
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>76.5%</t>
+          <t>77.4%</t>
         </is>
       </c>
     </row>
@@ -1752,65 +1752,69 @@
         <v>27</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q20" s="4" t="n">
         <v>7</v>
       </c>
       <c r="R20" s="4" t="inlineStr">
         <is>
-          <t>70.4%</t>
+          <t>74.1%</t>
         </is>
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>68.7%</t>
+          <t>69.7%</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>A1-A1</t>
         </is>
       </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="E21" s="5" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>05/07/2026</t>
         </is>
       </c>
-      <c r="F21" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G21" s="5" t="inlineStr"/>
-      <c r="H21" s="5" t="inlineStr">
-        <is>
-          <t>0/34</t>
-        </is>
-      </c>
-      <c r="I21" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>8/34</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
       <c r="K21" s="4" t="inlineStr">
@@ -1850,43 +1854,43 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B22" s="6" t="inlineStr">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
         <is>
           <t>A1-A1</t>
         </is>
       </c>
-      <c r="C22" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D22" s="6" t="inlineStr">
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="E22" s="6" t="inlineStr">
+      <c r="E22" s="5" t="inlineStr">
         <is>
           <t>06/07/2026</t>
         </is>
       </c>
-      <c r="F22" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G22" s="6" t="inlineStr"/>
-      <c r="H22" s="6" t="inlineStr">
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="inlineStr"/>
+      <c r="H22" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I22" s="6" t="inlineStr">
+      <c r="I22" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -1928,43 +1932,43 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B23" s="6" t="inlineStr">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
         <is>
           <t>A1-A1</t>
         </is>
       </c>
-      <c r="C23" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D23" s="6" t="inlineStr">
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="E23" s="6" t="inlineStr">
+      <c r="E23" s="5" t="inlineStr">
         <is>
           <t>11/07/2026</t>
         </is>
       </c>
-      <c r="F23" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G23" s="6" t="inlineStr"/>
-      <c r="H23" s="6" t="inlineStr">
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr"/>
+      <c r="H23" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I23" s="6" t="inlineStr">
+      <c r="I23" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -2006,43 +2010,43 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B24" s="6" t="inlineStr">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
         <is>
           <t>A1-A1</t>
         </is>
       </c>
-      <c r="C24" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D24" s="6" t="inlineStr">
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="E24" s="6" t="inlineStr">
+      <c r="E24" s="5" t="inlineStr">
         <is>
           <t>12/07/2026</t>
         </is>
       </c>
-      <c r="F24" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G24" s="6" t="inlineStr"/>
-      <c r="H24" s="6" t="inlineStr">
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="inlineStr"/>
+      <c r="H24" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I24" s="6" t="inlineStr">
+      <c r="I24" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -2084,43 +2088,43 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B25" s="6" t="inlineStr">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
         <is>
           <t>A1-A1</t>
         </is>
       </c>
-      <c r="C25" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D25" s="6" t="inlineStr">
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="E25" s="6" t="inlineStr">
+      <c r="E25" s="5" t="inlineStr">
         <is>
           <t>13/07/2026</t>
         </is>
       </c>
-      <c r="F25" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G25" s="6" t="inlineStr"/>
-      <c r="H25" s="6" t="inlineStr">
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr"/>
+      <c r="H25" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I25" s="6" t="inlineStr">
+      <c r="I25" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -2162,43 +2166,43 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B26" s="6" t="inlineStr">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
         <is>
           <t>A1-A1</t>
         </is>
       </c>
-      <c r="C26" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D26" s="6" t="inlineStr">
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="E26" s="6" t="inlineStr">
+      <c r="E26" s="5" t="inlineStr">
         <is>
           <t>18/07/2026</t>
         </is>
       </c>
-      <c r="F26" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G26" s="6" t="inlineStr"/>
-      <c r="H26" s="6" t="inlineStr">
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="inlineStr"/>
+      <c r="H26" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I26" s="6" t="inlineStr">
+      <c r="I26" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -2240,86 +2244,86 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B27" s="6" t="inlineStr">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
         <is>
           <t>A1-A1</t>
         </is>
       </c>
-      <c r="C27" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D27" s="6" t="inlineStr">
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="E27" s="6" t="inlineStr">
+      <c r="E27" s="5" t="inlineStr">
         <is>
           <t>19/07/2026</t>
         </is>
       </c>
-      <c r="F27" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G27" s="6" t="inlineStr"/>
-      <c r="H27" s="6" t="inlineStr">
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="inlineStr"/>
+      <c r="H27" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I27" s="6" t="inlineStr">
+      <c r="I27" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B28" s="6" t="inlineStr">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
         <is>
           <t>A1-A1</t>
         </is>
       </c>
-      <c r="C28" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D28" s="6" t="inlineStr">
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="E28" s="6" t="inlineStr">
+      <c r="E28" s="5" t="inlineStr">
         <is>
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="F28" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G28" s="6" t="inlineStr"/>
-      <c r="H28" s="6" t="inlineStr">
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G28" s="5" t="inlineStr"/>
+      <c r="H28" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I28" s="6" t="inlineStr">
+      <c r="I28" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -2490,7 +2494,7 @@
           <t>Recorded</t>
         </is>
       </c>
-      <c r="L31" s="7" t="inlineStr">
+      <c r="L31" s="6" t="inlineStr">
         <is>
           <t>Green</t>
         </is>
@@ -2552,7 +2556,7 @@
           <t>Not Recorded</t>
         </is>
       </c>
-      <c r="L32" s="8" t="inlineStr">
+      <c r="L32" s="7" t="inlineStr">
         <is>
           <t>Red</t>
         </is>
@@ -2614,7 +2618,7 @@
           <t>Pending</t>
         </is>
       </c>
-      <c r="L33" s="9" t="inlineStr">
+      <c r="L33" s="8" t="inlineStr">
         <is>
           <t>Yellow</t>
         </is>
@@ -3284,344 +3288,348 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B48" s="5" t="inlineStr">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>A1-A2</t>
         </is>
       </c>
-      <c r="C48" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D48" s="5" t="inlineStr">
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="E48" s="5" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>05/07/2026</t>
         </is>
       </c>
-      <c r="F48" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G48" s="5" t="inlineStr"/>
-      <c r="H48" s="5" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>10/33</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>A1-A2</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
+      <c r="F49" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G49" s="5" t="inlineStr"/>
+      <c r="H49" s="5" t="inlineStr">
         <is>
           <t>0/33</t>
         </is>
       </c>
-      <c r="I48" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B49" s="6" t="inlineStr">
+      <c r="I49" s="5" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="inlineStr">
         <is>
           <t>A1-A2</t>
         </is>
       </c>
-      <c r="C49" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D49" s="6" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="E49" s="6" t="inlineStr">
-        <is>
-          <t>06/07/2026</t>
-        </is>
-      </c>
-      <c r="F49" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G49" s="6" t="inlineStr"/>
-      <c r="H49" s="6" t="inlineStr">
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D50" s="5" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="E50" s="5" t="inlineStr">
+        <is>
+          <t>11/07/2026</t>
+        </is>
+      </c>
+      <c r="F50" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G50" s="5" t="inlineStr"/>
+      <c r="H50" s="5" t="inlineStr">
         <is>
           <t>0/33</t>
         </is>
       </c>
-      <c r="I49" s="6" t="inlineStr">
+      <c r="I50" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B50" s="6" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
         <is>
           <t>A1-A2</t>
         </is>
       </c>
-      <c r="C50" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D50" s="6" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="E50" s="6" t="inlineStr">
-        <is>
-          <t>11/07/2026</t>
-        </is>
-      </c>
-      <c r="F50" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G50" s="6" t="inlineStr"/>
-      <c r="H50" s="6" t="inlineStr">
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="E51" s="5" t="inlineStr">
+        <is>
+          <t>12/07/2026</t>
+        </is>
+      </c>
+      <c r="F51" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G51" s="5" t="inlineStr"/>
+      <c r="H51" s="5" t="inlineStr">
         <is>
           <t>0/33</t>
         </is>
       </c>
-      <c r="I50" s="6" t="inlineStr">
+      <c r="I51" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B51" s="6" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="inlineStr">
         <is>
           <t>A1-A2</t>
         </is>
       </c>
-      <c r="C51" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D51" s="6" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="E51" s="6" t="inlineStr">
-        <is>
-          <t>12/07/2026</t>
-        </is>
-      </c>
-      <c r="F51" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G51" s="6" t="inlineStr"/>
-      <c r="H51" s="6" t="inlineStr">
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D52" s="5" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="E52" s="5" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="F52" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G52" s="5" t="inlineStr"/>
+      <c r="H52" s="5" t="inlineStr">
         <is>
           <t>0/33</t>
         </is>
       </c>
-      <c r="I51" s="6" t="inlineStr">
+      <c r="I52" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B52" s="6" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
         <is>
           <t>A1-A2</t>
         </is>
       </c>
-      <c r="C52" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D52" s="6" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="E52" s="6" t="inlineStr">
-        <is>
-          <t>13/07/2026</t>
-        </is>
-      </c>
-      <c r="F52" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G52" s="6" t="inlineStr"/>
-      <c r="H52" s="6" t="inlineStr">
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D53" s="5" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E53" s="5" t="inlineStr">
+        <is>
+          <t>18/07/2026</t>
+        </is>
+      </c>
+      <c r="F53" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G53" s="5" t="inlineStr"/>
+      <c r="H53" s="5" t="inlineStr">
         <is>
           <t>0/33</t>
         </is>
       </c>
-      <c r="I52" s="6" t="inlineStr">
+      <c r="I53" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B53" s="6" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="inlineStr">
         <is>
           <t>A1-A2</t>
         </is>
       </c>
-      <c r="C53" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D53" s="6" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="E53" s="6" t="inlineStr">
-        <is>
-          <t>18/07/2026</t>
-        </is>
-      </c>
-      <c r="F53" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G53" s="6" t="inlineStr"/>
-      <c r="H53" s="6" t="inlineStr">
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D54" s="5" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="E54" s="5" t="inlineStr">
+        <is>
+          <t>19/07/2026</t>
+        </is>
+      </c>
+      <c r="F54" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G54" s="5" t="inlineStr"/>
+      <c r="H54" s="5" t="inlineStr">
         <is>
           <t>0/33</t>
         </is>
       </c>
-      <c r="I53" s="6" t="inlineStr">
+      <c r="I54" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B54" s="6" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="inlineStr">
         <is>
           <t>A1-A2</t>
         </is>
       </c>
-      <c r="C54" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D54" s="6" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="E54" s="6" t="inlineStr">
-        <is>
-          <t>19/07/2026</t>
-        </is>
-      </c>
-      <c r="F54" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G54" s="6" t="inlineStr"/>
-      <c r="H54" s="6" t="inlineStr">
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D55" s="5" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E55" s="5" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="F55" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G55" s="5" t="inlineStr"/>
+      <c r="H55" s="5" t="inlineStr">
         <is>
           <t>0/33</t>
         </is>
       </c>
-      <c r="I54" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B55" s="6" t="inlineStr">
-        <is>
-          <t>A1-A2</t>
-        </is>
-      </c>
-      <c r="C55" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D55" s="6" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="E55" s="6" t="inlineStr">
-        <is>
-          <t>20/07/2026</t>
-        </is>
-      </c>
-      <c r="F55" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G55" s="6" t="inlineStr"/>
-      <c r="H55" s="6" t="inlineStr">
-        <is>
-          <t>0/33</t>
-        </is>
-      </c>
-      <c r="I55" s="6" t="inlineStr">
+      <c r="I55" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -4521,344 +4529,348 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B75" s="5" t="inlineStr">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
         <is>
           <t>A1-B1</t>
         </is>
       </c>
-      <c r="C75" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D75" s="5" t="inlineStr">
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="E75" s="5" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
         <is>
           <t>05/07/2026</t>
         </is>
       </c>
-      <c r="F75" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G75" s="5" t="inlineStr"/>
-      <c r="H75" s="5" t="inlineStr">
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>31/34</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B76" s="5" t="inlineStr">
+        <is>
+          <t>A1-B1</t>
+        </is>
+      </c>
+      <c r="C76" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D76" s="5" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="E76" s="5" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
+      <c r="F76" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G76" s="5" t="inlineStr"/>
+      <c r="H76" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I75" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B76" s="6" t="inlineStr">
+      <c r="I76" s="5" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B77" s="5" t="inlineStr">
         <is>
           <t>A1-B1</t>
         </is>
       </c>
-      <c r="C76" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D76" s="6" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="E76" s="6" t="inlineStr">
-        <is>
-          <t>06/07/2026</t>
-        </is>
-      </c>
-      <c r="F76" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G76" s="6" t="inlineStr"/>
-      <c r="H76" s="6" t="inlineStr">
+      <c r="C77" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D77" s="5" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="E77" s="5" t="inlineStr">
+        <is>
+          <t>11/07/2026</t>
+        </is>
+      </c>
+      <c r="F77" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G77" s="5" t="inlineStr"/>
+      <c r="H77" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I76" s="6" t="inlineStr">
+      <c r="I77" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B77" s="6" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B78" s="5" t="inlineStr">
         <is>
           <t>A1-B1</t>
         </is>
       </c>
-      <c r="C77" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D77" s="6" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="E77" s="6" t="inlineStr">
-        <is>
-          <t>11/07/2026</t>
-        </is>
-      </c>
-      <c r="F77" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G77" s="6" t="inlineStr"/>
-      <c r="H77" s="6" t="inlineStr">
+      <c r="C78" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D78" s="5" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="E78" s="5" t="inlineStr">
+        <is>
+          <t>12/07/2026</t>
+        </is>
+      </c>
+      <c r="F78" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G78" s="5" t="inlineStr"/>
+      <c r="H78" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I77" s="6" t="inlineStr">
+      <c r="I78" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B78" s="6" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B79" s="5" t="inlineStr">
         <is>
           <t>A1-B1</t>
         </is>
       </c>
-      <c r="C78" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D78" s="6" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="E78" s="6" t="inlineStr">
-        <is>
-          <t>12/07/2026</t>
-        </is>
-      </c>
-      <c r="F78" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G78" s="6" t="inlineStr"/>
-      <c r="H78" s="6" t="inlineStr">
+      <c r="C79" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D79" s="5" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="E79" s="5" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="F79" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G79" s="5" t="inlineStr"/>
+      <c r="H79" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I78" s="6" t="inlineStr">
+      <c r="I79" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B79" s="6" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B80" s="5" t="inlineStr">
         <is>
           <t>A1-B1</t>
         </is>
       </c>
-      <c r="C79" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D79" s="6" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="E79" s="6" t="inlineStr">
-        <is>
-          <t>13/07/2026</t>
-        </is>
-      </c>
-      <c r="F79" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G79" s="6" t="inlineStr"/>
-      <c r="H79" s="6" t="inlineStr">
+      <c r="C80" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D80" s="5" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E80" s="5" t="inlineStr">
+        <is>
+          <t>18/07/2026</t>
+        </is>
+      </c>
+      <c r="F80" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G80" s="5" t="inlineStr"/>
+      <c r="H80" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I79" s="6" t="inlineStr">
+      <c r="I80" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B80" s="6" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B81" s="5" t="inlineStr">
         <is>
           <t>A1-B1</t>
         </is>
       </c>
-      <c r="C80" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D80" s="6" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="E80" s="6" t="inlineStr">
-        <is>
-          <t>18/07/2026</t>
-        </is>
-      </c>
-      <c r="F80" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G80" s="6" t="inlineStr"/>
-      <c r="H80" s="6" t="inlineStr">
+      <c r="C81" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D81" s="5" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="E81" s="5" t="inlineStr">
+        <is>
+          <t>19/07/2026</t>
+        </is>
+      </c>
+      <c r="F81" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G81" s="5" t="inlineStr"/>
+      <c r="H81" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I80" s="6" t="inlineStr">
+      <c r="I81" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B81" s="6" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B82" s="5" t="inlineStr">
         <is>
           <t>A1-B1</t>
         </is>
       </c>
-      <c r="C81" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D81" s="6" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="E81" s="6" t="inlineStr">
-        <is>
-          <t>19/07/2026</t>
-        </is>
-      </c>
-      <c r="F81" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G81" s="6" t="inlineStr"/>
-      <c r="H81" s="6" t="inlineStr">
+      <c r="C82" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D82" s="5" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E82" s="5" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="F82" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G82" s="5" t="inlineStr"/>
+      <c r="H82" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I81" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B82" s="6" t="inlineStr">
-        <is>
-          <t>A1-B1</t>
-        </is>
-      </c>
-      <c r="C82" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D82" s="6" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="E82" s="6" t="inlineStr">
-        <is>
-          <t>20/07/2026</t>
-        </is>
-      </c>
-      <c r="F82" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G82" s="6" t="inlineStr"/>
-      <c r="H82" s="6" t="inlineStr">
-        <is>
-          <t>0/34</t>
-        </is>
-      </c>
-      <c r="I82" s="6" t="inlineStr">
+      <c r="I82" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -5758,344 +5770,348 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B102" s="5" t="inlineStr">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
         <is>
           <t>A1-B2</t>
         </is>
       </c>
-      <c r="C102" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D102" s="5" t="inlineStr">
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="E102" s="5" t="inlineStr">
+      <c r="E102" s="2" t="inlineStr">
         <is>
           <t>05/07/2026</t>
         </is>
       </c>
-      <c r="F102" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G102" s="5" t="inlineStr"/>
-      <c r="H102" s="5" t="inlineStr">
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>31/34</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B103" s="5" t="inlineStr">
+        <is>
+          <t>A1-B2</t>
+        </is>
+      </c>
+      <c r="C103" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D103" s="5" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="E103" s="5" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
+      <c r="F103" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G103" s="5" t="inlineStr"/>
+      <c r="H103" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I102" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B103" s="6" t="inlineStr">
+      <c r="I103" s="5" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B104" s="5" t="inlineStr">
         <is>
           <t>A1-B2</t>
         </is>
       </c>
-      <c r="C103" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D103" s="6" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="E103" s="6" t="inlineStr">
-        <is>
-          <t>06/07/2026</t>
-        </is>
-      </c>
-      <c r="F103" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G103" s="6" t="inlineStr"/>
-      <c r="H103" s="6" t="inlineStr">
+      <c r="C104" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D104" s="5" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="E104" s="5" t="inlineStr">
+        <is>
+          <t>11/07/2026</t>
+        </is>
+      </c>
+      <c r="F104" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G104" s="5" t="inlineStr"/>
+      <c r="H104" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I103" s="6" t="inlineStr">
+      <c r="I104" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B104" s="6" t="inlineStr">
+    <row r="105">
+      <c r="A105" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B105" s="5" t="inlineStr">
         <is>
           <t>A1-B2</t>
         </is>
       </c>
-      <c r="C104" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D104" s="6" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="E104" s="6" t="inlineStr">
-        <is>
-          <t>11/07/2026</t>
-        </is>
-      </c>
-      <c r="F104" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G104" s="6" t="inlineStr"/>
-      <c r="H104" s="6" t="inlineStr">
+      <c r="C105" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D105" s="5" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="E105" s="5" t="inlineStr">
+        <is>
+          <t>12/07/2026</t>
+        </is>
+      </c>
+      <c r="F105" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G105" s="5" t="inlineStr"/>
+      <c r="H105" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I104" s="6" t="inlineStr">
+      <c r="I105" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B105" s="6" t="inlineStr">
+    <row r="106">
+      <c r="A106" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B106" s="5" t="inlineStr">
         <is>
           <t>A1-B2</t>
         </is>
       </c>
-      <c r="C105" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D105" s="6" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="E105" s="6" t="inlineStr">
-        <is>
-          <t>12/07/2026</t>
-        </is>
-      </c>
-      <c r="F105" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G105" s="6" t="inlineStr"/>
-      <c r="H105" s="6" t="inlineStr">
+      <c r="C106" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D106" s="5" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="E106" s="5" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="F106" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G106" s="5" t="inlineStr"/>
+      <c r="H106" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I105" s="6" t="inlineStr">
+      <c r="I106" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B106" s="6" t="inlineStr">
+    <row r="107">
+      <c r="A107" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B107" s="5" t="inlineStr">
         <is>
           <t>A1-B2</t>
         </is>
       </c>
-      <c r="C106" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D106" s="6" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="E106" s="6" t="inlineStr">
-        <is>
-          <t>13/07/2026</t>
-        </is>
-      </c>
-      <c r="F106" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G106" s="6" t="inlineStr"/>
-      <c r="H106" s="6" t="inlineStr">
+      <c r="C107" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D107" s="5" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E107" s="5" t="inlineStr">
+        <is>
+          <t>18/07/2026</t>
+        </is>
+      </c>
+      <c r="F107" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G107" s="5" t="inlineStr"/>
+      <c r="H107" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I106" s="6" t="inlineStr">
+      <c r="I107" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B107" s="6" t="inlineStr">
+    <row r="108">
+      <c r="A108" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B108" s="5" t="inlineStr">
         <is>
           <t>A1-B2</t>
         </is>
       </c>
-      <c r="C107" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D107" s="6" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="E107" s="6" t="inlineStr">
-        <is>
-          <t>18/07/2026</t>
-        </is>
-      </c>
-      <c r="F107" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G107" s="6" t="inlineStr"/>
-      <c r="H107" s="6" t="inlineStr">
+      <c r="C108" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D108" s="5" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="E108" s="5" t="inlineStr">
+        <is>
+          <t>19/07/2026</t>
+        </is>
+      </c>
+      <c r="F108" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G108" s="5" t="inlineStr"/>
+      <c r="H108" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I107" s="6" t="inlineStr">
+      <c r="I108" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B108" s="6" t="inlineStr">
+    <row r="109">
+      <c r="A109" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B109" s="5" t="inlineStr">
         <is>
           <t>A1-B2</t>
         </is>
       </c>
-      <c r="C108" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D108" s="6" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="E108" s="6" t="inlineStr">
-        <is>
-          <t>19/07/2026</t>
-        </is>
-      </c>
-      <c r="F108" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G108" s="6" t="inlineStr"/>
-      <c r="H108" s="6" t="inlineStr">
+      <c r="C109" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D109" s="5" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E109" s="5" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="F109" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G109" s="5" t="inlineStr"/>
+      <c r="H109" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I108" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B109" s="6" t="inlineStr">
-        <is>
-          <t>A1-B2</t>
-        </is>
-      </c>
-      <c r="C109" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D109" s="6" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="E109" s="6" t="inlineStr">
-        <is>
-          <t>20/07/2026</t>
-        </is>
-      </c>
-      <c r="F109" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G109" s="6" t="inlineStr"/>
-      <c r="H109" s="6" t="inlineStr">
-        <is>
-          <t>0/34</t>
-        </is>
-      </c>
-      <c r="I109" s="6" t="inlineStr">
+      <c r="I109" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -6995,344 +7011,348 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B129" s="5" t="inlineStr">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
         <is>
           <t>A1-C1</t>
         </is>
       </c>
-      <c r="C129" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D129" s="5" t="inlineStr">
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="E129" s="5" t="inlineStr">
+      <c r="E129" s="2" t="inlineStr">
         <is>
           <t>05/07/2026</t>
         </is>
       </c>
-      <c r="F129" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G129" s="5" t="inlineStr"/>
-      <c r="H129" s="5" t="inlineStr">
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G129" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H129" s="2" t="inlineStr">
+        <is>
+          <t>32/34</t>
+        </is>
+      </c>
+      <c r="I129" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B130" s="5" t="inlineStr">
+        <is>
+          <t>A1-C1</t>
+        </is>
+      </c>
+      <c r="C130" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D130" s="5" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="E130" s="5" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
+      <c r="F130" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G130" s="5" t="inlineStr"/>
+      <c r="H130" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I129" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B130" s="6" t="inlineStr">
+      <c r="I130" s="5" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B131" s="5" t="inlineStr">
         <is>
           <t>A1-C1</t>
         </is>
       </c>
-      <c r="C130" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D130" s="6" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="E130" s="6" t="inlineStr">
-        <is>
-          <t>06/07/2026</t>
-        </is>
-      </c>
-      <c r="F130" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G130" s="6" t="inlineStr"/>
-      <c r="H130" s="6" t="inlineStr">
+      <c r="C131" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D131" s="5" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="E131" s="5" t="inlineStr">
+        <is>
+          <t>11/07/2026</t>
+        </is>
+      </c>
+      <c r="F131" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G131" s="5" t="inlineStr"/>
+      <c r="H131" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I130" s="6" t="inlineStr">
+      <c r="I131" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B131" s="6" t="inlineStr">
+    <row r="132">
+      <c r="A132" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B132" s="5" t="inlineStr">
         <is>
           <t>A1-C1</t>
         </is>
       </c>
-      <c r="C131" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D131" s="6" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="E131" s="6" t="inlineStr">
-        <is>
-          <t>11/07/2026</t>
-        </is>
-      </c>
-      <c r="F131" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G131" s="6" t="inlineStr"/>
-      <c r="H131" s="6" t="inlineStr">
+      <c r="C132" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D132" s="5" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="E132" s="5" t="inlineStr">
+        <is>
+          <t>12/07/2026</t>
+        </is>
+      </c>
+      <c r="F132" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G132" s="5" t="inlineStr"/>
+      <c r="H132" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I131" s="6" t="inlineStr">
+      <c r="I132" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B132" s="6" t="inlineStr">
+    <row r="133">
+      <c r="A133" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B133" s="5" t="inlineStr">
         <is>
           <t>A1-C1</t>
         </is>
       </c>
-      <c r="C132" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D132" s="6" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="E132" s="6" t="inlineStr">
-        <is>
-          <t>12/07/2026</t>
-        </is>
-      </c>
-      <c r="F132" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G132" s="6" t="inlineStr"/>
-      <c r="H132" s="6" t="inlineStr">
+      <c r="C133" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D133" s="5" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="E133" s="5" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="F133" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G133" s="5" t="inlineStr"/>
+      <c r="H133" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I132" s="6" t="inlineStr">
+      <c r="I133" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B133" s="6" t="inlineStr">
+    <row r="134">
+      <c r="A134" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B134" s="5" t="inlineStr">
         <is>
           <t>A1-C1</t>
         </is>
       </c>
-      <c r="C133" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D133" s="6" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="E133" s="6" t="inlineStr">
-        <is>
-          <t>13/07/2026</t>
-        </is>
-      </c>
-      <c r="F133" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G133" s="6" t="inlineStr"/>
-      <c r="H133" s="6" t="inlineStr">
+      <c r="C134" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D134" s="5" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E134" s="5" t="inlineStr">
+        <is>
+          <t>18/07/2026</t>
+        </is>
+      </c>
+      <c r="F134" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G134" s="5" t="inlineStr"/>
+      <c r="H134" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I133" s="6" t="inlineStr">
+      <c r="I134" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="134">
-      <c r="A134" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B134" s="6" t="inlineStr">
+    <row r="135">
+      <c r="A135" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B135" s="5" t="inlineStr">
         <is>
           <t>A1-C1</t>
         </is>
       </c>
-      <c r="C134" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D134" s="6" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="E134" s="6" t="inlineStr">
-        <is>
-          <t>18/07/2026</t>
-        </is>
-      </c>
-      <c r="F134" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G134" s="6" t="inlineStr"/>
-      <c r="H134" s="6" t="inlineStr">
+      <c r="C135" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D135" s="5" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="E135" s="5" t="inlineStr">
+        <is>
+          <t>19/07/2026</t>
+        </is>
+      </c>
+      <c r="F135" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G135" s="5" t="inlineStr"/>
+      <c r="H135" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I134" s="6" t="inlineStr">
+      <c r="I135" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B135" s="6" t="inlineStr">
+    <row r="136">
+      <c r="A136" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B136" s="5" t="inlineStr">
         <is>
           <t>A1-C1</t>
         </is>
       </c>
-      <c r="C135" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D135" s="6" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="E135" s="6" t="inlineStr">
-        <is>
-          <t>19/07/2026</t>
-        </is>
-      </c>
-      <c r="F135" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G135" s="6" t="inlineStr"/>
-      <c r="H135" s="6" t="inlineStr">
+      <c r="C136" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D136" s="5" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E136" s="5" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="F136" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G136" s="5" t="inlineStr"/>
+      <c r="H136" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I135" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B136" s="6" t="inlineStr">
-        <is>
-          <t>A1-C1</t>
-        </is>
-      </c>
-      <c r="C136" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D136" s="6" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="E136" s="6" t="inlineStr">
-        <is>
-          <t>20/07/2026</t>
-        </is>
-      </c>
-      <c r="F136" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G136" s="6" t="inlineStr"/>
-      <c r="H136" s="6" t="inlineStr">
-        <is>
-          <t>0/34</t>
-        </is>
-      </c>
-      <c r="I136" s="6" t="inlineStr">
+      <c r="I136" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -8232,344 +8252,348 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B156" s="5" t="inlineStr">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
         <is>
           <t>A1-C2</t>
         </is>
       </c>
-      <c r="C156" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D156" s="5" t="inlineStr">
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="E156" s="5" t="inlineStr">
+      <c r="E156" s="2" t="inlineStr">
         <is>
           <t>05/07/2026</t>
         </is>
       </c>
-      <c r="F156" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G156" s="5" t="inlineStr"/>
-      <c r="H156" s="5" t="inlineStr">
+      <c r="F156" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G156" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H156" s="2" t="inlineStr">
+        <is>
+          <t>29/33</t>
+        </is>
+      </c>
+      <c r="I156" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B157" s="5" t="inlineStr">
+        <is>
+          <t>A1-C2</t>
+        </is>
+      </c>
+      <c r="C157" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D157" s="5" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="E157" s="5" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
+      <c r="F157" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G157" s="5" t="inlineStr"/>
+      <c r="H157" s="5" t="inlineStr">
         <is>
           <t>0/33</t>
         </is>
       </c>
-      <c r="I156" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B157" s="6" t="inlineStr">
+      <c r="I157" s="5" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B158" s="5" t="inlineStr">
         <is>
           <t>A1-C2</t>
         </is>
       </c>
-      <c r="C157" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D157" s="6" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="E157" s="6" t="inlineStr">
-        <is>
-          <t>06/07/2026</t>
-        </is>
-      </c>
-      <c r="F157" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G157" s="6" t="inlineStr"/>
-      <c r="H157" s="6" t="inlineStr">
+      <c r="C158" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D158" s="5" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="E158" s="5" t="inlineStr">
+        <is>
+          <t>11/07/2026</t>
+        </is>
+      </c>
+      <c r="F158" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G158" s="5" t="inlineStr"/>
+      <c r="H158" s="5" t="inlineStr">
         <is>
           <t>0/33</t>
         </is>
       </c>
-      <c r="I157" s="6" t="inlineStr">
+      <c r="I158" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="158">
-      <c r="A158" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B158" s="6" t="inlineStr">
+    <row r="159">
+      <c r="A159" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B159" s="5" t="inlineStr">
         <is>
           <t>A1-C2</t>
         </is>
       </c>
-      <c r="C158" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D158" s="6" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="E158" s="6" t="inlineStr">
-        <is>
-          <t>11/07/2026</t>
-        </is>
-      </c>
-      <c r="F158" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G158" s="6" t="inlineStr"/>
-      <c r="H158" s="6" t="inlineStr">
+      <c r="C159" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D159" s="5" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="E159" s="5" t="inlineStr">
+        <is>
+          <t>12/07/2026</t>
+        </is>
+      </c>
+      <c r="F159" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G159" s="5" t="inlineStr"/>
+      <c r="H159" s="5" t="inlineStr">
         <is>
           <t>0/33</t>
         </is>
       </c>
-      <c r="I158" s="6" t="inlineStr">
+      <c r="I159" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="159">
-      <c r="A159" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B159" s="6" t="inlineStr">
+    <row r="160">
+      <c r="A160" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B160" s="5" t="inlineStr">
         <is>
           <t>A1-C2</t>
         </is>
       </c>
-      <c r="C159" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D159" s="6" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="E159" s="6" t="inlineStr">
-        <is>
-          <t>12/07/2026</t>
-        </is>
-      </c>
-      <c r="F159" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G159" s="6" t="inlineStr"/>
-      <c r="H159" s="6" t="inlineStr">
+      <c r="C160" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D160" s="5" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="E160" s="5" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="F160" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G160" s="5" t="inlineStr"/>
+      <c r="H160" s="5" t="inlineStr">
         <is>
           <t>0/33</t>
         </is>
       </c>
-      <c r="I159" s="6" t="inlineStr">
+      <c r="I160" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="160">
-      <c r="A160" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B160" s="6" t="inlineStr">
+    <row r="161">
+      <c r="A161" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B161" s="5" t="inlineStr">
         <is>
           <t>A1-C2</t>
         </is>
       </c>
-      <c r="C160" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D160" s="6" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="E160" s="6" t="inlineStr">
-        <is>
-          <t>13/07/2026</t>
-        </is>
-      </c>
-      <c r="F160" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G160" s="6" t="inlineStr"/>
-      <c r="H160" s="6" t="inlineStr">
+      <c r="C161" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D161" s="5" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E161" s="5" t="inlineStr">
+        <is>
+          <t>18/07/2026</t>
+        </is>
+      </c>
+      <c r="F161" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G161" s="5" t="inlineStr"/>
+      <c r="H161" s="5" t="inlineStr">
         <is>
           <t>0/33</t>
         </is>
       </c>
-      <c r="I160" s="6" t="inlineStr">
+      <c r="I161" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="161">
-      <c r="A161" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B161" s="6" t="inlineStr">
+    <row r="162">
+      <c r="A162" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B162" s="5" t="inlineStr">
         <is>
           <t>A1-C2</t>
         </is>
       </c>
-      <c r="C161" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D161" s="6" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="E161" s="6" t="inlineStr">
-        <is>
-          <t>18/07/2026</t>
-        </is>
-      </c>
-      <c r="F161" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G161" s="6" t="inlineStr"/>
-      <c r="H161" s="6" t="inlineStr">
+      <c r="C162" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D162" s="5" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="E162" s="5" t="inlineStr">
+        <is>
+          <t>19/07/2026</t>
+        </is>
+      </c>
+      <c r="F162" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G162" s="5" t="inlineStr"/>
+      <c r="H162" s="5" t="inlineStr">
         <is>
           <t>0/33</t>
         </is>
       </c>
-      <c r="I161" s="6" t="inlineStr">
+      <c r="I162" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="162">
-      <c r="A162" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B162" s="6" t="inlineStr">
+    <row r="163">
+      <c r="A163" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B163" s="5" t="inlineStr">
         <is>
           <t>A1-C2</t>
         </is>
       </c>
-      <c r="C162" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D162" s="6" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="E162" s="6" t="inlineStr">
-        <is>
-          <t>19/07/2026</t>
-        </is>
-      </c>
-      <c r="F162" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G162" s="6" t="inlineStr"/>
-      <c r="H162" s="6" t="inlineStr">
+      <c r="C163" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D163" s="5" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E163" s="5" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="F163" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G163" s="5" t="inlineStr"/>
+      <c r="H163" s="5" t="inlineStr">
         <is>
           <t>0/33</t>
         </is>
       </c>
-      <c r="I162" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B163" s="6" t="inlineStr">
-        <is>
-          <t>A1-C2</t>
-        </is>
-      </c>
-      <c r="C163" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D163" s="6" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="E163" s="6" t="inlineStr">
-        <is>
-          <t>20/07/2026</t>
-        </is>
-      </c>
-      <c r="F163" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G163" s="6" t="inlineStr"/>
-      <c r="H163" s="6" t="inlineStr">
-        <is>
-          <t>0/33</t>
-        </is>
-      </c>
-      <c r="I163" s="6" t="inlineStr">
+      <c r="I163" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -8811,43 +8835,43 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B169" s="5" t="inlineStr">
+      <c r="A169" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B169" s="9" t="inlineStr">
         <is>
           <t>A1-D1</t>
         </is>
       </c>
-      <c r="C169" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D169" s="5" t="inlineStr">
+      <c r="C169" s="9" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D169" s="9" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E169" s="5" t="inlineStr">
+      <c r="E169" s="9" t="inlineStr">
         <is>
           <t>04/06/2026</t>
         </is>
       </c>
-      <c r="F169" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G169" s="5" t="inlineStr"/>
-      <c r="H169" s="5" t="inlineStr">
+      <c r="F169" s="9" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G169" s="9" t="inlineStr"/>
+      <c r="H169" s="9" t="inlineStr">
         <is>
           <t>0/35</t>
         </is>
       </c>
-      <c r="I169" s="5" t="inlineStr">
+      <c r="I169" s="9" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
@@ -9418,387 +9442,387 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B182" s="6" t="inlineStr">
+      <c r="A182" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B182" s="5" t="inlineStr">
         <is>
           <t>A1-D1</t>
         </is>
       </c>
-      <c r="C182" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D182" s="6" t="inlineStr">
+      <c r="C182" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D182" s="5" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="E182" s="6" t="inlineStr">
+      <c r="E182" s="5" t="inlineStr">
         <is>
           <t>07/07/2026</t>
         </is>
       </c>
-      <c r="F182" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G182" s="6" t="inlineStr"/>
-      <c r="H182" s="6" t="inlineStr">
+      <c r="F182" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G182" s="5" t="inlineStr"/>
+      <c r="H182" s="5" t="inlineStr">
         <is>
           <t>0/35</t>
         </is>
       </c>
-      <c r="I182" s="6" t="inlineStr">
+      <c r="I182" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B183" s="6" t="inlineStr">
+      <c r="A183" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B183" s="5" t="inlineStr">
         <is>
           <t>A1-D1</t>
         </is>
       </c>
-      <c r="C183" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D183" s="6" t="inlineStr">
+      <c r="C183" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D183" s="5" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="E183" s="6" t="inlineStr">
+      <c r="E183" s="5" t="inlineStr">
         <is>
           <t>08/07/2026</t>
         </is>
       </c>
-      <c r="F183" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G183" s="6" t="inlineStr"/>
-      <c r="H183" s="6" t="inlineStr">
+      <c r="F183" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G183" s="5" t="inlineStr"/>
+      <c r="H183" s="5" t="inlineStr">
         <is>
           <t>0/35</t>
         </is>
       </c>
-      <c r="I183" s="6" t="inlineStr">
+      <c r="I183" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B184" s="6" t="inlineStr">
+      <c r="A184" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B184" s="5" t="inlineStr">
         <is>
           <t>A1-D1</t>
         </is>
       </c>
-      <c r="C184" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D184" s="6" t="inlineStr">
+      <c r="C184" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D184" s="5" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="E184" s="6" t="inlineStr">
+      <c r="E184" s="5" t="inlineStr">
         <is>
           <t>09/07/2026</t>
         </is>
       </c>
-      <c r="F184" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G184" s="6" t="inlineStr"/>
-      <c r="H184" s="6" t="inlineStr">
+      <c r="F184" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G184" s="5" t="inlineStr"/>
+      <c r="H184" s="5" t="inlineStr">
         <is>
           <t>0/35</t>
         </is>
       </c>
-      <c r="I184" s="6" t="inlineStr">
+      <c r="I184" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B185" s="6" t="inlineStr">
+      <c r="A185" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B185" s="5" t="inlineStr">
         <is>
           <t>A1-D1</t>
         </is>
       </c>
-      <c r="C185" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D185" s="6" t="inlineStr">
+      <c r="C185" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D185" s="5" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="E185" s="6" t="inlineStr">
+      <c r="E185" s="5" t="inlineStr">
         <is>
           <t>14/07/2026</t>
         </is>
       </c>
-      <c r="F185" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G185" s="6" t="inlineStr"/>
-      <c r="H185" s="6" t="inlineStr">
+      <c r="F185" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G185" s="5" t="inlineStr"/>
+      <c r="H185" s="5" t="inlineStr">
         <is>
           <t>0/35</t>
         </is>
       </c>
-      <c r="I185" s="6" t="inlineStr">
+      <c r="I185" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B186" s="6" t="inlineStr">
+      <c r="A186" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B186" s="5" t="inlineStr">
         <is>
           <t>A1-D1</t>
         </is>
       </c>
-      <c r="C186" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D186" s="6" t="inlineStr">
+      <c r="C186" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D186" s="5" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="E186" s="6" t="inlineStr">
+      <c r="E186" s="5" t="inlineStr">
         <is>
           <t>15/07/2026</t>
         </is>
       </c>
-      <c r="F186" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G186" s="6" t="inlineStr"/>
-      <c r="H186" s="6" t="inlineStr">
+      <c r="F186" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G186" s="5" t="inlineStr"/>
+      <c r="H186" s="5" t="inlineStr">
         <is>
           <t>0/35</t>
         </is>
       </c>
-      <c r="I186" s="6" t="inlineStr">
+      <c r="I186" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B187" s="6" t="inlineStr">
+      <c r="A187" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B187" s="5" t="inlineStr">
         <is>
           <t>A1-D1</t>
         </is>
       </c>
-      <c r="C187" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D187" s="6" t="inlineStr">
+      <c r="C187" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D187" s="5" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="E187" s="6" t="inlineStr">
+      <c r="E187" s="5" t="inlineStr">
         <is>
           <t>16/07/2026</t>
         </is>
       </c>
-      <c r="F187" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G187" s="6" t="inlineStr"/>
-      <c r="H187" s="6" t="inlineStr">
+      <c r="F187" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G187" s="5" t="inlineStr"/>
+      <c r="H187" s="5" t="inlineStr">
         <is>
           <t>0/35</t>
         </is>
       </c>
-      <c r="I187" s="6" t="inlineStr">
+      <c r="I187" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B188" s="6" t="inlineStr">
+      <c r="A188" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B188" s="5" t="inlineStr">
         <is>
           <t>A1-D1</t>
         </is>
       </c>
-      <c r="C188" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D188" s="6" t="inlineStr">
+      <c r="C188" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D188" s="5" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="E188" s="6" t="inlineStr">
+      <c r="E188" s="5" t="inlineStr">
         <is>
           <t>21/07/2026</t>
         </is>
       </c>
-      <c r="F188" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G188" s="6" t="inlineStr"/>
-      <c r="H188" s="6" t="inlineStr">
+      <c r="F188" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G188" s="5" t="inlineStr"/>
+      <c r="H188" s="5" t="inlineStr">
         <is>
           <t>0/35</t>
         </is>
       </c>
-      <c r="I188" s="6" t="inlineStr">
+      <c r="I188" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B189" s="6" t="inlineStr">
+      <c r="A189" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B189" s="5" t="inlineStr">
         <is>
           <t>A1-D1</t>
         </is>
       </c>
-      <c r="C189" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D189" s="6" t="inlineStr">
+      <c r="C189" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D189" s="5" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="E189" s="6" t="inlineStr">
+      <c r="E189" s="5" t="inlineStr">
         <is>
           <t>22/07/2026</t>
         </is>
       </c>
-      <c r="F189" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G189" s="6" t="inlineStr"/>
-      <c r="H189" s="6" t="inlineStr">
+      <c r="F189" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G189" s="5" t="inlineStr"/>
+      <c r="H189" s="5" t="inlineStr">
         <is>
           <t>0/35</t>
         </is>
       </c>
-      <c r="I189" s="6" t="inlineStr">
+      <c r="I189" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B190" s="6" t="inlineStr">
+      <c r="A190" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B190" s="5" t="inlineStr">
         <is>
           <t>A1-D1</t>
         </is>
       </c>
-      <c r="C190" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D190" s="6" t="inlineStr">
+      <c r="C190" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D190" s="5" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="E190" s="6" t="inlineStr">
+      <c r="E190" s="5" t="inlineStr">
         <is>
           <t>23/07/2026</t>
         </is>
       </c>
-      <c r="F190" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G190" s="6" t="inlineStr"/>
-      <c r="H190" s="6" t="inlineStr">
+      <c r="F190" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G190" s="5" t="inlineStr"/>
+      <c r="H190" s="5" t="inlineStr">
         <is>
           <t>0/35</t>
         </is>
       </c>
-      <c r="I190" s="6" t="inlineStr">
+      <c r="I190" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -10040,43 +10064,43 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B196" s="5" t="inlineStr">
+      <c r="A196" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B196" s="9" t="inlineStr">
         <is>
           <t>A1-D2</t>
         </is>
       </c>
-      <c r="C196" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D196" s="5" t="inlineStr">
+      <c r="C196" s="9" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D196" s="9" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E196" s="5" t="inlineStr">
+      <c r="E196" s="9" t="inlineStr">
         <is>
           <t>04/06/2026</t>
         </is>
       </c>
-      <c r="F196" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G196" s="5" t="inlineStr"/>
-      <c r="H196" s="5" t="inlineStr">
+      <c r="F196" s="9" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G196" s="9" t="inlineStr"/>
+      <c r="H196" s="9" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I196" s="5" t="inlineStr">
+      <c r="I196" s="9" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
@@ -10647,387 +10671,387 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B209" s="6" t="inlineStr">
+      <c r="A209" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B209" s="5" t="inlineStr">
         <is>
           <t>A1-D2</t>
         </is>
       </c>
-      <c r="C209" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D209" s="6" t="inlineStr">
+      <c r="C209" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D209" s="5" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="E209" s="6" t="inlineStr">
+      <c r="E209" s="5" t="inlineStr">
         <is>
           <t>07/07/2026</t>
         </is>
       </c>
-      <c r="F209" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G209" s="6" t="inlineStr"/>
-      <c r="H209" s="6" t="inlineStr">
+      <c r="F209" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G209" s="5" t="inlineStr"/>
+      <c r="H209" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I209" s="6" t="inlineStr">
+      <c r="I209" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B210" s="6" t="inlineStr">
+      <c r="A210" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B210" s="5" t="inlineStr">
         <is>
           <t>A1-D2</t>
         </is>
       </c>
-      <c r="C210" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D210" s="6" t="inlineStr">
+      <c r="C210" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D210" s="5" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="E210" s="6" t="inlineStr">
+      <c r="E210" s="5" t="inlineStr">
         <is>
           <t>08/07/2026</t>
         </is>
       </c>
-      <c r="F210" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G210" s="6" t="inlineStr"/>
-      <c r="H210" s="6" t="inlineStr">
+      <c r="F210" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G210" s="5" t="inlineStr"/>
+      <c r="H210" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I210" s="6" t="inlineStr">
+      <c r="I210" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B211" s="6" t="inlineStr">
+      <c r="A211" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B211" s="5" t="inlineStr">
         <is>
           <t>A1-D2</t>
         </is>
       </c>
-      <c r="C211" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D211" s="6" t="inlineStr">
+      <c r="C211" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D211" s="5" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="E211" s="6" t="inlineStr">
+      <c r="E211" s="5" t="inlineStr">
         <is>
           <t>09/07/2026</t>
         </is>
       </c>
-      <c r="F211" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G211" s="6" t="inlineStr"/>
-      <c r="H211" s="6" t="inlineStr">
+      <c r="F211" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G211" s="5" t="inlineStr"/>
+      <c r="H211" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I211" s="6" t="inlineStr">
+      <c r="I211" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B212" s="6" t="inlineStr">
+      <c r="A212" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B212" s="5" t="inlineStr">
         <is>
           <t>A1-D2</t>
         </is>
       </c>
-      <c r="C212" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D212" s="6" t="inlineStr">
+      <c r="C212" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D212" s="5" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="E212" s="6" t="inlineStr">
+      <c r="E212" s="5" t="inlineStr">
         <is>
           <t>14/07/2026</t>
         </is>
       </c>
-      <c r="F212" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G212" s="6" t="inlineStr"/>
-      <c r="H212" s="6" t="inlineStr">
+      <c r="F212" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G212" s="5" t="inlineStr"/>
+      <c r="H212" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I212" s="6" t="inlineStr">
+      <c r="I212" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B213" s="6" t="inlineStr">
+      <c r="A213" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B213" s="5" t="inlineStr">
         <is>
           <t>A1-D2</t>
         </is>
       </c>
-      <c r="C213" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D213" s="6" t="inlineStr">
+      <c r="C213" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D213" s="5" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="E213" s="6" t="inlineStr">
+      <c r="E213" s="5" t="inlineStr">
         <is>
           <t>15/07/2026</t>
         </is>
       </c>
-      <c r="F213" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G213" s="6" t="inlineStr"/>
-      <c r="H213" s="6" t="inlineStr">
+      <c r="F213" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G213" s="5" t="inlineStr"/>
+      <c r="H213" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I213" s="6" t="inlineStr">
+      <c r="I213" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B214" s="6" t="inlineStr">
+      <c r="A214" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B214" s="5" t="inlineStr">
         <is>
           <t>A1-D2</t>
         </is>
       </c>
-      <c r="C214" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D214" s="6" t="inlineStr">
+      <c r="C214" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D214" s="5" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="E214" s="6" t="inlineStr">
+      <c r="E214" s="5" t="inlineStr">
         <is>
           <t>16/07/2026</t>
         </is>
       </c>
-      <c r="F214" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G214" s="6" t="inlineStr"/>
-      <c r="H214" s="6" t="inlineStr">
+      <c r="F214" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G214" s="5" t="inlineStr"/>
+      <c r="H214" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I214" s="6" t="inlineStr">
+      <c r="I214" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B215" s="6" t="inlineStr">
+      <c r="A215" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B215" s="5" t="inlineStr">
         <is>
           <t>A1-D2</t>
         </is>
       </c>
-      <c r="C215" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D215" s="6" t="inlineStr">
+      <c r="C215" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D215" s="5" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="E215" s="6" t="inlineStr">
+      <c r="E215" s="5" t="inlineStr">
         <is>
           <t>21/07/2026</t>
         </is>
       </c>
-      <c r="F215" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G215" s="6" t="inlineStr"/>
-      <c r="H215" s="6" t="inlineStr">
+      <c r="F215" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G215" s="5" t="inlineStr"/>
+      <c r="H215" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I215" s="6" t="inlineStr">
+      <c r="I215" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B216" s="6" t="inlineStr">
+      <c r="A216" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B216" s="5" t="inlineStr">
         <is>
           <t>A1-D2</t>
         </is>
       </c>
-      <c r="C216" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D216" s="6" t="inlineStr">
+      <c r="C216" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D216" s="5" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="E216" s="6" t="inlineStr">
+      <c r="E216" s="5" t="inlineStr">
         <is>
           <t>22/07/2026</t>
         </is>
       </c>
-      <c r="F216" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G216" s="6" t="inlineStr"/>
-      <c r="H216" s="6" t="inlineStr">
+      <c r="F216" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G216" s="5" t="inlineStr"/>
+      <c r="H216" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I216" s="6" t="inlineStr">
+      <c r="I216" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B217" s="6" t="inlineStr">
+      <c r="A217" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B217" s="5" t="inlineStr">
         <is>
           <t>A1-D2</t>
         </is>
       </c>
-      <c r="C217" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D217" s="6" t="inlineStr">
+      <c r="C217" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D217" s="5" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="E217" s="6" t="inlineStr">
+      <c r="E217" s="5" t="inlineStr">
         <is>
           <t>23/07/2026</t>
         </is>
       </c>
-      <c r="F217" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G217" s="6" t="inlineStr"/>
-      <c r="H217" s="6" t="inlineStr">
+      <c r="F217" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G217" s="5" t="inlineStr"/>
+      <c r="H217" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I217" s="6" t="inlineStr">
+      <c r="I217" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -11269,43 +11293,43 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B223" s="5" t="inlineStr">
+      <c r="A223" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B223" s="9" t="inlineStr">
         <is>
           <t>A1-E1</t>
         </is>
       </c>
-      <c r="C223" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D223" s="5" t="inlineStr">
+      <c r="C223" s="9" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D223" s="9" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E223" s="5" t="inlineStr">
+      <c r="E223" s="9" t="inlineStr">
         <is>
           <t>04/06/2026</t>
         </is>
       </c>
-      <c r="F223" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G223" s="5" t="inlineStr"/>
-      <c r="H223" s="5" t="inlineStr">
+      <c r="F223" s="9" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G223" s="9" t="inlineStr"/>
+      <c r="H223" s="9" t="inlineStr">
         <is>
           <t>0/38</t>
         </is>
       </c>
-      <c r="I223" s="5" t="inlineStr">
+      <c r="I223" s="9" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
@@ -11876,387 +11900,387 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B236" s="6" t="inlineStr">
+      <c r="A236" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B236" s="5" t="inlineStr">
         <is>
           <t>A1-E1</t>
         </is>
       </c>
-      <c r="C236" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D236" s="6" t="inlineStr">
+      <c r="C236" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D236" s="5" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="E236" s="6" t="inlineStr">
+      <c r="E236" s="5" t="inlineStr">
         <is>
           <t>07/07/2026</t>
         </is>
       </c>
-      <c r="F236" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G236" s="6" t="inlineStr"/>
-      <c r="H236" s="6" t="inlineStr">
+      <c r="F236" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G236" s="5" t="inlineStr"/>
+      <c r="H236" s="5" t="inlineStr">
         <is>
           <t>0/38</t>
         </is>
       </c>
-      <c r="I236" s="6" t="inlineStr">
+      <c r="I236" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B237" s="6" t="inlineStr">
+      <c r="A237" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B237" s="5" t="inlineStr">
         <is>
           <t>A1-E1</t>
         </is>
       </c>
-      <c r="C237" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D237" s="6" t="inlineStr">
+      <c r="C237" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D237" s="5" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="E237" s="6" t="inlineStr">
+      <c r="E237" s="5" t="inlineStr">
         <is>
           <t>08/07/2026</t>
         </is>
       </c>
-      <c r="F237" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G237" s="6" t="inlineStr"/>
-      <c r="H237" s="6" t="inlineStr">
+      <c r="F237" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G237" s="5" t="inlineStr"/>
+      <c r="H237" s="5" t="inlineStr">
         <is>
           <t>0/38</t>
         </is>
       </c>
-      <c r="I237" s="6" t="inlineStr">
+      <c r="I237" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B238" s="6" t="inlineStr">
+      <c r="A238" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B238" s="5" t="inlineStr">
         <is>
           <t>A1-E1</t>
         </is>
       </c>
-      <c r="C238" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D238" s="6" t="inlineStr">
+      <c r="C238" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D238" s="5" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="E238" s="6" t="inlineStr">
+      <c r="E238" s="5" t="inlineStr">
         <is>
           <t>09/07/2026</t>
         </is>
       </c>
-      <c r="F238" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G238" s="6" t="inlineStr"/>
-      <c r="H238" s="6" t="inlineStr">
+      <c r="F238" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G238" s="5" t="inlineStr"/>
+      <c r="H238" s="5" t="inlineStr">
         <is>
           <t>0/38</t>
         </is>
       </c>
-      <c r="I238" s="6" t="inlineStr">
+      <c r="I238" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B239" s="6" t="inlineStr">
+      <c r="A239" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B239" s="5" t="inlineStr">
         <is>
           <t>A1-E1</t>
         </is>
       </c>
-      <c r="C239" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D239" s="6" t="inlineStr">
+      <c r="C239" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D239" s="5" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="E239" s="6" t="inlineStr">
+      <c r="E239" s="5" t="inlineStr">
         <is>
           <t>14/07/2026</t>
         </is>
       </c>
-      <c r="F239" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G239" s="6" t="inlineStr"/>
-      <c r="H239" s="6" t="inlineStr">
+      <c r="F239" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G239" s="5" t="inlineStr"/>
+      <c r="H239" s="5" t="inlineStr">
         <is>
           <t>0/38</t>
         </is>
       </c>
-      <c r="I239" s="6" t="inlineStr">
+      <c r="I239" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B240" s="6" t="inlineStr">
+      <c r="A240" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B240" s="5" t="inlineStr">
         <is>
           <t>A1-E1</t>
         </is>
       </c>
-      <c r="C240" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D240" s="6" t="inlineStr">
+      <c r="C240" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D240" s="5" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="E240" s="6" t="inlineStr">
+      <c r="E240" s="5" t="inlineStr">
         <is>
           <t>15/07/2026</t>
         </is>
       </c>
-      <c r="F240" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G240" s="6" t="inlineStr"/>
-      <c r="H240" s="6" t="inlineStr">
+      <c r="F240" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G240" s="5" t="inlineStr"/>
+      <c r="H240" s="5" t="inlineStr">
         <is>
           <t>0/38</t>
         </is>
       </c>
-      <c r="I240" s="6" t="inlineStr">
+      <c r="I240" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B241" s="6" t="inlineStr">
+      <c r="A241" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B241" s="5" t="inlineStr">
         <is>
           <t>A1-E1</t>
         </is>
       </c>
-      <c r="C241" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D241" s="6" t="inlineStr">
+      <c r="C241" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D241" s="5" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="E241" s="6" t="inlineStr">
+      <c r="E241" s="5" t="inlineStr">
         <is>
           <t>16/07/2026</t>
         </is>
       </c>
-      <c r="F241" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G241" s="6" t="inlineStr"/>
-      <c r="H241" s="6" t="inlineStr">
+      <c r="F241" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G241" s="5" t="inlineStr"/>
+      <c r="H241" s="5" t="inlineStr">
         <is>
           <t>0/38</t>
         </is>
       </c>
-      <c r="I241" s="6" t="inlineStr">
+      <c r="I241" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B242" s="6" t="inlineStr">
+      <c r="A242" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B242" s="5" t="inlineStr">
         <is>
           <t>A1-E1</t>
         </is>
       </c>
-      <c r="C242" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D242" s="6" t="inlineStr">
+      <c r="C242" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D242" s="5" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="E242" s="6" t="inlineStr">
+      <c r="E242" s="5" t="inlineStr">
         <is>
           <t>21/07/2026</t>
         </is>
       </c>
-      <c r="F242" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G242" s="6" t="inlineStr"/>
-      <c r="H242" s="6" t="inlineStr">
+      <c r="F242" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G242" s="5" t="inlineStr"/>
+      <c r="H242" s="5" t="inlineStr">
         <is>
           <t>0/38</t>
         </is>
       </c>
-      <c r="I242" s="6" t="inlineStr">
+      <c r="I242" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B243" s="6" t="inlineStr">
+      <c r="A243" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B243" s="5" t="inlineStr">
         <is>
           <t>A1-E1</t>
         </is>
       </c>
-      <c r="C243" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D243" s="6" t="inlineStr">
+      <c r="C243" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D243" s="5" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="E243" s="6" t="inlineStr">
+      <c r="E243" s="5" t="inlineStr">
         <is>
           <t>22/07/2026</t>
         </is>
       </c>
-      <c r="F243" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G243" s="6" t="inlineStr"/>
-      <c r="H243" s="6" t="inlineStr">
+      <c r="F243" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G243" s="5" t="inlineStr"/>
+      <c r="H243" s="5" t="inlineStr">
         <is>
           <t>0/38</t>
         </is>
       </c>
-      <c r="I243" s="6" t="inlineStr">
+      <c r="I243" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B244" s="6" t="inlineStr">
+      <c r="A244" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B244" s="5" t="inlineStr">
         <is>
           <t>A1-E1</t>
         </is>
       </c>
-      <c r="C244" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D244" s="6" t="inlineStr">
+      <c r="C244" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D244" s="5" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="E244" s="6" t="inlineStr">
+      <c r="E244" s="5" t="inlineStr">
         <is>
           <t>23/07/2026</t>
         </is>
       </c>
-      <c r="F244" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G244" s="6" t="inlineStr"/>
-      <c r="H244" s="6" t="inlineStr">
+      <c r="F244" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G244" s="5" t="inlineStr"/>
+      <c r="H244" s="5" t="inlineStr">
         <is>
           <t>0/38</t>
         </is>
       </c>
-      <c r="I244" s="6" t="inlineStr">
+      <c r="I244" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -12498,43 +12522,43 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B250" s="5" t="inlineStr">
+      <c r="A250" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B250" s="9" t="inlineStr">
         <is>
           <t>A1-E2</t>
         </is>
       </c>
-      <c r="C250" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D250" s="5" t="inlineStr">
+      <c r="C250" s="9" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D250" s="9" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E250" s="5" t="inlineStr">
+      <c r="E250" s="9" t="inlineStr">
         <is>
           <t>04/06/2026</t>
         </is>
       </c>
-      <c r="F250" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G250" s="5" t="inlineStr"/>
-      <c r="H250" s="5" t="inlineStr">
+      <c r="F250" s="9" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G250" s="9" t="inlineStr"/>
+      <c r="H250" s="9" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I250" s="5" t="inlineStr">
+      <c r="I250" s="9" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
@@ -13105,387 +13129,387 @@
       </c>
     </row>
     <row r="263">
-      <c r="A263" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B263" s="6" t="inlineStr">
+      <c r="A263" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B263" s="5" t="inlineStr">
         <is>
           <t>A1-E2</t>
         </is>
       </c>
-      <c r="C263" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D263" s="6" t="inlineStr">
+      <c r="C263" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D263" s="5" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="E263" s="6" t="inlineStr">
+      <c r="E263" s="5" t="inlineStr">
         <is>
           <t>07/07/2026</t>
         </is>
       </c>
-      <c r="F263" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G263" s="6" t="inlineStr"/>
-      <c r="H263" s="6" t="inlineStr">
+      <c r="F263" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G263" s="5" t="inlineStr"/>
+      <c r="H263" s="5" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I263" s="6" t="inlineStr">
+      <c r="I263" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="264">
-      <c r="A264" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B264" s="6" t="inlineStr">
+      <c r="A264" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B264" s="5" t="inlineStr">
         <is>
           <t>A1-E2</t>
         </is>
       </c>
-      <c r="C264" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D264" s="6" t="inlineStr">
+      <c r="C264" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D264" s="5" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="E264" s="6" t="inlineStr">
+      <c r="E264" s="5" t="inlineStr">
         <is>
           <t>08/07/2026</t>
         </is>
       </c>
-      <c r="F264" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G264" s="6" t="inlineStr"/>
-      <c r="H264" s="6" t="inlineStr">
+      <c r="F264" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G264" s="5" t="inlineStr"/>
+      <c r="H264" s="5" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I264" s="6" t="inlineStr">
+      <c r="I264" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="265">
-      <c r="A265" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B265" s="6" t="inlineStr">
+      <c r="A265" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B265" s="5" t="inlineStr">
         <is>
           <t>A1-E2</t>
         </is>
       </c>
-      <c r="C265" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D265" s="6" t="inlineStr">
+      <c r="C265" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D265" s="5" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="E265" s="6" t="inlineStr">
+      <c r="E265" s="5" t="inlineStr">
         <is>
           <t>09/07/2026</t>
         </is>
       </c>
-      <c r="F265" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G265" s="6" t="inlineStr"/>
-      <c r="H265" s="6" t="inlineStr">
+      <c r="F265" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G265" s="5" t="inlineStr"/>
+      <c r="H265" s="5" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I265" s="6" t="inlineStr">
+      <c r="I265" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="266">
-      <c r="A266" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B266" s="6" t="inlineStr">
+      <c r="A266" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B266" s="5" t="inlineStr">
         <is>
           <t>A1-E2</t>
         </is>
       </c>
-      <c r="C266" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D266" s="6" t="inlineStr">
+      <c r="C266" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D266" s="5" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="E266" s="6" t="inlineStr">
+      <c r="E266" s="5" t="inlineStr">
         <is>
           <t>14/07/2026</t>
         </is>
       </c>
-      <c r="F266" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G266" s="6" t="inlineStr"/>
-      <c r="H266" s="6" t="inlineStr">
+      <c r="F266" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G266" s="5" t="inlineStr"/>
+      <c r="H266" s="5" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I266" s="6" t="inlineStr">
+      <c r="I266" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="267">
-      <c r="A267" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B267" s="6" t="inlineStr">
+      <c r="A267" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B267" s="5" t="inlineStr">
         <is>
           <t>A1-E2</t>
         </is>
       </c>
-      <c r="C267" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D267" s="6" t="inlineStr">
+      <c r="C267" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D267" s="5" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="E267" s="6" t="inlineStr">
+      <c r="E267" s="5" t="inlineStr">
         <is>
           <t>15/07/2026</t>
         </is>
       </c>
-      <c r="F267" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G267" s="6" t="inlineStr"/>
-      <c r="H267" s="6" t="inlineStr">
+      <c r="F267" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G267" s="5" t="inlineStr"/>
+      <c r="H267" s="5" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I267" s="6" t="inlineStr">
+      <c r="I267" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="268">
-      <c r="A268" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B268" s="6" t="inlineStr">
+      <c r="A268" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B268" s="5" t="inlineStr">
         <is>
           <t>A1-E2</t>
         </is>
       </c>
-      <c r="C268" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D268" s="6" t="inlineStr">
+      <c r="C268" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D268" s="5" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="E268" s="6" t="inlineStr">
+      <c r="E268" s="5" t="inlineStr">
         <is>
           <t>16/07/2026</t>
         </is>
       </c>
-      <c r="F268" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G268" s="6" t="inlineStr"/>
-      <c r="H268" s="6" t="inlineStr">
+      <c r="F268" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G268" s="5" t="inlineStr"/>
+      <c r="H268" s="5" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I268" s="6" t="inlineStr">
+      <c r="I268" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="269">
-      <c r="A269" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B269" s="6" t="inlineStr">
+      <c r="A269" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B269" s="5" t="inlineStr">
         <is>
           <t>A1-E2</t>
         </is>
       </c>
-      <c r="C269" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D269" s="6" t="inlineStr">
+      <c r="C269" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D269" s="5" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="E269" s="6" t="inlineStr">
+      <c r="E269" s="5" t="inlineStr">
         <is>
           <t>21/07/2026</t>
         </is>
       </c>
-      <c r="F269" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G269" s="6" t="inlineStr"/>
-      <c r="H269" s="6" t="inlineStr">
+      <c r="F269" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G269" s="5" t="inlineStr"/>
+      <c r="H269" s="5" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I269" s="6" t="inlineStr">
+      <c r="I269" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="270">
-      <c r="A270" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B270" s="6" t="inlineStr">
+      <c r="A270" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B270" s="5" t="inlineStr">
         <is>
           <t>A1-E2</t>
         </is>
       </c>
-      <c r="C270" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D270" s="6" t="inlineStr">
+      <c r="C270" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D270" s="5" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="E270" s="6" t="inlineStr">
+      <c r="E270" s="5" t="inlineStr">
         <is>
           <t>22/07/2026</t>
         </is>
       </c>
-      <c r="F270" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G270" s="6" t="inlineStr"/>
-      <c r="H270" s="6" t="inlineStr">
+      <c r="F270" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G270" s="5" t="inlineStr"/>
+      <c r="H270" s="5" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I270" s="6" t="inlineStr">
+      <c r="I270" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="271">
-      <c r="A271" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B271" s="6" t="inlineStr">
+      <c r="A271" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B271" s="5" t="inlineStr">
         <is>
           <t>A1-E2</t>
         </is>
       </c>
-      <c r="C271" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D271" s="6" t="inlineStr">
+      <c r="C271" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D271" s="5" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="E271" s="6" t="inlineStr">
+      <c r="E271" s="5" t="inlineStr">
         <is>
           <t>23/07/2026</t>
         </is>
       </c>
-      <c r="F271" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G271" s="6" t="inlineStr"/>
-      <c r="H271" s="6" t="inlineStr">
+      <c r="F271" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G271" s="5" t="inlineStr"/>
+      <c r="H271" s="5" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I271" s="6" t="inlineStr">
+      <c r="I271" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -13727,43 +13751,43 @@
       </c>
     </row>
     <row r="277">
-      <c r="A277" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B277" s="5" t="inlineStr">
+      <c r="A277" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B277" s="9" t="inlineStr">
         <is>
           <t>A1-F1</t>
         </is>
       </c>
-      <c r="C277" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D277" s="5" t="inlineStr">
+      <c r="C277" s="9" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D277" s="9" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E277" s="5" t="inlineStr">
+      <c r="E277" s="9" t="inlineStr">
         <is>
           <t>04/06/2026</t>
         </is>
       </c>
-      <c r="F277" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G277" s="5" t="inlineStr"/>
-      <c r="H277" s="5" t="inlineStr">
+      <c r="F277" s="9" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G277" s="9" t="inlineStr"/>
+      <c r="H277" s="9" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I277" s="5" t="inlineStr">
+      <c r="I277" s="9" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
@@ -14334,387 +14358,387 @@
       </c>
     </row>
     <row r="290">
-      <c r="A290" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B290" s="6" t="inlineStr">
+      <c r="A290" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B290" s="5" t="inlineStr">
         <is>
           <t>A1-F1</t>
         </is>
       </c>
-      <c r="C290" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D290" s="6" t="inlineStr">
+      <c r="C290" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D290" s="5" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="E290" s="6" t="inlineStr">
+      <c r="E290" s="5" t="inlineStr">
         <is>
           <t>07/07/2026</t>
         </is>
       </c>
-      <c r="F290" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G290" s="6" t="inlineStr"/>
-      <c r="H290" s="6" t="inlineStr">
+      <c r="F290" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G290" s="5" t="inlineStr"/>
+      <c r="H290" s="5" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I290" s="6" t="inlineStr">
+      <c r="I290" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="291">
-      <c r="A291" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B291" s="6" t="inlineStr">
+      <c r="A291" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B291" s="5" t="inlineStr">
         <is>
           <t>A1-F1</t>
         </is>
       </c>
-      <c r="C291" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D291" s="6" t="inlineStr">
+      <c r="C291" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D291" s="5" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="E291" s="6" t="inlineStr">
+      <c r="E291" s="5" t="inlineStr">
         <is>
           <t>08/07/2026</t>
         </is>
       </c>
-      <c r="F291" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G291" s="6" t="inlineStr"/>
-      <c r="H291" s="6" t="inlineStr">
+      <c r="F291" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G291" s="5" t="inlineStr"/>
+      <c r="H291" s="5" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I291" s="6" t="inlineStr">
+      <c r="I291" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="292">
-      <c r="A292" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B292" s="6" t="inlineStr">
+      <c r="A292" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B292" s="5" t="inlineStr">
         <is>
           <t>A1-F1</t>
         </is>
       </c>
-      <c r="C292" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D292" s="6" t="inlineStr">
+      <c r="C292" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D292" s="5" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="E292" s="6" t="inlineStr">
+      <c r="E292" s="5" t="inlineStr">
         <is>
           <t>09/07/2026</t>
         </is>
       </c>
-      <c r="F292" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G292" s="6" t="inlineStr"/>
-      <c r="H292" s="6" t="inlineStr">
+      <c r="F292" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G292" s="5" t="inlineStr"/>
+      <c r="H292" s="5" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I292" s="6" t="inlineStr">
+      <c r="I292" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="293">
-      <c r="A293" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B293" s="6" t="inlineStr">
+      <c r="A293" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B293" s="5" t="inlineStr">
         <is>
           <t>A1-F1</t>
         </is>
       </c>
-      <c r="C293" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D293" s="6" t="inlineStr">
+      <c r="C293" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D293" s="5" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="E293" s="6" t="inlineStr">
+      <c r="E293" s="5" t="inlineStr">
         <is>
           <t>14/07/2026</t>
         </is>
       </c>
-      <c r="F293" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G293" s="6" t="inlineStr"/>
-      <c r="H293" s="6" t="inlineStr">
+      <c r="F293" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G293" s="5" t="inlineStr"/>
+      <c r="H293" s="5" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I293" s="6" t="inlineStr">
+      <c r="I293" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="294">
-      <c r="A294" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B294" s="6" t="inlineStr">
+      <c r="A294" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B294" s="5" t="inlineStr">
         <is>
           <t>A1-F1</t>
         </is>
       </c>
-      <c r="C294" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D294" s="6" t="inlineStr">
+      <c r="C294" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D294" s="5" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="E294" s="6" t="inlineStr">
+      <c r="E294" s="5" t="inlineStr">
         <is>
           <t>15/07/2026</t>
         </is>
       </c>
-      <c r="F294" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G294" s="6" t="inlineStr"/>
-      <c r="H294" s="6" t="inlineStr">
+      <c r="F294" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G294" s="5" t="inlineStr"/>
+      <c r="H294" s="5" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I294" s="6" t="inlineStr">
+      <c r="I294" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="295">
-      <c r="A295" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B295" s="6" t="inlineStr">
+      <c r="A295" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B295" s="5" t="inlineStr">
         <is>
           <t>A1-F1</t>
         </is>
       </c>
-      <c r="C295" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D295" s="6" t="inlineStr">
+      <c r="C295" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D295" s="5" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="E295" s="6" t="inlineStr">
+      <c r="E295" s="5" t="inlineStr">
         <is>
           <t>16/07/2026</t>
         </is>
       </c>
-      <c r="F295" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G295" s="6" t="inlineStr"/>
-      <c r="H295" s="6" t="inlineStr">
+      <c r="F295" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G295" s="5" t="inlineStr"/>
+      <c r="H295" s="5" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I295" s="6" t="inlineStr">
+      <c r="I295" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="296">
-      <c r="A296" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B296" s="6" t="inlineStr">
+      <c r="A296" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B296" s="5" t="inlineStr">
         <is>
           <t>A1-F1</t>
         </is>
       </c>
-      <c r="C296" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D296" s="6" t="inlineStr">
+      <c r="C296" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D296" s="5" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="E296" s="6" t="inlineStr">
+      <c r="E296" s="5" t="inlineStr">
         <is>
           <t>21/07/2026</t>
         </is>
       </c>
-      <c r="F296" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G296" s="6" t="inlineStr"/>
-      <c r="H296" s="6" t="inlineStr">
+      <c r="F296" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G296" s="5" t="inlineStr"/>
+      <c r="H296" s="5" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I296" s="6" t="inlineStr">
+      <c r="I296" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="297">
-      <c r="A297" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B297" s="6" t="inlineStr">
+      <c r="A297" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B297" s="5" t="inlineStr">
         <is>
           <t>A1-F1</t>
         </is>
       </c>
-      <c r="C297" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D297" s="6" t="inlineStr">
+      <c r="C297" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D297" s="5" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="E297" s="6" t="inlineStr">
+      <c r="E297" s="5" t="inlineStr">
         <is>
           <t>22/07/2026</t>
         </is>
       </c>
-      <c r="F297" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G297" s="6" t="inlineStr"/>
-      <c r="H297" s="6" t="inlineStr">
+      <c r="F297" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G297" s="5" t="inlineStr"/>
+      <c r="H297" s="5" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I297" s="6" t="inlineStr">
+      <c r="I297" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="298">
-      <c r="A298" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B298" s="6" t="inlineStr">
+      <c r="A298" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B298" s="5" t="inlineStr">
         <is>
           <t>A1-F1</t>
         </is>
       </c>
-      <c r="C298" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D298" s="6" t="inlineStr">
+      <c r="C298" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D298" s="5" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="E298" s="6" t="inlineStr">
+      <c r="E298" s="5" t="inlineStr">
         <is>
           <t>23/07/2026</t>
         </is>
       </c>
-      <c r="F298" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G298" s="6" t="inlineStr"/>
-      <c r="H298" s="6" t="inlineStr">
+      <c r="F298" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G298" s="5" t="inlineStr"/>
+      <c r="H298" s="5" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I298" s="6" t="inlineStr">
+      <c r="I298" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -14956,43 +14980,43 @@
       </c>
     </row>
     <row r="304">
-      <c r="A304" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B304" s="5" t="inlineStr">
+      <c r="A304" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B304" s="9" t="inlineStr">
         <is>
           <t>A1-F2</t>
         </is>
       </c>
-      <c r="C304" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D304" s="5" t="inlineStr">
+      <c r="C304" s="9" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D304" s="9" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E304" s="5" t="inlineStr">
+      <c r="E304" s="9" t="inlineStr">
         <is>
           <t>04/06/2026</t>
         </is>
       </c>
-      <c r="F304" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G304" s="5" t="inlineStr"/>
-      <c r="H304" s="5" t="inlineStr">
+      <c r="F304" s="9" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G304" s="9" t="inlineStr"/>
+      <c r="H304" s="9" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I304" s="5" t="inlineStr">
+      <c r="I304" s="9" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
@@ -15563,387 +15587,387 @@
       </c>
     </row>
     <row r="317">
-      <c r="A317" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B317" s="6" t="inlineStr">
+      <c r="A317" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B317" s="5" t="inlineStr">
         <is>
           <t>A1-F2</t>
         </is>
       </c>
-      <c r="C317" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D317" s="6" t="inlineStr">
+      <c r="C317" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D317" s="5" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="E317" s="6" t="inlineStr">
+      <c r="E317" s="5" t="inlineStr">
         <is>
           <t>07/07/2026</t>
         </is>
       </c>
-      <c r="F317" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G317" s="6" t="inlineStr"/>
-      <c r="H317" s="6" t="inlineStr">
+      <c r="F317" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G317" s="5" t="inlineStr"/>
+      <c r="H317" s="5" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I317" s="6" t="inlineStr">
+      <c r="I317" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="318">
-      <c r="A318" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B318" s="6" t="inlineStr">
+      <c r="A318" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B318" s="5" t="inlineStr">
         <is>
           <t>A1-F2</t>
         </is>
       </c>
-      <c r="C318" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D318" s="6" t="inlineStr">
+      <c r="C318" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D318" s="5" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="E318" s="6" t="inlineStr">
+      <c r="E318" s="5" t="inlineStr">
         <is>
           <t>08/07/2026</t>
         </is>
       </c>
-      <c r="F318" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G318" s="6" t="inlineStr"/>
-      <c r="H318" s="6" t="inlineStr">
+      <c r="F318" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G318" s="5" t="inlineStr"/>
+      <c r="H318" s="5" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I318" s="6" t="inlineStr">
+      <c r="I318" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="319">
-      <c r="A319" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B319" s="6" t="inlineStr">
+      <c r="A319" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B319" s="5" t="inlineStr">
         <is>
           <t>A1-F2</t>
         </is>
       </c>
-      <c r="C319" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D319" s="6" t="inlineStr">
+      <c r="C319" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D319" s="5" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="E319" s="6" t="inlineStr">
+      <c r="E319" s="5" t="inlineStr">
         <is>
           <t>09/07/2026</t>
         </is>
       </c>
-      <c r="F319" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G319" s="6" t="inlineStr"/>
-      <c r="H319" s="6" t="inlineStr">
+      <c r="F319" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G319" s="5" t="inlineStr"/>
+      <c r="H319" s="5" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I319" s="6" t="inlineStr">
+      <c r="I319" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="320">
-      <c r="A320" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B320" s="6" t="inlineStr">
+      <c r="A320" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B320" s="5" t="inlineStr">
         <is>
           <t>A1-F2</t>
         </is>
       </c>
-      <c r="C320" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D320" s="6" t="inlineStr">
+      <c r="C320" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D320" s="5" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="E320" s="6" t="inlineStr">
+      <c r="E320" s="5" t="inlineStr">
         <is>
           <t>14/07/2026</t>
         </is>
       </c>
-      <c r="F320" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G320" s="6" t="inlineStr"/>
-      <c r="H320" s="6" t="inlineStr">
+      <c r="F320" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G320" s="5" t="inlineStr"/>
+      <c r="H320" s="5" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I320" s="6" t="inlineStr">
+      <c r="I320" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="321">
-      <c r="A321" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B321" s="6" t="inlineStr">
+      <c r="A321" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B321" s="5" t="inlineStr">
         <is>
           <t>A1-F2</t>
         </is>
       </c>
-      <c r="C321" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D321" s="6" t="inlineStr">
+      <c r="C321" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D321" s="5" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="E321" s="6" t="inlineStr">
+      <c r="E321" s="5" t="inlineStr">
         <is>
           <t>15/07/2026</t>
         </is>
       </c>
-      <c r="F321" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G321" s="6" t="inlineStr"/>
-      <c r="H321" s="6" t="inlineStr">
+      <c r="F321" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G321" s="5" t="inlineStr"/>
+      <c r="H321" s="5" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I321" s="6" t="inlineStr">
+      <c r="I321" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="322">
-      <c r="A322" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B322" s="6" t="inlineStr">
+      <c r="A322" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B322" s="5" t="inlineStr">
         <is>
           <t>A1-F2</t>
         </is>
       </c>
-      <c r="C322" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D322" s="6" t="inlineStr">
+      <c r="C322" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D322" s="5" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="E322" s="6" t="inlineStr">
+      <c r="E322" s="5" t="inlineStr">
         <is>
           <t>16/07/2026</t>
         </is>
       </c>
-      <c r="F322" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G322" s="6" t="inlineStr"/>
-      <c r="H322" s="6" t="inlineStr">
+      <c r="F322" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G322" s="5" t="inlineStr"/>
+      <c r="H322" s="5" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I322" s="6" t="inlineStr">
+      <c r="I322" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="323">
-      <c r="A323" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B323" s="6" t="inlineStr">
+      <c r="A323" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B323" s="5" t="inlineStr">
         <is>
           <t>A1-F2</t>
         </is>
       </c>
-      <c r="C323" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D323" s="6" t="inlineStr">
+      <c r="C323" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D323" s="5" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="E323" s="6" t="inlineStr">
+      <c r="E323" s="5" t="inlineStr">
         <is>
           <t>21/07/2026</t>
         </is>
       </c>
-      <c r="F323" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G323" s="6" t="inlineStr"/>
-      <c r="H323" s="6" t="inlineStr">
+      <c r="F323" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G323" s="5" t="inlineStr"/>
+      <c r="H323" s="5" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I323" s="6" t="inlineStr">
+      <c r="I323" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="324">
-      <c r="A324" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B324" s="6" t="inlineStr">
+      <c r="A324" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B324" s="5" t="inlineStr">
         <is>
           <t>A1-F2</t>
         </is>
       </c>
-      <c r="C324" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D324" s="6" t="inlineStr">
+      <c r="C324" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D324" s="5" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="E324" s="6" t="inlineStr">
+      <c r="E324" s="5" t="inlineStr">
         <is>
           <t>22/07/2026</t>
         </is>
       </c>
-      <c r="F324" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G324" s="6" t="inlineStr"/>
-      <c r="H324" s="6" t="inlineStr">
+      <c r="F324" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G324" s="5" t="inlineStr"/>
+      <c r="H324" s="5" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I324" s="6" t="inlineStr">
+      <c r="I324" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="325">
-      <c r="A325" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B325" s="6" t="inlineStr">
+      <c r="A325" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B325" s="5" t="inlineStr">
         <is>
           <t>A1-F2</t>
         </is>
       </c>
-      <c r="C325" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D325" s="6" t="inlineStr">
+      <c r="C325" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D325" s="5" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="E325" s="6" t="inlineStr">
+      <c r="E325" s="5" t="inlineStr">
         <is>
           <t>23/07/2026</t>
         </is>
       </c>
-      <c r="F325" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G325" s="6" t="inlineStr"/>
-      <c r="H325" s="6" t="inlineStr">
+      <c r="F325" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G325" s="5" t="inlineStr"/>
+      <c r="H325" s="5" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I325" s="6" t="inlineStr">
+      <c r="I325" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A1_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A1_session_analysis.xlsx
@@ -814,7 +814,7 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>222</v>
+        <v>228</v>
       </c>
     </row>
     <row r="7">
@@ -924,7 +924,7 @@
         </is>
       </c>
       <c r="L8" s="4" t="n">
-        <v>96</v>
+        <v>90</v>
       </c>
     </row>
     <row r="9">
@@ -980,7 +980,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>68.5%</t>
+          <t>70.4%</t>
         </is>
       </c>
     </row>
@@ -1037,7 +1037,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>76.4%</t>
+          <t>75.8%</t>
         </is>
       </c>
     </row>
@@ -1342,22 +1342,22 @@
         <v>27</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P15" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R15" s="4" t="inlineStr">
         <is>
-          <t>74.1%</t>
+          <t>77.8%</t>
         </is>
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>71.2%</t>
+          <t>71.4%</t>
         </is>
       </c>
     </row>
@@ -1424,22 +1424,22 @@
         <v>27</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P16" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R16" s="4" t="inlineStr">
         <is>
-          <t>74.1%</t>
+          <t>77.8%</t>
         </is>
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>72.4%</t>
+          <t>72.0%</t>
         </is>
       </c>
     </row>
@@ -1506,22 +1506,22 @@
         <v>27</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P17" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R17" s="4" t="inlineStr">
         <is>
-          <t>74.1%</t>
+          <t>77.8%</t>
         </is>
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>81.0%</t>
+          <t>77.6%</t>
         </is>
       </c>
     </row>
@@ -1588,22 +1588,22 @@
         <v>27</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P18" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R18" s="4" t="inlineStr">
         <is>
-          <t>74.1%</t>
+          <t>77.8%</t>
         </is>
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>78.7%</t>
+          <t>75.4%</t>
         </is>
       </c>
     </row>
@@ -1670,22 +1670,22 @@
         <v>27</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P19" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R19" s="4" t="inlineStr">
         <is>
-          <t>74.1%</t>
+          <t>77.8%</t>
         </is>
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>77.4%</t>
+          <t>78.2%</t>
         </is>
       </c>
     </row>
@@ -1752,22 +1752,22 @@
         <v>27</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P20" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R20" s="4" t="inlineStr">
         <is>
-          <t>74.1%</t>
+          <t>77.8%</t>
         </is>
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>69.7%</t>
+          <t>70.6%</t>
         </is>
       </c>
     </row>
@@ -1854,45 +1854,49 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="inlineStr">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>A1-A1</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="E22" s="5" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>06/07/2026</t>
         </is>
       </c>
-      <c r="F22" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G22" s="5" t="inlineStr"/>
-      <c r="H22" s="5" t="inlineStr">
-        <is>
-          <t>0/34</t>
-        </is>
-      </c>
-      <c r="I22" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>26/34</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
       <c r="K22" s="4" t="inlineStr">
@@ -3335,45 +3339,49 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B49" s="5" t="inlineStr">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
         <is>
           <t>A1-A2</t>
         </is>
       </c>
-      <c r="C49" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D49" s="5" t="inlineStr">
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="E49" s="5" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>06/07/2026</t>
         </is>
       </c>
-      <c r="F49" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G49" s="5" t="inlineStr"/>
-      <c r="H49" s="5" t="inlineStr">
-        <is>
-          <t>0/33</t>
-        </is>
-      </c>
-      <c r="I49" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>21/33</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -4576,45 +4584,49 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B76" s="5" t="inlineStr">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
         <is>
           <t>A1-B1</t>
         </is>
       </c>
-      <c r="C76" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D76" s="5" t="inlineStr">
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="E76" s="5" t="inlineStr">
+      <c r="E76" s="2" t="inlineStr">
         <is>
           <t>06/07/2026</t>
         </is>
       </c>
-      <c r="F76" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G76" s="5" t="inlineStr"/>
-      <c r="H76" s="5" t="inlineStr">
-        <is>
-          <t>0/34</t>
-        </is>
-      </c>
-      <c r="I76" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>3/34</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -5817,45 +5829,49 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B103" s="5" t="inlineStr">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
         <is>
           <t>A1-B2</t>
         </is>
       </c>
-      <c r="C103" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D103" s="5" t="inlineStr">
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="E103" s="5" t="inlineStr">
+      <c r="E103" s="2" t="inlineStr">
         <is>
           <t>06/07/2026</t>
         </is>
       </c>
-      <c r="F103" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G103" s="5" t="inlineStr"/>
-      <c r="H103" s="5" t="inlineStr">
-        <is>
-          <t>0/34</t>
-        </is>
-      </c>
-      <c r="I103" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>3/34</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -7058,45 +7074,49 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B130" s="5" t="inlineStr">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
         <is>
           <t>A1-C1</t>
         </is>
       </c>
-      <c r="C130" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D130" s="5" t="inlineStr">
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="E130" s="5" t="inlineStr">
+      <c r="E130" s="2" t="inlineStr">
         <is>
           <t>06/07/2026</t>
         </is>
       </c>
-      <c r="F130" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G130" s="5" t="inlineStr"/>
-      <c r="H130" s="5" t="inlineStr">
-        <is>
-          <t>0/34</t>
-        </is>
-      </c>
-      <c r="I130" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G130" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H130" s="2" t="inlineStr">
+        <is>
+          <t>32/34</t>
+        </is>
+      </c>
+      <c r="I130" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -8299,45 +8319,49 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B157" s="5" t="inlineStr">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
         <is>
           <t>A1-C2</t>
         </is>
       </c>
-      <c r="C157" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D157" s="5" t="inlineStr">
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="E157" s="5" t="inlineStr">
+      <c r="E157" s="2" t="inlineStr">
         <is>
           <t>06/07/2026</t>
         </is>
       </c>
-      <c r="F157" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G157" s="5" t="inlineStr"/>
-      <c r="H157" s="5" t="inlineStr">
-        <is>
-          <t>0/33</t>
-        </is>
-      </c>
-      <c r="I157" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F157" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G157" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H157" s="2" t="inlineStr">
+        <is>
+          <t>29/33</t>
+        </is>
+      </c>
+      <c r="I157" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A1_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A1_session_analysis.xlsx
@@ -814,7 +814,7 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>228</v>
+        <v>233</v>
       </c>
     </row>
     <row r="7">
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
@@ -924,7 +924,7 @@
         </is>
       </c>
       <c r="L8" s="4" t="n">
-        <v>90</v>
+        <v>84</v>
       </c>
     </row>
     <row r="9">
@@ -980,7 +980,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>70.4%</t>
+          <t>71.9%</t>
         </is>
       </c>
     </row>
@@ -1037,7 +1037,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>75.8%</t>
+          <t>75.7%</t>
         </is>
       </c>
     </row>
@@ -1834,22 +1834,22 @@
         <v>27</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="P21" s="4" t="n">
         <v>1</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R21" s="4" t="inlineStr">
         <is>
-          <t>63.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>75.6%</t>
+          <t>76.0%</t>
         </is>
       </c>
     </row>
@@ -1916,22 +1916,22 @@
         <v>27</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="P22" s="4" t="n">
         <v>1</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R22" s="4" t="inlineStr">
         <is>
-          <t>63.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>79.2%</t>
+          <t>80.2%</t>
         </is>
       </c>
     </row>
@@ -1994,22 +1994,22 @@
         <v>27</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="P23" s="4" t="n">
         <v>1</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R23" s="4" t="inlineStr">
         <is>
-          <t>63.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>78.6%</t>
+          <t>78.7%</t>
         </is>
       </c>
     </row>
@@ -2072,22 +2072,22 @@
         <v>27</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="P24" s="4" t="n">
         <v>1</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R24" s="4" t="inlineStr">
         <is>
-          <t>63.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>75.9%</t>
+          <t>76.2%</t>
         </is>
       </c>
     </row>
@@ -2150,22 +2150,22 @@
         <v>27</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="P25" s="4" t="n">
         <v>1</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R25" s="4" t="inlineStr">
         <is>
-          <t>63.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>80.7%</t>
+          <t>76.4%</t>
         </is>
       </c>
     </row>
@@ -2231,10 +2231,10 @@
         <v>17</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R26" s="4" t="inlineStr">
         <is>
@@ -9466,45 +9466,49 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B182" s="5" t="inlineStr">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B182" s="2" t="inlineStr">
         <is>
           <t>A1-D1</t>
         </is>
       </c>
-      <c r="C182" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D182" s="5" t="inlineStr">
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="E182" s="5" t="inlineStr">
+      <c r="E182" s="2" t="inlineStr">
         <is>
           <t>07/07/2026</t>
         </is>
       </c>
-      <c r="F182" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G182" s="5" t="inlineStr"/>
-      <c r="H182" s="5" t="inlineStr">
-        <is>
-          <t>0/35</t>
-        </is>
-      </c>
-      <c r="I182" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F182" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G182" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H182" s="2" t="inlineStr">
+        <is>
+          <t>29/35</t>
+        </is>
+      </c>
+      <c r="I182" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -10695,45 +10699,49 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B209" s="5" t="inlineStr">
+      <c r="A209" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B209" s="2" t="inlineStr">
         <is>
           <t>A1-D2</t>
         </is>
       </c>
-      <c r="C209" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D209" s="5" t="inlineStr">
+      <c r="C209" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D209" s="2" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="E209" s="5" t="inlineStr">
+      <c r="E209" s="2" t="inlineStr">
         <is>
           <t>07/07/2026</t>
         </is>
       </c>
-      <c r="F209" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G209" s="5" t="inlineStr"/>
-      <c r="H209" s="5" t="inlineStr">
-        <is>
-          <t>0/34</t>
-        </is>
-      </c>
-      <c r="I209" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F209" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G209" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H209" s="2" t="inlineStr">
+        <is>
+          <t>33/34</t>
+        </is>
+      </c>
+      <c r="I209" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -11924,45 +11932,49 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B236" s="5" t="inlineStr">
+      <c r="A236" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B236" s="2" t="inlineStr">
         <is>
           <t>A1-E1</t>
         </is>
       </c>
-      <c r="C236" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D236" s="5" t="inlineStr">
+      <c r="C236" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D236" s="2" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="E236" s="5" t="inlineStr">
+      <c r="E236" s="2" t="inlineStr">
         <is>
           <t>07/07/2026</t>
         </is>
       </c>
-      <c r="F236" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G236" s="5" t="inlineStr"/>
-      <c r="H236" s="5" t="inlineStr">
-        <is>
-          <t>0/38</t>
-        </is>
-      </c>
-      <c r="I236" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F236" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G236" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H236" s="2" t="inlineStr">
+        <is>
+          <t>30/38</t>
+        </is>
+      </c>
+      <c r="I236" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -13153,45 +13165,49 @@
       </c>
     </row>
     <row r="263">
-      <c r="A263" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B263" s="5" t="inlineStr">
+      <c r="A263" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B263" s="2" t="inlineStr">
         <is>
           <t>A1-E2</t>
         </is>
       </c>
-      <c r="C263" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D263" s="5" t="inlineStr">
+      <c r="C263" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D263" s="2" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="E263" s="5" t="inlineStr">
+      <c r="E263" s="2" t="inlineStr">
         <is>
           <t>07/07/2026</t>
         </is>
       </c>
-      <c r="F263" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G263" s="5" t="inlineStr"/>
-      <c r="H263" s="5" t="inlineStr">
-        <is>
-          <t>0/39</t>
-        </is>
-      </c>
-      <c r="I263" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F263" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G263" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H263" s="2" t="inlineStr">
+        <is>
+          <t>32/39</t>
+        </is>
+      </c>
+      <c r="I263" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -14382,45 +14398,49 @@
       </c>
     </row>
     <row r="290">
-      <c r="A290" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B290" s="5" t="inlineStr">
+      <c r="A290" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B290" s="2" t="inlineStr">
         <is>
           <t>A1-F1</t>
         </is>
       </c>
-      <c r="C290" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D290" s="5" t="inlineStr">
+      <c r="C290" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D290" s="2" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="E290" s="5" t="inlineStr">
+      <c r="E290" s="2" t="inlineStr">
         <is>
           <t>07/07/2026</t>
         </is>
       </c>
-      <c r="F290" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G290" s="5" t="inlineStr"/>
-      <c r="H290" s="5" t="inlineStr">
-        <is>
-          <t>0/39</t>
-        </is>
-      </c>
-      <c r="I290" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F290" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G290" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H290" s="2" t="inlineStr">
+        <is>
+          <t>1/39</t>
+        </is>
+      </c>
+      <c r="I290" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -15611,45 +15631,45 @@
       </c>
     </row>
     <row r="317">
-      <c r="A317" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B317" s="5" t="inlineStr">
+      <c r="A317" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B317" s="9" t="inlineStr">
         <is>
           <t>A1-F2</t>
         </is>
       </c>
-      <c r="C317" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D317" s="5" t="inlineStr">
+      <c r="C317" s="9" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D317" s="9" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="E317" s="5" t="inlineStr">
+      <c r="E317" s="9" t="inlineStr">
         <is>
           <t>07/07/2026</t>
         </is>
       </c>
-      <c r="F317" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G317" s="5" t="inlineStr"/>
-      <c r="H317" s="5" t="inlineStr">
+      <c r="F317" s="9" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G317" s="9" t="inlineStr"/>
+      <c r="H317" s="9" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I317" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I317" s="9" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A1_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A1_session_analysis.xlsx
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8">
@@ -924,7 +924,7 @@
         </is>
       </c>
       <c r="L8" s="4" t="n">
-        <v>84</v>
+        <v>78</v>
       </c>
     </row>
     <row r="9">
@@ -1837,10 +1837,10 @@
         <v>18</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R21" s="4" t="inlineStr">
         <is>
@@ -1919,10 +1919,10 @@
         <v>18</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R22" s="4" t="inlineStr">
         <is>
@@ -1997,10 +1997,10 @@
         <v>18</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R23" s="4" t="inlineStr">
         <is>
@@ -2075,10 +2075,10 @@
         <v>18</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R24" s="4" t="inlineStr">
         <is>
@@ -2153,10 +2153,10 @@
         <v>18</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R25" s="4" t="inlineStr">
         <is>
@@ -2231,10 +2231,10 @@
         <v>17</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R26" s="4" t="inlineStr">
         <is>
@@ -9513,45 +9513,45 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B183" s="5" t="inlineStr">
+      <c r="A183" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B183" s="9" t="inlineStr">
         <is>
           <t>A1-D1</t>
         </is>
       </c>
-      <c r="C183" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D183" s="5" t="inlineStr">
+      <c r="C183" s="9" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D183" s="9" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="E183" s="5" t="inlineStr">
+      <c r="E183" s="9" t="inlineStr">
         <is>
           <t>08/07/2026</t>
         </is>
       </c>
-      <c r="F183" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G183" s="5" t="inlineStr"/>
-      <c r="H183" s="5" t="inlineStr">
+      <c r="F183" s="9" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G183" s="9" t="inlineStr"/>
+      <c r="H183" s="9" t="inlineStr">
         <is>
           <t>0/35</t>
         </is>
       </c>
-      <c r="I183" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I183" s="9" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -10746,45 +10746,45 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B210" s="5" t="inlineStr">
+      <c r="A210" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B210" s="9" t="inlineStr">
         <is>
           <t>A1-D2</t>
         </is>
       </c>
-      <c r="C210" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D210" s="5" t="inlineStr">
+      <c r="C210" s="9" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D210" s="9" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="E210" s="5" t="inlineStr">
+      <c r="E210" s="9" t="inlineStr">
         <is>
           <t>08/07/2026</t>
         </is>
       </c>
-      <c r="F210" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G210" s="5" t="inlineStr"/>
-      <c r="H210" s="5" t="inlineStr">
+      <c r="F210" s="9" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G210" s="9" t="inlineStr"/>
+      <c r="H210" s="9" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I210" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I210" s="9" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -11979,45 +11979,45 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B237" s="5" t="inlineStr">
+      <c r="A237" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B237" s="9" t="inlineStr">
         <is>
           <t>A1-E1</t>
         </is>
       </c>
-      <c r="C237" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D237" s="5" t="inlineStr">
+      <c r="C237" s="9" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D237" s="9" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="E237" s="5" t="inlineStr">
+      <c r="E237" s="9" t="inlineStr">
         <is>
           <t>08/07/2026</t>
         </is>
       </c>
-      <c r="F237" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G237" s="5" t="inlineStr"/>
-      <c r="H237" s="5" t="inlineStr">
+      <c r="F237" s="9" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G237" s="9" t="inlineStr"/>
+      <c r="H237" s="9" t="inlineStr">
         <is>
           <t>0/38</t>
         </is>
       </c>
-      <c r="I237" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I237" s="9" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -13212,45 +13212,45 @@
       </c>
     </row>
     <row r="264">
-      <c r="A264" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B264" s="5" t="inlineStr">
+      <c r="A264" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B264" s="9" t="inlineStr">
         <is>
           <t>A1-E2</t>
         </is>
       </c>
-      <c r="C264" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D264" s="5" t="inlineStr">
+      <c r="C264" s="9" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D264" s="9" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="E264" s="5" t="inlineStr">
+      <c r="E264" s="9" t="inlineStr">
         <is>
           <t>08/07/2026</t>
         </is>
       </c>
-      <c r="F264" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G264" s="5" t="inlineStr"/>
-      <c r="H264" s="5" t="inlineStr">
+      <c r="F264" s="9" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G264" s="9" t="inlineStr"/>
+      <c r="H264" s="9" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I264" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I264" s="9" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -14445,45 +14445,45 @@
       </c>
     </row>
     <row r="291">
-      <c r="A291" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B291" s="5" t="inlineStr">
+      <c r="A291" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B291" s="9" t="inlineStr">
         <is>
           <t>A1-F1</t>
         </is>
       </c>
-      <c r="C291" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D291" s="5" t="inlineStr">
+      <c r="C291" s="9" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D291" s="9" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="E291" s="5" t="inlineStr">
+      <c r="E291" s="9" t="inlineStr">
         <is>
           <t>08/07/2026</t>
         </is>
       </c>
-      <c r="F291" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G291" s="5" t="inlineStr"/>
-      <c r="H291" s="5" t="inlineStr">
+      <c r="F291" s="9" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G291" s="9" t="inlineStr"/>
+      <c r="H291" s="9" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I291" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I291" s="9" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -15674,45 +15674,45 @@
       </c>
     </row>
     <row r="318">
-      <c r="A318" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B318" s="5" t="inlineStr">
+      <c r="A318" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B318" s="9" t="inlineStr">
         <is>
           <t>A1-F2</t>
         </is>
       </c>
-      <c r="C318" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D318" s="5" t="inlineStr">
+      <c r="C318" s="9" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D318" s="9" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="E318" s="5" t="inlineStr">
+      <c r="E318" s="9" t="inlineStr">
         <is>
           <t>08/07/2026</t>
         </is>
       </c>
-      <c r="F318" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G318" s="5" t="inlineStr"/>
-      <c r="H318" s="5" t="inlineStr">
+      <c r="F318" s="9" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G318" s="9" t="inlineStr"/>
+      <c r="H318" s="9" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I318" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I318" s="9" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A1_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A1_session_analysis.xlsx
@@ -814,7 +814,7 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>233</v>
+        <v>237</v>
       </c>
     </row>
     <row r="7">
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8">
@@ -980,7 +980,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>71.9%</t>
+          <t>73.1%</t>
         </is>
       </c>
     </row>
@@ -1037,7 +1037,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>75.7%</t>
+          <t>75.9%</t>
         </is>
       </c>
     </row>
@@ -1994,22 +1994,22 @@
         <v>27</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q23" s="4" t="n">
         <v>7</v>
       </c>
       <c r="R23" s="4" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>70.4%</t>
         </is>
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>78.7%</t>
+          <t>79.5%</t>
         </is>
       </c>
     </row>
@@ -2072,22 +2072,22 @@
         <v>27</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q24" s="4" t="n">
         <v>7</v>
       </c>
       <c r="R24" s="4" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>70.4%</t>
         </is>
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>76.2%</t>
+          <t>76.8%</t>
         </is>
       </c>
     </row>
@@ -2150,22 +2150,22 @@
         <v>27</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q25" s="4" t="n">
         <v>7</v>
       </c>
       <c r="R25" s="4" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>70.4%</t>
         </is>
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>76.4%</t>
+          <t>76.9%</t>
         </is>
       </c>
     </row>
@@ -2228,22 +2228,22 @@
         <v>27</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q26" s="4" t="n">
         <v>7</v>
       </c>
       <c r="R26" s="4" t="inlineStr">
         <is>
-          <t>63.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>77.4%</t>
+          <t>77.6%</t>
         </is>
       </c>
     </row>
@@ -11979,45 +11979,49 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B237" s="9" t="inlineStr">
+      <c r="A237" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B237" s="2" t="inlineStr">
         <is>
           <t>A1-E1</t>
         </is>
       </c>
-      <c r="C237" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D237" s="9" t="inlineStr">
+      <c r="C237" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D237" s="2" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="E237" s="9" t="inlineStr">
+      <c r="E237" s="2" t="inlineStr">
         <is>
           <t>08/07/2026</t>
         </is>
       </c>
-      <c r="F237" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G237" s="9" t="inlineStr"/>
-      <c r="H237" s="9" t="inlineStr">
-        <is>
-          <t>0/38</t>
-        </is>
-      </c>
-      <c r="I237" s="9" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F237" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G237" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H237" s="2" t="inlineStr">
+        <is>
+          <t>36/38</t>
+        </is>
+      </c>
+      <c r="I237" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -13212,45 +13216,49 @@
       </c>
     </row>
     <row r="264">
-      <c r="A264" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B264" s="9" t="inlineStr">
+      <c r="A264" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B264" s="2" t="inlineStr">
         <is>
           <t>A1-E2</t>
         </is>
       </c>
-      <c r="C264" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D264" s="9" t="inlineStr">
+      <c r="C264" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D264" s="2" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="E264" s="9" t="inlineStr">
+      <c r="E264" s="2" t="inlineStr">
         <is>
           <t>08/07/2026</t>
         </is>
       </c>
-      <c r="F264" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G264" s="9" t="inlineStr"/>
-      <c r="H264" s="9" t="inlineStr">
-        <is>
-          <t>0/39</t>
-        </is>
-      </c>
-      <c r="I264" s="9" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F264" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G264" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H264" s="2" t="inlineStr">
+        <is>
+          <t>34/39</t>
+        </is>
+      </c>
+      <c r="I264" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -14445,45 +14453,49 @@
       </c>
     </row>
     <row r="291">
-      <c r="A291" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B291" s="9" t="inlineStr">
+      <c r="A291" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B291" s="2" t="inlineStr">
         <is>
           <t>A1-F1</t>
         </is>
       </c>
-      <c r="C291" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D291" s="9" t="inlineStr">
+      <c r="C291" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D291" s="2" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="E291" s="9" t="inlineStr">
+      <c r="E291" s="2" t="inlineStr">
         <is>
           <t>08/07/2026</t>
         </is>
       </c>
-      <c r="F291" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G291" s="9" t="inlineStr"/>
-      <c r="H291" s="9" t="inlineStr">
-        <is>
-          <t>0/39</t>
-        </is>
-      </c>
-      <c r="I291" s="9" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F291" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G291" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H291" s="2" t="inlineStr">
+        <is>
+          <t>34/39</t>
+        </is>
+      </c>
+      <c r="I291" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -15674,45 +15686,49 @@
       </c>
     </row>
     <row r="318">
-      <c r="A318" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B318" s="9" t="inlineStr">
+      <c r="A318" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B318" s="2" t="inlineStr">
         <is>
           <t>A1-F2</t>
         </is>
       </c>
-      <c r="C318" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D318" s="9" t="inlineStr">
+      <c r="C318" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D318" s="2" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="E318" s="9" t="inlineStr">
+      <c r="E318" s="2" t="inlineStr">
         <is>
           <t>08/07/2026</t>
         </is>
       </c>
-      <c r="F318" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G318" s="9" t="inlineStr"/>
-      <c r="H318" s="9" t="inlineStr">
-        <is>
-          <t>0/39</t>
-        </is>
-      </c>
-      <c r="I318" s="9" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F318" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G318" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H318" s="2" t="inlineStr">
+        <is>
+          <t>32/39</t>
+        </is>
+      </c>
+      <c r="I318" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A1_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A1_session_analysis.xlsx
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8">
@@ -924,7 +924,7 @@
         </is>
       </c>
       <c r="L8" s="4" t="n">
-        <v>78</v>
+        <v>72</v>
       </c>
     </row>
     <row r="9">
@@ -1837,10 +1837,10 @@
         <v>18</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R21" s="4" t="inlineStr">
         <is>
@@ -1919,10 +1919,10 @@
         <v>18</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R22" s="4" t="inlineStr">
         <is>
@@ -1997,10 +1997,10 @@
         <v>19</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R23" s="4" t="inlineStr">
         <is>
@@ -2075,10 +2075,10 @@
         <v>19</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R24" s="4" t="inlineStr">
         <is>
@@ -2153,10 +2153,10 @@
         <v>19</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R25" s="4" t="inlineStr">
         <is>
@@ -2231,10 +2231,10 @@
         <v>18</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R26" s="4" t="inlineStr">
         <is>
@@ -9556,45 +9556,45 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B184" s="5" t="inlineStr">
+      <c r="A184" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B184" s="9" t="inlineStr">
         <is>
           <t>A1-D1</t>
         </is>
       </c>
-      <c r="C184" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D184" s="5" t="inlineStr">
+      <c r="C184" s="9" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D184" s="9" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="E184" s="5" t="inlineStr">
+      <c r="E184" s="9" t="inlineStr">
         <is>
           <t>09/07/2026</t>
         </is>
       </c>
-      <c r="F184" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G184" s="5" t="inlineStr"/>
-      <c r="H184" s="5" t="inlineStr">
+      <c r="F184" s="9" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G184" s="9" t="inlineStr"/>
+      <c r="H184" s="9" t="inlineStr">
         <is>
           <t>0/35</t>
         </is>
       </c>
-      <c r="I184" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I184" s="9" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -10789,45 +10789,45 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B211" s="5" t="inlineStr">
+      <c r="A211" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B211" s="9" t="inlineStr">
         <is>
           <t>A1-D2</t>
         </is>
       </c>
-      <c r="C211" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D211" s="5" t="inlineStr">
+      <c r="C211" s="9" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D211" s="9" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="E211" s="5" t="inlineStr">
+      <c r="E211" s="9" t="inlineStr">
         <is>
           <t>09/07/2026</t>
         </is>
       </c>
-      <c r="F211" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G211" s="5" t="inlineStr"/>
-      <c r="H211" s="5" t="inlineStr">
+      <c r="F211" s="9" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G211" s="9" t="inlineStr"/>
+      <c r="H211" s="9" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I211" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I211" s="9" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -12026,45 +12026,45 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B238" s="5" t="inlineStr">
+      <c r="A238" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B238" s="9" t="inlineStr">
         <is>
           <t>A1-E1</t>
         </is>
       </c>
-      <c r="C238" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D238" s="5" t="inlineStr">
+      <c r="C238" s="9" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D238" s="9" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="E238" s="5" t="inlineStr">
+      <c r="E238" s="9" t="inlineStr">
         <is>
           <t>09/07/2026</t>
         </is>
       </c>
-      <c r="F238" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G238" s="5" t="inlineStr"/>
-      <c r="H238" s="5" t="inlineStr">
+      <c r="F238" s="9" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G238" s="9" t="inlineStr"/>
+      <c r="H238" s="9" t="inlineStr">
         <is>
           <t>0/38</t>
         </is>
       </c>
-      <c r="I238" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I238" s="9" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -13263,45 +13263,45 @@
       </c>
     </row>
     <row r="265">
-      <c r="A265" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B265" s="5" t="inlineStr">
+      <c r="A265" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B265" s="9" t="inlineStr">
         <is>
           <t>A1-E2</t>
         </is>
       </c>
-      <c r="C265" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D265" s="5" t="inlineStr">
+      <c r="C265" s="9" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D265" s="9" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="E265" s="5" t="inlineStr">
+      <c r="E265" s="9" t="inlineStr">
         <is>
           <t>09/07/2026</t>
         </is>
       </c>
-      <c r="F265" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G265" s="5" t="inlineStr"/>
-      <c r="H265" s="5" t="inlineStr">
+      <c r="F265" s="9" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G265" s="9" t="inlineStr"/>
+      <c r="H265" s="9" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I265" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I265" s="9" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -14500,45 +14500,45 @@
       </c>
     </row>
     <row r="292">
-      <c r="A292" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B292" s="5" t="inlineStr">
+      <c r="A292" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B292" s="9" t="inlineStr">
         <is>
           <t>A1-F1</t>
         </is>
       </c>
-      <c r="C292" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D292" s="5" t="inlineStr">
+      <c r="C292" s="9" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D292" s="9" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="E292" s="5" t="inlineStr">
+      <c r="E292" s="9" t="inlineStr">
         <is>
           <t>09/07/2026</t>
         </is>
       </c>
-      <c r="F292" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G292" s="5" t="inlineStr"/>
-      <c r="H292" s="5" t="inlineStr">
+      <c r="F292" s="9" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G292" s="9" t="inlineStr"/>
+      <c r="H292" s="9" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I292" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I292" s="9" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -15733,45 +15733,45 @@
       </c>
     </row>
     <row r="319">
-      <c r="A319" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B319" s="5" t="inlineStr">
+      <c r="A319" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B319" s="9" t="inlineStr">
         <is>
           <t>A1-F2</t>
         </is>
       </c>
-      <c r="C319" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D319" s="5" t="inlineStr">
+      <c r="C319" s="9" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D319" s="9" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="E319" s="5" t="inlineStr">
+      <c r="E319" s="9" t="inlineStr">
         <is>
           <t>09/07/2026</t>
         </is>
       </c>
-      <c r="F319" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G319" s="5" t="inlineStr"/>
-      <c r="H319" s="5" t="inlineStr">
+      <c r="F319" s="9" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G319" s="9" t="inlineStr"/>
+      <c r="H319" s="9" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I319" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I319" s="9" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A1_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A1_session_analysis.xlsx
@@ -814,7 +814,7 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>237</v>
+        <v>241</v>
       </c>
     </row>
     <row r="7">
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8">
@@ -980,7 +980,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>73.1%</t>
+          <t>74.4%</t>
         </is>
       </c>
     </row>
@@ -1037,7 +1037,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>75.9%</t>
+          <t>75.2%</t>
         </is>
       </c>
     </row>
@@ -1834,22 +1834,22 @@
         <v>27</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q21" s="4" t="n">
         <v>6</v>
       </c>
       <c r="R21" s="4" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>70.4%</t>
         </is>
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>76.0%</t>
+          <t>74.0%</t>
         </is>
       </c>
     </row>
@@ -1916,22 +1916,22 @@
         <v>27</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q22" s="4" t="n">
         <v>6</v>
       </c>
       <c r="R22" s="4" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>70.4%</t>
         </is>
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>80.2%</t>
+          <t>77.9%</t>
         </is>
       </c>
     </row>
@@ -2150,22 +2150,22 @@
         <v>27</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q25" s="4" t="n">
         <v>6</v>
       </c>
       <c r="R25" s="4" t="inlineStr">
         <is>
-          <t>70.4%</t>
+          <t>74.1%</t>
         </is>
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>76.9%</t>
+          <t>75.4%</t>
         </is>
       </c>
     </row>
@@ -2228,22 +2228,22 @@
         <v>27</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q26" s="4" t="n">
         <v>6</v>
       </c>
       <c r="R26" s="4" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>70.4%</t>
         </is>
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>77.6%</t>
+          <t>74.2%</t>
         </is>
       </c>
     </row>
@@ -9556,45 +9556,49 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B184" s="9" t="inlineStr">
+      <c r="A184" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B184" s="2" t="inlineStr">
         <is>
           <t>A1-D1</t>
         </is>
       </c>
-      <c r="C184" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D184" s="9" t="inlineStr">
+      <c r="C184" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D184" s="2" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="E184" s="9" t="inlineStr">
+      <c r="E184" s="2" t="inlineStr">
         <is>
           <t>09/07/2026</t>
         </is>
       </c>
-      <c r="F184" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G184" s="9" t="inlineStr"/>
-      <c r="H184" s="9" t="inlineStr">
-        <is>
-          <t>0/35</t>
-        </is>
-      </c>
-      <c r="I184" s="9" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F184" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G184" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H184" s="2" t="inlineStr">
+        <is>
+          <t>13/35</t>
+        </is>
+      </c>
+      <c r="I184" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -10789,45 +10793,49 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B211" s="9" t="inlineStr">
+      <c r="A211" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B211" s="2" t="inlineStr">
         <is>
           <t>A1-D2</t>
         </is>
       </c>
-      <c r="C211" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D211" s="9" t="inlineStr">
+      <c r="C211" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D211" s="2" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="E211" s="9" t="inlineStr">
+      <c r="E211" s="2" t="inlineStr">
         <is>
           <t>09/07/2026</t>
         </is>
       </c>
-      <c r="F211" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G211" s="9" t="inlineStr"/>
-      <c r="H211" s="9" t="inlineStr">
-        <is>
-          <t>0/34</t>
-        </is>
-      </c>
-      <c r="I211" s="9" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F211" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G211" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H211" s="2" t="inlineStr">
+        <is>
+          <t>12/34</t>
+        </is>
+      </c>
+      <c r="I211" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -14500,45 +14508,49 @@
       </c>
     </row>
     <row r="292">
-      <c r="A292" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B292" s="9" t="inlineStr">
+      <c r="A292" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B292" s="2" t="inlineStr">
         <is>
           <t>A1-F1</t>
         </is>
       </c>
-      <c r="C292" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D292" s="9" t="inlineStr">
+      <c r="C292" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D292" s="2" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="E292" s="9" t="inlineStr">
+      <c r="E292" s="2" t="inlineStr">
         <is>
           <t>09/07/2026</t>
         </is>
       </c>
-      <c r="F292" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G292" s="9" t="inlineStr"/>
-      <c r="H292" s="9" t="inlineStr">
-        <is>
-          <t>0/39</t>
-        </is>
-      </c>
-      <c r="I292" s="9" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F292" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G292" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H292" s="2" t="inlineStr">
+        <is>
+          <t>18/39</t>
+        </is>
+      </c>
+      <c r="I292" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -15733,45 +15745,49 @@
       </c>
     </row>
     <row r="319">
-      <c r="A319" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B319" s="9" t="inlineStr">
+      <c r="A319" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B319" s="2" t="inlineStr">
         <is>
           <t>A1-F2</t>
         </is>
       </c>
-      <c r="C319" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D319" s="9" t="inlineStr">
+      <c r="C319" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D319" s="2" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="E319" s="9" t="inlineStr">
+      <c r="E319" s="2" t="inlineStr">
         <is>
           <t>09/07/2026</t>
         </is>
       </c>
-      <c r="F319" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G319" s="9" t="inlineStr"/>
-      <c r="H319" s="9" t="inlineStr">
-        <is>
-          <t>0/39</t>
-        </is>
-      </c>
-      <c r="I319" s="9" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F319" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G319" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H319" s="2" t="inlineStr">
+        <is>
+          <t>5/39</t>
+        </is>
+      </c>
+      <c r="I319" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A1_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A1_session_analysis.xlsx
@@ -58,14 +58,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFFE0"/>
-        <bgColor rgb="00FFFFE0"/>
+        <fgColor rgb="00FFB6C1"/>
+        <bgColor rgb="00FFB6C1"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFB6C1"/>
-        <bgColor rgb="00FFB6C1"/>
+        <fgColor rgb="00FFFFE0"/>
+        <bgColor rgb="00FFFFE0"/>
       </patternFill>
     </fill>
   </fills>
@@ -96,16 +96,16 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8">
@@ -924,7 +924,7 @@
         </is>
       </c>
       <c r="L8" s="4" t="n">
-        <v>72</v>
+        <v>66</v>
       </c>
     </row>
     <row r="9">
@@ -1345,10 +1345,10 @@
         <v>21</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R15" s="4" t="inlineStr">
         <is>
@@ -1427,10 +1427,10 @@
         <v>21</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R16" s="4" t="inlineStr">
         <is>
@@ -1509,10 +1509,10 @@
         <v>21</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R17" s="4" t="inlineStr">
         <is>
@@ -1591,10 +1591,10 @@
         <v>21</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R18" s="4" t="inlineStr">
         <is>
@@ -1673,10 +1673,10 @@
         <v>21</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R19" s="4" t="inlineStr">
         <is>
@@ -1755,10 +1755,10 @@
         <v>21</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R20" s="4" t="inlineStr">
         <is>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="I23" s="5" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Not Recorded</t>
         </is>
       </c>
       <c r="K23" s="4" t="inlineStr">
@@ -2014,43 +2014,43 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B24" s="5" t="inlineStr">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
         <is>
           <t>A1-A1</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D24" s="5" t="inlineStr">
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="E24" s="5" t="inlineStr">
+      <c r="E24" s="6" t="inlineStr">
         <is>
           <t>12/07/2026</t>
         </is>
       </c>
-      <c r="F24" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G24" s="5" t="inlineStr"/>
-      <c r="H24" s="5" t="inlineStr">
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G24" s="6" t="inlineStr"/>
+      <c r="H24" s="6" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I24" s="5" t="inlineStr">
+      <c r="I24" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -2092,43 +2092,43 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B25" s="5" t="inlineStr">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
         <is>
           <t>A1-A1</t>
         </is>
       </c>
-      <c r="C25" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="inlineStr">
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="E25" s="5" t="inlineStr">
+      <c r="E25" s="6" t="inlineStr">
         <is>
           <t>13/07/2026</t>
         </is>
       </c>
-      <c r="F25" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G25" s="5" t="inlineStr"/>
-      <c r="H25" s="5" t="inlineStr">
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G25" s="6" t="inlineStr"/>
+      <c r="H25" s="6" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I25" s="5" t="inlineStr">
+      <c r="I25" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -2170,43 +2170,43 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B26" s="5" t="inlineStr">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
         <is>
           <t>A1-A1</t>
         </is>
       </c>
-      <c r="C26" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D26" s="5" t="inlineStr">
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="E26" s="5" t="inlineStr">
+      <c r="E26" s="6" t="inlineStr">
         <is>
           <t>18/07/2026</t>
         </is>
       </c>
-      <c r="F26" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G26" s="5" t="inlineStr"/>
-      <c r="H26" s="5" t="inlineStr">
+      <c r="F26" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G26" s="6" t="inlineStr"/>
+      <c r="H26" s="6" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I26" s="5" t="inlineStr">
+      <c r="I26" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -2248,86 +2248,86 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B27" s="5" t="inlineStr">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
         <is>
           <t>A1-A1</t>
         </is>
       </c>
-      <c r="C27" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="inlineStr">
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="E27" s="5" t="inlineStr">
+      <c r="E27" s="6" t="inlineStr">
         <is>
           <t>19/07/2026</t>
         </is>
       </c>
-      <c r="F27" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G27" s="5" t="inlineStr"/>
-      <c r="H27" s="5" t="inlineStr">
+      <c r="F27" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G27" s="6" t="inlineStr"/>
+      <c r="H27" s="6" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I27" s="5" t="inlineStr">
+      <c r="I27" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B28" s="5" t="inlineStr">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
         <is>
           <t>A1-A1</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D28" s="5" t="inlineStr">
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="E28" s="5" t="inlineStr">
+      <c r="E28" s="6" t="inlineStr">
         <is>
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="F28" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G28" s="5" t="inlineStr"/>
-      <c r="H28" s="5" t="inlineStr">
+      <c r="F28" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G28" s="6" t="inlineStr"/>
+      <c r="H28" s="6" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I28" s="5" t="inlineStr">
+      <c r="I28" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -2498,7 +2498,7 @@
           <t>Recorded</t>
         </is>
       </c>
-      <c r="L31" s="6" t="inlineStr">
+      <c r="L31" s="7" t="inlineStr">
         <is>
           <t>Green</t>
         </is>
@@ -2560,7 +2560,7 @@
           <t>Not Recorded</t>
         </is>
       </c>
-      <c r="L32" s="7" t="inlineStr">
+      <c r="L32" s="8" t="inlineStr">
         <is>
           <t>Red</t>
         </is>
@@ -2622,7 +2622,7 @@
           <t>Pending</t>
         </is>
       </c>
-      <c r="L33" s="8" t="inlineStr">
+      <c r="L33" s="9" t="inlineStr">
         <is>
           <t>Yellow</t>
         </is>
@@ -3424,220 +3424,220 @@
       </c>
       <c r="I50" s="5" t="inlineStr">
         <is>
+          <t>Not Recorded</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B51" s="6" t="inlineStr">
+        <is>
+          <t>A1-A2</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D51" s="6" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="E51" s="6" t="inlineStr">
+        <is>
+          <t>12/07/2026</t>
+        </is>
+      </c>
+      <c r="F51" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G51" s="6" t="inlineStr"/>
+      <c r="H51" s="6" t="inlineStr">
+        <is>
+          <t>0/33</t>
+        </is>
+      </c>
+      <c r="I51" s="6" t="inlineStr">
+        <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B51" s="5" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B52" s="6" t="inlineStr">
         <is>
           <t>A1-A2</t>
         </is>
       </c>
-      <c r="C51" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D51" s="5" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="E51" s="5" t="inlineStr">
-        <is>
-          <t>12/07/2026</t>
-        </is>
-      </c>
-      <c r="F51" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G51" s="5" t="inlineStr"/>
-      <c r="H51" s="5" t="inlineStr">
+      <c r="C52" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D52" s="6" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="E52" s="6" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="F52" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G52" s="6" t="inlineStr"/>
+      <c r="H52" s="6" t="inlineStr">
         <is>
           <t>0/33</t>
         </is>
       </c>
-      <c r="I51" s="5" t="inlineStr">
+      <c r="I52" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B52" s="5" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B53" s="6" t="inlineStr">
         <is>
           <t>A1-A2</t>
         </is>
       </c>
-      <c r="C52" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D52" s="5" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="E52" s="5" t="inlineStr">
-        <is>
-          <t>13/07/2026</t>
-        </is>
-      </c>
-      <c r="F52" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G52" s="5" t="inlineStr"/>
-      <c r="H52" s="5" t="inlineStr">
+      <c r="C53" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D53" s="6" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E53" s="6" t="inlineStr">
+        <is>
+          <t>18/07/2026</t>
+        </is>
+      </c>
+      <c r="F53" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G53" s="6" t="inlineStr"/>
+      <c r="H53" s="6" t="inlineStr">
         <is>
           <t>0/33</t>
         </is>
       </c>
-      <c r="I52" s="5" t="inlineStr">
+      <c r="I53" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B53" s="5" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B54" s="6" t="inlineStr">
         <is>
           <t>A1-A2</t>
         </is>
       </c>
-      <c r="C53" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D53" s="5" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="E53" s="5" t="inlineStr">
-        <is>
-          <t>18/07/2026</t>
-        </is>
-      </c>
-      <c r="F53" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G53" s="5" t="inlineStr"/>
-      <c r="H53" s="5" t="inlineStr">
+      <c r="C54" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D54" s="6" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="E54" s="6" t="inlineStr">
+        <is>
+          <t>19/07/2026</t>
+        </is>
+      </c>
+      <c r="F54" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G54" s="6" t="inlineStr"/>
+      <c r="H54" s="6" t="inlineStr">
         <is>
           <t>0/33</t>
         </is>
       </c>
-      <c r="I53" s="5" t="inlineStr">
+      <c r="I54" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B54" s="5" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B55" s="6" t="inlineStr">
         <is>
           <t>A1-A2</t>
         </is>
       </c>
-      <c r="C54" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D54" s="5" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="E54" s="5" t="inlineStr">
-        <is>
-          <t>19/07/2026</t>
-        </is>
-      </c>
-      <c r="F54" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G54" s="5" t="inlineStr"/>
-      <c r="H54" s="5" t="inlineStr">
+      <c r="C55" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D55" s="6" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E55" s="6" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="F55" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G55" s="6" t="inlineStr"/>
+      <c r="H55" s="6" t="inlineStr">
         <is>
           <t>0/33</t>
         </is>
       </c>
-      <c r="I54" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B55" s="5" t="inlineStr">
-        <is>
-          <t>A1-A2</t>
-        </is>
-      </c>
-      <c r="C55" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D55" s="5" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="E55" s="5" t="inlineStr">
-        <is>
-          <t>20/07/2026</t>
-        </is>
-      </c>
-      <c r="F55" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G55" s="5" t="inlineStr"/>
-      <c r="H55" s="5" t="inlineStr">
-        <is>
-          <t>0/33</t>
-        </is>
-      </c>
-      <c r="I55" s="5" t="inlineStr">
+      <c r="I55" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -4669,220 +4669,220 @@
       </c>
       <c r="I77" s="5" t="inlineStr">
         <is>
+          <t>Not Recorded</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B78" s="6" t="inlineStr">
+        <is>
+          <t>A1-B1</t>
+        </is>
+      </c>
+      <c r="C78" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D78" s="6" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="E78" s="6" t="inlineStr">
+        <is>
+          <t>12/07/2026</t>
+        </is>
+      </c>
+      <c r="F78" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G78" s="6" t="inlineStr"/>
+      <c r="H78" s="6" t="inlineStr">
+        <is>
+          <t>0/34</t>
+        </is>
+      </c>
+      <c r="I78" s="6" t="inlineStr">
+        <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B78" s="5" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B79" s="6" t="inlineStr">
         <is>
           <t>A1-B1</t>
         </is>
       </c>
-      <c r="C78" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D78" s="5" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="E78" s="5" t="inlineStr">
-        <is>
-          <t>12/07/2026</t>
-        </is>
-      </c>
-      <c r="F78" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G78" s="5" t="inlineStr"/>
-      <c r="H78" s="5" t="inlineStr">
+      <c r="C79" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D79" s="6" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="E79" s="6" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="F79" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G79" s="6" t="inlineStr"/>
+      <c r="H79" s="6" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I78" s="5" t="inlineStr">
+      <c r="I79" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B79" s="5" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B80" s="6" t="inlineStr">
         <is>
           <t>A1-B1</t>
         </is>
       </c>
-      <c r="C79" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D79" s="5" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="E79" s="5" t="inlineStr">
-        <is>
-          <t>13/07/2026</t>
-        </is>
-      </c>
-      <c r="F79" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G79" s="5" t="inlineStr"/>
-      <c r="H79" s="5" t="inlineStr">
+      <c r="C80" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D80" s="6" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E80" s="6" t="inlineStr">
+        <is>
+          <t>18/07/2026</t>
+        </is>
+      </c>
+      <c r="F80" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G80" s="6" t="inlineStr"/>
+      <c r="H80" s="6" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I79" s="5" t="inlineStr">
+      <c r="I80" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B80" s="5" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B81" s="6" t="inlineStr">
         <is>
           <t>A1-B1</t>
         </is>
       </c>
-      <c r="C80" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D80" s="5" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="E80" s="5" t="inlineStr">
-        <is>
-          <t>18/07/2026</t>
-        </is>
-      </c>
-      <c r="F80" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G80" s="5" t="inlineStr"/>
-      <c r="H80" s="5" t="inlineStr">
+      <c r="C81" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D81" s="6" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="E81" s="6" t="inlineStr">
+        <is>
+          <t>19/07/2026</t>
+        </is>
+      </c>
+      <c r="F81" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G81" s="6" t="inlineStr"/>
+      <c r="H81" s="6" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I80" s="5" t="inlineStr">
+      <c r="I81" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B81" s="5" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B82" s="6" t="inlineStr">
         <is>
           <t>A1-B1</t>
         </is>
       </c>
-      <c r="C81" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D81" s="5" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="E81" s="5" t="inlineStr">
-        <is>
-          <t>19/07/2026</t>
-        </is>
-      </c>
-      <c r="F81" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G81" s="5" t="inlineStr"/>
-      <c r="H81" s="5" t="inlineStr">
+      <c r="C82" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D82" s="6" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E82" s="6" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="F82" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G82" s="6" t="inlineStr"/>
+      <c r="H82" s="6" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I81" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B82" s="5" t="inlineStr">
-        <is>
-          <t>A1-B1</t>
-        </is>
-      </c>
-      <c r="C82" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D82" s="5" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="E82" s="5" t="inlineStr">
-        <is>
-          <t>20/07/2026</t>
-        </is>
-      </c>
-      <c r="F82" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G82" s="5" t="inlineStr"/>
-      <c r="H82" s="5" t="inlineStr">
-        <is>
-          <t>0/34</t>
-        </is>
-      </c>
-      <c r="I82" s="5" t="inlineStr">
+      <c r="I82" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -5914,220 +5914,220 @@
       </c>
       <c r="I104" s="5" t="inlineStr">
         <is>
+          <t>Not Recorded</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B105" s="6" t="inlineStr">
+        <is>
+          <t>A1-B2</t>
+        </is>
+      </c>
+      <c r="C105" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D105" s="6" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="E105" s="6" t="inlineStr">
+        <is>
+          <t>12/07/2026</t>
+        </is>
+      </c>
+      <c r="F105" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G105" s="6" t="inlineStr"/>
+      <c r="H105" s="6" t="inlineStr">
+        <is>
+          <t>0/34</t>
+        </is>
+      </c>
+      <c r="I105" s="6" t="inlineStr">
+        <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B105" s="5" t="inlineStr">
+    <row r="106">
+      <c r="A106" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B106" s="6" t="inlineStr">
         <is>
           <t>A1-B2</t>
         </is>
       </c>
-      <c r="C105" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D105" s="5" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="E105" s="5" t="inlineStr">
-        <is>
-          <t>12/07/2026</t>
-        </is>
-      </c>
-      <c r="F105" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G105" s="5" t="inlineStr"/>
-      <c r="H105" s="5" t="inlineStr">
+      <c r="C106" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D106" s="6" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="E106" s="6" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="F106" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G106" s="6" t="inlineStr"/>
+      <c r="H106" s="6" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I105" s="5" t="inlineStr">
+      <c r="I106" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B106" s="5" t="inlineStr">
+    <row r="107">
+      <c r="A107" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B107" s="6" t="inlineStr">
         <is>
           <t>A1-B2</t>
         </is>
       </c>
-      <c r="C106" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D106" s="5" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="E106" s="5" t="inlineStr">
-        <is>
-          <t>13/07/2026</t>
-        </is>
-      </c>
-      <c r="F106" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G106" s="5" t="inlineStr"/>
-      <c r="H106" s="5" t="inlineStr">
+      <c r="C107" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D107" s="6" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E107" s="6" t="inlineStr">
+        <is>
+          <t>18/07/2026</t>
+        </is>
+      </c>
+      <c r="F107" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G107" s="6" t="inlineStr"/>
+      <c r="H107" s="6" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I106" s="5" t="inlineStr">
+      <c r="I107" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B107" s="5" t="inlineStr">
+    <row r="108">
+      <c r="A108" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B108" s="6" t="inlineStr">
         <is>
           <t>A1-B2</t>
         </is>
       </c>
-      <c r="C107" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D107" s="5" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="E107" s="5" t="inlineStr">
-        <is>
-          <t>18/07/2026</t>
-        </is>
-      </c>
-      <c r="F107" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G107" s="5" t="inlineStr"/>
-      <c r="H107" s="5" t="inlineStr">
+      <c r="C108" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D108" s="6" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="E108" s="6" t="inlineStr">
+        <is>
+          <t>19/07/2026</t>
+        </is>
+      </c>
+      <c r="F108" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G108" s="6" t="inlineStr"/>
+      <c r="H108" s="6" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I107" s="5" t="inlineStr">
+      <c r="I108" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B108" s="5" t="inlineStr">
+    <row r="109">
+      <c r="A109" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B109" s="6" t="inlineStr">
         <is>
           <t>A1-B2</t>
         </is>
       </c>
-      <c r="C108" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D108" s="5" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="E108" s="5" t="inlineStr">
-        <is>
-          <t>19/07/2026</t>
-        </is>
-      </c>
-      <c r="F108" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G108" s="5" t="inlineStr"/>
-      <c r="H108" s="5" t="inlineStr">
+      <c r="C109" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D109" s="6" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E109" s="6" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="F109" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G109" s="6" t="inlineStr"/>
+      <c r="H109" s="6" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I108" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B109" s="5" t="inlineStr">
-        <is>
-          <t>A1-B2</t>
-        </is>
-      </c>
-      <c r="C109" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D109" s="5" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="E109" s="5" t="inlineStr">
-        <is>
-          <t>20/07/2026</t>
-        </is>
-      </c>
-      <c r="F109" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G109" s="5" t="inlineStr"/>
-      <c r="H109" s="5" t="inlineStr">
-        <is>
-          <t>0/34</t>
-        </is>
-      </c>
-      <c r="I109" s="5" t="inlineStr">
+      <c r="I109" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -7159,220 +7159,220 @@
       </c>
       <c r="I131" s="5" t="inlineStr">
         <is>
+          <t>Not Recorded</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B132" s="6" t="inlineStr">
+        <is>
+          <t>A1-C1</t>
+        </is>
+      </c>
+      <c r="C132" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D132" s="6" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="E132" s="6" t="inlineStr">
+        <is>
+          <t>12/07/2026</t>
+        </is>
+      </c>
+      <c r="F132" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G132" s="6" t="inlineStr"/>
+      <c r="H132" s="6" t="inlineStr">
+        <is>
+          <t>0/34</t>
+        </is>
+      </c>
+      <c r="I132" s="6" t="inlineStr">
+        <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B132" s="5" t="inlineStr">
+    <row r="133">
+      <c r="A133" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B133" s="6" t="inlineStr">
         <is>
           <t>A1-C1</t>
         </is>
       </c>
-      <c r="C132" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D132" s="5" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="E132" s="5" t="inlineStr">
-        <is>
-          <t>12/07/2026</t>
-        </is>
-      </c>
-      <c r="F132" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G132" s="5" t="inlineStr"/>
-      <c r="H132" s="5" t="inlineStr">
+      <c r="C133" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D133" s="6" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="E133" s="6" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="F133" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G133" s="6" t="inlineStr"/>
+      <c r="H133" s="6" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I132" s="5" t="inlineStr">
+      <c r="I133" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B133" s="5" t="inlineStr">
+    <row r="134">
+      <c r="A134" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B134" s="6" t="inlineStr">
         <is>
           <t>A1-C1</t>
         </is>
       </c>
-      <c r="C133" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D133" s="5" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="E133" s="5" t="inlineStr">
-        <is>
-          <t>13/07/2026</t>
-        </is>
-      </c>
-      <c r="F133" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G133" s="5" t="inlineStr"/>
-      <c r="H133" s="5" t="inlineStr">
+      <c r="C134" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D134" s="6" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E134" s="6" t="inlineStr">
+        <is>
+          <t>18/07/2026</t>
+        </is>
+      </c>
+      <c r="F134" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G134" s="6" t="inlineStr"/>
+      <c r="H134" s="6" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I133" s="5" t="inlineStr">
+      <c r="I134" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="134">
-      <c r="A134" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B134" s="5" t="inlineStr">
+    <row r="135">
+      <c r="A135" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B135" s="6" t="inlineStr">
         <is>
           <t>A1-C1</t>
         </is>
       </c>
-      <c r="C134" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D134" s="5" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="E134" s="5" t="inlineStr">
-        <is>
-          <t>18/07/2026</t>
-        </is>
-      </c>
-      <c r="F134" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G134" s="5" t="inlineStr"/>
-      <c r="H134" s="5" t="inlineStr">
+      <c r="C135" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D135" s="6" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="E135" s="6" t="inlineStr">
+        <is>
+          <t>19/07/2026</t>
+        </is>
+      </c>
+      <c r="F135" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G135" s="6" t="inlineStr"/>
+      <c r="H135" s="6" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I134" s="5" t="inlineStr">
+      <c r="I135" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B135" s="5" t="inlineStr">
+    <row r="136">
+      <c r="A136" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B136" s="6" t="inlineStr">
         <is>
           <t>A1-C1</t>
         </is>
       </c>
-      <c r="C135" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D135" s="5" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="E135" s="5" t="inlineStr">
-        <is>
-          <t>19/07/2026</t>
-        </is>
-      </c>
-      <c r="F135" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G135" s="5" t="inlineStr"/>
-      <c r="H135" s="5" t="inlineStr">
+      <c r="C136" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D136" s="6" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E136" s="6" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="F136" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G136" s="6" t="inlineStr"/>
+      <c r="H136" s="6" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I135" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B136" s="5" t="inlineStr">
-        <is>
-          <t>A1-C1</t>
-        </is>
-      </c>
-      <c r="C136" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D136" s="5" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="E136" s="5" t="inlineStr">
-        <is>
-          <t>20/07/2026</t>
-        </is>
-      </c>
-      <c r="F136" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G136" s="5" t="inlineStr"/>
-      <c r="H136" s="5" t="inlineStr">
-        <is>
-          <t>0/34</t>
-        </is>
-      </c>
-      <c r="I136" s="5" t="inlineStr">
+      <c r="I136" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -8404,220 +8404,220 @@
       </c>
       <c r="I158" s="5" t="inlineStr">
         <is>
+          <t>Not Recorded</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B159" s="6" t="inlineStr">
+        <is>
+          <t>A1-C2</t>
+        </is>
+      </c>
+      <c r="C159" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D159" s="6" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="E159" s="6" t="inlineStr">
+        <is>
+          <t>12/07/2026</t>
+        </is>
+      </c>
+      <c r="F159" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G159" s="6" t="inlineStr"/>
+      <c r="H159" s="6" t="inlineStr">
+        <is>
+          <t>0/33</t>
+        </is>
+      </c>
+      <c r="I159" s="6" t="inlineStr">
+        <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="159">
-      <c r="A159" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B159" s="5" t="inlineStr">
+    <row r="160">
+      <c r="A160" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B160" s="6" t="inlineStr">
         <is>
           <t>A1-C2</t>
         </is>
       </c>
-      <c r="C159" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D159" s="5" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="E159" s="5" t="inlineStr">
-        <is>
-          <t>12/07/2026</t>
-        </is>
-      </c>
-      <c r="F159" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G159" s="5" t="inlineStr"/>
-      <c r="H159" s="5" t="inlineStr">
+      <c r="C160" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D160" s="6" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="E160" s="6" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="F160" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G160" s="6" t="inlineStr"/>
+      <c r="H160" s="6" t="inlineStr">
         <is>
           <t>0/33</t>
         </is>
       </c>
-      <c r="I159" s="5" t="inlineStr">
+      <c r="I160" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="160">
-      <c r="A160" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B160" s="5" t="inlineStr">
+    <row r="161">
+      <c r="A161" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B161" s="6" t="inlineStr">
         <is>
           <t>A1-C2</t>
         </is>
       </c>
-      <c r="C160" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D160" s="5" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="E160" s="5" t="inlineStr">
-        <is>
-          <t>13/07/2026</t>
-        </is>
-      </c>
-      <c r="F160" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G160" s="5" t="inlineStr"/>
-      <c r="H160" s="5" t="inlineStr">
+      <c r="C161" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D161" s="6" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E161" s="6" t="inlineStr">
+        <is>
+          <t>18/07/2026</t>
+        </is>
+      </c>
+      <c r="F161" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G161" s="6" t="inlineStr"/>
+      <c r="H161" s="6" t="inlineStr">
         <is>
           <t>0/33</t>
         </is>
       </c>
-      <c r="I160" s="5" t="inlineStr">
+      <c r="I161" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="161">
-      <c r="A161" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B161" s="5" t="inlineStr">
+    <row r="162">
+      <c r="A162" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B162" s="6" t="inlineStr">
         <is>
           <t>A1-C2</t>
         </is>
       </c>
-      <c r="C161" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D161" s="5" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="E161" s="5" t="inlineStr">
-        <is>
-          <t>18/07/2026</t>
-        </is>
-      </c>
-      <c r="F161" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G161" s="5" t="inlineStr"/>
-      <c r="H161" s="5" t="inlineStr">
+      <c r="C162" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D162" s="6" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="E162" s="6" t="inlineStr">
+        <is>
+          <t>19/07/2026</t>
+        </is>
+      </c>
+      <c r="F162" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G162" s="6" t="inlineStr"/>
+      <c r="H162" s="6" t="inlineStr">
         <is>
           <t>0/33</t>
         </is>
       </c>
-      <c r="I161" s="5" t="inlineStr">
+      <c r="I162" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="162">
-      <c r="A162" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B162" s="5" t="inlineStr">
+    <row r="163">
+      <c r="A163" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B163" s="6" t="inlineStr">
         <is>
           <t>A1-C2</t>
         </is>
       </c>
-      <c r="C162" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D162" s="5" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="E162" s="5" t="inlineStr">
-        <is>
-          <t>19/07/2026</t>
-        </is>
-      </c>
-      <c r="F162" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G162" s="5" t="inlineStr"/>
-      <c r="H162" s="5" t="inlineStr">
+      <c r="C163" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D163" s="6" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E163" s="6" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="F163" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G163" s="6" t="inlineStr"/>
+      <c r="H163" s="6" t="inlineStr">
         <is>
           <t>0/33</t>
         </is>
       </c>
-      <c r="I162" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B163" s="5" t="inlineStr">
-        <is>
-          <t>A1-C2</t>
-        </is>
-      </c>
-      <c r="C163" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D163" s="5" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="E163" s="5" t="inlineStr">
-        <is>
-          <t>20/07/2026</t>
-        </is>
-      </c>
-      <c r="F163" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G163" s="5" t="inlineStr"/>
-      <c r="H163" s="5" t="inlineStr">
-        <is>
-          <t>0/33</t>
-        </is>
-      </c>
-      <c r="I163" s="5" t="inlineStr">
+      <c r="I163" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -8859,43 +8859,43 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B169" s="9" t="inlineStr">
+      <c r="A169" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B169" s="5" t="inlineStr">
         <is>
           <t>A1-D1</t>
         </is>
       </c>
-      <c r="C169" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D169" s="9" t="inlineStr">
+      <c r="C169" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D169" s="5" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E169" s="9" t="inlineStr">
+      <c r="E169" s="5" t="inlineStr">
         <is>
           <t>04/06/2026</t>
         </is>
       </c>
-      <c r="F169" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G169" s="9" t="inlineStr"/>
-      <c r="H169" s="9" t="inlineStr">
+      <c r="F169" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G169" s="5" t="inlineStr"/>
+      <c r="H169" s="5" t="inlineStr">
         <is>
           <t>0/35</t>
         </is>
       </c>
-      <c r="I169" s="9" t="inlineStr">
+      <c r="I169" s="5" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
@@ -9513,43 +9513,43 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B183" s="9" t="inlineStr">
+      <c r="A183" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B183" s="5" t="inlineStr">
         <is>
           <t>A1-D1</t>
         </is>
       </c>
-      <c r="C183" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D183" s="9" t="inlineStr">
+      <c r="C183" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D183" s="5" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="E183" s="9" t="inlineStr">
+      <c r="E183" s="5" t="inlineStr">
         <is>
           <t>08/07/2026</t>
         </is>
       </c>
-      <c r="F183" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G183" s="9" t="inlineStr"/>
-      <c r="H183" s="9" t="inlineStr">
+      <c r="F183" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G183" s="5" t="inlineStr"/>
+      <c r="H183" s="5" t="inlineStr">
         <is>
           <t>0/35</t>
         </is>
       </c>
-      <c r="I183" s="9" t="inlineStr">
+      <c r="I183" s="5" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
@@ -9603,258 +9603,258 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B185" s="5" t="inlineStr">
+      <c r="A185" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B185" s="6" t="inlineStr">
         <is>
           <t>A1-D1</t>
         </is>
       </c>
-      <c r="C185" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D185" s="5" t="inlineStr">
+      <c r="C185" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D185" s="6" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="E185" s="5" t="inlineStr">
+      <c r="E185" s="6" t="inlineStr">
         <is>
           <t>14/07/2026</t>
         </is>
       </c>
-      <c r="F185" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G185" s="5" t="inlineStr"/>
-      <c r="H185" s="5" t="inlineStr">
+      <c r="F185" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G185" s="6" t="inlineStr"/>
+      <c r="H185" s="6" t="inlineStr">
         <is>
           <t>0/35</t>
         </is>
       </c>
-      <c r="I185" s="5" t="inlineStr">
+      <c r="I185" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B186" s="5" t="inlineStr">
+      <c r="A186" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B186" s="6" t="inlineStr">
         <is>
           <t>A1-D1</t>
         </is>
       </c>
-      <c r="C186" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D186" s="5" t="inlineStr">
+      <c r="C186" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D186" s="6" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="E186" s="5" t="inlineStr">
+      <c r="E186" s="6" t="inlineStr">
         <is>
           <t>15/07/2026</t>
         </is>
       </c>
-      <c r="F186" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G186" s="5" t="inlineStr"/>
-      <c r="H186" s="5" t="inlineStr">
+      <c r="F186" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G186" s="6" t="inlineStr"/>
+      <c r="H186" s="6" t="inlineStr">
         <is>
           <t>0/35</t>
         </is>
       </c>
-      <c r="I186" s="5" t="inlineStr">
+      <c r="I186" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B187" s="5" t="inlineStr">
+      <c r="A187" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B187" s="6" t="inlineStr">
         <is>
           <t>A1-D1</t>
         </is>
       </c>
-      <c r="C187" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D187" s="5" t="inlineStr">
+      <c r="C187" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D187" s="6" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="E187" s="5" t="inlineStr">
+      <c r="E187" s="6" t="inlineStr">
         <is>
           <t>16/07/2026</t>
         </is>
       </c>
-      <c r="F187" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G187" s="5" t="inlineStr"/>
-      <c r="H187" s="5" t="inlineStr">
+      <c r="F187" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G187" s="6" t="inlineStr"/>
+      <c r="H187" s="6" t="inlineStr">
         <is>
           <t>0/35</t>
         </is>
       </c>
-      <c r="I187" s="5" t="inlineStr">
+      <c r="I187" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B188" s="5" t="inlineStr">
+      <c r="A188" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B188" s="6" t="inlineStr">
         <is>
           <t>A1-D1</t>
         </is>
       </c>
-      <c r="C188" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D188" s="5" t="inlineStr">
+      <c r="C188" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D188" s="6" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="E188" s="5" t="inlineStr">
+      <c r="E188" s="6" t="inlineStr">
         <is>
           <t>21/07/2026</t>
         </is>
       </c>
-      <c r="F188" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G188" s="5" t="inlineStr"/>
-      <c r="H188" s="5" t="inlineStr">
+      <c r="F188" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G188" s="6" t="inlineStr"/>
+      <c r="H188" s="6" t="inlineStr">
         <is>
           <t>0/35</t>
         </is>
       </c>
-      <c r="I188" s="5" t="inlineStr">
+      <c r="I188" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B189" s="5" t="inlineStr">
+      <c r="A189" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B189" s="6" t="inlineStr">
         <is>
           <t>A1-D1</t>
         </is>
       </c>
-      <c r="C189" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D189" s="5" t="inlineStr">
+      <c r="C189" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D189" s="6" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="E189" s="5" t="inlineStr">
+      <c r="E189" s="6" t="inlineStr">
         <is>
           <t>22/07/2026</t>
         </is>
       </c>
-      <c r="F189" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G189" s="5" t="inlineStr"/>
-      <c r="H189" s="5" t="inlineStr">
+      <c r="F189" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G189" s="6" t="inlineStr"/>
+      <c r="H189" s="6" t="inlineStr">
         <is>
           <t>0/35</t>
         </is>
       </c>
-      <c r="I189" s="5" t="inlineStr">
+      <c r="I189" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B190" s="5" t="inlineStr">
+      <c r="A190" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B190" s="6" t="inlineStr">
         <is>
           <t>A1-D1</t>
         </is>
       </c>
-      <c r="C190" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D190" s="5" t="inlineStr">
+      <c r="C190" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D190" s="6" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="E190" s="5" t="inlineStr">
+      <c r="E190" s="6" t="inlineStr">
         <is>
           <t>23/07/2026</t>
         </is>
       </c>
-      <c r="F190" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G190" s="5" t="inlineStr"/>
-      <c r="H190" s="5" t="inlineStr">
+      <c r="F190" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G190" s="6" t="inlineStr"/>
+      <c r="H190" s="6" t="inlineStr">
         <is>
           <t>0/35</t>
         </is>
       </c>
-      <c r="I190" s="5" t="inlineStr">
+      <c r="I190" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -10096,43 +10096,43 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B196" s="9" t="inlineStr">
+      <c r="A196" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B196" s="5" t="inlineStr">
         <is>
           <t>A1-D2</t>
         </is>
       </c>
-      <c r="C196" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D196" s="9" t="inlineStr">
+      <c r="C196" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D196" s="5" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E196" s="9" t="inlineStr">
+      <c r="E196" s="5" t="inlineStr">
         <is>
           <t>04/06/2026</t>
         </is>
       </c>
-      <c r="F196" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G196" s="9" t="inlineStr"/>
-      <c r="H196" s="9" t="inlineStr">
+      <c r="F196" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G196" s="5" t="inlineStr"/>
+      <c r="H196" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I196" s="9" t="inlineStr">
+      <c r="I196" s="5" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
@@ -10750,43 +10750,43 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B210" s="9" t="inlineStr">
+      <c r="A210" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B210" s="5" t="inlineStr">
         <is>
           <t>A1-D2</t>
         </is>
       </c>
-      <c r="C210" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D210" s="9" t="inlineStr">
+      <c r="C210" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D210" s="5" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="E210" s="9" t="inlineStr">
+      <c r="E210" s="5" t="inlineStr">
         <is>
           <t>08/07/2026</t>
         </is>
       </c>
-      <c r="F210" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G210" s="9" t="inlineStr"/>
-      <c r="H210" s="9" t="inlineStr">
+      <c r="F210" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G210" s="5" t="inlineStr"/>
+      <c r="H210" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I210" s="9" t="inlineStr">
+      <c r="I210" s="5" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
@@ -10840,258 +10840,258 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B212" s="5" t="inlineStr">
+      <c r="A212" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B212" s="6" t="inlineStr">
         <is>
           <t>A1-D2</t>
         </is>
       </c>
-      <c r="C212" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D212" s="5" t="inlineStr">
+      <c r="C212" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D212" s="6" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="E212" s="5" t="inlineStr">
+      <c r="E212" s="6" t="inlineStr">
         <is>
           <t>14/07/2026</t>
         </is>
       </c>
-      <c r="F212" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G212" s="5" t="inlineStr"/>
-      <c r="H212" s="5" t="inlineStr">
+      <c r="F212" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G212" s="6" t="inlineStr"/>
+      <c r="H212" s="6" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I212" s="5" t="inlineStr">
+      <c r="I212" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B213" s="5" t="inlineStr">
+      <c r="A213" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B213" s="6" t="inlineStr">
         <is>
           <t>A1-D2</t>
         </is>
       </c>
-      <c r="C213" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D213" s="5" t="inlineStr">
+      <c r="C213" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D213" s="6" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="E213" s="5" t="inlineStr">
+      <c r="E213" s="6" t="inlineStr">
         <is>
           <t>15/07/2026</t>
         </is>
       </c>
-      <c r="F213" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G213" s="5" t="inlineStr"/>
-      <c r="H213" s="5" t="inlineStr">
+      <c r="F213" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G213" s="6" t="inlineStr"/>
+      <c r="H213" s="6" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I213" s="5" t="inlineStr">
+      <c r="I213" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B214" s="5" t="inlineStr">
+      <c r="A214" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B214" s="6" t="inlineStr">
         <is>
           <t>A1-D2</t>
         </is>
       </c>
-      <c r="C214" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D214" s="5" t="inlineStr">
+      <c r="C214" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D214" s="6" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="E214" s="5" t="inlineStr">
+      <c r="E214" s="6" t="inlineStr">
         <is>
           <t>16/07/2026</t>
         </is>
       </c>
-      <c r="F214" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G214" s="5" t="inlineStr"/>
-      <c r="H214" s="5" t="inlineStr">
+      <c r="F214" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G214" s="6" t="inlineStr"/>
+      <c r="H214" s="6" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I214" s="5" t="inlineStr">
+      <c r="I214" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B215" s="5" t="inlineStr">
+      <c r="A215" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B215" s="6" t="inlineStr">
         <is>
           <t>A1-D2</t>
         </is>
       </c>
-      <c r="C215" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D215" s="5" t="inlineStr">
+      <c r="C215" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D215" s="6" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="E215" s="5" t="inlineStr">
+      <c r="E215" s="6" t="inlineStr">
         <is>
           <t>21/07/2026</t>
         </is>
       </c>
-      <c r="F215" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G215" s="5" t="inlineStr"/>
-      <c r="H215" s="5" t="inlineStr">
+      <c r="F215" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G215" s="6" t="inlineStr"/>
+      <c r="H215" s="6" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I215" s="5" t="inlineStr">
+      <c r="I215" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B216" s="5" t="inlineStr">
+      <c r="A216" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B216" s="6" t="inlineStr">
         <is>
           <t>A1-D2</t>
         </is>
       </c>
-      <c r="C216" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D216" s="5" t="inlineStr">
+      <c r="C216" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D216" s="6" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="E216" s="5" t="inlineStr">
+      <c r="E216" s="6" t="inlineStr">
         <is>
           <t>22/07/2026</t>
         </is>
       </c>
-      <c r="F216" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G216" s="5" t="inlineStr"/>
-      <c r="H216" s="5" t="inlineStr">
+      <c r="F216" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G216" s="6" t="inlineStr"/>
+      <c r="H216" s="6" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I216" s="5" t="inlineStr">
+      <c r="I216" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B217" s="5" t="inlineStr">
+      <c r="A217" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B217" s="6" t="inlineStr">
         <is>
           <t>A1-D2</t>
         </is>
       </c>
-      <c r="C217" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D217" s="5" t="inlineStr">
+      <c r="C217" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D217" s="6" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="E217" s="5" t="inlineStr">
+      <c r="E217" s="6" t="inlineStr">
         <is>
           <t>23/07/2026</t>
         </is>
       </c>
-      <c r="F217" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G217" s="5" t="inlineStr"/>
-      <c r="H217" s="5" t="inlineStr">
+      <c r="F217" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G217" s="6" t="inlineStr"/>
+      <c r="H217" s="6" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I217" s="5" t="inlineStr">
+      <c r="I217" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -11333,43 +11333,43 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B223" s="9" t="inlineStr">
+      <c r="A223" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B223" s="5" t="inlineStr">
         <is>
           <t>A1-E1</t>
         </is>
       </c>
-      <c r="C223" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D223" s="9" t="inlineStr">
+      <c r="C223" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D223" s="5" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E223" s="9" t="inlineStr">
+      <c r="E223" s="5" t="inlineStr">
         <is>
           <t>04/06/2026</t>
         </is>
       </c>
-      <c r="F223" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G223" s="9" t="inlineStr"/>
-      <c r="H223" s="9" t="inlineStr">
+      <c r="F223" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G223" s="5" t="inlineStr"/>
+      <c r="H223" s="5" t="inlineStr">
         <is>
           <t>0/38</t>
         </is>
       </c>
-      <c r="I223" s="9" t="inlineStr">
+      <c r="I223" s="5" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
@@ -12034,301 +12034,301 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B238" s="9" t="inlineStr">
+      <c r="A238" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B238" s="5" t="inlineStr">
         <is>
           <t>A1-E1</t>
         </is>
       </c>
-      <c r="C238" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D238" s="9" t="inlineStr">
+      <c r="C238" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D238" s="5" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="E238" s="9" t="inlineStr">
+      <c r="E238" s="5" t="inlineStr">
         <is>
           <t>09/07/2026</t>
         </is>
       </c>
-      <c r="F238" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G238" s="9" t="inlineStr"/>
-      <c r="H238" s="9" t="inlineStr">
+      <c r="F238" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G238" s="5" t="inlineStr"/>
+      <c r="H238" s="5" t="inlineStr">
         <is>
           <t>0/38</t>
         </is>
       </c>
-      <c r="I238" s="9" t="inlineStr">
+      <c r="I238" s="5" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B239" s="5" t="inlineStr">
+      <c r="A239" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B239" s="6" t="inlineStr">
         <is>
           <t>A1-E1</t>
         </is>
       </c>
-      <c r="C239" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D239" s="5" t="inlineStr">
+      <c r="C239" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D239" s="6" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="E239" s="5" t="inlineStr">
+      <c r="E239" s="6" t="inlineStr">
         <is>
           <t>14/07/2026</t>
         </is>
       </c>
-      <c r="F239" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G239" s="5" t="inlineStr"/>
-      <c r="H239" s="5" t="inlineStr">
+      <c r="F239" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G239" s="6" t="inlineStr"/>
+      <c r="H239" s="6" t="inlineStr">
         <is>
           <t>0/38</t>
         </is>
       </c>
-      <c r="I239" s="5" t="inlineStr">
+      <c r="I239" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B240" s="5" t="inlineStr">
+      <c r="A240" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B240" s="6" t="inlineStr">
         <is>
           <t>A1-E1</t>
         </is>
       </c>
-      <c r="C240" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D240" s="5" t="inlineStr">
+      <c r="C240" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D240" s="6" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="E240" s="5" t="inlineStr">
+      <c r="E240" s="6" t="inlineStr">
         <is>
           <t>15/07/2026</t>
         </is>
       </c>
-      <c r="F240" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G240" s="5" t="inlineStr"/>
-      <c r="H240" s="5" t="inlineStr">
+      <c r="F240" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G240" s="6" t="inlineStr"/>
+      <c r="H240" s="6" t="inlineStr">
         <is>
           <t>0/38</t>
         </is>
       </c>
-      <c r="I240" s="5" t="inlineStr">
+      <c r="I240" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B241" s="5" t="inlineStr">
+      <c r="A241" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B241" s="6" t="inlineStr">
         <is>
           <t>A1-E1</t>
         </is>
       </c>
-      <c r="C241" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D241" s="5" t="inlineStr">
+      <c r="C241" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D241" s="6" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="E241" s="5" t="inlineStr">
+      <c r="E241" s="6" t="inlineStr">
         <is>
           <t>16/07/2026</t>
         </is>
       </c>
-      <c r="F241" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G241" s="5" t="inlineStr"/>
-      <c r="H241" s="5" t="inlineStr">
+      <c r="F241" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G241" s="6" t="inlineStr"/>
+      <c r="H241" s="6" t="inlineStr">
         <is>
           <t>0/38</t>
         </is>
       </c>
-      <c r="I241" s="5" t="inlineStr">
+      <c r="I241" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B242" s="5" t="inlineStr">
+      <c r="A242" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B242" s="6" t="inlineStr">
         <is>
           <t>A1-E1</t>
         </is>
       </c>
-      <c r="C242" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D242" s="5" t="inlineStr">
+      <c r="C242" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D242" s="6" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="E242" s="5" t="inlineStr">
+      <c r="E242" s="6" t="inlineStr">
         <is>
           <t>21/07/2026</t>
         </is>
       </c>
-      <c r="F242" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G242" s="5" t="inlineStr"/>
-      <c r="H242" s="5" t="inlineStr">
+      <c r="F242" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G242" s="6" t="inlineStr"/>
+      <c r="H242" s="6" t="inlineStr">
         <is>
           <t>0/38</t>
         </is>
       </c>
-      <c r="I242" s="5" t="inlineStr">
+      <c r="I242" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B243" s="5" t="inlineStr">
+      <c r="A243" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B243" s="6" t="inlineStr">
         <is>
           <t>A1-E1</t>
         </is>
       </c>
-      <c r="C243" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D243" s="5" t="inlineStr">
+      <c r="C243" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D243" s="6" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="E243" s="5" t="inlineStr">
+      <c r="E243" s="6" t="inlineStr">
         <is>
           <t>22/07/2026</t>
         </is>
       </c>
-      <c r="F243" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G243" s="5" t="inlineStr"/>
-      <c r="H243" s="5" t="inlineStr">
+      <c r="F243" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G243" s="6" t="inlineStr"/>
+      <c r="H243" s="6" t="inlineStr">
         <is>
           <t>0/38</t>
         </is>
       </c>
-      <c r="I243" s="5" t="inlineStr">
+      <c r="I243" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B244" s="5" t="inlineStr">
+      <c r="A244" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B244" s="6" t="inlineStr">
         <is>
           <t>A1-E1</t>
         </is>
       </c>
-      <c r="C244" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D244" s="5" t="inlineStr">
+      <c r="C244" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D244" s="6" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="E244" s="5" t="inlineStr">
+      <c r="E244" s="6" t="inlineStr">
         <is>
           <t>23/07/2026</t>
         </is>
       </c>
-      <c r="F244" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G244" s="5" t="inlineStr"/>
-      <c r="H244" s="5" t="inlineStr">
+      <c r="F244" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G244" s="6" t="inlineStr"/>
+      <c r="H244" s="6" t="inlineStr">
         <is>
           <t>0/38</t>
         </is>
       </c>
-      <c r="I244" s="5" t="inlineStr">
+      <c r="I244" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -12570,43 +12570,43 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B250" s="9" t="inlineStr">
+      <c r="A250" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B250" s="5" t="inlineStr">
         <is>
           <t>A1-E2</t>
         </is>
       </c>
-      <c r="C250" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D250" s="9" t="inlineStr">
+      <c r="C250" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D250" s="5" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E250" s="9" t="inlineStr">
+      <c r="E250" s="5" t="inlineStr">
         <is>
           <t>04/06/2026</t>
         </is>
       </c>
-      <c r="F250" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G250" s="9" t="inlineStr"/>
-      <c r="H250" s="9" t="inlineStr">
+      <c r="F250" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G250" s="5" t="inlineStr"/>
+      <c r="H250" s="5" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I250" s="9" t="inlineStr">
+      <c r="I250" s="5" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
@@ -13271,301 +13271,301 @@
       </c>
     </row>
     <row r="265">
-      <c r="A265" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B265" s="9" t="inlineStr">
+      <c r="A265" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B265" s="5" t="inlineStr">
         <is>
           <t>A1-E2</t>
         </is>
       </c>
-      <c r="C265" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D265" s="9" t="inlineStr">
+      <c r="C265" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D265" s="5" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="E265" s="9" t="inlineStr">
+      <c r="E265" s="5" t="inlineStr">
         <is>
           <t>09/07/2026</t>
         </is>
       </c>
-      <c r="F265" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G265" s="9" t="inlineStr"/>
-      <c r="H265" s="9" t="inlineStr">
+      <c r="F265" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G265" s="5" t="inlineStr"/>
+      <c r="H265" s="5" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I265" s="9" t="inlineStr">
+      <c r="I265" s="5" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
       </c>
     </row>
     <row r="266">
-      <c r="A266" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B266" s="5" t="inlineStr">
+      <c r="A266" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B266" s="6" t="inlineStr">
         <is>
           <t>A1-E2</t>
         </is>
       </c>
-      <c r="C266" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D266" s="5" t="inlineStr">
+      <c r="C266" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D266" s="6" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="E266" s="5" t="inlineStr">
+      <c r="E266" s="6" t="inlineStr">
         <is>
           <t>14/07/2026</t>
         </is>
       </c>
-      <c r="F266" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G266" s="5" t="inlineStr"/>
-      <c r="H266" s="5" t="inlineStr">
+      <c r="F266" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G266" s="6" t="inlineStr"/>
+      <c r="H266" s="6" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I266" s="5" t="inlineStr">
+      <c r="I266" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="267">
-      <c r="A267" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B267" s="5" t="inlineStr">
+      <c r="A267" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B267" s="6" t="inlineStr">
         <is>
           <t>A1-E2</t>
         </is>
       </c>
-      <c r="C267" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D267" s="5" t="inlineStr">
+      <c r="C267" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D267" s="6" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="E267" s="5" t="inlineStr">
+      <c r="E267" s="6" t="inlineStr">
         <is>
           <t>15/07/2026</t>
         </is>
       </c>
-      <c r="F267" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G267" s="5" t="inlineStr"/>
-      <c r="H267" s="5" t="inlineStr">
+      <c r="F267" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G267" s="6" t="inlineStr"/>
+      <c r="H267" s="6" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I267" s="5" t="inlineStr">
+      <c r="I267" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="268">
-      <c r="A268" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B268" s="5" t="inlineStr">
+      <c r="A268" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B268" s="6" t="inlineStr">
         <is>
           <t>A1-E2</t>
         </is>
       </c>
-      <c r="C268" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D268" s="5" t="inlineStr">
+      <c r="C268" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D268" s="6" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="E268" s="5" t="inlineStr">
+      <c r="E268" s="6" t="inlineStr">
         <is>
           <t>16/07/2026</t>
         </is>
       </c>
-      <c r="F268" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G268" s="5" t="inlineStr"/>
-      <c r="H268" s="5" t="inlineStr">
+      <c r="F268" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G268" s="6" t="inlineStr"/>
+      <c r="H268" s="6" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I268" s="5" t="inlineStr">
+      <c r="I268" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="269">
-      <c r="A269" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B269" s="5" t="inlineStr">
+      <c r="A269" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B269" s="6" t="inlineStr">
         <is>
           <t>A1-E2</t>
         </is>
       </c>
-      <c r="C269" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D269" s="5" t="inlineStr">
+      <c r="C269" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D269" s="6" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="E269" s="5" t="inlineStr">
+      <c r="E269" s="6" t="inlineStr">
         <is>
           <t>21/07/2026</t>
         </is>
       </c>
-      <c r="F269" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G269" s="5" t="inlineStr"/>
-      <c r="H269" s="5" t="inlineStr">
+      <c r="F269" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G269" s="6" t="inlineStr"/>
+      <c r="H269" s="6" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I269" s="5" t="inlineStr">
+      <c r="I269" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="270">
-      <c r="A270" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B270" s="5" t="inlineStr">
+      <c r="A270" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B270" s="6" t="inlineStr">
         <is>
           <t>A1-E2</t>
         </is>
       </c>
-      <c r="C270" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D270" s="5" t="inlineStr">
+      <c r="C270" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D270" s="6" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="E270" s="5" t="inlineStr">
+      <c r="E270" s="6" t="inlineStr">
         <is>
           <t>22/07/2026</t>
         </is>
       </c>
-      <c r="F270" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G270" s="5" t="inlineStr"/>
-      <c r="H270" s="5" t="inlineStr">
+      <c r="F270" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G270" s="6" t="inlineStr"/>
+      <c r="H270" s="6" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I270" s="5" t="inlineStr">
+      <c r="I270" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="271">
-      <c r="A271" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B271" s="5" t="inlineStr">
+      <c r="A271" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B271" s="6" t="inlineStr">
         <is>
           <t>A1-E2</t>
         </is>
       </c>
-      <c r="C271" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D271" s="5" t="inlineStr">
+      <c r="C271" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D271" s="6" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="E271" s="5" t="inlineStr">
+      <c r="E271" s="6" t="inlineStr">
         <is>
           <t>23/07/2026</t>
         </is>
       </c>
-      <c r="F271" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G271" s="5" t="inlineStr"/>
-      <c r="H271" s="5" t="inlineStr">
+      <c r="F271" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G271" s="6" t="inlineStr"/>
+      <c r="H271" s="6" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I271" s="5" t="inlineStr">
+      <c r="I271" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -13807,43 +13807,43 @@
       </c>
     </row>
     <row r="277">
-      <c r="A277" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B277" s="9" t="inlineStr">
+      <c r="A277" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B277" s="5" t="inlineStr">
         <is>
           <t>A1-F1</t>
         </is>
       </c>
-      <c r="C277" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D277" s="9" t="inlineStr">
+      <c r="C277" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D277" s="5" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E277" s="9" t="inlineStr">
+      <c r="E277" s="5" t="inlineStr">
         <is>
           <t>04/06/2026</t>
         </is>
       </c>
-      <c r="F277" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G277" s="9" t="inlineStr"/>
-      <c r="H277" s="9" t="inlineStr">
+      <c r="F277" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G277" s="5" t="inlineStr"/>
+      <c r="H277" s="5" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I277" s="9" t="inlineStr">
+      <c r="I277" s="5" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
@@ -14555,258 +14555,258 @@
       </c>
     </row>
     <row r="293">
-      <c r="A293" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B293" s="5" t="inlineStr">
+      <c r="A293" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B293" s="6" t="inlineStr">
         <is>
           <t>A1-F1</t>
         </is>
       </c>
-      <c r="C293" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D293" s="5" t="inlineStr">
+      <c r="C293" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D293" s="6" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="E293" s="5" t="inlineStr">
+      <c r="E293" s="6" t="inlineStr">
         <is>
           <t>14/07/2026</t>
         </is>
       </c>
-      <c r="F293" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G293" s="5" t="inlineStr"/>
-      <c r="H293" s="5" t="inlineStr">
+      <c r="F293" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G293" s="6" t="inlineStr"/>
+      <c r="H293" s="6" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I293" s="5" t="inlineStr">
+      <c r="I293" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="294">
-      <c r="A294" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B294" s="5" t="inlineStr">
+      <c r="A294" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B294" s="6" t="inlineStr">
         <is>
           <t>A1-F1</t>
         </is>
       </c>
-      <c r="C294" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D294" s="5" t="inlineStr">
+      <c r="C294" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D294" s="6" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="E294" s="5" t="inlineStr">
+      <c r="E294" s="6" t="inlineStr">
         <is>
           <t>15/07/2026</t>
         </is>
       </c>
-      <c r="F294" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G294" s="5" t="inlineStr"/>
-      <c r="H294" s="5" t="inlineStr">
+      <c r="F294" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G294" s="6" t="inlineStr"/>
+      <c r="H294" s="6" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I294" s="5" t="inlineStr">
+      <c r="I294" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="295">
-      <c r="A295" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B295" s="5" t="inlineStr">
+      <c r="A295" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B295" s="6" t="inlineStr">
         <is>
           <t>A1-F1</t>
         </is>
       </c>
-      <c r="C295" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D295" s="5" t="inlineStr">
+      <c r="C295" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D295" s="6" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="E295" s="5" t="inlineStr">
+      <c r="E295" s="6" t="inlineStr">
         <is>
           <t>16/07/2026</t>
         </is>
       </c>
-      <c r="F295" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G295" s="5" t="inlineStr"/>
-      <c r="H295" s="5" t="inlineStr">
+      <c r="F295" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G295" s="6" t="inlineStr"/>
+      <c r="H295" s="6" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I295" s="5" t="inlineStr">
+      <c r="I295" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="296">
-      <c r="A296" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B296" s="5" t="inlineStr">
+      <c r="A296" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B296" s="6" t="inlineStr">
         <is>
           <t>A1-F1</t>
         </is>
       </c>
-      <c r="C296" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D296" s="5" t="inlineStr">
+      <c r="C296" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D296" s="6" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="E296" s="5" t="inlineStr">
+      <c r="E296" s="6" t="inlineStr">
         <is>
           <t>21/07/2026</t>
         </is>
       </c>
-      <c r="F296" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G296" s="5" t="inlineStr"/>
-      <c r="H296" s="5" t="inlineStr">
+      <c r="F296" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G296" s="6" t="inlineStr"/>
+      <c r="H296" s="6" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I296" s="5" t="inlineStr">
+      <c r="I296" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="297">
-      <c r="A297" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B297" s="5" t="inlineStr">
+      <c r="A297" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B297" s="6" t="inlineStr">
         <is>
           <t>A1-F1</t>
         </is>
       </c>
-      <c r="C297" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D297" s="5" t="inlineStr">
+      <c r="C297" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D297" s="6" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="E297" s="5" t="inlineStr">
+      <c r="E297" s="6" t="inlineStr">
         <is>
           <t>22/07/2026</t>
         </is>
       </c>
-      <c r="F297" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G297" s="5" t="inlineStr"/>
-      <c r="H297" s="5" t="inlineStr">
+      <c r="F297" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G297" s="6" t="inlineStr"/>
+      <c r="H297" s="6" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I297" s="5" t="inlineStr">
+      <c r="I297" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="298">
-      <c r="A298" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B298" s="5" t="inlineStr">
+      <c r="A298" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B298" s="6" t="inlineStr">
         <is>
           <t>A1-F1</t>
         </is>
       </c>
-      <c r="C298" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D298" s="5" t="inlineStr">
+      <c r="C298" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D298" s="6" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="E298" s="5" t="inlineStr">
+      <c r="E298" s="6" t="inlineStr">
         <is>
           <t>23/07/2026</t>
         </is>
       </c>
-      <c r="F298" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G298" s="5" t="inlineStr"/>
-      <c r="H298" s="5" t="inlineStr">
+      <c r="F298" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G298" s="6" t="inlineStr"/>
+      <c r="H298" s="6" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I298" s="5" t="inlineStr">
+      <c r="I298" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -15048,43 +15048,43 @@
       </c>
     </row>
     <row r="304">
-      <c r="A304" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B304" s="9" t="inlineStr">
+      <c r="A304" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B304" s="5" t="inlineStr">
         <is>
           <t>A1-F2</t>
         </is>
       </c>
-      <c r="C304" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D304" s="9" t="inlineStr">
+      <c r="C304" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D304" s="5" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E304" s="9" t="inlineStr">
+      <c r="E304" s="5" t="inlineStr">
         <is>
           <t>04/06/2026</t>
         </is>
       </c>
-      <c r="F304" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G304" s="9" t="inlineStr"/>
-      <c r="H304" s="9" t="inlineStr">
+      <c r="F304" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G304" s="5" t="inlineStr"/>
+      <c r="H304" s="5" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I304" s="9" t="inlineStr">
+      <c r="I304" s="5" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
@@ -15655,43 +15655,43 @@
       </c>
     </row>
     <row r="317">
-      <c r="A317" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B317" s="9" t="inlineStr">
+      <c r="A317" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B317" s="5" t="inlineStr">
         <is>
           <t>A1-F2</t>
         </is>
       </c>
-      <c r="C317" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D317" s="9" t="inlineStr">
+      <c r="C317" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D317" s="5" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="E317" s="9" t="inlineStr">
+      <c r="E317" s="5" t="inlineStr">
         <is>
           <t>07/07/2026</t>
         </is>
       </c>
-      <c r="F317" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G317" s="9" t="inlineStr"/>
-      <c r="H317" s="9" t="inlineStr">
+      <c r="F317" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G317" s="5" t="inlineStr"/>
+      <c r="H317" s="5" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I317" s="9" t="inlineStr">
+      <c r="I317" s="5" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
@@ -15792,258 +15792,258 @@
       </c>
     </row>
     <row r="320">
-      <c r="A320" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B320" s="5" t="inlineStr">
+      <c r="A320" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B320" s="6" t="inlineStr">
         <is>
           <t>A1-F2</t>
         </is>
       </c>
-      <c r="C320" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D320" s="5" t="inlineStr">
+      <c r="C320" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D320" s="6" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="E320" s="5" t="inlineStr">
+      <c r="E320" s="6" t="inlineStr">
         <is>
           <t>14/07/2026</t>
         </is>
       </c>
-      <c r="F320" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G320" s="5" t="inlineStr"/>
-      <c r="H320" s="5" t="inlineStr">
+      <c r="F320" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G320" s="6" t="inlineStr"/>
+      <c r="H320" s="6" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I320" s="5" t="inlineStr">
+      <c r="I320" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="321">
-      <c r="A321" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B321" s="5" t="inlineStr">
+      <c r="A321" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B321" s="6" t="inlineStr">
         <is>
           <t>A1-F2</t>
         </is>
       </c>
-      <c r="C321" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D321" s="5" t="inlineStr">
+      <c r="C321" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D321" s="6" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="E321" s="5" t="inlineStr">
+      <c r="E321" s="6" t="inlineStr">
         <is>
           <t>15/07/2026</t>
         </is>
       </c>
-      <c r="F321" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G321" s="5" t="inlineStr"/>
-      <c r="H321" s="5" t="inlineStr">
+      <c r="F321" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G321" s="6" t="inlineStr"/>
+      <c r="H321" s="6" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I321" s="5" t="inlineStr">
+      <c r="I321" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="322">
-      <c r="A322" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B322" s="5" t="inlineStr">
+      <c r="A322" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B322" s="6" t="inlineStr">
         <is>
           <t>A1-F2</t>
         </is>
       </c>
-      <c r="C322" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D322" s="5" t="inlineStr">
+      <c r="C322" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D322" s="6" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="E322" s="5" t="inlineStr">
+      <c r="E322" s="6" t="inlineStr">
         <is>
           <t>16/07/2026</t>
         </is>
       </c>
-      <c r="F322" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G322" s="5" t="inlineStr"/>
-      <c r="H322" s="5" t="inlineStr">
+      <c r="F322" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G322" s="6" t="inlineStr"/>
+      <c r="H322" s="6" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I322" s="5" t="inlineStr">
+      <c r="I322" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="323">
-      <c r="A323" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B323" s="5" t="inlineStr">
+      <c r="A323" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B323" s="6" t="inlineStr">
         <is>
           <t>A1-F2</t>
         </is>
       </c>
-      <c r="C323" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D323" s="5" t="inlineStr">
+      <c r="C323" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D323" s="6" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="E323" s="5" t="inlineStr">
+      <c r="E323" s="6" t="inlineStr">
         <is>
           <t>21/07/2026</t>
         </is>
       </c>
-      <c r="F323" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G323" s="5" t="inlineStr"/>
-      <c r="H323" s="5" t="inlineStr">
+      <c r="F323" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G323" s="6" t="inlineStr"/>
+      <c r="H323" s="6" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I323" s="5" t="inlineStr">
+      <c r="I323" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="324">
-      <c r="A324" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B324" s="5" t="inlineStr">
+      <c r="A324" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B324" s="6" t="inlineStr">
         <is>
           <t>A1-F2</t>
         </is>
       </c>
-      <c r="C324" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D324" s="5" t="inlineStr">
+      <c r="C324" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D324" s="6" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="E324" s="5" t="inlineStr">
+      <c r="E324" s="6" t="inlineStr">
         <is>
           <t>22/07/2026</t>
         </is>
       </c>
-      <c r="F324" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G324" s="5" t="inlineStr"/>
-      <c r="H324" s="5" t="inlineStr">
+      <c r="F324" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G324" s="6" t="inlineStr"/>
+      <c r="H324" s="6" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I324" s="5" t="inlineStr">
+      <c r="I324" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="325">
-      <c r="A325" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B325" s="5" t="inlineStr">
+      <c r="A325" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B325" s="6" t="inlineStr">
         <is>
           <t>A1-F2</t>
         </is>
       </c>
-      <c r="C325" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D325" s="5" t="inlineStr">
+      <c r="C325" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D325" s="6" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="E325" s="5" t="inlineStr">
+      <c r="E325" s="6" t="inlineStr">
         <is>
           <t>23/07/2026</t>
         </is>
       </c>
-      <c r="F325" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G325" s="5" t="inlineStr"/>
-      <c r="H325" s="5" t="inlineStr">
+      <c r="F325" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G325" s="6" t="inlineStr"/>
+      <c r="H325" s="6" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I325" s="5" t="inlineStr">
+      <c r="I325" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A1_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A1_session_analysis.xlsx
@@ -58,14 +58,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFB6C1"/>
-        <bgColor rgb="00FFB6C1"/>
+        <fgColor rgb="00FFFFE0"/>
+        <bgColor rgb="00FFFFE0"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFFE0"/>
-        <bgColor rgb="00FFFFE0"/>
+        <fgColor rgb="00FFB6C1"/>
+        <bgColor rgb="00FFB6C1"/>
       </patternFill>
     </fill>
   </fills>
@@ -96,16 +96,16 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -814,7 +814,7 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>241</v>
+        <v>247</v>
       </c>
     </row>
     <row r="7">
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8">
@@ -980,7 +980,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>74.4%</t>
+          <t>76.2%</t>
         </is>
       </c>
     </row>
@@ -1037,7 +1037,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>75.2%</t>
+          <t>74.6%</t>
         </is>
       </c>
     </row>
@@ -1342,22 +1342,22 @@
         <v>27</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q15" s="4" t="n">
         <v>5</v>
       </c>
       <c r="R15" s="4" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>81.5%</t>
         </is>
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>70.2%</t>
         </is>
       </c>
     </row>
@@ -1424,22 +1424,22 @@
         <v>27</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q16" s="4" t="n">
         <v>5</v>
       </c>
       <c r="R16" s="4" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>81.5%</t>
         </is>
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>72.0%</t>
+          <t>70.9%</t>
         </is>
       </c>
     </row>
@@ -1506,22 +1506,22 @@
         <v>27</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q17" s="4" t="n">
         <v>5</v>
       </c>
       <c r="R17" s="4" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>81.5%</t>
         </is>
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>77.6%</t>
+          <t>76.1%</t>
         </is>
       </c>
     </row>
@@ -1588,22 +1588,22 @@
         <v>27</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q18" s="4" t="n">
         <v>5</v>
       </c>
       <c r="R18" s="4" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>81.5%</t>
         </is>
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>75.4%</t>
+          <t>74.5%</t>
         </is>
       </c>
     </row>
@@ -1670,22 +1670,22 @@
         <v>27</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q19" s="4" t="n">
         <v>5</v>
       </c>
       <c r="R19" s="4" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>81.5%</t>
         </is>
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>78.2%</t>
+          <t>77.0%</t>
         </is>
       </c>
     </row>
@@ -1752,22 +1752,22 @@
         <v>27</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q20" s="4" t="n">
         <v>5</v>
       </c>
       <c r="R20" s="4" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>81.5%</t>
         </is>
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>70.6%</t>
+          <t>69.7%</t>
         </is>
       </c>
     </row>
@@ -1936,45 +1936,49 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="inlineStr">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>A1-A1</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="E23" s="5" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>11/07/2026</t>
         </is>
       </c>
-      <c r="F23" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G23" s="5" t="inlineStr"/>
-      <c r="H23" s="5" t="inlineStr">
-        <is>
-          <t>0/34</t>
-        </is>
-      </c>
-      <c r="I23" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>15/34</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
       <c r="K23" s="4" t="inlineStr">
@@ -2014,43 +2018,43 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B24" s="6" t="inlineStr">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
         <is>
           <t>A1-A1</t>
         </is>
       </c>
-      <c r="C24" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D24" s="6" t="inlineStr">
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="E24" s="6" t="inlineStr">
+      <c r="E24" s="5" t="inlineStr">
         <is>
           <t>12/07/2026</t>
         </is>
       </c>
-      <c r="F24" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G24" s="6" t="inlineStr"/>
-      <c r="H24" s="6" t="inlineStr">
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="inlineStr"/>
+      <c r="H24" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I24" s="6" t="inlineStr">
+      <c r="I24" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -2092,43 +2096,43 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B25" s="6" t="inlineStr">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
         <is>
           <t>A1-A1</t>
         </is>
       </c>
-      <c r="C25" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D25" s="6" t="inlineStr">
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="E25" s="6" t="inlineStr">
+      <c r="E25" s="5" t="inlineStr">
         <is>
           <t>13/07/2026</t>
         </is>
       </c>
-      <c r="F25" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G25" s="6" t="inlineStr"/>
-      <c r="H25" s="6" t="inlineStr">
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr"/>
+      <c r="H25" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I25" s="6" t="inlineStr">
+      <c r="I25" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -2170,43 +2174,43 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B26" s="6" t="inlineStr">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
         <is>
           <t>A1-A1</t>
         </is>
       </c>
-      <c r="C26" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D26" s="6" t="inlineStr">
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="E26" s="6" t="inlineStr">
+      <c r="E26" s="5" t="inlineStr">
         <is>
           <t>18/07/2026</t>
         </is>
       </c>
-      <c r="F26" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G26" s="6" t="inlineStr"/>
-      <c r="H26" s="6" t="inlineStr">
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="inlineStr"/>
+      <c r="H26" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I26" s="6" t="inlineStr">
+      <c r="I26" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -2248,86 +2252,86 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B27" s="6" t="inlineStr">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
         <is>
           <t>A1-A1</t>
         </is>
       </c>
-      <c r="C27" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D27" s="6" t="inlineStr">
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="E27" s="6" t="inlineStr">
+      <c r="E27" s="5" t="inlineStr">
         <is>
           <t>19/07/2026</t>
         </is>
       </c>
-      <c r="F27" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G27" s="6" t="inlineStr"/>
-      <c r="H27" s="6" t="inlineStr">
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="inlineStr"/>
+      <c r="H27" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I27" s="6" t="inlineStr">
+      <c r="I27" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B28" s="6" t="inlineStr">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
         <is>
           <t>A1-A1</t>
         </is>
       </c>
-      <c r="C28" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D28" s="6" t="inlineStr">
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="E28" s="6" t="inlineStr">
+      <c r="E28" s="5" t="inlineStr">
         <is>
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="F28" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G28" s="6" t="inlineStr"/>
-      <c r="H28" s="6" t="inlineStr">
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G28" s="5" t="inlineStr"/>
+      <c r="H28" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I28" s="6" t="inlineStr">
+      <c r="I28" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -2498,7 +2502,7 @@
           <t>Recorded</t>
         </is>
       </c>
-      <c r="L31" s="7" t="inlineStr">
+      <c r="L31" s="6" t="inlineStr">
         <is>
           <t>Green</t>
         </is>
@@ -2560,7 +2564,7 @@
           <t>Not Recorded</t>
         </is>
       </c>
-      <c r="L32" s="8" t="inlineStr">
+      <c r="L32" s="7" t="inlineStr">
         <is>
           <t>Red</t>
         </is>
@@ -2622,7 +2626,7 @@
           <t>Pending</t>
         </is>
       </c>
-      <c r="L33" s="9" t="inlineStr">
+      <c r="L33" s="8" t="inlineStr">
         <is>
           <t>Yellow</t>
         </is>
@@ -3386,258 +3390,262 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B50" s="5" t="inlineStr">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>A1-A2</t>
         </is>
       </c>
-      <c r="C50" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D50" s="5" t="inlineStr">
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="E50" s="5" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>11/07/2026</t>
         </is>
       </c>
-      <c r="F50" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G50" s="5" t="inlineStr"/>
-      <c r="H50" s="5" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>16/33</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>A1-A2</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="E51" s="5" t="inlineStr">
+        <is>
+          <t>12/07/2026</t>
+        </is>
+      </c>
+      <c r="F51" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G51" s="5" t="inlineStr"/>
+      <c r="H51" s="5" t="inlineStr">
         <is>
           <t>0/33</t>
         </is>
       </c>
-      <c r="I50" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B51" s="6" t="inlineStr">
+      <c r="I51" s="5" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="inlineStr">
         <is>
           <t>A1-A2</t>
         </is>
       </c>
-      <c r="C51" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D51" s="6" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="E51" s="6" t="inlineStr">
-        <is>
-          <t>12/07/2026</t>
-        </is>
-      </c>
-      <c r="F51" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G51" s="6" t="inlineStr"/>
-      <c r="H51" s="6" t="inlineStr">
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D52" s="5" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="E52" s="5" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="F52" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G52" s="5" t="inlineStr"/>
+      <c r="H52" s="5" t="inlineStr">
         <is>
           <t>0/33</t>
         </is>
       </c>
-      <c r="I51" s="6" t="inlineStr">
+      <c r="I52" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B52" s="6" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
         <is>
           <t>A1-A2</t>
         </is>
       </c>
-      <c r="C52" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D52" s="6" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="E52" s="6" t="inlineStr">
-        <is>
-          <t>13/07/2026</t>
-        </is>
-      </c>
-      <c r="F52" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G52" s="6" t="inlineStr"/>
-      <c r="H52" s="6" t="inlineStr">
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D53" s="5" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E53" s="5" t="inlineStr">
+        <is>
+          <t>18/07/2026</t>
+        </is>
+      </c>
+      <c r="F53" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G53" s="5" t="inlineStr"/>
+      <c r="H53" s="5" t="inlineStr">
         <is>
           <t>0/33</t>
         </is>
       </c>
-      <c r="I52" s="6" t="inlineStr">
+      <c r="I53" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B53" s="6" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="inlineStr">
         <is>
           <t>A1-A2</t>
         </is>
       </c>
-      <c r="C53" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D53" s="6" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="E53" s="6" t="inlineStr">
-        <is>
-          <t>18/07/2026</t>
-        </is>
-      </c>
-      <c r="F53" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G53" s="6" t="inlineStr"/>
-      <c r="H53" s="6" t="inlineStr">
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D54" s="5" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="E54" s="5" t="inlineStr">
+        <is>
+          <t>19/07/2026</t>
+        </is>
+      </c>
+      <c r="F54" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G54" s="5" t="inlineStr"/>
+      <c r="H54" s="5" t="inlineStr">
         <is>
           <t>0/33</t>
         </is>
       </c>
-      <c r="I53" s="6" t="inlineStr">
+      <c r="I54" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B54" s="6" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="inlineStr">
         <is>
           <t>A1-A2</t>
         </is>
       </c>
-      <c r="C54" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D54" s="6" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="E54" s="6" t="inlineStr">
-        <is>
-          <t>19/07/2026</t>
-        </is>
-      </c>
-      <c r="F54" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G54" s="6" t="inlineStr"/>
-      <c r="H54" s="6" t="inlineStr">
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D55" s="5" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E55" s="5" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="F55" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G55" s="5" t="inlineStr"/>
+      <c r="H55" s="5" t="inlineStr">
         <is>
           <t>0/33</t>
         </is>
       </c>
-      <c r="I54" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B55" s="6" t="inlineStr">
-        <is>
-          <t>A1-A2</t>
-        </is>
-      </c>
-      <c r="C55" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D55" s="6" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="E55" s="6" t="inlineStr">
-        <is>
-          <t>20/07/2026</t>
-        </is>
-      </c>
-      <c r="F55" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G55" s="6" t="inlineStr"/>
-      <c r="H55" s="6" t="inlineStr">
-        <is>
-          <t>0/33</t>
-        </is>
-      </c>
-      <c r="I55" s="6" t="inlineStr">
+      <c r="I55" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -4631,258 +4639,262 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B77" s="5" t="inlineStr">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
         <is>
           <t>A1-B1</t>
         </is>
       </c>
-      <c r="C77" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D77" s="5" t="inlineStr">
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="E77" s="5" t="inlineStr">
+      <c r="E77" s="2" t="inlineStr">
         <is>
           <t>11/07/2026</t>
         </is>
       </c>
-      <c r="F77" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G77" s="5" t="inlineStr"/>
-      <c r="H77" s="5" t="inlineStr">
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>15/34</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B78" s="5" t="inlineStr">
+        <is>
+          <t>A1-B1</t>
+        </is>
+      </c>
+      <c r="C78" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D78" s="5" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="E78" s="5" t="inlineStr">
+        <is>
+          <t>12/07/2026</t>
+        </is>
+      </c>
+      <c r="F78" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G78" s="5" t="inlineStr"/>
+      <c r="H78" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I77" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B78" s="6" t="inlineStr">
+      <c r="I78" s="5" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B79" s="5" t="inlineStr">
         <is>
           <t>A1-B1</t>
         </is>
       </c>
-      <c r="C78" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D78" s="6" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="E78" s="6" t="inlineStr">
-        <is>
-          <t>12/07/2026</t>
-        </is>
-      </c>
-      <c r="F78" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G78" s="6" t="inlineStr"/>
-      <c r="H78" s="6" t="inlineStr">
+      <c r="C79" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D79" s="5" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="E79" s="5" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="F79" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G79" s="5" t="inlineStr"/>
+      <c r="H79" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I78" s="6" t="inlineStr">
+      <c r="I79" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B79" s="6" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B80" s="5" t="inlineStr">
         <is>
           <t>A1-B1</t>
         </is>
       </c>
-      <c r="C79" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D79" s="6" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="E79" s="6" t="inlineStr">
-        <is>
-          <t>13/07/2026</t>
-        </is>
-      </c>
-      <c r="F79" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G79" s="6" t="inlineStr"/>
-      <c r="H79" s="6" t="inlineStr">
+      <c r="C80" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D80" s="5" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E80" s="5" t="inlineStr">
+        <is>
+          <t>18/07/2026</t>
+        </is>
+      </c>
+      <c r="F80" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G80" s="5" t="inlineStr"/>
+      <c r="H80" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I79" s="6" t="inlineStr">
+      <c r="I80" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B80" s="6" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B81" s="5" t="inlineStr">
         <is>
           <t>A1-B1</t>
         </is>
       </c>
-      <c r="C80" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D80" s="6" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="E80" s="6" t="inlineStr">
-        <is>
-          <t>18/07/2026</t>
-        </is>
-      </c>
-      <c r="F80" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G80" s="6" t="inlineStr"/>
-      <c r="H80" s="6" t="inlineStr">
+      <c r="C81" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D81" s="5" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="E81" s="5" t="inlineStr">
+        <is>
+          <t>19/07/2026</t>
+        </is>
+      </c>
+      <c r="F81" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G81" s="5" t="inlineStr"/>
+      <c r="H81" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I80" s="6" t="inlineStr">
+      <c r="I81" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B81" s="6" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B82" s="5" t="inlineStr">
         <is>
           <t>A1-B1</t>
         </is>
       </c>
-      <c r="C81" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D81" s="6" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="E81" s="6" t="inlineStr">
-        <is>
-          <t>19/07/2026</t>
-        </is>
-      </c>
-      <c r="F81" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G81" s="6" t="inlineStr"/>
-      <c r="H81" s="6" t="inlineStr">
+      <c r="C82" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D82" s="5" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E82" s="5" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="F82" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G82" s="5" t="inlineStr"/>
+      <c r="H82" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I81" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B82" s="6" t="inlineStr">
-        <is>
-          <t>A1-B1</t>
-        </is>
-      </c>
-      <c r="C82" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D82" s="6" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="E82" s="6" t="inlineStr">
-        <is>
-          <t>20/07/2026</t>
-        </is>
-      </c>
-      <c r="F82" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G82" s="6" t="inlineStr"/>
-      <c r="H82" s="6" t="inlineStr">
-        <is>
-          <t>0/34</t>
-        </is>
-      </c>
-      <c r="I82" s="6" t="inlineStr">
+      <c r="I82" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -5876,258 +5888,262 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B104" s="5" t="inlineStr">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
         <is>
           <t>A1-B2</t>
         </is>
       </c>
-      <c r="C104" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D104" s="5" t="inlineStr">
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="E104" s="5" t="inlineStr">
+      <c r="E104" s="2" t="inlineStr">
         <is>
           <t>11/07/2026</t>
         </is>
       </c>
-      <c r="F104" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G104" s="5" t="inlineStr"/>
-      <c r="H104" s="5" t="inlineStr">
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>19/34</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B105" s="5" t="inlineStr">
+        <is>
+          <t>A1-B2</t>
+        </is>
+      </c>
+      <c r="C105" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D105" s="5" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="E105" s="5" t="inlineStr">
+        <is>
+          <t>12/07/2026</t>
+        </is>
+      </c>
+      <c r="F105" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G105" s="5" t="inlineStr"/>
+      <c r="H105" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I104" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B105" s="6" t="inlineStr">
+      <c r="I105" s="5" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B106" s="5" t="inlineStr">
         <is>
           <t>A1-B2</t>
         </is>
       </c>
-      <c r="C105" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D105" s="6" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="E105" s="6" t="inlineStr">
-        <is>
-          <t>12/07/2026</t>
-        </is>
-      </c>
-      <c r="F105" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G105" s="6" t="inlineStr"/>
-      <c r="H105" s="6" t="inlineStr">
+      <c r="C106" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D106" s="5" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="E106" s="5" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="F106" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G106" s="5" t="inlineStr"/>
+      <c r="H106" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I105" s="6" t="inlineStr">
+      <c r="I106" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B106" s="6" t="inlineStr">
+    <row r="107">
+      <c r="A107" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B107" s="5" t="inlineStr">
         <is>
           <t>A1-B2</t>
         </is>
       </c>
-      <c r="C106" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D106" s="6" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="E106" s="6" t="inlineStr">
-        <is>
-          <t>13/07/2026</t>
-        </is>
-      </c>
-      <c r="F106" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G106" s="6" t="inlineStr"/>
-      <c r="H106" s="6" t="inlineStr">
+      <c r="C107" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D107" s="5" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E107" s="5" t="inlineStr">
+        <is>
+          <t>18/07/2026</t>
+        </is>
+      </c>
+      <c r="F107" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G107" s="5" t="inlineStr"/>
+      <c r="H107" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I106" s="6" t="inlineStr">
+      <c r="I107" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B107" s="6" t="inlineStr">
+    <row r="108">
+      <c r="A108" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B108" s="5" t="inlineStr">
         <is>
           <t>A1-B2</t>
         </is>
       </c>
-      <c r="C107" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D107" s="6" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="E107" s="6" t="inlineStr">
-        <is>
-          <t>18/07/2026</t>
-        </is>
-      </c>
-      <c r="F107" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G107" s="6" t="inlineStr"/>
-      <c r="H107" s="6" t="inlineStr">
+      <c r="C108" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D108" s="5" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="E108" s="5" t="inlineStr">
+        <is>
+          <t>19/07/2026</t>
+        </is>
+      </c>
+      <c r="F108" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G108" s="5" t="inlineStr"/>
+      <c r="H108" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I107" s="6" t="inlineStr">
+      <c r="I108" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B108" s="6" t="inlineStr">
+    <row r="109">
+      <c r="A109" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B109" s="5" t="inlineStr">
         <is>
           <t>A1-B2</t>
         </is>
       </c>
-      <c r="C108" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D108" s="6" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="E108" s="6" t="inlineStr">
-        <is>
-          <t>19/07/2026</t>
-        </is>
-      </c>
-      <c r="F108" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G108" s="6" t="inlineStr"/>
-      <c r="H108" s="6" t="inlineStr">
+      <c r="C109" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D109" s="5" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E109" s="5" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="F109" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G109" s="5" t="inlineStr"/>
+      <c r="H109" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I108" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B109" s="6" t="inlineStr">
-        <is>
-          <t>A1-B2</t>
-        </is>
-      </c>
-      <c r="C109" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D109" s="6" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="E109" s="6" t="inlineStr">
-        <is>
-          <t>20/07/2026</t>
-        </is>
-      </c>
-      <c r="F109" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G109" s="6" t="inlineStr"/>
-      <c r="H109" s="6" t="inlineStr">
-        <is>
-          <t>0/34</t>
-        </is>
-      </c>
-      <c r="I109" s="6" t="inlineStr">
+      <c r="I109" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -7121,258 +7137,262 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B131" s="5" t="inlineStr">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
         <is>
           <t>A1-C1</t>
         </is>
       </c>
-      <c r="C131" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D131" s="5" t="inlineStr">
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="E131" s="5" t="inlineStr">
+      <c r="E131" s="2" t="inlineStr">
         <is>
           <t>11/07/2026</t>
         </is>
       </c>
-      <c r="F131" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G131" s="5" t="inlineStr"/>
-      <c r="H131" s="5" t="inlineStr">
+      <c r="F131" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G131" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H131" s="2" t="inlineStr">
+        <is>
+          <t>18/34</t>
+        </is>
+      </c>
+      <c r="I131" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B132" s="5" t="inlineStr">
+        <is>
+          <t>A1-C1</t>
+        </is>
+      </c>
+      <c r="C132" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D132" s="5" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="E132" s="5" t="inlineStr">
+        <is>
+          <t>12/07/2026</t>
+        </is>
+      </c>
+      <c r="F132" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G132" s="5" t="inlineStr"/>
+      <c r="H132" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I131" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B132" s="6" t="inlineStr">
+      <c r="I132" s="5" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B133" s="5" t="inlineStr">
         <is>
           <t>A1-C1</t>
         </is>
       </c>
-      <c r="C132" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D132" s="6" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="E132" s="6" t="inlineStr">
-        <is>
-          <t>12/07/2026</t>
-        </is>
-      </c>
-      <c r="F132" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G132" s="6" t="inlineStr"/>
-      <c r="H132" s="6" t="inlineStr">
+      <c r="C133" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D133" s="5" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="E133" s="5" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="F133" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G133" s="5" t="inlineStr"/>
+      <c r="H133" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I132" s="6" t="inlineStr">
+      <c r="I133" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B133" s="6" t="inlineStr">
+    <row r="134">
+      <c r="A134" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B134" s="5" t="inlineStr">
         <is>
           <t>A1-C1</t>
         </is>
       </c>
-      <c r="C133" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D133" s="6" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="E133" s="6" t="inlineStr">
-        <is>
-          <t>13/07/2026</t>
-        </is>
-      </c>
-      <c r="F133" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G133" s="6" t="inlineStr"/>
-      <c r="H133" s="6" t="inlineStr">
+      <c r="C134" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D134" s="5" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E134" s="5" t="inlineStr">
+        <is>
+          <t>18/07/2026</t>
+        </is>
+      </c>
+      <c r="F134" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G134" s="5" t="inlineStr"/>
+      <c r="H134" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I133" s="6" t="inlineStr">
+      <c r="I134" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="134">
-      <c r="A134" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B134" s="6" t="inlineStr">
+    <row r="135">
+      <c r="A135" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B135" s="5" t="inlineStr">
         <is>
           <t>A1-C1</t>
         </is>
       </c>
-      <c r="C134" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D134" s="6" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="E134" s="6" t="inlineStr">
-        <is>
-          <t>18/07/2026</t>
-        </is>
-      </c>
-      <c r="F134" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G134" s="6" t="inlineStr"/>
-      <c r="H134" s="6" t="inlineStr">
+      <c r="C135" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D135" s="5" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="E135" s="5" t="inlineStr">
+        <is>
+          <t>19/07/2026</t>
+        </is>
+      </c>
+      <c r="F135" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G135" s="5" t="inlineStr"/>
+      <c r="H135" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I134" s="6" t="inlineStr">
+      <c r="I135" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B135" s="6" t="inlineStr">
+    <row r="136">
+      <c r="A136" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B136" s="5" t="inlineStr">
         <is>
           <t>A1-C1</t>
         </is>
       </c>
-      <c r="C135" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D135" s="6" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="E135" s="6" t="inlineStr">
-        <is>
-          <t>19/07/2026</t>
-        </is>
-      </c>
-      <c r="F135" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G135" s="6" t="inlineStr"/>
-      <c r="H135" s="6" t="inlineStr">
+      <c r="C136" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D136" s="5" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E136" s="5" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="F136" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G136" s="5" t="inlineStr"/>
+      <c r="H136" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I135" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B136" s="6" t="inlineStr">
-        <is>
-          <t>A1-C1</t>
-        </is>
-      </c>
-      <c r="C136" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D136" s="6" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="E136" s="6" t="inlineStr">
-        <is>
-          <t>20/07/2026</t>
-        </is>
-      </c>
-      <c r="F136" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G136" s="6" t="inlineStr"/>
-      <c r="H136" s="6" t="inlineStr">
-        <is>
-          <t>0/34</t>
-        </is>
-      </c>
-      <c r="I136" s="6" t="inlineStr">
+      <c r="I136" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -8366,258 +8386,262 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B158" s="5" t="inlineStr">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
         <is>
           <t>A1-C2</t>
         </is>
       </c>
-      <c r="C158" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D158" s="5" t="inlineStr">
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="E158" s="5" t="inlineStr">
+      <c r="E158" s="2" t="inlineStr">
         <is>
           <t>11/07/2026</t>
         </is>
       </c>
-      <c r="F158" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G158" s="5" t="inlineStr"/>
-      <c r="H158" s="5" t="inlineStr">
+      <c r="F158" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G158" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H158" s="2" t="inlineStr">
+        <is>
+          <t>17/33</t>
+        </is>
+      </c>
+      <c r="I158" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B159" s="5" t="inlineStr">
+        <is>
+          <t>A1-C2</t>
+        </is>
+      </c>
+      <c r="C159" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D159" s="5" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="E159" s="5" t="inlineStr">
+        <is>
+          <t>12/07/2026</t>
+        </is>
+      </c>
+      <c r="F159" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G159" s="5" t="inlineStr"/>
+      <c r="H159" s="5" t="inlineStr">
         <is>
           <t>0/33</t>
         </is>
       </c>
-      <c r="I158" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B159" s="6" t="inlineStr">
+      <c r="I159" s="5" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B160" s="5" t="inlineStr">
         <is>
           <t>A1-C2</t>
         </is>
       </c>
-      <c r="C159" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D159" s="6" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="E159" s="6" t="inlineStr">
-        <is>
-          <t>12/07/2026</t>
-        </is>
-      </c>
-      <c r="F159" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G159" s="6" t="inlineStr"/>
-      <c r="H159" s="6" t="inlineStr">
+      <c r="C160" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D160" s="5" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="E160" s="5" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="F160" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G160" s="5" t="inlineStr"/>
+      <c r="H160" s="5" t="inlineStr">
         <is>
           <t>0/33</t>
         </is>
       </c>
-      <c r="I159" s="6" t="inlineStr">
+      <c r="I160" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="160">
-      <c r="A160" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B160" s="6" t="inlineStr">
+    <row r="161">
+      <c r="A161" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B161" s="5" t="inlineStr">
         <is>
           <t>A1-C2</t>
         </is>
       </c>
-      <c r="C160" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D160" s="6" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="E160" s="6" t="inlineStr">
-        <is>
-          <t>13/07/2026</t>
-        </is>
-      </c>
-      <c r="F160" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G160" s="6" t="inlineStr"/>
-      <c r="H160" s="6" t="inlineStr">
+      <c r="C161" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D161" s="5" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E161" s="5" t="inlineStr">
+        <is>
+          <t>18/07/2026</t>
+        </is>
+      </c>
+      <c r="F161" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G161" s="5" t="inlineStr"/>
+      <c r="H161" s="5" t="inlineStr">
         <is>
           <t>0/33</t>
         </is>
       </c>
-      <c r="I160" s="6" t="inlineStr">
+      <c r="I161" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="161">
-      <c r="A161" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B161" s="6" t="inlineStr">
+    <row r="162">
+      <c r="A162" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B162" s="5" t="inlineStr">
         <is>
           <t>A1-C2</t>
         </is>
       </c>
-      <c r="C161" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D161" s="6" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="E161" s="6" t="inlineStr">
-        <is>
-          <t>18/07/2026</t>
-        </is>
-      </c>
-      <c r="F161" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G161" s="6" t="inlineStr"/>
-      <c r="H161" s="6" t="inlineStr">
+      <c r="C162" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D162" s="5" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="E162" s="5" t="inlineStr">
+        <is>
+          <t>19/07/2026</t>
+        </is>
+      </c>
+      <c r="F162" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G162" s="5" t="inlineStr"/>
+      <c r="H162" s="5" t="inlineStr">
         <is>
           <t>0/33</t>
         </is>
       </c>
-      <c r="I161" s="6" t="inlineStr">
+      <c r="I162" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="162">
-      <c r="A162" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B162" s="6" t="inlineStr">
+    <row r="163">
+      <c r="A163" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B163" s="5" t="inlineStr">
         <is>
           <t>A1-C2</t>
         </is>
       </c>
-      <c r="C162" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D162" s="6" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="E162" s="6" t="inlineStr">
-        <is>
-          <t>19/07/2026</t>
-        </is>
-      </c>
-      <c r="F162" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G162" s="6" t="inlineStr"/>
-      <c r="H162" s="6" t="inlineStr">
+      <c r="C163" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D163" s="5" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E163" s="5" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="F163" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G163" s="5" t="inlineStr"/>
+      <c r="H163" s="5" t="inlineStr">
         <is>
           <t>0/33</t>
         </is>
       </c>
-      <c r="I162" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B163" s="6" t="inlineStr">
-        <is>
-          <t>A1-C2</t>
-        </is>
-      </c>
-      <c r="C163" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D163" s="6" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="E163" s="6" t="inlineStr">
-        <is>
-          <t>20/07/2026</t>
-        </is>
-      </c>
-      <c r="F163" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G163" s="6" t="inlineStr"/>
-      <c r="H163" s="6" t="inlineStr">
-        <is>
-          <t>0/33</t>
-        </is>
-      </c>
-      <c r="I163" s="6" t="inlineStr">
+      <c r="I163" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -8859,43 +8883,43 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B169" s="5" t="inlineStr">
+      <c r="A169" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B169" s="9" t="inlineStr">
         <is>
           <t>A1-D1</t>
         </is>
       </c>
-      <c r="C169" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D169" s="5" t="inlineStr">
+      <c r="C169" s="9" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D169" s="9" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E169" s="5" t="inlineStr">
+      <c r="E169" s="9" t="inlineStr">
         <is>
           <t>04/06/2026</t>
         </is>
       </c>
-      <c r="F169" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G169" s="5" t="inlineStr"/>
-      <c r="H169" s="5" t="inlineStr">
+      <c r="F169" s="9" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G169" s="9" t="inlineStr"/>
+      <c r="H169" s="9" t="inlineStr">
         <is>
           <t>0/35</t>
         </is>
       </c>
-      <c r="I169" s="5" t="inlineStr">
+      <c r="I169" s="9" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
@@ -9513,43 +9537,43 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B183" s="5" t="inlineStr">
+      <c r="A183" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B183" s="9" t="inlineStr">
         <is>
           <t>A1-D1</t>
         </is>
       </c>
-      <c r="C183" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D183" s="5" t="inlineStr">
+      <c r="C183" s="9" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D183" s="9" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="E183" s="5" t="inlineStr">
+      <c r="E183" s="9" t="inlineStr">
         <is>
           <t>08/07/2026</t>
         </is>
       </c>
-      <c r="F183" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G183" s="5" t="inlineStr"/>
-      <c r="H183" s="5" t="inlineStr">
+      <c r="F183" s="9" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G183" s="9" t="inlineStr"/>
+      <c r="H183" s="9" t="inlineStr">
         <is>
           <t>0/35</t>
         </is>
       </c>
-      <c r="I183" s="5" t="inlineStr">
+      <c r="I183" s="9" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
@@ -9603,258 +9627,258 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B185" s="6" t="inlineStr">
+      <c r="A185" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B185" s="5" t="inlineStr">
         <is>
           <t>A1-D1</t>
         </is>
       </c>
-      <c r="C185" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D185" s="6" t="inlineStr">
+      <c r="C185" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D185" s="5" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="E185" s="6" t="inlineStr">
+      <c r="E185" s="5" t="inlineStr">
         <is>
           <t>14/07/2026</t>
         </is>
       </c>
-      <c r="F185" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G185" s="6" t="inlineStr"/>
-      <c r="H185" s="6" t="inlineStr">
+      <c r="F185" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G185" s="5" t="inlineStr"/>
+      <c r="H185" s="5" t="inlineStr">
         <is>
           <t>0/35</t>
         </is>
       </c>
-      <c r="I185" s="6" t="inlineStr">
+      <c r="I185" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B186" s="6" t="inlineStr">
+      <c r="A186" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B186" s="5" t="inlineStr">
         <is>
           <t>A1-D1</t>
         </is>
       </c>
-      <c r="C186" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D186" s="6" t="inlineStr">
+      <c r="C186" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D186" s="5" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="E186" s="6" t="inlineStr">
+      <c r="E186" s="5" t="inlineStr">
         <is>
           <t>15/07/2026</t>
         </is>
       </c>
-      <c r="F186" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G186" s="6" t="inlineStr"/>
-      <c r="H186" s="6" t="inlineStr">
+      <c r="F186" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G186" s="5" t="inlineStr"/>
+      <c r="H186" s="5" t="inlineStr">
         <is>
           <t>0/35</t>
         </is>
       </c>
-      <c r="I186" s="6" t="inlineStr">
+      <c r="I186" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B187" s="6" t="inlineStr">
+      <c r="A187" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B187" s="5" t="inlineStr">
         <is>
           <t>A1-D1</t>
         </is>
       </c>
-      <c r="C187" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D187" s="6" t="inlineStr">
+      <c r="C187" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D187" s="5" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="E187" s="6" t="inlineStr">
+      <c r="E187" s="5" t="inlineStr">
         <is>
           <t>16/07/2026</t>
         </is>
       </c>
-      <c r="F187" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G187" s="6" t="inlineStr"/>
-      <c r="H187" s="6" t="inlineStr">
+      <c r="F187" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G187" s="5" t="inlineStr"/>
+      <c r="H187" s="5" t="inlineStr">
         <is>
           <t>0/35</t>
         </is>
       </c>
-      <c r="I187" s="6" t="inlineStr">
+      <c r="I187" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B188" s="6" t="inlineStr">
+      <c r="A188" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B188" s="5" t="inlineStr">
         <is>
           <t>A1-D1</t>
         </is>
       </c>
-      <c r="C188" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D188" s="6" t="inlineStr">
+      <c r="C188" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D188" s="5" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="E188" s="6" t="inlineStr">
+      <c r="E188" s="5" t="inlineStr">
         <is>
           <t>21/07/2026</t>
         </is>
       </c>
-      <c r="F188" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G188" s="6" t="inlineStr"/>
-      <c r="H188" s="6" t="inlineStr">
+      <c r="F188" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G188" s="5" t="inlineStr"/>
+      <c r="H188" s="5" t="inlineStr">
         <is>
           <t>0/35</t>
         </is>
       </c>
-      <c r="I188" s="6" t="inlineStr">
+      <c r="I188" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B189" s="6" t="inlineStr">
+      <c r="A189" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B189" s="5" t="inlineStr">
         <is>
           <t>A1-D1</t>
         </is>
       </c>
-      <c r="C189" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D189" s="6" t="inlineStr">
+      <c r="C189" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D189" s="5" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="E189" s="6" t="inlineStr">
+      <c r="E189" s="5" t="inlineStr">
         <is>
           <t>22/07/2026</t>
         </is>
       </c>
-      <c r="F189" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G189" s="6" t="inlineStr"/>
-      <c r="H189" s="6" t="inlineStr">
+      <c r="F189" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G189" s="5" t="inlineStr"/>
+      <c r="H189" s="5" t="inlineStr">
         <is>
           <t>0/35</t>
         </is>
       </c>
-      <c r="I189" s="6" t="inlineStr">
+      <c r="I189" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B190" s="6" t="inlineStr">
+      <c r="A190" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B190" s="5" t="inlineStr">
         <is>
           <t>A1-D1</t>
         </is>
       </c>
-      <c r="C190" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D190" s="6" t="inlineStr">
+      <c r="C190" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D190" s="5" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="E190" s="6" t="inlineStr">
+      <c r="E190" s="5" t="inlineStr">
         <is>
           <t>23/07/2026</t>
         </is>
       </c>
-      <c r="F190" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G190" s="6" t="inlineStr"/>
-      <c r="H190" s="6" t="inlineStr">
+      <c r="F190" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G190" s="5" t="inlineStr"/>
+      <c r="H190" s="5" t="inlineStr">
         <is>
           <t>0/35</t>
         </is>
       </c>
-      <c r="I190" s="6" t="inlineStr">
+      <c r="I190" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -10096,43 +10120,43 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B196" s="5" t="inlineStr">
+      <c r="A196" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B196" s="9" t="inlineStr">
         <is>
           <t>A1-D2</t>
         </is>
       </c>
-      <c r="C196" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D196" s="5" t="inlineStr">
+      <c r="C196" s="9" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D196" s="9" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E196" s="5" t="inlineStr">
+      <c r="E196" s="9" t="inlineStr">
         <is>
           <t>04/06/2026</t>
         </is>
       </c>
-      <c r="F196" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G196" s="5" t="inlineStr"/>
-      <c r="H196" s="5" t="inlineStr">
+      <c r="F196" s="9" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G196" s="9" t="inlineStr"/>
+      <c r="H196" s="9" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I196" s="5" t="inlineStr">
+      <c r="I196" s="9" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
@@ -10750,43 +10774,43 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B210" s="5" t="inlineStr">
+      <c r="A210" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B210" s="9" t="inlineStr">
         <is>
           <t>A1-D2</t>
         </is>
       </c>
-      <c r="C210" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D210" s="5" t="inlineStr">
+      <c r="C210" s="9" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D210" s="9" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="E210" s="5" t="inlineStr">
+      <c r="E210" s="9" t="inlineStr">
         <is>
           <t>08/07/2026</t>
         </is>
       </c>
-      <c r="F210" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G210" s="5" t="inlineStr"/>
-      <c r="H210" s="5" t="inlineStr">
+      <c r="F210" s="9" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G210" s="9" t="inlineStr"/>
+      <c r="H210" s="9" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I210" s="5" t="inlineStr">
+      <c r="I210" s="9" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
@@ -10840,258 +10864,258 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B212" s="6" t="inlineStr">
+      <c r="A212" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B212" s="5" t="inlineStr">
         <is>
           <t>A1-D2</t>
         </is>
       </c>
-      <c r="C212" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D212" s="6" t="inlineStr">
+      <c r="C212" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D212" s="5" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="E212" s="6" t="inlineStr">
+      <c r="E212" s="5" t="inlineStr">
         <is>
           <t>14/07/2026</t>
         </is>
       </c>
-      <c r="F212" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G212" s="6" t="inlineStr"/>
-      <c r="H212" s="6" t="inlineStr">
+      <c r="F212" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G212" s="5" t="inlineStr"/>
+      <c r="H212" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I212" s="6" t="inlineStr">
+      <c r="I212" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B213" s="6" t="inlineStr">
+      <c r="A213" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B213" s="5" t="inlineStr">
         <is>
           <t>A1-D2</t>
         </is>
       </c>
-      <c r="C213" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D213" s="6" t="inlineStr">
+      <c r="C213" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D213" s="5" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="E213" s="6" t="inlineStr">
+      <c r="E213" s="5" t="inlineStr">
         <is>
           <t>15/07/2026</t>
         </is>
       </c>
-      <c r="F213" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G213" s="6" t="inlineStr"/>
-      <c r="H213" s="6" t="inlineStr">
+      <c r="F213" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G213" s="5" t="inlineStr"/>
+      <c r="H213" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I213" s="6" t="inlineStr">
+      <c r="I213" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B214" s="6" t="inlineStr">
+      <c r="A214" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B214" s="5" t="inlineStr">
         <is>
           <t>A1-D2</t>
         </is>
       </c>
-      <c r="C214" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D214" s="6" t="inlineStr">
+      <c r="C214" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D214" s="5" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="E214" s="6" t="inlineStr">
+      <c r="E214" s="5" t="inlineStr">
         <is>
           <t>16/07/2026</t>
         </is>
       </c>
-      <c r="F214" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G214" s="6" t="inlineStr"/>
-      <c r="H214" s="6" t="inlineStr">
+      <c r="F214" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G214" s="5" t="inlineStr"/>
+      <c r="H214" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I214" s="6" t="inlineStr">
+      <c r="I214" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B215" s="6" t="inlineStr">
+      <c r="A215" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B215" s="5" t="inlineStr">
         <is>
           <t>A1-D2</t>
         </is>
       </c>
-      <c r="C215" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D215" s="6" t="inlineStr">
+      <c r="C215" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D215" s="5" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="E215" s="6" t="inlineStr">
+      <c r="E215" s="5" t="inlineStr">
         <is>
           <t>21/07/2026</t>
         </is>
       </c>
-      <c r="F215" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G215" s="6" t="inlineStr"/>
-      <c r="H215" s="6" t="inlineStr">
+      <c r="F215" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G215" s="5" t="inlineStr"/>
+      <c r="H215" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I215" s="6" t="inlineStr">
+      <c r="I215" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B216" s="6" t="inlineStr">
+      <c r="A216" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B216" s="5" t="inlineStr">
         <is>
           <t>A1-D2</t>
         </is>
       </c>
-      <c r="C216" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D216" s="6" t="inlineStr">
+      <c r="C216" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D216" s="5" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="E216" s="6" t="inlineStr">
+      <c r="E216" s="5" t="inlineStr">
         <is>
           <t>22/07/2026</t>
         </is>
       </c>
-      <c r="F216" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G216" s="6" t="inlineStr"/>
-      <c r="H216" s="6" t="inlineStr">
+      <c r="F216" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G216" s="5" t="inlineStr"/>
+      <c r="H216" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I216" s="6" t="inlineStr">
+      <c r="I216" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B217" s="6" t="inlineStr">
+      <c r="A217" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B217" s="5" t="inlineStr">
         <is>
           <t>A1-D2</t>
         </is>
       </c>
-      <c r="C217" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D217" s="6" t="inlineStr">
+      <c r="C217" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D217" s="5" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="E217" s="6" t="inlineStr">
+      <c r="E217" s="5" t="inlineStr">
         <is>
           <t>23/07/2026</t>
         </is>
       </c>
-      <c r="F217" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G217" s="6" t="inlineStr"/>
-      <c r="H217" s="6" t="inlineStr">
+      <c r="F217" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G217" s="5" t="inlineStr"/>
+      <c r="H217" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I217" s="6" t="inlineStr">
+      <c r="I217" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -11333,43 +11357,43 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B223" s="5" t="inlineStr">
+      <c r="A223" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B223" s="9" t="inlineStr">
         <is>
           <t>A1-E1</t>
         </is>
       </c>
-      <c r="C223" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D223" s="5" t="inlineStr">
+      <c r="C223" s="9" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D223" s="9" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E223" s="5" t="inlineStr">
+      <c r="E223" s="9" t="inlineStr">
         <is>
           <t>04/06/2026</t>
         </is>
       </c>
-      <c r="F223" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G223" s="5" t="inlineStr"/>
-      <c r="H223" s="5" t="inlineStr">
+      <c r="F223" s="9" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G223" s="9" t="inlineStr"/>
+      <c r="H223" s="9" t="inlineStr">
         <is>
           <t>0/38</t>
         </is>
       </c>
-      <c r="I223" s="5" t="inlineStr">
+      <c r="I223" s="9" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
@@ -12034,301 +12058,301 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B238" s="5" t="inlineStr">
+      <c r="A238" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B238" s="9" t="inlineStr">
         <is>
           <t>A1-E1</t>
         </is>
       </c>
-      <c r="C238" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D238" s="5" t="inlineStr">
+      <c r="C238" s="9" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D238" s="9" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="E238" s="5" t="inlineStr">
+      <c r="E238" s="9" t="inlineStr">
         <is>
           <t>09/07/2026</t>
         </is>
       </c>
-      <c r="F238" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G238" s="5" t="inlineStr"/>
-      <c r="H238" s="5" t="inlineStr">
+      <c r="F238" s="9" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G238" s="9" t="inlineStr"/>
+      <c r="H238" s="9" t="inlineStr">
         <is>
           <t>0/38</t>
         </is>
       </c>
-      <c r="I238" s="5" t="inlineStr">
+      <c r="I238" s="9" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B239" s="6" t="inlineStr">
+      <c r="A239" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B239" s="5" t="inlineStr">
         <is>
           <t>A1-E1</t>
         </is>
       </c>
-      <c r="C239" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D239" s="6" t="inlineStr">
+      <c r="C239" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D239" s="5" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="E239" s="6" t="inlineStr">
+      <c r="E239" s="5" t="inlineStr">
         <is>
           <t>14/07/2026</t>
         </is>
       </c>
-      <c r="F239" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G239" s="6" t="inlineStr"/>
-      <c r="H239" s="6" t="inlineStr">
+      <c r="F239" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G239" s="5" t="inlineStr"/>
+      <c r="H239" s="5" t="inlineStr">
         <is>
           <t>0/38</t>
         </is>
       </c>
-      <c r="I239" s="6" t="inlineStr">
+      <c r="I239" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B240" s="6" t="inlineStr">
+      <c r="A240" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B240" s="5" t="inlineStr">
         <is>
           <t>A1-E1</t>
         </is>
       </c>
-      <c r="C240" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D240" s="6" t="inlineStr">
+      <c r="C240" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D240" s="5" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="E240" s="6" t="inlineStr">
+      <c r="E240" s="5" t="inlineStr">
         <is>
           <t>15/07/2026</t>
         </is>
       </c>
-      <c r="F240" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G240" s="6" t="inlineStr"/>
-      <c r="H240" s="6" t="inlineStr">
+      <c r="F240" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G240" s="5" t="inlineStr"/>
+      <c r="H240" s="5" t="inlineStr">
         <is>
           <t>0/38</t>
         </is>
       </c>
-      <c r="I240" s="6" t="inlineStr">
+      <c r="I240" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B241" s="6" t="inlineStr">
+      <c r="A241" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B241" s="5" t="inlineStr">
         <is>
           <t>A1-E1</t>
         </is>
       </c>
-      <c r="C241" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D241" s="6" t="inlineStr">
+      <c r="C241" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D241" s="5" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="E241" s="6" t="inlineStr">
+      <c r="E241" s="5" t="inlineStr">
         <is>
           <t>16/07/2026</t>
         </is>
       </c>
-      <c r="F241" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G241" s="6" t="inlineStr"/>
-      <c r="H241" s="6" t="inlineStr">
+      <c r="F241" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G241" s="5" t="inlineStr"/>
+      <c r="H241" s="5" t="inlineStr">
         <is>
           <t>0/38</t>
         </is>
       </c>
-      <c r="I241" s="6" t="inlineStr">
+      <c r="I241" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B242" s="6" t="inlineStr">
+      <c r="A242" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B242" s="5" t="inlineStr">
         <is>
           <t>A1-E1</t>
         </is>
       </c>
-      <c r="C242" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D242" s="6" t="inlineStr">
+      <c r="C242" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D242" s="5" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="E242" s="6" t="inlineStr">
+      <c r="E242" s="5" t="inlineStr">
         <is>
           <t>21/07/2026</t>
         </is>
       </c>
-      <c r="F242" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G242" s="6" t="inlineStr"/>
-      <c r="H242" s="6" t="inlineStr">
+      <c r="F242" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G242" s="5" t="inlineStr"/>
+      <c r="H242" s="5" t="inlineStr">
         <is>
           <t>0/38</t>
         </is>
       </c>
-      <c r="I242" s="6" t="inlineStr">
+      <c r="I242" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B243" s="6" t="inlineStr">
+      <c r="A243" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B243" s="5" t="inlineStr">
         <is>
           <t>A1-E1</t>
         </is>
       </c>
-      <c r="C243" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D243" s="6" t="inlineStr">
+      <c r="C243" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D243" s="5" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="E243" s="6" t="inlineStr">
+      <c r="E243" s="5" t="inlineStr">
         <is>
           <t>22/07/2026</t>
         </is>
       </c>
-      <c r="F243" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G243" s="6" t="inlineStr"/>
-      <c r="H243" s="6" t="inlineStr">
+      <c r="F243" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G243" s="5" t="inlineStr"/>
+      <c r="H243" s="5" t="inlineStr">
         <is>
           <t>0/38</t>
         </is>
       </c>
-      <c r="I243" s="6" t="inlineStr">
+      <c r="I243" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B244" s="6" t="inlineStr">
+      <c r="A244" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B244" s="5" t="inlineStr">
         <is>
           <t>A1-E1</t>
         </is>
       </c>
-      <c r="C244" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D244" s="6" t="inlineStr">
+      <c r="C244" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D244" s="5" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="E244" s="6" t="inlineStr">
+      <c r="E244" s="5" t="inlineStr">
         <is>
           <t>23/07/2026</t>
         </is>
       </c>
-      <c r="F244" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G244" s="6" t="inlineStr"/>
-      <c r="H244" s="6" t="inlineStr">
+      <c r="F244" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G244" s="5" t="inlineStr"/>
+      <c r="H244" s="5" t="inlineStr">
         <is>
           <t>0/38</t>
         </is>
       </c>
-      <c r="I244" s="6" t="inlineStr">
+      <c r="I244" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -12570,43 +12594,43 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B250" s="5" t="inlineStr">
+      <c r="A250" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B250" s="9" t="inlineStr">
         <is>
           <t>A1-E2</t>
         </is>
       </c>
-      <c r="C250" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D250" s="5" t="inlineStr">
+      <c r="C250" s="9" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D250" s="9" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E250" s="5" t="inlineStr">
+      <c r="E250" s="9" t="inlineStr">
         <is>
           <t>04/06/2026</t>
         </is>
       </c>
-      <c r="F250" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G250" s="5" t="inlineStr"/>
-      <c r="H250" s="5" t="inlineStr">
+      <c r="F250" s="9" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G250" s="9" t="inlineStr"/>
+      <c r="H250" s="9" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I250" s="5" t="inlineStr">
+      <c r="I250" s="9" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
@@ -13271,301 +13295,301 @@
       </c>
     </row>
     <row r="265">
-      <c r="A265" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B265" s="5" t="inlineStr">
+      <c r="A265" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B265" s="9" t="inlineStr">
         <is>
           <t>A1-E2</t>
         </is>
       </c>
-      <c r="C265" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D265" s="5" t="inlineStr">
+      <c r="C265" s="9" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D265" s="9" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="E265" s="5" t="inlineStr">
+      <c r="E265" s="9" t="inlineStr">
         <is>
           <t>09/07/2026</t>
         </is>
       </c>
-      <c r="F265" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G265" s="5" t="inlineStr"/>
-      <c r="H265" s="5" t="inlineStr">
+      <c r="F265" s="9" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G265" s="9" t="inlineStr"/>
+      <c r="H265" s="9" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I265" s="5" t="inlineStr">
+      <c r="I265" s="9" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
       </c>
     </row>
     <row r="266">
-      <c r="A266" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B266" s="6" t="inlineStr">
+      <c r="A266" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B266" s="5" t="inlineStr">
         <is>
           <t>A1-E2</t>
         </is>
       </c>
-      <c r="C266" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D266" s="6" t="inlineStr">
+      <c r="C266" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D266" s="5" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="E266" s="6" t="inlineStr">
+      <c r="E266" s="5" t="inlineStr">
         <is>
           <t>14/07/2026</t>
         </is>
       </c>
-      <c r="F266" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G266" s="6" t="inlineStr"/>
-      <c r="H266" s="6" t="inlineStr">
+      <c r="F266" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G266" s="5" t="inlineStr"/>
+      <c r="H266" s="5" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I266" s="6" t="inlineStr">
+      <c r="I266" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="267">
-      <c r="A267" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B267" s="6" t="inlineStr">
+      <c r="A267" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B267" s="5" t="inlineStr">
         <is>
           <t>A1-E2</t>
         </is>
       </c>
-      <c r="C267" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D267" s="6" t="inlineStr">
+      <c r="C267" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D267" s="5" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="E267" s="6" t="inlineStr">
+      <c r="E267" s="5" t="inlineStr">
         <is>
           <t>15/07/2026</t>
         </is>
       </c>
-      <c r="F267" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G267" s="6" t="inlineStr"/>
-      <c r="H267" s="6" t="inlineStr">
+      <c r="F267" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G267" s="5" t="inlineStr"/>
+      <c r="H267" s="5" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I267" s="6" t="inlineStr">
+      <c r="I267" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="268">
-      <c r="A268" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B268" s="6" t="inlineStr">
+      <c r="A268" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B268" s="5" t="inlineStr">
         <is>
           <t>A1-E2</t>
         </is>
       </c>
-      <c r="C268" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D268" s="6" t="inlineStr">
+      <c r="C268" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D268" s="5" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="E268" s="6" t="inlineStr">
+      <c r="E268" s="5" t="inlineStr">
         <is>
           <t>16/07/2026</t>
         </is>
       </c>
-      <c r="F268" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G268" s="6" t="inlineStr"/>
-      <c r="H268" s="6" t="inlineStr">
+      <c r="F268" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G268" s="5" t="inlineStr"/>
+      <c r="H268" s="5" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I268" s="6" t="inlineStr">
+      <c r="I268" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="269">
-      <c r="A269" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B269" s="6" t="inlineStr">
+      <c r="A269" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B269" s="5" t="inlineStr">
         <is>
           <t>A1-E2</t>
         </is>
       </c>
-      <c r="C269" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D269" s="6" t="inlineStr">
+      <c r="C269" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D269" s="5" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="E269" s="6" t="inlineStr">
+      <c r="E269" s="5" t="inlineStr">
         <is>
           <t>21/07/2026</t>
         </is>
       </c>
-      <c r="F269" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G269" s="6" t="inlineStr"/>
-      <c r="H269" s="6" t="inlineStr">
+      <c r="F269" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G269" s="5" t="inlineStr"/>
+      <c r="H269" s="5" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I269" s="6" t="inlineStr">
+      <c r="I269" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="270">
-      <c r="A270" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B270" s="6" t="inlineStr">
+      <c r="A270" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B270" s="5" t="inlineStr">
         <is>
           <t>A1-E2</t>
         </is>
       </c>
-      <c r="C270" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D270" s="6" t="inlineStr">
+      <c r="C270" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D270" s="5" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="E270" s="6" t="inlineStr">
+      <c r="E270" s="5" t="inlineStr">
         <is>
           <t>22/07/2026</t>
         </is>
       </c>
-      <c r="F270" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G270" s="6" t="inlineStr"/>
-      <c r="H270" s="6" t="inlineStr">
+      <c r="F270" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G270" s="5" t="inlineStr"/>
+      <c r="H270" s="5" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I270" s="6" t="inlineStr">
+      <c r="I270" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="271">
-      <c r="A271" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B271" s="6" t="inlineStr">
+      <c r="A271" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B271" s="5" t="inlineStr">
         <is>
           <t>A1-E2</t>
         </is>
       </c>
-      <c r="C271" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D271" s="6" t="inlineStr">
+      <c r="C271" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D271" s="5" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="E271" s="6" t="inlineStr">
+      <c r="E271" s="5" t="inlineStr">
         <is>
           <t>23/07/2026</t>
         </is>
       </c>
-      <c r="F271" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G271" s="6" t="inlineStr"/>
-      <c r="H271" s="6" t="inlineStr">
+      <c r="F271" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G271" s="5" t="inlineStr"/>
+      <c r="H271" s="5" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I271" s="6" t="inlineStr">
+      <c r="I271" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -13807,43 +13831,43 @@
       </c>
     </row>
     <row r="277">
-      <c r="A277" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B277" s="5" t="inlineStr">
+      <c r="A277" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B277" s="9" t="inlineStr">
         <is>
           <t>A1-F1</t>
         </is>
       </c>
-      <c r="C277" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D277" s="5" t="inlineStr">
+      <c r="C277" s="9" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D277" s="9" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E277" s="5" t="inlineStr">
+      <c r="E277" s="9" t="inlineStr">
         <is>
           <t>04/06/2026</t>
         </is>
       </c>
-      <c r="F277" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G277" s="5" t="inlineStr"/>
-      <c r="H277" s="5" t="inlineStr">
+      <c r="F277" s="9" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G277" s="9" t="inlineStr"/>
+      <c r="H277" s="9" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I277" s="5" t="inlineStr">
+      <c r="I277" s="9" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
@@ -14555,258 +14579,258 @@
       </c>
     </row>
     <row r="293">
-      <c r="A293" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B293" s="6" t="inlineStr">
+      <c r="A293" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B293" s="5" t="inlineStr">
         <is>
           <t>A1-F1</t>
         </is>
       </c>
-      <c r="C293" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D293" s="6" t="inlineStr">
+      <c r="C293" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D293" s="5" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="E293" s="6" t="inlineStr">
+      <c r="E293" s="5" t="inlineStr">
         <is>
           <t>14/07/2026</t>
         </is>
       </c>
-      <c r="F293" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G293" s="6" t="inlineStr"/>
-      <c r="H293" s="6" t="inlineStr">
+      <c r="F293" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G293" s="5" t="inlineStr"/>
+      <c r="H293" s="5" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I293" s="6" t="inlineStr">
+      <c r="I293" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="294">
-      <c r="A294" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B294" s="6" t="inlineStr">
+      <c r="A294" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B294" s="5" t="inlineStr">
         <is>
           <t>A1-F1</t>
         </is>
       </c>
-      <c r="C294" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D294" s="6" t="inlineStr">
+      <c r="C294" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D294" s="5" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="E294" s="6" t="inlineStr">
+      <c r="E294" s="5" t="inlineStr">
         <is>
           <t>15/07/2026</t>
         </is>
       </c>
-      <c r="F294" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G294" s="6" t="inlineStr"/>
-      <c r="H294" s="6" t="inlineStr">
+      <c r="F294" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G294" s="5" t="inlineStr"/>
+      <c r="H294" s="5" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I294" s="6" t="inlineStr">
+      <c r="I294" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="295">
-      <c r="A295" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B295" s="6" t="inlineStr">
+      <c r="A295" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B295" s="5" t="inlineStr">
         <is>
           <t>A1-F1</t>
         </is>
       </c>
-      <c r="C295" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D295" s="6" t="inlineStr">
+      <c r="C295" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D295" s="5" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="E295" s="6" t="inlineStr">
+      <c r="E295" s="5" t="inlineStr">
         <is>
           <t>16/07/2026</t>
         </is>
       </c>
-      <c r="F295" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G295" s="6" t="inlineStr"/>
-      <c r="H295" s="6" t="inlineStr">
+      <c r="F295" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G295" s="5" t="inlineStr"/>
+      <c r="H295" s="5" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I295" s="6" t="inlineStr">
+      <c r="I295" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="296">
-      <c r="A296" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B296" s="6" t="inlineStr">
+      <c r="A296" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B296" s="5" t="inlineStr">
         <is>
           <t>A1-F1</t>
         </is>
       </c>
-      <c r="C296" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D296" s="6" t="inlineStr">
+      <c r="C296" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D296" s="5" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="E296" s="6" t="inlineStr">
+      <c r="E296" s="5" t="inlineStr">
         <is>
           <t>21/07/2026</t>
         </is>
       </c>
-      <c r="F296" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G296" s="6" t="inlineStr"/>
-      <c r="H296" s="6" t="inlineStr">
+      <c r="F296" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G296" s="5" t="inlineStr"/>
+      <c r="H296" s="5" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I296" s="6" t="inlineStr">
+      <c r="I296" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="297">
-      <c r="A297" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B297" s="6" t="inlineStr">
+      <c r="A297" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B297" s="5" t="inlineStr">
         <is>
           <t>A1-F1</t>
         </is>
       </c>
-      <c r="C297" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D297" s="6" t="inlineStr">
+      <c r="C297" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D297" s="5" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="E297" s="6" t="inlineStr">
+      <c r="E297" s="5" t="inlineStr">
         <is>
           <t>22/07/2026</t>
         </is>
       </c>
-      <c r="F297" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G297" s="6" t="inlineStr"/>
-      <c r="H297" s="6" t="inlineStr">
+      <c r="F297" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G297" s="5" t="inlineStr"/>
+      <c r="H297" s="5" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I297" s="6" t="inlineStr">
+      <c r="I297" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="298">
-      <c r="A298" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B298" s="6" t="inlineStr">
+      <c r="A298" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B298" s="5" t="inlineStr">
         <is>
           <t>A1-F1</t>
         </is>
       </c>
-      <c r="C298" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D298" s="6" t="inlineStr">
+      <c r="C298" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D298" s="5" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="E298" s="6" t="inlineStr">
+      <c r="E298" s="5" t="inlineStr">
         <is>
           <t>23/07/2026</t>
         </is>
       </c>
-      <c r="F298" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G298" s="6" t="inlineStr"/>
-      <c r="H298" s="6" t="inlineStr">
+      <c r="F298" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G298" s="5" t="inlineStr"/>
+      <c r="H298" s="5" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I298" s="6" t="inlineStr">
+      <c r="I298" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -15048,43 +15072,43 @@
       </c>
     </row>
     <row r="304">
-      <c r="A304" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B304" s="5" t="inlineStr">
+      <c r="A304" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B304" s="9" t="inlineStr">
         <is>
           <t>A1-F2</t>
         </is>
       </c>
-      <c r="C304" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D304" s="5" t="inlineStr">
+      <c r="C304" s="9" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D304" s="9" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E304" s="5" t="inlineStr">
+      <c r="E304" s="9" t="inlineStr">
         <is>
           <t>04/06/2026</t>
         </is>
       </c>
-      <c r="F304" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G304" s="5" t="inlineStr"/>
-      <c r="H304" s="5" t="inlineStr">
+      <c r="F304" s="9" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G304" s="9" t="inlineStr"/>
+      <c r="H304" s="9" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I304" s="5" t="inlineStr">
+      <c r="I304" s="9" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
@@ -15655,43 +15679,43 @@
       </c>
     </row>
     <row r="317">
-      <c r="A317" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B317" s="5" t="inlineStr">
+      <c r="A317" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B317" s="9" t="inlineStr">
         <is>
           <t>A1-F2</t>
         </is>
       </c>
-      <c r="C317" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D317" s="5" t="inlineStr">
+      <c r="C317" s="9" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D317" s="9" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="E317" s="5" t="inlineStr">
+      <c r="E317" s="9" t="inlineStr">
         <is>
           <t>07/07/2026</t>
         </is>
       </c>
-      <c r="F317" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G317" s="5" t="inlineStr"/>
-      <c r="H317" s="5" t="inlineStr">
+      <c r="F317" s="9" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G317" s="9" t="inlineStr"/>
+      <c r="H317" s="9" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I317" s="5" t="inlineStr">
+      <c r="I317" s="9" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
@@ -15792,258 +15816,258 @@
       </c>
     </row>
     <row r="320">
-      <c r="A320" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B320" s="6" t="inlineStr">
+      <c r="A320" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B320" s="5" t="inlineStr">
         <is>
           <t>A1-F2</t>
         </is>
       </c>
-      <c r="C320" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D320" s="6" t="inlineStr">
+      <c r="C320" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D320" s="5" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="E320" s="6" t="inlineStr">
+      <c r="E320" s="5" t="inlineStr">
         <is>
           <t>14/07/2026</t>
         </is>
       </c>
-      <c r="F320" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G320" s="6" t="inlineStr"/>
-      <c r="H320" s="6" t="inlineStr">
+      <c r="F320" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G320" s="5" t="inlineStr"/>
+      <c r="H320" s="5" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I320" s="6" t="inlineStr">
+      <c r="I320" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="321">
-      <c r="A321" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B321" s="6" t="inlineStr">
+      <c r="A321" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B321" s="5" t="inlineStr">
         <is>
           <t>A1-F2</t>
         </is>
       </c>
-      <c r="C321" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D321" s="6" t="inlineStr">
+      <c r="C321" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D321" s="5" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="E321" s="6" t="inlineStr">
+      <c r="E321" s="5" t="inlineStr">
         <is>
           <t>15/07/2026</t>
         </is>
       </c>
-      <c r="F321" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G321" s="6" t="inlineStr"/>
-      <c r="H321" s="6" t="inlineStr">
+      <c r="F321" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G321" s="5" t="inlineStr"/>
+      <c r="H321" s="5" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I321" s="6" t="inlineStr">
+      <c r="I321" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="322">
-      <c r="A322" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B322" s="6" t="inlineStr">
+      <c r="A322" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B322" s="5" t="inlineStr">
         <is>
           <t>A1-F2</t>
         </is>
       </c>
-      <c r="C322" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D322" s="6" t="inlineStr">
+      <c r="C322" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D322" s="5" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="E322" s="6" t="inlineStr">
+      <c r="E322" s="5" t="inlineStr">
         <is>
           <t>16/07/2026</t>
         </is>
       </c>
-      <c r="F322" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G322" s="6" t="inlineStr"/>
-      <c r="H322" s="6" t="inlineStr">
+      <c r="F322" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G322" s="5" t="inlineStr"/>
+      <c r="H322" s="5" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I322" s="6" t="inlineStr">
+      <c r="I322" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="323">
-      <c r="A323" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B323" s="6" t="inlineStr">
+      <c r="A323" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B323" s="5" t="inlineStr">
         <is>
           <t>A1-F2</t>
         </is>
       </c>
-      <c r="C323" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D323" s="6" t="inlineStr">
+      <c r="C323" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D323" s="5" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="E323" s="6" t="inlineStr">
+      <c r="E323" s="5" t="inlineStr">
         <is>
           <t>21/07/2026</t>
         </is>
       </c>
-      <c r="F323" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G323" s="6" t="inlineStr"/>
-      <c r="H323" s="6" t="inlineStr">
+      <c r="F323" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G323" s="5" t="inlineStr"/>
+      <c r="H323" s="5" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I323" s="6" t="inlineStr">
+      <c r="I323" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="324">
-      <c r="A324" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B324" s="6" t="inlineStr">
+      <c r="A324" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B324" s="5" t="inlineStr">
         <is>
           <t>A1-F2</t>
         </is>
       </c>
-      <c r="C324" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D324" s="6" t="inlineStr">
+      <c r="C324" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D324" s="5" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="E324" s="6" t="inlineStr">
+      <c r="E324" s="5" t="inlineStr">
         <is>
           <t>22/07/2026</t>
         </is>
       </c>
-      <c r="F324" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G324" s="6" t="inlineStr"/>
-      <c r="H324" s="6" t="inlineStr">
+      <c r="F324" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G324" s="5" t="inlineStr"/>
+      <c r="H324" s="5" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I324" s="6" t="inlineStr">
+      <c r="I324" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="325">
-      <c r="A325" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B325" s="6" t="inlineStr">
+      <c r="A325" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B325" s="5" t="inlineStr">
         <is>
           <t>A1-F2</t>
         </is>
       </c>
-      <c r="C325" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D325" s="6" t="inlineStr">
+      <c r="C325" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D325" s="5" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="E325" s="6" t="inlineStr">
+      <c r="E325" s="5" t="inlineStr">
         <is>
           <t>23/07/2026</t>
         </is>
       </c>
-      <c r="F325" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G325" s="6" t="inlineStr"/>
-      <c r="H325" s="6" t="inlineStr">
+      <c r="F325" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G325" s="5" t="inlineStr"/>
+      <c r="H325" s="5" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I325" s="6" t="inlineStr">
+      <c r="I325" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A1_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A1_session_analysis.xlsx
@@ -58,14 +58,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFFE0"/>
-        <bgColor rgb="00FFFFE0"/>
+        <fgColor rgb="00FFB6C1"/>
+        <bgColor rgb="00FFB6C1"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFB6C1"/>
-        <bgColor rgb="00FFB6C1"/>
+        <fgColor rgb="00FFFFE0"/>
+        <bgColor rgb="00FFFFE0"/>
       </patternFill>
     </fill>
   </fills>
@@ -96,16 +96,16 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8">
@@ -924,7 +924,7 @@
         </is>
       </c>
       <c r="L8" s="4" t="n">
-        <v>66</v>
+        <v>60</v>
       </c>
     </row>
     <row r="9">
@@ -1345,10 +1345,10 @@
         <v>22</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R15" s="4" t="inlineStr">
         <is>
@@ -1427,10 +1427,10 @@
         <v>22</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R16" s="4" t="inlineStr">
         <is>
@@ -1509,10 +1509,10 @@
         <v>22</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R17" s="4" t="inlineStr">
         <is>
@@ -1591,10 +1591,10 @@
         <v>22</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R18" s="4" t="inlineStr">
         <is>
@@ -1673,10 +1673,10 @@
         <v>22</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R19" s="4" t="inlineStr">
         <is>
@@ -1755,10 +1755,10 @@
         <v>22</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R20" s="4" t="inlineStr">
         <is>
@@ -2056,7 +2056,7 @@
       </c>
       <c r="I24" s="5" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Not Recorded</t>
         </is>
       </c>
       <c r="K24" s="4" t="inlineStr">
@@ -2096,43 +2096,43 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B25" s="5" t="inlineStr">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
         <is>
           <t>A1-A1</t>
         </is>
       </c>
-      <c r="C25" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="inlineStr">
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="E25" s="5" t="inlineStr">
+      <c r="E25" s="6" t="inlineStr">
         <is>
           <t>13/07/2026</t>
         </is>
       </c>
-      <c r="F25" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G25" s="5" t="inlineStr"/>
-      <c r="H25" s="5" t="inlineStr">
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G25" s="6" t="inlineStr"/>
+      <c r="H25" s="6" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I25" s="5" t="inlineStr">
+      <c r="I25" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -2174,43 +2174,43 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B26" s="5" t="inlineStr">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
         <is>
           <t>A1-A1</t>
         </is>
       </c>
-      <c r="C26" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D26" s="5" t="inlineStr">
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="E26" s="5" t="inlineStr">
+      <c r="E26" s="6" t="inlineStr">
         <is>
           <t>18/07/2026</t>
         </is>
       </c>
-      <c r="F26" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G26" s="5" t="inlineStr"/>
-      <c r="H26" s="5" t="inlineStr">
+      <c r="F26" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G26" s="6" t="inlineStr"/>
+      <c r="H26" s="6" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I26" s="5" t="inlineStr">
+      <c r="I26" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -2252,86 +2252,86 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B27" s="5" t="inlineStr">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
         <is>
           <t>A1-A1</t>
         </is>
       </c>
-      <c r="C27" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="inlineStr">
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="E27" s="5" t="inlineStr">
+      <c r="E27" s="6" t="inlineStr">
         <is>
           <t>19/07/2026</t>
         </is>
       </c>
-      <c r="F27" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G27" s="5" t="inlineStr"/>
-      <c r="H27" s="5" t="inlineStr">
+      <c r="F27" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G27" s="6" t="inlineStr"/>
+      <c r="H27" s="6" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I27" s="5" t="inlineStr">
+      <c r="I27" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B28" s="5" t="inlineStr">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
         <is>
           <t>A1-A1</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D28" s="5" t="inlineStr">
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="E28" s="5" t="inlineStr">
+      <c r="E28" s="6" t="inlineStr">
         <is>
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="F28" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G28" s="5" t="inlineStr"/>
-      <c r="H28" s="5" t="inlineStr">
+      <c r="F28" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G28" s="6" t="inlineStr"/>
+      <c r="H28" s="6" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I28" s="5" t="inlineStr">
+      <c r="I28" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -2502,7 +2502,7 @@
           <t>Recorded</t>
         </is>
       </c>
-      <c r="L31" s="6" t="inlineStr">
+      <c r="L31" s="7" t="inlineStr">
         <is>
           <t>Green</t>
         </is>
@@ -2564,7 +2564,7 @@
           <t>Not Recorded</t>
         </is>
       </c>
-      <c r="L32" s="7" t="inlineStr">
+      <c r="L32" s="8" t="inlineStr">
         <is>
           <t>Red</t>
         </is>
@@ -2626,7 +2626,7 @@
           <t>Pending</t>
         </is>
       </c>
-      <c r="L33" s="8" t="inlineStr">
+      <c r="L33" s="9" t="inlineStr">
         <is>
           <t>Yellow</t>
         </is>
@@ -3475,177 +3475,177 @@
       </c>
       <c r="I51" s="5" t="inlineStr">
         <is>
+          <t>Not Recorded</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B52" s="6" t="inlineStr">
+        <is>
+          <t>A1-A2</t>
+        </is>
+      </c>
+      <c r="C52" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D52" s="6" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="E52" s="6" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="F52" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G52" s="6" t="inlineStr"/>
+      <c r="H52" s="6" t="inlineStr">
+        <is>
+          <t>0/33</t>
+        </is>
+      </c>
+      <c r="I52" s="6" t="inlineStr">
+        <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B52" s="5" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B53" s="6" t="inlineStr">
         <is>
           <t>A1-A2</t>
         </is>
       </c>
-      <c r="C52" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D52" s="5" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="E52" s="5" t="inlineStr">
-        <is>
-          <t>13/07/2026</t>
-        </is>
-      </c>
-      <c r="F52" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G52" s="5" t="inlineStr"/>
-      <c r="H52" s="5" t="inlineStr">
+      <c r="C53" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D53" s="6" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E53" s="6" t="inlineStr">
+        <is>
+          <t>18/07/2026</t>
+        </is>
+      </c>
+      <c r="F53" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G53" s="6" t="inlineStr"/>
+      <c r="H53" s="6" t="inlineStr">
         <is>
           <t>0/33</t>
         </is>
       </c>
-      <c r="I52" s="5" t="inlineStr">
+      <c r="I53" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B53" s="5" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B54" s="6" t="inlineStr">
         <is>
           <t>A1-A2</t>
         </is>
       </c>
-      <c r="C53" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D53" s="5" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="E53" s="5" t="inlineStr">
-        <is>
-          <t>18/07/2026</t>
-        </is>
-      </c>
-      <c r="F53" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G53" s="5" t="inlineStr"/>
-      <c r="H53" s="5" t="inlineStr">
+      <c r="C54" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D54" s="6" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="E54" s="6" t="inlineStr">
+        <is>
+          <t>19/07/2026</t>
+        </is>
+      </c>
+      <c r="F54" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G54" s="6" t="inlineStr"/>
+      <c r="H54" s="6" t="inlineStr">
         <is>
           <t>0/33</t>
         </is>
       </c>
-      <c r="I53" s="5" t="inlineStr">
+      <c r="I54" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B54" s="5" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B55" s="6" t="inlineStr">
         <is>
           <t>A1-A2</t>
         </is>
       </c>
-      <c r="C54" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D54" s="5" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="E54" s="5" t="inlineStr">
-        <is>
-          <t>19/07/2026</t>
-        </is>
-      </c>
-      <c r="F54" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G54" s="5" t="inlineStr"/>
-      <c r="H54" s="5" t="inlineStr">
+      <c r="C55" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D55" s="6" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E55" s="6" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="F55" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G55" s="6" t="inlineStr"/>
+      <c r="H55" s="6" t="inlineStr">
         <is>
           <t>0/33</t>
         </is>
       </c>
-      <c r="I54" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B55" s="5" t="inlineStr">
-        <is>
-          <t>A1-A2</t>
-        </is>
-      </c>
-      <c r="C55" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D55" s="5" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="E55" s="5" t="inlineStr">
-        <is>
-          <t>20/07/2026</t>
-        </is>
-      </c>
-      <c r="F55" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G55" s="5" t="inlineStr"/>
-      <c r="H55" s="5" t="inlineStr">
-        <is>
-          <t>0/33</t>
-        </is>
-      </c>
-      <c r="I55" s="5" t="inlineStr">
+      <c r="I55" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -4724,177 +4724,177 @@
       </c>
       <c r="I78" s="5" t="inlineStr">
         <is>
+          <t>Not Recorded</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B79" s="6" t="inlineStr">
+        <is>
+          <t>A1-B1</t>
+        </is>
+      </c>
+      <c r="C79" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D79" s="6" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="E79" s="6" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="F79" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G79" s="6" t="inlineStr"/>
+      <c r="H79" s="6" t="inlineStr">
+        <is>
+          <t>0/34</t>
+        </is>
+      </c>
+      <c r="I79" s="6" t="inlineStr">
+        <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B79" s="5" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B80" s="6" t="inlineStr">
         <is>
           <t>A1-B1</t>
         </is>
       </c>
-      <c r="C79" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D79" s="5" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="E79" s="5" t="inlineStr">
-        <is>
-          <t>13/07/2026</t>
-        </is>
-      </c>
-      <c r="F79" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G79" s="5" t="inlineStr"/>
-      <c r="H79" s="5" t="inlineStr">
+      <c r="C80" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D80" s="6" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E80" s="6" t="inlineStr">
+        <is>
+          <t>18/07/2026</t>
+        </is>
+      </c>
+      <c r="F80" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G80" s="6" t="inlineStr"/>
+      <c r="H80" s="6" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I79" s="5" t="inlineStr">
+      <c r="I80" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B80" s="5" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B81" s="6" t="inlineStr">
         <is>
           <t>A1-B1</t>
         </is>
       </c>
-      <c r="C80" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D80" s="5" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="E80" s="5" t="inlineStr">
-        <is>
-          <t>18/07/2026</t>
-        </is>
-      </c>
-      <c r="F80" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G80" s="5" t="inlineStr"/>
-      <c r="H80" s="5" t="inlineStr">
+      <c r="C81" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D81" s="6" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="E81" s="6" t="inlineStr">
+        <is>
+          <t>19/07/2026</t>
+        </is>
+      </c>
+      <c r="F81" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G81" s="6" t="inlineStr"/>
+      <c r="H81" s="6" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I80" s="5" t="inlineStr">
+      <c r="I81" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B81" s="5" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B82" s="6" t="inlineStr">
         <is>
           <t>A1-B1</t>
         </is>
       </c>
-      <c r="C81" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D81" s="5" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="E81" s="5" t="inlineStr">
-        <is>
-          <t>19/07/2026</t>
-        </is>
-      </c>
-      <c r="F81" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G81" s="5" t="inlineStr"/>
-      <c r="H81" s="5" t="inlineStr">
+      <c r="C82" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D82" s="6" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E82" s="6" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="F82" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G82" s="6" t="inlineStr"/>
+      <c r="H82" s="6" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I81" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B82" s="5" t="inlineStr">
-        <is>
-          <t>A1-B1</t>
-        </is>
-      </c>
-      <c r="C82" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D82" s="5" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="E82" s="5" t="inlineStr">
-        <is>
-          <t>20/07/2026</t>
-        </is>
-      </c>
-      <c r="F82" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G82" s="5" t="inlineStr"/>
-      <c r="H82" s="5" t="inlineStr">
-        <is>
-          <t>0/34</t>
-        </is>
-      </c>
-      <c r="I82" s="5" t="inlineStr">
+      <c r="I82" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -5973,177 +5973,177 @@
       </c>
       <c r="I105" s="5" t="inlineStr">
         <is>
+          <t>Not Recorded</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B106" s="6" t="inlineStr">
+        <is>
+          <t>A1-B2</t>
+        </is>
+      </c>
+      <c r="C106" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D106" s="6" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="E106" s="6" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="F106" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G106" s="6" t="inlineStr"/>
+      <c r="H106" s="6" t="inlineStr">
+        <is>
+          <t>0/34</t>
+        </is>
+      </c>
+      <c r="I106" s="6" t="inlineStr">
+        <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B106" s="5" t="inlineStr">
+    <row r="107">
+      <c r="A107" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B107" s="6" t="inlineStr">
         <is>
           <t>A1-B2</t>
         </is>
       </c>
-      <c r="C106" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D106" s="5" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="E106" s="5" t="inlineStr">
-        <is>
-          <t>13/07/2026</t>
-        </is>
-      </c>
-      <c r="F106" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G106" s="5" t="inlineStr"/>
-      <c r="H106" s="5" t="inlineStr">
+      <c r="C107" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D107" s="6" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E107" s="6" t="inlineStr">
+        <is>
+          <t>18/07/2026</t>
+        </is>
+      </c>
+      <c r="F107" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G107" s="6" t="inlineStr"/>
+      <c r="H107" s="6" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I106" s="5" t="inlineStr">
+      <c r="I107" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B107" s="5" t="inlineStr">
+    <row r="108">
+      <c r="A108" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B108" s="6" t="inlineStr">
         <is>
           <t>A1-B2</t>
         </is>
       </c>
-      <c r="C107" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D107" s="5" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="E107" s="5" t="inlineStr">
-        <is>
-          <t>18/07/2026</t>
-        </is>
-      </c>
-      <c r="F107" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G107" s="5" t="inlineStr"/>
-      <c r="H107" s="5" t="inlineStr">
+      <c r="C108" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D108" s="6" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="E108" s="6" t="inlineStr">
+        <is>
+          <t>19/07/2026</t>
+        </is>
+      </c>
+      <c r="F108" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G108" s="6" t="inlineStr"/>
+      <c r="H108" s="6" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I107" s="5" t="inlineStr">
+      <c r="I108" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B108" s="5" t="inlineStr">
+    <row r="109">
+      <c r="A109" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B109" s="6" t="inlineStr">
         <is>
           <t>A1-B2</t>
         </is>
       </c>
-      <c r="C108" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D108" s="5" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="E108" s="5" t="inlineStr">
-        <is>
-          <t>19/07/2026</t>
-        </is>
-      </c>
-      <c r="F108" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G108" s="5" t="inlineStr"/>
-      <c r="H108" s="5" t="inlineStr">
+      <c r="C109" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D109" s="6" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E109" s="6" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="F109" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G109" s="6" t="inlineStr"/>
+      <c r="H109" s="6" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I108" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B109" s="5" t="inlineStr">
-        <is>
-          <t>A1-B2</t>
-        </is>
-      </c>
-      <c r="C109" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D109" s="5" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="E109" s="5" t="inlineStr">
-        <is>
-          <t>20/07/2026</t>
-        </is>
-      </c>
-      <c r="F109" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G109" s="5" t="inlineStr"/>
-      <c r="H109" s="5" t="inlineStr">
-        <is>
-          <t>0/34</t>
-        </is>
-      </c>
-      <c r="I109" s="5" t="inlineStr">
+      <c r="I109" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -7222,177 +7222,177 @@
       </c>
       <c r="I132" s="5" t="inlineStr">
         <is>
+          <t>Not Recorded</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B133" s="6" t="inlineStr">
+        <is>
+          <t>A1-C1</t>
+        </is>
+      </c>
+      <c r="C133" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D133" s="6" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="E133" s="6" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="F133" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G133" s="6" t="inlineStr"/>
+      <c r="H133" s="6" t="inlineStr">
+        <is>
+          <t>0/34</t>
+        </is>
+      </c>
+      <c r="I133" s="6" t="inlineStr">
+        <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B133" s="5" t="inlineStr">
+    <row r="134">
+      <c r="A134" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B134" s="6" t="inlineStr">
         <is>
           <t>A1-C1</t>
         </is>
       </c>
-      <c r="C133" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D133" s="5" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="E133" s="5" t="inlineStr">
-        <is>
-          <t>13/07/2026</t>
-        </is>
-      </c>
-      <c r="F133" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G133" s="5" t="inlineStr"/>
-      <c r="H133" s="5" t="inlineStr">
+      <c r="C134" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D134" s="6" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E134" s="6" t="inlineStr">
+        <is>
+          <t>18/07/2026</t>
+        </is>
+      </c>
+      <c r="F134" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G134" s="6" t="inlineStr"/>
+      <c r="H134" s="6" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I133" s="5" t="inlineStr">
+      <c r="I134" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="134">
-      <c r="A134" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B134" s="5" t="inlineStr">
+    <row r="135">
+      <c r="A135" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B135" s="6" t="inlineStr">
         <is>
           <t>A1-C1</t>
         </is>
       </c>
-      <c r="C134" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D134" s="5" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="E134" s="5" t="inlineStr">
-        <is>
-          <t>18/07/2026</t>
-        </is>
-      </c>
-      <c r="F134" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G134" s="5" t="inlineStr"/>
-      <c r="H134" s="5" t="inlineStr">
+      <c r="C135" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D135" s="6" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="E135" s="6" t="inlineStr">
+        <is>
+          <t>19/07/2026</t>
+        </is>
+      </c>
+      <c r="F135" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G135" s="6" t="inlineStr"/>
+      <c r="H135" s="6" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I134" s="5" t="inlineStr">
+      <c r="I135" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B135" s="5" t="inlineStr">
+    <row r="136">
+      <c r="A136" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B136" s="6" t="inlineStr">
         <is>
           <t>A1-C1</t>
         </is>
       </c>
-      <c r="C135" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D135" s="5" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="E135" s="5" t="inlineStr">
-        <is>
-          <t>19/07/2026</t>
-        </is>
-      </c>
-      <c r="F135" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G135" s="5" t="inlineStr"/>
-      <c r="H135" s="5" t="inlineStr">
+      <c r="C136" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D136" s="6" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E136" s="6" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="F136" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G136" s="6" t="inlineStr"/>
+      <c r="H136" s="6" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I135" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B136" s="5" t="inlineStr">
-        <is>
-          <t>A1-C1</t>
-        </is>
-      </c>
-      <c r="C136" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D136" s="5" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="E136" s="5" t="inlineStr">
-        <is>
-          <t>20/07/2026</t>
-        </is>
-      </c>
-      <c r="F136" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G136" s="5" t="inlineStr"/>
-      <c r="H136" s="5" t="inlineStr">
-        <is>
-          <t>0/34</t>
-        </is>
-      </c>
-      <c r="I136" s="5" t="inlineStr">
+      <c r="I136" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -8471,177 +8471,177 @@
       </c>
       <c r="I159" s="5" t="inlineStr">
         <is>
+          <t>Not Recorded</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B160" s="6" t="inlineStr">
+        <is>
+          <t>A1-C2</t>
+        </is>
+      </c>
+      <c r="C160" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D160" s="6" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="E160" s="6" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="F160" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G160" s="6" t="inlineStr"/>
+      <c r="H160" s="6" t="inlineStr">
+        <is>
+          <t>0/33</t>
+        </is>
+      </c>
+      <c r="I160" s="6" t="inlineStr">
+        <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="160">
-      <c r="A160" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B160" s="5" t="inlineStr">
+    <row r="161">
+      <c r="A161" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B161" s="6" t="inlineStr">
         <is>
           <t>A1-C2</t>
         </is>
       </c>
-      <c r="C160" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D160" s="5" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="E160" s="5" t="inlineStr">
-        <is>
-          <t>13/07/2026</t>
-        </is>
-      </c>
-      <c r="F160" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G160" s="5" t="inlineStr"/>
-      <c r="H160" s="5" t="inlineStr">
+      <c r="C161" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D161" s="6" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E161" s="6" t="inlineStr">
+        <is>
+          <t>18/07/2026</t>
+        </is>
+      </c>
+      <c r="F161" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G161" s="6" t="inlineStr"/>
+      <c r="H161" s="6" t="inlineStr">
         <is>
           <t>0/33</t>
         </is>
       </c>
-      <c r="I160" s="5" t="inlineStr">
+      <c r="I161" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="161">
-      <c r="A161" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B161" s="5" t="inlineStr">
+    <row r="162">
+      <c r="A162" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B162" s="6" t="inlineStr">
         <is>
           <t>A1-C2</t>
         </is>
       </c>
-      <c r="C161" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D161" s="5" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="E161" s="5" t="inlineStr">
-        <is>
-          <t>18/07/2026</t>
-        </is>
-      </c>
-      <c r="F161" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G161" s="5" t="inlineStr"/>
-      <c r="H161" s="5" t="inlineStr">
+      <c r="C162" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D162" s="6" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="E162" s="6" t="inlineStr">
+        <is>
+          <t>19/07/2026</t>
+        </is>
+      </c>
+      <c r="F162" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G162" s="6" t="inlineStr"/>
+      <c r="H162" s="6" t="inlineStr">
         <is>
           <t>0/33</t>
         </is>
       </c>
-      <c r="I161" s="5" t="inlineStr">
+      <c r="I162" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="162">
-      <c r="A162" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B162" s="5" t="inlineStr">
+    <row r="163">
+      <c r="A163" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B163" s="6" t="inlineStr">
         <is>
           <t>A1-C2</t>
         </is>
       </c>
-      <c r="C162" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D162" s="5" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="E162" s="5" t="inlineStr">
-        <is>
-          <t>19/07/2026</t>
-        </is>
-      </c>
-      <c r="F162" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G162" s="5" t="inlineStr"/>
-      <c r="H162" s="5" t="inlineStr">
+      <c r="C163" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D163" s="6" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E163" s="6" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="F163" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G163" s="6" t="inlineStr"/>
+      <c r="H163" s="6" t="inlineStr">
         <is>
           <t>0/33</t>
         </is>
       </c>
-      <c r="I162" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B163" s="5" t="inlineStr">
-        <is>
-          <t>A1-C2</t>
-        </is>
-      </c>
-      <c r="C163" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D163" s="5" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="E163" s="5" t="inlineStr">
-        <is>
-          <t>20/07/2026</t>
-        </is>
-      </c>
-      <c r="F163" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G163" s="5" t="inlineStr"/>
-      <c r="H163" s="5" t="inlineStr">
-        <is>
-          <t>0/33</t>
-        </is>
-      </c>
-      <c r="I163" s="5" t="inlineStr">
+      <c r="I163" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -8883,43 +8883,43 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B169" s="9" t="inlineStr">
+      <c r="A169" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B169" s="5" t="inlineStr">
         <is>
           <t>A1-D1</t>
         </is>
       </c>
-      <c r="C169" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D169" s="9" t="inlineStr">
+      <c r="C169" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D169" s="5" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E169" s="9" t="inlineStr">
+      <c r="E169" s="5" t="inlineStr">
         <is>
           <t>04/06/2026</t>
         </is>
       </c>
-      <c r="F169" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G169" s="9" t="inlineStr"/>
-      <c r="H169" s="9" t="inlineStr">
+      <c r="F169" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G169" s="5" t="inlineStr"/>
+      <c r="H169" s="5" t="inlineStr">
         <is>
           <t>0/35</t>
         </is>
       </c>
-      <c r="I169" s="9" t="inlineStr">
+      <c r="I169" s="5" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
@@ -9537,43 +9537,43 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B183" s="9" t="inlineStr">
+      <c r="A183" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B183" s="5" t="inlineStr">
         <is>
           <t>A1-D1</t>
         </is>
       </c>
-      <c r="C183" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D183" s="9" t="inlineStr">
+      <c r="C183" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D183" s="5" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="E183" s="9" t="inlineStr">
+      <c r="E183" s="5" t="inlineStr">
         <is>
           <t>08/07/2026</t>
         </is>
       </c>
-      <c r="F183" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G183" s="9" t="inlineStr"/>
-      <c r="H183" s="9" t="inlineStr">
+      <c r="F183" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G183" s="5" t="inlineStr"/>
+      <c r="H183" s="5" t="inlineStr">
         <is>
           <t>0/35</t>
         </is>
       </c>
-      <c r="I183" s="9" t="inlineStr">
+      <c r="I183" s="5" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
@@ -9627,258 +9627,258 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B185" s="5" t="inlineStr">
+      <c r="A185" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B185" s="6" t="inlineStr">
         <is>
           <t>A1-D1</t>
         </is>
       </c>
-      <c r="C185" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D185" s="5" t="inlineStr">
+      <c r="C185" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D185" s="6" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="E185" s="5" t="inlineStr">
+      <c r="E185" s="6" t="inlineStr">
         <is>
           <t>14/07/2026</t>
         </is>
       </c>
-      <c r="F185" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G185" s="5" t="inlineStr"/>
-      <c r="H185" s="5" t="inlineStr">
+      <c r="F185" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G185" s="6" t="inlineStr"/>
+      <c r="H185" s="6" t="inlineStr">
         <is>
           <t>0/35</t>
         </is>
       </c>
-      <c r="I185" s="5" t="inlineStr">
+      <c r="I185" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B186" s="5" t="inlineStr">
+      <c r="A186" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B186" s="6" t="inlineStr">
         <is>
           <t>A1-D1</t>
         </is>
       </c>
-      <c r="C186" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D186" s="5" t="inlineStr">
+      <c r="C186" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D186" s="6" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="E186" s="5" t="inlineStr">
+      <c r="E186" s="6" t="inlineStr">
         <is>
           <t>15/07/2026</t>
         </is>
       </c>
-      <c r="F186" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G186" s="5" t="inlineStr"/>
-      <c r="H186" s="5" t="inlineStr">
+      <c r="F186" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G186" s="6" t="inlineStr"/>
+      <c r="H186" s="6" t="inlineStr">
         <is>
           <t>0/35</t>
         </is>
       </c>
-      <c r="I186" s="5" t="inlineStr">
+      <c r="I186" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B187" s="5" t="inlineStr">
+      <c r="A187" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B187" s="6" t="inlineStr">
         <is>
           <t>A1-D1</t>
         </is>
       </c>
-      <c r="C187" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D187" s="5" t="inlineStr">
+      <c r="C187" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D187" s="6" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="E187" s="5" t="inlineStr">
+      <c r="E187" s="6" t="inlineStr">
         <is>
           <t>16/07/2026</t>
         </is>
       </c>
-      <c r="F187" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G187" s="5" t="inlineStr"/>
-      <c r="H187" s="5" t="inlineStr">
+      <c r="F187" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G187" s="6" t="inlineStr"/>
+      <c r="H187" s="6" t="inlineStr">
         <is>
           <t>0/35</t>
         </is>
       </c>
-      <c r="I187" s="5" t="inlineStr">
+      <c r="I187" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B188" s="5" t="inlineStr">
+      <c r="A188" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B188" s="6" t="inlineStr">
         <is>
           <t>A1-D1</t>
         </is>
       </c>
-      <c r="C188" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D188" s="5" t="inlineStr">
+      <c r="C188" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D188" s="6" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="E188" s="5" t="inlineStr">
+      <c r="E188" s="6" t="inlineStr">
         <is>
           <t>21/07/2026</t>
         </is>
       </c>
-      <c r="F188" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G188" s="5" t="inlineStr"/>
-      <c r="H188" s="5" t="inlineStr">
+      <c r="F188" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G188" s="6" t="inlineStr"/>
+      <c r="H188" s="6" t="inlineStr">
         <is>
           <t>0/35</t>
         </is>
       </c>
-      <c r="I188" s="5" t="inlineStr">
+      <c r="I188" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B189" s="5" t="inlineStr">
+      <c r="A189" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B189" s="6" t="inlineStr">
         <is>
           <t>A1-D1</t>
         </is>
       </c>
-      <c r="C189" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D189" s="5" t="inlineStr">
+      <c r="C189" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D189" s="6" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="E189" s="5" t="inlineStr">
+      <c r="E189" s="6" t="inlineStr">
         <is>
           <t>22/07/2026</t>
         </is>
       </c>
-      <c r="F189" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G189" s="5" t="inlineStr"/>
-      <c r="H189" s="5" t="inlineStr">
+      <c r="F189" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G189" s="6" t="inlineStr"/>
+      <c r="H189" s="6" t="inlineStr">
         <is>
           <t>0/35</t>
         </is>
       </c>
-      <c r="I189" s="5" t="inlineStr">
+      <c r="I189" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B190" s="5" t="inlineStr">
+      <c r="A190" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B190" s="6" t="inlineStr">
         <is>
           <t>A1-D1</t>
         </is>
       </c>
-      <c r="C190" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D190" s="5" t="inlineStr">
+      <c r="C190" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D190" s="6" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="E190" s="5" t="inlineStr">
+      <c r="E190" s="6" t="inlineStr">
         <is>
           <t>23/07/2026</t>
         </is>
       </c>
-      <c r="F190" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G190" s="5" t="inlineStr"/>
-      <c r="H190" s="5" t="inlineStr">
+      <c r="F190" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G190" s="6" t="inlineStr"/>
+      <c r="H190" s="6" t="inlineStr">
         <is>
           <t>0/35</t>
         </is>
       </c>
-      <c r="I190" s="5" t="inlineStr">
+      <c r="I190" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -10120,43 +10120,43 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B196" s="9" t="inlineStr">
+      <c r="A196" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B196" s="5" t="inlineStr">
         <is>
           <t>A1-D2</t>
         </is>
       </c>
-      <c r="C196" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D196" s="9" t="inlineStr">
+      <c r="C196" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D196" s="5" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E196" s="9" t="inlineStr">
+      <c r="E196" s="5" t="inlineStr">
         <is>
           <t>04/06/2026</t>
         </is>
       </c>
-      <c r="F196" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G196" s="9" t="inlineStr"/>
-      <c r="H196" s="9" t="inlineStr">
+      <c r="F196" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G196" s="5" t="inlineStr"/>
+      <c r="H196" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I196" s="9" t="inlineStr">
+      <c r="I196" s="5" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
@@ -10774,43 +10774,43 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B210" s="9" t="inlineStr">
+      <c r="A210" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B210" s="5" t="inlineStr">
         <is>
           <t>A1-D2</t>
         </is>
       </c>
-      <c r="C210" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D210" s="9" t="inlineStr">
+      <c r="C210" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D210" s="5" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="E210" s="9" t="inlineStr">
+      <c r="E210" s="5" t="inlineStr">
         <is>
           <t>08/07/2026</t>
         </is>
       </c>
-      <c r="F210" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G210" s="9" t="inlineStr"/>
-      <c r="H210" s="9" t="inlineStr">
+      <c r="F210" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G210" s="5" t="inlineStr"/>
+      <c r="H210" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I210" s="9" t="inlineStr">
+      <c r="I210" s="5" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
@@ -10864,258 +10864,258 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B212" s="5" t="inlineStr">
+      <c r="A212" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B212" s="6" t="inlineStr">
         <is>
           <t>A1-D2</t>
         </is>
       </c>
-      <c r="C212" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D212" s="5" t="inlineStr">
+      <c r="C212" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D212" s="6" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="E212" s="5" t="inlineStr">
+      <c r="E212" s="6" t="inlineStr">
         <is>
           <t>14/07/2026</t>
         </is>
       </c>
-      <c r="F212" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G212" s="5" t="inlineStr"/>
-      <c r="H212" s="5" t="inlineStr">
+      <c r="F212" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G212" s="6" t="inlineStr"/>
+      <c r="H212" s="6" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I212" s="5" t="inlineStr">
+      <c r="I212" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B213" s="5" t="inlineStr">
+      <c r="A213" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B213" s="6" t="inlineStr">
         <is>
           <t>A1-D2</t>
         </is>
       </c>
-      <c r="C213" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D213" s="5" t="inlineStr">
+      <c r="C213" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D213" s="6" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="E213" s="5" t="inlineStr">
+      <c r="E213" s="6" t="inlineStr">
         <is>
           <t>15/07/2026</t>
         </is>
       </c>
-      <c r="F213" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G213" s="5" t="inlineStr"/>
-      <c r="H213" s="5" t="inlineStr">
+      <c r="F213" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G213" s="6" t="inlineStr"/>
+      <c r="H213" s="6" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I213" s="5" t="inlineStr">
+      <c r="I213" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B214" s="5" t="inlineStr">
+      <c r="A214" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B214" s="6" t="inlineStr">
         <is>
           <t>A1-D2</t>
         </is>
       </c>
-      <c r="C214" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D214" s="5" t="inlineStr">
+      <c r="C214" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D214" s="6" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="E214" s="5" t="inlineStr">
+      <c r="E214" s="6" t="inlineStr">
         <is>
           <t>16/07/2026</t>
         </is>
       </c>
-      <c r="F214" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G214" s="5" t="inlineStr"/>
-      <c r="H214" s="5" t="inlineStr">
+      <c r="F214" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G214" s="6" t="inlineStr"/>
+      <c r="H214" s="6" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I214" s="5" t="inlineStr">
+      <c r="I214" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B215" s="5" t="inlineStr">
+      <c r="A215" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B215" s="6" t="inlineStr">
         <is>
           <t>A1-D2</t>
         </is>
       </c>
-      <c r="C215" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D215" s="5" t="inlineStr">
+      <c r="C215" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D215" s="6" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="E215" s="5" t="inlineStr">
+      <c r="E215" s="6" t="inlineStr">
         <is>
           <t>21/07/2026</t>
         </is>
       </c>
-      <c r="F215" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G215" s="5" t="inlineStr"/>
-      <c r="H215" s="5" t="inlineStr">
+      <c r="F215" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G215" s="6" t="inlineStr"/>
+      <c r="H215" s="6" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I215" s="5" t="inlineStr">
+      <c r="I215" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B216" s="5" t="inlineStr">
+      <c r="A216" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B216" s="6" t="inlineStr">
         <is>
           <t>A1-D2</t>
         </is>
       </c>
-      <c r="C216" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D216" s="5" t="inlineStr">
+      <c r="C216" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D216" s="6" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="E216" s="5" t="inlineStr">
+      <c r="E216" s="6" t="inlineStr">
         <is>
           <t>22/07/2026</t>
         </is>
       </c>
-      <c r="F216" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G216" s="5" t="inlineStr"/>
-      <c r="H216" s="5" t="inlineStr">
+      <c r="F216" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G216" s="6" t="inlineStr"/>
+      <c r="H216" s="6" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I216" s="5" t="inlineStr">
+      <c r="I216" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B217" s="5" t="inlineStr">
+      <c r="A217" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B217" s="6" t="inlineStr">
         <is>
           <t>A1-D2</t>
         </is>
       </c>
-      <c r="C217" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D217" s="5" t="inlineStr">
+      <c r="C217" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D217" s="6" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="E217" s="5" t="inlineStr">
+      <c r="E217" s="6" t="inlineStr">
         <is>
           <t>23/07/2026</t>
         </is>
       </c>
-      <c r="F217" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G217" s="5" t="inlineStr"/>
-      <c r="H217" s="5" t="inlineStr">
+      <c r="F217" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G217" s="6" t="inlineStr"/>
+      <c r="H217" s="6" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I217" s="5" t="inlineStr">
+      <c r="I217" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -11357,43 +11357,43 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B223" s="9" t="inlineStr">
+      <c r="A223" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B223" s="5" t="inlineStr">
         <is>
           <t>A1-E1</t>
         </is>
       </c>
-      <c r="C223" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D223" s="9" t="inlineStr">
+      <c r="C223" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D223" s="5" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E223" s="9" t="inlineStr">
+      <c r="E223" s="5" t="inlineStr">
         <is>
           <t>04/06/2026</t>
         </is>
       </c>
-      <c r="F223" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G223" s="9" t="inlineStr"/>
-      <c r="H223" s="9" t="inlineStr">
+      <c r="F223" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G223" s="5" t="inlineStr"/>
+      <c r="H223" s="5" t="inlineStr">
         <is>
           <t>0/38</t>
         </is>
       </c>
-      <c r="I223" s="9" t="inlineStr">
+      <c r="I223" s="5" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
@@ -12058,301 +12058,301 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B238" s="9" t="inlineStr">
+      <c r="A238" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B238" s="5" t="inlineStr">
         <is>
           <t>A1-E1</t>
         </is>
       </c>
-      <c r="C238" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D238" s="9" t="inlineStr">
+      <c r="C238" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D238" s="5" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="E238" s="9" t="inlineStr">
+      <c r="E238" s="5" t="inlineStr">
         <is>
           <t>09/07/2026</t>
         </is>
       </c>
-      <c r="F238" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G238" s="9" t="inlineStr"/>
-      <c r="H238" s="9" t="inlineStr">
+      <c r="F238" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G238" s="5" t="inlineStr"/>
+      <c r="H238" s="5" t="inlineStr">
         <is>
           <t>0/38</t>
         </is>
       </c>
-      <c r="I238" s="9" t="inlineStr">
+      <c r="I238" s="5" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B239" s="5" t="inlineStr">
+      <c r="A239" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B239" s="6" t="inlineStr">
         <is>
           <t>A1-E1</t>
         </is>
       </c>
-      <c r="C239" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D239" s="5" t="inlineStr">
+      <c r="C239" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D239" s="6" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="E239" s="5" t="inlineStr">
+      <c r="E239" s="6" t="inlineStr">
         <is>
           <t>14/07/2026</t>
         </is>
       </c>
-      <c r="F239" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G239" s="5" t="inlineStr"/>
-      <c r="H239" s="5" t="inlineStr">
+      <c r="F239" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G239" s="6" t="inlineStr"/>
+      <c r="H239" s="6" t="inlineStr">
         <is>
           <t>0/38</t>
         </is>
       </c>
-      <c r="I239" s="5" t="inlineStr">
+      <c r="I239" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B240" s="5" t="inlineStr">
+      <c r="A240" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B240" s="6" t="inlineStr">
         <is>
           <t>A1-E1</t>
         </is>
       </c>
-      <c r="C240" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D240" s="5" t="inlineStr">
+      <c r="C240" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D240" s="6" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="E240" s="5" t="inlineStr">
+      <c r="E240" s="6" t="inlineStr">
         <is>
           <t>15/07/2026</t>
         </is>
       </c>
-      <c r="F240" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G240" s="5" t="inlineStr"/>
-      <c r="H240" s="5" t="inlineStr">
+      <c r="F240" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G240" s="6" t="inlineStr"/>
+      <c r="H240" s="6" t="inlineStr">
         <is>
           <t>0/38</t>
         </is>
       </c>
-      <c r="I240" s="5" t="inlineStr">
+      <c r="I240" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B241" s="5" t="inlineStr">
+      <c r="A241" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B241" s="6" t="inlineStr">
         <is>
           <t>A1-E1</t>
         </is>
       </c>
-      <c r="C241" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D241" s="5" t="inlineStr">
+      <c r="C241" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D241" s="6" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="E241" s="5" t="inlineStr">
+      <c r="E241" s="6" t="inlineStr">
         <is>
           <t>16/07/2026</t>
         </is>
       </c>
-      <c r="F241" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G241" s="5" t="inlineStr"/>
-      <c r="H241" s="5" t="inlineStr">
+      <c r="F241" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G241" s="6" t="inlineStr"/>
+      <c r="H241" s="6" t="inlineStr">
         <is>
           <t>0/38</t>
         </is>
       </c>
-      <c r="I241" s="5" t="inlineStr">
+      <c r="I241" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B242" s="5" t="inlineStr">
+      <c r="A242" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B242" s="6" t="inlineStr">
         <is>
           <t>A1-E1</t>
         </is>
       </c>
-      <c r="C242" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D242" s="5" t="inlineStr">
+      <c r="C242" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D242" s="6" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="E242" s="5" t="inlineStr">
+      <c r="E242" s="6" t="inlineStr">
         <is>
           <t>21/07/2026</t>
         </is>
       </c>
-      <c r="F242" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G242" s="5" t="inlineStr"/>
-      <c r="H242" s="5" t="inlineStr">
+      <c r="F242" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G242" s="6" t="inlineStr"/>
+      <c r="H242" s="6" t="inlineStr">
         <is>
           <t>0/38</t>
         </is>
       </c>
-      <c r="I242" s="5" t="inlineStr">
+      <c r="I242" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B243" s="5" t="inlineStr">
+      <c r="A243" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B243" s="6" t="inlineStr">
         <is>
           <t>A1-E1</t>
         </is>
       </c>
-      <c r="C243" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D243" s="5" t="inlineStr">
+      <c r="C243" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D243" s="6" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="E243" s="5" t="inlineStr">
+      <c r="E243" s="6" t="inlineStr">
         <is>
           <t>22/07/2026</t>
         </is>
       </c>
-      <c r="F243" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G243" s="5" t="inlineStr"/>
-      <c r="H243" s="5" t="inlineStr">
+      <c r="F243" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G243" s="6" t="inlineStr"/>
+      <c r="H243" s="6" t="inlineStr">
         <is>
           <t>0/38</t>
         </is>
       </c>
-      <c r="I243" s="5" t="inlineStr">
+      <c r="I243" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B244" s="5" t="inlineStr">
+      <c r="A244" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B244" s="6" t="inlineStr">
         <is>
           <t>A1-E1</t>
         </is>
       </c>
-      <c r="C244" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D244" s="5" t="inlineStr">
+      <c r="C244" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D244" s="6" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="E244" s="5" t="inlineStr">
+      <c r="E244" s="6" t="inlineStr">
         <is>
           <t>23/07/2026</t>
         </is>
       </c>
-      <c r="F244" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G244" s="5" t="inlineStr"/>
-      <c r="H244" s="5" t="inlineStr">
+      <c r="F244" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G244" s="6" t="inlineStr"/>
+      <c r="H244" s="6" t="inlineStr">
         <is>
           <t>0/38</t>
         </is>
       </c>
-      <c r="I244" s="5" t="inlineStr">
+      <c r="I244" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -12594,43 +12594,43 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B250" s="9" t="inlineStr">
+      <c r="A250" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B250" s="5" t="inlineStr">
         <is>
           <t>A1-E2</t>
         </is>
       </c>
-      <c r="C250" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D250" s="9" t="inlineStr">
+      <c r="C250" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D250" s="5" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E250" s="9" t="inlineStr">
+      <c r="E250" s="5" t="inlineStr">
         <is>
           <t>04/06/2026</t>
         </is>
       </c>
-      <c r="F250" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G250" s="9" t="inlineStr"/>
-      <c r="H250" s="9" t="inlineStr">
+      <c r="F250" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G250" s="5" t="inlineStr"/>
+      <c r="H250" s="5" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I250" s="9" t="inlineStr">
+      <c r="I250" s="5" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
@@ -13295,301 +13295,301 @@
       </c>
     </row>
     <row r="265">
-      <c r="A265" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B265" s="9" t="inlineStr">
+      <c r="A265" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B265" s="5" t="inlineStr">
         <is>
           <t>A1-E2</t>
         </is>
       </c>
-      <c r="C265" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D265" s="9" t="inlineStr">
+      <c r="C265" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D265" s="5" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="E265" s="9" t="inlineStr">
+      <c r="E265" s="5" t="inlineStr">
         <is>
           <t>09/07/2026</t>
         </is>
       </c>
-      <c r="F265" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G265" s="9" t="inlineStr"/>
-      <c r="H265" s="9" t="inlineStr">
+      <c r="F265" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G265" s="5" t="inlineStr"/>
+      <c r="H265" s="5" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I265" s="9" t="inlineStr">
+      <c r="I265" s="5" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
       </c>
     </row>
     <row r="266">
-      <c r="A266" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B266" s="5" t="inlineStr">
+      <c r="A266" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B266" s="6" t="inlineStr">
         <is>
           <t>A1-E2</t>
         </is>
       </c>
-      <c r="C266" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D266" s="5" t="inlineStr">
+      <c r="C266" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D266" s="6" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="E266" s="5" t="inlineStr">
+      <c r="E266" s="6" t="inlineStr">
         <is>
           <t>14/07/2026</t>
         </is>
       </c>
-      <c r="F266" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G266" s="5" t="inlineStr"/>
-      <c r="H266" s="5" t="inlineStr">
+      <c r="F266" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G266" s="6" t="inlineStr"/>
+      <c r="H266" s="6" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I266" s="5" t="inlineStr">
+      <c r="I266" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="267">
-      <c r="A267" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B267" s="5" t="inlineStr">
+      <c r="A267" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B267" s="6" t="inlineStr">
         <is>
           <t>A1-E2</t>
         </is>
       </c>
-      <c r="C267" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D267" s="5" t="inlineStr">
+      <c r="C267" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D267" s="6" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="E267" s="5" t="inlineStr">
+      <c r="E267" s="6" t="inlineStr">
         <is>
           <t>15/07/2026</t>
         </is>
       </c>
-      <c r="F267" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G267" s="5" t="inlineStr"/>
-      <c r="H267" s="5" t="inlineStr">
+      <c r="F267" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G267" s="6" t="inlineStr"/>
+      <c r="H267" s="6" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I267" s="5" t="inlineStr">
+      <c r="I267" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="268">
-      <c r="A268" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B268" s="5" t="inlineStr">
+      <c r="A268" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B268" s="6" t="inlineStr">
         <is>
           <t>A1-E2</t>
         </is>
       </c>
-      <c r="C268" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D268" s="5" t="inlineStr">
+      <c r="C268" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D268" s="6" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="E268" s="5" t="inlineStr">
+      <c r="E268" s="6" t="inlineStr">
         <is>
           <t>16/07/2026</t>
         </is>
       </c>
-      <c r="F268" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G268" s="5" t="inlineStr"/>
-      <c r="H268" s="5" t="inlineStr">
+      <c r="F268" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G268" s="6" t="inlineStr"/>
+      <c r="H268" s="6" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I268" s="5" t="inlineStr">
+      <c r="I268" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="269">
-      <c r="A269" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B269" s="5" t="inlineStr">
+      <c r="A269" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B269" s="6" t="inlineStr">
         <is>
           <t>A1-E2</t>
         </is>
       </c>
-      <c r="C269" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D269" s="5" t="inlineStr">
+      <c r="C269" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D269" s="6" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="E269" s="5" t="inlineStr">
+      <c r="E269" s="6" t="inlineStr">
         <is>
           <t>21/07/2026</t>
         </is>
       </c>
-      <c r="F269" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G269" s="5" t="inlineStr"/>
-      <c r="H269" s="5" t="inlineStr">
+      <c r="F269" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G269" s="6" t="inlineStr"/>
+      <c r="H269" s="6" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I269" s="5" t="inlineStr">
+      <c r="I269" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="270">
-      <c r="A270" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B270" s="5" t="inlineStr">
+      <c r="A270" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B270" s="6" t="inlineStr">
         <is>
           <t>A1-E2</t>
         </is>
       </c>
-      <c r="C270" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D270" s="5" t="inlineStr">
+      <c r="C270" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D270" s="6" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="E270" s="5" t="inlineStr">
+      <c r="E270" s="6" t="inlineStr">
         <is>
           <t>22/07/2026</t>
         </is>
       </c>
-      <c r="F270" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G270" s="5" t="inlineStr"/>
-      <c r="H270" s="5" t="inlineStr">
+      <c r="F270" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G270" s="6" t="inlineStr"/>
+      <c r="H270" s="6" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I270" s="5" t="inlineStr">
+      <c r="I270" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="271">
-      <c r="A271" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B271" s="5" t="inlineStr">
+      <c r="A271" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B271" s="6" t="inlineStr">
         <is>
           <t>A1-E2</t>
         </is>
       </c>
-      <c r="C271" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D271" s="5" t="inlineStr">
+      <c r="C271" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D271" s="6" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="E271" s="5" t="inlineStr">
+      <c r="E271" s="6" t="inlineStr">
         <is>
           <t>23/07/2026</t>
         </is>
       </c>
-      <c r="F271" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G271" s="5" t="inlineStr"/>
-      <c r="H271" s="5" t="inlineStr">
+      <c r="F271" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G271" s="6" t="inlineStr"/>
+      <c r="H271" s="6" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I271" s="5" t="inlineStr">
+      <c r="I271" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -13831,43 +13831,43 @@
       </c>
     </row>
     <row r="277">
-      <c r="A277" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B277" s="9" t="inlineStr">
+      <c r="A277" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B277" s="5" t="inlineStr">
         <is>
           <t>A1-F1</t>
         </is>
       </c>
-      <c r="C277" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D277" s="9" t="inlineStr">
+      <c r="C277" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D277" s="5" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E277" s="9" t="inlineStr">
+      <c r="E277" s="5" t="inlineStr">
         <is>
           <t>04/06/2026</t>
         </is>
       </c>
-      <c r="F277" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G277" s="9" t="inlineStr"/>
-      <c r="H277" s="9" t="inlineStr">
+      <c r="F277" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G277" s="5" t="inlineStr"/>
+      <c r="H277" s="5" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I277" s="9" t="inlineStr">
+      <c r="I277" s="5" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
@@ -14579,258 +14579,258 @@
       </c>
     </row>
     <row r="293">
-      <c r="A293" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B293" s="5" t="inlineStr">
+      <c r="A293" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B293" s="6" t="inlineStr">
         <is>
           <t>A1-F1</t>
         </is>
       </c>
-      <c r="C293" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D293" s="5" t="inlineStr">
+      <c r="C293" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D293" s="6" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="E293" s="5" t="inlineStr">
+      <c r="E293" s="6" t="inlineStr">
         <is>
           <t>14/07/2026</t>
         </is>
       </c>
-      <c r="F293" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G293" s="5" t="inlineStr"/>
-      <c r="H293" s="5" t="inlineStr">
+      <c r="F293" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G293" s="6" t="inlineStr"/>
+      <c r="H293" s="6" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I293" s="5" t="inlineStr">
+      <c r="I293" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="294">
-      <c r="A294" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B294" s="5" t="inlineStr">
+      <c r="A294" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B294" s="6" t="inlineStr">
         <is>
           <t>A1-F1</t>
         </is>
       </c>
-      <c r="C294" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D294" s="5" t="inlineStr">
+      <c r="C294" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D294" s="6" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="E294" s="5" t="inlineStr">
+      <c r="E294" s="6" t="inlineStr">
         <is>
           <t>15/07/2026</t>
         </is>
       </c>
-      <c r="F294" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G294" s="5" t="inlineStr"/>
-      <c r="H294" s="5" t="inlineStr">
+      <c r="F294" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G294" s="6" t="inlineStr"/>
+      <c r="H294" s="6" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I294" s="5" t="inlineStr">
+      <c r="I294" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="295">
-      <c r="A295" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B295" s="5" t="inlineStr">
+      <c r="A295" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B295" s="6" t="inlineStr">
         <is>
           <t>A1-F1</t>
         </is>
       </c>
-      <c r="C295" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D295" s="5" t="inlineStr">
+      <c r="C295" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D295" s="6" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="E295" s="5" t="inlineStr">
+      <c r="E295" s="6" t="inlineStr">
         <is>
           <t>16/07/2026</t>
         </is>
       </c>
-      <c r="F295" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G295" s="5" t="inlineStr"/>
-      <c r="H295" s="5" t="inlineStr">
+      <c r="F295" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G295" s="6" t="inlineStr"/>
+      <c r="H295" s="6" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I295" s="5" t="inlineStr">
+      <c r="I295" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="296">
-      <c r="A296" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B296" s="5" t="inlineStr">
+      <c r="A296" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B296" s="6" t="inlineStr">
         <is>
           <t>A1-F1</t>
         </is>
       </c>
-      <c r="C296" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D296" s="5" t="inlineStr">
+      <c r="C296" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D296" s="6" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="E296" s="5" t="inlineStr">
+      <c r="E296" s="6" t="inlineStr">
         <is>
           <t>21/07/2026</t>
         </is>
       </c>
-      <c r="F296" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G296" s="5" t="inlineStr"/>
-      <c r="H296" s="5" t="inlineStr">
+      <c r="F296" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G296" s="6" t="inlineStr"/>
+      <c r="H296" s="6" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I296" s="5" t="inlineStr">
+      <c r="I296" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="297">
-      <c r="A297" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B297" s="5" t="inlineStr">
+      <c r="A297" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B297" s="6" t="inlineStr">
         <is>
           <t>A1-F1</t>
         </is>
       </c>
-      <c r="C297" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D297" s="5" t="inlineStr">
+      <c r="C297" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D297" s="6" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="E297" s="5" t="inlineStr">
+      <c r="E297" s="6" t="inlineStr">
         <is>
           <t>22/07/2026</t>
         </is>
       </c>
-      <c r="F297" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G297" s="5" t="inlineStr"/>
-      <c r="H297" s="5" t="inlineStr">
+      <c r="F297" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G297" s="6" t="inlineStr"/>
+      <c r="H297" s="6" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I297" s="5" t="inlineStr">
+      <c r="I297" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="298">
-      <c r="A298" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B298" s="5" t="inlineStr">
+      <c r="A298" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B298" s="6" t="inlineStr">
         <is>
           <t>A1-F1</t>
         </is>
       </c>
-      <c r="C298" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D298" s="5" t="inlineStr">
+      <c r="C298" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D298" s="6" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="E298" s="5" t="inlineStr">
+      <c r="E298" s="6" t="inlineStr">
         <is>
           <t>23/07/2026</t>
         </is>
       </c>
-      <c r="F298" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G298" s="5" t="inlineStr"/>
-      <c r="H298" s="5" t="inlineStr">
+      <c r="F298" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G298" s="6" t="inlineStr"/>
+      <c r="H298" s="6" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I298" s="5" t="inlineStr">
+      <c r="I298" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -15072,43 +15072,43 @@
       </c>
     </row>
     <row r="304">
-      <c r="A304" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B304" s="9" t="inlineStr">
+      <c r="A304" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B304" s="5" t="inlineStr">
         <is>
           <t>A1-F2</t>
         </is>
       </c>
-      <c r="C304" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D304" s="9" t="inlineStr">
+      <c r="C304" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D304" s="5" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E304" s="9" t="inlineStr">
+      <c r="E304" s="5" t="inlineStr">
         <is>
           <t>04/06/2026</t>
         </is>
       </c>
-      <c r="F304" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G304" s="9" t="inlineStr"/>
-      <c r="H304" s="9" t="inlineStr">
+      <c r="F304" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G304" s="5" t="inlineStr"/>
+      <c r="H304" s="5" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I304" s="9" t="inlineStr">
+      <c r="I304" s="5" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
@@ -15679,43 +15679,43 @@
       </c>
     </row>
     <row r="317">
-      <c r="A317" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B317" s="9" t="inlineStr">
+      <c r="A317" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B317" s="5" t="inlineStr">
         <is>
           <t>A1-F2</t>
         </is>
       </c>
-      <c r="C317" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D317" s="9" t="inlineStr">
+      <c r="C317" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D317" s="5" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="E317" s="9" t="inlineStr">
+      <c r="E317" s="5" t="inlineStr">
         <is>
           <t>07/07/2026</t>
         </is>
       </c>
-      <c r="F317" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G317" s="9" t="inlineStr"/>
-      <c r="H317" s="9" t="inlineStr">
+      <c r="F317" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G317" s="5" t="inlineStr"/>
+      <c r="H317" s="5" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I317" s="9" t="inlineStr">
+      <c r="I317" s="5" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
@@ -15816,258 +15816,258 @@
       </c>
     </row>
     <row r="320">
-      <c r="A320" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B320" s="5" t="inlineStr">
+      <c r="A320" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B320" s="6" t="inlineStr">
         <is>
           <t>A1-F2</t>
         </is>
       </c>
-      <c r="C320" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D320" s="5" t="inlineStr">
+      <c r="C320" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D320" s="6" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="E320" s="5" t="inlineStr">
+      <c r="E320" s="6" t="inlineStr">
         <is>
           <t>14/07/2026</t>
         </is>
       </c>
-      <c r="F320" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G320" s="5" t="inlineStr"/>
-      <c r="H320" s="5" t="inlineStr">
+      <c r="F320" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G320" s="6" t="inlineStr"/>
+      <c r="H320" s="6" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I320" s="5" t="inlineStr">
+      <c r="I320" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="321">
-      <c r="A321" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B321" s="5" t="inlineStr">
+      <c r="A321" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B321" s="6" t="inlineStr">
         <is>
           <t>A1-F2</t>
         </is>
       </c>
-      <c r="C321" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D321" s="5" t="inlineStr">
+      <c r="C321" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D321" s="6" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="E321" s="5" t="inlineStr">
+      <c r="E321" s="6" t="inlineStr">
         <is>
           <t>15/07/2026</t>
         </is>
       </c>
-      <c r="F321" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G321" s="5" t="inlineStr"/>
-      <c r="H321" s="5" t="inlineStr">
+      <c r="F321" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G321" s="6" t="inlineStr"/>
+      <c r="H321" s="6" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I321" s="5" t="inlineStr">
+      <c r="I321" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="322">
-      <c r="A322" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B322" s="5" t="inlineStr">
+      <c r="A322" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B322" s="6" t="inlineStr">
         <is>
           <t>A1-F2</t>
         </is>
       </c>
-      <c r="C322" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D322" s="5" t="inlineStr">
+      <c r="C322" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D322" s="6" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="E322" s="5" t="inlineStr">
+      <c r="E322" s="6" t="inlineStr">
         <is>
           <t>16/07/2026</t>
         </is>
       </c>
-      <c r="F322" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G322" s="5" t="inlineStr"/>
-      <c r="H322" s="5" t="inlineStr">
+      <c r="F322" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G322" s="6" t="inlineStr"/>
+      <c r="H322" s="6" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I322" s="5" t="inlineStr">
+      <c r="I322" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="323">
-      <c r="A323" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B323" s="5" t="inlineStr">
+      <c r="A323" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B323" s="6" t="inlineStr">
         <is>
           <t>A1-F2</t>
         </is>
       </c>
-      <c r="C323" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D323" s="5" t="inlineStr">
+      <c r="C323" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D323" s="6" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="E323" s="5" t="inlineStr">
+      <c r="E323" s="6" t="inlineStr">
         <is>
           <t>21/07/2026</t>
         </is>
       </c>
-      <c r="F323" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G323" s="5" t="inlineStr"/>
-      <c r="H323" s="5" t="inlineStr">
+      <c r="F323" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G323" s="6" t="inlineStr"/>
+      <c r="H323" s="6" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I323" s="5" t="inlineStr">
+      <c r="I323" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="324">
-      <c r="A324" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B324" s="5" t="inlineStr">
+      <c r="A324" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B324" s="6" t="inlineStr">
         <is>
           <t>A1-F2</t>
         </is>
       </c>
-      <c r="C324" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D324" s="5" t="inlineStr">
+      <c r="C324" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D324" s="6" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="E324" s="5" t="inlineStr">
+      <c r="E324" s="6" t="inlineStr">
         <is>
           <t>22/07/2026</t>
         </is>
       </c>
-      <c r="F324" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G324" s="5" t="inlineStr"/>
-      <c r="H324" s="5" t="inlineStr">
+      <c r="F324" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G324" s="6" t="inlineStr"/>
+      <c r="H324" s="6" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I324" s="5" t="inlineStr">
+      <c r="I324" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="325">
-      <c r="A325" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B325" s="5" t="inlineStr">
+      <c r="A325" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B325" s="6" t="inlineStr">
         <is>
           <t>A1-F2</t>
         </is>
       </c>
-      <c r="C325" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D325" s="5" t="inlineStr">
+      <c r="C325" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D325" s="6" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="E325" s="5" t="inlineStr">
+      <c r="E325" s="6" t="inlineStr">
         <is>
           <t>23/07/2026</t>
         </is>
       </c>
-      <c r="F325" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G325" s="5" t="inlineStr"/>
-      <c r="H325" s="5" t="inlineStr">
+      <c r="F325" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G325" s="6" t="inlineStr"/>
+      <c r="H325" s="6" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I325" s="5" t="inlineStr">
+      <c r="I325" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A1_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A1_session_analysis.xlsx
@@ -58,14 +58,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFB6C1"/>
-        <bgColor rgb="00FFB6C1"/>
+        <fgColor rgb="00FFFFE0"/>
+        <bgColor rgb="00FFFFE0"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFFE0"/>
-        <bgColor rgb="00FFFFE0"/>
+        <fgColor rgb="00FFB6C1"/>
+        <bgColor rgb="00FFB6C1"/>
       </patternFill>
     </fill>
   </fills>
@@ -96,16 +96,16 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -814,7 +814,7 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>247</v>
+        <v>253</v>
       </c>
     </row>
     <row r="7">
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8">
@@ -980,7 +980,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>76.2%</t>
+          <t>78.1%</t>
         </is>
       </c>
     </row>
@@ -1037,7 +1037,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>74.6%</t>
+          <t>73.8%</t>
         </is>
       </c>
     </row>
@@ -1342,22 +1342,22 @@
         <v>27</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q15" s="4" t="n">
         <v>4</v>
       </c>
       <c r="R15" s="4" t="inlineStr">
         <is>
-          <t>81.5%</t>
+          <t>85.2%</t>
         </is>
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>70.2%</t>
+          <t>68.8%</t>
         </is>
       </c>
     </row>
@@ -1424,22 +1424,22 @@
         <v>27</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q16" s="4" t="n">
         <v>4</v>
       </c>
       <c r="R16" s="4" t="inlineStr">
         <is>
-          <t>81.5%</t>
+          <t>85.2%</t>
         </is>
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>70.9%</t>
+          <t>69.7%</t>
         </is>
       </c>
     </row>
@@ -1506,22 +1506,22 @@
         <v>27</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q17" s="4" t="n">
         <v>4</v>
       </c>
       <c r="R17" s="4" t="inlineStr">
         <is>
-          <t>81.5%</t>
+          <t>85.2%</t>
         </is>
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>76.1%</t>
+          <t>74.3%</t>
         </is>
       </c>
     </row>
@@ -1588,22 +1588,22 @@
         <v>27</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q18" s="4" t="n">
         <v>4</v>
       </c>
       <c r="R18" s="4" t="inlineStr">
         <is>
-          <t>81.5%</t>
+          <t>85.2%</t>
         </is>
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>74.5%</t>
+          <t>73.0%</t>
         </is>
       </c>
     </row>
@@ -1670,22 +1670,22 @@
         <v>27</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q19" s="4" t="n">
         <v>4</v>
       </c>
       <c r="R19" s="4" t="inlineStr">
         <is>
-          <t>81.5%</t>
+          <t>85.2%</t>
         </is>
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>77.0%</t>
+          <t>75.1%</t>
         </is>
       </c>
     </row>
@@ -1752,22 +1752,22 @@
         <v>27</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q20" s="4" t="n">
         <v>4</v>
       </c>
       <c r="R20" s="4" t="inlineStr">
         <is>
-          <t>81.5%</t>
+          <t>85.2%</t>
         </is>
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>69.7%</t>
+          <t>69.3%</t>
         </is>
       </c>
     </row>
@@ -2018,45 +2018,49 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B24" s="5" t="inlineStr">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>A1-A1</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D24" s="5" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="E24" s="5" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>12/07/2026</t>
         </is>
       </c>
-      <c r="F24" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G24" s="5" t="inlineStr"/>
-      <c r="H24" s="5" t="inlineStr">
-        <is>
-          <t>0/34</t>
-        </is>
-      </c>
-      <c r="I24" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>13/34</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
       <c r="K24" s="4" t="inlineStr">
@@ -2096,43 +2100,43 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B25" s="6" t="inlineStr">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
         <is>
           <t>A1-A1</t>
         </is>
       </c>
-      <c r="C25" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D25" s="6" t="inlineStr">
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="E25" s="6" t="inlineStr">
+      <c r="E25" s="5" t="inlineStr">
         <is>
           <t>13/07/2026</t>
         </is>
       </c>
-      <c r="F25" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G25" s="6" t="inlineStr"/>
-      <c r="H25" s="6" t="inlineStr">
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr"/>
+      <c r="H25" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I25" s="6" t="inlineStr">
+      <c r="I25" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -2174,43 +2178,43 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B26" s="6" t="inlineStr">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
         <is>
           <t>A1-A1</t>
         </is>
       </c>
-      <c r="C26" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D26" s="6" t="inlineStr">
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="E26" s="6" t="inlineStr">
+      <c r="E26" s="5" t="inlineStr">
         <is>
           <t>18/07/2026</t>
         </is>
       </c>
-      <c r="F26" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G26" s="6" t="inlineStr"/>
-      <c r="H26" s="6" t="inlineStr">
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="inlineStr"/>
+      <c r="H26" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I26" s="6" t="inlineStr">
+      <c r="I26" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -2252,86 +2256,86 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B27" s="6" t="inlineStr">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
         <is>
           <t>A1-A1</t>
         </is>
       </c>
-      <c r="C27" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D27" s="6" t="inlineStr">
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="E27" s="6" t="inlineStr">
+      <c r="E27" s="5" t="inlineStr">
         <is>
           <t>19/07/2026</t>
         </is>
       </c>
-      <c r="F27" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G27" s="6" t="inlineStr"/>
-      <c r="H27" s="6" t="inlineStr">
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="inlineStr"/>
+      <c r="H27" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I27" s="6" t="inlineStr">
+      <c r="I27" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B28" s="6" t="inlineStr">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
         <is>
           <t>A1-A1</t>
         </is>
       </c>
-      <c r="C28" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D28" s="6" t="inlineStr">
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="E28" s="6" t="inlineStr">
+      <c r="E28" s="5" t="inlineStr">
         <is>
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="F28" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G28" s="6" t="inlineStr"/>
-      <c r="H28" s="6" t="inlineStr">
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G28" s="5" t="inlineStr"/>
+      <c r="H28" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I28" s="6" t="inlineStr">
+      <c r="I28" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -2502,7 +2506,7 @@
           <t>Recorded</t>
         </is>
       </c>
-      <c r="L31" s="7" t="inlineStr">
+      <c r="L31" s="6" t="inlineStr">
         <is>
           <t>Green</t>
         </is>
@@ -2564,7 +2568,7 @@
           <t>Not Recorded</t>
         </is>
       </c>
-      <c r="L32" s="8" t="inlineStr">
+      <c r="L32" s="7" t="inlineStr">
         <is>
           <t>Red</t>
         </is>
@@ -2626,7 +2630,7 @@
           <t>Pending</t>
         </is>
       </c>
-      <c r="L33" s="9" t="inlineStr">
+      <c r="L33" s="8" t="inlineStr">
         <is>
           <t>Yellow</t>
         </is>
@@ -3437,215 +3441,219 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B51" s="5" t="inlineStr">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
         <is>
           <t>A1-A2</t>
         </is>
       </c>
-      <c r="C51" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D51" s="5" t="inlineStr">
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="E51" s="5" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>12/07/2026</t>
         </is>
       </c>
-      <c r="F51" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G51" s="5" t="inlineStr"/>
-      <c r="H51" s="5" t="inlineStr">
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>14/33</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="inlineStr">
+        <is>
+          <t>A1-A2</t>
+        </is>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D52" s="5" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="E52" s="5" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="F52" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G52" s="5" t="inlineStr"/>
+      <c r="H52" s="5" t="inlineStr">
         <is>
           <t>0/33</t>
         </is>
       </c>
-      <c r="I51" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B52" s="6" t="inlineStr">
+      <c r="I52" s="5" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
         <is>
           <t>A1-A2</t>
         </is>
       </c>
-      <c r="C52" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D52" s="6" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="E52" s="6" t="inlineStr">
-        <is>
-          <t>13/07/2026</t>
-        </is>
-      </c>
-      <c r="F52" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G52" s="6" t="inlineStr"/>
-      <c r="H52" s="6" t="inlineStr">
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D53" s="5" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E53" s="5" t="inlineStr">
+        <is>
+          <t>18/07/2026</t>
+        </is>
+      </c>
+      <c r="F53" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G53" s="5" t="inlineStr"/>
+      <c r="H53" s="5" t="inlineStr">
         <is>
           <t>0/33</t>
         </is>
       </c>
-      <c r="I52" s="6" t="inlineStr">
+      <c r="I53" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B53" s="6" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="inlineStr">
         <is>
           <t>A1-A2</t>
         </is>
       </c>
-      <c r="C53" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D53" s="6" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="E53" s="6" t="inlineStr">
-        <is>
-          <t>18/07/2026</t>
-        </is>
-      </c>
-      <c r="F53" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G53" s="6" t="inlineStr"/>
-      <c r="H53" s="6" t="inlineStr">
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D54" s="5" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="E54" s="5" t="inlineStr">
+        <is>
+          <t>19/07/2026</t>
+        </is>
+      </c>
+      <c r="F54" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G54" s="5" t="inlineStr"/>
+      <c r="H54" s="5" t="inlineStr">
         <is>
           <t>0/33</t>
         </is>
       </c>
-      <c r="I53" s="6" t="inlineStr">
+      <c r="I54" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B54" s="6" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="inlineStr">
         <is>
           <t>A1-A2</t>
         </is>
       </c>
-      <c r="C54" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D54" s="6" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="E54" s="6" t="inlineStr">
-        <is>
-          <t>19/07/2026</t>
-        </is>
-      </c>
-      <c r="F54" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G54" s="6" t="inlineStr"/>
-      <c r="H54" s="6" t="inlineStr">
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D55" s="5" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E55" s="5" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="F55" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G55" s="5" t="inlineStr"/>
+      <c r="H55" s="5" t="inlineStr">
         <is>
           <t>0/33</t>
         </is>
       </c>
-      <c r="I54" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B55" s="6" t="inlineStr">
-        <is>
-          <t>A1-A2</t>
-        </is>
-      </c>
-      <c r="C55" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D55" s="6" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="E55" s="6" t="inlineStr">
-        <is>
-          <t>20/07/2026</t>
-        </is>
-      </c>
-      <c r="F55" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G55" s="6" t="inlineStr"/>
-      <c r="H55" s="6" t="inlineStr">
-        <is>
-          <t>0/33</t>
-        </is>
-      </c>
-      <c r="I55" s="6" t="inlineStr">
+      <c r="I55" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -4686,215 +4694,219 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B78" s="5" t="inlineStr">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
         <is>
           <t>A1-B1</t>
         </is>
       </c>
-      <c r="C78" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D78" s="5" t="inlineStr">
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="E78" s="5" t="inlineStr">
+      <c r="E78" s="2" t="inlineStr">
         <is>
           <t>12/07/2026</t>
         </is>
       </c>
-      <c r="F78" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G78" s="5" t="inlineStr"/>
-      <c r="H78" s="5" t="inlineStr">
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>12/34</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B79" s="5" t="inlineStr">
+        <is>
+          <t>A1-B1</t>
+        </is>
+      </c>
+      <c r="C79" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D79" s="5" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="E79" s="5" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="F79" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G79" s="5" t="inlineStr"/>
+      <c r="H79" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I78" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B79" s="6" t="inlineStr">
+      <c r="I79" s="5" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B80" s="5" t="inlineStr">
         <is>
           <t>A1-B1</t>
         </is>
       </c>
-      <c r="C79" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D79" s="6" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="E79" s="6" t="inlineStr">
-        <is>
-          <t>13/07/2026</t>
-        </is>
-      </c>
-      <c r="F79" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G79" s="6" t="inlineStr"/>
-      <c r="H79" s="6" t="inlineStr">
+      <c r="C80" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D80" s="5" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E80" s="5" t="inlineStr">
+        <is>
+          <t>18/07/2026</t>
+        </is>
+      </c>
+      <c r="F80" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G80" s="5" t="inlineStr"/>
+      <c r="H80" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I79" s="6" t="inlineStr">
+      <c r="I80" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B80" s="6" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B81" s="5" t="inlineStr">
         <is>
           <t>A1-B1</t>
         </is>
       </c>
-      <c r="C80" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D80" s="6" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="E80" s="6" t="inlineStr">
-        <is>
-          <t>18/07/2026</t>
-        </is>
-      </c>
-      <c r="F80" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G80" s="6" t="inlineStr"/>
-      <c r="H80" s="6" t="inlineStr">
+      <c r="C81" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D81" s="5" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="E81" s="5" t="inlineStr">
+        <is>
+          <t>19/07/2026</t>
+        </is>
+      </c>
+      <c r="F81" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G81" s="5" t="inlineStr"/>
+      <c r="H81" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I80" s="6" t="inlineStr">
+      <c r="I81" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B81" s="6" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B82" s="5" t="inlineStr">
         <is>
           <t>A1-B1</t>
         </is>
       </c>
-      <c r="C81" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D81" s="6" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="E81" s="6" t="inlineStr">
-        <is>
-          <t>19/07/2026</t>
-        </is>
-      </c>
-      <c r="F81" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G81" s="6" t="inlineStr"/>
-      <c r="H81" s="6" t="inlineStr">
+      <c r="C82" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D82" s="5" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E82" s="5" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="F82" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G82" s="5" t="inlineStr"/>
+      <c r="H82" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I81" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B82" s="6" t="inlineStr">
-        <is>
-          <t>A1-B1</t>
-        </is>
-      </c>
-      <c r="C82" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D82" s="6" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="E82" s="6" t="inlineStr">
-        <is>
-          <t>20/07/2026</t>
-        </is>
-      </c>
-      <c r="F82" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G82" s="6" t="inlineStr"/>
-      <c r="H82" s="6" t="inlineStr">
-        <is>
-          <t>0/34</t>
-        </is>
-      </c>
-      <c r="I82" s="6" t="inlineStr">
+      <c r="I82" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -5935,215 +5947,219 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B105" s="5" t="inlineStr">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
         <is>
           <t>A1-B2</t>
         </is>
       </c>
-      <c r="C105" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D105" s="5" t="inlineStr">
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="E105" s="5" t="inlineStr">
+      <c r="E105" s="2" t="inlineStr">
         <is>
           <t>12/07/2026</t>
         </is>
       </c>
-      <c r="F105" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G105" s="5" t="inlineStr"/>
-      <c r="H105" s="5" t="inlineStr">
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>14/34</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B106" s="5" t="inlineStr">
+        <is>
+          <t>A1-B2</t>
+        </is>
+      </c>
+      <c r="C106" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D106" s="5" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="E106" s="5" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="F106" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G106" s="5" t="inlineStr"/>
+      <c r="H106" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I105" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B106" s="6" t="inlineStr">
+      <c r="I106" s="5" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B107" s="5" t="inlineStr">
         <is>
           <t>A1-B2</t>
         </is>
       </c>
-      <c r="C106" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D106" s="6" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="E106" s="6" t="inlineStr">
-        <is>
-          <t>13/07/2026</t>
-        </is>
-      </c>
-      <c r="F106" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G106" s="6" t="inlineStr"/>
-      <c r="H106" s="6" t="inlineStr">
+      <c r="C107" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D107" s="5" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E107" s="5" t="inlineStr">
+        <is>
+          <t>18/07/2026</t>
+        </is>
+      </c>
+      <c r="F107" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G107" s="5" t="inlineStr"/>
+      <c r="H107" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I106" s="6" t="inlineStr">
+      <c r="I107" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B107" s="6" t="inlineStr">
+    <row r="108">
+      <c r="A108" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B108" s="5" t="inlineStr">
         <is>
           <t>A1-B2</t>
         </is>
       </c>
-      <c r="C107" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D107" s="6" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="E107" s="6" t="inlineStr">
-        <is>
-          <t>18/07/2026</t>
-        </is>
-      </c>
-      <c r="F107" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G107" s="6" t="inlineStr"/>
-      <c r="H107" s="6" t="inlineStr">
+      <c r="C108" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D108" s="5" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="E108" s="5" t="inlineStr">
+        <is>
+          <t>19/07/2026</t>
+        </is>
+      </c>
+      <c r="F108" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G108" s="5" t="inlineStr"/>
+      <c r="H108" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I107" s="6" t="inlineStr">
+      <c r="I108" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B108" s="6" t="inlineStr">
+    <row r="109">
+      <c r="A109" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B109" s="5" t="inlineStr">
         <is>
           <t>A1-B2</t>
         </is>
       </c>
-      <c r="C108" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D108" s="6" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="E108" s="6" t="inlineStr">
-        <is>
-          <t>19/07/2026</t>
-        </is>
-      </c>
-      <c r="F108" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G108" s="6" t="inlineStr"/>
-      <c r="H108" s="6" t="inlineStr">
+      <c r="C109" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D109" s="5" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E109" s="5" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="F109" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G109" s="5" t="inlineStr"/>
+      <c r="H109" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I108" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B109" s="6" t="inlineStr">
-        <is>
-          <t>A1-B2</t>
-        </is>
-      </c>
-      <c r="C109" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D109" s="6" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="E109" s="6" t="inlineStr">
-        <is>
-          <t>20/07/2026</t>
-        </is>
-      </c>
-      <c r="F109" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G109" s="6" t="inlineStr"/>
-      <c r="H109" s="6" t="inlineStr">
-        <is>
-          <t>0/34</t>
-        </is>
-      </c>
-      <c r="I109" s="6" t="inlineStr">
+      <c r="I109" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -7184,215 +7200,219 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B132" s="5" t="inlineStr">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
         <is>
           <t>A1-C1</t>
         </is>
       </c>
-      <c r="C132" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D132" s="5" t="inlineStr">
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="E132" s="5" t="inlineStr">
+      <c r="E132" s="2" t="inlineStr">
         <is>
           <t>12/07/2026</t>
         </is>
       </c>
-      <c r="F132" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G132" s="5" t="inlineStr"/>
-      <c r="H132" s="5" t="inlineStr">
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G132" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H132" s="2" t="inlineStr">
+        <is>
+          <t>11/34</t>
+        </is>
+      </c>
+      <c r="I132" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B133" s="5" t="inlineStr">
+        <is>
+          <t>A1-C1</t>
+        </is>
+      </c>
+      <c r="C133" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D133" s="5" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="E133" s="5" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="F133" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G133" s="5" t="inlineStr"/>
+      <c r="H133" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I132" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B133" s="6" t="inlineStr">
+      <c r="I133" s="5" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B134" s="5" t="inlineStr">
         <is>
           <t>A1-C1</t>
         </is>
       </c>
-      <c r="C133" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D133" s="6" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="E133" s="6" t="inlineStr">
-        <is>
-          <t>13/07/2026</t>
-        </is>
-      </c>
-      <c r="F133" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G133" s="6" t="inlineStr"/>
-      <c r="H133" s="6" t="inlineStr">
+      <c r="C134" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D134" s="5" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E134" s="5" t="inlineStr">
+        <is>
+          <t>18/07/2026</t>
+        </is>
+      </c>
+      <c r="F134" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G134" s="5" t="inlineStr"/>
+      <c r="H134" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I133" s="6" t="inlineStr">
+      <c r="I134" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="134">
-      <c r="A134" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B134" s="6" t="inlineStr">
+    <row r="135">
+      <c r="A135" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B135" s="5" t="inlineStr">
         <is>
           <t>A1-C1</t>
         </is>
       </c>
-      <c r="C134" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D134" s="6" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="E134" s="6" t="inlineStr">
-        <is>
-          <t>18/07/2026</t>
-        </is>
-      </c>
-      <c r="F134" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G134" s="6" t="inlineStr"/>
-      <c r="H134" s="6" t="inlineStr">
+      <c r="C135" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D135" s="5" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="E135" s="5" t="inlineStr">
+        <is>
+          <t>19/07/2026</t>
+        </is>
+      </c>
+      <c r="F135" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G135" s="5" t="inlineStr"/>
+      <c r="H135" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I134" s="6" t="inlineStr">
+      <c r="I135" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B135" s="6" t="inlineStr">
+    <row r="136">
+      <c r="A136" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B136" s="5" t="inlineStr">
         <is>
           <t>A1-C1</t>
         </is>
       </c>
-      <c r="C135" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D135" s="6" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="E135" s="6" t="inlineStr">
-        <is>
-          <t>19/07/2026</t>
-        </is>
-      </c>
-      <c r="F135" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G135" s="6" t="inlineStr"/>
-      <c r="H135" s="6" t="inlineStr">
+      <c r="C136" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D136" s="5" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E136" s="5" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="F136" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G136" s="5" t="inlineStr"/>
+      <c r="H136" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I135" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B136" s="6" t="inlineStr">
-        <is>
-          <t>A1-C1</t>
-        </is>
-      </c>
-      <c r="C136" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D136" s="6" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="E136" s="6" t="inlineStr">
-        <is>
-          <t>20/07/2026</t>
-        </is>
-      </c>
-      <c r="F136" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G136" s="6" t="inlineStr"/>
-      <c r="H136" s="6" t="inlineStr">
-        <is>
-          <t>0/34</t>
-        </is>
-      </c>
-      <c r="I136" s="6" t="inlineStr">
+      <c r="I136" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -8000,7 +8020,7 @@
       </c>
       <c r="H149" s="2" t="inlineStr">
         <is>
-          <t>22/33</t>
+          <t>23/33</t>
         </is>
       </c>
       <c r="I149" s="2" t="inlineStr">
@@ -8433,215 +8453,219 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B159" s="5" t="inlineStr">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
         <is>
           <t>A1-C2</t>
         </is>
       </c>
-      <c r="C159" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D159" s="5" t="inlineStr">
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="E159" s="5" t="inlineStr">
+      <c r="E159" s="2" t="inlineStr">
         <is>
           <t>12/07/2026</t>
         </is>
       </c>
-      <c r="F159" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G159" s="5" t="inlineStr"/>
-      <c r="H159" s="5" t="inlineStr">
+      <c r="F159" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G159" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H159" s="2" t="inlineStr">
+        <is>
+          <t>19/33</t>
+        </is>
+      </c>
+      <c r="I159" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B160" s="5" t="inlineStr">
+        <is>
+          <t>A1-C2</t>
+        </is>
+      </c>
+      <c r="C160" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D160" s="5" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="E160" s="5" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="F160" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G160" s="5" t="inlineStr"/>
+      <c r="H160" s="5" t="inlineStr">
         <is>
           <t>0/33</t>
         </is>
       </c>
-      <c r="I159" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B160" s="6" t="inlineStr">
+      <c r="I160" s="5" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B161" s="5" t="inlineStr">
         <is>
           <t>A1-C2</t>
         </is>
       </c>
-      <c r="C160" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D160" s="6" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="E160" s="6" t="inlineStr">
-        <is>
-          <t>13/07/2026</t>
-        </is>
-      </c>
-      <c r="F160" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G160" s="6" t="inlineStr"/>
-      <c r="H160" s="6" t="inlineStr">
+      <c r="C161" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D161" s="5" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E161" s="5" t="inlineStr">
+        <is>
+          <t>18/07/2026</t>
+        </is>
+      </c>
+      <c r="F161" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G161" s="5" t="inlineStr"/>
+      <c r="H161" s="5" t="inlineStr">
         <is>
           <t>0/33</t>
         </is>
       </c>
-      <c r="I160" s="6" t="inlineStr">
+      <c r="I161" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="161">
-      <c r="A161" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B161" s="6" t="inlineStr">
+    <row r="162">
+      <c r="A162" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B162" s="5" t="inlineStr">
         <is>
           <t>A1-C2</t>
         </is>
       </c>
-      <c r="C161" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D161" s="6" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="E161" s="6" t="inlineStr">
-        <is>
-          <t>18/07/2026</t>
-        </is>
-      </c>
-      <c r="F161" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G161" s="6" t="inlineStr"/>
-      <c r="H161" s="6" t="inlineStr">
+      <c r="C162" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D162" s="5" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="E162" s="5" t="inlineStr">
+        <is>
+          <t>19/07/2026</t>
+        </is>
+      </c>
+      <c r="F162" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G162" s="5" t="inlineStr"/>
+      <c r="H162" s="5" t="inlineStr">
         <is>
           <t>0/33</t>
         </is>
       </c>
-      <c r="I161" s="6" t="inlineStr">
+      <c r="I162" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="162">
-      <c r="A162" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B162" s="6" t="inlineStr">
+    <row r="163">
+      <c r="A163" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B163" s="5" t="inlineStr">
         <is>
           <t>A1-C2</t>
         </is>
       </c>
-      <c r="C162" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D162" s="6" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="E162" s="6" t="inlineStr">
-        <is>
-          <t>19/07/2026</t>
-        </is>
-      </c>
-      <c r="F162" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G162" s="6" t="inlineStr"/>
-      <c r="H162" s="6" t="inlineStr">
+      <c r="C163" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D163" s="5" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E163" s="5" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="F163" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G163" s="5" t="inlineStr"/>
+      <c r="H163" s="5" t="inlineStr">
         <is>
           <t>0/33</t>
         </is>
       </c>
-      <c r="I162" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B163" s="6" t="inlineStr">
-        <is>
-          <t>A1-C2</t>
-        </is>
-      </c>
-      <c r="C163" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D163" s="6" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="E163" s="6" t="inlineStr">
-        <is>
-          <t>20/07/2026</t>
-        </is>
-      </c>
-      <c r="F163" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G163" s="6" t="inlineStr"/>
-      <c r="H163" s="6" t="inlineStr">
-        <is>
-          <t>0/33</t>
-        </is>
-      </c>
-      <c r="I163" s="6" t="inlineStr">
+      <c r="I163" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -8883,43 +8907,43 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B169" s="5" t="inlineStr">
+      <c r="A169" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B169" s="9" t="inlineStr">
         <is>
           <t>A1-D1</t>
         </is>
       </c>
-      <c r="C169" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D169" s="5" t="inlineStr">
+      <c r="C169" s="9" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D169" s="9" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E169" s="5" t="inlineStr">
+      <c r="E169" s="9" t="inlineStr">
         <is>
           <t>04/06/2026</t>
         </is>
       </c>
-      <c r="F169" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G169" s="5" t="inlineStr"/>
-      <c r="H169" s="5" t="inlineStr">
+      <c r="F169" s="9" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G169" s="9" t="inlineStr"/>
+      <c r="H169" s="9" t="inlineStr">
         <is>
           <t>0/35</t>
         </is>
       </c>
-      <c r="I169" s="5" t="inlineStr">
+      <c r="I169" s="9" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
@@ -9537,43 +9561,43 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B183" s="5" t="inlineStr">
+      <c r="A183" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B183" s="9" t="inlineStr">
         <is>
           <t>A1-D1</t>
         </is>
       </c>
-      <c r="C183" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D183" s="5" t="inlineStr">
+      <c r="C183" s="9" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D183" s="9" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="E183" s="5" t="inlineStr">
+      <c r="E183" s="9" t="inlineStr">
         <is>
           <t>08/07/2026</t>
         </is>
       </c>
-      <c r="F183" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G183" s="5" t="inlineStr"/>
-      <c r="H183" s="5" t="inlineStr">
+      <c r="F183" s="9" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G183" s="9" t="inlineStr"/>
+      <c r="H183" s="9" t="inlineStr">
         <is>
           <t>0/35</t>
         </is>
       </c>
-      <c r="I183" s="5" t="inlineStr">
+      <c r="I183" s="9" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
@@ -9627,258 +9651,258 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B185" s="6" t="inlineStr">
+      <c r="A185" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B185" s="5" t="inlineStr">
         <is>
           <t>A1-D1</t>
         </is>
       </c>
-      <c r="C185" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D185" s="6" t="inlineStr">
+      <c r="C185" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D185" s="5" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="E185" s="6" t="inlineStr">
+      <c r="E185" s="5" t="inlineStr">
         <is>
           <t>14/07/2026</t>
         </is>
       </c>
-      <c r="F185" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G185" s="6" t="inlineStr"/>
-      <c r="H185" s="6" t="inlineStr">
+      <c r="F185" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G185" s="5" t="inlineStr"/>
+      <c r="H185" s="5" t="inlineStr">
         <is>
           <t>0/35</t>
         </is>
       </c>
-      <c r="I185" s="6" t="inlineStr">
+      <c r="I185" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B186" s="6" t="inlineStr">
+      <c r="A186" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B186" s="5" t="inlineStr">
         <is>
           <t>A1-D1</t>
         </is>
       </c>
-      <c r="C186" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D186" s="6" t="inlineStr">
+      <c r="C186" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D186" s="5" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="E186" s="6" t="inlineStr">
+      <c r="E186" s="5" t="inlineStr">
         <is>
           <t>15/07/2026</t>
         </is>
       </c>
-      <c r="F186" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G186" s="6" t="inlineStr"/>
-      <c r="H186" s="6" t="inlineStr">
+      <c r="F186" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G186" s="5" t="inlineStr"/>
+      <c r="H186" s="5" t="inlineStr">
         <is>
           <t>0/35</t>
         </is>
       </c>
-      <c r="I186" s="6" t="inlineStr">
+      <c r="I186" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B187" s="6" t="inlineStr">
+      <c r="A187" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B187" s="5" t="inlineStr">
         <is>
           <t>A1-D1</t>
         </is>
       </c>
-      <c r="C187" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D187" s="6" t="inlineStr">
+      <c r="C187" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D187" s="5" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="E187" s="6" t="inlineStr">
+      <c r="E187" s="5" t="inlineStr">
         <is>
           <t>16/07/2026</t>
         </is>
       </c>
-      <c r="F187" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G187" s="6" t="inlineStr"/>
-      <c r="H187" s="6" t="inlineStr">
+      <c r="F187" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G187" s="5" t="inlineStr"/>
+      <c r="H187" s="5" t="inlineStr">
         <is>
           <t>0/35</t>
         </is>
       </c>
-      <c r="I187" s="6" t="inlineStr">
+      <c r="I187" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B188" s="6" t="inlineStr">
+      <c r="A188" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B188" s="5" t="inlineStr">
         <is>
           <t>A1-D1</t>
         </is>
       </c>
-      <c r="C188" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D188" s="6" t="inlineStr">
+      <c r="C188" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D188" s="5" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="E188" s="6" t="inlineStr">
+      <c r="E188" s="5" t="inlineStr">
         <is>
           <t>21/07/2026</t>
         </is>
       </c>
-      <c r="F188" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G188" s="6" t="inlineStr"/>
-      <c r="H188" s="6" t="inlineStr">
+      <c r="F188" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G188" s="5" t="inlineStr"/>
+      <c r="H188" s="5" t="inlineStr">
         <is>
           <t>0/35</t>
         </is>
       </c>
-      <c r="I188" s="6" t="inlineStr">
+      <c r="I188" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B189" s="6" t="inlineStr">
+      <c r="A189" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B189" s="5" t="inlineStr">
         <is>
           <t>A1-D1</t>
         </is>
       </c>
-      <c r="C189" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D189" s="6" t="inlineStr">
+      <c r="C189" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D189" s="5" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="E189" s="6" t="inlineStr">
+      <c r="E189" s="5" t="inlineStr">
         <is>
           <t>22/07/2026</t>
         </is>
       </c>
-      <c r="F189" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G189" s="6" t="inlineStr"/>
-      <c r="H189" s="6" t="inlineStr">
+      <c r="F189" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G189" s="5" t="inlineStr"/>
+      <c r="H189" s="5" t="inlineStr">
         <is>
           <t>0/35</t>
         </is>
       </c>
-      <c r="I189" s="6" t="inlineStr">
+      <c r="I189" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B190" s="6" t="inlineStr">
+      <c r="A190" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B190" s="5" t="inlineStr">
         <is>
           <t>A1-D1</t>
         </is>
       </c>
-      <c r="C190" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D190" s="6" t="inlineStr">
+      <c r="C190" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D190" s="5" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="E190" s="6" t="inlineStr">
+      <c r="E190" s="5" t="inlineStr">
         <is>
           <t>23/07/2026</t>
         </is>
       </c>
-      <c r="F190" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G190" s="6" t="inlineStr"/>
-      <c r="H190" s="6" t="inlineStr">
+      <c r="F190" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G190" s="5" t="inlineStr"/>
+      <c r="H190" s="5" t="inlineStr">
         <is>
           <t>0/35</t>
         </is>
       </c>
-      <c r="I190" s="6" t="inlineStr">
+      <c r="I190" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -10120,43 +10144,43 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B196" s="5" t="inlineStr">
+      <c r="A196" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B196" s="9" t="inlineStr">
         <is>
           <t>A1-D2</t>
         </is>
       </c>
-      <c r="C196" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D196" s="5" t="inlineStr">
+      <c r="C196" s="9" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D196" s="9" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E196" s="5" t="inlineStr">
+      <c r="E196" s="9" t="inlineStr">
         <is>
           <t>04/06/2026</t>
         </is>
       </c>
-      <c r="F196" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G196" s="5" t="inlineStr"/>
-      <c r="H196" s="5" t="inlineStr">
+      <c r="F196" s="9" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G196" s="9" t="inlineStr"/>
+      <c r="H196" s="9" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I196" s="5" t="inlineStr">
+      <c r="I196" s="9" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
@@ -10774,43 +10798,43 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B210" s="5" t="inlineStr">
+      <c r="A210" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B210" s="9" t="inlineStr">
         <is>
           <t>A1-D2</t>
         </is>
       </c>
-      <c r="C210" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D210" s="5" t="inlineStr">
+      <c r="C210" s="9" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D210" s="9" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="E210" s="5" t="inlineStr">
+      <c r="E210" s="9" t="inlineStr">
         <is>
           <t>08/07/2026</t>
         </is>
       </c>
-      <c r="F210" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G210" s="5" t="inlineStr"/>
-      <c r="H210" s="5" t="inlineStr">
+      <c r="F210" s="9" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G210" s="9" t="inlineStr"/>
+      <c r="H210" s="9" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I210" s="5" t="inlineStr">
+      <c r="I210" s="9" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
@@ -10864,258 +10888,258 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B212" s="6" t="inlineStr">
+      <c r="A212" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B212" s="5" t="inlineStr">
         <is>
           <t>A1-D2</t>
         </is>
       </c>
-      <c r="C212" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D212" s="6" t="inlineStr">
+      <c r="C212" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D212" s="5" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="E212" s="6" t="inlineStr">
+      <c r="E212" s="5" t="inlineStr">
         <is>
           <t>14/07/2026</t>
         </is>
       </c>
-      <c r="F212" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G212" s="6" t="inlineStr"/>
-      <c r="H212" s="6" t="inlineStr">
+      <c r="F212" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G212" s="5" t="inlineStr"/>
+      <c r="H212" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I212" s="6" t="inlineStr">
+      <c r="I212" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B213" s="6" t="inlineStr">
+      <c r="A213" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B213" s="5" t="inlineStr">
         <is>
           <t>A1-D2</t>
         </is>
       </c>
-      <c r="C213" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D213" s="6" t="inlineStr">
+      <c r="C213" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D213" s="5" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="E213" s="6" t="inlineStr">
+      <c r="E213" s="5" t="inlineStr">
         <is>
           <t>15/07/2026</t>
         </is>
       </c>
-      <c r="F213" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G213" s="6" t="inlineStr"/>
-      <c r="H213" s="6" t="inlineStr">
+      <c r="F213" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G213" s="5" t="inlineStr"/>
+      <c r="H213" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I213" s="6" t="inlineStr">
+      <c r="I213" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B214" s="6" t="inlineStr">
+      <c r="A214" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B214" s="5" t="inlineStr">
         <is>
           <t>A1-D2</t>
         </is>
       </c>
-      <c r="C214" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D214" s="6" t="inlineStr">
+      <c r="C214" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D214" s="5" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="E214" s="6" t="inlineStr">
+      <c r="E214" s="5" t="inlineStr">
         <is>
           <t>16/07/2026</t>
         </is>
       </c>
-      <c r="F214" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G214" s="6" t="inlineStr"/>
-      <c r="H214" s="6" t="inlineStr">
+      <c r="F214" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G214" s="5" t="inlineStr"/>
+      <c r="H214" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I214" s="6" t="inlineStr">
+      <c r="I214" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B215" s="6" t="inlineStr">
+      <c r="A215" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B215" s="5" t="inlineStr">
         <is>
           <t>A1-D2</t>
         </is>
       </c>
-      <c r="C215" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D215" s="6" t="inlineStr">
+      <c r="C215" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D215" s="5" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="E215" s="6" t="inlineStr">
+      <c r="E215" s="5" t="inlineStr">
         <is>
           <t>21/07/2026</t>
         </is>
       </c>
-      <c r="F215" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G215" s="6" t="inlineStr"/>
-      <c r="H215" s="6" t="inlineStr">
+      <c r="F215" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G215" s="5" t="inlineStr"/>
+      <c r="H215" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I215" s="6" t="inlineStr">
+      <c r="I215" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B216" s="6" t="inlineStr">
+      <c r="A216" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B216" s="5" t="inlineStr">
         <is>
           <t>A1-D2</t>
         </is>
       </c>
-      <c r="C216" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D216" s="6" t="inlineStr">
+      <c r="C216" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D216" s="5" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="E216" s="6" t="inlineStr">
+      <c r="E216" s="5" t="inlineStr">
         <is>
           <t>22/07/2026</t>
         </is>
       </c>
-      <c r="F216" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G216" s="6" t="inlineStr"/>
-      <c r="H216" s="6" t="inlineStr">
+      <c r="F216" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G216" s="5" t="inlineStr"/>
+      <c r="H216" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I216" s="6" t="inlineStr">
+      <c r="I216" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B217" s="6" t="inlineStr">
+      <c r="A217" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B217" s="5" t="inlineStr">
         <is>
           <t>A1-D2</t>
         </is>
       </c>
-      <c r="C217" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D217" s="6" t="inlineStr">
+      <c r="C217" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D217" s="5" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="E217" s="6" t="inlineStr">
+      <c r="E217" s="5" t="inlineStr">
         <is>
           <t>23/07/2026</t>
         </is>
       </c>
-      <c r="F217" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G217" s="6" t="inlineStr"/>
-      <c r="H217" s="6" t="inlineStr">
+      <c r="F217" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G217" s="5" t="inlineStr"/>
+      <c r="H217" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I217" s="6" t="inlineStr">
+      <c r="I217" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -11357,43 +11381,43 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B223" s="5" t="inlineStr">
+      <c r="A223" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B223" s="9" t="inlineStr">
         <is>
           <t>A1-E1</t>
         </is>
       </c>
-      <c r="C223" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D223" s="5" t="inlineStr">
+      <c r="C223" s="9" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D223" s="9" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E223" s="5" t="inlineStr">
+      <c r="E223" s="9" t="inlineStr">
         <is>
           <t>04/06/2026</t>
         </is>
       </c>
-      <c r="F223" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G223" s="5" t="inlineStr"/>
-      <c r="H223" s="5" t="inlineStr">
+      <c r="F223" s="9" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G223" s="9" t="inlineStr"/>
+      <c r="H223" s="9" t="inlineStr">
         <is>
           <t>0/38</t>
         </is>
       </c>
-      <c r="I223" s="5" t="inlineStr">
+      <c r="I223" s="9" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
@@ -12058,301 +12082,301 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B238" s="5" t="inlineStr">
+      <c r="A238" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B238" s="9" t="inlineStr">
         <is>
           <t>A1-E1</t>
         </is>
       </c>
-      <c r="C238" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D238" s="5" t="inlineStr">
+      <c r="C238" s="9" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D238" s="9" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="E238" s="5" t="inlineStr">
+      <c r="E238" s="9" t="inlineStr">
         <is>
           <t>09/07/2026</t>
         </is>
       </c>
-      <c r="F238" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G238" s="5" t="inlineStr"/>
-      <c r="H238" s="5" t="inlineStr">
+      <c r="F238" s="9" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G238" s="9" t="inlineStr"/>
+      <c r="H238" s="9" t="inlineStr">
         <is>
           <t>0/38</t>
         </is>
       </c>
-      <c r="I238" s="5" t="inlineStr">
+      <c r="I238" s="9" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B239" s="6" t="inlineStr">
+      <c r="A239" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B239" s="5" t="inlineStr">
         <is>
           <t>A1-E1</t>
         </is>
       </c>
-      <c r="C239" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D239" s="6" t="inlineStr">
+      <c r="C239" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D239" s="5" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="E239" s="6" t="inlineStr">
+      <c r="E239" s="5" t="inlineStr">
         <is>
           <t>14/07/2026</t>
         </is>
       </c>
-      <c r="F239" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G239" s="6" t="inlineStr"/>
-      <c r="H239" s="6" t="inlineStr">
+      <c r="F239" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G239" s="5" t="inlineStr"/>
+      <c r="H239" s="5" t="inlineStr">
         <is>
           <t>0/38</t>
         </is>
       </c>
-      <c r="I239" s="6" t="inlineStr">
+      <c r="I239" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B240" s="6" t="inlineStr">
+      <c r="A240" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B240" s="5" t="inlineStr">
         <is>
           <t>A1-E1</t>
         </is>
       </c>
-      <c r="C240" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D240" s="6" t="inlineStr">
+      <c r="C240" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D240" s="5" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="E240" s="6" t="inlineStr">
+      <c r="E240" s="5" t="inlineStr">
         <is>
           <t>15/07/2026</t>
         </is>
       </c>
-      <c r="F240" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G240" s="6" t="inlineStr"/>
-      <c r="H240" s="6" t="inlineStr">
+      <c r="F240" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G240" s="5" t="inlineStr"/>
+      <c r="H240" s="5" t="inlineStr">
         <is>
           <t>0/38</t>
         </is>
       </c>
-      <c r="I240" s="6" t="inlineStr">
+      <c r="I240" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B241" s="6" t="inlineStr">
+      <c r="A241" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B241" s="5" t="inlineStr">
         <is>
           <t>A1-E1</t>
         </is>
       </c>
-      <c r="C241" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D241" s="6" t="inlineStr">
+      <c r="C241" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D241" s="5" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="E241" s="6" t="inlineStr">
+      <c r="E241" s="5" t="inlineStr">
         <is>
           <t>16/07/2026</t>
         </is>
       </c>
-      <c r="F241" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G241" s="6" t="inlineStr"/>
-      <c r="H241" s="6" t="inlineStr">
+      <c r="F241" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G241" s="5" t="inlineStr"/>
+      <c r="H241" s="5" t="inlineStr">
         <is>
           <t>0/38</t>
         </is>
       </c>
-      <c r="I241" s="6" t="inlineStr">
+      <c r="I241" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B242" s="6" t="inlineStr">
+      <c r="A242" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B242" s="5" t="inlineStr">
         <is>
           <t>A1-E1</t>
         </is>
       </c>
-      <c r="C242" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D242" s="6" t="inlineStr">
+      <c r="C242" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D242" s="5" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="E242" s="6" t="inlineStr">
+      <c r="E242" s="5" t="inlineStr">
         <is>
           <t>21/07/2026</t>
         </is>
       </c>
-      <c r="F242" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G242" s="6" t="inlineStr"/>
-      <c r="H242" s="6" t="inlineStr">
+      <c r="F242" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G242" s="5" t="inlineStr"/>
+      <c r="H242" s="5" t="inlineStr">
         <is>
           <t>0/38</t>
         </is>
       </c>
-      <c r="I242" s="6" t="inlineStr">
+      <c r="I242" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B243" s="6" t="inlineStr">
+      <c r="A243" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B243" s="5" t="inlineStr">
         <is>
           <t>A1-E1</t>
         </is>
       </c>
-      <c r="C243" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D243" s="6" t="inlineStr">
+      <c r="C243" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D243" s="5" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="E243" s="6" t="inlineStr">
+      <c r="E243" s="5" t="inlineStr">
         <is>
           <t>22/07/2026</t>
         </is>
       </c>
-      <c r="F243" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G243" s="6" t="inlineStr"/>
-      <c r="H243" s="6" t="inlineStr">
+      <c r="F243" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G243" s="5" t="inlineStr"/>
+      <c r="H243" s="5" t="inlineStr">
         <is>
           <t>0/38</t>
         </is>
       </c>
-      <c r="I243" s="6" t="inlineStr">
+      <c r="I243" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B244" s="6" t="inlineStr">
+      <c r="A244" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B244" s="5" t="inlineStr">
         <is>
           <t>A1-E1</t>
         </is>
       </c>
-      <c r="C244" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D244" s="6" t="inlineStr">
+      <c r="C244" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D244" s="5" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="E244" s="6" t="inlineStr">
+      <c r="E244" s="5" t="inlineStr">
         <is>
           <t>23/07/2026</t>
         </is>
       </c>
-      <c r="F244" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G244" s="6" t="inlineStr"/>
-      <c r="H244" s="6" t="inlineStr">
+      <c r="F244" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G244" s="5" t="inlineStr"/>
+      <c r="H244" s="5" t="inlineStr">
         <is>
           <t>0/38</t>
         </is>
       </c>
-      <c r="I244" s="6" t="inlineStr">
+      <c r="I244" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -12594,43 +12618,43 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B250" s="5" t="inlineStr">
+      <c r="A250" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B250" s="9" t="inlineStr">
         <is>
           <t>A1-E2</t>
         </is>
       </c>
-      <c r="C250" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D250" s="5" t="inlineStr">
+      <c r="C250" s="9" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D250" s="9" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E250" s="5" t="inlineStr">
+      <c r="E250" s="9" t="inlineStr">
         <is>
           <t>04/06/2026</t>
         </is>
       </c>
-      <c r="F250" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G250" s="5" t="inlineStr"/>
-      <c r="H250" s="5" t="inlineStr">
+      <c r="F250" s="9" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G250" s="9" t="inlineStr"/>
+      <c r="H250" s="9" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I250" s="5" t="inlineStr">
+      <c r="I250" s="9" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
@@ -13295,301 +13319,301 @@
       </c>
     </row>
     <row r="265">
-      <c r="A265" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B265" s="5" t="inlineStr">
+      <c r="A265" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B265" s="9" t="inlineStr">
         <is>
           <t>A1-E2</t>
         </is>
       </c>
-      <c r="C265" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D265" s="5" t="inlineStr">
+      <c r="C265" s="9" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D265" s="9" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="E265" s="5" t="inlineStr">
+      <c r="E265" s="9" t="inlineStr">
         <is>
           <t>09/07/2026</t>
         </is>
       </c>
-      <c r="F265" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G265" s="5" t="inlineStr"/>
-      <c r="H265" s="5" t="inlineStr">
+      <c r="F265" s="9" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G265" s="9" t="inlineStr"/>
+      <c r="H265" s="9" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I265" s="5" t="inlineStr">
+      <c r="I265" s="9" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
       </c>
     </row>
     <row r="266">
-      <c r="A266" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B266" s="6" t="inlineStr">
+      <c r="A266" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B266" s="5" t="inlineStr">
         <is>
           <t>A1-E2</t>
         </is>
       </c>
-      <c r="C266" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D266" s="6" t="inlineStr">
+      <c r="C266" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D266" s="5" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="E266" s="6" t="inlineStr">
+      <c r="E266" s="5" t="inlineStr">
         <is>
           <t>14/07/2026</t>
         </is>
       </c>
-      <c r="F266" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G266" s="6" t="inlineStr"/>
-      <c r="H266" s="6" t="inlineStr">
+      <c r="F266" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G266" s="5" t="inlineStr"/>
+      <c r="H266" s="5" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I266" s="6" t="inlineStr">
+      <c r="I266" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="267">
-      <c r="A267" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B267" s="6" t="inlineStr">
+      <c r="A267" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B267" s="5" t="inlineStr">
         <is>
           <t>A1-E2</t>
         </is>
       </c>
-      <c r="C267" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D267" s="6" t="inlineStr">
+      <c r="C267" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D267" s="5" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="E267" s="6" t="inlineStr">
+      <c r="E267" s="5" t="inlineStr">
         <is>
           <t>15/07/2026</t>
         </is>
       </c>
-      <c r="F267" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G267" s="6" t="inlineStr"/>
-      <c r="H267" s="6" t="inlineStr">
+      <c r="F267" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G267" s="5" t="inlineStr"/>
+      <c r="H267" s="5" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I267" s="6" t="inlineStr">
+      <c r="I267" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="268">
-      <c r="A268" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B268" s="6" t="inlineStr">
+      <c r="A268" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B268" s="5" t="inlineStr">
         <is>
           <t>A1-E2</t>
         </is>
       </c>
-      <c r="C268" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D268" s="6" t="inlineStr">
+      <c r="C268" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D268" s="5" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="E268" s="6" t="inlineStr">
+      <c r="E268" s="5" t="inlineStr">
         <is>
           <t>16/07/2026</t>
         </is>
       </c>
-      <c r="F268" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G268" s="6" t="inlineStr"/>
-      <c r="H268" s="6" t="inlineStr">
+      <c r="F268" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G268" s="5" t="inlineStr"/>
+      <c r="H268" s="5" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I268" s="6" t="inlineStr">
+      <c r="I268" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="269">
-      <c r="A269" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B269" s="6" t="inlineStr">
+      <c r="A269" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B269" s="5" t="inlineStr">
         <is>
           <t>A1-E2</t>
         </is>
       </c>
-      <c r="C269" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D269" s="6" t="inlineStr">
+      <c r="C269" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D269" s="5" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="E269" s="6" t="inlineStr">
+      <c r="E269" s="5" t="inlineStr">
         <is>
           <t>21/07/2026</t>
         </is>
       </c>
-      <c r="F269" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G269" s="6" t="inlineStr"/>
-      <c r="H269" s="6" t="inlineStr">
+      <c r="F269" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G269" s="5" t="inlineStr"/>
+      <c r="H269" s="5" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I269" s="6" t="inlineStr">
+      <c r="I269" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="270">
-      <c r="A270" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B270" s="6" t="inlineStr">
+      <c r="A270" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B270" s="5" t="inlineStr">
         <is>
           <t>A1-E2</t>
         </is>
       </c>
-      <c r="C270" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D270" s="6" t="inlineStr">
+      <c r="C270" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D270" s="5" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="E270" s="6" t="inlineStr">
+      <c r="E270" s="5" t="inlineStr">
         <is>
           <t>22/07/2026</t>
         </is>
       </c>
-      <c r="F270" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G270" s="6" t="inlineStr"/>
-      <c r="H270" s="6" t="inlineStr">
+      <c r="F270" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G270" s="5" t="inlineStr"/>
+      <c r="H270" s="5" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I270" s="6" t="inlineStr">
+      <c r="I270" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="271">
-      <c r="A271" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B271" s="6" t="inlineStr">
+      <c r="A271" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B271" s="5" t="inlineStr">
         <is>
           <t>A1-E2</t>
         </is>
       </c>
-      <c r="C271" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D271" s="6" t="inlineStr">
+      <c r="C271" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D271" s="5" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="E271" s="6" t="inlineStr">
+      <c r="E271" s="5" t="inlineStr">
         <is>
           <t>23/07/2026</t>
         </is>
       </c>
-      <c r="F271" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G271" s="6" t="inlineStr"/>
-      <c r="H271" s="6" t="inlineStr">
+      <c r="F271" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G271" s="5" t="inlineStr"/>
+      <c r="H271" s="5" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I271" s="6" t="inlineStr">
+      <c r="I271" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -13831,43 +13855,43 @@
       </c>
     </row>
     <row r="277">
-      <c r="A277" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B277" s="5" t="inlineStr">
+      <c r="A277" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B277" s="9" t="inlineStr">
         <is>
           <t>A1-F1</t>
         </is>
       </c>
-      <c r="C277" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D277" s="5" t="inlineStr">
+      <c r="C277" s="9" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D277" s="9" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E277" s="5" t="inlineStr">
+      <c r="E277" s="9" t="inlineStr">
         <is>
           <t>04/06/2026</t>
         </is>
       </c>
-      <c r="F277" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G277" s="5" t="inlineStr"/>
-      <c r="H277" s="5" t="inlineStr">
+      <c r="F277" s="9" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G277" s="9" t="inlineStr"/>
+      <c r="H277" s="9" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I277" s="5" t="inlineStr">
+      <c r="I277" s="9" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
@@ -14579,258 +14603,258 @@
       </c>
     </row>
     <row r="293">
-      <c r="A293" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B293" s="6" t="inlineStr">
+      <c r="A293" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B293" s="5" t="inlineStr">
         <is>
           <t>A1-F1</t>
         </is>
       </c>
-      <c r="C293" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D293" s="6" t="inlineStr">
+      <c r="C293" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D293" s="5" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="E293" s="6" t="inlineStr">
+      <c r="E293" s="5" t="inlineStr">
         <is>
           <t>14/07/2026</t>
         </is>
       </c>
-      <c r="F293" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G293" s="6" t="inlineStr"/>
-      <c r="H293" s="6" t="inlineStr">
+      <c r="F293" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G293" s="5" t="inlineStr"/>
+      <c r="H293" s="5" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I293" s="6" t="inlineStr">
+      <c r="I293" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="294">
-      <c r="A294" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B294" s="6" t="inlineStr">
+      <c r="A294" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B294" s="5" t="inlineStr">
         <is>
           <t>A1-F1</t>
         </is>
       </c>
-      <c r="C294" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D294" s="6" t="inlineStr">
+      <c r="C294" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D294" s="5" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="E294" s="6" t="inlineStr">
+      <c r="E294" s="5" t="inlineStr">
         <is>
           <t>15/07/2026</t>
         </is>
       </c>
-      <c r="F294" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G294" s="6" t="inlineStr"/>
-      <c r="H294" s="6" t="inlineStr">
+      <c r="F294" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G294" s="5" t="inlineStr"/>
+      <c r="H294" s="5" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I294" s="6" t="inlineStr">
+      <c r="I294" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="295">
-      <c r="A295" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B295" s="6" t="inlineStr">
+      <c r="A295" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B295" s="5" t="inlineStr">
         <is>
           <t>A1-F1</t>
         </is>
       </c>
-      <c r="C295" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D295" s="6" t="inlineStr">
+      <c r="C295" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D295" s="5" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="E295" s="6" t="inlineStr">
+      <c r="E295" s="5" t="inlineStr">
         <is>
           <t>16/07/2026</t>
         </is>
       </c>
-      <c r="F295" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G295" s="6" t="inlineStr"/>
-      <c r="H295" s="6" t="inlineStr">
+      <c r="F295" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G295" s="5" t="inlineStr"/>
+      <c r="H295" s="5" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I295" s="6" t="inlineStr">
+      <c r="I295" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="296">
-      <c r="A296" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B296" s="6" t="inlineStr">
+      <c r="A296" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B296" s="5" t="inlineStr">
         <is>
           <t>A1-F1</t>
         </is>
       </c>
-      <c r="C296" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D296" s="6" t="inlineStr">
+      <c r="C296" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D296" s="5" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="E296" s="6" t="inlineStr">
+      <c r="E296" s="5" t="inlineStr">
         <is>
           <t>21/07/2026</t>
         </is>
       </c>
-      <c r="F296" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G296" s="6" t="inlineStr"/>
-      <c r="H296" s="6" t="inlineStr">
+      <c r="F296" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G296" s="5" t="inlineStr"/>
+      <c r="H296" s="5" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I296" s="6" t="inlineStr">
+      <c r="I296" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="297">
-      <c r="A297" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B297" s="6" t="inlineStr">
+      <c r="A297" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B297" s="5" t="inlineStr">
         <is>
           <t>A1-F1</t>
         </is>
       </c>
-      <c r="C297" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D297" s="6" t="inlineStr">
+      <c r="C297" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D297" s="5" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="E297" s="6" t="inlineStr">
+      <c r="E297" s="5" t="inlineStr">
         <is>
           <t>22/07/2026</t>
         </is>
       </c>
-      <c r="F297" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G297" s="6" t="inlineStr"/>
-      <c r="H297" s="6" t="inlineStr">
+      <c r="F297" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G297" s="5" t="inlineStr"/>
+      <c r="H297" s="5" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I297" s="6" t="inlineStr">
+      <c r="I297" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="298">
-      <c r="A298" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B298" s="6" t="inlineStr">
+      <c r="A298" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B298" s="5" t="inlineStr">
         <is>
           <t>A1-F1</t>
         </is>
       </c>
-      <c r="C298" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D298" s="6" t="inlineStr">
+      <c r="C298" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D298" s="5" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="E298" s="6" t="inlineStr">
+      <c r="E298" s="5" t="inlineStr">
         <is>
           <t>23/07/2026</t>
         </is>
       </c>
-      <c r="F298" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G298" s="6" t="inlineStr"/>
-      <c r="H298" s="6" t="inlineStr">
+      <c r="F298" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G298" s="5" t="inlineStr"/>
+      <c r="H298" s="5" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I298" s="6" t="inlineStr">
+      <c r="I298" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -15072,43 +15096,43 @@
       </c>
     </row>
     <row r="304">
-      <c r="A304" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B304" s="5" t="inlineStr">
+      <c r="A304" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B304" s="9" t="inlineStr">
         <is>
           <t>A1-F2</t>
         </is>
       </c>
-      <c r="C304" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D304" s="5" t="inlineStr">
+      <c r="C304" s="9" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D304" s="9" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E304" s="5" t="inlineStr">
+      <c r="E304" s="9" t="inlineStr">
         <is>
           <t>04/06/2026</t>
         </is>
       </c>
-      <c r="F304" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G304" s="5" t="inlineStr"/>
-      <c r="H304" s="5" t="inlineStr">
+      <c r="F304" s="9" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G304" s="9" t="inlineStr"/>
+      <c r="H304" s="9" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I304" s="5" t="inlineStr">
+      <c r="I304" s="9" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
@@ -15679,43 +15703,43 @@
       </c>
     </row>
     <row r="317">
-      <c r="A317" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B317" s="5" t="inlineStr">
+      <c r="A317" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B317" s="9" t="inlineStr">
         <is>
           <t>A1-F2</t>
         </is>
       </c>
-      <c r="C317" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D317" s="5" t="inlineStr">
+      <c r="C317" s="9" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D317" s="9" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="E317" s="5" t="inlineStr">
+      <c r="E317" s="9" t="inlineStr">
         <is>
           <t>07/07/2026</t>
         </is>
       </c>
-      <c r="F317" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G317" s="5" t="inlineStr"/>
-      <c r="H317" s="5" t="inlineStr">
+      <c r="F317" s="9" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G317" s="9" t="inlineStr"/>
+      <c r="H317" s="9" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I317" s="5" t="inlineStr">
+      <c r="I317" s="9" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
@@ -15816,258 +15840,258 @@
       </c>
     </row>
     <row r="320">
-      <c r="A320" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B320" s="6" t="inlineStr">
+      <c r="A320" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B320" s="5" t="inlineStr">
         <is>
           <t>A1-F2</t>
         </is>
       </c>
-      <c r="C320" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D320" s="6" t="inlineStr">
+      <c r="C320" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D320" s="5" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="E320" s="6" t="inlineStr">
+      <c r="E320" s="5" t="inlineStr">
         <is>
           <t>14/07/2026</t>
         </is>
       </c>
-      <c r="F320" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G320" s="6" t="inlineStr"/>
-      <c r="H320" s="6" t="inlineStr">
+      <c r="F320" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G320" s="5" t="inlineStr"/>
+      <c r="H320" s="5" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I320" s="6" t="inlineStr">
+      <c r="I320" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="321">
-      <c r="A321" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B321" s="6" t="inlineStr">
+      <c r="A321" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B321" s="5" t="inlineStr">
         <is>
           <t>A1-F2</t>
         </is>
       </c>
-      <c r="C321" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D321" s="6" t="inlineStr">
+      <c r="C321" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D321" s="5" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="E321" s="6" t="inlineStr">
+      <c r="E321" s="5" t="inlineStr">
         <is>
           <t>15/07/2026</t>
         </is>
       </c>
-      <c r="F321" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G321" s="6" t="inlineStr"/>
-      <c r="H321" s="6" t="inlineStr">
+      <c r="F321" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G321" s="5" t="inlineStr"/>
+      <c r="H321" s="5" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I321" s="6" t="inlineStr">
+      <c r="I321" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="322">
-      <c r="A322" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B322" s="6" t="inlineStr">
+      <c r="A322" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B322" s="5" t="inlineStr">
         <is>
           <t>A1-F2</t>
         </is>
       </c>
-      <c r="C322" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D322" s="6" t="inlineStr">
+      <c r="C322" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D322" s="5" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="E322" s="6" t="inlineStr">
+      <c r="E322" s="5" t="inlineStr">
         <is>
           <t>16/07/2026</t>
         </is>
       </c>
-      <c r="F322" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G322" s="6" t="inlineStr"/>
-      <c r="H322" s="6" t="inlineStr">
+      <c r="F322" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G322" s="5" t="inlineStr"/>
+      <c r="H322" s="5" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I322" s="6" t="inlineStr">
+      <c r="I322" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="323">
-      <c r="A323" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B323" s="6" t="inlineStr">
+      <c r="A323" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B323" s="5" t="inlineStr">
         <is>
           <t>A1-F2</t>
         </is>
       </c>
-      <c r="C323" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D323" s="6" t="inlineStr">
+      <c r="C323" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D323" s="5" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="E323" s="6" t="inlineStr">
+      <c r="E323" s="5" t="inlineStr">
         <is>
           <t>21/07/2026</t>
         </is>
       </c>
-      <c r="F323" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G323" s="6" t="inlineStr"/>
-      <c r="H323" s="6" t="inlineStr">
+      <c r="F323" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G323" s="5" t="inlineStr"/>
+      <c r="H323" s="5" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I323" s="6" t="inlineStr">
+      <c r="I323" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="324">
-      <c r="A324" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B324" s="6" t="inlineStr">
+      <c r="A324" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B324" s="5" t="inlineStr">
         <is>
           <t>A1-F2</t>
         </is>
       </c>
-      <c r="C324" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D324" s="6" t="inlineStr">
+      <c r="C324" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D324" s="5" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="E324" s="6" t="inlineStr">
+      <c r="E324" s="5" t="inlineStr">
         <is>
           <t>22/07/2026</t>
         </is>
       </c>
-      <c r="F324" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G324" s="6" t="inlineStr"/>
-      <c r="H324" s="6" t="inlineStr">
+      <c r="F324" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G324" s="5" t="inlineStr"/>
+      <c r="H324" s="5" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I324" s="6" t="inlineStr">
+      <c r="I324" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="325">
-      <c r="A325" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B325" s="6" t="inlineStr">
+      <c r="A325" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B325" s="5" t="inlineStr">
         <is>
           <t>A1-F2</t>
         </is>
       </c>
-      <c r="C325" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D325" s="6" t="inlineStr">
+      <c r="C325" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D325" s="5" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="E325" s="6" t="inlineStr">
+      <c r="E325" s="5" t="inlineStr">
         <is>
           <t>23/07/2026</t>
         </is>
       </c>
-      <c r="F325" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G325" s="6" t="inlineStr"/>
-      <c r="H325" s="6" t="inlineStr">
+      <c r="F325" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G325" s="5" t="inlineStr"/>
+      <c r="H325" s="5" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I325" s="6" t="inlineStr">
+      <c r="I325" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A1_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A1_session_analysis.xlsx
@@ -58,14 +58,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFFE0"/>
-        <bgColor rgb="00FFFFE0"/>
+        <fgColor rgb="00FFB6C1"/>
+        <bgColor rgb="00FFB6C1"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFB6C1"/>
-        <bgColor rgb="00FFB6C1"/>
+        <fgColor rgb="00FFFFE0"/>
+        <bgColor rgb="00FFFFE0"/>
       </patternFill>
     </fill>
   </fills>
@@ -96,16 +96,16 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8">
@@ -924,7 +924,7 @@
         </is>
       </c>
       <c r="L8" s="4" t="n">
-        <v>60</v>
+        <v>54</v>
       </c>
     </row>
     <row r="9">
@@ -1345,10 +1345,10 @@
         <v>23</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R15" s="4" t="inlineStr">
         <is>
@@ -1427,10 +1427,10 @@
         <v>23</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R16" s="4" t="inlineStr">
         <is>
@@ -1509,10 +1509,10 @@
         <v>23</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R17" s="4" t="inlineStr">
         <is>
@@ -1591,10 +1591,10 @@
         <v>23</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R18" s="4" t="inlineStr">
         <is>
@@ -1673,10 +1673,10 @@
         <v>23</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R19" s="4" t="inlineStr">
         <is>
@@ -1755,10 +1755,10 @@
         <v>23</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R20" s="4" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
       </c>
       <c r="I25" s="5" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Not Recorded</t>
         </is>
       </c>
       <c r="K25" s="4" t="inlineStr">
@@ -2178,43 +2178,43 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B26" s="5" t="inlineStr">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
         <is>
           <t>A1-A1</t>
         </is>
       </c>
-      <c r="C26" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D26" s="5" t="inlineStr">
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="E26" s="5" t="inlineStr">
+      <c r="E26" s="6" t="inlineStr">
         <is>
           <t>18/07/2026</t>
         </is>
       </c>
-      <c r="F26" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G26" s="5" t="inlineStr"/>
-      <c r="H26" s="5" t="inlineStr">
+      <c r="F26" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G26" s="6" t="inlineStr"/>
+      <c r="H26" s="6" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I26" s="5" t="inlineStr">
+      <c r="I26" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -2256,86 +2256,86 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B27" s="5" t="inlineStr">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
         <is>
           <t>A1-A1</t>
         </is>
       </c>
-      <c r="C27" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="inlineStr">
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="E27" s="5" t="inlineStr">
+      <c r="E27" s="6" t="inlineStr">
         <is>
           <t>19/07/2026</t>
         </is>
       </c>
-      <c r="F27" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G27" s="5" t="inlineStr"/>
-      <c r="H27" s="5" t="inlineStr">
+      <c r="F27" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G27" s="6" t="inlineStr"/>
+      <c r="H27" s="6" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I27" s="5" t="inlineStr">
+      <c r="I27" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B28" s="5" t="inlineStr">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
         <is>
           <t>A1-A1</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D28" s="5" t="inlineStr">
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="E28" s="5" t="inlineStr">
+      <c r="E28" s="6" t="inlineStr">
         <is>
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="F28" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G28" s="5" t="inlineStr"/>
-      <c r="H28" s="5" t="inlineStr">
+      <c r="F28" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G28" s="6" t="inlineStr"/>
+      <c r="H28" s="6" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I28" s="5" t="inlineStr">
+      <c r="I28" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -2506,7 +2506,7 @@
           <t>Recorded</t>
         </is>
       </c>
-      <c r="L31" s="6" t="inlineStr">
+      <c r="L31" s="7" t="inlineStr">
         <is>
           <t>Green</t>
         </is>
@@ -2568,7 +2568,7 @@
           <t>Not Recorded</t>
         </is>
       </c>
-      <c r="L32" s="7" t="inlineStr">
+      <c r="L32" s="8" t="inlineStr">
         <is>
           <t>Red</t>
         </is>
@@ -2630,7 +2630,7 @@
           <t>Pending</t>
         </is>
       </c>
-      <c r="L33" s="8" t="inlineStr">
+      <c r="L33" s="9" t="inlineStr">
         <is>
           <t>Yellow</t>
         </is>
@@ -3526,134 +3526,134 @@
       </c>
       <c r="I52" s="5" t="inlineStr">
         <is>
+          <t>Not Recorded</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B53" s="6" t="inlineStr">
+        <is>
+          <t>A1-A2</t>
+        </is>
+      </c>
+      <c r="C53" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D53" s="6" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E53" s="6" t="inlineStr">
+        <is>
+          <t>18/07/2026</t>
+        </is>
+      </c>
+      <c r="F53" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G53" s="6" t="inlineStr"/>
+      <c r="H53" s="6" t="inlineStr">
+        <is>
+          <t>0/33</t>
+        </is>
+      </c>
+      <c r="I53" s="6" t="inlineStr">
+        <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B53" s="5" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B54" s="6" t="inlineStr">
         <is>
           <t>A1-A2</t>
         </is>
       </c>
-      <c r="C53" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D53" s="5" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="E53" s="5" t="inlineStr">
-        <is>
-          <t>18/07/2026</t>
-        </is>
-      </c>
-      <c r="F53" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G53" s="5" t="inlineStr"/>
-      <c r="H53" s="5" t="inlineStr">
+      <c r="C54" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D54" s="6" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="E54" s="6" t="inlineStr">
+        <is>
+          <t>19/07/2026</t>
+        </is>
+      </c>
+      <c r="F54" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G54" s="6" t="inlineStr"/>
+      <c r="H54" s="6" t="inlineStr">
         <is>
           <t>0/33</t>
         </is>
       </c>
-      <c r="I53" s="5" t="inlineStr">
+      <c r="I54" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B54" s="5" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B55" s="6" t="inlineStr">
         <is>
           <t>A1-A2</t>
         </is>
       </c>
-      <c r="C54" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D54" s="5" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="E54" s="5" t="inlineStr">
-        <is>
-          <t>19/07/2026</t>
-        </is>
-      </c>
-      <c r="F54" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G54" s="5" t="inlineStr"/>
-      <c r="H54" s="5" t="inlineStr">
+      <c r="C55" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D55" s="6" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E55" s="6" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="F55" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G55" s="6" t="inlineStr"/>
+      <c r="H55" s="6" t="inlineStr">
         <is>
           <t>0/33</t>
         </is>
       </c>
-      <c r="I54" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B55" s="5" t="inlineStr">
-        <is>
-          <t>A1-A2</t>
-        </is>
-      </c>
-      <c r="C55" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D55" s="5" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="E55" s="5" t="inlineStr">
-        <is>
-          <t>20/07/2026</t>
-        </is>
-      </c>
-      <c r="F55" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G55" s="5" t="inlineStr"/>
-      <c r="H55" s="5" t="inlineStr">
-        <is>
-          <t>0/33</t>
-        </is>
-      </c>
-      <c r="I55" s="5" t="inlineStr">
+      <c r="I55" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -4779,134 +4779,134 @@
       </c>
       <c r="I79" s="5" t="inlineStr">
         <is>
+          <t>Not Recorded</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B80" s="6" t="inlineStr">
+        <is>
+          <t>A1-B1</t>
+        </is>
+      </c>
+      <c r="C80" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D80" s="6" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E80" s="6" t="inlineStr">
+        <is>
+          <t>18/07/2026</t>
+        </is>
+      </c>
+      <c r="F80" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G80" s="6" t="inlineStr"/>
+      <c r="H80" s="6" t="inlineStr">
+        <is>
+          <t>0/34</t>
+        </is>
+      </c>
+      <c r="I80" s="6" t="inlineStr">
+        <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B80" s="5" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B81" s="6" t="inlineStr">
         <is>
           <t>A1-B1</t>
         </is>
       </c>
-      <c r="C80" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D80" s="5" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="E80" s="5" t="inlineStr">
-        <is>
-          <t>18/07/2026</t>
-        </is>
-      </c>
-      <c r="F80" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G80" s="5" t="inlineStr"/>
-      <c r="H80" s="5" t="inlineStr">
+      <c r="C81" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D81" s="6" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="E81" s="6" t="inlineStr">
+        <is>
+          <t>19/07/2026</t>
+        </is>
+      </c>
+      <c r="F81" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G81" s="6" t="inlineStr"/>
+      <c r="H81" s="6" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I80" s="5" t="inlineStr">
+      <c r="I81" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B81" s="5" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B82" s="6" t="inlineStr">
         <is>
           <t>A1-B1</t>
         </is>
       </c>
-      <c r="C81" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D81" s="5" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="E81" s="5" t="inlineStr">
-        <is>
-          <t>19/07/2026</t>
-        </is>
-      </c>
-      <c r="F81" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G81" s="5" t="inlineStr"/>
-      <c r="H81" s="5" t="inlineStr">
+      <c r="C82" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D82" s="6" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E82" s="6" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="F82" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G82" s="6" t="inlineStr"/>
+      <c r="H82" s="6" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I81" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B82" s="5" t="inlineStr">
-        <is>
-          <t>A1-B1</t>
-        </is>
-      </c>
-      <c r="C82" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D82" s="5" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="E82" s="5" t="inlineStr">
-        <is>
-          <t>20/07/2026</t>
-        </is>
-      </c>
-      <c r="F82" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G82" s="5" t="inlineStr"/>
-      <c r="H82" s="5" t="inlineStr">
-        <is>
-          <t>0/34</t>
-        </is>
-      </c>
-      <c r="I82" s="5" t="inlineStr">
+      <c r="I82" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -6032,134 +6032,134 @@
       </c>
       <c r="I106" s="5" t="inlineStr">
         <is>
+          <t>Not Recorded</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B107" s="6" t="inlineStr">
+        <is>
+          <t>A1-B2</t>
+        </is>
+      </c>
+      <c r="C107" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D107" s="6" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E107" s="6" t="inlineStr">
+        <is>
+          <t>18/07/2026</t>
+        </is>
+      </c>
+      <c r="F107" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G107" s="6" t="inlineStr"/>
+      <c r="H107" s="6" t="inlineStr">
+        <is>
+          <t>0/34</t>
+        </is>
+      </c>
+      <c r="I107" s="6" t="inlineStr">
+        <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B107" s="5" t="inlineStr">
+    <row r="108">
+      <c r="A108" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B108" s="6" t="inlineStr">
         <is>
           <t>A1-B2</t>
         </is>
       </c>
-      <c r="C107" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D107" s="5" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="E107" s="5" t="inlineStr">
-        <is>
-          <t>18/07/2026</t>
-        </is>
-      </c>
-      <c r="F107" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G107" s="5" t="inlineStr"/>
-      <c r="H107" s="5" t="inlineStr">
+      <c r="C108" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D108" s="6" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="E108" s="6" t="inlineStr">
+        <is>
+          <t>19/07/2026</t>
+        </is>
+      </c>
+      <c r="F108" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G108" s="6" t="inlineStr"/>
+      <c r="H108" s="6" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I107" s="5" t="inlineStr">
+      <c r="I108" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B108" s="5" t="inlineStr">
+    <row r="109">
+      <c r="A109" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B109" s="6" t="inlineStr">
         <is>
           <t>A1-B2</t>
         </is>
       </c>
-      <c r="C108" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D108" s="5" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="E108" s="5" t="inlineStr">
-        <is>
-          <t>19/07/2026</t>
-        </is>
-      </c>
-      <c r="F108" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G108" s="5" t="inlineStr"/>
-      <c r="H108" s="5" t="inlineStr">
+      <c r="C109" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D109" s="6" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E109" s="6" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="F109" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G109" s="6" t="inlineStr"/>
+      <c r="H109" s="6" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I108" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B109" s="5" t="inlineStr">
-        <is>
-          <t>A1-B2</t>
-        </is>
-      </c>
-      <c r="C109" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D109" s="5" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="E109" s="5" t="inlineStr">
-        <is>
-          <t>20/07/2026</t>
-        </is>
-      </c>
-      <c r="F109" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G109" s="5" t="inlineStr"/>
-      <c r="H109" s="5" t="inlineStr">
-        <is>
-          <t>0/34</t>
-        </is>
-      </c>
-      <c r="I109" s="5" t="inlineStr">
+      <c r="I109" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -7285,134 +7285,134 @@
       </c>
       <c r="I133" s="5" t="inlineStr">
         <is>
+          <t>Not Recorded</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B134" s="6" t="inlineStr">
+        <is>
+          <t>A1-C1</t>
+        </is>
+      </c>
+      <c r="C134" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D134" s="6" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E134" s="6" t="inlineStr">
+        <is>
+          <t>18/07/2026</t>
+        </is>
+      </c>
+      <c r="F134" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G134" s="6" t="inlineStr"/>
+      <c r="H134" s="6" t="inlineStr">
+        <is>
+          <t>0/34</t>
+        </is>
+      </c>
+      <c r="I134" s="6" t="inlineStr">
+        <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="134">
-      <c r="A134" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B134" s="5" t="inlineStr">
+    <row r="135">
+      <c r="A135" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B135" s="6" t="inlineStr">
         <is>
           <t>A1-C1</t>
         </is>
       </c>
-      <c r="C134" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D134" s="5" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="E134" s="5" t="inlineStr">
-        <is>
-          <t>18/07/2026</t>
-        </is>
-      </c>
-      <c r="F134" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G134" s="5" t="inlineStr"/>
-      <c r="H134" s="5" t="inlineStr">
+      <c r="C135" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D135" s="6" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="E135" s="6" t="inlineStr">
+        <is>
+          <t>19/07/2026</t>
+        </is>
+      </c>
+      <c r="F135" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G135" s="6" t="inlineStr"/>
+      <c r="H135" s="6" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I134" s="5" t="inlineStr">
+      <c r="I135" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B135" s="5" t="inlineStr">
+    <row r="136">
+      <c r="A136" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B136" s="6" t="inlineStr">
         <is>
           <t>A1-C1</t>
         </is>
       </c>
-      <c r="C135" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D135" s="5" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="E135" s="5" t="inlineStr">
-        <is>
-          <t>19/07/2026</t>
-        </is>
-      </c>
-      <c r="F135" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G135" s="5" t="inlineStr"/>
-      <c r="H135" s="5" t="inlineStr">
+      <c r="C136" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D136" s="6" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E136" s="6" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="F136" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G136" s="6" t="inlineStr"/>
+      <c r="H136" s="6" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I135" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B136" s="5" t="inlineStr">
-        <is>
-          <t>A1-C1</t>
-        </is>
-      </c>
-      <c r="C136" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D136" s="5" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="E136" s="5" t="inlineStr">
-        <is>
-          <t>20/07/2026</t>
-        </is>
-      </c>
-      <c r="F136" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G136" s="5" t="inlineStr"/>
-      <c r="H136" s="5" t="inlineStr">
-        <is>
-          <t>0/34</t>
-        </is>
-      </c>
-      <c r="I136" s="5" t="inlineStr">
+      <c r="I136" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -8538,134 +8538,134 @@
       </c>
       <c r="I160" s="5" t="inlineStr">
         <is>
+          <t>Not Recorded</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B161" s="6" t="inlineStr">
+        <is>
+          <t>A1-C2</t>
+        </is>
+      </c>
+      <c r="C161" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D161" s="6" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E161" s="6" t="inlineStr">
+        <is>
+          <t>18/07/2026</t>
+        </is>
+      </c>
+      <c r="F161" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G161" s="6" t="inlineStr"/>
+      <c r="H161" s="6" t="inlineStr">
+        <is>
+          <t>0/33</t>
+        </is>
+      </c>
+      <c r="I161" s="6" t="inlineStr">
+        <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="161">
-      <c r="A161" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B161" s="5" t="inlineStr">
+    <row r="162">
+      <c r="A162" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B162" s="6" t="inlineStr">
         <is>
           <t>A1-C2</t>
         </is>
       </c>
-      <c r="C161" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D161" s="5" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="E161" s="5" t="inlineStr">
-        <is>
-          <t>18/07/2026</t>
-        </is>
-      </c>
-      <c r="F161" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G161" s="5" t="inlineStr"/>
-      <c r="H161" s="5" t="inlineStr">
+      <c r="C162" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D162" s="6" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="E162" s="6" t="inlineStr">
+        <is>
+          <t>19/07/2026</t>
+        </is>
+      </c>
+      <c r="F162" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G162" s="6" t="inlineStr"/>
+      <c r="H162" s="6" t="inlineStr">
         <is>
           <t>0/33</t>
         </is>
       </c>
-      <c r="I161" s="5" t="inlineStr">
+      <c r="I162" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="162">
-      <c r="A162" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B162" s="5" t="inlineStr">
+    <row r="163">
+      <c r="A163" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B163" s="6" t="inlineStr">
         <is>
           <t>A1-C2</t>
         </is>
       </c>
-      <c r="C162" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D162" s="5" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="E162" s="5" t="inlineStr">
-        <is>
-          <t>19/07/2026</t>
-        </is>
-      </c>
-      <c r="F162" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G162" s="5" t="inlineStr"/>
-      <c r="H162" s="5" t="inlineStr">
+      <c r="C163" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D163" s="6" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E163" s="6" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="F163" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G163" s="6" t="inlineStr"/>
+      <c r="H163" s="6" t="inlineStr">
         <is>
           <t>0/33</t>
         </is>
       </c>
-      <c r="I162" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B163" s="5" t="inlineStr">
-        <is>
-          <t>A1-C2</t>
-        </is>
-      </c>
-      <c r="C163" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D163" s="5" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="E163" s="5" t="inlineStr">
-        <is>
-          <t>20/07/2026</t>
-        </is>
-      </c>
-      <c r="F163" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G163" s="5" t="inlineStr"/>
-      <c r="H163" s="5" t="inlineStr">
-        <is>
-          <t>0/33</t>
-        </is>
-      </c>
-      <c r="I163" s="5" t="inlineStr">
+      <c r="I163" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -8907,43 +8907,43 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B169" s="9" t="inlineStr">
+      <c r="A169" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B169" s="5" t="inlineStr">
         <is>
           <t>A1-D1</t>
         </is>
       </c>
-      <c r="C169" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D169" s="9" t="inlineStr">
+      <c r="C169" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D169" s="5" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E169" s="9" t="inlineStr">
+      <c r="E169" s="5" t="inlineStr">
         <is>
           <t>04/06/2026</t>
         </is>
       </c>
-      <c r="F169" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G169" s="9" t="inlineStr"/>
-      <c r="H169" s="9" t="inlineStr">
+      <c r="F169" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G169" s="5" t="inlineStr"/>
+      <c r="H169" s="5" t="inlineStr">
         <is>
           <t>0/35</t>
         </is>
       </c>
-      <c r="I169" s="9" t="inlineStr">
+      <c r="I169" s="5" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
@@ -9561,43 +9561,43 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B183" s="9" t="inlineStr">
+      <c r="A183" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B183" s="5" t="inlineStr">
         <is>
           <t>A1-D1</t>
         </is>
       </c>
-      <c r="C183" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D183" s="9" t="inlineStr">
+      <c r="C183" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D183" s="5" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="E183" s="9" t="inlineStr">
+      <c r="E183" s="5" t="inlineStr">
         <is>
           <t>08/07/2026</t>
         </is>
       </c>
-      <c r="F183" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G183" s="9" t="inlineStr"/>
-      <c r="H183" s="9" t="inlineStr">
+      <c r="F183" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G183" s="5" t="inlineStr"/>
+      <c r="H183" s="5" t="inlineStr">
         <is>
           <t>0/35</t>
         </is>
       </c>
-      <c r="I183" s="9" t="inlineStr">
+      <c r="I183" s="5" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
@@ -9651,258 +9651,258 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B185" s="5" t="inlineStr">
+      <c r="A185" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B185" s="6" t="inlineStr">
         <is>
           <t>A1-D1</t>
         </is>
       </c>
-      <c r="C185" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D185" s="5" t="inlineStr">
+      <c r="C185" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D185" s="6" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="E185" s="5" t="inlineStr">
+      <c r="E185" s="6" t="inlineStr">
         <is>
           <t>14/07/2026</t>
         </is>
       </c>
-      <c r="F185" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G185" s="5" t="inlineStr"/>
-      <c r="H185" s="5" t="inlineStr">
+      <c r="F185" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G185" s="6" t="inlineStr"/>
+      <c r="H185" s="6" t="inlineStr">
         <is>
           <t>0/35</t>
         </is>
       </c>
-      <c r="I185" s="5" t="inlineStr">
+      <c r="I185" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B186" s="5" t="inlineStr">
+      <c r="A186" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B186" s="6" t="inlineStr">
         <is>
           <t>A1-D1</t>
         </is>
       </c>
-      <c r="C186" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D186" s="5" t="inlineStr">
+      <c r="C186" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D186" s="6" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="E186" s="5" t="inlineStr">
+      <c r="E186" s="6" t="inlineStr">
         <is>
           <t>15/07/2026</t>
         </is>
       </c>
-      <c r="F186" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G186" s="5" t="inlineStr"/>
-      <c r="H186" s="5" t="inlineStr">
+      <c r="F186" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G186" s="6" t="inlineStr"/>
+      <c r="H186" s="6" t="inlineStr">
         <is>
           <t>0/35</t>
         </is>
       </c>
-      <c r="I186" s="5" t="inlineStr">
+      <c r="I186" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B187" s="5" t="inlineStr">
+      <c r="A187" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B187" s="6" t="inlineStr">
         <is>
           <t>A1-D1</t>
         </is>
       </c>
-      <c r="C187" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D187" s="5" t="inlineStr">
+      <c r="C187" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D187" s="6" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="E187" s="5" t="inlineStr">
+      <c r="E187" s="6" t="inlineStr">
         <is>
           <t>16/07/2026</t>
         </is>
       </c>
-      <c r="F187" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G187" s="5" t="inlineStr"/>
-      <c r="H187" s="5" t="inlineStr">
+      <c r="F187" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G187" s="6" t="inlineStr"/>
+      <c r="H187" s="6" t="inlineStr">
         <is>
           <t>0/35</t>
         </is>
       </c>
-      <c r="I187" s="5" t="inlineStr">
+      <c r="I187" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B188" s="5" t="inlineStr">
+      <c r="A188" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B188" s="6" t="inlineStr">
         <is>
           <t>A1-D1</t>
         </is>
       </c>
-      <c r="C188" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D188" s="5" t="inlineStr">
+      <c r="C188" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D188" s="6" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="E188" s="5" t="inlineStr">
+      <c r="E188" s="6" t="inlineStr">
         <is>
           <t>21/07/2026</t>
         </is>
       </c>
-      <c r="F188" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G188" s="5" t="inlineStr"/>
-      <c r="H188" s="5" t="inlineStr">
+      <c r="F188" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G188" s="6" t="inlineStr"/>
+      <c r="H188" s="6" t="inlineStr">
         <is>
           <t>0/35</t>
         </is>
       </c>
-      <c r="I188" s="5" t="inlineStr">
+      <c r="I188" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B189" s="5" t="inlineStr">
+      <c r="A189" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B189" s="6" t="inlineStr">
         <is>
           <t>A1-D1</t>
         </is>
       </c>
-      <c r="C189" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D189" s="5" t="inlineStr">
+      <c r="C189" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D189" s="6" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="E189" s="5" t="inlineStr">
+      <c r="E189" s="6" t="inlineStr">
         <is>
           <t>22/07/2026</t>
         </is>
       </c>
-      <c r="F189" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G189" s="5" t="inlineStr"/>
-      <c r="H189" s="5" t="inlineStr">
+      <c r="F189" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G189" s="6" t="inlineStr"/>
+      <c r="H189" s="6" t="inlineStr">
         <is>
           <t>0/35</t>
         </is>
       </c>
-      <c r="I189" s="5" t="inlineStr">
+      <c r="I189" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B190" s="5" t="inlineStr">
+      <c r="A190" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B190" s="6" t="inlineStr">
         <is>
           <t>A1-D1</t>
         </is>
       </c>
-      <c r="C190" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D190" s="5" t="inlineStr">
+      <c r="C190" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D190" s="6" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="E190" s="5" t="inlineStr">
+      <c r="E190" s="6" t="inlineStr">
         <is>
           <t>23/07/2026</t>
         </is>
       </c>
-      <c r="F190" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G190" s="5" t="inlineStr"/>
-      <c r="H190" s="5" t="inlineStr">
+      <c r="F190" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G190" s="6" t="inlineStr"/>
+      <c r="H190" s="6" t="inlineStr">
         <is>
           <t>0/35</t>
         </is>
       </c>
-      <c r="I190" s="5" t="inlineStr">
+      <c r="I190" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -10144,43 +10144,43 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B196" s="9" t="inlineStr">
+      <c r="A196" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B196" s="5" t="inlineStr">
         <is>
           <t>A1-D2</t>
         </is>
       </c>
-      <c r="C196" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D196" s="9" t="inlineStr">
+      <c r="C196" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D196" s="5" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E196" s="9" t="inlineStr">
+      <c r="E196" s="5" t="inlineStr">
         <is>
           <t>04/06/2026</t>
         </is>
       </c>
-      <c r="F196" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G196" s="9" t="inlineStr"/>
-      <c r="H196" s="9" t="inlineStr">
+      <c r="F196" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G196" s="5" t="inlineStr"/>
+      <c r="H196" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I196" s="9" t="inlineStr">
+      <c r="I196" s="5" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
@@ -10798,43 +10798,43 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B210" s="9" t="inlineStr">
+      <c r="A210" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B210" s="5" t="inlineStr">
         <is>
           <t>A1-D2</t>
         </is>
       </c>
-      <c r="C210" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D210" s="9" t="inlineStr">
+      <c r="C210" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D210" s="5" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="E210" s="9" t="inlineStr">
+      <c r="E210" s="5" t="inlineStr">
         <is>
           <t>08/07/2026</t>
         </is>
       </c>
-      <c r="F210" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G210" s="9" t="inlineStr"/>
-      <c r="H210" s="9" t="inlineStr">
+      <c r="F210" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G210" s="5" t="inlineStr"/>
+      <c r="H210" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I210" s="9" t="inlineStr">
+      <c r="I210" s="5" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
@@ -10888,258 +10888,258 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B212" s="5" t="inlineStr">
+      <c r="A212" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B212" s="6" t="inlineStr">
         <is>
           <t>A1-D2</t>
         </is>
       </c>
-      <c r="C212" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D212" s="5" t="inlineStr">
+      <c r="C212" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D212" s="6" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="E212" s="5" t="inlineStr">
+      <c r="E212" s="6" t="inlineStr">
         <is>
           <t>14/07/2026</t>
         </is>
       </c>
-      <c r="F212" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G212" s="5" t="inlineStr"/>
-      <c r="H212" s="5" t="inlineStr">
+      <c r="F212" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G212" s="6" t="inlineStr"/>
+      <c r="H212" s="6" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I212" s="5" t="inlineStr">
+      <c r="I212" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B213" s="5" t="inlineStr">
+      <c r="A213" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B213" s="6" t="inlineStr">
         <is>
           <t>A1-D2</t>
         </is>
       </c>
-      <c r="C213" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D213" s="5" t="inlineStr">
+      <c r="C213" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D213" s="6" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="E213" s="5" t="inlineStr">
+      <c r="E213" s="6" t="inlineStr">
         <is>
           <t>15/07/2026</t>
         </is>
       </c>
-      <c r="F213" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G213" s="5" t="inlineStr"/>
-      <c r="H213" s="5" t="inlineStr">
+      <c r="F213" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G213" s="6" t="inlineStr"/>
+      <c r="H213" s="6" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I213" s="5" t="inlineStr">
+      <c r="I213" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B214" s="5" t="inlineStr">
+      <c r="A214" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B214" s="6" t="inlineStr">
         <is>
           <t>A1-D2</t>
         </is>
       </c>
-      <c r="C214" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D214" s="5" t="inlineStr">
+      <c r="C214" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D214" s="6" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="E214" s="5" t="inlineStr">
+      <c r="E214" s="6" t="inlineStr">
         <is>
           <t>16/07/2026</t>
         </is>
       </c>
-      <c r="F214" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G214" s="5" t="inlineStr"/>
-      <c r="H214" s="5" t="inlineStr">
+      <c r="F214" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G214" s="6" t="inlineStr"/>
+      <c r="H214" s="6" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I214" s="5" t="inlineStr">
+      <c r="I214" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B215" s="5" t="inlineStr">
+      <c r="A215" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B215" s="6" t="inlineStr">
         <is>
           <t>A1-D2</t>
         </is>
       </c>
-      <c r="C215" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D215" s="5" t="inlineStr">
+      <c r="C215" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D215" s="6" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="E215" s="5" t="inlineStr">
+      <c r="E215" s="6" t="inlineStr">
         <is>
           <t>21/07/2026</t>
         </is>
       </c>
-      <c r="F215" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G215" s="5" t="inlineStr"/>
-      <c r="H215" s="5" t="inlineStr">
+      <c r="F215" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G215" s="6" t="inlineStr"/>
+      <c r="H215" s="6" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I215" s="5" t="inlineStr">
+      <c r="I215" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B216" s="5" t="inlineStr">
+      <c r="A216" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B216" s="6" t="inlineStr">
         <is>
           <t>A1-D2</t>
         </is>
       </c>
-      <c r="C216" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D216" s="5" t="inlineStr">
+      <c r="C216" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D216" s="6" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="E216" s="5" t="inlineStr">
+      <c r="E216" s="6" t="inlineStr">
         <is>
           <t>22/07/2026</t>
         </is>
       </c>
-      <c r="F216" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G216" s="5" t="inlineStr"/>
-      <c r="H216" s="5" t="inlineStr">
+      <c r="F216" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G216" s="6" t="inlineStr"/>
+      <c r="H216" s="6" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I216" s="5" t="inlineStr">
+      <c r="I216" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B217" s="5" t="inlineStr">
+      <c r="A217" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B217" s="6" t="inlineStr">
         <is>
           <t>A1-D2</t>
         </is>
       </c>
-      <c r="C217" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D217" s="5" t="inlineStr">
+      <c r="C217" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D217" s="6" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="E217" s="5" t="inlineStr">
+      <c r="E217" s="6" t="inlineStr">
         <is>
           <t>23/07/2026</t>
         </is>
       </c>
-      <c r="F217" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G217" s="5" t="inlineStr"/>
-      <c r="H217" s="5" t="inlineStr">
+      <c r="F217" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G217" s="6" t="inlineStr"/>
+      <c r="H217" s="6" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I217" s="5" t="inlineStr">
+      <c r="I217" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -11381,43 +11381,43 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B223" s="9" t="inlineStr">
+      <c r="A223" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B223" s="5" t="inlineStr">
         <is>
           <t>A1-E1</t>
         </is>
       </c>
-      <c r="C223" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D223" s="9" t="inlineStr">
+      <c r="C223" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D223" s="5" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E223" s="9" t="inlineStr">
+      <c r="E223" s="5" t="inlineStr">
         <is>
           <t>04/06/2026</t>
         </is>
       </c>
-      <c r="F223" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G223" s="9" t="inlineStr"/>
-      <c r="H223" s="9" t="inlineStr">
+      <c r="F223" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G223" s="5" t="inlineStr"/>
+      <c r="H223" s="5" t="inlineStr">
         <is>
           <t>0/38</t>
         </is>
       </c>
-      <c r="I223" s="9" t="inlineStr">
+      <c r="I223" s="5" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
@@ -12082,301 +12082,301 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B238" s="9" t="inlineStr">
+      <c r="A238" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B238" s="5" t="inlineStr">
         <is>
           <t>A1-E1</t>
         </is>
       </c>
-      <c r="C238" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D238" s="9" t="inlineStr">
+      <c r="C238" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D238" s="5" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="E238" s="9" t="inlineStr">
+      <c r="E238" s="5" t="inlineStr">
         <is>
           <t>09/07/2026</t>
         </is>
       </c>
-      <c r="F238" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G238" s="9" t="inlineStr"/>
-      <c r="H238" s="9" t="inlineStr">
+      <c r="F238" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G238" s="5" t="inlineStr"/>
+      <c r="H238" s="5" t="inlineStr">
         <is>
           <t>0/38</t>
         </is>
       </c>
-      <c r="I238" s="9" t="inlineStr">
+      <c r="I238" s="5" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B239" s="5" t="inlineStr">
+      <c r="A239" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B239" s="6" t="inlineStr">
         <is>
           <t>A1-E1</t>
         </is>
       </c>
-      <c r="C239" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D239" s="5" t="inlineStr">
+      <c r="C239" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D239" s="6" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="E239" s="5" t="inlineStr">
+      <c r="E239" s="6" t="inlineStr">
         <is>
           <t>14/07/2026</t>
         </is>
       </c>
-      <c r="F239" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G239" s="5" t="inlineStr"/>
-      <c r="H239" s="5" t="inlineStr">
+      <c r="F239" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G239" s="6" t="inlineStr"/>
+      <c r="H239" s="6" t="inlineStr">
         <is>
           <t>0/38</t>
         </is>
       </c>
-      <c r="I239" s="5" t="inlineStr">
+      <c r="I239" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B240" s="5" t="inlineStr">
+      <c r="A240" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B240" s="6" t="inlineStr">
         <is>
           <t>A1-E1</t>
         </is>
       </c>
-      <c r="C240" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D240" s="5" t="inlineStr">
+      <c r="C240" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D240" s="6" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="E240" s="5" t="inlineStr">
+      <c r="E240" s="6" t="inlineStr">
         <is>
           <t>15/07/2026</t>
         </is>
       </c>
-      <c r="F240" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G240" s="5" t="inlineStr"/>
-      <c r="H240" s="5" t="inlineStr">
+      <c r="F240" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G240" s="6" t="inlineStr"/>
+      <c r="H240" s="6" t="inlineStr">
         <is>
           <t>0/38</t>
         </is>
       </c>
-      <c r="I240" s="5" t="inlineStr">
+      <c r="I240" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B241" s="5" t="inlineStr">
+      <c r="A241" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B241" s="6" t="inlineStr">
         <is>
           <t>A1-E1</t>
         </is>
       </c>
-      <c r="C241" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D241" s="5" t="inlineStr">
+      <c r="C241" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D241" s="6" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="E241" s="5" t="inlineStr">
+      <c r="E241" s="6" t="inlineStr">
         <is>
           <t>16/07/2026</t>
         </is>
       </c>
-      <c r="F241" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G241" s="5" t="inlineStr"/>
-      <c r="H241" s="5" t="inlineStr">
+      <c r="F241" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G241" s="6" t="inlineStr"/>
+      <c r="H241" s="6" t="inlineStr">
         <is>
           <t>0/38</t>
         </is>
       </c>
-      <c r="I241" s="5" t="inlineStr">
+      <c r="I241" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B242" s="5" t="inlineStr">
+      <c r="A242" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B242" s="6" t="inlineStr">
         <is>
           <t>A1-E1</t>
         </is>
       </c>
-      <c r="C242" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D242" s="5" t="inlineStr">
+      <c r="C242" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D242" s="6" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="E242" s="5" t="inlineStr">
+      <c r="E242" s="6" t="inlineStr">
         <is>
           <t>21/07/2026</t>
         </is>
       </c>
-      <c r="F242" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G242" s="5" t="inlineStr"/>
-      <c r="H242" s="5" t="inlineStr">
+      <c r="F242" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G242" s="6" t="inlineStr"/>
+      <c r="H242" s="6" t="inlineStr">
         <is>
           <t>0/38</t>
         </is>
       </c>
-      <c r="I242" s="5" t="inlineStr">
+      <c r="I242" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B243" s="5" t="inlineStr">
+      <c r="A243" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B243" s="6" t="inlineStr">
         <is>
           <t>A1-E1</t>
         </is>
       </c>
-      <c r="C243" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D243" s="5" t="inlineStr">
+      <c r="C243" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D243" s="6" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="E243" s="5" t="inlineStr">
+      <c r="E243" s="6" t="inlineStr">
         <is>
           <t>22/07/2026</t>
         </is>
       </c>
-      <c r="F243" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G243" s="5" t="inlineStr"/>
-      <c r="H243" s="5" t="inlineStr">
+      <c r="F243" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G243" s="6" t="inlineStr"/>
+      <c r="H243" s="6" t="inlineStr">
         <is>
           <t>0/38</t>
         </is>
       </c>
-      <c r="I243" s="5" t="inlineStr">
+      <c r="I243" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B244" s="5" t="inlineStr">
+      <c r="A244" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B244" s="6" t="inlineStr">
         <is>
           <t>A1-E1</t>
         </is>
       </c>
-      <c r="C244" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D244" s="5" t="inlineStr">
+      <c r="C244" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D244" s="6" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="E244" s="5" t="inlineStr">
+      <c r="E244" s="6" t="inlineStr">
         <is>
           <t>23/07/2026</t>
         </is>
       </c>
-      <c r="F244" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G244" s="5" t="inlineStr"/>
-      <c r="H244" s="5" t="inlineStr">
+      <c r="F244" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G244" s="6" t="inlineStr"/>
+      <c r="H244" s="6" t="inlineStr">
         <is>
           <t>0/38</t>
         </is>
       </c>
-      <c r="I244" s="5" t="inlineStr">
+      <c r="I244" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -12618,43 +12618,43 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B250" s="9" t="inlineStr">
+      <c r="A250" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B250" s="5" t="inlineStr">
         <is>
           <t>A1-E2</t>
         </is>
       </c>
-      <c r="C250" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D250" s="9" t="inlineStr">
+      <c r="C250" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D250" s="5" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E250" s="9" t="inlineStr">
+      <c r="E250" s="5" t="inlineStr">
         <is>
           <t>04/06/2026</t>
         </is>
       </c>
-      <c r="F250" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G250" s="9" t="inlineStr"/>
-      <c r="H250" s="9" t="inlineStr">
+      <c r="F250" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G250" s="5" t="inlineStr"/>
+      <c r="H250" s="5" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I250" s="9" t="inlineStr">
+      <c r="I250" s="5" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
@@ -13319,301 +13319,301 @@
       </c>
     </row>
     <row r="265">
-      <c r="A265" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B265" s="9" t="inlineStr">
+      <c r="A265" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B265" s="5" t="inlineStr">
         <is>
           <t>A1-E2</t>
         </is>
       </c>
-      <c r="C265" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D265" s="9" t="inlineStr">
+      <c r="C265" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D265" s="5" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="E265" s="9" t="inlineStr">
+      <c r="E265" s="5" t="inlineStr">
         <is>
           <t>09/07/2026</t>
         </is>
       </c>
-      <c r="F265" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G265" s="9" t="inlineStr"/>
-      <c r="H265" s="9" t="inlineStr">
+      <c r="F265" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G265" s="5" t="inlineStr"/>
+      <c r="H265" s="5" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I265" s="9" t="inlineStr">
+      <c r="I265" s="5" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
       </c>
     </row>
     <row r="266">
-      <c r="A266" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B266" s="5" t="inlineStr">
+      <c r="A266" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B266" s="6" t="inlineStr">
         <is>
           <t>A1-E2</t>
         </is>
       </c>
-      <c r="C266" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D266" s="5" t="inlineStr">
+      <c r="C266" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D266" s="6" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="E266" s="5" t="inlineStr">
+      <c r="E266" s="6" t="inlineStr">
         <is>
           <t>14/07/2026</t>
         </is>
       </c>
-      <c r="F266" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G266" s="5" t="inlineStr"/>
-      <c r="H266" s="5" t="inlineStr">
+      <c r="F266" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G266" s="6" t="inlineStr"/>
+      <c r="H266" s="6" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I266" s="5" t="inlineStr">
+      <c r="I266" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="267">
-      <c r="A267" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B267" s="5" t="inlineStr">
+      <c r="A267" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B267" s="6" t="inlineStr">
         <is>
           <t>A1-E2</t>
         </is>
       </c>
-      <c r="C267" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D267" s="5" t="inlineStr">
+      <c r="C267" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D267" s="6" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="E267" s="5" t="inlineStr">
+      <c r="E267" s="6" t="inlineStr">
         <is>
           <t>15/07/2026</t>
         </is>
       </c>
-      <c r="F267" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G267" s="5" t="inlineStr"/>
-      <c r="H267" s="5" t="inlineStr">
+      <c r="F267" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G267" s="6" t="inlineStr"/>
+      <c r="H267" s="6" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I267" s="5" t="inlineStr">
+      <c r="I267" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="268">
-      <c r="A268" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B268" s="5" t="inlineStr">
+      <c r="A268" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B268" s="6" t="inlineStr">
         <is>
           <t>A1-E2</t>
         </is>
       </c>
-      <c r="C268" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D268" s="5" t="inlineStr">
+      <c r="C268" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D268" s="6" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="E268" s="5" t="inlineStr">
+      <c r="E268" s="6" t="inlineStr">
         <is>
           <t>16/07/2026</t>
         </is>
       </c>
-      <c r="F268" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G268" s="5" t="inlineStr"/>
-      <c r="H268" s="5" t="inlineStr">
+      <c r="F268" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G268" s="6" t="inlineStr"/>
+      <c r="H268" s="6" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I268" s="5" t="inlineStr">
+      <c r="I268" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="269">
-      <c r="A269" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B269" s="5" t="inlineStr">
+      <c r="A269" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B269" s="6" t="inlineStr">
         <is>
           <t>A1-E2</t>
         </is>
       </c>
-      <c r="C269" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D269" s="5" t="inlineStr">
+      <c r="C269" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D269" s="6" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="E269" s="5" t="inlineStr">
+      <c r="E269" s="6" t="inlineStr">
         <is>
           <t>21/07/2026</t>
         </is>
       </c>
-      <c r="F269" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G269" s="5" t="inlineStr"/>
-      <c r="H269" s="5" t="inlineStr">
+      <c r="F269" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G269" s="6" t="inlineStr"/>
+      <c r="H269" s="6" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I269" s="5" t="inlineStr">
+      <c r="I269" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="270">
-      <c r="A270" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B270" s="5" t="inlineStr">
+      <c r="A270" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B270" s="6" t="inlineStr">
         <is>
           <t>A1-E2</t>
         </is>
       </c>
-      <c r="C270" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D270" s="5" t="inlineStr">
+      <c r="C270" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D270" s="6" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="E270" s="5" t="inlineStr">
+      <c r="E270" s="6" t="inlineStr">
         <is>
           <t>22/07/2026</t>
         </is>
       </c>
-      <c r="F270" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G270" s="5" t="inlineStr"/>
-      <c r="H270" s="5" t="inlineStr">
+      <c r="F270" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G270" s="6" t="inlineStr"/>
+      <c r="H270" s="6" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I270" s="5" t="inlineStr">
+      <c r="I270" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="271">
-      <c r="A271" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B271" s="5" t="inlineStr">
+      <c r="A271" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B271" s="6" t="inlineStr">
         <is>
           <t>A1-E2</t>
         </is>
       </c>
-      <c r="C271" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D271" s="5" t="inlineStr">
+      <c r="C271" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D271" s="6" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="E271" s="5" t="inlineStr">
+      <c r="E271" s="6" t="inlineStr">
         <is>
           <t>23/07/2026</t>
         </is>
       </c>
-      <c r="F271" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G271" s="5" t="inlineStr"/>
-      <c r="H271" s="5" t="inlineStr">
+      <c r="F271" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G271" s="6" t="inlineStr"/>
+      <c r="H271" s="6" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I271" s="5" t="inlineStr">
+      <c r="I271" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -13855,43 +13855,43 @@
       </c>
     </row>
     <row r="277">
-      <c r="A277" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B277" s="9" t="inlineStr">
+      <c r="A277" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B277" s="5" t="inlineStr">
         <is>
           <t>A1-F1</t>
         </is>
       </c>
-      <c r="C277" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D277" s="9" t="inlineStr">
+      <c r="C277" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D277" s="5" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E277" s="9" t="inlineStr">
+      <c r="E277" s="5" t="inlineStr">
         <is>
           <t>04/06/2026</t>
         </is>
       </c>
-      <c r="F277" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G277" s="9" t="inlineStr"/>
-      <c r="H277" s="9" t="inlineStr">
+      <c r="F277" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G277" s="5" t="inlineStr"/>
+      <c r="H277" s="5" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I277" s="9" t="inlineStr">
+      <c r="I277" s="5" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
@@ -14603,258 +14603,258 @@
       </c>
     </row>
     <row r="293">
-      <c r="A293" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B293" s="5" t="inlineStr">
+      <c r="A293" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B293" s="6" t="inlineStr">
         <is>
           <t>A1-F1</t>
         </is>
       </c>
-      <c r="C293" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D293" s="5" t="inlineStr">
+      <c r="C293" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D293" s="6" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="E293" s="5" t="inlineStr">
+      <c r="E293" s="6" t="inlineStr">
         <is>
           <t>14/07/2026</t>
         </is>
       </c>
-      <c r="F293" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G293" s="5" t="inlineStr"/>
-      <c r="H293" s="5" t="inlineStr">
+      <c r="F293" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G293" s="6" t="inlineStr"/>
+      <c r="H293" s="6" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I293" s="5" t="inlineStr">
+      <c r="I293" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="294">
-      <c r="A294" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B294" s="5" t="inlineStr">
+      <c r="A294" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B294" s="6" t="inlineStr">
         <is>
           <t>A1-F1</t>
         </is>
       </c>
-      <c r="C294" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D294" s="5" t="inlineStr">
+      <c r="C294" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D294" s="6" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="E294" s="5" t="inlineStr">
+      <c r="E294" s="6" t="inlineStr">
         <is>
           <t>15/07/2026</t>
         </is>
       </c>
-      <c r="F294" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G294" s="5" t="inlineStr"/>
-      <c r="H294" s="5" t="inlineStr">
+      <c r="F294" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G294" s="6" t="inlineStr"/>
+      <c r="H294" s="6" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I294" s="5" t="inlineStr">
+      <c r="I294" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="295">
-      <c r="A295" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B295" s="5" t="inlineStr">
+      <c r="A295" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B295" s="6" t="inlineStr">
         <is>
           <t>A1-F1</t>
         </is>
       </c>
-      <c r="C295" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D295" s="5" t="inlineStr">
+      <c r="C295" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D295" s="6" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="E295" s="5" t="inlineStr">
+      <c r="E295" s="6" t="inlineStr">
         <is>
           <t>16/07/2026</t>
         </is>
       </c>
-      <c r="F295" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G295" s="5" t="inlineStr"/>
-      <c r="H295" s="5" t="inlineStr">
+      <c r="F295" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G295" s="6" t="inlineStr"/>
+      <c r="H295" s="6" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I295" s="5" t="inlineStr">
+      <c r="I295" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="296">
-      <c r="A296" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B296" s="5" t="inlineStr">
+      <c r="A296" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B296" s="6" t="inlineStr">
         <is>
           <t>A1-F1</t>
         </is>
       </c>
-      <c r="C296" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D296" s="5" t="inlineStr">
+      <c r="C296" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D296" s="6" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="E296" s="5" t="inlineStr">
+      <c r="E296" s="6" t="inlineStr">
         <is>
           <t>21/07/2026</t>
         </is>
       </c>
-      <c r="F296" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G296" s="5" t="inlineStr"/>
-      <c r="H296" s="5" t="inlineStr">
+      <c r="F296" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G296" s="6" t="inlineStr"/>
+      <c r="H296" s="6" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I296" s="5" t="inlineStr">
+      <c r="I296" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="297">
-      <c r="A297" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B297" s="5" t="inlineStr">
+      <c r="A297" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B297" s="6" t="inlineStr">
         <is>
           <t>A1-F1</t>
         </is>
       </c>
-      <c r="C297" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D297" s="5" t="inlineStr">
+      <c r="C297" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D297" s="6" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="E297" s="5" t="inlineStr">
+      <c r="E297" s="6" t="inlineStr">
         <is>
           <t>22/07/2026</t>
         </is>
       </c>
-      <c r="F297" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G297" s="5" t="inlineStr"/>
-      <c r="H297" s="5" t="inlineStr">
+      <c r="F297" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G297" s="6" t="inlineStr"/>
+      <c r="H297" s="6" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I297" s="5" t="inlineStr">
+      <c r="I297" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="298">
-      <c r="A298" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B298" s="5" t="inlineStr">
+      <c r="A298" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B298" s="6" t="inlineStr">
         <is>
           <t>A1-F1</t>
         </is>
       </c>
-      <c r="C298" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D298" s="5" t="inlineStr">
+      <c r="C298" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D298" s="6" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="E298" s="5" t="inlineStr">
+      <c r="E298" s="6" t="inlineStr">
         <is>
           <t>23/07/2026</t>
         </is>
       </c>
-      <c r="F298" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G298" s="5" t="inlineStr"/>
-      <c r="H298" s="5" t="inlineStr">
+      <c r="F298" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G298" s="6" t="inlineStr"/>
+      <c r="H298" s="6" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I298" s="5" t="inlineStr">
+      <c r="I298" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -15096,43 +15096,43 @@
       </c>
     </row>
     <row r="304">
-      <c r="A304" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B304" s="9" t="inlineStr">
+      <c r="A304" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B304" s="5" t="inlineStr">
         <is>
           <t>A1-F2</t>
         </is>
       </c>
-      <c r="C304" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D304" s="9" t="inlineStr">
+      <c r="C304" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D304" s="5" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E304" s="9" t="inlineStr">
+      <c r="E304" s="5" t="inlineStr">
         <is>
           <t>04/06/2026</t>
         </is>
       </c>
-      <c r="F304" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G304" s="9" t="inlineStr"/>
-      <c r="H304" s="9" t="inlineStr">
+      <c r="F304" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G304" s="5" t="inlineStr"/>
+      <c r="H304" s="5" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I304" s="9" t="inlineStr">
+      <c r="I304" s="5" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
@@ -15703,43 +15703,43 @@
       </c>
     </row>
     <row r="317">
-      <c r="A317" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B317" s="9" t="inlineStr">
+      <c r="A317" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B317" s="5" t="inlineStr">
         <is>
           <t>A1-F2</t>
         </is>
       </c>
-      <c r="C317" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D317" s="9" t="inlineStr">
+      <c r="C317" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D317" s="5" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="E317" s="9" t="inlineStr">
+      <c r="E317" s="5" t="inlineStr">
         <is>
           <t>07/07/2026</t>
         </is>
       </c>
-      <c r="F317" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G317" s="9" t="inlineStr"/>
-      <c r="H317" s="9" t="inlineStr">
+      <c r="F317" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G317" s="5" t="inlineStr"/>
+      <c r="H317" s="5" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I317" s="9" t="inlineStr">
+      <c r="I317" s="5" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
@@ -15840,258 +15840,258 @@
       </c>
     </row>
     <row r="320">
-      <c r="A320" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B320" s="5" t="inlineStr">
+      <c r="A320" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B320" s="6" t="inlineStr">
         <is>
           <t>A1-F2</t>
         </is>
       </c>
-      <c r="C320" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D320" s="5" t="inlineStr">
+      <c r="C320" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D320" s="6" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="E320" s="5" t="inlineStr">
+      <c r="E320" s="6" t="inlineStr">
         <is>
           <t>14/07/2026</t>
         </is>
       </c>
-      <c r="F320" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G320" s="5" t="inlineStr"/>
-      <c r="H320" s="5" t="inlineStr">
+      <c r="F320" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G320" s="6" t="inlineStr"/>
+      <c r="H320" s="6" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I320" s="5" t="inlineStr">
+      <c r="I320" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="321">
-      <c r="A321" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B321" s="5" t="inlineStr">
+      <c r="A321" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B321" s="6" t="inlineStr">
         <is>
           <t>A1-F2</t>
         </is>
       </c>
-      <c r="C321" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D321" s="5" t="inlineStr">
+      <c r="C321" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D321" s="6" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="E321" s="5" t="inlineStr">
+      <c r="E321" s="6" t="inlineStr">
         <is>
           <t>15/07/2026</t>
         </is>
       </c>
-      <c r="F321" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G321" s="5" t="inlineStr"/>
-      <c r="H321" s="5" t="inlineStr">
+      <c r="F321" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G321" s="6" t="inlineStr"/>
+      <c r="H321" s="6" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I321" s="5" t="inlineStr">
+      <c r="I321" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="322">
-      <c r="A322" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B322" s="5" t="inlineStr">
+      <c r="A322" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B322" s="6" t="inlineStr">
         <is>
           <t>A1-F2</t>
         </is>
       </c>
-      <c r="C322" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D322" s="5" t="inlineStr">
+      <c r="C322" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D322" s="6" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="E322" s="5" t="inlineStr">
+      <c r="E322" s="6" t="inlineStr">
         <is>
           <t>16/07/2026</t>
         </is>
       </c>
-      <c r="F322" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G322" s="5" t="inlineStr"/>
-      <c r="H322" s="5" t="inlineStr">
+      <c r="F322" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G322" s="6" t="inlineStr"/>
+      <c r="H322" s="6" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I322" s="5" t="inlineStr">
+      <c r="I322" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="323">
-      <c r="A323" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B323" s="5" t="inlineStr">
+      <c r="A323" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B323" s="6" t="inlineStr">
         <is>
           <t>A1-F2</t>
         </is>
       </c>
-      <c r="C323" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D323" s="5" t="inlineStr">
+      <c r="C323" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D323" s="6" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="E323" s="5" t="inlineStr">
+      <c r="E323" s="6" t="inlineStr">
         <is>
           <t>21/07/2026</t>
         </is>
       </c>
-      <c r="F323" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G323" s="5" t="inlineStr"/>
-      <c r="H323" s="5" t="inlineStr">
+      <c r="F323" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G323" s="6" t="inlineStr"/>
+      <c r="H323" s="6" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I323" s="5" t="inlineStr">
+      <c r="I323" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="324">
-      <c r="A324" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B324" s="5" t="inlineStr">
+      <c r="A324" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B324" s="6" t="inlineStr">
         <is>
           <t>A1-F2</t>
         </is>
       </c>
-      <c r="C324" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D324" s="5" t="inlineStr">
+      <c r="C324" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D324" s="6" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="E324" s="5" t="inlineStr">
+      <c r="E324" s="6" t="inlineStr">
         <is>
           <t>22/07/2026</t>
         </is>
       </c>
-      <c r="F324" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G324" s="5" t="inlineStr"/>
-      <c r="H324" s="5" t="inlineStr">
+      <c r="F324" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G324" s="6" t="inlineStr"/>
+      <c r="H324" s="6" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I324" s="5" t="inlineStr">
+      <c r="I324" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="325">
-      <c r="A325" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B325" s="5" t="inlineStr">
+      <c r="A325" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B325" s="6" t="inlineStr">
         <is>
           <t>A1-F2</t>
         </is>
       </c>
-      <c r="C325" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D325" s="5" t="inlineStr">
+      <c r="C325" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D325" s="6" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="E325" s="5" t="inlineStr">
+      <c r="E325" s="6" t="inlineStr">
         <is>
           <t>23/07/2026</t>
         </is>
       </c>
-      <c r="F325" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G325" s="5" t="inlineStr"/>
-      <c r="H325" s="5" t="inlineStr">
+      <c r="F325" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G325" s="6" t="inlineStr"/>
+      <c r="H325" s="6" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I325" s="5" t="inlineStr">
+      <c r="I325" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A1_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A1_session_analysis.xlsx
@@ -58,14 +58,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFB6C1"/>
-        <bgColor rgb="00FFB6C1"/>
+        <fgColor rgb="00FFFFE0"/>
+        <bgColor rgb="00FFFFE0"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFFE0"/>
-        <bgColor rgb="00FFFFE0"/>
+        <fgColor rgb="00FFB6C1"/>
+        <bgColor rgb="00FFB6C1"/>
       </patternFill>
     </fill>
   </fills>
@@ -96,16 +96,16 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -814,7 +814,7 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>253</v>
+        <v>259</v>
       </c>
     </row>
     <row r="7">
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8">
@@ -980,7 +980,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>78.1%</t>
+          <t>79.9%</t>
         </is>
       </c>
     </row>
@@ -1037,7 +1037,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>73.8%</t>
+          <t>72.8%</t>
         </is>
       </c>
     </row>
@@ -1342,22 +1342,22 @@
         <v>27</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q15" s="4" t="n">
         <v>3</v>
       </c>
       <c r="R15" s="4" t="inlineStr">
         <is>
-          <t>85.2%</t>
+          <t>88.9%</t>
         </is>
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>68.8%</t>
+          <t>67.0%</t>
         </is>
       </c>
     </row>
@@ -1424,22 +1424,22 @@
         <v>27</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q16" s="4" t="n">
         <v>3</v>
       </c>
       <c r="R16" s="4" t="inlineStr">
         <is>
-          <t>85.2%</t>
+          <t>88.9%</t>
         </is>
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>69.7%</t>
+          <t>68.6%</t>
         </is>
       </c>
     </row>
@@ -1506,22 +1506,22 @@
         <v>27</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q17" s="4" t="n">
         <v>3</v>
       </c>
       <c r="R17" s="4" t="inlineStr">
         <is>
-          <t>85.2%</t>
+          <t>88.9%</t>
         </is>
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>74.3%</t>
+          <t>72.3%</t>
         </is>
       </c>
     </row>
@@ -1588,22 +1588,22 @@
         <v>27</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q18" s="4" t="n">
         <v>3</v>
       </c>
       <c r="R18" s="4" t="inlineStr">
         <is>
-          <t>85.2%</t>
+          <t>88.9%</t>
         </is>
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>73.0%</t>
+          <t>71.0%</t>
         </is>
       </c>
     </row>
@@ -1670,22 +1670,22 @@
         <v>27</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q19" s="4" t="n">
         <v>3</v>
       </c>
       <c r="R19" s="4" t="inlineStr">
         <is>
-          <t>85.2%</t>
+          <t>88.9%</t>
         </is>
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>75.1%</t>
+          <t>72.5%</t>
         </is>
       </c>
     </row>
@@ -1752,22 +1752,22 @@
         <v>27</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q20" s="4" t="n">
         <v>3</v>
       </c>
       <c r="R20" s="4" t="inlineStr">
         <is>
-          <t>85.2%</t>
+          <t>88.9%</t>
         </is>
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>69.3%</t>
+          <t>68.2%</t>
         </is>
       </c>
     </row>
@@ -2100,45 +2100,49 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B25" s="5" t="inlineStr">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>A1-A1</t>
         </is>
       </c>
-      <c r="C25" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="E25" s="5" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>13/07/2026</t>
         </is>
       </c>
-      <c r="F25" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G25" s="5" t="inlineStr"/>
-      <c r="H25" s="5" t="inlineStr">
-        <is>
-          <t>0/34</t>
-        </is>
-      </c>
-      <c r="I25" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>9/34</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
       <c r="K25" s="4" t="inlineStr">
@@ -2178,43 +2182,43 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B26" s="6" t="inlineStr">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
         <is>
           <t>A1-A1</t>
         </is>
       </c>
-      <c r="C26" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D26" s="6" t="inlineStr">
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="E26" s="6" t="inlineStr">
+      <c r="E26" s="5" t="inlineStr">
         <is>
           <t>18/07/2026</t>
         </is>
       </c>
-      <c r="F26" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G26" s="6" t="inlineStr"/>
-      <c r="H26" s="6" t="inlineStr">
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="inlineStr"/>
+      <c r="H26" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I26" s="6" t="inlineStr">
+      <c r="I26" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -2256,86 +2260,86 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B27" s="6" t="inlineStr">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
         <is>
           <t>A1-A1</t>
         </is>
       </c>
-      <c r="C27" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D27" s="6" t="inlineStr">
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="E27" s="6" t="inlineStr">
+      <c r="E27" s="5" t="inlineStr">
         <is>
           <t>19/07/2026</t>
         </is>
       </c>
-      <c r="F27" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G27" s="6" t="inlineStr"/>
-      <c r="H27" s="6" t="inlineStr">
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="inlineStr"/>
+      <c r="H27" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I27" s="6" t="inlineStr">
+      <c r="I27" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B28" s="6" t="inlineStr">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
         <is>
           <t>A1-A1</t>
         </is>
       </c>
-      <c r="C28" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D28" s="6" t="inlineStr">
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="E28" s="6" t="inlineStr">
+      <c r="E28" s="5" t="inlineStr">
         <is>
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="F28" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G28" s="6" t="inlineStr"/>
-      <c r="H28" s="6" t="inlineStr">
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G28" s="5" t="inlineStr"/>
+      <c r="H28" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I28" s="6" t="inlineStr">
+      <c r="I28" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -2506,7 +2510,7 @@
           <t>Recorded</t>
         </is>
       </c>
-      <c r="L31" s="7" t="inlineStr">
+      <c r="L31" s="6" t="inlineStr">
         <is>
           <t>Green</t>
         </is>
@@ -2568,7 +2572,7 @@
           <t>Not Recorded</t>
         </is>
       </c>
-      <c r="L32" s="8" t="inlineStr">
+      <c r="L32" s="7" t="inlineStr">
         <is>
           <t>Red</t>
         </is>
@@ -2630,7 +2634,7 @@
           <t>Pending</t>
         </is>
       </c>
-      <c r="L33" s="9" t="inlineStr">
+      <c r="L33" s="8" t="inlineStr">
         <is>
           <t>Yellow</t>
         </is>
@@ -3488,172 +3492,176 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B52" s="5" t="inlineStr">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
         <is>
           <t>A1-A2</t>
         </is>
       </c>
-      <c r="C52" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D52" s="5" t="inlineStr">
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="E52" s="5" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>13/07/2026</t>
         </is>
       </c>
-      <c r="F52" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G52" s="5" t="inlineStr"/>
-      <c r="H52" s="5" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>14/33</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>A1-A2</t>
+        </is>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D53" s="5" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E53" s="5" t="inlineStr">
+        <is>
+          <t>18/07/2026</t>
+        </is>
+      </c>
+      <c r="F53" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G53" s="5" t="inlineStr"/>
+      <c r="H53" s="5" t="inlineStr">
         <is>
           <t>0/33</t>
         </is>
       </c>
-      <c r="I52" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B53" s="6" t="inlineStr">
+      <c r="I53" s="5" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="inlineStr">
         <is>
           <t>A1-A2</t>
         </is>
       </c>
-      <c r="C53" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D53" s="6" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="E53" s="6" t="inlineStr">
-        <is>
-          <t>18/07/2026</t>
-        </is>
-      </c>
-      <c r="F53" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G53" s="6" t="inlineStr"/>
-      <c r="H53" s="6" t="inlineStr">
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D54" s="5" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="E54" s="5" t="inlineStr">
+        <is>
+          <t>19/07/2026</t>
+        </is>
+      </c>
+      <c r="F54" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G54" s="5" t="inlineStr"/>
+      <c r="H54" s="5" t="inlineStr">
         <is>
           <t>0/33</t>
         </is>
       </c>
-      <c r="I53" s="6" t="inlineStr">
+      <c r="I54" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B54" s="6" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="inlineStr">
         <is>
           <t>A1-A2</t>
         </is>
       </c>
-      <c r="C54" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D54" s="6" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="E54" s="6" t="inlineStr">
-        <is>
-          <t>19/07/2026</t>
-        </is>
-      </c>
-      <c r="F54" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G54" s="6" t="inlineStr"/>
-      <c r="H54" s="6" t="inlineStr">
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D55" s="5" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E55" s="5" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="F55" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G55" s="5" t="inlineStr"/>
+      <c r="H55" s="5" t="inlineStr">
         <is>
           <t>0/33</t>
         </is>
       </c>
-      <c r="I54" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B55" s="6" t="inlineStr">
-        <is>
-          <t>A1-A2</t>
-        </is>
-      </c>
-      <c r="C55" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D55" s="6" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="E55" s="6" t="inlineStr">
-        <is>
-          <t>20/07/2026</t>
-        </is>
-      </c>
-      <c r="F55" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G55" s="6" t="inlineStr"/>
-      <c r="H55" s="6" t="inlineStr">
-        <is>
-          <t>0/33</t>
-        </is>
-      </c>
-      <c r="I55" s="6" t="inlineStr">
+      <c r="I55" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -4741,172 +4749,176 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B79" s="5" t="inlineStr">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
         <is>
           <t>A1-B1</t>
         </is>
       </c>
-      <c r="C79" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D79" s="5" t="inlineStr">
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="E79" s="5" t="inlineStr">
+      <c r="E79" s="2" t="inlineStr">
         <is>
           <t>13/07/2026</t>
         </is>
       </c>
-      <c r="F79" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G79" s="5" t="inlineStr"/>
-      <c r="H79" s="5" t="inlineStr">
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>9/34</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B80" s="5" t="inlineStr">
+        <is>
+          <t>A1-B1</t>
+        </is>
+      </c>
+      <c r="C80" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D80" s="5" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E80" s="5" t="inlineStr">
+        <is>
+          <t>18/07/2026</t>
+        </is>
+      </c>
+      <c r="F80" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G80" s="5" t="inlineStr"/>
+      <c r="H80" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I79" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B80" s="6" t="inlineStr">
+      <c r="I80" s="5" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B81" s="5" t="inlineStr">
         <is>
           <t>A1-B1</t>
         </is>
       </c>
-      <c r="C80" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D80" s="6" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="E80" s="6" t="inlineStr">
-        <is>
-          <t>18/07/2026</t>
-        </is>
-      </c>
-      <c r="F80" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G80" s="6" t="inlineStr"/>
-      <c r="H80" s="6" t="inlineStr">
+      <c r="C81" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D81" s="5" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="E81" s="5" t="inlineStr">
+        <is>
+          <t>19/07/2026</t>
+        </is>
+      </c>
+      <c r="F81" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G81" s="5" t="inlineStr"/>
+      <c r="H81" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I80" s="6" t="inlineStr">
+      <c r="I81" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B81" s="6" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B82" s="5" t="inlineStr">
         <is>
           <t>A1-B1</t>
         </is>
       </c>
-      <c r="C81" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D81" s="6" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="E81" s="6" t="inlineStr">
-        <is>
-          <t>19/07/2026</t>
-        </is>
-      </c>
-      <c r="F81" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G81" s="6" t="inlineStr"/>
-      <c r="H81" s="6" t="inlineStr">
+      <c r="C82" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D82" s="5" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E82" s="5" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="F82" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G82" s="5" t="inlineStr"/>
+      <c r="H82" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I81" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B82" s="6" t="inlineStr">
-        <is>
-          <t>A1-B1</t>
-        </is>
-      </c>
-      <c r="C82" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D82" s="6" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="E82" s="6" t="inlineStr">
-        <is>
-          <t>20/07/2026</t>
-        </is>
-      </c>
-      <c r="F82" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G82" s="6" t="inlineStr"/>
-      <c r="H82" s="6" t="inlineStr">
-        <is>
-          <t>0/34</t>
-        </is>
-      </c>
-      <c r="I82" s="6" t="inlineStr">
+      <c r="I82" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -5994,172 +6006,176 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B106" s="5" t="inlineStr">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
         <is>
           <t>A1-B2</t>
         </is>
       </c>
-      <c r="C106" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D106" s="5" t="inlineStr">
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="E106" s="5" t="inlineStr">
+      <c r="E106" s="2" t="inlineStr">
         <is>
           <t>13/07/2026</t>
         </is>
       </c>
-      <c r="F106" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G106" s="5" t="inlineStr"/>
-      <c r="H106" s="5" t="inlineStr">
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>8/34</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B107" s="5" t="inlineStr">
+        <is>
+          <t>A1-B2</t>
+        </is>
+      </c>
+      <c r="C107" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D107" s="5" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E107" s="5" t="inlineStr">
+        <is>
+          <t>18/07/2026</t>
+        </is>
+      </c>
+      <c r="F107" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G107" s="5" t="inlineStr"/>
+      <c r="H107" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I106" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B107" s="6" t="inlineStr">
+      <c r="I107" s="5" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B108" s="5" t="inlineStr">
         <is>
           <t>A1-B2</t>
         </is>
       </c>
-      <c r="C107" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D107" s="6" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="E107" s="6" t="inlineStr">
-        <is>
-          <t>18/07/2026</t>
-        </is>
-      </c>
-      <c r="F107" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G107" s="6" t="inlineStr"/>
-      <c r="H107" s="6" t="inlineStr">
+      <c r="C108" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D108" s="5" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="E108" s="5" t="inlineStr">
+        <is>
+          <t>19/07/2026</t>
+        </is>
+      </c>
+      <c r="F108" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G108" s="5" t="inlineStr"/>
+      <c r="H108" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I107" s="6" t="inlineStr">
+      <c r="I108" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B108" s="6" t="inlineStr">
+    <row r="109">
+      <c r="A109" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B109" s="5" t="inlineStr">
         <is>
           <t>A1-B2</t>
         </is>
       </c>
-      <c r="C108" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D108" s="6" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="E108" s="6" t="inlineStr">
-        <is>
-          <t>19/07/2026</t>
-        </is>
-      </c>
-      <c r="F108" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G108" s="6" t="inlineStr"/>
-      <c r="H108" s="6" t="inlineStr">
+      <c r="C109" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D109" s="5" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E109" s="5" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="F109" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G109" s="5" t="inlineStr"/>
+      <c r="H109" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I108" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B109" s="6" t="inlineStr">
-        <is>
-          <t>A1-B2</t>
-        </is>
-      </c>
-      <c r="C109" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D109" s="6" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="E109" s="6" t="inlineStr">
-        <is>
-          <t>20/07/2026</t>
-        </is>
-      </c>
-      <c r="F109" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G109" s="6" t="inlineStr"/>
-      <c r="H109" s="6" t="inlineStr">
-        <is>
-          <t>0/34</t>
-        </is>
-      </c>
-      <c r="I109" s="6" t="inlineStr">
+      <c r="I109" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -7247,172 +7263,176 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B133" s="5" t="inlineStr">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
         <is>
           <t>A1-C1</t>
         </is>
       </c>
-      <c r="C133" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D133" s="5" t="inlineStr">
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="E133" s="5" t="inlineStr">
+      <c r="E133" s="2" t="inlineStr">
         <is>
           <t>13/07/2026</t>
         </is>
       </c>
-      <c r="F133" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G133" s="5" t="inlineStr"/>
-      <c r="H133" s="5" t="inlineStr">
+      <c r="F133" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G133" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H133" s="2" t="inlineStr">
+        <is>
+          <t>5/34</t>
+        </is>
+      </c>
+      <c r="I133" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B134" s="5" t="inlineStr">
+        <is>
+          <t>A1-C1</t>
+        </is>
+      </c>
+      <c r="C134" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D134" s="5" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E134" s="5" t="inlineStr">
+        <is>
+          <t>18/07/2026</t>
+        </is>
+      </c>
+      <c r="F134" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G134" s="5" t="inlineStr"/>
+      <c r="H134" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I133" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B134" s="6" t="inlineStr">
+      <c r="I134" s="5" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B135" s="5" t="inlineStr">
         <is>
           <t>A1-C1</t>
         </is>
       </c>
-      <c r="C134" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D134" s="6" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="E134" s="6" t="inlineStr">
-        <is>
-          <t>18/07/2026</t>
-        </is>
-      </c>
-      <c r="F134" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G134" s="6" t="inlineStr"/>
-      <c r="H134" s="6" t="inlineStr">
+      <c r="C135" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D135" s="5" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="E135" s="5" t="inlineStr">
+        <is>
+          <t>19/07/2026</t>
+        </is>
+      </c>
+      <c r="F135" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G135" s="5" t="inlineStr"/>
+      <c r="H135" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I134" s="6" t="inlineStr">
+      <c r="I135" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B135" s="6" t="inlineStr">
+    <row r="136">
+      <c r="A136" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B136" s="5" t="inlineStr">
         <is>
           <t>A1-C1</t>
         </is>
       </c>
-      <c r="C135" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D135" s="6" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="E135" s="6" t="inlineStr">
-        <is>
-          <t>19/07/2026</t>
-        </is>
-      </c>
-      <c r="F135" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G135" s="6" t="inlineStr"/>
-      <c r="H135" s="6" t="inlineStr">
+      <c r="C136" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D136" s="5" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E136" s="5" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="F136" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G136" s="5" t="inlineStr"/>
+      <c r="H136" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I135" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B136" s="6" t="inlineStr">
-        <is>
-          <t>A1-C1</t>
-        </is>
-      </c>
-      <c r="C136" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D136" s="6" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="E136" s="6" t="inlineStr">
-        <is>
-          <t>20/07/2026</t>
-        </is>
-      </c>
-      <c r="F136" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G136" s="6" t="inlineStr"/>
-      <c r="H136" s="6" t="inlineStr">
-        <is>
-          <t>0/34</t>
-        </is>
-      </c>
-      <c r="I136" s="6" t="inlineStr">
+      <c r="I136" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -8500,172 +8520,176 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B160" s="5" t="inlineStr">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
         <is>
           <t>A1-C2</t>
         </is>
       </c>
-      <c r="C160" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D160" s="5" t="inlineStr">
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="E160" s="5" t="inlineStr">
+      <c r="E160" s="2" t="inlineStr">
         <is>
           <t>13/07/2026</t>
         </is>
       </c>
-      <c r="F160" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G160" s="5" t="inlineStr"/>
-      <c r="H160" s="5" t="inlineStr">
+      <c r="F160" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G160" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H160" s="2" t="inlineStr">
+        <is>
+          <t>14/33</t>
+        </is>
+      </c>
+      <c r="I160" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B161" s="5" t="inlineStr">
+        <is>
+          <t>A1-C2</t>
+        </is>
+      </c>
+      <c r="C161" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D161" s="5" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E161" s="5" t="inlineStr">
+        <is>
+          <t>18/07/2026</t>
+        </is>
+      </c>
+      <c r="F161" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G161" s="5" t="inlineStr"/>
+      <c r="H161" s="5" t="inlineStr">
         <is>
           <t>0/33</t>
         </is>
       </c>
-      <c r="I160" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B161" s="6" t="inlineStr">
+      <c r="I161" s="5" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B162" s="5" t="inlineStr">
         <is>
           <t>A1-C2</t>
         </is>
       </c>
-      <c r="C161" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D161" s="6" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="E161" s="6" t="inlineStr">
-        <is>
-          <t>18/07/2026</t>
-        </is>
-      </c>
-      <c r="F161" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G161" s="6" t="inlineStr"/>
-      <c r="H161" s="6" t="inlineStr">
+      <c r="C162" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D162" s="5" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="E162" s="5" t="inlineStr">
+        <is>
+          <t>19/07/2026</t>
+        </is>
+      </c>
+      <c r="F162" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G162" s="5" t="inlineStr"/>
+      <c r="H162" s="5" t="inlineStr">
         <is>
           <t>0/33</t>
         </is>
       </c>
-      <c r="I161" s="6" t="inlineStr">
+      <c r="I162" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="162">
-      <c r="A162" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B162" s="6" t="inlineStr">
+    <row r="163">
+      <c r="A163" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B163" s="5" t="inlineStr">
         <is>
           <t>A1-C2</t>
         </is>
       </c>
-      <c r="C162" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D162" s="6" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="E162" s="6" t="inlineStr">
-        <is>
-          <t>19/07/2026</t>
-        </is>
-      </c>
-      <c r="F162" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G162" s="6" t="inlineStr"/>
-      <c r="H162" s="6" t="inlineStr">
+      <c r="C163" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D163" s="5" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E163" s="5" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="F163" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G163" s="5" t="inlineStr"/>
+      <c r="H163" s="5" t="inlineStr">
         <is>
           <t>0/33</t>
         </is>
       </c>
-      <c r="I162" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B163" s="6" t="inlineStr">
-        <is>
-          <t>A1-C2</t>
-        </is>
-      </c>
-      <c r="C163" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D163" s="6" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="E163" s="6" t="inlineStr">
-        <is>
-          <t>20/07/2026</t>
-        </is>
-      </c>
-      <c r="F163" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G163" s="6" t="inlineStr"/>
-      <c r="H163" s="6" t="inlineStr">
-        <is>
-          <t>0/33</t>
-        </is>
-      </c>
-      <c r="I163" s="6" t="inlineStr">
+      <c r="I163" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -8907,43 +8931,43 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B169" s="5" t="inlineStr">
+      <c r="A169" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B169" s="9" t="inlineStr">
         <is>
           <t>A1-D1</t>
         </is>
       </c>
-      <c r="C169" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D169" s="5" t="inlineStr">
+      <c r="C169" s="9" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D169" s="9" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E169" s="5" t="inlineStr">
+      <c r="E169" s="9" t="inlineStr">
         <is>
           <t>04/06/2026</t>
         </is>
       </c>
-      <c r="F169" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G169" s="5" t="inlineStr"/>
-      <c r="H169" s="5" t="inlineStr">
+      <c r="F169" s="9" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G169" s="9" t="inlineStr"/>
+      <c r="H169" s="9" t="inlineStr">
         <is>
           <t>0/35</t>
         </is>
       </c>
-      <c r="I169" s="5" t="inlineStr">
+      <c r="I169" s="9" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
@@ -9561,43 +9585,43 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B183" s="5" t="inlineStr">
+      <c r="A183" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B183" s="9" t="inlineStr">
         <is>
           <t>A1-D1</t>
         </is>
       </c>
-      <c r="C183" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D183" s="5" t="inlineStr">
+      <c r="C183" s="9" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D183" s="9" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="E183" s="5" t="inlineStr">
+      <c r="E183" s="9" t="inlineStr">
         <is>
           <t>08/07/2026</t>
         </is>
       </c>
-      <c r="F183" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G183" s="5" t="inlineStr"/>
-      <c r="H183" s="5" t="inlineStr">
+      <c r="F183" s="9" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G183" s="9" t="inlineStr"/>
+      <c r="H183" s="9" t="inlineStr">
         <is>
           <t>0/35</t>
         </is>
       </c>
-      <c r="I183" s="5" t="inlineStr">
+      <c r="I183" s="9" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
@@ -9651,258 +9675,258 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B185" s="6" t="inlineStr">
+      <c r="A185" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B185" s="5" t="inlineStr">
         <is>
           <t>A1-D1</t>
         </is>
       </c>
-      <c r="C185" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D185" s="6" t="inlineStr">
+      <c r="C185" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D185" s="5" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="E185" s="6" t="inlineStr">
+      <c r="E185" s="5" t="inlineStr">
         <is>
           <t>14/07/2026</t>
         </is>
       </c>
-      <c r="F185" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G185" s="6" t="inlineStr"/>
-      <c r="H185" s="6" t="inlineStr">
+      <c r="F185" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G185" s="5" t="inlineStr"/>
+      <c r="H185" s="5" t="inlineStr">
         <is>
           <t>0/35</t>
         </is>
       </c>
-      <c r="I185" s="6" t="inlineStr">
+      <c r="I185" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B186" s="6" t="inlineStr">
+      <c r="A186" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B186" s="5" t="inlineStr">
         <is>
           <t>A1-D1</t>
         </is>
       </c>
-      <c r="C186" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D186" s="6" t="inlineStr">
+      <c r="C186" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D186" s="5" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="E186" s="6" t="inlineStr">
+      <c r="E186" s="5" t="inlineStr">
         <is>
           <t>15/07/2026</t>
         </is>
       </c>
-      <c r="F186" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G186" s="6" t="inlineStr"/>
-      <c r="H186" s="6" t="inlineStr">
+      <c r="F186" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G186" s="5" t="inlineStr"/>
+      <c r="H186" s="5" t="inlineStr">
         <is>
           <t>0/35</t>
         </is>
       </c>
-      <c r="I186" s="6" t="inlineStr">
+      <c r="I186" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B187" s="6" t="inlineStr">
+      <c r="A187" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B187" s="5" t="inlineStr">
         <is>
           <t>A1-D1</t>
         </is>
       </c>
-      <c r="C187" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D187" s="6" t="inlineStr">
+      <c r="C187" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D187" s="5" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="E187" s="6" t="inlineStr">
+      <c r="E187" s="5" t="inlineStr">
         <is>
           <t>16/07/2026</t>
         </is>
       </c>
-      <c r="F187" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G187" s="6" t="inlineStr"/>
-      <c r="H187" s="6" t="inlineStr">
+      <c r="F187" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G187" s="5" t="inlineStr"/>
+      <c r="H187" s="5" t="inlineStr">
         <is>
           <t>0/35</t>
         </is>
       </c>
-      <c r="I187" s="6" t="inlineStr">
+      <c r="I187" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B188" s="6" t="inlineStr">
+      <c r="A188" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B188" s="5" t="inlineStr">
         <is>
           <t>A1-D1</t>
         </is>
       </c>
-      <c r="C188" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D188" s="6" t="inlineStr">
+      <c r="C188" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D188" s="5" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="E188" s="6" t="inlineStr">
+      <c r="E188" s="5" t="inlineStr">
         <is>
           <t>21/07/2026</t>
         </is>
       </c>
-      <c r="F188" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G188" s="6" t="inlineStr"/>
-      <c r="H188" s="6" t="inlineStr">
+      <c r="F188" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G188" s="5" t="inlineStr"/>
+      <c r="H188" s="5" t="inlineStr">
         <is>
           <t>0/35</t>
         </is>
       </c>
-      <c r="I188" s="6" t="inlineStr">
+      <c r="I188" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B189" s="6" t="inlineStr">
+      <c r="A189" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B189" s="5" t="inlineStr">
         <is>
           <t>A1-D1</t>
         </is>
       </c>
-      <c r="C189" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D189" s="6" t="inlineStr">
+      <c r="C189" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D189" s="5" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="E189" s="6" t="inlineStr">
+      <c r="E189" s="5" t="inlineStr">
         <is>
           <t>22/07/2026</t>
         </is>
       </c>
-      <c r="F189" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G189" s="6" t="inlineStr"/>
-      <c r="H189" s="6" t="inlineStr">
+      <c r="F189" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G189" s="5" t="inlineStr"/>
+      <c r="H189" s="5" t="inlineStr">
         <is>
           <t>0/35</t>
         </is>
       </c>
-      <c r="I189" s="6" t="inlineStr">
+      <c r="I189" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B190" s="6" t="inlineStr">
+      <c r="A190" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B190" s="5" t="inlineStr">
         <is>
           <t>A1-D1</t>
         </is>
       </c>
-      <c r="C190" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D190" s="6" t="inlineStr">
+      <c r="C190" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D190" s="5" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="E190" s="6" t="inlineStr">
+      <c r="E190" s="5" t="inlineStr">
         <is>
           <t>23/07/2026</t>
         </is>
       </c>
-      <c r="F190" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G190" s="6" t="inlineStr"/>
-      <c r="H190" s="6" t="inlineStr">
+      <c r="F190" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G190" s="5" t="inlineStr"/>
+      <c r="H190" s="5" t="inlineStr">
         <is>
           <t>0/35</t>
         </is>
       </c>
-      <c r="I190" s="6" t="inlineStr">
+      <c r="I190" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -10144,43 +10168,43 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B196" s="5" t="inlineStr">
+      <c r="A196" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B196" s="9" t="inlineStr">
         <is>
           <t>A1-D2</t>
         </is>
       </c>
-      <c r="C196" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D196" s="5" t="inlineStr">
+      <c r="C196" s="9" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D196" s="9" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E196" s="5" t="inlineStr">
+      <c r="E196" s="9" t="inlineStr">
         <is>
           <t>04/06/2026</t>
         </is>
       </c>
-      <c r="F196" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G196" s="5" t="inlineStr"/>
-      <c r="H196" s="5" t="inlineStr">
+      <c r="F196" s="9" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G196" s="9" t="inlineStr"/>
+      <c r="H196" s="9" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I196" s="5" t="inlineStr">
+      <c r="I196" s="9" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
@@ -10798,43 +10822,43 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B210" s="5" t="inlineStr">
+      <c r="A210" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B210" s="9" t="inlineStr">
         <is>
           <t>A1-D2</t>
         </is>
       </c>
-      <c r="C210" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D210" s="5" t="inlineStr">
+      <c r="C210" s="9" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D210" s="9" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="E210" s="5" t="inlineStr">
+      <c r="E210" s="9" t="inlineStr">
         <is>
           <t>08/07/2026</t>
         </is>
       </c>
-      <c r="F210" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G210" s="5" t="inlineStr"/>
-      <c r="H210" s="5" t="inlineStr">
+      <c r="F210" s="9" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G210" s="9" t="inlineStr"/>
+      <c r="H210" s="9" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I210" s="5" t="inlineStr">
+      <c r="I210" s="9" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
@@ -10888,258 +10912,258 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B212" s="6" t="inlineStr">
+      <c r="A212" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B212" s="5" t="inlineStr">
         <is>
           <t>A1-D2</t>
         </is>
       </c>
-      <c r="C212" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D212" s="6" t="inlineStr">
+      <c r="C212" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D212" s="5" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="E212" s="6" t="inlineStr">
+      <c r="E212" s="5" t="inlineStr">
         <is>
           <t>14/07/2026</t>
         </is>
       </c>
-      <c r="F212" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G212" s="6" t="inlineStr"/>
-      <c r="H212" s="6" t="inlineStr">
+      <c r="F212" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G212" s="5" t="inlineStr"/>
+      <c r="H212" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I212" s="6" t="inlineStr">
+      <c r="I212" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B213" s="6" t="inlineStr">
+      <c r="A213" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B213" s="5" t="inlineStr">
         <is>
           <t>A1-D2</t>
         </is>
       </c>
-      <c r="C213" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D213" s="6" t="inlineStr">
+      <c r="C213" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D213" s="5" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="E213" s="6" t="inlineStr">
+      <c r="E213" s="5" t="inlineStr">
         <is>
           <t>15/07/2026</t>
         </is>
       </c>
-      <c r="F213" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G213" s="6" t="inlineStr"/>
-      <c r="H213" s="6" t="inlineStr">
+      <c r="F213" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G213" s="5" t="inlineStr"/>
+      <c r="H213" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I213" s="6" t="inlineStr">
+      <c r="I213" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B214" s="6" t="inlineStr">
+      <c r="A214" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B214" s="5" t="inlineStr">
         <is>
           <t>A1-D2</t>
         </is>
       </c>
-      <c r="C214" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D214" s="6" t="inlineStr">
+      <c r="C214" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D214" s="5" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="E214" s="6" t="inlineStr">
+      <c r="E214" s="5" t="inlineStr">
         <is>
           <t>16/07/2026</t>
         </is>
       </c>
-      <c r="F214" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G214" s="6" t="inlineStr"/>
-      <c r="H214" s="6" t="inlineStr">
+      <c r="F214" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G214" s="5" t="inlineStr"/>
+      <c r="H214" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I214" s="6" t="inlineStr">
+      <c r="I214" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B215" s="6" t="inlineStr">
+      <c r="A215" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B215" s="5" t="inlineStr">
         <is>
           <t>A1-D2</t>
         </is>
       </c>
-      <c r="C215" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D215" s="6" t="inlineStr">
+      <c r="C215" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D215" s="5" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="E215" s="6" t="inlineStr">
+      <c r="E215" s="5" t="inlineStr">
         <is>
           <t>21/07/2026</t>
         </is>
       </c>
-      <c r="F215" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G215" s="6" t="inlineStr"/>
-      <c r="H215" s="6" t="inlineStr">
+      <c r="F215" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G215" s="5" t="inlineStr"/>
+      <c r="H215" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I215" s="6" t="inlineStr">
+      <c r="I215" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B216" s="6" t="inlineStr">
+      <c r="A216" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B216" s="5" t="inlineStr">
         <is>
           <t>A1-D2</t>
         </is>
       </c>
-      <c r="C216" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D216" s="6" t="inlineStr">
+      <c r="C216" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D216" s="5" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="E216" s="6" t="inlineStr">
+      <c r="E216" s="5" t="inlineStr">
         <is>
           <t>22/07/2026</t>
         </is>
       </c>
-      <c r="F216" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G216" s="6" t="inlineStr"/>
-      <c r="H216" s="6" t="inlineStr">
+      <c r="F216" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G216" s="5" t="inlineStr"/>
+      <c r="H216" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I216" s="6" t="inlineStr">
+      <c r="I216" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B217" s="6" t="inlineStr">
+      <c r="A217" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B217" s="5" t="inlineStr">
         <is>
           <t>A1-D2</t>
         </is>
       </c>
-      <c r="C217" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D217" s="6" t="inlineStr">
+      <c r="C217" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D217" s="5" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="E217" s="6" t="inlineStr">
+      <c r="E217" s="5" t="inlineStr">
         <is>
           <t>23/07/2026</t>
         </is>
       </c>
-      <c r="F217" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G217" s="6" t="inlineStr"/>
-      <c r="H217" s="6" t="inlineStr">
+      <c r="F217" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G217" s="5" t="inlineStr"/>
+      <c r="H217" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I217" s="6" t="inlineStr">
+      <c r="I217" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -11381,43 +11405,43 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B223" s="5" t="inlineStr">
+      <c r="A223" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B223" s="9" t="inlineStr">
         <is>
           <t>A1-E1</t>
         </is>
       </c>
-      <c r="C223" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D223" s="5" t="inlineStr">
+      <c r="C223" s="9" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D223" s="9" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E223" s="5" t="inlineStr">
+      <c r="E223" s="9" t="inlineStr">
         <is>
           <t>04/06/2026</t>
         </is>
       </c>
-      <c r="F223" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G223" s="5" t="inlineStr"/>
-      <c r="H223" s="5" t="inlineStr">
+      <c r="F223" s="9" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G223" s="9" t="inlineStr"/>
+      <c r="H223" s="9" t="inlineStr">
         <is>
           <t>0/38</t>
         </is>
       </c>
-      <c r="I223" s="5" t="inlineStr">
+      <c r="I223" s="9" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
@@ -12082,301 +12106,301 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B238" s="5" t="inlineStr">
+      <c r="A238" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B238" s="9" t="inlineStr">
         <is>
           <t>A1-E1</t>
         </is>
       </c>
-      <c r="C238" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D238" s="5" t="inlineStr">
+      <c r="C238" s="9" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D238" s="9" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="E238" s="5" t="inlineStr">
+      <c r="E238" s="9" t="inlineStr">
         <is>
           <t>09/07/2026</t>
         </is>
       </c>
-      <c r="F238" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G238" s="5" t="inlineStr"/>
-      <c r="H238" s="5" t="inlineStr">
+      <c r="F238" s="9" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G238" s="9" t="inlineStr"/>
+      <c r="H238" s="9" t="inlineStr">
         <is>
           <t>0/38</t>
         </is>
       </c>
-      <c r="I238" s="5" t="inlineStr">
+      <c r="I238" s="9" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B239" s="6" t="inlineStr">
+      <c r="A239" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B239" s="5" t="inlineStr">
         <is>
           <t>A1-E1</t>
         </is>
       </c>
-      <c r="C239" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D239" s="6" t="inlineStr">
+      <c r="C239" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D239" s="5" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="E239" s="6" t="inlineStr">
+      <c r="E239" s="5" t="inlineStr">
         <is>
           <t>14/07/2026</t>
         </is>
       </c>
-      <c r="F239" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G239" s="6" t="inlineStr"/>
-      <c r="H239" s="6" t="inlineStr">
+      <c r="F239" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G239" s="5" t="inlineStr"/>
+      <c r="H239" s="5" t="inlineStr">
         <is>
           <t>0/38</t>
         </is>
       </c>
-      <c r="I239" s="6" t="inlineStr">
+      <c r="I239" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B240" s="6" t="inlineStr">
+      <c r="A240" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B240" s="5" t="inlineStr">
         <is>
           <t>A1-E1</t>
         </is>
       </c>
-      <c r="C240" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D240" s="6" t="inlineStr">
+      <c r="C240" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D240" s="5" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="E240" s="6" t="inlineStr">
+      <c r="E240" s="5" t="inlineStr">
         <is>
           <t>15/07/2026</t>
         </is>
       </c>
-      <c r="F240" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G240" s="6" t="inlineStr"/>
-      <c r="H240" s="6" t="inlineStr">
+      <c r="F240" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G240" s="5" t="inlineStr"/>
+      <c r="H240" s="5" t="inlineStr">
         <is>
           <t>0/38</t>
         </is>
       </c>
-      <c r="I240" s="6" t="inlineStr">
+      <c r="I240" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B241" s="6" t="inlineStr">
+      <c r="A241" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B241" s="5" t="inlineStr">
         <is>
           <t>A1-E1</t>
         </is>
       </c>
-      <c r="C241" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D241" s="6" t="inlineStr">
+      <c r="C241" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D241" s="5" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="E241" s="6" t="inlineStr">
+      <c r="E241" s="5" t="inlineStr">
         <is>
           <t>16/07/2026</t>
         </is>
       </c>
-      <c r="F241" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G241" s="6" t="inlineStr"/>
-      <c r="H241" s="6" t="inlineStr">
+      <c r="F241" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G241" s="5" t="inlineStr"/>
+      <c r="H241" s="5" t="inlineStr">
         <is>
           <t>0/38</t>
         </is>
       </c>
-      <c r="I241" s="6" t="inlineStr">
+      <c r="I241" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B242" s="6" t="inlineStr">
+      <c r="A242" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B242" s="5" t="inlineStr">
         <is>
           <t>A1-E1</t>
         </is>
       </c>
-      <c r="C242" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D242" s="6" t="inlineStr">
+      <c r="C242" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D242" s="5" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="E242" s="6" t="inlineStr">
+      <c r="E242" s="5" t="inlineStr">
         <is>
           <t>21/07/2026</t>
         </is>
       </c>
-      <c r="F242" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G242" s="6" t="inlineStr"/>
-      <c r="H242" s="6" t="inlineStr">
+      <c r="F242" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G242" s="5" t="inlineStr"/>
+      <c r="H242" s="5" t="inlineStr">
         <is>
           <t>0/38</t>
         </is>
       </c>
-      <c r="I242" s="6" t="inlineStr">
+      <c r="I242" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B243" s="6" t="inlineStr">
+      <c r="A243" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B243" s="5" t="inlineStr">
         <is>
           <t>A1-E1</t>
         </is>
       </c>
-      <c r="C243" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D243" s="6" t="inlineStr">
+      <c r="C243" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D243" s="5" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="E243" s="6" t="inlineStr">
+      <c r="E243" s="5" t="inlineStr">
         <is>
           <t>22/07/2026</t>
         </is>
       </c>
-      <c r="F243" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G243" s="6" t="inlineStr"/>
-      <c r="H243" s="6" t="inlineStr">
+      <c r="F243" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G243" s="5" t="inlineStr"/>
+      <c r="H243" s="5" t="inlineStr">
         <is>
           <t>0/38</t>
         </is>
       </c>
-      <c r="I243" s="6" t="inlineStr">
+      <c r="I243" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B244" s="6" t="inlineStr">
+      <c r="A244" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B244" s="5" t="inlineStr">
         <is>
           <t>A1-E1</t>
         </is>
       </c>
-      <c r="C244" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D244" s="6" t="inlineStr">
+      <c r="C244" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D244" s="5" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="E244" s="6" t="inlineStr">
+      <c r="E244" s="5" t="inlineStr">
         <is>
           <t>23/07/2026</t>
         </is>
       </c>
-      <c r="F244" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G244" s="6" t="inlineStr"/>
-      <c r="H244" s="6" t="inlineStr">
+      <c r="F244" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G244" s="5" t="inlineStr"/>
+      <c r="H244" s="5" t="inlineStr">
         <is>
           <t>0/38</t>
         </is>
       </c>
-      <c r="I244" s="6" t="inlineStr">
+      <c r="I244" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -12618,43 +12642,43 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B250" s="5" t="inlineStr">
+      <c r="A250" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B250" s="9" t="inlineStr">
         <is>
           <t>A1-E2</t>
         </is>
       </c>
-      <c r="C250" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D250" s="5" t="inlineStr">
+      <c r="C250" s="9" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D250" s="9" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E250" s="5" t="inlineStr">
+      <c r="E250" s="9" t="inlineStr">
         <is>
           <t>04/06/2026</t>
         </is>
       </c>
-      <c r="F250" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G250" s="5" t="inlineStr"/>
-      <c r="H250" s="5" t="inlineStr">
+      <c r="F250" s="9" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G250" s="9" t="inlineStr"/>
+      <c r="H250" s="9" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I250" s="5" t="inlineStr">
+      <c r="I250" s="9" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
@@ -13319,301 +13343,301 @@
       </c>
     </row>
     <row r="265">
-      <c r="A265" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B265" s="5" t="inlineStr">
+      <c r="A265" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B265" s="9" t="inlineStr">
         <is>
           <t>A1-E2</t>
         </is>
       </c>
-      <c r="C265" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D265" s="5" t="inlineStr">
+      <c r="C265" s="9" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D265" s="9" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="E265" s="5" t="inlineStr">
+      <c r="E265" s="9" t="inlineStr">
         <is>
           <t>09/07/2026</t>
         </is>
       </c>
-      <c r="F265" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G265" s="5" t="inlineStr"/>
-      <c r="H265" s="5" t="inlineStr">
+      <c r="F265" s="9" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G265" s="9" t="inlineStr"/>
+      <c r="H265" s="9" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I265" s="5" t="inlineStr">
+      <c r="I265" s="9" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
       </c>
     </row>
     <row r="266">
-      <c r="A266" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B266" s="6" t="inlineStr">
+      <c r="A266" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B266" s="5" t="inlineStr">
         <is>
           <t>A1-E2</t>
         </is>
       </c>
-      <c r="C266" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D266" s="6" t="inlineStr">
+      <c r="C266" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D266" s="5" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="E266" s="6" t="inlineStr">
+      <c r="E266" s="5" t="inlineStr">
         <is>
           <t>14/07/2026</t>
         </is>
       </c>
-      <c r="F266" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G266" s="6" t="inlineStr"/>
-      <c r="H266" s="6" t="inlineStr">
+      <c r="F266" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G266" s="5" t="inlineStr"/>
+      <c r="H266" s="5" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I266" s="6" t="inlineStr">
+      <c r="I266" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="267">
-      <c r="A267" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B267" s="6" t="inlineStr">
+      <c r="A267" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B267" s="5" t="inlineStr">
         <is>
           <t>A1-E2</t>
         </is>
       </c>
-      <c r="C267" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D267" s="6" t="inlineStr">
+      <c r="C267" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D267" s="5" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="E267" s="6" t="inlineStr">
+      <c r="E267" s="5" t="inlineStr">
         <is>
           <t>15/07/2026</t>
         </is>
       </c>
-      <c r="F267" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G267" s="6" t="inlineStr"/>
-      <c r="H267" s="6" t="inlineStr">
+      <c r="F267" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G267" s="5" t="inlineStr"/>
+      <c r="H267" s="5" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I267" s="6" t="inlineStr">
+      <c r="I267" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="268">
-      <c r="A268" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B268" s="6" t="inlineStr">
+      <c r="A268" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B268" s="5" t="inlineStr">
         <is>
           <t>A1-E2</t>
         </is>
       </c>
-      <c r="C268" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D268" s="6" t="inlineStr">
+      <c r="C268" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D268" s="5" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="E268" s="6" t="inlineStr">
+      <c r="E268" s="5" t="inlineStr">
         <is>
           <t>16/07/2026</t>
         </is>
       </c>
-      <c r="F268" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G268" s="6" t="inlineStr"/>
-      <c r="H268" s="6" t="inlineStr">
+      <c r="F268" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G268" s="5" t="inlineStr"/>
+      <c r="H268" s="5" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I268" s="6" t="inlineStr">
+      <c r="I268" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="269">
-      <c r="A269" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B269" s="6" t="inlineStr">
+      <c r="A269" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B269" s="5" t="inlineStr">
         <is>
           <t>A1-E2</t>
         </is>
       </c>
-      <c r="C269" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D269" s="6" t="inlineStr">
+      <c r="C269" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D269" s="5" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="E269" s="6" t="inlineStr">
+      <c r="E269" s="5" t="inlineStr">
         <is>
           <t>21/07/2026</t>
         </is>
       </c>
-      <c r="F269" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G269" s="6" t="inlineStr"/>
-      <c r="H269" s="6" t="inlineStr">
+      <c r="F269" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G269" s="5" t="inlineStr"/>
+      <c r="H269" s="5" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I269" s="6" t="inlineStr">
+      <c r="I269" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="270">
-      <c r="A270" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B270" s="6" t="inlineStr">
+      <c r="A270" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B270" s="5" t="inlineStr">
         <is>
           <t>A1-E2</t>
         </is>
       </c>
-      <c r="C270" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D270" s="6" t="inlineStr">
+      <c r="C270" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D270" s="5" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="E270" s="6" t="inlineStr">
+      <c r="E270" s="5" t="inlineStr">
         <is>
           <t>22/07/2026</t>
         </is>
       </c>
-      <c r="F270" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G270" s="6" t="inlineStr"/>
-      <c r="H270" s="6" t="inlineStr">
+      <c r="F270" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G270" s="5" t="inlineStr"/>
+      <c r="H270" s="5" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I270" s="6" t="inlineStr">
+      <c r="I270" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="271">
-      <c r="A271" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B271" s="6" t="inlineStr">
+      <c r="A271" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B271" s="5" t="inlineStr">
         <is>
           <t>A1-E2</t>
         </is>
       </c>
-      <c r="C271" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D271" s="6" t="inlineStr">
+      <c r="C271" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D271" s="5" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="E271" s="6" t="inlineStr">
+      <c r="E271" s="5" t="inlineStr">
         <is>
           <t>23/07/2026</t>
         </is>
       </c>
-      <c r="F271" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G271" s="6" t="inlineStr"/>
-      <c r="H271" s="6" t="inlineStr">
+      <c r="F271" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G271" s="5" t="inlineStr"/>
+      <c r="H271" s="5" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I271" s="6" t="inlineStr">
+      <c r="I271" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -13855,43 +13879,43 @@
       </c>
     </row>
     <row r="277">
-      <c r="A277" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B277" s="5" t="inlineStr">
+      <c r="A277" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B277" s="9" t="inlineStr">
         <is>
           <t>A1-F1</t>
         </is>
       </c>
-      <c r="C277" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D277" s="5" t="inlineStr">
+      <c r="C277" s="9" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D277" s="9" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E277" s="5" t="inlineStr">
+      <c r="E277" s="9" t="inlineStr">
         <is>
           <t>04/06/2026</t>
         </is>
       </c>
-      <c r="F277" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G277" s="5" t="inlineStr"/>
-      <c r="H277" s="5" t="inlineStr">
+      <c r="F277" s="9" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G277" s="9" t="inlineStr"/>
+      <c r="H277" s="9" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I277" s="5" t="inlineStr">
+      <c r="I277" s="9" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
@@ -14603,258 +14627,258 @@
       </c>
     </row>
     <row r="293">
-      <c r="A293" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B293" s="6" t="inlineStr">
+      <c r="A293" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B293" s="5" t="inlineStr">
         <is>
           <t>A1-F1</t>
         </is>
       </c>
-      <c r="C293" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D293" s="6" t="inlineStr">
+      <c r="C293" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D293" s="5" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="E293" s="6" t="inlineStr">
+      <c r="E293" s="5" t="inlineStr">
         <is>
           <t>14/07/2026</t>
         </is>
       </c>
-      <c r="F293" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G293" s="6" t="inlineStr"/>
-      <c r="H293" s="6" t="inlineStr">
+      <c r="F293" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G293" s="5" t="inlineStr"/>
+      <c r="H293" s="5" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I293" s="6" t="inlineStr">
+      <c r="I293" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="294">
-      <c r="A294" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B294" s="6" t="inlineStr">
+      <c r="A294" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B294" s="5" t="inlineStr">
         <is>
           <t>A1-F1</t>
         </is>
       </c>
-      <c r="C294" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D294" s="6" t="inlineStr">
+      <c r="C294" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D294" s="5" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="E294" s="6" t="inlineStr">
+      <c r="E294" s="5" t="inlineStr">
         <is>
           <t>15/07/2026</t>
         </is>
       </c>
-      <c r="F294" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G294" s="6" t="inlineStr"/>
-      <c r="H294" s="6" t="inlineStr">
+      <c r="F294" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G294" s="5" t="inlineStr"/>
+      <c r="H294" s="5" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I294" s="6" t="inlineStr">
+      <c r="I294" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="295">
-      <c r="A295" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B295" s="6" t="inlineStr">
+      <c r="A295" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B295" s="5" t="inlineStr">
         <is>
           <t>A1-F1</t>
         </is>
       </c>
-      <c r="C295" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D295" s="6" t="inlineStr">
+      <c r="C295" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D295" s="5" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="E295" s="6" t="inlineStr">
+      <c r="E295" s="5" t="inlineStr">
         <is>
           <t>16/07/2026</t>
         </is>
       </c>
-      <c r="F295" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G295" s="6" t="inlineStr"/>
-      <c r="H295" s="6" t="inlineStr">
+      <c r="F295" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G295" s="5" t="inlineStr"/>
+      <c r="H295" s="5" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I295" s="6" t="inlineStr">
+      <c r="I295" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="296">
-      <c r="A296" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B296" s="6" t="inlineStr">
+      <c r="A296" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B296" s="5" t="inlineStr">
         <is>
           <t>A1-F1</t>
         </is>
       </c>
-      <c r="C296" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D296" s="6" t="inlineStr">
+      <c r="C296" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D296" s="5" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="E296" s="6" t="inlineStr">
+      <c r="E296" s="5" t="inlineStr">
         <is>
           <t>21/07/2026</t>
         </is>
       </c>
-      <c r="F296" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G296" s="6" t="inlineStr"/>
-      <c r="H296" s="6" t="inlineStr">
+      <c r="F296" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G296" s="5" t="inlineStr"/>
+      <c r="H296" s="5" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I296" s="6" t="inlineStr">
+      <c r="I296" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="297">
-      <c r="A297" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B297" s="6" t="inlineStr">
+      <c r="A297" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B297" s="5" t="inlineStr">
         <is>
           <t>A1-F1</t>
         </is>
       </c>
-      <c r="C297" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D297" s="6" t="inlineStr">
+      <c r="C297" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D297" s="5" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="E297" s="6" t="inlineStr">
+      <c r="E297" s="5" t="inlineStr">
         <is>
           <t>22/07/2026</t>
         </is>
       </c>
-      <c r="F297" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G297" s="6" t="inlineStr"/>
-      <c r="H297" s="6" t="inlineStr">
+      <c r="F297" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G297" s="5" t="inlineStr"/>
+      <c r="H297" s="5" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I297" s="6" t="inlineStr">
+      <c r="I297" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="298">
-      <c r="A298" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B298" s="6" t="inlineStr">
+      <c r="A298" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B298" s="5" t="inlineStr">
         <is>
           <t>A1-F1</t>
         </is>
       </c>
-      <c r="C298" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D298" s="6" t="inlineStr">
+      <c r="C298" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D298" s="5" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="E298" s="6" t="inlineStr">
+      <c r="E298" s="5" t="inlineStr">
         <is>
           <t>23/07/2026</t>
         </is>
       </c>
-      <c r="F298" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G298" s="6" t="inlineStr"/>
-      <c r="H298" s="6" t="inlineStr">
+      <c r="F298" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G298" s="5" t="inlineStr"/>
+      <c r="H298" s="5" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I298" s="6" t="inlineStr">
+      <c r="I298" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -15096,43 +15120,43 @@
       </c>
     </row>
     <row r="304">
-      <c r="A304" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B304" s="5" t="inlineStr">
+      <c r="A304" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B304" s="9" t="inlineStr">
         <is>
           <t>A1-F2</t>
         </is>
       </c>
-      <c r="C304" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D304" s="5" t="inlineStr">
+      <c r="C304" s="9" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D304" s="9" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E304" s="5" t="inlineStr">
+      <c r="E304" s="9" t="inlineStr">
         <is>
           <t>04/06/2026</t>
         </is>
       </c>
-      <c r="F304" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G304" s="5" t="inlineStr"/>
-      <c r="H304" s="5" t="inlineStr">
+      <c r="F304" s="9" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G304" s="9" t="inlineStr"/>
+      <c r="H304" s="9" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I304" s="5" t="inlineStr">
+      <c r="I304" s="9" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
@@ -15703,43 +15727,43 @@
       </c>
     </row>
     <row r="317">
-      <c r="A317" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B317" s="5" t="inlineStr">
+      <c r="A317" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B317" s="9" t="inlineStr">
         <is>
           <t>A1-F2</t>
         </is>
       </c>
-      <c r="C317" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D317" s="5" t="inlineStr">
+      <c r="C317" s="9" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D317" s="9" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="E317" s="5" t="inlineStr">
+      <c r="E317" s="9" t="inlineStr">
         <is>
           <t>07/07/2026</t>
         </is>
       </c>
-      <c r="F317" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G317" s="5" t="inlineStr"/>
-      <c r="H317" s="5" t="inlineStr">
+      <c r="F317" s="9" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G317" s="9" t="inlineStr"/>
+      <c r="H317" s="9" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I317" s="5" t="inlineStr">
+      <c r="I317" s="9" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
@@ -15840,258 +15864,258 @@
       </c>
     </row>
     <row r="320">
-      <c r="A320" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B320" s="6" t="inlineStr">
+      <c r="A320" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B320" s="5" t="inlineStr">
         <is>
           <t>A1-F2</t>
         </is>
       </c>
-      <c r="C320" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D320" s="6" t="inlineStr">
+      <c r="C320" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D320" s="5" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="E320" s="6" t="inlineStr">
+      <c r="E320" s="5" t="inlineStr">
         <is>
           <t>14/07/2026</t>
         </is>
       </c>
-      <c r="F320" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G320" s="6" t="inlineStr"/>
-      <c r="H320" s="6" t="inlineStr">
+      <c r="F320" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G320" s="5" t="inlineStr"/>
+      <c r="H320" s="5" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I320" s="6" t="inlineStr">
+      <c r="I320" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="321">
-      <c r="A321" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B321" s="6" t="inlineStr">
+      <c r="A321" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B321" s="5" t="inlineStr">
         <is>
           <t>A1-F2</t>
         </is>
       </c>
-      <c r="C321" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D321" s="6" t="inlineStr">
+      <c r="C321" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D321" s="5" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="E321" s="6" t="inlineStr">
+      <c r="E321" s="5" t="inlineStr">
         <is>
           <t>15/07/2026</t>
         </is>
       </c>
-      <c r="F321" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G321" s="6" t="inlineStr"/>
-      <c r="H321" s="6" t="inlineStr">
+      <c r="F321" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G321" s="5" t="inlineStr"/>
+      <c r="H321" s="5" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I321" s="6" t="inlineStr">
+      <c r="I321" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="322">
-      <c r="A322" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B322" s="6" t="inlineStr">
+      <c r="A322" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B322" s="5" t="inlineStr">
         <is>
           <t>A1-F2</t>
         </is>
       </c>
-      <c r="C322" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D322" s="6" t="inlineStr">
+      <c r="C322" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D322" s="5" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="E322" s="6" t="inlineStr">
+      <c r="E322" s="5" t="inlineStr">
         <is>
           <t>16/07/2026</t>
         </is>
       </c>
-      <c r="F322" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G322" s="6" t="inlineStr"/>
-      <c r="H322" s="6" t="inlineStr">
+      <c r="F322" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G322" s="5" t="inlineStr"/>
+      <c r="H322" s="5" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I322" s="6" t="inlineStr">
+      <c r="I322" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="323">
-      <c r="A323" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B323" s="6" t="inlineStr">
+      <c r="A323" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B323" s="5" t="inlineStr">
         <is>
           <t>A1-F2</t>
         </is>
       </c>
-      <c r="C323" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D323" s="6" t="inlineStr">
+      <c r="C323" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D323" s="5" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="E323" s="6" t="inlineStr">
+      <c r="E323" s="5" t="inlineStr">
         <is>
           <t>21/07/2026</t>
         </is>
       </c>
-      <c r="F323" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G323" s="6" t="inlineStr"/>
-      <c r="H323" s="6" t="inlineStr">
+      <c r="F323" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G323" s="5" t="inlineStr"/>
+      <c r="H323" s="5" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I323" s="6" t="inlineStr">
+      <c r="I323" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="324">
-      <c r="A324" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B324" s="6" t="inlineStr">
+      <c r="A324" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B324" s="5" t="inlineStr">
         <is>
           <t>A1-F2</t>
         </is>
       </c>
-      <c r="C324" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D324" s="6" t="inlineStr">
+      <c r="C324" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D324" s="5" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="E324" s="6" t="inlineStr">
+      <c r="E324" s="5" t="inlineStr">
         <is>
           <t>22/07/2026</t>
         </is>
       </c>
-      <c r="F324" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G324" s="6" t="inlineStr"/>
-      <c r="H324" s="6" t="inlineStr">
+      <c r="F324" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G324" s="5" t="inlineStr"/>
+      <c r="H324" s="5" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I324" s="6" t="inlineStr">
+      <c r="I324" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="325">
-      <c r="A325" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B325" s="6" t="inlineStr">
+      <c r="A325" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B325" s="5" t="inlineStr">
         <is>
           <t>A1-F2</t>
         </is>
       </c>
-      <c r="C325" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D325" s="6" t="inlineStr">
+      <c r="C325" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D325" s="5" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="E325" s="6" t="inlineStr">
+      <c r="E325" s="5" t="inlineStr">
         <is>
           <t>23/07/2026</t>
         </is>
       </c>
-      <c r="F325" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G325" s="6" t="inlineStr"/>
-      <c r="H325" s="6" t="inlineStr">
+      <c r="F325" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G325" s="5" t="inlineStr"/>
+      <c r="H325" s="5" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I325" s="6" t="inlineStr">
+      <c r="I325" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A1_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A1_session_analysis.xlsx
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8">
@@ -924,7 +924,7 @@
         </is>
       </c>
       <c r="L8" s="4" t="n">
-        <v>54</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9">
@@ -1837,10 +1837,10 @@
         <v>19</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R21" s="4" t="inlineStr">
         <is>
@@ -1919,10 +1919,10 @@
         <v>19</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R22" s="4" t="inlineStr">
         <is>
@@ -2001,10 +2001,10 @@
         <v>19</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R23" s="4" t="inlineStr">
         <is>
@@ -2083,10 +2083,10 @@
         <v>19</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R24" s="4" t="inlineStr">
         <is>
@@ -2165,10 +2165,10 @@
         <v>20</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R25" s="4" t="inlineStr">
         <is>
@@ -2243,10 +2243,10 @@
         <v>19</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R26" s="4" t="inlineStr">
         <is>
@@ -9675,45 +9675,45 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B185" s="5" t="inlineStr">
+      <c r="A185" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B185" s="9" t="inlineStr">
         <is>
           <t>A1-D1</t>
         </is>
       </c>
-      <c r="C185" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D185" s="5" t="inlineStr">
+      <c r="C185" s="9" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D185" s="9" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="E185" s="5" t="inlineStr">
+      <c r="E185" s="9" t="inlineStr">
         <is>
           <t>14/07/2026</t>
         </is>
       </c>
-      <c r="F185" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G185" s="5" t="inlineStr"/>
-      <c r="H185" s="5" t="inlineStr">
+      <c r="F185" s="9" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G185" s="9" t="inlineStr"/>
+      <c r="H185" s="9" t="inlineStr">
         <is>
           <t>0/35</t>
         </is>
       </c>
-      <c r="I185" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I185" s="9" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -10912,45 +10912,45 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B212" s="5" t="inlineStr">
+      <c r="A212" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B212" s="9" t="inlineStr">
         <is>
           <t>A1-D2</t>
         </is>
       </c>
-      <c r="C212" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D212" s="5" t="inlineStr">
+      <c r="C212" s="9" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D212" s="9" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="E212" s="5" t="inlineStr">
+      <c r="E212" s="9" t="inlineStr">
         <is>
           <t>14/07/2026</t>
         </is>
       </c>
-      <c r="F212" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G212" s="5" t="inlineStr"/>
-      <c r="H212" s="5" t="inlineStr">
+      <c r="F212" s="9" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G212" s="9" t="inlineStr"/>
+      <c r="H212" s="9" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I212" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I212" s="9" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -12149,45 +12149,45 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B239" s="5" t="inlineStr">
+      <c r="A239" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B239" s="9" t="inlineStr">
         <is>
           <t>A1-E1</t>
         </is>
       </c>
-      <c r="C239" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D239" s="5" t="inlineStr">
+      <c r="C239" s="9" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D239" s="9" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="E239" s="5" t="inlineStr">
+      <c r="E239" s="9" t="inlineStr">
         <is>
           <t>14/07/2026</t>
         </is>
       </c>
-      <c r="F239" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G239" s="5" t="inlineStr"/>
-      <c r="H239" s="5" t="inlineStr">
+      <c r="F239" s="9" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G239" s="9" t="inlineStr"/>
+      <c r="H239" s="9" t="inlineStr">
         <is>
           <t>0/38</t>
         </is>
       </c>
-      <c r="I239" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I239" s="9" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -13386,45 +13386,45 @@
       </c>
     </row>
     <row r="266">
-      <c r="A266" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B266" s="5" t="inlineStr">
+      <c r="A266" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B266" s="9" t="inlineStr">
         <is>
           <t>A1-E2</t>
         </is>
       </c>
-      <c r="C266" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D266" s="5" t="inlineStr">
+      <c r="C266" s="9" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D266" s="9" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="E266" s="5" t="inlineStr">
+      <c r="E266" s="9" t="inlineStr">
         <is>
           <t>14/07/2026</t>
         </is>
       </c>
-      <c r="F266" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G266" s="5" t="inlineStr"/>
-      <c r="H266" s="5" t="inlineStr">
+      <c r="F266" s="9" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G266" s="9" t="inlineStr"/>
+      <c r="H266" s="9" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I266" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I266" s="9" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -14627,45 +14627,45 @@
       </c>
     </row>
     <row r="293">
-      <c r="A293" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B293" s="5" t="inlineStr">
+      <c r="A293" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B293" s="9" t="inlineStr">
         <is>
           <t>A1-F1</t>
         </is>
       </c>
-      <c r="C293" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D293" s="5" t="inlineStr">
+      <c r="C293" s="9" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D293" s="9" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="E293" s="5" t="inlineStr">
+      <c r="E293" s="9" t="inlineStr">
         <is>
           <t>14/07/2026</t>
         </is>
       </c>
-      <c r="F293" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G293" s="5" t="inlineStr"/>
-      <c r="H293" s="5" t="inlineStr">
+      <c r="F293" s="9" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G293" s="9" t="inlineStr"/>
+      <c r="H293" s="9" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I293" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I293" s="9" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -15864,45 +15864,45 @@
       </c>
     </row>
     <row r="320">
-      <c r="A320" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B320" s="5" t="inlineStr">
+      <c r="A320" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B320" s="9" t="inlineStr">
         <is>
           <t>A1-F2</t>
         </is>
       </c>
-      <c r="C320" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D320" s="5" t="inlineStr">
+      <c r="C320" s="9" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D320" s="9" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="E320" s="5" t="inlineStr">
+      <c r="E320" s="9" t="inlineStr">
         <is>
           <t>14/07/2026</t>
         </is>
       </c>
-      <c r="F320" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G320" s="5" t="inlineStr"/>
-      <c r="H320" s="5" t="inlineStr">
+      <c r="F320" s="9" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G320" s="9" t="inlineStr"/>
+      <c r="H320" s="9" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I320" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I320" s="9" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A1_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A1_session_analysis.xlsx
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8">
@@ -924,7 +924,7 @@
         </is>
       </c>
       <c r="L8" s="4" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
     </row>
     <row r="9">
@@ -1837,10 +1837,10 @@
         <v>19</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R21" s="4" t="inlineStr">
         <is>
@@ -1919,10 +1919,10 @@
         <v>19</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R22" s="4" t="inlineStr">
         <is>
@@ -2001,10 +2001,10 @@
         <v>19</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R23" s="4" t="inlineStr">
         <is>
@@ -2083,10 +2083,10 @@
         <v>19</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R24" s="4" t="inlineStr">
         <is>
@@ -2165,10 +2165,10 @@
         <v>20</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R25" s="4" t="inlineStr">
         <is>
@@ -2243,10 +2243,10 @@
         <v>19</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R26" s="4" t="inlineStr">
         <is>
@@ -9718,45 +9718,45 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B186" s="5" t="inlineStr">
+      <c r="A186" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B186" s="9" t="inlineStr">
         <is>
           <t>A1-D1</t>
         </is>
       </c>
-      <c r="C186" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D186" s="5" t="inlineStr">
+      <c r="C186" s="9" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D186" s="9" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="E186" s="5" t="inlineStr">
+      <c r="E186" s="9" t="inlineStr">
         <is>
           <t>15/07/2026</t>
         </is>
       </c>
-      <c r="F186" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G186" s="5" t="inlineStr"/>
-      <c r="H186" s="5" t="inlineStr">
+      <c r="F186" s="9" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G186" s="9" t="inlineStr"/>
+      <c r="H186" s="9" t="inlineStr">
         <is>
           <t>0/35</t>
         </is>
       </c>
-      <c r="I186" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I186" s="9" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -10955,45 +10955,45 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B213" s="5" t="inlineStr">
+      <c r="A213" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B213" s="9" t="inlineStr">
         <is>
           <t>A1-D2</t>
         </is>
       </c>
-      <c r="C213" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D213" s="5" t="inlineStr">
+      <c r="C213" s="9" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D213" s="9" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="E213" s="5" t="inlineStr">
+      <c r="E213" s="9" t="inlineStr">
         <is>
           <t>15/07/2026</t>
         </is>
       </c>
-      <c r="F213" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G213" s="5" t="inlineStr"/>
-      <c r="H213" s="5" t="inlineStr">
+      <c r="F213" s="9" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G213" s="9" t="inlineStr"/>
+      <c r="H213" s="9" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I213" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I213" s="9" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -12192,45 +12192,45 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B240" s="5" t="inlineStr">
+      <c r="A240" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B240" s="9" t="inlineStr">
         <is>
           <t>A1-E1</t>
         </is>
       </c>
-      <c r="C240" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D240" s="5" t="inlineStr">
+      <c r="C240" s="9" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D240" s="9" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="E240" s="5" t="inlineStr">
+      <c r="E240" s="9" t="inlineStr">
         <is>
           <t>15/07/2026</t>
         </is>
       </c>
-      <c r="F240" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G240" s="5" t="inlineStr"/>
-      <c r="H240" s="5" t="inlineStr">
+      <c r="F240" s="9" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G240" s="9" t="inlineStr"/>
+      <c r="H240" s="9" t="inlineStr">
         <is>
           <t>0/38</t>
         </is>
       </c>
-      <c r="I240" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I240" s="9" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -13429,45 +13429,45 @@
       </c>
     </row>
     <row r="267">
-      <c r="A267" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B267" s="5" t="inlineStr">
+      <c r="A267" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B267" s="9" t="inlineStr">
         <is>
           <t>A1-E2</t>
         </is>
       </c>
-      <c r="C267" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D267" s="5" t="inlineStr">
+      <c r="C267" s="9" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D267" s="9" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="E267" s="5" t="inlineStr">
+      <c r="E267" s="9" t="inlineStr">
         <is>
           <t>15/07/2026</t>
         </is>
       </c>
-      <c r="F267" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G267" s="5" t="inlineStr"/>
-      <c r="H267" s="5" t="inlineStr">
+      <c r="F267" s="9" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G267" s="9" t="inlineStr"/>
+      <c r="H267" s="9" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I267" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I267" s="9" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -14670,45 +14670,45 @@
       </c>
     </row>
     <row r="294">
-      <c r="A294" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B294" s="5" t="inlineStr">
+      <c r="A294" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B294" s="9" t="inlineStr">
         <is>
           <t>A1-F1</t>
         </is>
       </c>
-      <c r="C294" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D294" s="5" t="inlineStr">
+      <c r="C294" s="9" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D294" s="9" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="E294" s="5" t="inlineStr">
+      <c r="E294" s="9" t="inlineStr">
         <is>
           <t>15/07/2026</t>
         </is>
       </c>
-      <c r="F294" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G294" s="5" t="inlineStr"/>
-      <c r="H294" s="5" t="inlineStr">
+      <c r="F294" s="9" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G294" s="9" t="inlineStr"/>
+      <c r="H294" s="9" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I294" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I294" s="9" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -15907,45 +15907,45 @@
       </c>
     </row>
     <row r="321">
-      <c r="A321" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B321" s="5" t="inlineStr">
+      <c r="A321" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B321" s="9" t="inlineStr">
         <is>
           <t>A1-F2</t>
         </is>
       </c>
-      <c r="C321" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D321" s="5" t="inlineStr">
+      <c r="C321" s="9" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D321" s="9" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="E321" s="5" t="inlineStr">
+      <c r="E321" s="9" t="inlineStr">
         <is>
           <t>15/07/2026</t>
         </is>
       </c>
-      <c r="F321" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G321" s="5" t="inlineStr"/>
-      <c r="H321" s="5" t="inlineStr">
+      <c r="F321" s="9" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G321" s="9" t="inlineStr"/>
+      <c r="H321" s="9" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I321" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I321" s="9" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A1_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A1_session_analysis.xlsx
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8">
@@ -924,7 +924,7 @@
         </is>
       </c>
       <c r="L8" s="4" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9">
@@ -1837,10 +1837,10 @@
         <v>19</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R21" s="4" t="inlineStr">
         <is>
@@ -1919,10 +1919,10 @@
         <v>19</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R22" s="4" t="inlineStr">
         <is>
@@ -2001,10 +2001,10 @@
         <v>19</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R23" s="4" t="inlineStr">
         <is>
@@ -2083,10 +2083,10 @@
         <v>19</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R24" s="4" t="inlineStr">
         <is>
@@ -2165,10 +2165,10 @@
         <v>20</v>
       </c>
       <c r="P25" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q25" s="4" t="n">
         <v>3</v>
-      </c>
-      <c r="Q25" s="4" t="n">
-        <v>4</v>
       </c>
       <c r="R25" s="4" t="inlineStr">
         <is>
@@ -2243,10 +2243,10 @@
         <v>19</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R26" s="4" t="inlineStr">
         <is>
@@ -9761,45 +9761,45 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B187" s="5" t="inlineStr">
+      <c r="A187" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B187" s="9" t="inlineStr">
         <is>
           <t>A1-D1</t>
         </is>
       </c>
-      <c r="C187" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D187" s="5" t="inlineStr">
+      <c r="C187" s="9" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D187" s="9" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="E187" s="5" t="inlineStr">
+      <c r="E187" s="9" t="inlineStr">
         <is>
           <t>16/07/2026</t>
         </is>
       </c>
-      <c r="F187" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G187" s="5" t="inlineStr"/>
-      <c r="H187" s="5" t="inlineStr">
+      <c r="F187" s="9" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G187" s="9" t="inlineStr"/>
+      <c r="H187" s="9" t="inlineStr">
         <is>
           <t>0/35</t>
         </is>
       </c>
-      <c r="I187" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I187" s="9" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -10998,45 +10998,45 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B214" s="5" t="inlineStr">
+      <c r="A214" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B214" s="9" t="inlineStr">
         <is>
           <t>A1-D2</t>
         </is>
       </c>
-      <c r="C214" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D214" s="5" t="inlineStr">
+      <c r="C214" s="9" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D214" s="9" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="E214" s="5" t="inlineStr">
+      <c r="E214" s="9" t="inlineStr">
         <is>
           <t>16/07/2026</t>
         </is>
       </c>
-      <c r="F214" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G214" s="5" t="inlineStr"/>
-      <c r="H214" s="5" t="inlineStr">
+      <c r="F214" s="9" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G214" s="9" t="inlineStr"/>
+      <c r="H214" s="9" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I214" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I214" s="9" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -12235,45 +12235,45 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B241" s="5" t="inlineStr">
+      <c r="A241" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B241" s="9" t="inlineStr">
         <is>
           <t>A1-E1</t>
         </is>
       </c>
-      <c r="C241" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D241" s="5" t="inlineStr">
+      <c r="C241" s="9" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D241" s="9" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="E241" s="5" t="inlineStr">
+      <c r="E241" s="9" t="inlineStr">
         <is>
           <t>16/07/2026</t>
         </is>
       </c>
-      <c r="F241" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G241" s="5" t="inlineStr"/>
-      <c r="H241" s="5" t="inlineStr">
+      <c r="F241" s="9" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G241" s="9" t="inlineStr"/>
+      <c r="H241" s="9" t="inlineStr">
         <is>
           <t>0/38</t>
         </is>
       </c>
-      <c r="I241" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I241" s="9" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -13472,45 +13472,45 @@
       </c>
     </row>
     <row r="268">
-      <c r="A268" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B268" s="5" t="inlineStr">
+      <c r="A268" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B268" s="9" t="inlineStr">
         <is>
           <t>A1-E2</t>
         </is>
       </c>
-      <c r="C268" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D268" s="5" t="inlineStr">
+      <c r="C268" s="9" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D268" s="9" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="E268" s="5" t="inlineStr">
+      <c r="E268" s="9" t="inlineStr">
         <is>
           <t>16/07/2026</t>
         </is>
       </c>
-      <c r="F268" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G268" s="5" t="inlineStr"/>
-      <c r="H268" s="5" t="inlineStr">
+      <c r="F268" s="9" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G268" s="9" t="inlineStr"/>
+      <c r="H268" s="9" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I268" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I268" s="9" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -14713,45 +14713,45 @@
       </c>
     </row>
     <row r="295">
-      <c r="A295" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B295" s="5" t="inlineStr">
+      <c r="A295" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B295" s="9" t="inlineStr">
         <is>
           <t>A1-F1</t>
         </is>
       </c>
-      <c r="C295" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D295" s="5" t="inlineStr">
+      <c r="C295" s="9" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D295" s="9" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="E295" s="5" t="inlineStr">
+      <c r="E295" s="9" t="inlineStr">
         <is>
           <t>16/07/2026</t>
         </is>
       </c>
-      <c r="F295" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G295" s="5" t="inlineStr"/>
-      <c r="H295" s="5" t="inlineStr">
+      <c r="F295" s="9" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G295" s="9" t="inlineStr"/>
+      <c r="H295" s="9" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I295" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I295" s="9" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -15950,45 +15950,45 @@
       </c>
     </row>
     <row r="322">
-      <c r="A322" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B322" s="5" t="inlineStr">
+      <c r="A322" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B322" s="9" t="inlineStr">
         <is>
           <t>A1-F2</t>
         </is>
       </c>
-      <c r="C322" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D322" s="5" t="inlineStr">
+      <c r="C322" s="9" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D322" s="9" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="E322" s="5" t="inlineStr">
+      <c r="E322" s="9" t="inlineStr">
         <is>
           <t>16/07/2026</t>
         </is>
       </c>
-      <c r="F322" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G322" s="5" t="inlineStr"/>
-      <c r="H322" s="5" t="inlineStr">
+      <c r="F322" s="9" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G322" s="9" t="inlineStr"/>
+      <c r="H322" s="9" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I322" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I322" s="9" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A1_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A1_session_analysis.xlsx
@@ -814,7 +814,7 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>259</v>
+        <v>271</v>
       </c>
     </row>
     <row r="7">
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8">
@@ -980,7 +980,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>79.9%</t>
+          <t>83.6%</t>
         </is>
       </c>
     </row>
@@ -1037,7 +1037,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>72.8%</t>
+          <t>72.0%</t>
         </is>
       </c>
     </row>
@@ -1834,22 +1834,22 @@
         <v>27</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Q21" s="4" t="n">
         <v>3</v>
       </c>
       <c r="R21" s="4" t="inlineStr">
         <is>
-          <t>70.4%</t>
+          <t>77.8%</t>
         </is>
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>74.0%</t>
+          <t>71.2%</t>
         </is>
       </c>
     </row>
@@ -1916,22 +1916,22 @@
         <v>27</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Q22" s="4" t="n">
         <v>3</v>
       </c>
       <c r="R22" s="4" t="inlineStr">
         <is>
-          <t>70.4%</t>
+          <t>77.8%</t>
         </is>
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>77.9%</t>
+          <t>73.4%</t>
         </is>
       </c>
     </row>
@@ -1998,22 +1998,22 @@
         <v>27</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Q23" s="4" t="n">
         <v>3</v>
       </c>
       <c r="R23" s="4" t="inlineStr">
         <is>
-          <t>70.4%</t>
+          <t>77.8%</t>
         </is>
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>79.5%</t>
+          <t>77.8%</t>
         </is>
       </c>
     </row>
@@ -2080,22 +2080,22 @@
         <v>27</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Q24" s="4" t="n">
         <v>3</v>
       </c>
       <c r="R24" s="4" t="inlineStr">
         <is>
-          <t>70.4%</t>
+          <t>77.8%</t>
         </is>
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>76.8%</t>
+          <t>76.6%</t>
         </is>
       </c>
     </row>
@@ -2162,22 +2162,22 @@
         <v>27</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q25" s="4" t="n">
         <v>3</v>
       </c>
       <c r="R25" s="4" t="inlineStr">
         <is>
-          <t>74.1%</t>
+          <t>81.5%</t>
         </is>
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>75.4%</t>
+          <t>74.7%</t>
         </is>
       </c>
     </row>
@@ -2240,22 +2240,22 @@
         <v>27</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Q26" s="4" t="n">
         <v>3</v>
       </c>
       <c r="R26" s="4" t="inlineStr">
         <is>
-          <t>70.4%</t>
+          <t>77.8%</t>
         </is>
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>74.2%</t>
+          <t>72.2%</t>
         </is>
       </c>
     </row>
@@ -9718,88 +9718,96 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B186" s="9" t="inlineStr">
+      <c r="A186" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B186" s="2" t="inlineStr">
         <is>
           <t>A1-D1</t>
         </is>
       </c>
-      <c r="C186" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D186" s="9" t="inlineStr">
+      <c r="C186" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D186" s="2" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="E186" s="9" t="inlineStr">
+      <c r="E186" s="2" t="inlineStr">
         <is>
           <t>15/07/2026</t>
         </is>
       </c>
-      <c r="F186" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G186" s="9" t="inlineStr"/>
-      <c r="H186" s="9" t="inlineStr">
-        <is>
-          <t>0/35</t>
-        </is>
-      </c>
-      <c r="I186" s="9" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F186" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G186" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H186" s="2" t="inlineStr">
+        <is>
+          <t>17/35</t>
+        </is>
+      </c>
+      <c r="I186" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B187" s="9" t="inlineStr">
+      <c r="A187" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B187" s="2" t="inlineStr">
         <is>
           <t>A1-D1</t>
         </is>
       </c>
-      <c r="C187" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D187" s="9" t="inlineStr">
+      <c r="C187" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D187" s="2" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="E187" s="9" t="inlineStr">
+      <c r="E187" s="2" t="inlineStr">
         <is>
           <t>16/07/2026</t>
         </is>
       </c>
-      <c r="F187" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G187" s="9" t="inlineStr"/>
-      <c r="H187" s="9" t="inlineStr">
-        <is>
-          <t>0/35</t>
-        </is>
-      </c>
-      <c r="I187" s="9" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F187" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G187" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H187" s="2" t="inlineStr">
+        <is>
+          <t>14/35</t>
+        </is>
+      </c>
+      <c r="I187" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -10955,88 +10963,96 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B213" s="9" t="inlineStr">
+      <c r="A213" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B213" s="2" t="inlineStr">
         <is>
           <t>A1-D2</t>
         </is>
       </c>
-      <c r="C213" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D213" s="9" t="inlineStr">
+      <c r="C213" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D213" s="2" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="E213" s="9" t="inlineStr">
+      <c r="E213" s="2" t="inlineStr">
         <is>
           <t>15/07/2026</t>
         </is>
       </c>
-      <c r="F213" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G213" s="9" t="inlineStr"/>
-      <c r="H213" s="9" t="inlineStr">
-        <is>
-          <t>0/34</t>
-        </is>
-      </c>
-      <c r="I213" s="9" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F213" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G213" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H213" s="2" t="inlineStr">
+        <is>
+          <t>13/34</t>
+        </is>
+      </c>
+      <c r="I213" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B214" s="9" t="inlineStr">
+      <c r="A214" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B214" s="2" t="inlineStr">
         <is>
           <t>A1-D2</t>
         </is>
       </c>
-      <c r="C214" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D214" s="9" t="inlineStr">
+      <c r="C214" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D214" s="2" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="E214" s="9" t="inlineStr">
+      <c r="E214" s="2" t="inlineStr">
         <is>
           <t>16/07/2026</t>
         </is>
       </c>
-      <c r="F214" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G214" s="9" t="inlineStr"/>
-      <c r="H214" s="9" t="inlineStr">
-        <is>
-          <t>0/34</t>
-        </is>
-      </c>
-      <c r="I214" s="9" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F214" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G214" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H214" s="2" t="inlineStr">
+        <is>
+          <t>8/34</t>
+        </is>
+      </c>
+      <c r="I214" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -12192,88 +12208,96 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B240" s="9" t="inlineStr">
+      <c r="A240" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B240" s="2" t="inlineStr">
         <is>
           <t>A1-E1</t>
         </is>
       </c>
-      <c r="C240" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D240" s="9" t="inlineStr">
+      <c r="C240" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D240" s="2" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="E240" s="9" t="inlineStr">
+      <c r="E240" s="2" t="inlineStr">
         <is>
           <t>15/07/2026</t>
         </is>
       </c>
-      <c r="F240" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G240" s="9" t="inlineStr"/>
-      <c r="H240" s="9" t="inlineStr">
-        <is>
-          <t>0/38</t>
-        </is>
-      </c>
-      <c r="I240" s="9" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F240" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G240" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H240" s="2" t="inlineStr">
+        <is>
+          <t>25/38</t>
+        </is>
+      </c>
+      <c r="I240" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B241" s="9" t="inlineStr">
+      <c r="A241" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B241" s="2" t="inlineStr">
         <is>
           <t>A1-E1</t>
         </is>
       </c>
-      <c r="C241" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D241" s="9" t="inlineStr">
+      <c r="C241" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D241" s="2" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="E241" s="9" t="inlineStr">
+      <c r="E241" s="2" t="inlineStr">
         <is>
           <t>16/07/2026</t>
         </is>
       </c>
-      <c r="F241" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G241" s="9" t="inlineStr"/>
-      <c r="H241" s="9" t="inlineStr">
-        <is>
-          <t>0/38</t>
-        </is>
-      </c>
-      <c r="I241" s="9" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F241" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G241" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H241" s="2" t="inlineStr">
+        <is>
+          <t>22/38</t>
+        </is>
+      </c>
+      <c r="I241" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -13429,88 +13453,96 @@
       </c>
     </row>
     <row r="267">
-      <c r="A267" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B267" s="9" t="inlineStr">
+      <c r="A267" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B267" s="2" t="inlineStr">
         <is>
           <t>A1-E2</t>
         </is>
       </c>
-      <c r="C267" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D267" s="9" t="inlineStr">
+      <c r="C267" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D267" s="2" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="E267" s="9" t="inlineStr">
+      <c r="E267" s="2" t="inlineStr">
         <is>
           <t>15/07/2026</t>
         </is>
       </c>
-      <c r="F267" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G267" s="9" t="inlineStr"/>
-      <c r="H267" s="9" t="inlineStr">
-        <is>
-          <t>0/39</t>
-        </is>
-      </c>
-      <c r="I267" s="9" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F267" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G267" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H267" s="2" t="inlineStr">
+        <is>
+          <t>33/39</t>
+        </is>
+      </c>
+      <c r="I267" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="268">
-      <c r="A268" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B268" s="9" t="inlineStr">
+      <c r="A268" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B268" s="2" t="inlineStr">
         <is>
           <t>A1-E2</t>
         </is>
       </c>
-      <c r="C268" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D268" s="9" t="inlineStr">
+      <c r="C268" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D268" s="2" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="E268" s="9" t="inlineStr">
+      <c r="E268" s="2" t="inlineStr">
         <is>
           <t>16/07/2026</t>
         </is>
       </c>
-      <c r="F268" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G268" s="9" t="inlineStr"/>
-      <c r="H268" s="9" t="inlineStr">
-        <is>
-          <t>0/39</t>
-        </is>
-      </c>
-      <c r="I268" s="9" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F268" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G268" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H268" s="2" t="inlineStr">
+        <is>
+          <t>25/39</t>
+        </is>
+      </c>
+      <c r="I268" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -14670,88 +14702,96 @@
       </c>
     </row>
     <row r="294">
-      <c r="A294" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B294" s="9" t="inlineStr">
+      <c r="A294" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B294" s="2" t="inlineStr">
         <is>
           <t>A1-F1</t>
         </is>
       </c>
-      <c r="C294" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D294" s="9" t="inlineStr">
+      <c r="C294" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D294" s="2" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="E294" s="9" t="inlineStr">
+      <c r="E294" s="2" t="inlineStr">
         <is>
           <t>15/07/2026</t>
         </is>
       </c>
-      <c r="F294" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G294" s="9" t="inlineStr"/>
-      <c r="H294" s="9" t="inlineStr">
-        <is>
-          <t>0/39</t>
-        </is>
-      </c>
-      <c r="I294" s="9" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F294" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G294" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H294" s="2" t="inlineStr">
+        <is>
+          <t>27/39</t>
+        </is>
+      </c>
+      <c r="I294" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="295">
-      <c r="A295" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B295" s="9" t="inlineStr">
+      <c r="A295" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B295" s="2" t="inlineStr">
         <is>
           <t>A1-F1</t>
         </is>
       </c>
-      <c r="C295" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D295" s="9" t="inlineStr">
+      <c r="C295" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D295" s="2" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="E295" s="9" t="inlineStr">
+      <c r="E295" s="2" t="inlineStr">
         <is>
           <t>16/07/2026</t>
         </is>
       </c>
-      <c r="F295" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G295" s="9" t="inlineStr"/>
-      <c r="H295" s="9" t="inlineStr">
-        <is>
-          <t>0/39</t>
-        </is>
-      </c>
-      <c r="I295" s="9" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F295" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G295" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H295" s="2" t="inlineStr">
+        <is>
+          <t>26/39</t>
+        </is>
+      </c>
+      <c r="I295" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -15907,88 +15947,96 @@
       </c>
     </row>
     <row r="321">
-      <c r="A321" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B321" s="9" t="inlineStr">
+      <c r="A321" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B321" s="2" t="inlineStr">
         <is>
           <t>A1-F2</t>
         </is>
       </c>
-      <c r="C321" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D321" s="9" t="inlineStr">
+      <c r="C321" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D321" s="2" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="E321" s="9" t="inlineStr">
+      <c r="E321" s="2" t="inlineStr">
         <is>
           <t>15/07/2026</t>
         </is>
       </c>
-      <c r="F321" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G321" s="9" t="inlineStr"/>
-      <c r="H321" s="9" t="inlineStr">
-        <is>
-          <t>0/39</t>
-        </is>
-      </c>
-      <c r="I321" s="9" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F321" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G321" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H321" s="2" t="inlineStr">
+        <is>
+          <t>20/39</t>
+        </is>
+      </c>
+      <c r="I321" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="322">
-      <c r="A322" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B322" s="9" t="inlineStr">
+      <c r="A322" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B322" s="2" t="inlineStr">
         <is>
           <t>A1-F2</t>
         </is>
       </c>
-      <c r="C322" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D322" s="9" t="inlineStr">
+      <c r="C322" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D322" s="2" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="E322" s="9" t="inlineStr">
+      <c r="E322" s="2" t="inlineStr">
         <is>
           <t>16/07/2026</t>
         </is>
       </c>
-      <c r="F322" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G322" s="9" t="inlineStr"/>
-      <c r="H322" s="9" t="inlineStr">
-        <is>
-          <t>0/39</t>
-        </is>
-      </c>
-      <c r="I322" s="9" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F322" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G322" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H322" s="2" t="inlineStr">
+        <is>
+          <t>21/39</t>
+        </is>
+      </c>
+      <c r="I322" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A1_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A1_session_analysis.xlsx
@@ -58,14 +58,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFFE0"/>
-        <bgColor rgb="00FFFFE0"/>
+        <fgColor rgb="00FFB6C1"/>
+        <bgColor rgb="00FFB6C1"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFB6C1"/>
-        <bgColor rgb="00FFB6C1"/>
+        <fgColor rgb="00FFFFE0"/>
+        <bgColor rgb="00FFFFE0"/>
       </patternFill>
     </fill>
   </fills>
@@ -96,16 +96,16 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8">
@@ -924,7 +924,7 @@
         </is>
       </c>
       <c r="L8" s="4" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9">
@@ -1345,10 +1345,10 @@
         <v>24</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R15" s="4" t="inlineStr">
         <is>
@@ -1427,10 +1427,10 @@
         <v>24</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R16" s="4" t="inlineStr">
         <is>
@@ -1509,10 +1509,10 @@
         <v>24</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R17" s="4" t="inlineStr">
         <is>
@@ -1591,10 +1591,10 @@
         <v>24</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R18" s="4" t="inlineStr">
         <is>
@@ -1673,10 +1673,10 @@
         <v>24</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R19" s="4" t="inlineStr">
         <is>
@@ -1755,10 +1755,10 @@
         <v>24</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R20" s="4" t="inlineStr">
         <is>
@@ -2220,7 +2220,7 @@
       </c>
       <c r="I26" s="5" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Not Recorded</t>
         </is>
       </c>
       <c r="K26" s="4" t="inlineStr">
@@ -2260,86 +2260,86 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B27" s="5" t="inlineStr">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
         <is>
           <t>A1-A1</t>
         </is>
       </c>
-      <c r="C27" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="inlineStr">
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="E27" s="5" t="inlineStr">
+      <c r="E27" s="6" t="inlineStr">
         <is>
           <t>19/07/2026</t>
         </is>
       </c>
-      <c r="F27" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G27" s="5" t="inlineStr"/>
-      <c r="H27" s="5" t="inlineStr">
+      <c r="F27" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G27" s="6" t="inlineStr"/>
+      <c r="H27" s="6" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I27" s="5" t="inlineStr">
+      <c r="I27" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B28" s="5" t="inlineStr">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
         <is>
           <t>A1-A1</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D28" s="5" t="inlineStr">
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="E28" s="5" t="inlineStr">
+      <c r="E28" s="6" t="inlineStr">
         <is>
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="F28" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G28" s="5" t="inlineStr"/>
-      <c r="H28" s="5" t="inlineStr">
+      <c r="F28" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G28" s="6" t="inlineStr"/>
+      <c r="H28" s="6" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I28" s="5" t="inlineStr">
+      <c r="I28" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -2510,7 +2510,7 @@
           <t>Recorded</t>
         </is>
       </c>
-      <c r="L31" s="6" t="inlineStr">
+      <c r="L31" s="7" t="inlineStr">
         <is>
           <t>Green</t>
         </is>
@@ -2572,7 +2572,7 @@
           <t>Not Recorded</t>
         </is>
       </c>
-      <c r="L32" s="7" t="inlineStr">
+      <c r="L32" s="8" t="inlineStr">
         <is>
           <t>Red</t>
         </is>
@@ -2634,7 +2634,7 @@
           <t>Pending</t>
         </is>
       </c>
-      <c r="L33" s="8" t="inlineStr">
+      <c r="L33" s="9" t="inlineStr">
         <is>
           <t>Yellow</t>
         </is>
@@ -3577,91 +3577,91 @@
       </c>
       <c r="I53" s="5" t="inlineStr">
         <is>
+          <t>Not Recorded</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B54" s="6" t="inlineStr">
+        <is>
+          <t>A1-A2</t>
+        </is>
+      </c>
+      <c r="C54" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D54" s="6" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="E54" s="6" t="inlineStr">
+        <is>
+          <t>19/07/2026</t>
+        </is>
+      </c>
+      <c r="F54" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G54" s="6" t="inlineStr"/>
+      <c r="H54" s="6" t="inlineStr">
+        <is>
+          <t>0/33</t>
+        </is>
+      </c>
+      <c r="I54" s="6" t="inlineStr">
+        <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B54" s="5" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B55" s="6" t="inlineStr">
         <is>
           <t>A1-A2</t>
         </is>
       </c>
-      <c r="C54" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D54" s="5" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="E54" s="5" t="inlineStr">
-        <is>
-          <t>19/07/2026</t>
-        </is>
-      </c>
-      <c r="F54" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G54" s="5" t="inlineStr"/>
-      <c r="H54" s="5" t="inlineStr">
+      <c r="C55" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D55" s="6" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E55" s="6" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="F55" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G55" s="6" t="inlineStr"/>
+      <c r="H55" s="6" t="inlineStr">
         <is>
           <t>0/33</t>
         </is>
       </c>
-      <c r="I54" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B55" s="5" t="inlineStr">
-        <is>
-          <t>A1-A2</t>
-        </is>
-      </c>
-      <c r="C55" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D55" s="5" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="E55" s="5" t="inlineStr">
-        <is>
-          <t>20/07/2026</t>
-        </is>
-      </c>
-      <c r="F55" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G55" s="5" t="inlineStr"/>
-      <c r="H55" s="5" t="inlineStr">
-        <is>
-          <t>0/33</t>
-        </is>
-      </c>
-      <c r="I55" s="5" t="inlineStr">
+      <c r="I55" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -4834,91 +4834,91 @@
       </c>
       <c r="I80" s="5" t="inlineStr">
         <is>
+          <t>Not Recorded</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B81" s="6" t="inlineStr">
+        <is>
+          <t>A1-B1</t>
+        </is>
+      </c>
+      <c r="C81" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D81" s="6" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="E81" s="6" t="inlineStr">
+        <is>
+          <t>19/07/2026</t>
+        </is>
+      </c>
+      <c r="F81" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G81" s="6" t="inlineStr"/>
+      <c r="H81" s="6" t="inlineStr">
+        <is>
+          <t>0/34</t>
+        </is>
+      </c>
+      <c r="I81" s="6" t="inlineStr">
+        <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B81" s="5" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B82" s="6" t="inlineStr">
         <is>
           <t>A1-B1</t>
         </is>
       </c>
-      <c r="C81" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D81" s="5" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="E81" s="5" t="inlineStr">
-        <is>
-          <t>19/07/2026</t>
-        </is>
-      </c>
-      <c r="F81" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G81" s="5" t="inlineStr"/>
-      <c r="H81" s="5" t="inlineStr">
+      <c r="C82" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D82" s="6" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E82" s="6" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="F82" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G82" s="6" t="inlineStr"/>
+      <c r="H82" s="6" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I81" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B82" s="5" t="inlineStr">
-        <is>
-          <t>A1-B1</t>
-        </is>
-      </c>
-      <c r="C82" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D82" s="5" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="E82" s="5" t="inlineStr">
-        <is>
-          <t>20/07/2026</t>
-        </is>
-      </c>
-      <c r="F82" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G82" s="5" t="inlineStr"/>
-      <c r="H82" s="5" t="inlineStr">
-        <is>
-          <t>0/34</t>
-        </is>
-      </c>
-      <c r="I82" s="5" t="inlineStr">
+      <c r="I82" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -6091,91 +6091,91 @@
       </c>
       <c r="I107" s="5" t="inlineStr">
         <is>
+          <t>Not Recorded</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B108" s="6" t="inlineStr">
+        <is>
+          <t>A1-B2</t>
+        </is>
+      </c>
+      <c r="C108" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D108" s="6" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="E108" s="6" t="inlineStr">
+        <is>
+          <t>19/07/2026</t>
+        </is>
+      </c>
+      <c r="F108" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G108" s="6" t="inlineStr"/>
+      <c r="H108" s="6" t="inlineStr">
+        <is>
+          <t>0/34</t>
+        </is>
+      </c>
+      <c r="I108" s="6" t="inlineStr">
+        <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B108" s="5" t="inlineStr">
+    <row r="109">
+      <c r="A109" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B109" s="6" t="inlineStr">
         <is>
           <t>A1-B2</t>
         </is>
       </c>
-      <c r="C108" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D108" s="5" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="E108" s="5" t="inlineStr">
-        <is>
-          <t>19/07/2026</t>
-        </is>
-      </c>
-      <c r="F108" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G108" s="5" t="inlineStr"/>
-      <c r="H108" s="5" t="inlineStr">
+      <c r="C109" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D109" s="6" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E109" s="6" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="F109" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G109" s="6" t="inlineStr"/>
+      <c r="H109" s="6" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I108" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B109" s="5" t="inlineStr">
-        <is>
-          <t>A1-B2</t>
-        </is>
-      </c>
-      <c r="C109" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D109" s="5" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="E109" s="5" t="inlineStr">
-        <is>
-          <t>20/07/2026</t>
-        </is>
-      </c>
-      <c r="F109" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G109" s="5" t="inlineStr"/>
-      <c r="H109" s="5" t="inlineStr">
-        <is>
-          <t>0/34</t>
-        </is>
-      </c>
-      <c r="I109" s="5" t="inlineStr">
+      <c r="I109" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -7348,91 +7348,91 @@
       </c>
       <c r="I134" s="5" t="inlineStr">
         <is>
+          <t>Not Recorded</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B135" s="6" t="inlineStr">
+        <is>
+          <t>A1-C1</t>
+        </is>
+      </c>
+      <c r="C135" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D135" s="6" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="E135" s="6" t="inlineStr">
+        <is>
+          <t>19/07/2026</t>
+        </is>
+      </c>
+      <c r="F135" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G135" s="6" t="inlineStr"/>
+      <c r="H135" s="6" t="inlineStr">
+        <is>
+          <t>0/34</t>
+        </is>
+      </c>
+      <c r="I135" s="6" t="inlineStr">
+        <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B135" s="5" t="inlineStr">
+    <row r="136">
+      <c r="A136" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B136" s="6" t="inlineStr">
         <is>
           <t>A1-C1</t>
         </is>
       </c>
-      <c r="C135" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D135" s="5" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="E135" s="5" t="inlineStr">
-        <is>
-          <t>19/07/2026</t>
-        </is>
-      </c>
-      <c r="F135" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G135" s="5" t="inlineStr"/>
-      <c r="H135" s="5" t="inlineStr">
+      <c r="C136" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D136" s="6" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E136" s="6" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="F136" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G136" s="6" t="inlineStr"/>
+      <c r="H136" s="6" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I135" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B136" s="5" t="inlineStr">
-        <is>
-          <t>A1-C1</t>
-        </is>
-      </c>
-      <c r="C136" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D136" s="5" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="E136" s="5" t="inlineStr">
-        <is>
-          <t>20/07/2026</t>
-        </is>
-      </c>
-      <c r="F136" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G136" s="5" t="inlineStr"/>
-      <c r="H136" s="5" t="inlineStr">
-        <is>
-          <t>0/34</t>
-        </is>
-      </c>
-      <c r="I136" s="5" t="inlineStr">
+      <c r="I136" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -8605,91 +8605,91 @@
       </c>
       <c r="I161" s="5" t="inlineStr">
         <is>
+          <t>Not Recorded</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B162" s="6" t="inlineStr">
+        <is>
+          <t>A1-C2</t>
+        </is>
+      </c>
+      <c r="C162" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D162" s="6" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="E162" s="6" t="inlineStr">
+        <is>
+          <t>19/07/2026</t>
+        </is>
+      </c>
+      <c r="F162" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G162" s="6" t="inlineStr"/>
+      <c r="H162" s="6" t="inlineStr">
+        <is>
+          <t>0/33</t>
+        </is>
+      </c>
+      <c r="I162" s="6" t="inlineStr">
+        <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="162">
-      <c r="A162" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B162" s="5" t="inlineStr">
+    <row r="163">
+      <c r="A163" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B163" s="6" t="inlineStr">
         <is>
           <t>A1-C2</t>
         </is>
       </c>
-      <c r="C162" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D162" s="5" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="E162" s="5" t="inlineStr">
-        <is>
-          <t>19/07/2026</t>
-        </is>
-      </c>
-      <c r="F162" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G162" s="5" t="inlineStr"/>
-      <c r="H162" s="5" t="inlineStr">
+      <c r="C163" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D163" s="6" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E163" s="6" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="F163" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G163" s="6" t="inlineStr"/>
+      <c r="H163" s="6" t="inlineStr">
         <is>
           <t>0/33</t>
         </is>
       </c>
-      <c r="I162" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B163" s="5" t="inlineStr">
-        <is>
-          <t>A1-C2</t>
-        </is>
-      </c>
-      <c r="C163" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D163" s="5" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="E163" s="5" t="inlineStr">
-        <is>
-          <t>20/07/2026</t>
-        </is>
-      </c>
-      <c r="F163" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G163" s="5" t="inlineStr"/>
-      <c r="H163" s="5" t="inlineStr">
-        <is>
-          <t>0/33</t>
-        </is>
-      </c>
-      <c r="I163" s="5" t="inlineStr">
+      <c r="I163" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -8931,43 +8931,43 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B169" s="9" t="inlineStr">
+      <c r="A169" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B169" s="5" t="inlineStr">
         <is>
           <t>A1-D1</t>
         </is>
       </c>
-      <c r="C169" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D169" s="9" t="inlineStr">
+      <c r="C169" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D169" s="5" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E169" s="9" t="inlineStr">
+      <c r="E169" s="5" t="inlineStr">
         <is>
           <t>04/06/2026</t>
         </is>
       </c>
-      <c r="F169" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G169" s="9" t="inlineStr"/>
-      <c r="H169" s="9" t="inlineStr">
+      <c r="F169" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G169" s="5" t="inlineStr"/>
+      <c r="H169" s="5" t="inlineStr">
         <is>
           <t>0/35</t>
         </is>
       </c>
-      <c r="I169" s="9" t="inlineStr">
+      <c r="I169" s="5" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
@@ -9585,43 +9585,43 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B183" s="9" t="inlineStr">
+      <c r="A183" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B183" s="5" t="inlineStr">
         <is>
           <t>A1-D1</t>
         </is>
       </c>
-      <c r="C183" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D183" s="9" t="inlineStr">
+      <c r="C183" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D183" s="5" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="E183" s="9" t="inlineStr">
+      <c r="E183" s="5" t="inlineStr">
         <is>
           <t>08/07/2026</t>
         </is>
       </c>
-      <c r="F183" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G183" s="9" t="inlineStr"/>
-      <c r="H183" s="9" t="inlineStr">
+      <c r="F183" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G183" s="5" t="inlineStr"/>
+      <c r="H183" s="5" t="inlineStr">
         <is>
           <t>0/35</t>
         </is>
       </c>
-      <c r="I183" s="9" t="inlineStr">
+      <c r="I183" s="5" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
@@ -9675,43 +9675,43 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B185" s="9" t="inlineStr">
+      <c r="A185" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B185" s="5" t="inlineStr">
         <is>
           <t>A1-D1</t>
         </is>
       </c>
-      <c r="C185" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D185" s="9" t="inlineStr">
+      <c r="C185" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D185" s="5" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="E185" s="9" t="inlineStr">
+      <c r="E185" s="5" t="inlineStr">
         <is>
           <t>14/07/2026</t>
         </is>
       </c>
-      <c r="F185" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G185" s="9" t="inlineStr"/>
-      <c r="H185" s="9" t="inlineStr">
+      <c r="F185" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G185" s="5" t="inlineStr"/>
+      <c r="H185" s="5" t="inlineStr">
         <is>
           <t>0/35</t>
         </is>
       </c>
-      <c r="I185" s="9" t="inlineStr">
+      <c r="I185" s="5" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
@@ -9812,129 +9812,129 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B188" s="5" t="inlineStr">
+      <c r="A188" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B188" s="6" t="inlineStr">
         <is>
           <t>A1-D1</t>
         </is>
       </c>
-      <c r="C188" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D188" s="5" t="inlineStr">
+      <c r="C188" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D188" s="6" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="E188" s="5" t="inlineStr">
+      <c r="E188" s="6" t="inlineStr">
         <is>
           <t>21/07/2026</t>
         </is>
       </c>
-      <c r="F188" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G188" s="5" t="inlineStr"/>
-      <c r="H188" s="5" t="inlineStr">
+      <c r="F188" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G188" s="6" t="inlineStr"/>
+      <c r="H188" s="6" t="inlineStr">
         <is>
           <t>0/35</t>
         </is>
       </c>
-      <c r="I188" s="5" t="inlineStr">
+      <c r="I188" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B189" s="5" t="inlineStr">
+      <c r="A189" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B189" s="6" t="inlineStr">
         <is>
           <t>A1-D1</t>
         </is>
       </c>
-      <c r="C189" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D189" s="5" t="inlineStr">
+      <c r="C189" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D189" s="6" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="E189" s="5" t="inlineStr">
+      <c r="E189" s="6" t="inlineStr">
         <is>
           <t>22/07/2026</t>
         </is>
       </c>
-      <c r="F189" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G189" s="5" t="inlineStr"/>
-      <c r="H189" s="5" t="inlineStr">
+      <c r="F189" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G189" s="6" t="inlineStr"/>
+      <c r="H189" s="6" t="inlineStr">
         <is>
           <t>0/35</t>
         </is>
       </c>
-      <c r="I189" s="5" t="inlineStr">
+      <c r="I189" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B190" s="5" t="inlineStr">
+      <c r="A190" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B190" s="6" t="inlineStr">
         <is>
           <t>A1-D1</t>
         </is>
       </c>
-      <c r="C190" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D190" s="5" t="inlineStr">
+      <c r="C190" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D190" s="6" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="E190" s="5" t="inlineStr">
+      <c r="E190" s="6" t="inlineStr">
         <is>
           <t>23/07/2026</t>
         </is>
       </c>
-      <c r="F190" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G190" s="5" t="inlineStr"/>
-      <c r="H190" s="5" t="inlineStr">
+      <c r="F190" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G190" s="6" t="inlineStr"/>
+      <c r="H190" s="6" t="inlineStr">
         <is>
           <t>0/35</t>
         </is>
       </c>
-      <c r="I190" s="5" t="inlineStr">
+      <c r="I190" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -10176,43 +10176,43 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B196" s="9" t="inlineStr">
+      <c r="A196" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B196" s="5" t="inlineStr">
         <is>
           <t>A1-D2</t>
         </is>
       </c>
-      <c r="C196" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D196" s="9" t="inlineStr">
+      <c r="C196" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D196" s="5" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E196" s="9" t="inlineStr">
+      <c r="E196" s="5" t="inlineStr">
         <is>
           <t>04/06/2026</t>
         </is>
       </c>
-      <c r="F196" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G196" s="9" t="inlineStr"/>
-      <c r="H196" s="9" t="inlineStr">
+      <c r="F196" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G196" s="5" t="inlineStr"/>
+      <c r="H196" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I196" s="9" t="inlineStr">
+      <c r="I196" s="5" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
@@ -10830,43 +10830,43 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B210" s="9" t="inlineStr">
+      <c r="A210" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B210" s="5" t="inlineStr">
         <is>
           <t>A1-D2</t>
         </is>
       </c>
-      <c r="C210" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D210" s="9" t="inlineStr">
+      <c r="C210" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D210" s="5" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="E210" s="9" t="inlineStr">
+      <c r="E210" s="5" t="inlineStr">
         <is>
           <t>08/07/2026</t>
         </is>
       </c>
-      <c r="F210" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G210" s="9" t="inlineStr"/>
-      <c r="H210" s="9" t="inlineStr">
+      <c r="F210" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G210" s="5" t="inlineStr"/>
+      <c r="H210" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I210" s="9" t="inlineStr">
+      <c r="I210" s="5" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
@@ -10920,43 +10920,43 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B212" s="9" t="inlineStr">
+      <c r="A212" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B212" s="5" t="inlineStr">
         <is>
           <t>A1-D2</t>
         </is>
       </c>
-      <c r="C212" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D212" s="9" t="inlineStr">
+      <c r="C212" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D212" s="5" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="E212" s="9" t="inlineStr">
+      <c r="E212" s="5" t="inlineStr">
         <is>
           <t>14/07/2026</t>
         </is>
       </c>
-      <c r="F212" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G212" s="9" t="inlineStr"/>
-      <c r="H212" s="9" t="inlineStr">
+      <c r="F212" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G212" s="5" t="inlineStr"/>
+      <c r="H212" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I212" s="9" t="inlineStr">
+      <c r="I212" s="5" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
@@ -11057,129 +11057,129 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B215" s="5" t="inlineStr">
+      <c r="A215" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B215" s="6" t="inlineStr">
         <is>
           <t>A1-D2</t>
         </is>
       </c>
-      <c r="C215" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D215" s="5" t="inlineStr">
+      <c r="C215" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D215" s="6" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="E215" s="5" t="inlineStr">
+      <c r="E215" s="6" t="inlineStr">
         <is>
           <t>21/07/2026</t>
         </is>
       </c>
-      <c r="F215" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G215" s="5" t="inlineStr"/>
-      <c r="H215" s="5" t="inlineStr">
+      <c r="F215" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G215" s="6" t="inlineStr"/>
+      <c r="H215" s="6" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I215" s="5" t="inlineStr">
+      <c r="I215" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B216" s="5" t="inlineStr">
+      <c r="A216" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B216" s="6" t="inlineStr">
         <is>
           <t>A1-D2</t>
         </is>
       </c>
-      <c r="C216" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D216" s="5" t="inlineStr">
+      <c r="C216" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D216" s="6" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="E216" s="5" t="inlineStr">
+      <c r="E216" s="6" t="inlineStr">
         <is>
           <t>22/07/2026</t>
         </is>
       </c>
-      <c r="F216" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G216" s="5" t="inlineStr"/>
-      <c r="H216" s="5" t="inlineStr">
+      <c r="F216" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G216" s="6" t="inlineStr"/>
+      <c r="H216" s="6" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I216" s="5" t="inlineStr">
+      <c r="I216" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B217" s="5" t="inlineStr">
+      <c r="A217" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B217" s="6" t="inlineStr">
         <is>
           <t>A1-D2</t>
         </is>
       </c>
-      <c r="C217" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D217" s="5" t="inlineStr">
+      <c r="C217" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D217" s="6" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="E217" s="5" t="inlineStr">
+      <c r="E217" s="6" t="inlineStr">
         <is>
           <t>23/07/2026</t>
         </is>
       </c>
-      <c r="F217" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G217" s="5" t="inlineStr"/>
-      <c r="H217" s="5" t="inlineStr">
+      <c r="F217" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G217" s="6" t="inlineStr"/>
+      <c r="H217" s="6" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I217" s="5" t="inlineStr">
+      <c r="I217" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -11421,43 +11421,43 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B223" s="9" t="inlineStr">
+      <c r="A223" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B223" s="5" t="inlineStr">
         <is>
           <t>A1-E1</t>
         </is>
       </c>
-      <c r="C223" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D223" s="9" t="inlineStr">
+      <c r="C223" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D223" s="5" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E223" s="9" t="inlineStr">
+      <c r="E223" s="5" t="inlineStr">
         <is>
           <t>04/06/2026</t>
         </is>
       </c>
-      <c r="F223" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G223" s="9" t="inlineStr"/>
-      <c r="H223" s="9" t="inlineStr">
+      <c r="F223" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G223" s="5" t="inlineStr"/>
+      <c r="H223" s="5" t="inlineStr">
         <is>
           <t>0/38</t>
         </is>
       </c>
-      <c r="I223" s="9" t="inlineStr">
+      <c r="I223" s="5" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
@@ -12122,86 +12122,86 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B238" s="9" t="inlineStr">
+      <c r="A238" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B238" s="5" t="inlineStr">
         <is>
           <t>A1-E1</t>
         </is>
       </c>
-      <c r="C238" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D238" s="9" t="inlineStr">
+      <c r="C238" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D238" s="5" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="E238" s="9" t="inlineStr">
+      <c r="E238" s="5" t="inlineStr">
         <is>
           <t>09/07/2026</t>
         </is>
       </c>
-      <c r="F238" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G238" s="9" t="inlineStr"/>
-      <c r="H238" s="9" t="inlineStr">
+      <c r="F238" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G238" s="5" t="inlineStr"/>
+      <c r="H238" s="5" t="inlineStr">
         <is>
           <t>0/38</t>
         </is>
       </c>
-      <c r="I238" s="9" t="inlineStr">
+      <c r="I238" s="5" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B239" s="9" t="inlineStr">
+      <c r="A239" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B239" s="5" t="inlineStr">
         <is>
           <t>A1-E1</t>
         </is>
       </c>
-      <c r="C239" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D239" s="9" t="inlineStr">
+      <c r="C239" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D239" s="5" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="E239" s="9" t="inlineStr">
+      <c r="E239" s="5" t="inlineStr">
         <is>
           <t>14/07/2026</t>
         </is>
       </c>
-      <c r="F239" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G239" s="9" t="inlineStr"/>
-      <c r="H239" s="9" t="inlineStr">
+      <c r="F239" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G239" s="5" t="inlineStr"/>
+      <c r="H239" s="5" t="inlineStr">
         <is>
           <t>0/38</t>
         </is>
       </c>
-      <c r="I239" s="9" t="inlineStr">
+      <c r="I239" s="5" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
@@ -12302,129 +12302,129 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B242" s="5" t="inlineStr">
+      <c r="A242" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B242" s="6" t="inlineStr">
         <is>
           <t>A1-E1</t>
         </is>
       </c>
-      <c r="C242" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D242" s="5" t="inlineStr">
+      <c r="C242" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D242" s="6" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="E242" s="5" t="inlineStr">
+      <c r="E242" s="6" t="inlineStr">
         <is>
           <t>21/07/2026</t>
         </is>
       </c>
-      <c r="F242" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G242" s="5" t="inlineStr"/>
-      <c r="H242" s="5" t="inlineStr">
+      <c r="F242" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G242" s="6" t="inlineStr"/>
+      <c r="H242" s="6" t="inlineStr">
         <is>
           <t>0/38</t>
         </is>
       </c>
-      <c r="I242" s="5" t="inlineStr">
+      <c r="I242" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B243" s="5" t="inlineStr">
+      <c r="A243" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B243" s="6" t="inlineStr">
         <is>
           <t>A1-E1</t>
         </is>
       </c>
-      <c r="C243" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D243" s="5" t="inlineStr">
+      <c r="C243" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D243" s="6" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="E243" s="5" t="inlineStr">
+      <c r="E243" s="6" t="inlineStr">
         <is>
           <t>22/07/2026</t>
         </is>
       </c>
-      <c r="F243" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G243" s="5" t="inlineStr"/>
-      <c r="H243" s="5" t="inlineStr">
+      <c r="F243" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G243" s="6" t="inlineStr"/>
+      <c r="H243" s="6" t="inlineStr">
         <is>
           <t>0/38</t>
         </is>
       </c>
-      <c r="I243" s="5" t="inlineStr">
+      <c r="I243" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B244" s="5" t="inlineStr">
+      <c r="A244" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B244" s="6" t="inlineStr">
         <is>
           <t>A1-E1</t>
         </is>
       </c>
-      <c r="C244" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D244" s="5" t="inlineStr">
+      <c r="C244" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D244" s="6" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="E244" s="5" t="inlineStr">
+      <c r="E244" s="6" t="inlineStr">
         <is>
           <t>23/07/2026</t>
         </is>
       </c>
-      <c r="F244" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G244" s="5" t="inlineStr"/>
-      <c r="H244" s="5" t="inlineStr">
+      <c r="F244" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G244" s="6" t="inlineStr"/>
+      <c r="H244" s="6" t="inlineStr">
         <is>
           <t>0/38</t>
         </is>
       </c>
-      <c r="I244" s="5" t="inlineStr">
+      <c r="I244" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -12666,43 +12666,43 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B250" s="9" t="inlineStr">
+      <c r="A250" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B250" s="5" t="inlineStr">
         <is>
           <t>A1-E2</t>
         </is>
       </c>
-      <c r="C250" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D250" s="9" t="inlineStr">
+      <c r="C250" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D250" s="5" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E250" s="9" t="inlineStr">
+      <c r="E250" s="5" t="inlineStr">
         <is>
           <t>04/06/2026</t>
         </is>
       </c>
-      <c r="F250" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G250" s="9" t="inlineStr"/>
-      <c r="H250" s="9" t="inlineStr">
+      <c r="F250" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G250" s="5" t="inlineStr"/>
+      <c r="H250" s="5" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I250" s="9" t="inlineStr">
+      <c r="I250" s="5" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
@@ -13367,86 +13367,86 @@
       </c>
     </row>
     <row r="265">
-      <c r="A265" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B265" s="9" t="inlineStr">
+      <c r="A265" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B265" s="5" t="inlineStr">
         <is>
           <t>A1-E2</t>
         </is>
       </c>
-      <c r="C265" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D265" s="9" t="inlineStr">
+      <c r="C265" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D265" s="5" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="E265" s="9" t="inlineStr">
+      <c r="E265" s="5" t="inlineStr">
         <is>
           <t>09/07/2026</t>
         </is>
       </c>
-      <c r="F265" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G265" s="9" t="inlineStr"/>
-      <c r="H265" s="9" t="inlineStr">
+      <c r="F265" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G265" s="5" t="inlineStr"/>
+      <c r="H265" s="5" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I265" s="9" t="inlineStr">
+      <c r="I265" s="5" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
       </c>
     </row>
     <row r="266">
-      <c r="A266" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B266" s="9" t="inlineStr">
+      <c r="A266" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B266" s="5" t="inlineStr">
         <is>
           <t>A1-E2</t>
         </is>
       </c>
-      <c r="C266" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D266" s="9" t="inlineStr">
+      <c r="C266" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D266" s="5" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="E266" s="9" t="inlineStr">
+      <c r="E266" s="5" t="inlineStr">
         <is>
           <t>14/07/2026</t>
         </is>
       </c>
-      <c r="F266" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G266" s="9" t="inlineStr"/>
-      <c r="H266" s="9" t="inlineStr">
+      <c r="F266" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G266" s="5" t="inlineStr"/>
+      <c r="H266" s="5" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I266" s="9" t="inlineStr">
+      <c r="I266" s="5" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
@@ -13547,129 +13547,129 @@
       </c>
     </row>
     <row r="269">
-      <c r="A269" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B269" s="5" t="inlineStr">
+      <c r="A269" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B269" s="6" t="inlineStr">
         <is>
           <t>A1-E2</t>
         </is>
       </c>
-      <c r="C269" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D269" s="5" t="inlineStr">
+      <c r="C269" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D269" s="6" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="E269" s="5" t="inlineStr">
+      <c r="E269" s="6" t="inlineStr">
         <is>
           <t>21/07/2026</t>
         </is>
       </c>
-      <c r="F269" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G269" s="5" t="inlineStr"/>
-      <c r="H269" s="5" t="inlineStr">
+      <c r="F269" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G269" s="6" t="inlineStr"/>
+      <c r="H269" s="6" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I269" s="5" t="inlineStr">
+      <c r="I269" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="270">
-      <c r="A270" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B270" s="5" t="inlineStr">
+      <c r="A270" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B270" s="6" t="inlineStr">
         <is>
           <t>A1-E2</t>
         </is>
       </c>
-      <c r="C270" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D270" s="5" t="inlineStr">
+      <c r="C270" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D270" s="6" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="E270" s="5" t="inlineStr">
+      <c r="E270" s="6" t="inlineStr">
         <is>
           <t>22/07/2026</t>
         </is>
       </c>
-      <c r="F270" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G270" s="5" t="inlineStr"/>
-      <c r="H270" s="5" t="inlineStr">
+      <c r="F270" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G270" s="6" t="inlineStr"/>
+      <c r="H270" s="6" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I270" s="5" t="inlineStr">
+      <c r="I270" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="271">
-      <c r="A271" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B271" s="5" t="inlineStr">
+      <c r="A271" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B271" s="6" t="inlineStr">
         <is>
           <t>A1-E2</t>
         </is>
       </c>
-      <c r="C271" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D271" s="5" t="inlineStr">
+      <c r="C271" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D271" s="6" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="E271" s="5" t="inlineStr">
+      <c r="E271" s="6" t="inlineStr">
         <is>
           <t>23/07/2026</t>
         </is>
       </c>
-      <c r="F271" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G271" s="5" t="inlineStr"/>
-      <c r="H271" s="5" t="inlineStr">
+      <c r="F271" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G271" s="6" t="inlineStr"/>
+      <c r="H271" s="6" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I271" s="5" t="inlineStr">
+      <c r="I271" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -13911,43 +13911,43 @@
       </c>
     </row>
     <row r="277">
-      <c r="A277" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B277" s="9" t="inlineStr">
+      <c r="A277" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B277" s="5" t="inlineStr">
         <is>
           <t>A1-F1</t>
         </is>
       </c>
-      <c r="C277" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D277" s="9" t="inlineStr">
+      <c r="C277" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D277" s="5" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E277" s="9" t="inlineStr">
+      <c r="E277" s="5" t="inlineStr">
         <is>
           <t>04/06/2026</t>
         </is>
       </c>
-      <c r="F277" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G277" s="9" t="inlineStr"/>
-      <c r="H277" s="9" t="inlineStr">
+      <c r="F277" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G277" s="5" t="inlineStr"/>
+      <c r="H277" s="5" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I277" s="9" t="inlineStr">
+      <c r="I277" s="5" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
@@ -14659,43 +14659,43 @@
       </c>
     </row>
     <row r="293">
-      <c r="A293" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B293" s="9" t="inlineStr">
+      <c r="A293" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B293" s="5" t="inlineStr">
         <is>
           <t>A1-F1</t>
         </is>
       </c>
-      <c r="C293" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D293" s="9" t="inlineStr">
+      <c r="C293" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D293" s="5" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="E293" s="9" t="inlineStr">
+      <c r="E293" s="5" t="inlineStr">
         <is>
           <t>14/07/2026</t>
         </is>
       </c>
-      <c r="F293" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G293" s="9" t="inlineStr"/>
-      <c r="H293" s="9" t="inlineStr">
+      <c r="F293" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G293" s="5" t="inlineStr"/>
+      <c r="H293" s="5" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I293" s="9" t="inlineStr">
+      <c r="I293" s="5" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
@@ -14796,129 +14796,129 @@
       </c>
     </row>
     <row r="296">
-      <c r="A296" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B296" s="5" t="inlineStr">
+      <c r="A296" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B296" s="6" t="inlineStr">
         <is>
           <t>A1-F1</t>
         </is>
       </c>
-      <c r="C296" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D296" s="5" t="inlineStr">
+      <c r="C296" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D296" s="6" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="E296" s="5" t="inlineStr">
+      <c r="E296" s="6" t="inlineStr">
         <is>
           <t>21/07/2026</t>
         </is>
       </c>
-      <c r="F296" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G296" s="5" t="inlineStr"/>
-      <c r="H296" s="5" t="inlineStr">
+      <c r="F296" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G296" s="6" t="inlineStr"/>
+      <c r="H296" s="6" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I296" s="5" t="inlineStr">
+      <c r="I296" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="297">
-      <c r="A297" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B297" s="5" t="inlineStr">
+      <c r="A297" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B297" s="6" t="inlineStr">
         <is>
           <t>A1-F1</t>
         </is>
       </c>
-      <c r="C297" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D297" s="5" t="inlineStr">
+      <c r="C297" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D297" s="6" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="E297" s="5" t="inlineStr">
+      <c r="E297" s="6" t="inlineStr">
         <is>
           <t>22/07/2026</t>
         </is>
       </c>
-      <c r="F297" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G297" s="5" t="inlineStr"/>
-      <c r="H297" s="5" t="inlineStr">
+      <c r="F297" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G297" s="6" t="inlineStr"/>
+      <c r="H297" s="6" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I297" s="5" t="inlineStr">
+      <c r="I297" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="298">
-      <c r="A298" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B298" s="5" t="inlineStr">
+      <c r="A298" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B298" s="6" t="inlineStr">
         <is>
           <t>A1-F1</t>
         </is>
       </c>
-      <c r="C298" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D298" s="5" t="inlineStr">
+      <c r="C298" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D298" s="6" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="E298" s="5" t="inlineStr">
+      <c r="E298" s="6" t="inlineStr">
         <is>
           <t>23/07/2026</t>
         </is>
       </c>
-      <c r="F298" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G298" s="5" t="inlineStr"/>
-      <c r="H298" s="5" t="inlineStr">
+      <c r="F298" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G298" s="6" t="inlineStr"/>
+      <c r="H298" s="6" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I298" s="5" t="inlineStr">
+      <c r="I298" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -15160,43 +15160,43 @@
       </c>
     </row>
     <row r="304">
-      <c r="A304" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B304" s="9" t="inlineStr">
+      <c r="A304" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B304" s="5" t="inlineStr">
         <is>
           <t>A1-F2</t>
         </is>
       </c>
-      <c r="C304" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D304" s="9" t="inlineStr">
+      <c r="C304" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D304" s="5" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E304" s="9" t="inlineStr">
+      <c r="E304" s="5" t="inlineStr">
         <is>
           <t>04/06/2026</t>
         </is>
       </c>
-      <c r="F304" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G304" s="9" t="inlineStr"/>
-      <c r="H304" s="9" t="inlineStr">
+      <c r="F304" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G304" s="5" t="inlineStr"/>
+      <c r="H304" s="5" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I304" s="9" t="inlineStr">
+      <c r="I304" s="5" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
@@ -15767,43 +15767,43 @@
       </c>
     </row>
     <row r="317">
-      <c r="A317" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B317" s="9" t="inlineStr">
+      <c r="A317" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B317" s="5" t="inlineStr">
         <is>
           <t>A1-F2</t>
         </is>
       </c>
-      <c r="C317" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D317" s="9" t="inlineStr">
+      <c r="C317" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D317" s="5" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="E317" s="9" t="inlineStr">
+      <c r="E317" s="5" t="inlineStr">
         <is>
           <t>07/07/2026</t>
         </is>
       </c>
-      <c r="F317" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G317" s="9" t="inlineStr"/>
-      <c r="H317" s="9" t="inlineStr">
+      <c r="F317" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G317" s="5" t="inlineStr"/>
+      <c r="H317" s="5" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I317" s="9" t="inlineStr">
+      <c r="I317" s="5" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
@@ -15904,43 +15904,43 @@
       </c>
     </row>
     <row r="320">
-      <c r="A320" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B320" s="9" t="inlineStr">
+      <c r="A320" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B320" s="5" t="inlineStr">
         <is>
           <t>A1-F2</t>
         </is>
       </c>
-      <c r="C320" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D320" s="9" t="inlineStr">
+      <c r="C320" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D320" s="5" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="E320" s="9" t="inlineStr">
+      <c r="E320" s="5" t="inlineStr">
         <is>
           <t>14/07/2026</t>
         </is>
       </c>
-      <c r="F320" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G320" s="9" t="inlineStr"/>
-      <c r="H320" s="9" t="inlineStr">
+      <c r="F320" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G320" s="5" t="inlineStr"/>
+      <c r="H320" s="5" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I320" s="9" t="inlineStr">
+      <c r="I320" s="5" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
@@ -16041,129 +16041,129 @@
       </c>
     </row>
     <row r="323">
-      <c r="A323" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B323" s="5" t="inlineStr">
+      <c r="A323" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B323" s="6" t="inlineStr">
         <is>
           <t>A1-F2</t>
         </is>
       </c>
-      <c r="C323" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D323" s="5" t="inlineStr">
+      <c r="C323" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D323" s="6" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="E323" s="5" t="inlineStr">
+      <c r="E323" s="6" t="inlineStr">
         <is>
           <t>21/07/2026</t>
         </is>
       </c>
-      <c r="F323" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G323" s="5" t="inlineStr"/>
-      <c r="H323" s="5" t="inlineStr">
+      <c r="F323" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G323" s="6" t="inlineStr"/>
+      <c r="H323" s="6" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I323" s="5" t="inlineStr">
+      <c r="I323" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="324">
-      <c r="A324" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B324" s="5" t="inlineStr">
+      <c r="A324" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B324" s="6" t="inlineStr">
         <is>
           <t>A1-F2</t>
         </is>
       </c>
-      <c r="C324" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D324" s="5" t="inlineStr">
+      <c r="C324" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D324" s="6" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="E324" s="5" t="inlineStr">
+      <c r="E324" s="6" t="inlineStr">
         <is>
           <t>22/07/2026</t>
         </is>
       </c>
-      <c r="F324" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G324" s="5" t="inlineStr"/>
-      <c r="H324" s="5" t="inlineStr">
+      <c r="F324" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G324" s="6" t="inlineStr"/>
+      <c r="H324" s="6" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I324" s="5" t="inlineStr">
+      <c r="I324" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="325">
-      <c r="A325" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B325" s="5" t="inlineStr">
+      <c r="A325" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B325" s="6" t="inlineStr">
         <is>
           <t>A1-F2</t>
         </is>
       </c>
-      <c r="C325" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D325" s="5" t="inlineStr">
+      <c r="C325" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D325" s="6" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="E325" s="5" t="inlineStr">
+      <c r="E325" s="6" t="inlineStr">
         <is>
           <t>23/07/2026</t>
         </is>
       </c>
-      <c r="F325" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G325" s="5" t="inlineStr"/>
-      <c r="H325" s="5" t="inlineStr">
+      <c r="F325" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G325" s="6" t="inlineStr"/>
+      <c r="H325" s="6" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I325" s="5" t="inlineStr">
+      <c r="I325" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A1_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A1_session_analysis.xlsx
@@ -814,7 +814,7 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>271</v>
+        <v>277</v>
       </c>
     </row>
     <row r="7">
@@ -924,7 +924,7 @@
         </is>
       </c>
       <c r="L8" s="4" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9">
@@ -980,7 +980,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>83.6%</t>
+          <t>85.5%</t>
         </is>
       </c>
     </row>
@@ -1037,7 +1037,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>72.0%</t>
+          <t>71.6%</t>
         </is>
       </c>
     </row>
@@ -1345,10 +1345,10 @@
         <v>24</v>
       </c>
       <c r="P15" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q15" s="4" t="n">
         <v>1</v>
-      </c>
-      <c r="Q15" s="4" t="n">
-        <v>2</v>
       </c>
       <c r="R15" s="4" t="inlineStr">
         <is>
@@ -1427,10 +1427,10 @@
         <v>24</v>
       </c>
       <c r="P16" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q16" s="4" t="n">
         <v>1</v>
-      </c>
-      <c r="Q16" s="4" t="n">
-        <v>2</v>
       </c>
       <c r="R16" s="4" t="inlineStr">
         <is>
@@ -1509,10 +1509,10 @@
         <v>24</v>
       </c>
       <c r="P17" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q17" s="4" t="n">
         <v>1</v>
-      </c>
-      <c r="Q17" s="4" t="n">
-        <v>2</v>
       </c>
       <c r="R17" s="4" t="inlineStr">
         <is>
@@ -1591,10 +1591,10 @@
         <v>24</v>
       </c>
       <c r="P18" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q18" s="4" t="n">
         <v>1</v>
-      </c>
-      <c r="Q18" s="4" t="n">
-        <v>2</v>
       </c>
       <c r="R18" s="4" t="inlineStr">
         <is>
@@ -1673,10 +1673,10 @@
         <v>24</v>
       </c>
       <c r="P19" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q19" s="4" t="n">
         <v>1</v>
-      </c>
-      <c r="Q19" s="4" t="n">
-        <v>2</v>
       </c>
       <c r="R19" s="4" t="inlineStr">
         <is>
@@ -1755,10 +1755,10 @@
         <v>24</v>
       </c>
       <c r="P20" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q20" s="4" t="n">
         <v>1</v>
-      </c>
-      <c r="Q20" s="4" t="n">
-        <v>2</v>
       </c>
       <c r="R20" s="4" t="inlineStr">
         <is>
@@ -1834,22 +1834,22 @@
         <v>27</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q21" s="4" t="n">
         <v>3</v>
       </c>
       <c r="R21" s="4" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>81.5%</t>
         </is>
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>71.2%</t>
+          <t>70.1%</t>
         </is>
       </c>
     </row>
@@ -1916,22 +1916,22 @@
         <v>27</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q22" s="4" t="n">
         <v>3</v>
       </c>
       <c r="R22" s="4" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>81.5%</t>
         </is>
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>73.4%</t>
+          <t>72.1%</t>
         </is>
       </c>
     </row>
@@ -1998,22 +1998,22 @@
         <v>27</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q23" s="4" t="n">
         <v>3</v>
       </c>
       <c r="R23" s="4" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>81.5%</t>
         </is>
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>76.6%</t>
         </is>
       </c>
     </row>
@@ -2080,22 +2080,22 @@
         <v>27</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q24" s="4" t="n">
         <v>3</v>
       </c>
       <c r="R24" s="4" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>81.5%</t>
         </is>
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>76.6%</t>
+          <t>76.1%</t>
         </is>
       </c>
     </row>
@@ -2162,22 +2162,22 @@
         <v>27</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q25" s="4" t="n">
         <v>3</v>
       </c>
       <c r="R25" s="4" t="inlineStr">
         <is>
-          <t>81.5%</t>
+          <t>85.2%</t>
         </is>
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>74.7%</t>
+          <t>74.0%</t>
         </is>
       </c>
     </row>
@@ -2240,65 +2240,65 @@
         <v>27</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q26" s="4" t="n">
         <v>3</v>
       </c>
       <c r="R26" s="4" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>81.5%</t>
         </is>
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>72.2%</t>
+          <t>71.9%</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B27" s="6" t="inlineStr">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
         <is>
           <t>A1-A1</t>
         </is>
       </c>
-      <c r="C27" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D27" s="6" t="inlineStr">
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="E27" s="6" t="inlineStr">
+      <c r="E27" s="5" t="inlineStr">
         <is>
           <t>19/07/2026</t>
         </is>
       </c>
-      <c r="F27" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G27" s="6" t="inlineStr"/>
-      <c r="H27" s="6" t="inlineStr">
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="inlineStr"/>
+      <c r="H27" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I27" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I27" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -3582,45 +3582,45 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B54" s="6" t="inlineStr">
+      <c r="A54" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="inlineStr">
         <is>
           <t>A1-A2</t>
         </is>
       </c>
-      <c r="C54" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D54" s="6" t="inlineStr">
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D54" s="5" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="E54" s="6" t="inlineStr">
+      <c r="E54" s="5" t="inlineStr">
         <is>
           <t>19/07/2026</t>
         </is>
       </c>
-      <c r="F54" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G54" s="6" t="inlineStr"/>
-      <c r="H54" s="6" t="inlineStr">
+      <c r="F54" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G54" s="5" t="inlineStr"/>
+      <c r="H54" s="5" t="inlineStr">
         <is>
           <t>0/33</t>
         </is>
       </c>
-      <c r="I54" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I54" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -4839,45 +4839,45 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B81" s="6" t="inlineStr">
+      <c r="A81" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B81" s="5" t="inlineStr">
         <is>
           <t>A1-B1</t>
         </is>
       </c>
-      <c r="C81" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D81" s="6" t="inlineStr">
+      <c r="C81" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D81" s="5" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="E81" s="6" t="inlineStr">
+      <c r="E81" s="5" t="inlineStr">
         <is>
           <t>19/07/2026</t>
         </is>
       </c>
-      <c r="F81" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G81" s="6" t="inlineStr"/>
-      <c r="H81" s="6" t="inlineStr">
+      <c r="F81" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G81" s="5" t="inlineStr"/>
+      <c r="H81" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I81" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I81" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -6096,45 +6096,45 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B108" s="6" t="inlineStr">
+      <c r="A108" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B108" s="5" t="inlineStr">
         <is>
           <t>A1-B2</t>
         </is>
       </c>
-      <c r="C108" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D108" s="6" t="inlineStr">
+      <c r="C108" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D108" s="5" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="E108" s="6" t="inlineStr">
+      <c r="E108" s="5" t="inlineStr">
         <is>
           <t>19/07/2026</t>
         </is>
       </c>
-      <c r="F108" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G108" s="6" t="inlineStr"/>
-      <c r="H108" s="6" t="inlineStr">
+      <c r="F108" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G108" s="5" t="inlineStr"/>
+      <c r="H108" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I108" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I108" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -7353,45 +7353,45 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B135" s="6" t="inlineStr">
+      <c r="A135" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B135" s="5" t="inlineStr">
         <is>
           <t>A1-C1</t>
         </is>
       </c>
-      <c r="C135" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D135" s="6" t="inlineStr">
+      <c r="C135" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D135" s="5" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="E135" s="6" t="inlineStr">
+      <c r="E135" s="5" t="inlineStr">
         <is>
           <t>19/07/2026</t>
         </is>
       </c>
-      <c r="F135" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G135" s="6" t="inlineStr"/>
-      <c r="H135" s="6" t="inlineStr">
+      <c r="F135" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G135" s="5" t="inlineStr"/>
+      <c r="H135" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I135" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I135" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -8610,45 +8610,45 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B162" s="6" t="inlineStr">
+      <c r="A162" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B162" s="5" t="inlineStr">
         <is>
           <t>A1-C2</t>
         </is>
       </c>
-      <c r="C162" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D162" s="6" t="inlineStr">
+      <c r="C162" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D162" s="5" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="E162" s="6" t="inlineStr">
+      <c r="E162" s="5" t="inlineStr">
         <is>
           <t>19/07/2026</t>
         </is>
       </c>
-      <c r="F162" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G162" s="6" t="inlineStr"/>
-      <c r="H162" s="6" t="inlineStr">
+      <c r="F162" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G162" s="5" t="inlineStr"/>
+      <c r="H162" s="5" t="inlineStr">
         <is>
           <t>0/33</t>
         </is>
       </c>
-      <c r="I162" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I162" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -9675,45 +9675,49 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B185" s="5" t="inlineStr">
+      <c r="A185" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B185" s="2" t="inlineStr">
         <is>
           <t>A1-D1</t>
         </is>
       </c>
-      <c r="C185" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D185" s="5" t="inlineStr">
+      <c r="C185" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D185" s="2" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="E185" s="5" t="inlineStr">
+      <c r="E185" s="2" t="inlineStr">
         <is>
           <t>14/07/2026</t>
         </is>
       </c>
-      <c r="F185" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G185" s="5" t="inlineStr"/>
-      <c r="H185" s="5" t="inlineStr">
-        <is>
-          <t>0/35</t>
-        </is>
-      </c>
-      <c r="I185" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F185" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G185" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H185" s="2" t="inlineStr">
+        <is>
+          <t>17/35</t>
+        </is>
+      </c>
+      <c r="I185" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -10920,45 +10924,49 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B212" s="5" t="inlineStr">
+      <c r="A212" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B212" s="2" t="inlineStr">
         <is>
           <t>A1-D2</t>
         </is>
       </c>
-      <c r="C212" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D212" s="5" t="inlineStr">
+      <c r="C212" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D212" s="2" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="E212" s="5" t="inlineStr">
+      <c r="E212" s="2" t="inlineStr">
         <is>
           <t>14/07/2026</t>
         </is>
       </c>
-      <c r="F212" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G212" s="5" t="inlineStr"/>
-      <c r="H212" s="5" t="inlineStr">
-        <is>
-          <t>0/34</t>
-        </is>
-      </c>
-      <c r="I212" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F212" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G212" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H212" s="2" t="inlineStr">
+        <is>
+          <t>15/34</t>
+        </is>
+      </c>
+      <c r="I212" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -12165,45 +12173,49 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B239" s="5" t="inlineStr">
+      <c r="A239" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B239" s="2" t="inlineStr">
         <is>
           <t>A1-E1</t>
         </is>
       </c>
-      <c r="C239" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D239" s="5" t="inlineStr">
+      <c r="C239" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D239" s="2" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="E239" s="5" t="inlineStr">
+      <c r="E239" s="2" t="inlineStr">
         <is>
           <t>14/07/2026</t>
         </is>
       </c>
-      <c r="F239" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G239" s="5" t="inlineStr"/>
-      <c r="H239" s="5" t="inlineStr">
-        <is>
-          <t>0/38</t>
-        </is>
-      </c>
-      <c r="I239" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F239" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G239" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H239" s="2" t="inlineStr">
+        <is>
+          <t>19/38</t>
+        </is>
+      </c>
+      <c r="I239" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -13410,45 +13422,49 @@
       </c>
     </row>
     <row r="266">
-      <c r="A266" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B266" s="5" t="inlineStr">
+      <c r="A266" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B266" s="2" t="inlineStr">
         <is>
           <t>A1-E2</t>
         </is>
       </c>
-      <c r="C266" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D266" s="5" t="inlineStr">
+      <c r="C266" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D266" s="2" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="E266" s="5" t="inlineStr">
+      <c r="E266" s="2" t="inlineStr">
         <is>
           <t>14/07/2026</t>
         </is>
       </c>
-      <c r="F266" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G266" s="5" t="inlineStr"/>
-      <c r="H266" s="5" t="inlineStr">
-        <is>
-          <t>0/39</t>
-        </is>
-      </c>
-      <c r="I266" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F266" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G266" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H266" s="2" t="inlineStr">
+        <is>
+          <t>26/39</t>
+        </is>
+      </c>
+      <c r="I266" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -14659,45 +14675,49 @@
       </c>
     </row>
     <row r="293">
-      <c r="A293" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B293" s="5" t="inlineStr">
+      <c r="A293" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B293" s="2" t="inlineStr">
         <is>
           <t>A1-F1</t>
         </is>
       </c>
-      <c r="C293" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D293" s="5" t="inlineStr">
+      <c r="C293" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D293" s="2" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="E293" s="5" t="inlineStr">
+      <c r="E293" s="2" t="inlineStr">
         <is>
           <t>14/07/2026</t>
         </is>
       </c>
-      <c r="F293" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G293" s="5" t="inlineStr"/>
-      <c r="H293" s="5" t="inlineStr">
-        <is>
-          <t>0/39</t>
-        </is>
-      </c>
-      <c r="I293" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F293" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G293" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H293" s="2" t="inlineStr">
+        <is>
+          <t>23/39</t>
+        </is>
+      </c>
+      <c r="I293" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -15904,45 +15924,49 @@
       </c>
     </row>
     <row r="320">
-      <c r="A320" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B320" s="5" t="inlineStr">
+      <c r="A320" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B320" s="2" t="inlineStr">
         <is>
           <t>A1-F2</t>
         </is>
       </c>
-      <c r="C320" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D320" s="5" t="inlineStr">
+      <c r="C320" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D320" s="2" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="E320" s="5" t="inlineStr">
+      <c r="E320" s="2" t="inlineStr">
         <is>
           <t>14/07/2026</t>
         </is>
       </c>
-      <c r="F320" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G320" s="5" t="inlineStr"/>
-      <c r="H320" s="5" t="inlineStr">
-        <is>
-          <t>0/39</t>
-        </is>
-      </c>
-      <c r="I320" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F320" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G320" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H320" s="2" t="inlineStr">
+        <is>
+          <t>26/39</t>
+        </is>
+      </c>
+      <c r="I320" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A1_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A1_session_analysis.xlsx
@@ -1037,7 +1037,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>71.6%</t>
+          <t>71.8%</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2013,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>76.6%</t>
+          <t>77.3%</t>
         </is>
       </c>
     </row>
@@ -2095,7 +2095,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>76.1%</t>
+          <t>76.8%</t>
         </is>
       </c>
     </row>
@@ -2177,7 +2177,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>74.0%</t>
+          <t>74.7%</t>
         </is>
       </c>
     </row>
@@ -12210,7 +12210,7 @@
       </c>
       <c r="H239" s="2" t="inlineStr">
         <is>
-          <t>19/38</t>
+          <t>25/38</t>
         </is>
       </c>
       <c r="I239" s="2" t="inlineStr">
@@ -13459,7 +13459,7 @@
       </c>
       <c r="H266" s="2" t="inlineStr">
         <is>
-          <t>26/39</t>
+          <t>32/39</t>
         </is>
       </c>
       <c r="I266" s="2" t="inlineStr">
@@ -14712,7 +14712,7 @@
       </c>
       <c r="H293" s="2" t="inlineStr">
         <is>
-          <t>23/39</t>
+          <t>29/39</t>
         </is>
       </c>
       <c r="I293" s="2" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A1_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A1_session_analysis.xlsx
@@ -96,9 +96,6 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -106,6 +103,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8">
@@ -924,7 +924,7 @@
         </is>
       </c>
       <c r="L8" s="4" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9">
@@ -1345,10 +1345,10 @@
         <v>24</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R15" s="4" t="inlineStr">
         <is>
@@ -1427,10 +1427,10 @@
         <v>24</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R16" s="4" t="inlineStr">
         <is>
@@ -1509,10 +1509,10 @@
         <v>24</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R17" s="4" t="inlineStr">
         <is>
@@ -1591,10 +1591,10 @@
         <v>24</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R18" s="4" t="inlineStr">
         <is>
@@ -1673,10 +1673,10 @@
         <v>24</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R19" s="4" t="inlineStr">
         <is>
@@ -1755,10 +1755,10 @@
         <v>24</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R20" s="4" t="inlineStr">
         <is>
@@ -2303,45 +2303,45 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B28" s="6" t="inlineStr">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
         <is>
           <t>A1-A1</t>
         </is>
       </c>
-      <c r="C28" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D28" s="6" t="inlineStr">
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="E28" s="6" t="inlineStr">
+      <c r="E28" s="5" t="inlineStr">
         <is>
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="F28" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G28" s="6" t="inlineStr"/>
-      <c r="H28" s="6" t="inlineStr">
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G28" s="5" t="inlineStr"/>
+      <c r="H28" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I28" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I28" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -2510,7 +2510,7 @@
           <t>Recorded</t>
         </is>
       </c>
-      <c r="L31" s="7" t="inlineStr">
+      <c r="L31" s="6" t="inlineStr">
         <is>
           <t>Green</t>
         </is>
@@ -2572,7 +2572,7 @@
           <t>Not Recorded</t>
         </is>
       </c>
-      <c r="L32" s="8" t="inlineStr">
+      <c r="L32" s="7" t="inlineStr">
         <is>
           <t>Red</t>
         </is>
@@ -2634,7 +2634,7 @@
           <t>Pending</t>
         </is>
       </c>
-      <c r="L33" s="9" t="inlineStr">
+      <c r="L33" s="8" t="inlineStr">
         <is>
           <t>Yellow</t>
         </is>
@@ -3625,45 +3625,45 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B55" s="6" t="inlineStr">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="inlineStr">
         <is>
           <t>A1-A2</t>
         </is>
       </c>
-      <c r="C55" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D55" s="6" t="inlineStr">
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D55" s="5" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="E55" s="6" t="inlineStr">
+      <c r="E55" s="5" t="inlineStr">
         <is>
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="F55" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G55" s="6" t="inlineStr"/>
-      <c r="H55" s="6" t="inlineStr">
+      <c r="F55" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G55" s="5" t="inlineStr"/>
+      <c r="H55" s="5" t="inlineStr">
         <is>
           <t>0/33</t>
         </is>
       </c>
-      <c r="I55" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I55" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -4882,45 +4882,45 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B82" s="6" t="inlineStr">
+      <c r="A82" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B82" s="5" t="inlineStr">
         <is>
           <t>A1-B1</t>
         </is>
       </c>
-      <c r="C82" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D82" s="6" t="inlineStr">
+      <c r="C82" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D82" s="5" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="E82" s="6" t="inlineStr">
+      <c r="E82" s="5" t="inlineStr">
         <is>
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="F82" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G82" s="6" t="inlineStr"/>
-      <c r="H82" s="6" t="inlineStr">
+      <c r="F82" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G82" s="5" t="inlineStr"/>
+      <c r="H82" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I82" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I82" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -6139,45 +6139,45 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B109" s="6" t="inlineStr">
+      <c r="A109" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B109" s="5" t="inlineStr">
         <is>
           <t>A1-B2</t>
         </is>
       </c>
-      <c r="C109" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D109" s="6" t="inlineStr">
+      <c r="C109" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D109" s="5" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="E109" s="6" t="inlineStr">
+      <c r="E109" s="5" t="inlineStr">
         <is>
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="F109" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G109" s="6" t="inlineStr"/>
-      <c r="H109" s="6" t="inlineStr">
+      <c r="F109" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G109" s="5" t="inlineStr"/>
+      <c r="H109" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I109" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I109" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -7396,45 +7396,45 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B136" s="6" t="inlineStr">
+      <c r="A136" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B136" s="5" t="inlineStr">
         <is>
           <t>A1-C1</t>
         </is>
       </c>
-      <c r="C136" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D136" s="6" t="inlineStr">
+      <c r="C136" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D136" s="5" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="E136" s="6" t="inlineStr">
+      <c r="E136" s="5" t="inlineStr">
         <is>
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="F136" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G136" s="6" t="inlineStr"/>
-      <c r="H136" s="6" t="inlineStr">
+      <c r="F136" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G136" s="5" t="inlineStr"/>
+      <c r="H136" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I136" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I136" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -8653,45 +8653,45 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B163" s="6" t="inlineStr">
+      <c r="A163" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B163" s="5" t="inlineStr">
         <is>
           <t>A1-C2</t>
         </is>
       </c>
-      <c r="C163" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D163" s="6" t="inlineStr">
+      <c r="C163" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D163" s="5" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="E163" s="6" t="inlineStr">
+      <c r="E163" s="5" t="inlineStr">
         <is>
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="F163" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G163" s="6" t="inlineStr"/>
-      <c r="H163" s="6" t="inlineStr">
+      <c r="F163" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G163" s="5" t="inlineStr"/>
+      <c r="H163" s="5" t="inlineStr">
         <is>
           <t>0/33</t>
         </is>
       </c>
-      <c r="I163" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I163" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -9816,129 +9816,129 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B188" s="6" t="inlineStr">
+      <c r="A188" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B188" s="9" t="inlineStr">
         <is>
           <t>A1-D1</t>
         </is>
       </c>
-      <c r="C188" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D188" s="6" t="inlineStr">
+      <c r="C188" s="9" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D188" s="9" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="E188" s="6" t="inlineStr">
+      <c r="E188" s="9" t="inlineStr">
         <is>
           <t>21/07/2026</t>
         </is>
       </c>
-      <c r="F188" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G188" s="6" t="inlineStr"/>
-      <c r="H188" s="6" t="inlineStr">
+      <c r="F188" s="9" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G188" s="9" t="inlineStr"/>
+      <c r="H188" s="9" t="inlineStr">
         <is>
           <t>0/35</t>
         </is>
       </c>
-      <c r="I188" s="6" t="inlineStr">
+      <c r="I188" s="9" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B189" s="6" t="inlineStr">
+      <c r="A189" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B189" s="9" t="inlineStr">
         <is>
           <t>A1-D1</t>
         </is>
       </c>
-      <c r="C189" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D189" s="6" t="inlineStr">
+      <c r="C189" s="9" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D189" s="9" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="E189" s="6" t="inlineStr">
+      <c r="E189" s="9" t="inlineStr">
         <is>
           <t>22/07/2026</t>
         </is>
       </c>
-      <c r="F189" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G189" s="6" t="inlineStr"/>
-      <c r="H189" s="6" t="inlineStr">
+      <c r="F189" s="9" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G189" s="9" t="inlineStr"/>
+      <c r="H189" s="9" t="inlineStr">
         <is>
           <t>0/35</t>
         </is>
       </c>
-      <c r="I189" s="6" t="inlineStr">
+      <c r="I189" s="9" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B190" s="6" t="inlineStr">
+      <c r="A190" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B190" s="9" t="inlineStr">
         <is>
           <t>A1-D1</t>
         </is>
       </c>
-      <c r="C190" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D190" s="6" t="inlineStr">
+      <c r="C190" s="9" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D190" s="9" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="E190" s="6" t="inlineStr">
+      <c r="E190" s="9" t="inlineStr">
         <is>
           <t>23/07/2026</t>
         </is>
       </c>
-      <c r="F190" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G190" s="6" t="inlineStr"/>
-      <c r="H190" s="6" t="inlineStr">
+      <c r="F190" s="9" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G190" s="9" t="inlineStr"/>
+      <c r="H190" s="9" t="inlineStr">
         <is>
           <t>0/35</t>
         </is>
       </c>
-      <c r="I190" s="6" t="inlineStr">
+      <c r="I190" s="9" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -11065,129 +11065,129 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B215" s="6" t="inlineStr">
+      <c r="A215" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B215" s="9" t="inlineStr">
         <is>
           <t>A1-D2</t>
         </is>
       </c>
-      <c r="C215" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D215" s="6" t="inlineStr">
+      <c r="C215" s="9" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D215" s="9" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="E215" s="6" t="inlineStr">
+      <c r="E215" s="9" t="inlineStr">
         <is>
           <t>21/07/2026</t>
         </is>
       </c>
-      <c r="F215" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G215" s="6" t="inlineStr"/>
-      <c r="H215" s="6" t="inlineStr">
+      <c r="F215" s="9" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G215" s="9" t="inlineStr"/>
+      <c r="H215" s="9" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I215" s="6" t="inlineStr">
+      <c r="I215" s="9" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B216" s="6" t="inlineStr">
+      <c r="A216" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B216" s="9" t="inlineStr">
         <is>
           <t>A1-D2</t>
         </is>
       </c>
-      <c r="C216" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D216" s="6" t="inlineStr">
+      <c r="C216" s="9" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D216" s="9" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="E216" s="6" t="inlineStr">
+      <c r="E216" s="9" t="inlineStr">
         <is>
           <t>22/07/2026</t>
         </is>
       </c>
-      <c r="F216" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G216" s="6" t="inlineStr"/>
-      <c r="H216" s="6" t="inlineStr">
+      <c r="F216" s="9" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G216" s="9" t="inlineStr"/>
+      <c r="H216" s="9" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I216" s="6" t="inlineStr">
+      <c r="I216" s="9" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B217" s="6" t="inlineStr">
+      <c r="A217" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B217" s="9" t="inlineStr">
         <is>
           <t>A1-D2</t>
         </is>
       </c>
-      <c r="C217" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D217" s="6" t="inlineStr">
+      <c r="C217" s="9" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D217" s="9" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="E217" s="6" t="inlineStr">
+      <c r="E217" s="9" t="inlineStr">
         <is>
           <t>23/07/2026</t>
         </is>
       </c>
-      <c r="F217" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G217" s="6" t="inlineStr"/>
-      <c r="H217" s="6" t="inlineStr">
+      <c r="F217" s="9" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G217" s="9" t="inlineStr"/>
+      <c r="H217" s="9" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I217" s="6" t="inlineStr">
+      <c r="I217" s="9" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -12314,129 +12314,129 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B242" s="6" t="inlineStr">
+      <c r="A242" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B242" s="9" t="inlineStr">
         <is>
           <t>A1-E1</t>
         </is>
       </c>
-      <c r="C242" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D242" s="6" t="inlineStr">
+      <c r="C242" s="9" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D242" s="9" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="E242" s="6" t="inlineStr">
+      <c r="E242" s="9" t="inlineStr">
         <is>
           <t>21/07/2026</t>
         </is>
       </c>
-      <c r="F242" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G242" s="6" t="inlineStr"/>
-      <c r="H242" s="6" t="inlineStr">
+      <c r="F242" s="9" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G242" s="9" t="inlineStr"/>
+      <c r="H242" s="9" t="inlineStr">
         <is>
           <t>0/38</t>
         </is>
       </c>
-      <c r="I242" s="6" t="inlineStr">
+      <c r="I242" s="9" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B243" s="6" t="inlineStr">
+      <c r="A243" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B243" s="9" t="inlineStr">
         <is>
           <t>A1-E1</t>
         </is>
       </c>
-      <c r="C243" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D243" s="6" t="inlineStr">
+      <c r="C243" s="9" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D243" s="9" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="E243" s="6" t="inlineStr">
+      <c r="E243" s="9" t="inlineStr">
         <is>
           <t>22/07/2026</t>
         </is>
       </c>
-      <c r="F243" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G243" s="6" t="inlineStr"/>
-      <c r="H243" s="6" t="inlineStr">
+      <c r="F243" s="9" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G243" s="9" t="inlineStr"/>
+      <c r="H243" s="9" t="inlineStr">
         <is>
           <t>0/38</t>
         </is>
       </c>
-      <c r="I243" s="6" t="inlineStr">
+      <c r="I243" s="9" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B244" s="6" t="inlineStr">
+      <c r="A244" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B244" s="9" t="inlineStr">
         <is>
           <t>A1-E1</t>
         </is>
       </c>
-      <c r="C244" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D244" s="6" t="inlineStr">
+      <c r="C244" s="9" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D244" s="9" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="E244" s="6" t="inlineStr">
+      <c r="E244" s="9" t="inlineStr">
         <is>
           <t>23/07/2026</t>
         </is>
       </c>
-      <c r="F244" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G244" s="6" t="inlineStr"/>
-      <c r="H244" s="6" t="inlineStr">
+      <c r="F244" s="9" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G244" s="9" t="inlineStr"/>
+      <c r="H244" s="9" t="inlineStr">
         <is>
           <t>0/38</t>
         </is>
       </c>
-      <c r="I244" s="6" t="inlineStr">
+      <c r="I244" s="9" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -13563,129 +13563,129 @@
       </c>
     </row>
     <row r="269">
-      <c r="A269" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B269" s="6" t="inlineStr">
+      <c r="A269" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B269" s="9" t="inlineStr">
         <is>
           <t>A1-E2</t>
         </is>
       </c>
-      <c r="C269" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D269" s="6" t="inlineStr">
+      <c r="C269" s="9" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D269" s="9" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="E269" s="6" t="inlineStr">
+      <c r="E269" s="9" t="inlineStr">
         <is>
           <t>21/07/2026</t>
         </is>
       </c>
-      <c r="F269" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G269" s="6" t="inlineStr"/>
-      <c r="H269" s="6" t="inlineStr">
+      <c r="F269" s="9" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G269" s="9" t="inlineStr"/>
+      <c r="H269" s="9" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I269" s="6" t="inlineStr">
+      <c r="I269" s="9" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="270">
-      <c r="A270" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B270" s="6" t="inlineStr">
+      <c r="A270" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B270" s="9" t="inlineStr">
         <is>
           <t>A1-E2</t>
         </is>
       </c>
-      <c r="C270" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D270" s="6" t="inlineStr">
+      <c r="C270" s="9" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D270" s="9" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="E270" s="6" t="inlineStr">
+      <c r="E270" s="9" t="inlineStr">
         <is>
           <t>22/07/2026</t>
         </is>
       </c>
-      <c r="F270" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G270" s="6" t="inlineStr"/>
-      <c r="H270" s="6" t="inlineStr">
+      <c r="F270" s="9" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G270" s="9" t="inlineStr"/>
+      <c r="H270" s="9" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I270" s="6" t="inlineStr">
+      <c r="I270" s="9" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="271">
-      <c r="A271" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B271" s="6" t="inlineStr">
+      <c r="A271" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B271" s="9" t="inlineStr">
         <is>
           <t>A1-E2</t>
         </is>
       </c>
-      <c r="C271" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D271" s="6" t="inlineStr">
+      <c r="C271" s="9" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D271" s="9" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="E271" s="6" t="inlineStr">
+      <c r="E271" s="9" t="inlineStr">
         <is>
           <t>23/07/2026</t>
         </is>
       </c>
-      <c r="F271" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G271" s="6" t="inlineStr"/>
-      <c r="H271" s="6" t="inlineStr">
+      <c r="F271" s="9" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G271" s="9" t="inlineStr"/>
+      <c r="H271" s="9" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I271" s="6" t="inlineStr">
+      <c r="I271" s="9" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -14816,129 +14816,129 @@
       </c>
     </row>
     <row r="296">
-      <c r="A296" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B296" s="6" t="inlineStr">
+      <c r="A296" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B296" s="9" t="inlineStr">
         <is>
           <t>A1-F1</t>
         </is>
       </c>
-      <c r="C296" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D296" s="6" t="inlineStr">
+      <c r="C296" s="9" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D296" s="9" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="E296" s="6" t="inlineStr">
+      <c r="E296" s="9" t="inlineStr">
         <is>
           <t>21/07/2026</t>
         </is>
       </c>
-      <c r="F296" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G296" s="6" t="inlineStr"/>
-      <c r="H296" s="6" t="inlineStr">
+      <c r="F296" s="9" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G296" s="9" t="inlineStr"/>
+      <c r="H296" s="9" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I296" s="6" t="inlineStr">
+      <c r="I296" s="9" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="297">
-      <c r="A297" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B297" s="6" t="inlineStr">
+      <c r="A297" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B297" s="9" t="inlineStr">
         <is>
           <t>A1-F1</t>
         </is>
       </c>
-      <c r="C297" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D297" s="6" t="inlineStr">
+      <c r="C297" s="9" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D297" s="9" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="E297" s="6" t="inlineStr">
+      <c r="E297" s="9" t="inlineStr">
         <is>
           <t>22/07/2026</t>
         </is>
       </c>
-      <c r="F297" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G297" s="6" t="inlineStr"/>
-      <c r="H297" s="6" t="inlineStr">
+      <c r="F297" s="9" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G297" s="9" t="inlineStr"/>
+      <c r="H297" s="9" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I297" s="6" t="inlineStr">
+      <c r="I297" s="9" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="298">
-      <c r="A298" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B298" s="6" t="inlineStr">
+      <c r="A298" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B298" s="9" t="inlineStr">
         <is>
           <t>A1-F1</t>
         </is>
       </c>
-      <c r="C298" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D298" s="6" t="inlineStr">
+      <c r="C298" s="9" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D298" s="9" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="E298" s="6" t="inlineStr">
+      <c r="E298" s="9" t="inlineStr">
         <is>
           <t>23/07/2026</t>
         </is>
       </c>
-      <c r="F298" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G298" s="6" t="inlineStr"/>
-      <c r="H298" s="6" t="inlineStr">
+      <c r="F298" s="9" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G298" s="9" t="inlineStr"/>
+      <c r="H298" s="9" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I298" s="6" t="inlineStr">
+      <c r="I298" s="9" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -16065,129 +16065,129 @@
       </c>
     </row>
     <row r="323">
-      <c r="A323" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B323" s="6" t="inlineStr">
+      <c r="A323" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B323" s="9" t="inlineStr">
         <is>
           <t>A1-F2</t>
         </is>
       </c>
-      <c r="C323" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D323" s="6" t="inlineStr">
+      <c r="C323" s="9" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D323" s="9" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="E323" s="6" t="inlineStr">
+      <c r="E323" s="9" t="inlineStr">
         <is>
           <t>21/07/2026</t>
         </is>
       </c>
-      <c r="F323" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G323" s="6" t="inlineStr"/>
-      <c r="H323" s="6" t="inlineStr">
+      <c r="F323" s="9" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G323" s="9" t="inlineStr"/>
+      <c r="H323" s="9" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I323" s="6" t="inlineStr">
+      <c r="I323" s="9" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="324">
-      <c r="A324" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B324" s="6" t="inlineStr">
+      <c r="A324" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B324" s="9" t="inlineStr">
         <is>
           <t>A1-F2</t>
         </is>
       </c>
-      <c r="C324" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D324" s="6" t="inlineStr">
+      <c r="C324" s="9" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D324" s="9" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="E324" s="6" t="inlineStr">
+      <c r="E324" s="9" t="inlineStr">
         <is>
           <t>22/07/2026</t>
         </is>
       </c>
-      <c r="F324" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G324" s="6" t="inlineStr"/>
-      <c r="H324" s="6" t="inlineStr">
+      <c r="F324" s="9" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G324" s="9" t="inlineStr"/>
+      <c r="H324" s="9" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I324" s="6" t="inlineStr">
+      <c r="I324" s="9" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="325">
-      <c r="A325" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B325" s="6" t="inlineStr">
+      <c r="A325" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B325" s="9" t="inlineStr">
         <is>
           <t>A1-F2</t>
         </is>
       </c>
-      <c r="C325" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D325" s="6" t="inlineStr">
+      <c r="C325" s="9" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D325" s="9" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="E325" s="6" t="inlineStr">
+      <c r="E325" s="9" t="inlineStr">
         <is>
           <t>23/07/2026</t>
         </is>
       </c>
-      <c r="F325" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G325" s="6" t="inlineStr"/>
-      <c r="H325" s="6" t="inlineStr">
+      <c r="F325" s="9" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G325" s="9" t="inlineStr"/>
+      <c r="H325" s="9" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I325" s="6" t="inlineStr">
+      <c r="I325" s="9" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A1_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A1_session_analysis.xlsx
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8">
@@ -924,7 +924,7 @@
         </is>
       </c>
       <c r="L8" s="4" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9">
@@ -1837,10 +1837,10 @@
         <v>22</v>
       </c>
       <c r="P21" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q21" s="4" t="n">
         <v>2</v>
-      </c>
-      <c r="Q21" s="4" t="n">
-        <v>3</v>
       </c>
       <c r="R21" s="4" t="inlineStr">
         <is>
@@ -1919,10 +1919,10 @@
         <v>22</v>
       </c>
       <c r="P22" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q22" s="4" t="n">
         <v>2</v>
-      </c>
-      <c r="Q22" s="4" t="n">
-        <v>3</v>
       </c>
       <c r="R22" s="4" t="inlineStr">
         <is>
@@ -2001,10 +2001,10 @@
         <v>22</v>
       </c>
       <c r="P23" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q23" s="4" t="n">
         <v>2</v>
-      </c>
-      <c r="Q23" s="4" t="n">
-        <v>3</v>
       </c>
       <c r="R23" s="4" t="inlineStr">
         <is>
@@ -2083,10 +2083,10 @@
         <v>22</v>
       </c>
       <c r="P24" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q24" s="4" t="n">
         <v>2</v>
-      </c>
-      <c r="Q24" s="4" t="n">
-        <v>3</v>
       </c>
       <c r="R24" s="4" t="inlineStr">
         <is>
@@ -2165,10 +2165,10 @@
         <v>23</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R25" s="4" t="inlineStr">
         <is>
@@ -2243,10 +2243,10 @@
         <v>22</v>
       </c>
       <c r="P26" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q26" s="4" t="n">
         <v>2</v>
-      </c>
-      <c r="Q26" s="4" t="n">
-        <v>3</v>
       </c>
       <c r="R26" s="4" t="inlineStr">
         <is>
@@ -9816,45 +9816,45 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B188" s="9" t="inlineStr">
+      <c r="A188" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B188" s="5" t="inlineStr">
         <is>
           <t>A1-D1</t>
         </is>
       </c>
-      <c r="C188" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D188" s="9" t="inlineStr">
+      <c r="C188" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D188" s="5" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="E188" s="9" t="inlineStr">
+      <c r="E188" s="5" t="inlineStr">
         <is>
           <t>21/07/2026</t>
         </is>
       </c>
-      <c r="F188" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G188" s="9" t="inlineStr"/>
-      <c r="H188" s="9" t="inlineStr">
+      <c r="F188" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G188" s="5" t="inlineStr"/>
+      <c r="H188" s="5" t="inlineStr">
         <is>
           <t>0/35</t>
         </is>
       </c>
-      <c r="I188" s="9" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I188" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -11065,45 +11065,45 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B215" s="9" t="inlineStr">
+      <c r="A215" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B215" s="5" t="inlineStr">
         <is>
           <t>A1-D2</t>
         </is>
       </c>
-      <c r="C215" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D215" s="9" t="inlineStr">
+      <c r="C215" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D215" s="5" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="E215" s="9" t="inlineStr">
+      <c r="E215" s="5" t="inlineStr">
         <is>
           <t>21/07/2026</t>
         </is>
       </c>
-      <c r="F215" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G215" s="9" t="inlineStr"/>
-      <c r="H215" s="9" t="inlineStr">
+      <c r="F215" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G215" s="5" t="inlineStr"/>
+      <c r="H215" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I215" s="9" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I215" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -12314,45 +12314,45 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B242" s="9" t="inlineStr">
+      <c r="A242" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B242" s="5" t="inlineStr">
         <is>
           <t>A1-E1</t>
         </is>
       </c>
-      <c r="C242" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D242" s="9" t="inlineStr">
+      <c r="C242" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D242" s="5" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="E242" s="9" t="inlineStr">
+      <c r="E242" s="5" t="inlineStr">
         <is>
           <t>21/07/2026</t>
         </is>
       </c>
-      <c r="F242" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G242" s="9" t="inlineStr"/>
-      <c r="H242" s="9" t="inlineStr">
+      <c r="F242" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G242" s="5" t="inlineStr"/>
+      <c r="H242" s="5" t="inlineStr">
         <is>
           <t>0/38</t>
         </is>
       </c>
-      <c r="I242" s="9" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I242" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -13563,45 +13563,45 @@
       </c>
     </row>
     <row r="269">
-      <c r="A269" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B269" s="9" t="inlineStr">
+      <c r="A269" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B269" s="5" t="inlineStr">
         <is>
           <t>A1-E2</t>
         </is>
       </c>
-      <c r="C269" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D269" s="9" t="inlineStr">
+      <c r="C269" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D269" s="5" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="E269" s="9" t="inlineStr">
+      <c r="E269" s="5" t="inlineStr">
         <is>
           <t>21/07/2026</t>
         </is>
       </c>
-      <c r="F269" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G269" s="9" t="inlineStr"/>
-      <c r="H269" s="9" t="inlineStr">
+      <c r="F269" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G269" s="5" t="inlineStr"/>
+      <c r="H269" s="5" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I269" s="9" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I269" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -14816,45 +14816,45 @@
       </c>
     </row>
     <row r="296">
-      <c r="A296" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B296" s="9" t="inlineStr">
+      <c r="A296" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B296" s="5" t="inlineStr">
         <is>
           <t>A1-F1</t>
         </is>
       </c>
-      <c r="C296" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D296" s="9" t="inlineStr">
+      <c r="C296" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D296" s="5" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="E296" s="9" t="inlineStr">
+      <c r="E296" s="5" t="inlineStr">
         <is>
           <t>21/07/2026</t>
         </is>
       </c>
-      <c r="F296" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G296" s="9" t="inlineStr"/>
-      <c r="H296" s="9" t="inlineStr">
+      <c r="F296" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G296" s="5" t="inlineStr"/>
+      <c r="H296" s="5" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I296" s="9" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I296" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -16065,45 +16065,45 @@
       </c>
     </row>
     <row r="323">
-      <c r="A323" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B323" s="9" t="inlineStr">
+      <c r="A323" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B323" s="5" t="inlineStr">
         <is>
           <t>A1-F2</t>
         </is>
       </c>
-      <c r="C323" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D323" s="9" t="inlineStr">
+      <c r="C323" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D323" s="5" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="E323" s="9" t="inlineStr">
+      <c r="E323" s="5" t="inlineStr">
         <is>
           <t>21/07/2026</t>
         </is>
       </c>
-      <c r="F323" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G323" s="9" t="inlineStr"/>
-      <c r="H323" s="9" t="inlineStr">
+      <c r="F323" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G323" s="5" t="inlineStr"/>
+      <c r="H323" s="5" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I323" s="9" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I323" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A1_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A1_session_analysis.xlsx
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8">
@@ -924,7 +924,7 @@
         </is>
       </c>
       <c r="L8" s="4" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
@@ -1837,10 +1837,10 @@
         <v>22</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R21" s="4" t="inlineStr">
         <is>
@@ -1919,10 +1919,10 @@
         <v>22</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R22" s="4" t="inlineStr">
         <is>
@@ -2001,10 +2001,10 @@
         <v>22</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R23" s="4" t="inlineStr">
         <is>
@@ -2083,10 +2083,10 @@
         <v>22</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R24" s="4" t="inlineStr">
         <is>
@@ -2165,10 +2165,10 @@
         <v>23</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R25" s="4" t="inlineStr">
         <is>
@@ -2243,10 +2243,10 @@
         <v>22</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R26" s="4" t="inlineStr">
         <is>
@@ -9859,45 +9859,45 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B189" s="9" t="inlineStr">
+      <c r="A189" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B189" s="5" t="inlineStr">
         <is>
           <t>A1-D1</t>
         </is>
       </c>
-      <c r="C189" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D189" s="9" t="inlineStr">
+      <c r="C189" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D189" s="5" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="E189" s="9" t="inlineStr">
+      <c r="E189" s="5" t="inlineStr">
         <is>
           <t>22/07/2026</t>
         </is>
       </c>
-      <c r="F189" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G189" s="9" t="inlineStr"/>
-      <c r="H189" s="9" t="inlineStr">
+      <c r="F189" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G189" s="5" t="inlineStr"/>
+      <c r="H189" s="5" t="inlineStr">
         <is>
           <t>0/35</t>
         </is>
       </c>
-      <c r="I189" s="9" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I189" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -11108,45 +11108,45 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B216" s="9" t="inlineStr">
+      <c r="A216" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B216" s="5" t="inlineStr">
         <is>
           <t>A1-D2</t>
         </is>
       </c>
-      <c r="C216" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D216" s="9" t="inlineStr">
+      <c r="C216" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D216" s="5" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="E216" s="9" t="inlineStr">
+      <c r="E216" s="5" t="inlineStr">
         <is>
           <t>22/07/2026</t>
         </is>
       </c>
-      <c r="F216" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G216" s="9" t="inlineStr"/>
-      <c r="H216" s="9" t="inlineStr">
+      <c r="F216" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G216" s="5" t="inlineStr"/>
+      <c r="H216" s="5" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I216" s="9" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I216" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -12357,45 +12357,45 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B243" s="9" t="inlineStr">
+      <c r="A243" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B243" s="5" t="inlineStr">
         <is>
           <t>A1-E1</t>
         </is>
       </c>
-      <c r="C243" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D243" s="9" t="inlineStr">
+      <c r="C243" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D243" s="5" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="E243" s="9" t="inlineStr">
+      <c r="E243" s="5" t="inlineStr">
         <is>
           <t>22/07/2026</t>
         </is>
       </c>
-      <c r="F243" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G243" s="9" t="inlineStr"/>
-      <c r="H243" s="9" t="inlineStr">
+      <c r="F243" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G243" s="5" t="inlineStr"/>
+      <c r="H243" s="5" t="inlineStr">
         <is>
           <t>0/38</t>
         </is>
       </c>
-      <c r="I243" s="9" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I243" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -13606,45 +13606,45 @@
       </c>
     </row>
     <row r="270">
-      <c r="A270" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B270" s="9" t="inlineStr">
+      <c r="A270" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B270" s="5" t="inlineStr">
         <is>
           <t>A1-E2</t>
         </is>
       </c>
-      <c r="C270" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D270" s="9" t="inlineStr">
+      <c r="C270" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D270" s="5" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="E270" s="9" t="inlineStr">
+      <c r="E270" s="5" t="inlineStr">
         <is>
           <t>22/07/2026</t>
         </is>
       </c>
-      <c r="F270" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G270" s="9" t="inlineStr"/>
-      <c r="H270" s="9" t="inlineStr">
+      <c r="F270" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G270" s="5" t="inlineStr"/>
+      <c r="H270" s="5" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I270" s="9" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I270" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -14859,45 +14859,45 @@
       </c>
     </row>
     <row r="297">
-      <c r="A297" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B297" s="9" t="inlineStr">
+      <c r="A297" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B297" s="5" t="inlineStr">
         <is>
           <t>A1-F1</t>
         </is>
       </c>
-      <c r="C297" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D297" s="9" t="inlineStr">
+      <c r="C297" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D297" s="5" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="E297" s="9" t="inlineStr">
+      <c r="E297" s="5" t="inlineStr">
         <is>
           <t>22/07/2026</t>
         </is>
       </c>
-      <c r="F297" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G297" s="9" t="inlineStr"/>
-      <c r="H297" s="9" t="inlineStr">
+      <c r="F297" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G297" s="5" t="inlineStr"/>
+      <c r="H297" s="5" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I297" s="9" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I297" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -16108,45 +16108,45 @@
       </c>
     </row>
     <row r="324">
-      <c r="A324" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B324" s="9" t="inlineStr">
+      <c r="A324" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B324" s="5" t="inlineStr">
         <is>
           <t>A1-F2</t>
         </is>
       </c>
-      <c r="C324" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D324" s="9" t="inlineStr">
+      <c r="C324" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D324" s="5" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="E324" s="9" t="inlineStr">
+      <c r="E324" s="5" t="inlineStr">
         <is>
           <t>22/07/2026</t>
         </is>
       </c>
-      <c r="F324" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G324" s="9" t="inlineStr"/>
-      <c r="H324" s="9" t="inlineStr">
+      <c r="F324" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G324" s="5" t="inlineStr"/>
+      <c r="H324" s="5" t="inlineStr">
         <is>
           <t>0/39</t>
         </is>
       </c>
-      <c r="I324" s="9" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I324" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A1_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A1_session_analysis.xlsx
@@ -81,7 +81,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -103,9 +103,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -869,7 +866,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>41</v>
+        <v>47</v>
       </c>
     </row>
     <row r="8">
@@ -924,7 +921,7 @@
         </is>
       </c>
       <c r="L8" s="4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1837,10 +1834,10 @@
         <v>22</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R21" s="4" t="inlineStr">
         <is>
@@ -1919,10 +1916,10 @@
         <v>22</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R22" s="4" t="inlineStr">
         <is>
@@ -2001,10 +1998,10 @@
         <v>22</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R23" s="4" t="inlineStr">
         <is>
@@ -2083,10 +2080,10 @@
         <v>22</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R24" s="4" t="inlineStr">
         <is>
@@ -2165,10 +2162,10 @@
         <v>23</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R25" s="4" t="inlineStr">
         <is>
@@ -2243,10 +2240,10 @@
         <v>22</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R26" s="4" t="inlineStr">
         <is>
@@ -9902,45 +9899,45 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B190" s="9" t="inlineStr">
+      <c r="A190" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B190" s="5" t="inlineStr">
         <is>
           <t>A1-D1</t>
         </is>
       </c>
-      <c r="C190" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D190" s="9" t="inlineStr">
+      <c r="C190" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D190" s="5" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="E190" s="9" t="inlineStr">
+      <c r="E190" s="5" t="inlineStr">
         <is>
           <t>23/07/2026</t>
         </is>
       </c>
-      <c r="F190" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G190" s="9" t="inlineStr"/>
-      <c r="H190" s="9" t="inlineStr">
+      <c r="F190" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G190" s="5" t="inlineStr"/>
+      <c r="H190" s="5" t="inlineStr">
         <is>
           <t>0/35</t>
         </is>
       </c>
-      <c r="I190" s="9" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I190" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -11151,45 +11148,45 @@
       </c>
 